--- a/data/台股_外資雷達.xlsx
+++ b/data/台股_外資雷達.xlsx
@@ -501,7 +501,7 @@
         <v>179988</v>
       </c>
       <c r="E2" t="n">
-        <v>-152172</v>
+        <v>-151947</v>
       </c>
       <c r="F2" t="n">
         <v>45434</v>
@@ -552,7 +552,7 @@
         <v>60410</v>
       </c>
       <c r="E3" t="n">
-        <v>19059</v>
+        <v>20366</v>
       </c>
       <c r="F3" t="n">
         <v>-7765</v>
@@ -603,7 +603,7 @@
         <v>23898</v>
       </c>
       <c r="E4" t="n">
-        <v>24937</v>
+        <v>15412</v>
       </c>
       <c r="F4" t="n">
         <v>18083</v>
@@ -654,7 +654,7 @@
         <v>8699</v>
       </c>
       <c r="E5" t="n">
-        <v>14872</v>
+        <v>15088</v>
       </c>
       <c r="F5" t="n">
         <v>-4791</v>
@@ -705,7 +705,7 @@
         <v>8442</v>
       </c>
       <c r="E6" t="n">
-        <v>174150</v>
+        <v>168890</v>
       </c>
       <c r="F6" t="n">
         <v>-9806</v>
@@ -756,7 +756,7 @@
         <v>6406</v>
       </c>
       <c r="E7" t="n">
-        <v>12048</v>
+        <v>12204</v>
       </c>
       <c r="F7" t="n">
         <v>2179</v>
@@ -807,7 +807,7 @@
         <v>5930</v>
       </c>
       <c r="E8" t="n">
-        <v>5022</v>
+        <v>6460</v>
       </c>
       <c r="F8" t="n">
         <v>-215</v>
@@ -858,7 +858,7 @@
         <v>5793</v>
       </c>
       <c r="E9" t="n">
-        <v>11139</v>
+        <v>10646</v>
       </c>
       <c r="F9" t="n">
         <v>-41</v>
@@ -909,7 +909,7 @@
         <v>4169</v>
       </c>
       <c r="E10" t="n">
-        <v>6562</v>
+        <v>6649</v>
       </c>
       <c r="F10" t="n">
         <v>-2719</v>
@@ -948,7 +948,7 @@
         <v>4165</v>
       </c>
       <c r="E11" t="n">
-        <v>5609</v>
+        <v>5490</v>
       </c>
       <c r="F11" t="n">
         <v>2856</v>
@@ -999,7 +999,7 @@
         <v>3827</v>
       </c>
       <c r="E12" t="n">
-        <v>2440</v>
+        <v>2130</v>
       </c>
       <c r="F12" t="n">
         <v>-473</v>
@@ -1050,7 +1050,7 @@
         <v>3593</v>
       </c>
       <c r="E13" t="n">
-        <v>-8897</v>
+        <v>-8452</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1101,7 +1101,7 @@
         <v>3431</v>
       </c>
       <c r="E14" t="n">
-        <v>-2187</v>
+        <v>-1919</v>
       </c>
       <c r="F14" t="n">
         <v>-83</v>
@@ -1152,7 +1152,7 @@
         <v>3255</v>
       </c>
       <c r="E15" t="n">
-        <v>1813</v>
+        <v>1452</v>
       </c>
       <c r="F15" t="n">
         <v>-943</v>
@@ -1203,7 +1203,7 @@
         <v>2931</v>
       </c>
       <c r="E16" t="n">
-        <v>21004</v>
+        <v>19085</v>
       </c>
       <c r="F16" t="n">
         <v>212</v>
@@ -1254,7 +1254,7 @@
         <v>2575</v>
       </c>
       <c r="E17" t="n">
-        <v>1856</v>
+        <v>1535</v>
       </c>
       <c r="F17" t="n">
         <v>131</v>
@@ -1305,7 +1305,7 @@
         <v>2325</v>
       </c>
       <c r="E18" t="n">
-        <v>-92</v>
+        <v>24</v>
       </c>
       <c r="F18" t="n">
         <v>-103</v>
@@ -1356,7 +1356,7 @@
         <v>2238</v>
       </c>
       <c r="E19" t="n">
-        <v>249</v>
+        <v>-1850</v>
       </c>
       <c r="F19" t="n">
         <v>2457</v>
@@ -1407,7 +1407,7 @@
         <v>2163</v>
       </c>
       <c r="E20" t="n">
-        <v>6907</v>
+        <v>6744</v>
       </c>
       <c r="F20" t="n">
         <v>529</v>
@@ -1458,7 +1458,7 @@
         <v>1920</v>
       </c>
       <c r="E21" t="n">
-        <v>148</v>
+        <v>101</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1509,7 +1509,7 @@
         <v>1863</v>
       </c>
       <c r="E22" t="n">
-        <v>4946</v>
+        <v>4996</v>
       </c>
       <c r="F22" t="n">
         <v>-437</v>
@@ -1560,7 +1560,7 @@
         <v>1642</v>
       </c>
       <c r="E23" t="n">
-        <v>8115</v>
+        <v>8400</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1611,7 +1611,7 @@
         <v>1642</v>
       </c>
       <c r="E24" t="n">
-        <v>2014</v>
+        <v>1826</v>
       </c>
       <c r="F24" t="n">
         <v>2400</v>
@@ -1662,7 +1662,7 @@
         <v>1479</v>
       </c>
       <c r="E25" t="n">
-        <v>-203</v>
+        <v>-46</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1713,7 +1713,7 @@
         <v>1354</v>
       </c>
       <c r="E26" t="n">
-        <v>-2537</v>
+        <v>-4516</v>
       </c>
       <c r="F26" t="n">
         <v>-1560</v>
@@ -1764,7 +1764,7 @@
         <v>1330</v>
       </c>
       <c r="E27" t="n">
-        <v>2512</v>
+        <v>2470</v>
       </c>
       <c r="F27" t="n">
         <v>134</v>
@@ -1815,7 +1815,7 @@
         <v>1229</v>
       </c>
       <c r="E28" t="n">
-        <v>5520</v>
+        <v>5395</v>
       </c>
       <c r="F28" t="n">
         <v>-352</v>
@@ -1866,7 +1866,7 @@
         <v>1151</v>
       </c>
       <c r="E29" t="n">
-        <v>-1625</v>
+        <v>-1457</v>
       </c>
       <c r="F29" t="n">
         <v>-323</v>
@@ -1917,7 +1917,7 @@
         <v>1099</v>
       </c>
       <c r="E30" t="n">
-        <v>746</v>
+        <v>722</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -1968,7 +1968,7 @@
         <v>1096</v>
       </c>
       <c r="E31" t="n">
-        <v>-1506</v>
+        <v>-1478</v>
       </c>
       <c r="F31" t="n">
         <v>263</v>
@@ -2019,7 +2019,7 @@
         <v>980</v>
       </c>
       <c r="E32" t="n">
-        <v>846</v>
+        <v>902</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -2070,7 +2070,7 @@
         <v>955</v>
       </c>
       <c r="E33" t="n">
-        <v>-9138</v>
+        <v>-7790</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -2121,7 +2121,7 @@
         <v>810</v>
       </c>
       <c r="E34" t="n">
-        <v>2063</v>
+        <v>2069</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -2172,7 +2172,7 @@
         <v>805</v>
       </c>
       <c r="E35" t="n">
-        <v>-689</v>
+        <v>-516</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -2223,7 +2223,7 @@
         <v>682</v>
       </c>
       <c r="E36" t="n">
-        <v>-5288</v>
+        <v>-5767</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -2262,7 +2262,7 @@
         <v>600</v>
       </c>
       <c r="E37" t="n">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -2313,7 +2313,7 @@
         <v>585</v>
       </c>
       <c r="E38" t="n">
-        <v>-2397</v>
+        <v>-1861</v>
       </c>
       <c r="F38" t="n">
         <v>728</v>
@@ -2364,7 +2364,7 @@
         <v>575</v>
       </c>
       <c r="E39" t="n">
-        <v>1857</v>
+        <v>1719</v>
       </c>
       <c r="F39" t="n">
         <v>136</v>
@@ -2415,7 +2415,7 @@
         <v>322</v>
       </c>
       <c r="E40" t="n">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -2466,7 +2466,7 @@
         <v>196</v>
       </c>
       <c r="E41" t="n">
-        <v>630</v>
+        <v>750</v>
       </c>
       <c r="F41" t="n">
         <v>-192</v>
@@ -2505,7 +2505,7 @@
         <v>167</v>
       </c>
       <c r="E42" t="n">
-        <v>-956</v>
+        <v>-948</v>
       </c>
       <c r="F42" t="n">
         <v>-23</v>
@@ -2556,7 +2556,7 @@
         <v>112</v>
       </c>
       <c r="E43" t="n">
-        <v>-2175</v>
+        <v>-2073</v>
       </c>
       <c r="F43" t="n">
         <v>1058</v>
@@ -2607,7 +2607,7 @@
         <v>86</v>
       </c>
       <c r="E44" t="n">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -2658,7 +2658,7 @@
         <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>5079</v>
+        <v>4521</v>
       </c>
       <c r="F45" t="n">
         <v>1</v>
@@ -2709,7 +2709,7 @@
         <v>40</v>
       </c>
       <c r="E46" t="n">
-        <v>-564</v>
+        <v>-576</v>
       </c>
       <c r="F46" t="n">
         <v>-508</v>
@@ -2760,7 +2760,7 @@
         <v>4</v>
       </c>
       <c r="E47" t="n">
-        <v>-344</v>
+        <v>-281</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -2811,7 +2811,7 @@
         <v>-37</v>
       </c>
       <c r="E48" t="n">
-        <v>-70</v>
+        <v>-71</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -2862,7 +2862,7 @@
         <v>-156</v>
       </c>
       <c r="E49" t="n">
-        <v>-365</v>
+        <v>-344</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -2913,7 +2913,7 @@
         <v>-233</v>
       </c>
       <c r="E50" t="n">
-        <v>914</v>
+        <v>883</v>
       </c>
       <c r="F50" t="n">
         <v>6</v>
@@ -2964,7 +2964,7 @@
         <v>-248</v>
       </c>
       <c r="E51" t="n">
-        <v>-3404</v>
+        <v>-3440</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -3015,7 +3015,7 @@
         <v>-291</v>
       </c>
       <c r="E52" t="n">
-        <v>-9396</v>
+        <v>-8295</v>
       </c>
       <c r="F52" t="n">
         <v>1106</v>
@@ -3066,7 +3066,7 @@
         <v>-317</v>
       </c>
       <c r="E53" t="n">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="F53" t="n">
         <v>-383</v>
@@ -3117,7 +3117,7 @@
         <v>-334</v>
       </c>
       <c r="E54" t="n">
-        <v>-350</v>
+        <v>-345</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -3168,7 +3168,7 @@
         <v>-372</v>
       </c>
       <c r="E55" t="n">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="F55" t="n">
         <v>-853</v>
@@ -3219,7 +3219,7 @@
         <v>-403</v>
       </c>
       <c r="E56" t="n">
-        <v>1002</v>
+        <v>281</v>
       </c>
       <c r="F56" t="n">
         <v>-5</v>
@@ -3270,7 +3270,7 @@
         <v>-493</v>
       </c>
       <c r="E57" t="n">
-        <v>-405</v>
+        <v>-300</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -3321,7 +3321,7 @@
         <v>-762</v>
       </c>
       <c r="E58" t="n">
-        <v>-1007</v>
+        <v>-1022</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -3372,7 +3372,7 @@
         <v>-880</v>
       </c>
       <c r="E59" t="n">
-        <v>-424</v>
+        <v>-2141</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -3423,7 +3423,7 @@
         <v>-963</v>
       </c>
       <c r="E60" t="n">
-        <v>-1833</v>
+        <v>-2863</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -3474,7 +3474,7 @@
         <v>-1239</v>
       </c>
       <c r="E61" t="n">
-        <v>-1067</v>
+        <v>-930</v>
       </c>
       <c r="F61" t="n">
         <v>35</v>
@@ -3525,7 +3525,7 @@
         <v>-1316</v>
       </c>
       <c r="E62" t="n">
-        <v>-1981</v>
+        <v>-1983</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -3576,7 +3576,7 @@
         <v>-1407</v>
       </c>
       <c r="E63" t="n">
-        <v>-2863</v>
+        <v>-2831</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -3627,7 +3627,7 @@
         <v>-1417</v>
       </c>
       <c r="E64" t="n">
-        <v>-6546</v>
+        <v>-6773</v>
       </c>
       <c r="F64" t="n">
         <v>-15</v>
@@ -3678,7 +3678,7 @@
         <v>-1722</v>
       </c>
       <c r="E65" t="n">
-        <v>-4062</v>
+        <v>-4851</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
         <v>-1733</v>
       </c>
       <c r="E66" t="n">
-        <v>1644</v>
+        <v>1459</v>
       </c>
       <c r="F66" t="n">
         <v>-416</v>
@@ -3780,7 +3780,7 @@
         <v>-1786</v>
       </c>
       <c r="E67" t="n">
-        <v>3920</v>
+        <v>3700</v>
       </c>
       <c r="F67" t="n">
         <v>-4</v>
@@ -3831,7 +3831,7 @@
         <v>-1930</v>
       </c>
       <c r="E68" t="n">
-        <v>719</v>
+        <v>576</v>
       </c>
       <c r="F68" t="n">
         <v>59</v>
@@ -3882,7 +3882,7 @@
         <v>-2025</v>
       </c>
       <c r="E69" t="n">
-        <v>-4034</v>
+        <v>-3641</v>
       </c>
       <c r="F69" t="n">
         <v>2</v>
@@ -3933,7 +3933,7 @@
         <v>-2049</v>
       </c>
       <c r="E70" t="n">
-        <v>-6579</v>
+        <v>-5731</v>
       </c>
       <c r="F70" t="n">
         <v>-1279</v>
@@ -3972,7 +3972,7 @@
         <v>-2104</v>
       </c>
       <c r="E71" t="n">
-        <v>-562</v>
+        <v>-1201</v>
       </c>
       <c r="F71" t="n">
         <v>-6</v>
@@ -4023,7 +4023,7 @@
         <v>-2141</v>
       </c>
       <c r="E72" t="n">
-        <v>-2549</v>
+        <v>-2451</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
         <v>-2470</v>
       </c>
       <c r="E73" t="n">
-        <v>6646</v>
+        <v>6819</v>
       </c>
       <c r="F73" t="n">
         <v>-655</v>
@@ -4125,7 +4125,7 @@
         <v>-2580</v>
       </c>
       <c r="E74" t="n">
-        <v>8730</v>
+        <v>3390</v>
       </c>
       <c r="F74" t="n">
         <v>-4078</v>
@@ -4176,7 +4176,7 @@
         <v>-2928</v>
       </c>
       <c r="E75" t="n">
-        <v>-7370</v>
+        <v>-7836</v>
       </c>
       <c r="F75" t="n">
         <v>-287</v>
@@ -4227,7 +4227,7 @@
         <v>-3918</v>
       </c>
       <c r="E76" t="n">
-        <v>-7418</v>
+        <v>-7848</v>
       </c>
       <c r="F76" t="n">
         <v>729</v>
@@ -4278,7 +4278,7 @@
         <v>-4712</v>
       </c>
       <c r="E77" t="n">
-        <v>-8150</v>
+        <v>-8955</v>
       </c>
       <c r="F77" t="n">
         <v>43</v>
@@ -4329,7 +4329,7 @@
         <v>-4742</v>
       </c>
       <c r="E78" t="n">
-        <v>-6883</v>
+        <v>-7124</v>
       </c>
       <c r="F78" t="n">
         <v>23</v>
@@ -4380,7 +4380,7 @@
         <v>-4753</v>
       </c>
       <c r="E79" t="n">
-        <v>-4717</v>
+        <v>-4643</v>
       </c>
       <c r="F79" t="n">
         <v>533</v>
@@ -4431,7 +4431,7 @@
         <v>-4831</v>
       </c>
       <c r="E80" t="n">
-        <v>-5658</v>
+        <v>-5740</v>
       </c>
       <c r="F80" t="n">
         <v>383</v>
@@ -4482,7 +4482,7 @@
         <v>-5597</v>
       </c>
       <c r="E81" t="n">
-        <v>-3971</v>
+        <v>-2996</v>
       </c>
       <c r="F81" t="n">
         <v>219</v>
@@ -4533,7 +4533,7 @@
         <v>-5692</v>
       </c>
       <c r="E82" t="n">
-        <v>-12351</v>
+        <v>-11413</v>
       </c>
       <c r="F82" t="n">
         <v>4558</v>
@@ -4584,7 +4584,7 @@
         <v>-5809</v>
       </c>
       <c r="E83" t="n">
-        <v>-7631</v>
+        <v>-7848</v>
       </c>
       <c r="F83" t="n">
         <v>-2</v>
@@ -4635,7 +4635,7 @@
         <v>-6031</v>
       </c>
       <c r="E84" t="n">
-        <v>-1953</v>
+        <v>-2996</v>
       </c>
       <c r="F84" t="n">
         <v>1</v>
@@ -4686,7 +4686,7 @@
         <v>-6780</v>
       </c>
       <c r="E85" t="n">
-        <v>-19129</v>
+        <v>-19302</v>
       </c>
       <c r="F85" t="n">
         <v>1</v>
@@ -4737,7 +4737,7 @@
         <v>-6997</v>
       </c>
       <c r="E86" t="n">
-        <v>-11959</v>
+        <v>-11513</v>
       </c>
       <c r="F86" t="n">
         <v>-384</v>
@@ -4788,7 +4788,7 @@
         <v>-8457</v>
       </c>
       <c r="E87" t="n">
-        <v>23455</v>
+        <v>26299</v>
       </c>
       <c r="F87" t="n">
         <v>-942</v>
@@ -4839,7 +4839,7 @@
         <v>-9396</v>
       </c>
       <c r="E88" t="n">
-        <v>-9853</v>
+        <v>-10694</v>
       </c>
       <c r="F88" t="n">
         <v>4410</v>
@@ -4890,7 +4890,7 @@
         <v>-11949</v>
       </c>
       <c r="E89" t="n">
-        <v>143202</v>
+        <v>128433</v>
       </c>
       <c r="F89" t="n">
         <v>19171</v>
@@ -4941,7 +4941,7 @@
         <v>-13156</v>
       </c>
       <c r="E90" t="n">
-        <v>-20583</v>
+        <v>-22845</v>
       </c>
       <c r="F90" t="n">
         <v>-1025</v>
@@ -4992,7 +4992,7 @@
         <v>-13475</v>
       </c>
       <c r="E91" t="n">
-        <v>6416</v>
+        <v>5854</v>
       </c>
       <c r="F91" t="n">
         <v>7042</v>
@@ -5043,7 +5043,7 @@
         <v>-20334</v>
       </c>
       <c r="E92" t="n">
-        <v>-45802</v>
+        <v>-44737</v>
       </c>
       <c r="F92" t="n">
         <v>6847</v>
@@ -5094,7 +5094,7 @@
         <v>-20582</v>
       </c>
       <c r="E93" t="n">
-        <v>-8332</v>
+        <v>-9408</v>
       </c>
       <c r="F93" t="n">
         <v>5503</v>
@@ -5145,7 +5145,7 @@
         <v>-21387</v>
       </c>
       <c r="E94" t="n">
-        <v>-68154</v>
+        <v>-69281</v>
       </c>
       <c r="F94" t="n">
         <v>1573</v>
@@ -5196,7 +5196,7 @@
         <v>-22668</v>
       </c>
       <c r="E95" t="n">
-        <v>-29077</v>
+        <v>-28202</v>
       </c>
       <c r="F95" t="n">
         <v>-2218</v>
@@ -5247,7 +5247,7 @@
         <v>-44624</v>
       </c>
       <c r="E96" t="n">
-        <v>134240</v>
+        <v>136000</v>
       </c>
       <c r="F96" t="n">
         <v>19833</v>
@@ -5298,7 +5298,7 @@
         <v>-45635</v>
       </c>
       <c r="E97" t="n">
-        <v>-100439</v>
+        <v>-105759</v>
       </c>
       <c r="F97" t="n">
         <v>14251</v>
@@ -5349,7 +5349,7 @@
         <v>-55350</v>
       </c>
       <c r="E98" t="n">
-        <v>-74920</v>
+        <v>-71280</v>
       </c>
       <c r="F98" t="n">
         <v>-7860</v>
@@ -5400,7 +5400,7 @@
         <v>-119327</v>
       </c>
       <c r="E99" t="n">
-        <v>-264470</v>
+        <v>-255087</v>
       </c>
       <c r="F99" t="n">
         <v>6486</v>
@@ -5451,7 +5451,7 @@
         <v>-121095</v>
       </c>
       <c r="E100" t="n">
-        <v>-248729</v>
+        <v>-258356</v>
       </c>
       <c r="F100" t="n">
         <v>12696</v>
@@ -5502,7 +5502,7 @@
         <v>-123197</v>
       </c>
       <c r="E101" t="n">
-        <v>-152302</v>
+        <v>-156397</v>
       </c>
       <c r="F101" t="n">
         <v>37937</v>
@@ -5553,7 +5553,7 @@
         <v>-221747</v>
       </c>
       <c r="E102" t="n">
-        <v>523102</v>
+        <v>525726</v>
       </c>
       <c r="F102" t="n">
         <v>2576</v>
@@ -5604,7 +5604,7 @@
         <v>-237629</v>
       </c>
       <c r="E103" t="n">
-        <v>14028</v>
+        <v>3021</v>
       </c>
       <c r="F103" t="n">
         <v>31925</v>
@@ -5655,7 +5655,7 @@
         <v>-250196</v>
       </c>
       <c r="E104" t="n">
-        <v>75319</v>
+        <v>66126</v>
       </c>
       <c r="F104" t="n">
         <v>40239</v>

--- a/data/台股_外資雷達.xlsx
+++ b/data/台股_外資雷達.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="總覽" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="翻轉警報" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,22 +496,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-19295</v>
+        <v>-40077</v>
       </c>
       <c r="D2" t="n">
-        <v>179988</v>
+        <v>190400</v>
       </c>
       <c r="E2" t="n">
-        <v>-151947</v>
+        <v>-159305</v>
       </c>
       <c r="F2" t="n">
-        <v>45434</v>
+        <v>49864</v>
       </c>
       <c r="G2" t="n">
-        <v>16411</v>
+        <v>-7806</v>
       </c>
       <c r="H2" t="n">
-        <v>9800</v>
+        <v>10348</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -546,22 +547,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14184</v>
+        <v>14233</v>
       </c>
       <c r="D3" t="n">
-        <v>60410</v>
+        <v>59160</v>
       </c>
       <c r="E3" t="n">
-        <v>20366</v>
+        <v>20651</v>
       </c>
       <c r="F3" t="n">
-        <v>-7765</v>
+        <v>170</v>
       </c>
       <c r="G3" t="n">
-        <v>-60545</v>
+        <v>-53549</v>
       </c>
       <c r="H3" t="n">
-        <v>3543</v>
+        <v>3630</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -588,31 +589,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-21970</v>
+        <v>6851</v>
       </c>
       <c r="D4" t="n">
-        <v>23898</v>
+        <v>10701</v>
       </c>
       <c r="E4" t="n">
-        <v>15412</v>
+        <v>172066</v>
       </c>
       <c r="F4" t="n">
-        <v>18083</v>
+        <v>-7035</v>
       </c>
       <c r="G4" t="n">
-        <v>20537</v>
+        <v>-30746</v>
       </c>
       <c r="H4" t="n">
-        <v>-252</v>
+        <v>17</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -621,11 +622,11 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -633,7 +634,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5">
@@ -648,26 +649,26 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3268</v>
+        <v>5707</v>
       </c>
       <c r="D5" t="n">
-        <v>8699</v>
+        <v>10549</v>
       </c>
       <c r="E5" t="n">
-        <v>15088</v>
+        <v>17627</v>
       </c>
       <c r="F5" t="n">
-        <v>-4791</v>
+        <v>-7954</v>
       </c>
       <c r="G5" t="n">
-        <v>-6025</v>
+        <v>-8791</v>
       </c>
       <c r="H5" t="n">
-        <v>261</v>
+        <v>310</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>🟢 加碼</t>
+          <t>🚀 大買</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -690,44 +691,44 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2383</v>
+        <v>-36629</v>
       </c>
       <c r="D6" t="n">
-        <v>8442</v>
+        <v>10121</v>
       </c>
       <c r="E6" t="n">
-        <v>168890</v>
+        <v>4527</v>
       </c>
       <c r="F6" t="n">
-        <v>-9806</v>
+        <v>22780</v>
       </c>
       <c r="G6" t="n">
-        <v>-31268</v>
+        <v>25702</v>
       </c>
       <c r="H6" t="n">
-        <v>-271</v>
+        <v>179</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>🟢 加碼</t>
+          <t>🚀 大買</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -735,37 +736,37 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>長榮航太</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5413</v>
+        <v>4955</v>
       </c>
       <c r="D7" t="n">
-        <v>6406</v>
+        <v>7975</v>
       </c>
       <c r="E7" t="n">
-        <v>12204</v>
+        <v>12765</v>
       </c>
       <c r="F7" t="n">
-        <v>2179</v>
+        <v>-52</v>
       </c>
       <c r="G7" t="n">
-        <v>2391</v>
+        <v>-567</v>
       </c>
       <c r="H7" t="n">
-        <v>66</v>
+        <v>533</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -778,45 +779,45 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>原相</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>368</v>
+        <v>3782</v>
       </c>
       <c r="D8" t="n">
-        <v>5930</v>
+        <v>6412</v>
       </c>
       <c r="E8" t="n">
-        <v>6460</v>
+        <v>12064</v>
       </c>
       <c r="F8" t="n">
-        <v>-215</v>
+        <v>2851</v>
       </c>
       <c r="G8" t="n">
-        <v>-4557</v>
+        <v>2968</v>
       </c>
       <c r="H8" t="n">
-        <v>263</v>
+        <v>174</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -825,11 +826,11 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -837,37 +838,37 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2804</v>
+        <v>106</v>
       </c>
       <c r="D9" t="n">
-        <v>5793</v>
+        <v>5705</v>
       </c>
       <c r="E9" t="n">
-        <v>10646</v>
+        <v>6459</v>
       </c>
       <c r="F9" t="n">
-        <v>-41</v>
+        <v>-20</v>
       </c>
       <c r="G9" t="n">
-        <v>-557</v>
+        <v>-4627</v>
       </c>
       <c r="H9" t="n">
-        <v>605</v>
+        <v>265</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -876,15 +877,15 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M9" t="n">
@@ -894,70 +895,82 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>智易</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5080</v>
+        <v>-1949</v>
       </c>
       <c r="D10" t="n">
-        <v>4169</v>
+        <v>3865</v>
       </c>
       <c r="E10" t="n">
-        <v>6649</v>
+        <v>5169</v>
       </c>
       <c r="F10" t="n">
-        <v>-2719</v>
+        <v>2335</v>
       </c>
       <c r="G10" t="n">
-        <v>-5164</v>
+        <v>5520</v>
       </c>
       <c r="H10" t="n">
-        <v>-245</v>
+        <v>-97</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>🟢 加碼</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>78</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>📉 減速</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-925</v>
+        <v>1271</v>
       </c>
       <c r="D11" t="n">
-        <v>4165</v>
+        <v>3446</v>
       </c>
       <c r="E11" t="n">
-        <v>5490</v>
+        <v>2025</v>
       </c>
       <c r="F11" t="n">
-        <v>2856</v>
+        <v>-1151</v>
       </c>
       <c r="G11" t="n">
-        <v>5479</v>
+        <v>-3257</v>
       </c>
       <c r="H11" t="n">
-        <v>-113</v>
+        <v>-137</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -970,45 +983,45 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1015</v>
+        <v>1893</v>
       </c>
       <c r="D12" t="n">
-        <v>3827</v>
+        <v>3309</v>
       </c>
       <c r="E12" t="n">
-        <v>2130</v>
+        <v>-2664</v>
       </c>
       <c r="F12" t="n">
-        <v>-473</v>
+        <v>-2654</v>
       </c>
       <c r="G12" t="n">
-        <v>2317</v>
+        <v>-5881</v>
       </c>
       <c r="H12" t="n">
-        <v>85</v>
+        <v>-6</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1017,11 +1030,11 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1029,37 +1042,37 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>漢科</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-1186</v>
+        <v>994</v>
       </c>
       <c r="D13" t="n">
-        <v>3593</v>
+        <v>3033</v>
       </c>
       <c r="E13" t="n">
-        <v>-8452</v>
+        <v>2037</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="G13" t="n">
-        <v>-10510</v>
+        <v>135</v>
       </c>
       <c r="H13" t="n">
-        <v>-18</v>
+        <v>-3</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1068,19 +1081,19 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="14">
@@ -1095,22 +1108,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1620</v>
+        <v>1774</v>
       </c>
       <c r="D14" t="n">
-        <v>3431</v>
+        <v>3031</v>
       </c>
       <c r="E14" t="n">
-        <v>-1919</v>
+        <v>-1783</v>
       </c>
       <c r="F14" t="n">
-        <v>-83</v>
+        <v>-126</v>
       </c>
       <c r="G14" t="n">
-        <v>16</v>
+        <v>-108</v>
       </c>
       <c r="H14" t="n">
-        <v>-53</v>
+        <v>-27</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1137,31 +1150,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>全友</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1173</v>
+        <v>889</v>
       </c>
       <c r="D15" t="n">
-        <v>3255</v>
+        <v>2992</v>
       </c>
       <c r="E15" t="n">
-        <v>1452</v>
+        <v>8509</v>
       </c>
       <c r="F15" t="n">
-        <v>-943</v>
+        <v>-1</v>
       </c>
       <c r="G15" t="n">
-        <v>-2758</v>
+        <v>-6</v>
       </c>
       <c r="H15" t="n">
-        <v>29</v>
+        <v>-204</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1174,7 +1187,7 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1182,37 +1195,37 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>零壹</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2119</v>
+        <v>682</v>
       </c>
       <c r="D16" t="n">
-        <v>2931</v>
+        <v>2924</v>
       </c>
       <c r="E16" t="n">
-        <v>19085</v>
+        <v>519</v>
       </c>
       <c r="F16" t="n">
-        <v>212</v>
+        <v>-96</v>
       </c>
       <c r="G16" t="n">
-        <v>268</v>
+        <v>-155</v>
       </c>
       <c r="H16" t="n">
-        <v>-25</v>
+        <v>-786</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1221,49 +1234,49 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1602</v>
+        <v>699</v>
       </c>
       <c r="D17" t="n">
-        <v>2575</v>
+        <v>2748</v>
       </c>
       <c r="E17" t="n">
-        <v>1535</v>
+        <v>1831</v>
       </c>
       <c r="F17" t="n">
-        <v>131</v>
+        <v>-698</v>
       </c>
       <c r="G17" t="n">
-        <v>131</v>
+        <v>1996</v>
       </c>
       <c r="H17" t="n">
-        <v>-12</v>
+        <v>52</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1272,49 +1285,49 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>207</v>
+        <v>2362</v>
       </c>
       <c r="D18" t="n">
-        <v>2325</v>
+        <v>2478</v>
       </c>
       <c r="E18" t="n">
-        <v>24</v>
+        <v>19682</v>
       </c>
       <c r="F18" t="n">
-        <v>-103</v>
+        <v>287</v>
       </c>
       <c r="G18" t="n">
-        <v>-161</v>
+        <v>196</v>
       </c>
       <c r="H18" t="n">
-        <v>-805</v>
+        <v>-34</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1323,53 +1336,53 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>97</v>
+        <v>61</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2221</v>
+        <v>-2594</v>
       </c>
       <c r="D19" t="n">
-        <v>2238</v>
+        <v>1934</v>
       </c>
       <c r="E19" t="n">
-        <v>-1850</v>
+        <v>-10036</v>
       </c>
       <c r="F19" t="n">
-        <v>2457</v>
+        <v>2</v>
       </c>
       <c r="G19" t="n">
-        <v>3630</v>
+        <v>-8758</v>
       </c>
       <c r="H19" t="n">
-        <v>-1211</v>
+        <v>-28</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>🟢 加碼</t>
+          <t>🟡 中性</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1378,96 +1391,96 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>5</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>達欣工</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>183</v>
+        <v>-149</v>
       </c>
       <c r="D20" t="n">
-        <v>2163</v>
+        <v>1840</v>
       </c>
       <c r="E20" t="n">
-        <v>6744</v>
+        <v>100</v>
       </c>
       <c r="F20" t="n">
-        <v>529</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>1380</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>-131</v>
+        <v>-367</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>🟢 加碼</t>
+          <t>🟡 中性</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-7</v>
+        <v>84</v>
       </c>
       <c r="D21" t="n">
-        <v>1920</v>
+        <v>1774</v>
       </c>
       <c r="E21" t="n">
-        <v>101</v>
+        <v>4959</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>-445</v>
       </c>
       <c r="G21" t="n">
-        <v>-1</v>
+        <v>-202</v>
       </c>
       <c r="H21" t="n">
-        <v>-363</v>
+        <v>16</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1476,49 +1489,49 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>合機</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>475</v>
+        <v>435</v>
       </c>
       <c r="D22" t="n">
-        <v>1863</v>
+        <v>1733</v>
       </c>
       <c r="E22" t="n">
-        <v>4996</v>
+        <v>903</v>
       </c>
       <c r="F22" t="n">
-        <v>-437</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>-209</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-25</v>
+        <v>118</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1531,96 +1544,84 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>681</v>
+        <v>3415</v>
       </c>
       <c r="D23" t="n">
-        <v>1642</v>
+        <v>1681</v>
       </c>
       <c r="E23" t="n">
-        <v>8400</v>
+        <v>6583</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>-2255</v>
       </c>
       <c r="G23" t="n">
-        <v>-5</v>
+        <v>-5113</v>
       </c>
       <c r="H23" t="n">
-        <v>-192</v>
+        <v>-132</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>75</v>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>🐌 龜速</t>
-        </is>
-      </c>
-      <c r="M23" t="n">
-        <v>1</v>
-      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-1240</v>
+        <v>22</v>
       </c>
       <c r="D24" t="n">
-        <v>1642</v>
+        <v>1579</v>
       </c>
       <c r="E24" t="n">
-        <v>1826</v>
+        <v>6746</v>
       </c>
       <c r="F24" t="n">
-        <v>2400</v>
+        <v>543</v>
       </c>
       <c r="G24" t="n">
-        <v>1723</v>
+        <v>1375</v>
       </c>
       <c r="H24" t="n">
-        <v>-33</v>
+        <v>-115</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1633,45 +1634,45 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>343</v>
+        <v>1297</v>
       </c>
       <c r="D25" t="n">
-        <v>1479</v>
+        <v>1536</v>
       </c>
       <c r="E25" t="n">
-        <v>-46</v>
+        <v>-1407</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>-250</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H25" t="n">
-        <v>331</v>
+        <v>-150</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1684,45 +1685,45 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>880</v>
+        <v>154</v>
       </c>
       <c r="D26" t="n">
-        <v>1354</v>
+        <v>1404</v>
       </c>
       <c r="E26" t="n">
-        <v>-4516</v>
+        <v>-85</v>
       </c>
       <c r="F26" t="n">
-        <v>-1560</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>-4224</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>54</v>
+        <v>322</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1731,19 +1732,19 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="27">
@@ -1758,22 +1759,22 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-177</v>
+        <v>-303</v>
       </c>
       <c r="D27" t="n">
-        <v>1330</v>
+        <v>1300</v>
       </c>
       <c r="E27" t="n">
-        <v>2470</v>
+        <v>2401</v>
       </c>
       <c r="F27" t="n">
-        <v>134</v>
+        <v>69</v>
       </c>
       <c r="G27" t="n">
-        <v>241</v>
+        <v>197</v>
       </c>
       <c r="H27" t="n">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1800,82 +1801,70 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1226</v>
+        <v>-361</v>
       </c>
       <c r="D28" t="n">
-        <v>1229</v>
+        <v>1274</v>
       </c>
       <c r="E28" t="n">
-        <v>5395</v>
+        <v>-5260</v>
       </c>
       <c r="F28" t="n">
-        <v>-352</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>-669</v>
+        <v>-6246</v>
       </c>
       <c r="H28" t="n">
-        <v>-222</v>
+        <v>-91</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K28" t="n">
-        <v>80</v>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>🚀 加速器</t>
-        </is>
-      </c>
-      <c r="M28" t="n">
-        <v>4</v>
-      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1501</v>
+        <v>1220</v>
       </c>
       <c r="D29" t="n">
-        <v>1151</v>
+        <v>1265</v>
       </c>
       <c r="E29" t="n">
-        <v>-1457</v>
+        <v>5079</v>
       </c>
       <c r="F29" t="n">
-        <v>-323</v>
+        <v>200</v>
       </c>
       <c r="G29" t="n">
-        <v>75</v>
+        <v>-497</v>
       </c>
       <c r="H29" t="n">
-        <v>-149</v>
+        <v>42</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1888,45 +1877,45 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>德昌</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>67</v>
+        <v>-2201</v>
       </c>
       <c r="D30" t="n">
-        <v>1099</v>
+        <v>1192</v>
       </c>
       <c r="E30" t="n">
-        <v>722</v>
+        <v>1338</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>3317</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>2488</v>
       </c>
       <c r="H30" t="n">
-        <v>-19</v>
+        <v>-40</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1935,49 +1924,49 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M30" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>德昌</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-296</v>
+        <v>56</v>
       </c>
       <c r="D31" t="n">
         <v>1096</v>
       </c>
       <c r="E31" t="n">
-        <v>-1478</v>
+        <v>754</v>
       </c>
       <c r="F31" t="n">
-        <v>263</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>237</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>18</v>
+        <v>-19</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1986,49 +1975,49 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>🐌 龜速*</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>合機</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>321</v>
+        <v>939</v>
       </c>
       <c r="D32" t="n">
-        <v>980</v>
+        <v>989</v>
       </c>
       <c r="E32" t="n">
-        <v>902</v>
+        <v>-8180</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>2179</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-830</v>
       </c>
       <c r="H32" t="n">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2041,45 +2030,45 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-469</v>
+        <v>-569</v>
       </c>
       <c r="D33" t="n">
-        <v>955</v>
+        <v>963</v>
       </c>
       <c r="E33" t="n">
-        <v>-7790</v>
+        <v>-1528</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>261</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>237</v>
       </c>
       <c r="H33" t="n">
-        <v>-78</v>
+        <v>17</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2092,45 +2081,45 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速*</t>
         </is>
       </c>
       <c r="M33" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-1344</v>
+        <v>273</v>
       </c>
       <c r="D34" t="n">
-        <v>810</v>
+        <v>777</v>
       </c>
       <c r="E34" t="n">
-        <v>2069</v>
+        <v>1863</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>341</v>
       </c>
       <c r="H34" t="n">
-        <v>76</v>
+        <v>-17</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2143,36 +2132,36 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-101</v>
+        <v>-1510</v>
       </c>
       <c r="D35" t="n">
-        <v>805</v>
+        <v>596</v>
       </c>
       <c r="E35" t="n">
-        <v>-516</v>
+        <v>1876</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -2181,7 +2170,7 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0</v>
+        <v>68</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2194,7 +2183,7 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2202,67 +2191,79 @@
         </is>
       </c>
       <c r="M35" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>智冠</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>-1136</v>
+        <v>61</v>
       </c>
       <c r="D36" t="n">
-        <v>682</v>
+        <v>589</v>
       </c>
       <c r="E36" t="n">
-        <v>-5767</v>
+        <v>362</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>-6196</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-165</v>
+        <v>-154</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>80</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>智冠</t>
+          <t>信立</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>102</v>
+        <v>9</v>
       </c>
       <c r="D37" t="n">
-        <v>600</v>
+        <v>556</v>
       </c>
       <c r="E37" t="n">
-        <v>362</v>
+        <v>-490</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -2271,7 +2272,7 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-157</v>
+        <v>-1</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2280,49 +2281,49 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M37" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>881</v>
+        <v>-206</v>
       </c>
       <c r="D38" t="n">
-        <v>585</v>
+        <v>546</v>
       </c>
       <c r="E38" t="n">
-        <v>-1861</v>
+        <v>-7809</v>
       </c>
       <c r="F38" t="n">
-        <v>728</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>6163</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-2219</v>
+        <v>-67</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2331,11 +2332,11 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2343,37 +2344,37 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>151</v>
+        <v>-40</v>
       </c>
       <c r="D39" t="n">
-        <v>575</v>
+        <v>367</v>
       </c>
       <c r="E39" t="n">
-        <v>1719</v>
+        <v>-1992</v>
       </c>
       <c r="F39" t="n">
-        <v>136</v>
+        <v>1303</v>
       </c>
       <c r="G39" t="n">
-        <v>324</v>
+        <v>1281</v>
       </c>
       <c r="H39" t="n">
-        <v>-35</v>
+        <v>-34</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2382,19 +2383,19 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M39" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="40">
@@ -2409,13 +2410,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="D40" t="n">
-        <v>322</v>
+        <v>356</v>
       </c>
       <c r="E40" t="n">
-        <v>496</v>
+        <v>517</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -2460,22 +2461,22 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="D41" t="n">
-        <v>196</v>
+        <v>270</v>
       </c>
       <c r="E41" t="n">
-        <v>750</v>
+        <v>798</v>
       </c>
       <c r="F41" t="n">
-        <v>-192</v>
+        <v>-124</v>
       </c>
       <c r="G41" t="n">
-        <v>-228</v>
+        <v>-180</v>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2490,31 +2491,31 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>8</v>
+        <v>385</v>
       </c>
       <c r="D42" t="n">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E42" t="n">
-        <v>-948</v>
+        <v>-1213</v>
       </c>
       <c r="F42" t="n">
-        <v>-23</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>-32</v>
+        <v>972</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2523,49 +2524,49 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M42" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-107</v>
+        <v>-177</v>
       </c>
       <c r="D43" t="n">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="E43" t="n">
-        <v>-2073</v>
+        <v>-1007</v>
       </c>
       <c r="F43" t="n">
-        <v>1058</v>
+        <v>39</v>
       </c>
       <c r="G43" t="n">
-        <v>1028</v>
+        <v>18</v>
       </c>
       <c r="H43" t="n">
-        <v>-40</v>
+        <v>-32</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2574,49 +2575,49 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M43" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>勝一</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-35</v>
+        <v>-124</v>
       </c>
       <c r="D44" t="n">
-        <v>86</v>
+        <v>130</v>
       </c>
       <c r="E44" t="n">
-        <v>-19</v>
+        <v>4598</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H44" t="n">
-        <v>6</v>
+        <v>-69</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2629,11 +2630,11 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M44" t="n">
@@ -2643,31 +2644,31 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>勝一</t>
+          <t>六方科-KY</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-195</v>
+        <v>7</v>
       </c>
       <c r="D45" t="n">
-        <v>59</v>
+        <v>97</v>
       </c>
       <c r="E45" t="n">
-        <v>4521</v>
+        <v>-2</v>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>-70</v>
+        <v>5</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2680,11 +2681,11 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M45" t="n">
@@ -2703,22 +2704,22 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="D46" t="n">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="E46" t="n">
-        <v>-576</v>
+        <v>-562</v>
       </c>
       <c r="F46" t="n">
-        <v>-508</v>
+        <v>-639</v>
       </c>
       <c r="G46" t="n">
-        <v>-852</v>
+        <v>-1029</v>
       </c>
       <c r="H46" t="n">
-        <v>-126</v>
+        <v>-130</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2754,13 +2755,13 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D47" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="E47" t="n">
-        <v>-281</v>
+        <v>-283</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -2769,7 +2770,7 @@
         <v>-60</v>
       </c>
       <c r="H47" t="n">
-        <v>-4</v>
+        <v>4</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2796,22 +2797,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>方土霖</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D48" t="n">
-        <v>-37</v>
+        <v>3</v>
       </c>
       <c r="E48" t="n">
-        <v>-71</v>
+        <v>-302</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -2820,7 +2821,7 @@
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2829,40 +2830,40 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M48" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>大車隊</t>
+          <t>方土霖</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>-156</v>
+        <v>-16</v>
       </c>
       <c r="E49" t="n">
-        <v>-344</v>
+        <v>-72</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -2871,7 +2872,7 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2884,45 +2885,45 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M49" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>大車隊</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>166</v>
+        <v>15</v>
       </c>
       <c r="D50" t="n">
-        <v>-233</v>
+        <v>-144</v>
       </c>
       <c r="E50" t="n">
-        <v>883</v>
+        <v>-342</v>
       </c>
       <c r="F50" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-44</v>
+        <v>-1</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2931,19 +2932,19 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M50" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="51">
@@ -2958,13 +2959,13 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-44</v>
+        <v>-112</v>
       </c>
       <c r="D51" t="n">
-        <v>-248</v>
+        <v>-267</v>
       </c>
       <c r="E51" t="n">
-        <v>-3440</v>
+        <v>-3499</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -2973,7 +2974,7 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3000,31 +3001,31 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>478</v>
+        <v>-958</v>
       </c>
       <c r="D52" t="n">
-        <v>-291</v>
+        <v>-273</v>
       </c>
       <c r="E52" t="n">
-        <v>-8295</v>
+        <v>-296</v>
       </c>
       <c r="F52" t="n">
-        <v>1106</v>
+        <v>-6</v>
       </c>
       <c r="G52" t="n">
-        <v>-1950</v>
+        <v>17</v>
       </c>
       <c r="H52" t="n">
-        <v>-68</v>
+        <v>-412</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3037,7 +3038,7 @@
         </is>
       </c>
       <c r="K52" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -3045,7 +3046,7 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
@@ -3060,22 +3061,22 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>175</v>
+        <v>263</v>
       </c>
       <c r="D53" t="n">
-        <v>-317</v>
+        <v>-316</v>
       </c>
       <c r="E53" t="n">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="F53" t="n">
-        <v>-383</v>
+        <v>-374</v>
       </c>
       <c r="G53" t="n">
-        <v>170</v>
+        <v>114</v>
       </c>
       <c r="H53" t="n">
-        <v>-34</v>
+        <v>-51</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3111,13 +3112,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-120</v>
+        <v>-88</v>
       </c>
       <c r="D54" t="n">
-        <v>-334</v>
+        <v>-391</v>
       </c>
       <c r="E54" t="n">
-        <v>-345</v>
+        <v>-349</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -3126,7 +3127,7 @@
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3153,31 +3154,31 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>友輝</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>-357</v>
+        <v>153</v>
       </c>
       <c r="D55" t="n">
-        <v>-372</v>
+        <v>-431</v>
       </c>
       <c r="E55" t="n">
-        <v>271</v>
+        <v>900</v>
       </c>
       <c r="F55" t="n">
-        <v>-853</v>
+        <v>6</v>
       </c>
       <c r="G55" t="n">
-        <v>-1213</v>
+        <v>26</v>
       </c>
       <c r="H55" t="n">
-        <v>-160</v>
+        <v>-43</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3186,49 +3187,49 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K55" t="n">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M55" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>億泰</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>677</v>
+        <v>67</v>
       </c>
       <c r="D56" t="n">
-        <v>-403</v>
+        <v>-711</v>
       </c>
       <c r="E56" t="n">
-        <v>281</v>
+        <v>-2507</v>
       </c>
       <c r="F56" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>885</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-11</v>
+        <v>220</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3237,49 +3238,49 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K56" t="n">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M56" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>65</v>
+        <v>387</v>
       </c>
       <c r="D57" t="n">
-        <v>-493</v>
+        <v>-753</v>
       </c>
       <c r="E57" t="n">
-        <v>-300</v>
+        <v>285</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>893</v>
       </c>
       <c r="H57" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3288,11 +3289,11 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K57" t="n">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -3300,37 +3301,37 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-365</v>
+        <v>729</v>
       </c>
       <c r="D58" t="n">
-        <v>-762</v>
+        <v>-811</v>
       </c>
       <c r="E58" t="n">
-        <v>-1022</v>
+        <v>-2548</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>706</v>
       </c>
       <c r="G58" t="n">
-        <v>-1</v>
+        <v>5808</v>
       </c>
       <c r="H58" t="n">
-        <v>19</v>
+        <v>-2051</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3339,49 +3340,49 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K58" t="n">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M58" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>大統益</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>-815</v>
+        <v>-296</v>
       </c>
       <c r="D59" t="n">
-        <v>-880</v>
+        <v>-818</v>
       </c>
       <c r="E59" t="n">
-        <v>-2141</v>
+        <v>-1057</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H59" t="n">
-        <v>762</v>
+        <v>18</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3390,49 +3391,49 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K59" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M59" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>-58</v>
+        <v>2234</v>
       </c>
       <c r="D60" t="n">
-        <v>-963</v>
+        <v>-840</v>
       </c>
       <c r="E60" t="n">
-        <v>-2863</v>
+        <v>689</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="G60" t="n">
-        <v>-102</v>
+        <v>-30</v>
       </c>
       <c r="H60" t="n">
-        <v>14</v>
+        <v>186</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3441,49 +3442,49 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K60" t="n">
-        <v>96</v>
+        <v>32</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M60" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-91</v>
+        <v>-800</v>
       </c>
       <c r="D61" t="n">
-        <v>-1239</v>
+        <v>-929</v>
       </c>
       <c r="E61" t="n">
-        <v>-930</v>
+        <v>-2083</v>
       </c>
       <c r="F61" t="n">
-        <v>35</v>
+        <v>2795</v>
       </c>
       <c r="G61" t="n">
-        <v>1364</v>
+        <v>3804</v>
       </c>
       <c r="H61" t="n">
-        <v>-15</v>
+        <v>-1190</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3496,45 +3497,45 @@
         </is>
       </c>
       <c r="K61" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-450</v>
+        <v>-91</v>
       </c>
       <c r="D62" t="n">
-        <v>-1316</v>
+        <v>-956</v>
       </c>
       <c r="E62" t="n">
-        <v>-1983</v>
+        <v>226</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>-588</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>-1078</v>
       </c>
       <c r="H62" t="n">
-        <v>12</v>
+        <v>-71</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3543,49 +3544,49 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K62" t="n">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M62" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>鑫龍騰</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>248</v>
+        <v>216</v>
       </c>
       <c r="D63" t="n">
-        <v>-1407</v>
+        <v>-1047</v>
       </c>
       <c r="E63" t="n">
-        <v>-2831</v>
+        <v>-840</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>1498</v>
       </c>
       <c r="H63" t="n">
-        <v>-0</v>
+        <v>-42</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3594,11 +3595,11 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K63" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -3606,37 +3607,37 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>377</v>
+        <v>19</v>
       </c>
       <c r="D64" t="n">
-        <v>-1417</v>
+        <v>-1094</v>
       </c>
       <c r="E64" t="n">
-        <v>-6773</v>
+        <v>-2923</v>
       </c>
       <c r="F64" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>74</v>
+        <v>-102</v>
       </c>
       <c r="H64" t="n">
-        <v>-983</v>
+        <v>-43</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3645,40 +3646,40 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K64" t="n">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M64" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>735</v>
+        <v>-1</v>
       </c>
       <c r="D65" t="n">
-        <v>-1722</v>
+        <v>-1162</v>
       </c>
       <c r="E65" t="n">
-        <v>-4851</v>
+        <v>-1964</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -3687,7 +3688,7 @@
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-202</v>
+        <v>12</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3696,49 +3697,49 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K65" t="n">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M65" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>鑫龍騰</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-2006</v>
+        <v>210</v>
       </c>
       <c r="D66" t="n">
-        <v>-1733</v>
+        <v>-1413</v>
       </c>
       <c r="E66" t="n">
-        <v>1459</v>
+        <v>-2838</v>
       </c>
       <c r="F66" t="n">
-        <v>-416</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>928</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>154</v>
+        <v>-0</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3747,49 +3748,49 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K66" t="n">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M66" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-104</v>
+        <v>388</v>
       </c>
       <c r="D67" t="n">
-        <v>-1786</v>
+        <v>-1909</v>
       </c>
       <c r="E67" t="n">
-        <v>3700</v>
+        <v>-7324</v>
       </c>
       <c r="F67" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="G67" t="n">
-        <v>-618</v>
+        <v>76</v>
       </c>
       <c r="H67" t="n">
-        <v>83</v>
+        <v>-1472</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3798,100 +3799,100 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K67" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M67" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1487</v>
+        <v>-1614</v>
       </c>
       <c r="D68" t="n">
-        <v>-1930</v>
+        <v>-2021</v>
       </c>
       <c r="E68" t="n">
-        <v>576</v>
+        <v>1157</v>
       </c>
       <c r="F68" t="n">
-        <v>59</v>
+        <v>-735</v>
       </c>
       <c r="G68" t="n">
-        <v>-43</v>
+        <v>782</v>
       </c>
       <c r="H68" t="n">
-        <v>157</v>
+        <v>239</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>🟡 中性</t>
+          <t>🟠 減碼</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K68" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M68" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-1182</v>
+        <v>-124</v>
       </c>
       <c r="D69" t="n">
-        <v>-2025</v>
+        <v>-2114</v>
       </c>
       <c r="E69" t="n">
-        <v>-3641</v>
+        <v>3369</v>
       </c>
       <c r="F69" t="n">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="G69" t="n">
-        <v>5</v>
+        <v>-360</v>
       </c>
       <c r="H69" t="n">
-        <v>-456</v>
+        <v>297</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3900,19 +3901,19 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K69" t="n">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -3927,22 +3928,22 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>55</v>
+        <v>-295</v>
       </c>
       <c r="D70" t="n">
-        <v>-2049</v>
+        <v>-2560</v>
       </c>
       <c r="E70" t="n">
-        <v>-5731</v>
+        <v>-6156</v>
       </c>
       <c r="F70" t="n">
-        <v>-1279</v>
+        <v>-1573</v>
       </c>
       <c r="G70" t="n">
-        <v>903</v>
+        <v>405</v>
       </c>
       <c r="H70" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3957,31 +3958,31 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>湧德</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-2119</v>
+        <v>1346</v>
       </c>
       <c r="D71" t="n">
-        <v>-2104</v>
+        <v>-2594</v>
       </c>
       <c r="E71" t="n">
-        <v>-1201</v>
+        <v>-4099</v>
       </c>
       <c r="F71" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-633</v>
+        <v>-376</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -3994,45 +3995,45 @@
         </is>
       </c>
       <c r="K71" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M71" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>億泰</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>96</v>
+        <v>-132</v>
       </c>
       <c r="D72" t="n">
-        <v>-2141</v>
+        <v>-2809</v>
       </c>
       <c r="E72" t="n">
-        <v>-2451</v>
+        <v>-7657</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>-580</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>-1239</v>
       </c>
       <c r="H72" t="n">
-        <v>225</v>
+        <v>-62</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -4041,49 +4042,49 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K72" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M72" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>944</v>
+        <v>-3341</v>
       </c>
       <c r="D73" t="n">
-        <v>-2470</v>
+        <v>-3305</v>
       </c>
       <c r="E73" t="n">
-        <v>6819</v>
+        <v>-3057</v>
       </c>
       <c r="F73" t="n">
-        <v>-655</v>
+        <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>-923</v>
+        <v>1</v>
       </c>
       <c r="H73" t="n">
-        <v>-22</v>
+        <v>-1058</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -4092,49 +4093,49 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K73" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M73" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>玉晶光</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>-1442</v>
+        <v>51</v>
       </c>
       <c r="D74" t="n">
-        <v>-2580</v>
+        <v>-3383</v>
       </c>
       <c r="E74" t="n">
-        <v>3390</v>
+        <v>6581</v>
       </c>
       <c r="F74" t="n">
-        <v>-4078</v>
+        <v>-435</v>
       </c>
       <c r="G74" t="n">
-        <v>-9065</v>
+        <v>-892</v>
       </c>
       <c r="H74" t="n">
-        <v>-673</v>
+        <v>-85</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -4143,11 +4144,11 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K74" t="n">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -4155,37 +4156,37 @@
         </is>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>-710</v>
+        <v>-706</v>
       </c>
       <c r="D75" t="n">
-        <v>-2928</v>
+        <v>-3879</v>
       </c>
       <c r="E75" t="n">
-        <v>-7836</v>
+        <v>-19045</v>
       </c>
       <c r="F75" t="n">
-        <v>-287</v>
+        <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>-849</v>
+        <v>284</v>
       </c>
       <c r="H75" t="n">
-        <v>-70</v>
+        <v>-125</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -4194,49 +4195,49 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K75" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M75" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-779</v>
+        <v>-3918</v>
       </c>
       <c r="D76" t="n">
-        <v>-3918</v>
+        <v>-4011</v>
       </c>
       <c r="E76" t="n">
-        <v>-7848</v>
+        <v>2277</v>
       </c>
       <c r="F76" t="n">
-        <v>729</v>
+        <v>-2302</v>
       </c>
       <c r="G76" t="n">
-        <v>-284</v>
+        <v>-8647</v>
       </c>
       <c r="H76" t="n">
-        <v>-168</v>
+        <v>-506</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -4245,49 +4246,49 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K76" t="n">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-1432</v>
+        <v>-339</v>
       </c>
       <c r="D77" t="n">
-        <v>-4712</v>
+        <v>-4549</v>
       </c>
       <c r="E77" t="n">
-        <v>-8955</v>
+        <v>-3553</v>
       </c>
       <c r="F77" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="G77" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="H77" t="n">
-        <v>-27</v>
+        <v>-480</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -4296,49 +4297,49 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K77" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M77" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-2718</v>
+        <v>129</v>
       </c>
       <c r="D78" t="n">
-        <v>-4742</v>
+        <v>-4619</v>
       </c>
       <c r="E78" t="n">
-        <v>-7124</v>
+        <v>-4398</v>
       </c>
       <c r="F78" t="n">
-        <v>23</v>
+        <v>407</v>
       </c>
       <c r="G78" t="n">
-        <v>1394</v>
+        <v>3380</v>
       </c>
       <c r="H78" t="n">
-        <v>-800</v>
+        <v>-418</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -4351,45 +4352,45 @@
         </is>
       </c>
       <c r="K78" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M78" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-159</v>
+        <v>-1599</v>
       </c>
       <c r="D79" t="n">
-        <v>-4753</v>
+        <v>-4637</v>
       </c>
       <c r="E79" t="n">
-        <v>-4643</v>
+        <v>-8760</v>
       </c>
       <c r="F79" t="n">
-        <v>533</v>
+        <v>1683</v>
       </c>
       <c r="G79" t="n">
-        <v>3273</v>
+        <v>622</v>
       </c>
       <c r="H79" t="n">
-        <v>-478</v>
+        <v>-156</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -4398,49 +4399,49 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K79" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M79" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>-1713</v>
+        <v>-804</v>
       </c>
       <c r="D80" t="n">
-        <v>-4831</v>
+        <v>-4808</v>
       </c>
       <c r="E80" t="n">
-        <v>-5740</v>
+        <v>-8693</v>
       </c>
       <c r="F80" t="n">
-        <v>383</v>
+        <v>64</v>
       </c>
       <c r="G80" t="n">
-        <v>1476</v>
+        <v>52</v>
       </c>
       <c r="H80" t="n">
-        <v>-86</v>
+        <v>8</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -4453,7 +4454,7 @@
         </is>
       </c>
       <c r="K80" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -4467,31 +4468,31 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-914</v>
+        <v>-1237</v>
       </c>
       <c r="D81" t="n">
-        <v>-5597</v>
+        <v>-4942</v>
       </c>
       <c r="E81" t="n">
-        <v>-2996</v>
+        <v>-7160</v>
       </c>
       <c r="F81" t="n">
-        <v>219</v>
+        <v>9</v>
       </c>
       <c r="G81" t="n">
-        <v>-91</v>
+        <v>1401</v>
       </c>
       <c r="H81" t="n">
-        <v>-568</v>
+        <v>-638</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4500,11 +4501,11 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K81" t="n">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -4512,37 +4513,37 @@
         </is>
       </c>
       <c r="M81" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-18</v>
+        <v>-1382</v>
       </c>
       <c r="D82" t="n">
-        <v>-5692</v>
+        <v>-5669</v>
       </c>
       <c r="E82" t="n">
-        <v>-11413</v>
+        <v>-5897</v>
       </c>
       <c r="F82" t="n">
-        <v>4558</v>
+        <v>2</v>
       </c>
       <c r="G82" t="n">
-        <v>7049</v>
+        <v>1523</v>
       </c>
       <c r="H82" t="n">
-        <v>20</v>
+        <v>-90</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -4555,7 +4556,7 @@
         </is>
       </c>
       <c r="K82" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -4563,37 +4564,37 @@
         </is>
       </c>
       <c r="M82" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-1847</v>
+        <v>76</v>
       </c>
       <c r="D83" t="n">
-        <v>-5809</v>
+        <v>-6097</v>
       </c>
       <c r="E83" t="n">
-        <v>-7848</v>
+        <v>-2639</v>
       </c>
       <c r="F83" t="n">
-        <v>-2</v>
+        <v>224</v>
       </c>
       <c r="G83" t="n">
-        <v>-9</v>
+        <v>-96</v>
       </c>
       <c r="H83" t="n">
-        <v>-849</v>
+        <v>-587</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -4602,49 +4603,49 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K83" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M83" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-4420</v>
+        <v>-2239</v>
       </c>
       <c r="D84" t="n">
-        <v>-6031</v>
+        <v>-6183</v>
       </c>
       <c r="E84" t="n">
-        <v>-2996</v>
+        <v>-11635</v>
       </c>
       <c r="F84" t="n">
-        <v>1</v>
+        <v>-354</v>
       </c>
       <c r="G84" t="n">
-        <v>1</v>
+        <v>-105</v>
       </c>
       <c r="H84" t="n">
-        <v>-1072</v>
+        <v>-397</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -4653,49 +4654,49 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K84" t="n">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M84" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>-1396</v>
+        <v>-3416</v>
       </c>
       <c r="D85" t="n">
-        <v>-6780</v>
+        <v>-7034</v>
       </c>
       <c r="E85" t="n">
-        <v>-19302</v>
+        <v>-22161</v>
       </c>
       <c r="F85" t="n">
-        <v>1</v>
+        <v>-727</v>
       </c>
       <c r="G85" t="n">
-        <v>284</v>
+        <v>-3229</v>
       </c>
       <c r="H85" t="n">
-        <v>-297</v>
+        <v>-2442</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -4708,45 +4709,45 @@
         </is>
       </c>
       <c r="K85" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M85" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-2482</v>
+        <v>-607</v>
       </c>
       <c r="D86" t="n">
-        <v>-6997</v>
+        <v>-7145</v>
       </c>
       <c r="E86" t="n">
-        <v>-11513</v>
+        <v>-8543</v>
       </c>
       <c r="F86" t="n">
-        <v>-384</v>
+        <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>-84</v>
+        <v>-8</v>
       </c>
       <c r="H86" t="n">
-        <v>-730</v>
+        <v>-1352</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -4755,15 +4756,15 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K86" t="n">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M86" t="n">
@@ -4773,31 +4774,31 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>鈊象</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>795</v>
+        <v>-1325</v>
       </c>
       <c r="D87" t="n">
-        <v>-8457</v>
+        <v>-7578</v>
       </c>
       <c r="E87" t="n">
-        <v>26299</v>
+        <v>-11028</v>
       </c>
       <c r="F87" t="n">
-        <v>-942</v>
+        <v>4622</v>
       </c>
       <c r="G87" t="n">
-        <v>-11126</v>
+        <v>13082</v>
       </c>
       <c r="H87" t="n">
-        <v>-936</v>
+        <v>-32</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -4806,49 +4807,49 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K87" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M87" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>-1178</v>
+        <v>331</v>
       </c>
       <c r="D88" t="n">
-        <v>-9396</v>
+        <v>-7774</v>
       </c>
       <c r="E88" t="n">
-        <v>-10694</v>
+        <v>26716</v>
       </c>
       <c r="F88" t="n">
-        <v>4410</v>
+        <v>-86</v>
       </c>
       <c r="G88" t="n">
-        <v>14382</v>
+        <v>-11036</v>
       </c>
       <c r="H88" t="n">
-        <v>-18</v>
+        <v>-714</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -4857,53 +4858,53 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K88" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M88" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>立隆電</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-12800</v>
+        <v>-4693</v>
       </c>
       <c r="D89" t="n">
-        <v>-11949</v>
+        <v>-7796</v>
       </c>
       <c r="E89" t="n">
-        <v>128433</v>
+        <v>-13152</v>
       </c>
       <c r="F89" t="n">
-        <v>19171</v>
+        <v>5646</v>
       </c>
       <c r="G89" t="n">
-        <v>15187</v>
+        <v>8206</v>
       </c>
       <c r="H89" t="n">
-        <v>16525</v>
+        <v>0</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>🔴 大賣</t>
+          <t>🟠 減碼</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -4912,7 +4913,7 @@
         </is>
       </c>
       <c r="K89" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -4920,37 +4921,37 @@
         </is>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>-3640</v>
+        <v>-19001</v>
       </c>
       <c r="D90" t="n">
-        <v>-13156</v>
+        <v>-12948</v>
       </c>
       <c r="E90" t="n">
-        <v>-22845</v>
+        <v>124968</v>
       </c>
       <c r="F90" t="n">
-        <v>-1025</v>
+        <v>24054</v>
       </c>
       <c r="G90" t="n">
-        <v>-3287</v>
+        <v>19887</v>
       </c>
       <c r="H90" t="n">
-        <v>-2663</v>
+        <v>19609</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -4963,7 +4964,7 @@
         </is>
       </c>
       <c r="K90" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -4971,37 +4972,37 @@
         </is>
       </c>
       <c r="M90" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>-16677</v>
+        <v>-5328</v>
       </c>
       <c r="D91" t="n">
-        <v>-13475</v>
+        <v>-15891</v>
       </c>
       <c r="E91" t="n">
-        <v>5854</v>
+        <v>-45301</v>
       </c>
       <c r="F91" t="n">
-        <v>7042</v>
+        <v>2463</v>
       </c>
       <c r="G91" t="n">
-        <v>13138</v>
+        <v>22748</v>
       </c>
       <c r="H91" t="n">
-        <v>-49</v>
+        <v>-1911</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -5010,49 +5011,49 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K91" t="n">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M91" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>-5855</v>
+        <v>-1607</v>
       </c>
       <c r="D92" t="n">
-        <v>-20334</v>
+        <v>-16185</v>
       </c>
       <c r="E92" t="n">
-        <v>-44737</v>
+        <v>-67435</v>
       </c>
       <c r="F92" t="n">
-        <v>6847</v>
+        <v>980</v>
       </c>
       <c r="G92" t="n">
-        <v>22729</v>
+        <v>15646</v>
       </c>
       <c r="H92" t="n">
-        <v>-2134</v>
+        <v>-335</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -5061,49 +5062,49 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K92" t="n">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M92" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>-6334</v>
+        <v>-12828</v>
       </c>
       <c r="D93" t="n">
-        <v>-20582</v>
+        <v>-17393</v>
       </c>
       <c r="E93" t="n">
-        <v>-9408</v>
+        <v>3961</v>
       </c>
       <c r="F93" t="n">
-        <v>5503</v>
+        <v>5902</v>
       </c>
       <c r="G93" t="n">
-        <v>22277</v>
+        <v>13010</v>
       </c>
       <c r="H93" t="n">
-        <v>-649</v>
+        <v>-55</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -5112,11 +5113,11 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K93" t="n">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -5130,31 +5131,31 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-2198</v>
+        <v>-6915</v>
       </c>
       <c r="D94" t="n">
-        <v>-21387</v>
+        <v>-18949</v>
       </c>
       <c r="E94" t="n">
-        <v>-69281</v>
+        <v>-10818</v>
       </c>
       <c r="F94" t="n">
-        <v>1573</v>
+        <v>6363</v>
       </c>
       <c r="G94" t="n">
-        <v>22699</v>
+        <v>20179</v>
       </c>
       <c r="H94" t="n">
-        <v>-334</v>
+        <v>-625</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -5167,15 +5168,15 @@
         </is>
       </c>
       <c r="K94" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M94" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="95">
@@ -5190,22 +5191,22 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>-6431</v>
+        <v>-7784</v>
       </c>
       <c r="D95" t="n">
-        <v>-22668</v>
+        <v>-24005</v>
       </c>
       <c r="E95" t="n">
-        <v>-28202</v>
+        <v>-29693</v>
       </c>
       <c r="F95" t="n">
-        <v>-2218</v>
+        <v>-933</v>
       </c>
       <c r="G95" t="n">
-        <v>-11384</v>
+        <v>-11516</v>
       </c>
       <c r="H95" t="n">
-        <v>-1896</v>
+        <v>-2060</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -5241,22 +5242,22 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>-33777</v>
+        <v>-17323</v>
       </c>
       <c r="D96" t="n">
-        <v>-44624</v>
+        <v>-26508</v>
       </c>
       <c r="E96" t="n">
-        <v>136000</v>
+        <v>142209</v>
       </c>
       <c r="F96" t="n">
-        <v>19833</v>
+        <v>-3047</v>
       </c>
       <c r="G96" t="n">
-        <v>78326</v>
+        <v>71628</v>
       </c>
       <c r="H96" t="n">
-        <v>-11212</v>
+        <v>-9000</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -5283,31 +5284,31 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>-35824</v>
+        <v>1188</v>
       </c>
       <c r="D97" t="n">
-        <v>-45635</v>
+        <v>-52374</v>
       </c>
       <c r="E97" t="n">
-        <v>-105759</v>
+        <v>-74863</v>
       </c>
       <c r="F97" t="n">
-        <v>14251</v>
+        <v>-11840</v>
       </c>
       <c r="G97" t="n">
-        <v>18678</v>
+        <v>33721</v>
       </c>
       <c r="H97" t="n">
-        <v>5373</v>
+        <v>-1298</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -5320,45 +5321,45 @@
         </is>
       </c>
       <c r="K97" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M97" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>2061</v>
+        <v>-46281</v>
       </c>
       <c r="D98" t="n">
-        <v>-55350</v>
+        <v>-54978</v>
       </c>
       <c r="E98" t="n">
-        <v>-71280</v>
+        <v>-116120</v>
       </c>
       <c r="F98" t="n">
-        <v>-7860</v>
+        <v>17617</v>
       </c>
       <c r="G98" t="n">
-        <v>34596</v>
+        <v>20761</v>
       </c>
       <c r="H98" t="n">
-        <v>-1497</v>
+        <v>4554</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -5371,45 +5372,45 @@
         </is>
       </c>
       <c r="K98" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M98" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>-16323</v>
+        <v>-1319</v>
       </c>
       <c r="D99" t="n">
-        <v>-119327</v>
+        <v>-89742</v>
       </c>
       <c r="E99" t="n">
-        <v>-255087</v>
+        <v>-259716</v>
       </c>
       <c r="F99" t="n">
-        <v>6486</v>
+        <v>12377</v>
       </c>
       <c r="G99" t="n">
-        <v>10184</v>
+        <v>118771</v>
       </c>
       <c r="H99" t="n">
-        <v>8554</v>
+        <v>1239</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -5418,49 +5419,49 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K99" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M99" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>-5549</v>
+        <v>-22473</v>
       </c>
       <c r="D100" t="n">
-        <v>-121095</v>
+        <v>-120324</v>
       </c>
       <c r="E100" t="n">
-        <v>-258356</v>
+        <v>-267341</v>
       </c>
       <c r="F100" t="n">
-        <v>12696</v>
+        <v>7332</v>
       </c>
       <c r="G100" t="n">
-        <v>150097</v>
+        <v>10672</v>
       </c>
       <c r="H100" t="n">
-        <v>886</v>
+        <v>7672</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -5469,19 +5470,19 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K100" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M100" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
@@ -5496,22 +5497,22 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-43644</v>
+        <v>-38177</v>
       </c>
       <c r="D101" t="n">
-        <v>-123197</v>
+        <v>-129839</v>
       </c>
       <c r="E101" t="n">
-        <v>-156397</v>
+        <v>-163989</v>
       </c>
       <c r="F101" t="n">
-        <v>37937</v>
+        <v>26213</v>
       </c>
       <c r="G101" t="n">
-        <v>121263</v>
+        <v>123785</v>
       </c>
       <c r="H101" t="n">
-        <v>6717</v>
+        <v>6201</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -5538,31 +5539,31 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>-76458</v>
+        <v>-42264</v>
       </c>
       <c r="D102" t="n">
-        <v>-221747</v>
+        <v>-199254</v>
       </c>
       <c r="E102" t="n">
-        <v>525726</v>
+        <v>107517</v>
       </c>
       <c r="F102" t="n">
-        <v>2576</v>
+        <v>-32107</v>
       </c>
       <c r="G102" t="n">
-        <v>941</v>
+        <v>138293</v>
       </c>
       <c r="H102" t="n">
-        <v>-6508</v>
+        <v>-3564</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -5571,19 +5572,19 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K102" t="n">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M102" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
@@ -5598,22 +5599,22 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>-56912</v>
+        <v>-51598</v>
       </c>
       <c r="D103" t="n">
-        <v>-237629</v>
+        <v>-202897</v>
       </c>
       <c r="E103" t="n">
-        <v>3021</v>
+        <v>-5345</v>
       </c>
       <c r="F103" t="n">
-        <v>31925</v>
+        <v>27258</v>
       </c>
       <c r="G103" t="n">
-        <v>49657</v>
+        <v>51698</v>
       </c>
       <c r="H103" t="n">
-        <v>-1520</v>
+        <v>-70</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -5640,52 +5641,3032 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
+          <t>2317</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>鴻海</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>-99074</v>
+      </c>
+      <c r="D104" t="n">
+        <v>-218817</v>
+      </c>
+      <c r="E104" t="n">
+        <v>500479</v>
+      </c>
+      <c r="F104" t="n">
+        <v>2963</v>
+      </c>
+      <c r="G104" t="n">
+        <v>1640</v>
+      </c>
+      <c r="H104" t="n">
+        <v>-7852</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>🔴 大賣</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K104" t="n">
+        <v>77</v>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M104" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G102"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>代號</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>訊號</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>外資5d</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>外資20d</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>外資5d(昨)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>外資20d(昨)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>名稱</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -3,167 千股)</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>-800201</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-928939</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2221404</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2237966</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>亞翔</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>8996</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -1,079 千股)</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>699280</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2747557</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1015205</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3826862</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -89 千股)</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>83675</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1774295</v>
+      </c>
+      <c r="E4" t="n">
+        <v>474598</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1863124</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>8210</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 119 千股)</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>-132094</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-2808924</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-709616</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-2928253</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>勤誠</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 1,280 千股)</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>938605</v>
+      </c>
+      <c r="D6" t="n">
+        <v>988549</v>
+      </c>
+      <c r="E6" t="n">
+        <v>478408</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-291379</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>3653</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 385 千股)</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1297337</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1536366</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1500819</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1151151</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -225 千股)</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>106496</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5704945</v>
+      </c>
+      <c r="E8" t="n">
+        <v>367992</v>
+      </c>
+      <c r="F8" t="n">
+        <v>5930008</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>6442</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -584 千股)</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>-91018</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-956229</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-357307</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-371924</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>光聖</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 192 千股)</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>216158</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-1046867</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-91346</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-1239231</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 36 千股)</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1219620</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1265482</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1225843</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1229271</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -997 千股)</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>-22473322</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-120324084</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-16323468</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-119326610</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -2,524 千股)</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>-339140</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-4549268</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-1182410</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-2025299</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>雙鴻</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2308</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -1,337 千股)</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>-7783974</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-24004830</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-6430743</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-22668318</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>台達電</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>6196</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -350 千股)</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>386508</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-753279</v>
+      </c>
+      <c r="E15" t="n">
+        <v>677088</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-402934</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>帆宣</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 1,850 千股)</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>5706754</v>
+      </c>
+      <c r="D16" t="n">
+        <v>10548997</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3268019</v>
+      </c>
+      <c r="F16" t="n">
+        <v>8699075</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3583</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -400 千股)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1774135</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3030859</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1619690</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3431095</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>辛耘</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>6197</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 1,831 千股)</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>-958250</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-272605</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-2118763</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-2103936</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>佳必琪</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -31 千股)</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>-176894</v>
+      </c>
+      <c r="D19" t="n">
+        <v>136336</v>
+      </c>
+      <c r="E19" t="n">
+        <v>8324</v>
+      </c>
+      <c r="F19" t="n">
+        <v>167197</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>5434</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -449 千股)</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>-2200986</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1192438</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-1240239</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1641824</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>崇越</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1513</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 4,442 千股)</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>-5327595</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-15891394</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-5855026</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-20333622</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>中興電</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>5340</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -409 千股)</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>-205986</v>
+      </c>
+      <c r="D22" t="n">
+        <v>545695</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-468546</v>
+      </c>
+      <c r="F22" t="n">
+        <v>955091</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>建榮</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1560</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -585 千股)</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>21670</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1578571</v>
+      </c>
+      <c r="E23" t="n">
+        <v>183148</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2163246</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>中砂</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1519</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 814 千股)</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>-2239320</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-6183357</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-2482395</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-6997483</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>華城</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -288 千股)</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>-1614307</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-2021046</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-2005703</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-1732730</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2640</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 12 千股)</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>15070</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-144136</v>
+      </c>
+      <c r="E26" t="n">
+        <v>13030</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-156176</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>大車隊</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>3029</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 598 千股)</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>682338</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2923758</v>
+      </c>
+      <c r="E27" t="n">
+        <v>207068</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2325399</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>零壹</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>4506</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 34 千股)</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>49273</v>
+      </c>
+      <c r="D28" t="n">
+        <v>356037</v>
+      </c>
+      <c r="E28" t="n">
+        <v>88630</v>
+      </c>
+      <c r="F28" t="n">
+        <v>321994</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>崇友</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>5519</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -75 千股)</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>153502</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1403663</v>
+      </c>
+      <c r="E29" t="n">
+        <v>343424</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1479161</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>隆大</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2421</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -500 千股)</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>76291</v>
+      </c>
+      <c r="D30" t="n">
+        <v>-6097204</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-913675</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-5596978</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>建準</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>3689</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -872 千股)</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1346049</v>
+      </c>
+      <c r="D31" t="n">
+        <v>-2593883</v>
+      </c>
+      <c r="E31" t="n">
+        <v>734796</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-1721583</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>湧德</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1618</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 753 千股)</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>434825</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1733134</v>
+      </c>
+      <c r="E32" t="n">
+        <v>320599</v>
+      </c>
+      <c r="F32" t="n">
+        <v>979888</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>合機</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2618</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 10,412 千股)</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>-40076614</v>
+      </c>
+      <c r="D33" t="n">
+        <v>190400051</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-19295293</v>
+      </c>
+      <c r="F33" t="n">
+        <v>179987736</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>長榮航</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -1,660 千股)</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>-2594232</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1933566</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-1185638</v>
+      </c>
+      <c r="F34" t="n">
+        <v>3593460</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>卜蜂</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>5904</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -30 千股)</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>-303075</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1299977</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-177113</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1330293</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>寶雅</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>6189</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 1,091 千股)</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>2234168</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-839539</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1487478</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-1930060</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>豐藝</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>1232</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -56 千股)</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>-295750</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-817582</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-365030</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-761791</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>大統益</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>5478</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -11 千股)</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>60749</v>
+      </c>
+      <c r="D38" t="n">
+        <v>588845</v>
+      </c>
+      <c r="E38" t="n">
+        <v>102372</v>
+      </c>
+      <c r="F38" t="n">
+        <v>600214</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>智冠</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>4527</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 21 千股)</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-16000</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-37000</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>方土霖</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>6788</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -131 千股)</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>18543</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-1093984</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-58354</v>
+      </c>
+      <c r="F40" t="n">
+        <v>-963165</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>華景電</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2753</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -133 千股)</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>-568650</v>
+      </c>
+      <c r="D41" t="n">
+        <v>963359</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-295900</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1096119</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>八方雲集</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>3045</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -13,777 千股)</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>-36628981</v>
+      </c>
+      <c r="D42" t="n">
+        <v>10120854</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-21969977</v>
+      </c>
+      <c r="F42" t="n">
+        <v>23897674</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>台灣大</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2912</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 5,202 千股)</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>-1607048</v>
+      </c>
+      <c r="D43" t="n">
+        <v>-16184928</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-2198490</v>
+      </c>
+      <c r="F43" t="n">
+        <v>-21387001</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>統一超</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>4129</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -19 千股)</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>-112000</v>
+      </c>
+      <c r="D44" t="n">
+        <v>-267000</v>
+      </c>
+      <c r="E44" t="n">
+        <v>-44000</v>
+      </c>
+      <c r="F44" t="n">
+        <v>-248132</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>聯合</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>1514</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -1,336 千股)</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>-606801</v>
+      </c>
+      <c r="D45" t="n">
+        <v>-7145116</v>
+      </c>
+      <c r="E45" t="n">
+        <v>-1846605</v>
+      </c>
+      <c r="F45" t="n">
+        <v>-5809350</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>亞力</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>3402</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 457 千股)</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>994079</v>
+      </c>
+      <c r="D46" t="n">
+        <v>3032890</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1602333</v>
+      </c>
+      <c r="F46" t="n">
+        <v>2575458</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>漢科</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>3147</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -214 千股)</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>-1509877</v>
+      </c>
+      <c r="D47" t="n">
+        <v>595769</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-1343877</v>
+      </c>
+      <c r="F47" t="n">
+        <v>809669</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>大綜</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -1,396 千股)</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>728627</v>
+      </c>
+      <c r="D48" t="n">
+        <v>-810566</v>
+      </c>
+      <c r="E48" t="n">
+        <v>880568</v>
+      </c>
+      <c r="F48" t="n">
+        <v>585153</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2472</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -2,104 千股)</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>-4693114</v>
+      </c>
+      <c r="D49" t="n">
+        <v>-7796106</v>
+      </c>
+      <c r="E49" t="n">
+        <v>-18426</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-5691759</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>立隆電</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>3406</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -913 千股)</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>51493</v>
+      </c>
+      <c r="D50" t="n">
+        <v>-3383069</v>
+      </c>
+      <c r="E50" t="n">
+        <v>943946</v>
+      </c>
+      <c r="F50" t="n">
+        <v>-2470408</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>玉晶光</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>3260</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 6,122 千股)</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>-3416100</v>
+      </c>
+      <c r="D51" t="n">
+        <v>-7033507</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-3640214</v>
+      </c>
+      <c r="F51" t="n">
+        <v>-13155791</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>威剛</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>3661</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -328 千股)</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>-124305</v>
+      </c>
+      <c r="D52" t="n">
+        <v>-2114187</v>
+      </c>
+      <c r="E52" t="n">
+        <v>-103989</v>
+      </c>
+      <c r="F52" t="n">
+        <v>-1786193</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>世芯-KY</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2327</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 2,976 千股)</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>1187789</v>
+      </c>
+      <c r="D53" t="n">
+        <v>-52374080</v>
+      </c>
+      <c r="E53" t="n">
+        <v>2060861</v>
+      </c>
+      <c r="F53" t="n">
+        <v>-55349731</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 18,117 千股)</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>-17322902</v>
+      </c>
+      <c r="D54" t="n">
+        <v>-26507588</v>
+      </c>
+      <c r="E54" t="n">
+        <v>-33777436</v>
+      </c>
+      <c r="F54" t="n">
+        <v>-44624115</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -1,250 千股)</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>14233120</v>
+      </c>
+      <c r="D55" t="n">
+        <v>59160199</v>
+      </c>
+      <c r="E55" t="n">
+        <v>14184467</v>
+      </c>
+      <c r="F55" t="n">
+        <v>60409860</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>3293</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 1,818 千股)</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>-1325216</v>
+      </c>
+      <c r="D56" t="n">
+        <v>-7578161</v>
+      </c>
+      <c r="E56" t="n">
+        <v>-1178265</v>
+      </c>
+      <c r="F56" t="n">
+        <v>-9395891</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>鈊象</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>1503</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -492 千股)</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>388495</v>
+      </c>
+      <c r="D57" t="n">
+        <v>-1908898</v>
+      </c>
+      <c r="E57" t="n">
+        <v>377165</v>
+      </c>
+      <c r="F57" t="n">
+        <v>-1416505</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>士電</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>6263</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 154 千股)</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>-845</v>
+      </c>
+      <c r="D58" t="n">
+        <v>-1161744</v>
+      </c>
+      <c r="E58" t="n">
+        <v>-450488</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-1315786</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>普萊德</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2535</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -80 千股)</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>-148563</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1840221</v>
+      </c>
+      <c r="E59" t="n">
+        <v>-6714</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1919964</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>達欣工</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2476</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 1,052 千股)</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>384803</v>
+      </c>
+      <c r="D60" t="n">
+        <v>171932</v>
+      </c>
+      <c r="E60" t="n">
+        <v>-815013</v>
+      </c>
+      <c r="F60" t="n">
+        <v>-879830</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>1773</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 71 千股)</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>-124160</v>
+      </c>
+      <c r="D61" t="n">
+        <v>129819</v>
+      </c>
+      <c r="E61" t="n">
+        <v>-195344</v>
+      </c>
+      <c r="F61" t="n">
+        <v>59117</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>勝一</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>1590</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 202 千股)</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>272953</v>
+      </c>
+      <c r="D62" t="n">
+        <v>776562</v>
+      </c>
+      <c r="E62" t="n">
+        <v>150521</v>
+      </c>
+      <c r="F62" t="n">
+        <v>574950</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>亞德客-KY</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -249 千股)</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>9050</v>
+      </c>
+      <c r="D63" t="n">
+        <v>555900</v>
+      </c>
+      <c r="E63" t="n">
+        <v>-100660</v>
+      </c>
+      <c r="F63" t="n">
+        <v>805190</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>信立</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>5269</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 255 千股)</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>-39925</v>
+      </c>
+      <c r="D64" t="n">
+        <v>367295</v>
+      </c>
+      <c r="E64" t="n">
+        <v>-107206</v>
+      </c>
+      <c r="F64" t="n">
+        <v>112116</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>祥碩</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>4979</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 1,955 千股)</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>1893080</v>
+      </c>
+      <c r="D65" t="n">
+        <v>3309115</v>
+      </c>
+      <c r="E65" t="n">
+        <v>879602</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1353770</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>華星光</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>3450</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -199 千股)</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>-1237054</v>
+      </c>
+      <c r="D66" t="n">
+        <v>-4941647</v>
+      </c>
+      <c r="E66" t="n">
+        <v>-2718403</v>
+      </c>
+      <c r="F66" t="n">
+        <v>-4742207</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>聯鈞</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2379</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 1,633 千股)</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>-6914795</v>
+      </c>
+      <c r="D67" t="n">
+        <v>-18948592</v>
+      </c>
+      <c r="E67" t="n">
+        <v>-6334213</v>
+      </c>
+      <c r="F67" t="n">
+        <v>-20581790</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>瑞昱</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2382</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 31,353 千股)</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>-1319042</v>
+      </c>
+      <c r="D68" t="n">
+        <v>-89742469</v>
+      </c>
+      <c r="E68" t="n">
+        <v>-5549289</v>
+      </c>
+      <c r="F68" t="n">
+        <v>-121095499</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>廣達</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 34,732 千股)</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>-51598125</v>
+      </c>
+      <c r="D69" t="n">
+        <v>-202897294</v>
+      </c>
+      <c r="E69" t="n">
+        <v>-56911898</v>
+      </c>
+      <c r="F69" t="n">
+        <v>-237629422</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>8271</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -96 千股)</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>-804332</v>
+      </c>
+      <c r="D70" t="n">
+        <v>-4807799</v>
+      </c>
+      <c r="E70" t="n">
+        <v>-1432201</v>
+      </c>
+      <c r="F70" t="n">
+        <v>-4712074</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>宇瞻</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>3081</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 191 千股)</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>1270512</v>
+      </c>
+      <c r="D71" t="n">
+        <v>3445681</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1172548</v>
+      </c>
+      <c r="F71" t="n">
+        <v>3254812</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 2,259 千股)</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>6851192</v>
+      </c>
+      <c r="D72" t="n">
+        <v>10700718</v>
+      </c>
+      <c r="E72" t="n">
+        <v>2382918</v>
+      </c>
+      <c r="F72" t="n">
+        <v>8441619</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>光寶科</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>8926</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -3,919 千股)</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>-12828305</v>
+      </c>
+      <c r="D73" t="n">
+        <v>-17393261</v>
+      </c>
+      <c r="E73" t="n">
+        <v>-16676813</v>
+      </c>
+      <c r="F73" t="n">
+        <v>-13474533</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>台汽電</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>4933</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -197 千股)</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>153195</v>
+      </c>
+      <c r="D74" t="n">
+        <v>-430684</v>
+      </c>
+      <c r="E74" t="n">
+        <v>166213</v>
+      </c>
+      <c r="F74" t="n">
+        <v>-233434</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>友輝</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3596</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -300 千股)</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>-1949477</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3864876</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-924698</v>
+      </c>
+      <c r="F75" t="n">
+        <v>4165298</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>智易</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>1616</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 1,430 千股)</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>66659</v>
+      </c>
+      <c r="D76" t="n">
+        <v>-710737</v>
+      </c>
+      <c r="E76" t="n">
+        <v>95769</v>
+      </c>
+      <c r="F76" t="n">
+        <v>-2140726</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>億泰</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>3227</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 6 千股)</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>3782190</v>
+      </c>
+      <c r="D77" t="n">
+        <v>6411835</v>
+      </c>
+      <c r="E77" t="n">
+        <v>5412854</v>
+      </c>
+      <c r="F77" t="n">
+        <v>6406220</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>原相</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>6285</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 684 千股)</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>330900</v>
+      </c>
+      <c r="D78" t="n">
+        <v>-7773557</v>
+      </c>
+      <c r="E78" t="n">
+        <v>794806</v>
+      </c>
+      <c r="F78" t="n">
+        <v>-8457319</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>啟碁</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>6510</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 33 千股)</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>239004</v>
+      </c>
+      <c r="D79" t="n">
+        <v>72756</v>
+      </c>
+      <c r="E79" t="n">
+        <v>220533</v>
+      </c>
+      <c r="F79" t="n">
+        <v>40010</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>精測</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2356</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -1,000 千股)</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>-19001106</v>
+      </c>
+      <c r="D80" t="n">
+        <v>-12948152</v>
+      </c>
+      <c r="E80" t="n">
+        <v>-12799990</v>
+      </c>
+      <c r="F80" t="n">
+        <v>-11948556</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>英業達</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2317</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 2,930 千股)</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>-99074232</v>
+      </c>
+      <c r="D81" t="n">
+        <v>-218817336</v>
+      </c>
+      <c r="E81" t="n">
+        <v>-76458409</v>
+      </c>
+      <c r="F81" t="n">
+        <v>-221747342</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>鴻海</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>5243</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 2,901 千股)</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>-706287</v>
+      </c>
+      <c r="D82" t="n">
+        <v>-3879336</v>
+      </c>
+      <c r="E82" t="n">
+        <v>-1396099</v>
+      </c>
+      <c r="F82" t="n">
+        <v>-6779974</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>乙盛-KY</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>5225</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 496 千股)</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>10373</v>
+      </c>
+      <c r="D83" t="n">
+        <v>3102</v>
+      </c>
+      <c r="E83" t="n">
+        <v>65123</v>
+      </c>
+      <c r="F83" t="n">
+        <v>-493048</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>東科-KY</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2305</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 1,349 千股)</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>889250</v>
+      </c>
+      <c r="D84" t="n">
+        <v>2991504</v>
+      </c>
+      <c r="E84" t="n">
+        <v>681000</v>
+      </c>
+      <c r="F84" t="n">
+        <v>1642214</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>全友</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>3188</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -6 千股)</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>210469</v>
+      </c>
+      <c r="D85" t="n">
+        <v>-1412623</v>
+      </c>
+      <c r="E85" t="n">
+        <v>248000</v>
+      </c>
+      <c r="F85" t="n">
+        <v>-1406962</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>鑫龍騰</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>8086</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 2,726 千股)</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>-3341098</v>
+      </c>
+      <c r="D86" t="n">
+        <v>-3305190</v>
+      </c>
+      <c r="E86" t="n">
+        <v>-4420252</v>
+      </c>
+      <c r="F86" t="n">
+        <v>-6030896</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>宏捷科</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2395</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -453 千股)</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>2361825</v>
+      </c>
+      <c r="D87" t="n">
+        <v>2477701</v>
+      </c>
+      <c r="E87" t="n">
+        <v>2119415</v>
+      </c>
+      <c r="F87" t="n">
+        <v>2931181</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2412</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -9,343 千股)</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>-46281468</v>
+      </c>
+      <c r="D88" t="n">
+        <v>-54977869</v>
+      </c>
+      <c r="E88" t="n">
+        <v>-35824111</v>
+      </c>
+      <c r="F88" t="n">
+        <v>-45634511</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>中華電</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>9917</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -837 千股)</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>-1382384</v>
+      </c>
+      <c r="D89" t="n">
+        <v>-5668599</v>
+      </c>
+      <c r="E89" t="n">
+        <v>-1712881</v>
+      </c>
+      <c r="F89" t="n">
+        <v>-4831108</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>中保科</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>6739</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 26 千股)</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>63395</v>
+      </c>
+      <c r="D90" t="n">
+        <v>29421</v>
+      </c>
+      <c r="E90" t="n">
+        <v>50779</v>
+      </c>
+      <c r="F90" t="n">
+        <v>3639</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>6690</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -56 千股)</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>-88334</v>
+      </c>
+      <c r="D91" t="n">
+        <v>-390520</v>
+      </c>
+      <c r="E91" t="n">
+        <v>-119920</v>
+      </c>
+      <c r="F91" t="n">
+        <v>-334115</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>安碁資訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2645</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 2,182 千股)</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>4954518</v>
+      </c>
+      <c r="D92" t="n">
+        <v>7974993</v>
+      </c>
+      <c r="E92" t="n">
+        <v>2804322</v>
+      </c>
+      <c r="F92" t="n">
+        <v>5793196</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>長榮航太</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>4569</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 10 千股)</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>6800</v>
+      </c>
+      <c r="D93" t="n">
+        <v>96605</v>
+      </c>
+      <c r="E93" t="n">
+        <v>-35117</v>
+      </c>
+      <c r="F93" t="n">
+        <v>86311</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>六方科-KY</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>4904</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -6,642 千股)</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>-38176568</v>
+      </c>
+      <c r="D94" t="n">
+        <v>-129839374</v>
+      </c>
+      <c r="E94" t="n">
+        <v>-43643905</v>
+      </c>
+      <c r="F94" t="n">
+        <v>-123197445</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>遠傳</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
           <t>2344</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 50,942 千股)</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>-42264080</v>
+      </c>
+      <c r="D95" t="n">
+        <v>-199253908</v>
+      </c>
+      <c r="E95" t="n">
+        <v>-100573740</v>
+      </c>
+      <c r="F95" t="n">
+        <v>-250196137</v>
+      </c>
+      <c r="G95" t="inlineStr">
         <is>
           <t>華邦電</t>
         </is>
       </c>
-      <c r="C104" t="n">
-        <v>-100574</v>
-      </c>
-      <c r="D104" t="n">
-        <v>-250196</v>
-      </c>
-      <c r="E104" t="n">
-        <v>66126</v>
-      </c>
-      <c r="F104" t="n">
-        <v>40239</v>
-      </c>
-      <c r="G104" t="n">
-        <v>174708</v>
-      </c>
-      <c r="H104" t="n">
-        <v>-4967</v>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>🔴 大賣</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K104" t="n">
-        <v>56</v>
-      </c>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>📉 減速</t>
-        </is>
-      </c>
-      <c r="M104" t="n">
-        <v>2</v>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -1,430 千股)</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>-3918232</v>
+      </c>
+      <c r="D96" t="n">
+        <v>-4010798</v>
+      </c>
+      <c r="E96" t="n">
+        <v>-1442400</v>
+      </c>
+      <c r="F96" t="n">
+        <v>-2580348</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 134 千股)</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>129100</v>
+      </c>
+      <c r="D97" t="n">
+        <v>-4619395</v>
+      </c>
+      <c r="E97" t="n">
+        <v>-159369</v>
+      </c>
+      <c r="F97" t="n">
+        <v>-4753207</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -719 千股)</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>-1598545</v>
+      </c>
+      <c r="D98" t="n">
+        <v>-4637437</v>
+      </c>
+      <c r="E98" t="n">
+        <v>-778527</v>
+      </c>
+      <c r="F98" t="n">
+        <v>-3918276</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>5274</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 75 千股)</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>85783</v>
+      </c>
+      <c r="D99" t="n">
+        <v>270401</v>
+      </c>
+      <c r="E99" t="n">
+        <v>36613</v>
+      </c>
+      <c r="F99" t="n">
+        <v>195714</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -2,487 千股)</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>3415495</v>
+      </c>
+      <c r="D100" t="n">
+        <v>1681307</v>
+      </c>
+      <c r="E100" t="n">
+        <v>5079686</v>
+      </c>
+      <c r="F100" t="n">
+        <v>4168699</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>5439</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 592 千股)</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>-360963</v>
+      </c>
+      <c r="D101" t="n">
+        <v>1274192</v>
+      </c>
+      <c r="E101" t="n">
+        <v>-1135965</v>
+      </c>
+      <c r="F101" t="n">
+        <v>682062</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>高技</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -512 千股)</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>-294585</v>
+      </c>
+      <c r="D102" t="n">
+        <v>-2560418</v>
+      </c>
+      <c r="E102" t="n">
+        <v>54750</v>
+      </c>
+      <c r="F102" t="n">
+        <v>-2048783</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/台股_外資雷達.xlsx
+++ b/data/台股_外資雷達.xlsx
@@ -496,22 +496,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-40077</v>
+        <v>-52105</v>
       </c>
       <c r="D2" t="n">
-        <v>190400</v>
+        <v>197618</v>
       </c>
       <c r="E2" t="n">
-        <v>-159305</v>
+        <v>-152783</v>
       </c>
       <c r="F2" t="n">
-        <v>49864</v>
+        <v>54852</v>
       </c>
       <c r="G2" t="n">
-        <v>-7806</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
-        <v>10348</v>
+        <v>11913</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -547,22 +547,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14233</v>
+        <v>-10587</v>
       </c>
       <c r="D3" t="n">
-        <v>59160</v>
+        <v>41673</v>
       </c>
       <c r="E3" t="n">
-        <v>20651</v>
+        <v>-111</v>
       </c>
       <c r="F3" t="n">
-        <v>170</v>
+        <v>1734</v>
       </c>
       <c r="G3" t="n">
-        <v>-53549</v>
+        <v>-52231</v>
       </c>
       <c r="H3" t="n">
-        <v>3630</v>
+        <v>3657</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6851</v>
+        <v>17375</v>
       </c>
       <c r="D4" t="n">
-        <v>10701</v>
+        <v>11837</v>
       </c>
       <c r="E4" t="n">
-        <v>172066</v>
+        <v>147380</v>
       </c>
       <c r="F4" t="n">
-        <v>-7035</v>
+        <v>-5806</v>
       </c>
       <c r="G4" t="n">
-        <v>-30746</v>
+        <v>-31687</v>
       </c>
       <c r="H4" t="n">
-        <v>17</v>
+        <v>931</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -649,22 +649,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5707</v>
+        <v>5709</v>
       </c>
       <c r="D5" t="n">
-        <v>10549</v>
+        <v>11089</v>
       </c>
       <c r="E5" t="n">
-        <v>17627</v>
+        <v>16385</v>
       </c>
       <c r="F5" t="n">
-        <v>-7954</v>
+        <v>-7461</v>
       </c>
       <c r="G5" t="n">
-        <v>-8791</v>
+        <v>-9169</v>
       </c>
       <c r="H5" t="n">
-        <v>310</v>
+        <v>371</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -691,82 +691,82 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>長榮航太</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-36629</v>
+        <v>4711</v>
       </c>
       <c r="D6" t="n">
-        <v>10121</v>
+        <v>7977</v>
       </c>
       <c r="E6" t="n">
-        <v>4527</v>
+        <v>11602</v>
       </c>
       <c r="F6" t="n">
-        <v>22780</v>
+        <v>-53</v>
       </c>
       <c r="G6" t="n">
-        <v>25702</v>
+        <v>-565</v>
       </c>
       <c r="H6" t="n">
-        <v>179</v>
+        <v>644</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>🚀 大買</t>
+          <t>🟢 加碼</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>原相</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4955</v>
+        <v>4842</v>
       </c>
       <c r="D7" t="n">
-        <v>7975</v>
+        <v>6567</v>
       </c>
       <c r="E7" t="n">
-        <v>12765</v>
+        <v>11204</v>
       </c>
       <c r="F7" t="n">
-        <v>-52</v>
+        <v>3394</v>
       </c>
       <c r="G7" t="n">
-        <v>-567</v>
+        <v>3579</v>
       </c>
       <c r="H7" t="n">
-        <v>533</v>
+        <v>247</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -779,45 +779,45 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3782</v>
+        <v>20</v>
       </c>
       <c r="D8" t="n">
-        <v>6412</v>
+        <v>5745</v>
       </c>
       <c r="E8" t="n">
-        <v>12064</v>
+        <v>9982</v>
       </c>
       <c r="F8" t="n">
-        <v>2851</v>
+        <v>-46</v>
       </c>
       <c r="G8" t="n">
-        <v>2968</v>
+        <v>-4883</v>
       </c>
       <c r="H8" t="n">
-        <v>174</v>
+        <v>296</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -826,11 +826,11 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -838,37 +838,37 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>106</v>
+        <v>1217</v>
       </c>
       <c r="D9" t="n">
-        <v>5705</v>
+        <v>4003</v>
       </c>
       <c r="E9" t="n">
-        <v>6459</v>
+        <v>2120</v>
       </c>
       <c r="F9" t="n">
-        <v>-20</v>
+        <v>-1306</v>
       </c>
       <c r="G9" t="n">
-        <v>-4627</v>
+        <v>-3454</v>
       </c>
       <c r="H9" t="n">
-        <v>265</v>
+        <v>7</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -877,11 +877,11 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -895,31 +895,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-1949</v>
+        <v>3362</v>
       </c>
       <c r="D10" t="n">
-        <v>3865</v>
+        <v>3826</v>
       </c>
       <c r="E10" t="n">
-        <v>5169</v>
+        <v>18861</v>
       </c>
       <c r="F10" t="n">
-        <v>2335</v>
+        <v>129</v>
       </c>
       <c r="G10" t="n">
-        <v>5520</v>
+        <v>225</v>
       </c>
       <c r="H10" t="n">
-        <v>-97</v>
+        <v>16</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -928,11 +928,11 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -946,31 +946,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>零壹</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1271</v>
+        <v>1395</v>
       </c>
       <c r="D11" t="n">
-        <v>3446</v>
+        <v>3649</v>
       </c>
       <c r="E11" t="n">
-        <v>2025</v>
+        <v>1400</v>
       </c>
       <c r="F11" t="n">
-        <v>-1151</v>
+        <v>-92</v>
       </c>
       <c r="G11" t="n">
-        <v>-3257</v>
+        <v>-148</v>
       </c>
       <c r="H11" t="n">
-        <v>-137</v>
+        <v>-753</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -979,49 +979,49 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>漢科</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1893</v>
+        <v>1535</v>
       </c>
       <c r="D12" t="n">
-        <v>3309</v>
+        <v>3409</v>
       </c>
       <c r="E12" t="n">
-        <v>-2664</v>
+        <v>2399</v>
       </c>
       <c r="F12" t="n">
-        <v>-2654</v>
+        <v>135</v>
       </c>
       <c r="G12" t="n">
-        <v>-5881</v>
+        <v>135</v>
       </c>
       <c r="H12" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1034,45 +1034,45 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>智易</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>994</v>
+        <v>-163</v>
       </c>
       <c r="D13" t="n">
-        <v>3033</v>
+        <v>3276</v>
       </c>
       <c r="E13" t="n">
-        <v>2037</v>
+        <v>5595</v>
       </c>
       <c r="F13" t="n">
-        <v>135</v>
+        <v>1756</v>
       </c>
       <c r="G13" t="n">
-        <v>135</v>
+        <v>5534</v>
       </c>
       <c r="H13" t="n">
-        <v>-3</v>
+        <v>-55</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1085,11 +1085,11 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M13" t="n">
@@ -1099,31 +1099,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1774</v>
+        <v>436</v>
       </c>
       <c r="D14" t="n">
-        <v>3031</v>
+        <v>3239</v>
       </c>
       <c r="E14" t="n">
-        <v>-1783</v>
+        <v>2692</v>
       </c>
       <c r="F14" t="n">
-        <v>-126</v>
+        <v>-824</v>
       </c>
       <c r="G14" t="n">
-        <v>-108</v>
+        <v>1134</v>
       </c>
       <c r="H14" t="n">
-        <v>-27</v>
+        <v>33</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1136,15 +1136,15 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -1159,13 +1159,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>889</v>
+        <v>452</v>
       </c>
       <c r="D15" t="n">
-        <v>2992</v>
+        <v>2466</v>
       </c>
       <c r="E15" t="n">
-        <v>8509</v>
+        <v>8011</v>
       </c>
       <c r="F15" t="n">
         <v>-1</v>
@@ -1174,7 +1174,7 @@
         <v>-6</v>
       </c>
       <c r="H15" t="n">
-        <v>-204</v>
+        <v>-167</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1201,31 +1201,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>合機</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>682</v>
+        <v>691</v>
       </c>
       <c r="D16" t="n">
-        <v>2924</v>
+        <v>2235</v>
       </c>
       <c r="E16" t="n">
-        <v>519</v>
+        <v>2100</v>
       </c>
       <c r="F16" t="n">
-        <v>-96</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>-155</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>-786</v>
+        <v>144</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1238,45 +1238,45 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>699</v>
+        <v>321</v>
       </c>
       <c r="D17" t="n">
-        <v>2748</v>
+        <v>2091</v>
       </c>
       <c r="E17" t="n">
-        <v>1831</v>
+        <v>5309</v>
       </c>
       <c r="F17" t="n">
-        <v>-698</v>
+        <v>-285</v>
       </c>
       <c r="G17" t="n">
-        <v>1996</v>
+        <v>-193</v>
       </c>
       <c r="H17" t="n">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1303,184 +1303,172 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2362</v>
+        <v>665</v>
       </c>
       <c r="D18" t="n">
-        <v>2478</v>
+        <v>1879</v>
       </c>
       <c r="E18" t="n">
-        <v>19682</v>
+        <v>-2267</v>
       </c>
       <c r="F18" t="n">
-        <v>287</v>
+        <v>-145</v>
       </c>
       <c r="G18" t="n">
-        <v>196</v>
+        <v>-127</v>
       </c>
       <c r="H18" t="n">
-        <v>-34</v>
+        <v>-75</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>🟢 加碼</t>
+          <t>🟡 中性</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-2594</v>
+        <v>-20</v>
       </c>
       <c r="D19" t="n">
-        <v>1934</v>
+        <v>1878</v>
       </c>
       <c r="E19" t="n">
-        <v>-10036</v>
+        <v>-3897</v>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-8758</v>
+        <v>-6246</v>
       </c>
       <c r="H19" t="n">
-        <v>-28</v>
+        <v>-91</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>94</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>📉 減速</t>
-        </is>
-      </c>
-      <c r="M19" t="n">
-        <v>-4</v>
-      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-149</v>
+        <v>3288</v>
       </c>
       <c r="D20" t="n">
-        <v>1840</v>
+        <v>1788</v>
       </c>
       <c r="E20" t="n">
+        <v>-7558</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2412</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-238</v>
+      </c>
+      <c r="H20" t="n">
+        <v>141</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
         <v>100</v>
       </c>
-      <c r="F20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-367</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>79</v>
-      </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>84</v>
+        <v>-214</v>
       </c>
       <c r="D21" t="n">
-        <v>1774</v>
+        <v>1777</v>
       </c>
       <c r="E21" t="n">
-        <v>4959</v>
+        <v>-5421</v>
       </c>
       <c r="F21" t="n">
-        <v>-445</v>
+        <v>-1910</v>
       </c>
       <c r="G21" t="n">
-        <v>-202</v>
+        <v>-5612</v>
       </c>
       <c r="H21" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1489,11 +1477,11 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1501,127 +1489,127 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>合機</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>435</v>
+        <v>1051</v>
       </c>
       <c r="D22" t="n">
-        <v>1733</v>
+        <v>1755</v>
       </c>
       <c r="E22" t="n">
-        <v>903</v>
+        <v>6207</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>-677</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-4159</v>
       </c>
       <c r="H22" t="n">
-        <v>118</v>
+        <v>157</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>84</v>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>🛬 穩定</t>
-        </is>
-      </c>
-      <c r="M22" t="n">
-        <v>-2</v>
-      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>達欣工</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3415</v>
+        <v>-296</v>
       </c>
       <c r="D23" t="n">
-        <v>1681</v>
+        <v>1753</v>
       </c>
       <c r="E23" t="n">
-        <v>6583</v>
+        <v>82</v>
       </c>
       <c r="F23" t="n">
-        <v>-2255</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>-5113</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>-132</v>
+        <v>-343</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>79</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>🛬 穩定</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>22</v>
+        <v>485</v>
       </c>
       <c r="D24" t="n">
-        <v>1579</v>
+        <v>1544</v>
       </c>
       <c r="E24" t="n">
-        <v>6746</v>
+        <v>-1318</v>
       </c>
       <c r="F24" t="n">
-        <v>543</v>
+        <v>-307</v>
       </c>
       <c r="G24" t="n">
-        <v>1375</v>
+        <v>-138</v>
       </c>
       <c r="H24" t="n">
-        <v>-115</v>
+        <v>-114</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1634,45 +1622,45 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1297</v>
+        <v>-46</v>
       </c>
       <c r="D25" t="n">
-        <v>1536</v>
+        <v>1343</v>
       </c>
       <c r="E25" t="n">
-        <v>-1407</v>
+        <v>5240</v>
       </c>
       <c r="F25" t="n">
-        <v>-250</v>
+        <v>474</v>
       </c>
       <c r="G25" t="n">
-        <v>13</v>
+        <v>1381</v>
       </c>
       <c r="H25" t="n">
-        <v>-150</v>
+        <v>-115</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1685,45 +1673,45 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>154</v>
+        <v>332</v>
       </c>
       <c r="D26" t="n">
-        <v>1404</v>
+        <v>1307</v>
       </c>
       <c r="E26" t="n">
-        <v>-85</v>
+        <v>5181</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>-658</v>
       </c>
       <c r="H26" t="n">
-        <v>322</v>
+        <v>139</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1736,45 +1724,45 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>寶雅</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-303</v>
+        <v>-519</v>
       </c>
       <c r="D27" t="n">
-        <v>1300</v>
+        <v>1122</v>
       </c>
       <c r="E27" t="n">
-        <v>2401</v>
+        <v>-1369</v>
       </c>
       <c r="F27" t="n">
-        <v>69</v>
+        <v>259</v>
       </c>
       <c r="G27" t="n">
-        <v>197</v>
+        <v>240</v>
       </c>
       <c r="H27" t="n">
-        <v>254</v>
+        <v>16</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1787,84 +1775,96 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速*</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-361</v>
+        <v>-2233</v>
       </c>
       <c r="D28" t="n">
-        <v>1274</v>
+        <v>1060</v>
       </c>
       <c r="E28" t="n">
-        <v>-5260</v>
+        <v>-9566</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G28" t="n">
-        <v>-6246</v>
+        <v>-7046</v>
       </c>
       <c r="H28" t="n">
-        <v>-91</v>
+        <v>-15</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>94</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>📉 減速</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>-4</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>寶雅</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1220</v>
+        <v>-457</v>
       </c>
       <c r="D29" t="n">
-        <v>1265</v>
+        <v>1054</v>
       </c>
       <c r="E29" t="n">
-        <v>5079</v>
+        <v>1904</v>
       </c>
       <c r="F29" t="n">
-        <v>200</v>
+        <v>19</v>
       </c>
       <c r="G29" t="n">
-        <v>-497</v>
+        <v>156</v>
       </c>
       <c r="H29" t="n">
-        <v>42</v>
+        <v>242</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1877,45 +1877,45 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>德昌</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-2201</v>
+        <v>17</v>
       </c>
       <c r="D30" t="n">
-        <v>1192</v>
+        <v>973</v>
       </c>
       <c r="E30" t="n">
-        <v>1338</v>
+        <v>712</v>
       </c>
       <c r="F30" t="n">
-        <v>3317</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>2488</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-40</v>
+        <v>-19</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1924,40 +1924,40 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M30" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>德昌</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>56</v>
+        <v>-458</v>
       </c>
       <c r="D31" t="n">
-        <v>1096</v>
+        <v>944</v>
       </c>
       <c r="E31" t="n">
-        <v>754</v>
+        <v>-220</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1966,7 +1966,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-19</v>
+        <v>316</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1975,15 +1975,15 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M31" t="n">
@@ -1993,31 +1993,31 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>939</v>
+        <v>358</v>
       </c>
       <c r="D32" t="n">
-        <v>989</v>
+        <v>848</v>
       </c>
       <c r="E32" t="n">
-        <v>-8180</v>
+        <v>1752</v>
       </c>
       <c r="F32" t="n">
-        <v>2179</v>
+        <v>20</v>
       </c>
       <c r="G32" t="n">
-        <v>-830</v>
+        <v>342</v>
       </c>
       <c r="H32" t="n">
-        <v>92</v>
+        <v>-11</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2026,49 +2026,49 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-569</v>
+        <v>-255</v>
       </c>
       <c r="D33" t="n">
-        <v>963</v>
+        <v>833</v>
       </c>
       <c r="E33" t="n">
-        <v>-1528</v>
+        <v>-4999</v>
       </c>
       <c r="F33" t="n">
-        <v>261</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>237</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>17</v>
+        <v>-47</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2081,45 +2081,45 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>🐌 龜速*</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M33" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>勝一</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>273</v>
+        <v>491</v>
       </c>
       <c r="D34" t="n">
-        <v>777</v>
+        <v>643</v>
       </c>
       <c r="E34" t="n">
-        <v>1863</v>
+        <v>4276</v>
       </c>
       <c r="F34" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="G34" t="n">
-        <v>341</v>
+        <v>7</v>
       </c>
       <c r="H34" t="n">
-        <v>-17</v>
+        <v>-61</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2132,36 +2132,36 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M34" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>智冠</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-1510</v>
+        <v>78</v>
       </c>
       <c r="D35" t="n">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="E35" t="n">
-        <v>1876</v>
+        <v>425</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>68</v>
+        <v>-156</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2179,40 +2179,40 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>智冠</t>
+          <t>信立</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>61</v>
+        <v>225</v>
       </c>
       <c r="D36" t="n">
-        <v>589</v>
+        <v>540</v>
       </c>
       <c r="E36" t="n">
-        <v>362</v>
+        <v>-741</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -2221,7 +2221,7 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-154</v>
+        <v>-0</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2230,40 +2230,40 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M36" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>9</v>
+        <v>-1265</v>
       </c>
       <c r="D37" t="n">
-        <v>556</v>
+        <v>536</v>
       </c>
       <c r="E37" t="n">
-        <v>-490</v>
+        <v>2111</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -2272,7 +2272,7 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2299,31 +2299,31 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-206</v>
+        <v>-2407</v>
       </c>
       <c r="D38" t="n">
-        <v>546</v>
+        <v>526</v>
       </c>
       <c r="E38" t="n">
-        <v>-7809</v>
+        <v>254</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>3165</v>
       </c>
       <c r="H38" t="n">
-        <v>-67</v>
+        <v>-50</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2336,15 +2336,15 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M38" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="39">
@@ -2359,22 +2359,22 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-40</v>
+        <v>126</v>
       </c>
       <c r="D39" t="n">
-        <v>367</v>
+        <v>471</v>
       </c>
       <c r="E39" t="n">
-        <v>-1992</v>
+        <v>-1936</v>
       </c>
       <c r="F39" t="n">
-        <v>1303</v>
+        <v>1379</v>
       </c>
       <c r="G39" t="n">
-        <v>1281</v>
+        <v>1577</v>
       </c>
       <c r="H39" t="n">
-        <v>-34</v>
+        <v>6</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         <v>49</v>
       </c>
       <c r="D40" t="n">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="E40" t="n">
-        <v>517</v>
+        <v>538</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -2452,70 +2452,82 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>86</v>
+        <v>132</v>
       </c>
       <c r="D41" t="n">
-        <v>270</v>
+        <v>310</v>
       </c>
       <c r="E41" t="n">
-        <v>798</v>
+        <v>-317</v>
       </c>
       <c r="F41" t="n">
-        <v>-124</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>-180</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-5</v>
+        <v>-0</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>78</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>📉 減速</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>-3</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>385</v>
+        <v>-240</v>
       </c>
       <c r="D42" t="n">
-        <v>172</v>
+        <v>287</v>
       </c>
       <c r="E42" t="n">
-        <v>-1213</v>
+        <v>-791</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H42" t="n">
-        <v>972</v>
+        <v>-53</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2524,121 +2536,109 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M42" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-177</v>
+        <v>169</v>
       </c>
       <c r="D43" t="n">
-        <v>136</v>
+        <v>237</v>
       </c>
       <c r="E43" t="n">
-        <v>-1007</v>
+        <v>757</v>
       </c>
       <c r="F43" t="n">
-        <v>39</v>
+        <v>-69</v>
       </c>
       <c r="G43" t="n">
-        <v>18</v>
+        <v>-186</v>
       </c>
       <c r="H43" t="n">
-        <v>-32</v>
+        <v>-9</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K43" t="n">
-        <v>96</v>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>🚀 加速器</t>
-        </is>
-      </c>
-      <c r="M43" t="n">
-        <v>4</v>
-      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>勝一</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-124</v>
+        <v>310</v>
       </c>
       <c r="D44" t="n">
-        <v>130</v>
+        <v>167</v>
       </c>
       <c r="E44" t="n">
-        <v>4598</v>
+        <v>-373</v>
       </c>
       <c r="F44" t="n">
+        <v>-650</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-1283</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-113</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>66</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
         <v>2</v>
-      </c>
-      <c r="G44" t="n">
-        <v>3</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-69</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K44" t="n">
-        <v>71</v>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>📉 減速</t>
-        </is>
-      </c>
-      <c r="M44" t="n">
-        <v>-3</v>
       </c>
     </row>
     <row r="45">
@@ -2653,13 +2653,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="D45" t="n">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="E45" t="n">
-        <v>-2</v>
+        <v>-11</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -2695,31 +2695,31 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>方土霖</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>239</v>
+        <v>3</v>
       </c>
       <c r="D46" t="n">
-        <v>73</v>
+        <v>-19</v>
       </c>
       <c r="E46" t="n">
-        <v>-562</v>
+        <v>-66</v>
       </c>
       <c r="F46" t="n">
-        <v>-639</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>-1029</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>-130</v>
+        <v>-2</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2728,11 +2728,11 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         </is>
       </c>
       <c r="M46" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="47">
@@ -2755,13 +2755,13 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>63</v>
+        <v>-54</v>
       </c>
       <c r="D47" t="n">
-        <v>29</v>
+        <v>-57</v>
       </c>
       <c r="E47" t="n">
-        <v>-283</v>
+        <v>-351</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -2770,7 +2770,7 @@
         <v>-60</v>
       </c>
       <c r="H47" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2791,28 +2791,28 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>大車隊</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D48" t="n">
-        <v>3</v>
+        <v>-155</v>
       </c>
       <c r="E48" t="n">
-        <v>-302</v>
+        <v>-306</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -2821,7 +2821,7 @@
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2830,49 +2830,49 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M48" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>方土霖</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>456</v>
       </c>
       <c r="D49" t="n">
-        <v>-16</v>
+        <v>-250</v>
       </c>
       <c r="E49" t="n">
-        <v>-72</v>
+        <v>386</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H49" t="n">
-        <v>-2</v>
+        <v>-231</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2885,36 +2885,36 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M49" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>大車隊</t>
+          <t>億泰</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>15</v>
+        <v>142</v>
       </c>
       <c r="D50" t="n">
-        <v>-144</v>
+        <v>-266</v>
       </c>
       <c r="E50" t="n">
-        <v>-342</v>
+        <v>-2348</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -2923,7 +2923,7 @@
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-1</v>
+        <v>202</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2932,11 +2932,11 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="51">
@@ -2959,13 +2959,13 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-112</v>
+        <v>-48</v>
       </c>
       <c r="D51" t="n">
-        <v>-267</v>
+        <v>-275</v>
       </c>
       <c r="E51" t="n">
-        <v>-3499</v>
+        <v>-3539</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -2974,7 +2974,7 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3001,31 +3001,31 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>友輝</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-958</v>
+        <v>204</v>
       </c>
       <c r="D52" t="n">
-        <v>-273</v>
+        <v>-277</v>
       </c>
       <c r="E52" t="n">
-        <v>-296</v>
+        <v>950</v>
       </c>
       <c r="F52" t="n">
-        <v>-6</v>
+        <v>6</v>
       </c>
       <c r="G52" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H52" t="n">
-        <v>-412</v>
+        <v>-144</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3034,19 +3034,19 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M52" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="53">
@@ -3061,22 +3061,22 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>263</v>
+        <v>72</v>
       </c>
       <c r="D53" t="n">
-        <v>-316</v>
+        <v>-351</v>
       </c>
       <c r="E53" t="n">
-        <v>235</v>
+        <v>207</v>
       </c>
       <c r="F53" t="n">
-        <v>-374</v>
+        <v>-107</v>
       </c>
       <c r="G53" t="n">
-        <v>114</v>
+        <v>279</v>
       </c>
       <c r="H53" t="n">
-        <v>-51</v>
+        <v>-57</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3112,13 +3112,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-88</v>
+        <v>-94</v>
       </c>
       <c r="D54" t="n">
-        <v>-391</v>
+        <v>-419</v>
       </c>
       <c r="E54" t="n">
-        <v>-349</v>
+        <v>-363</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -3127,7 +3127,7 @@
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3154,31 +3154,31 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>大統益</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>153</v>
+        <v>187</v>
       </c>
       <c r="D55" t="n">
-        <v>-431</v>
+        <v>-476</v>
       </c>
       <c r="E55" t="n">
-        <v>900</v>
+        <v>-749</v>
       </c>
       <c r="F55" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>26</v>
+        <v>-1</v>
       </c>
       <c r="H55" t="n">
-        <v>-43</v>
+        <v>19</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3187,49 +3187,49 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K55" t="n">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M55" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>億泰</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>67</v>
+        <v>254</v>
       </c>
       <c r="D56" t="n">
-        <v>-711</v>
+        <v>-525</v>
       </c>
       <c r="E56" t="n">
-        <v>-2507</v>
+        <v>-1201</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>883</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>5834</v>
       </c>
       <c r="H56" t="n">
-        <v>220</v>
+        <v>-1915</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3242,45 +3242,45 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M56" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>387</v>
+        <v>262</v>
       </c>
       <c r="D57" t="n">
-        <v>-753</v>
+        <v>-674</v>
       </c>
       <c r="E57" t="n">
-        <v>285</v>
+        <v>-1613</v>
       </c>
       <c r="F57" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>893</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3289,49 +3289,49 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K57" t="n">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M57" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>729</v>
+        <v>-3721</v>
       </c>
       <c r="D58" t="n">
-        <v>-811</v>
+        <v>-699</v>
       </c>
       <c r="E58" t="n">
-        <v>-2548</v>
+        <v>-3404</v>
       </c>
       <c r="F58" t="n">
-        <v>706</v>
+        <v>2966</v>
       </c>
       <c r="G58" t="n">
-        <v>5808</v>
+        <v>3989</v>
       </c>
       <c r="H58" t="n">
-        <v>-2051</v>
+        <v>-1127</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3340,100 +3340,100 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K58" t="n">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>-296</v>
+        <v>-534</v>
       </c>
       <c r="D59" t="n">
-        <v>-818</v>
+        <v>-854</v>
       </c>
       <c r="E59" t="n">
-        <v>-1057</v>
+        <v>-2602</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
       </c>
       <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1332</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>78</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M59" t="n">
         <v>-1</v>
-      </c>
-      <c r="H59" t="n">
-        <v>18</v>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K59" t="n">
-        <v>86</v>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>📉 減速</t>
-        </is>
-      </c>
-      <c r="M59" t="n">
-        <v>-3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2234</v>
+        <v>205</v>
       </c>
       <c r="D60" t="n">
-        <v>-840</v>
+        <v>-857</v>
       </c>
       <c r="E60" t="n">
-        <v>689</v>
+        <v>-3911</v>
       </c>
       <c r="F60" t="n">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="G60" t="n">
-        <v>-30</v>
+        <v>-100</v>
       </c>
       <c r="H60" t="n">
-        <v>186</v>
+        <v>-13</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3442,49 +3442,49 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K60" t="n">
-        <v>32</v>
+        <v>96</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M60" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-800</v>
+        <v>865</v>
       </c>
       <c r="D61" t="n">
-        <v>-929</v>
+        <v>-862</v>
       </c>
       <c r="E61" t="n">
-        <v>-2083</v>
+        <v>1541</v>
       </c>
       <c r="F61" t="n">
-        <v>2795</v>
+        <v>38</v>
       </c>
       <c r="G61" t="n">
-        <v>3804</v>
+        <v>886</v>
       </c>
       <c r="H61" t="n">
-        <v>-1190</v>
+        <v>42</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3497,45 +3497,45 @@
         </is>
       </c>
       <c r="K61" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M61" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-91</v>
+        <v>1748</v>
       </c>
       <c r="D62" t="n">
-        <v>-956</v>
+        <v>-894</v>
       </c>
       <c r="E62" t="n">
-        <v>226</v>
+        <v>323</v>
       </c>
       <c r="F62" t="n">
-        <v>-588</v>
+        <v>57</v>
       </c>
       <c r="G62" t="n">
-        <v>-1078</v>
+        <v>-18</v>
       </c>
       <c r="H62" t="n">
-        <v>-71</v>
+        <v>185</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3544,19 +3544,19 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K62" t="n">
-        <v>96</v>
+        <v>32</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M62" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="63">
@@ -3571,22 +3571,22 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>216</v>
+        <v>270</v>
       </c>
       <c r="D63" t="n">
-        <v>-1047</v>
+        <v>-1032</v>
       </c>
       <c r="E63" t="n">
-        <v>-840</v>
+        <v>-68</v>
       </c>
       <c r="F63" t="n">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="G63" t="n">
-        <v>1498</v>
+        <v>1523</v>
       </c>
       <c r="H63" t="n">
-        <v>-42</v>
+        <v>-46</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3613,31 +3613,31 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>鑫龍騰</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>19</v>
+        <v>204</v>
       </c>
       <c r="D64" t="n">
-        <v>-1094</v>
+        <v>-1170</v>
       </c>
       <c r="E64" t="n">
-        <v>-2923</v>
+        <v>-2712</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>-102</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-43</v>
+        <v>-0</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3646,49 +3646,49 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K64" t="n">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-1</v>
+        <v>102</v>
       </c>
       <c r="D65" t="n">
-        <v>-1162</v>
+        <v>-1277</v>
       </c>
       <c r="E65" t="n">
-        <v>-1964</v>
+        <v>-892</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>-233</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>-965</v>
       </c>
       <c r="H65" t="n">
-        <v>12</v>
+        <v>-69</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3697,49 +3697,49 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K65" t="n">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M65" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>鑫龍騰</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>210</v>
+        <v>-43779</v>
       </c>
       <c r="D66" t="n">
-        <v>-1413</v>
+        <v>-1281</v>
       </c>
       <c r="E66" t="n">
-        <v>-2838</v>
+        <v>-3429</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>23673</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>29975</v>
       </c>
       <c r="H66" t="n">
-        <v>-0</v>
+        <v>775</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3748,100 +3748,88 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K66" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>388</v>
+        <v>203</v>
       </c>
       <c r="D67" t="n">
-        <v>-1909</v>
+        <v>-1842</v>
       </c>
       <c r="E67" t="n">
-        <v>-7324</v>
+        <v>-4003</v>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
+        <v>-1575</v>
       </c>
       <c r="G67" t="n">
-        <v>76</v>
+        <v>-170</v>
       </c>
       <c r="H67" t="n">
-        <v>-1472</v>
+        <v>40</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K67" t="n">
-        <v>65</v>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>🐌 龜速</t>
-        </is>
-      </c>
-      <c r="M67" t="n">
-        <v>-2</v>
-      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-1614</v>
+        <v>84</v>
       </c>
       <c r="D68" t="n">
-        <v>-2021</v>
+        <v>-2207</v>
       </c>
       <c r="E68" t="n">
-        <v>1157</v>
+        <v>-7557</v>
       </c>
       <c r="F68" t="n">
-        <v>-735</v>
+        <v>-756</v>
       </c>
       <c r="G68" t="n">
-        <v>782</v>
+        <v>-1448</v>
       </c>
       <c r="H68" t="n">
-        <v>239</v>
+        <v>-17</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3850,49 +3838,49 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K68" t="n">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M68" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>湧德</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-124</v>
+        <v>2217</v>
       </c>
       <c r="D69" t="n">
-        <v>-2114</v>
+        <v>-2347</v>
       </c>
       <c r="E69" t="n">
-        <v>3369</v>
+        <v>-3325</v>
       </c>
       <c r="F69" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>-360</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>297</v>
+        <v>-295</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3901,88 +3889,100 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K69" t="n">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M69" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-295</v>
+        <v>-1743</v>
       </c>
       <c r="D70" t="n">
-        <v>-2560</v>
+        <v>-2352</v>
       </c>
       <c r="E70" t="n">
-        <v>-6156</v>
+        <v>-30</v>
       </c>
       <c r="F70" t="n">
-        <v>-1573</v>
+        <v>-726</v>
       </c>
       <c r="G70" t="n">
-        <v>405</v>
+        <v>801</v>
       </c>
       <c r="H70" t="n">
-        <v>34</v>
+        <v>359</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
           <t>🟠 減碼</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>51</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M70" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1346</v>
+        <v>18</v>
       </c>
       <c r="D71" t="n">
-        <v>-2594</v>
+        <v>-2544</v>
       </c>
       <c r="E71" t="n">
-        <v>-4099</v>
+        <v>-7308</v>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H71" t="n">
-        <v>-376</v>
+        <v>-1235</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -3991,15 +3991,15 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K71" t="n">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M71" t="n">
@@ -4009,31 +4009,31 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-132</v>
+        <v>-522</v>
       </c>
       <c r="D72" t="n">
-        <v>-2809</v>
+        <v>-2609</v>
       </c>
       <c r="E72" t="n">
-        <v>-7657</v>
+        <v>917</v>
       </c>
       <c r="F72" t="n">
-        <v>-580</v>
+        <v>115</v>
       </c>
       <c r="G72" t="n">
-        <v>-1239</v>
+        <v>-206</v>
       </c>
       <c r="H72" t="n">
-        <v>-62</v>
+        <v>241</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -4042,11 +4042,11 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K72" t="n">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -4054,37 +4054,37 @@
         </is>
       </c>
       <c r="M72" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-3341</v>
+        <v>-541</v>
       </c>
       <c r="D73" t="n">
-        <v>-3305</v>
+        <v>-2842</v>
       </c>
       <c r="E73" t="n">
-        <v>-3057</v>
+        <v>-11554</v>
       </c>
       <c r="F73" t="n">
-        <v>1</v>
+        <v>214</v>
       </c>
       <c r="G73" t="n">
-        <v>1</v>
+        <v>202</v>
       </c>
       <c r="H73" t="n">
-        <v>-1058</v>
+        <v>27</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -4093,19 +4093,19 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K73" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M73" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="74">
@@ -4120,22 +4120,22 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>51</v>
+        <v>-17</v>
       </c>
       <c r="D74" t="n">
-        <v>-3383</v>
+        <v>-2903</v>
       </c>
       <c r="E74" t="n">
-        <v>6581</v>
+        <v>5132</v>
       </c>
       <c r="F74" t="n">
-        <v>-435</v>
+        <v>-177</v>
       </c>
       <c r="G74" t="n">
-        <v>-892</v>
+        <v>-1277</v>
       </c>
       <c r="H74" t="n">
-        <v>-85</v>
+        <v>-93</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -4162,82 +4162,82 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>-706</v>
+        <v>-1151</v>
       </c>
       <c r="D75" t="n">
-        <v>-3879</v>
+        <v>-3202</v>
       </c>
       <c r="E75" t="n">
-        <v>-19045</v>
+        <v>-2686</v>
       </c>
       <c r="F75" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1362</v>
+      </c>
+      <c r="H75" t="n">
+        <v>-678</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>🟠 減碼</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>64</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M75" t="n">
         <v>1</v>
-      </c>
-      <c r="G75" t="n">
-        <v>284</v>
-      </c>
-      <c r="H75" t="n">
-        <v>-125</v>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>🟠 減碼</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K75" t="n">
-        <v>78</v>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>📉 減速</t>
-        </is>
-      </c>
-      <c r="M75" t="n">
-        <v>-3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-3918</v>
+        <v>-1952</v>
       </c>
       <c r="D76" t="n">
-        <v>-4011</v>
+        <v>-3467</v>
       </c>
       <c r="E76" t="n">
-        <v>2277</v>
+        <v>-381</v>
       </c>
       <c r="F76" t="n">
-        <v>-2302</v>
+        <v>1</v>
       </c>
       <c r="G76" t="n">
-        <v>-8647</v>
+        <v>1</v>
       </c>
       <c r="H76" t="n">
-        <v>-506</v>
+        <v>-998</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -4246,19 +4246,19 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K76" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="77">
@@ -4273,22 +4273,22 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-339</v>
+        <v>222</v>
       </c>
       <c r="D77" t="n">
-        <v>-4549</v>
+        <v>-3990</v>
       </c>
       <c r="E77" t="n">
-        <v>-3553</v>
+        <v>-3889</v>
       </c>
       <c r="F77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G77" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H77" t="n">
-        <v>-480</v>
+        <v>-357</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -4315,31 +4315,31 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>129</v>
+        <v>177</v>
       </c>
       <c r="D78" t="n">
-        <v>-4619</v>
+        <v>-4447</v>
       </c>
       <c r="E78" t="n">
-        <v>-4398</v>
+        <v>-18947</v>
       </c>
       <c r="F78" t="n">
-        <v>407</v>
+        <v>2</v>
       </c>
       <c r="G78" t="n">
-        <v>3380</v>
+        <v>285</v>
       </c>
       <c r="H78" t="n">
-        <v>-418</v>
+        <v>17</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -4348,19 +4348,19 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K78" t="n">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M78" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="79">
@@ -4375,22 +4375,22 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-1599</v>
+        <v>-1636</v>
       </c>
       <c r="D79" t="n">
-        <v>-4637</v>
+        <v>-4588</v>
       </c>
       <c r="E79" t="n">
-        <v>-8760</v>
+        <v>-8768</v>
       </c>
       <c r="F79" t="n">
-        <v>1683</v>
+        <v>1985</v>
       </c>
       <c r="G79" t="n">
-        <v>622</v>
+        <v>871</v>
       </c>
       <c r="H79" t="n">
-        <v>-156</v>
+        <v>-161</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -4411,88 +4411,88 @@
         </is>
       </c>
       <c r="M79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>-804</v>
+        <v>-152</v>
       </c>
       <c r="D80" t="n">
-        <v>-4808</v>
+        <v>-5200</v>
       </c>
       <c r="E80" t="n">
-        <v>-8693</v>
+        <v>-4497</v>
       </c>
       <c r="F80" t="n">
-        <v>64</v>
+        <v>304</v>
       </c>
       <c r="G80" t="n">
+        <v>3373</v>
+      </c>
+      <c r="H80" t="n">
+        <v>-414</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>🟠 減碼</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
         <v>52</v>
       </c>
-      <c r="H80" t="n">
-        <v>8</v>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>🟠 減碼</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K80" t="n">
-        <v>69</v>
-      </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M80" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-1237</v>
+        <v>-372</v>
       </c>
       <c r="D81" t="n">
-        <v>-4942</v>
+        <v>-5206</v>
       </c>
       <c r="E81" t="n">
-        <v>-7160</v>
+        <v>-5621</v>
       </c>
       <c r="F81" t="n">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="G81" t="n">
-        <v>1401</v>
+        <v>1592</v>
       </c>
       <c r="H81" t="n">
-        <v>-638</v>
+        <v>-95</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4501,11 +4501,11 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K81" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -4513,37 +4513,37 @@
         </is>
       </c>
       <c r="M81" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-1382</v>
+        <v>1694</v>
       </c>
       <c r="D82" t="n">
-        <v>-5669</v>
+        <v>-5368</v>
       </c>
       <c r="E82" t="n">
-        <v>-5897</v>
+        <v>-2302</v>
       </c>
       <c r="F82" t="n">
-        <v>2</v>
+        <v>226</v>
       </c>
       <c r="G82" t="n">
-        <v>1523</v>
+        <v>-89</v>
       </c>
       <c r="H82" t="n">
-        <v>-90</v>
+        <v>-305</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -4552,11 +4552,11 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K82" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -4564,37 +4564,37 @@
         </is>
       </c>
       <c r="M82" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>76</v>
+        <v>-1078</v>
       </c>
       <c r="D83" t="n">
-        <v>-6097</v>
+        <v>-5614</v>
       </c>
       <c r="E83" t="n">
-        <v>-2639</v>
+        <v>-9481</v>
       </c>
       <c r="F83" t="n">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>-96</v>
+        <v>-8</v>
       </c>
       <c r="H83" t="n">
-        <v>-587</v>
+        <v>-602</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -4603,19 +4603,19 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K83" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M83" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="84">
@@ -4630,22 +4630,22 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-2239</v>
+        <v>-2057</v>
       </c>
       <c r="D84" t="n">
-        <v>-6183</v>
+        <v>-5760</v>
       </c>
       <c r="E84" t="n">
-        <v>-11635</v>
+        <v>-12511</v>
       </c>
       <c r="F84" t="n">
-        <v>-354</v>
+        <v>-392</v>
       </c>
       <c r="G84" t="n">
-        <v>-105</v>
+        <v>-191</v>
       </c>
       <c r="H84" t="n">
-        <v>-397</v>
+        <v>-197</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -4672,31 +4672,31 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>鈊象</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>-3416</v>
+        <v>-1234</v>
       </c>
       <c r="D85" t="n">
-        <v>-7034</v>
+        <v>-6582</v>
       </c>
       <c r="E85" t="n">
-        <v>-22161</v>
+        <v>-12264</v>
       </c>
       <c r="F85" t="n">
-        <v>-727</v>
+        <v>4748</v>
       </c>
       <c r="G85" t="n">
-        <v>-3229</v>
+        <v>11692</v>
       </c>
       <c r="H85" t="n">
-        <v>-2442</v>
+        <v>-145</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -4709,11 +4709,11 @@
         </is>
       </c>
       <c r="K85" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M85" t="n">
@@ -4723,82 +4723,82 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-607</v>
+        <v>-2046</v>
       </c>
       <c r="D86" t="n">
-        <v>-7145</v>
+        <v>-7792</v>
       </c>
       <c r="E86" t="n">
-        <v>-8543</v>
+        <v>-5365</v>
       </c>
       <c r="F86" t="n">
+        <v>-1430</v>
+      </c>
+      <c r="G86" t="n">
+        <v>-8609</v>
+      </c>
+      <c r="H86" t="n">
+        <v>16</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>🟠 減碼</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>44</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>📉 減速</t>
+        </is>
+      </c>
+      <c r="M86" t="n">
         <v>0</v>
-      </c>
-      <c r="G86" t="n">
-        <v>-8</v>
-      </c>
-      <c r="H86" t="n">
-        <v>-1352</v>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>🟠 減碼</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K86" t="n">
-        <v>79</v>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>🛬 穩定</t>
-        </is>
-      </c>
-      <c r="M86" t="n">
-        <v>-2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>-1325</v>
+        <v>-886</v>
       </c>
       <c r="D87" t="n">
-        <v>-7578</v>
+        <v>-8669</v>
       </c>
       <c r="E87" t="n">
-        <v>-11028</v>
+        <v>29461</v>
       </c>
       <c r="F87" t="n">
-        <v>4622</v>
+        <v>-71</v>
       </c>
       <c r="G87" t="n">
-        <v>13082</v>
+        <v>-11067</v>
       </c>
       <c r="H87" t="n">
-        <v>-32</v>
+        <v>-544</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -4807,49 +4807,49 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K87" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M87" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>立隆電</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>331</v>
+        <v>-7499</v>
       </c>
       <c r="D88" t="n">
-        <v>-7774</v>
+        <v>-9450</v>
       </c>
       <c r="E88" t="n">
-        <v>26716</v>
+        <v>-15102</v>
       </c>
       <c r="F88" t="n">
-        <v>-86</v>
+        <v>3840</v>
       </c>
       <c r="G88" t="n">
-        <v>-11036</v>
+        <v>8208</v>
       </c>
       <c r="H88" t="n">
-        <v>-714</v>
+        <v>107</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -4858,49 +4858,49 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K88" t="n">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M88" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-4693</v>
+        <v>-3092</v>
       </c>
       <c r="D89" t="n">
-        <v>-7796</v>
+        <v>-9656</v>
       </c>
       <c r="E89" t="n">
-        <v>-13152</v>
+        <v>-28342</v>
       </c>
       <c r="F89" t="n">
-        <v>5646</v>
+        <v>-224</v>
       </c>
       <c r="G89" t="n">
-        <v>8206</v>
+        <v>-2905</v>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>-2248</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4913,7 +4913,7 @@
         </is>
       </c>
       <c r="K89" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -4921,37 +4921,37 @@
         </is>
       </c>
       <c r="M89" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>-19001</v>
+        <v>783</v>
       </c>
       <c r="D90" t="n">
-        <v>-12948</v>
+        <v>-13492</v>
       </c>
       <c r="E90" t="n">
-        <v>124968</v>
+        <v>-67538</v>
       </c>
       <c r="F90" t="n">
-        <v>24054</v>
+        <v>608</v>
       </c>
       <c r="G90" t="n">
-        <v>19887</v>
+        <v>8103</v>
       </c>
       <c r="H90" t="n">
-        <v>19609</v>
+        <v>-293</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -4960,11 +4960,11 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K90" t="n">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -4972,37 +4972,37 @@
         </is>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>-5328</v>
+        <v>-9774</v>
       </c>
       <c r="D91" t="n">
-        <v>-15891</v>
+        <v>-16113</v>
       </c>
       <c r="E91" t="n">
-        <v>-45301</v>
+        <v>3009</v>
       </c>
       <c r="F91" t="n">
-        <v>2463</v>
+        <v>3713</v>
       </c>
       <c r="G91" t="n">
-        <v>22748</v>
+        <v>12988</v>
       </c>
       <c r="H91" t="n">
-        <v>-1911</v>
+        <v>-22</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -5011,49 +5011,49 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K91" t="n">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M91" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>-1607</v>
+        <v>-2545</v>
       </c>
       <c r="D92" t="n">
-        <v>-16185</v>
+        <v>-17025</v>
       </c>
       <c r="E92" t="n">
-        <v>-67435</v>
+        <v>-45192</v>
       </c>
       <c r="F92" t="n">
-        <v>980</v>
+        <v>1767</v>
       </c>
       <c r="G92" t="n">
-        <v>15646</v>
+        <v>22841</v>
       </c>
       <c r="H92" t="n">
-        <v>-335</v>
+        <v>-1129</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -5062,49 +5062,49 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K92" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M92" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>-12828</v>
+        <v>-7836</v>
       </c>
       <c r="D93" t="n">
-        <v>-17393</v>
+        <v>-18408</v>
       </c>
       <c r="E93" t="n">
-        <v>3961</v>
+        <v>-18183</v>
       </c>
       <c r="F93" t="n">
-        <v>5902</v>
+        <v>6388</v>
       </c>
       <c r="G93" t="n">
-        <v>13010</v>
+        <v>18303</v>
       </c>
       <c r="H93" t="n">
-        <v>-55</v>
+        <v>-651</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -5113,11 +5113,11 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K93" t="n">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -5131,31 +5131,31 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-6915</v>
+        <v>-1868</v>
       </c>
       <c r="D94" t="n">
-        <v>-18949</v>
+        <v>-21207</v>
       </c>
       <c r="E94" t="n">
-        <v>-10818</v>
+        <v>-29704</v>
       </c>
       <c r="F94" t="n">
-        <v>6363</v>
+        <v>-338</v>
       </c>
       <c r="G94" t="n">
-        <v>20179</v>
+        <v>-11905</v>
       </c>
       <c r="H94" t="n">
-        <v>-625</v>
+        <v>-2059</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -5164,49 +5164,49 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K94" t="n">
-        <v>61</v>
+        <v>100</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M94" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>-7784</v>
+        <v>-24206</v>
       </c>
       <c r="D95" t="n">
-        <v>-24005</v>
+        <v>-22579</v>
       </c>
       <c r="E95" t="n">
-        <v>-29693</v>
+        <v>119088</v>
       </c>
       <c r="F95" t="n">
-        <v>-933</v>
+        <v>-13136</v>
       </c>
       <c r="G95" t="n">
-        <v>-11516</v>
+        <v>65569</v>
       </c>
       <c r="H95" t="n">
-        <v>-2060</v>
+        <v>-6176</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -5215,15 +5215,15 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K95" t="n">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M95" t="n">
@@ -5233,31 +5233,31 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>-17323</v>
+        <v>-15093</v>
       </c>
       <c r="D96" t="n">
-        <v>-26508</v>
+        <v>-23657</v>
       </c>
       <c r="E96" t="n">
-        <v>142209</v>
+        <v>102056</v>
       </c>
       <c r="F96" t="n">
-        <v>-3047</v>
+        <v>24363</v>
       </c>
       <c r="G96" t="n">
-        <v>71628</v>
+        <v>23855</v>
       </c>
       <c r="H96" t="n">
-        <v>-9000</v>
+        <v>21376</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -5266,11 +5266,11 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K96" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         </is>
       </c>
       <c r="M96" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="97">
@@ -5293,22 +5293,22 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1188</v>
+        <v>8223</v>
       </c>
       <c r="D97" t="n">
-        <v>-52374</v>
+        <v>-50738</v>
       </c>
       <c r="E97" t="n">
-        <v>-74863</v>
+        <v>-85025</v>
       </c>
       <c r="F97" t="n">
-        <v>-11840</v>
+        <v>-12923</v>
       </c>
       <c r="G97" t="n">
-        <v>33721</v>
+        <v>32843</v>
       </c>
       <c r="H97" t="n">
-        <v>-1298</v>
+        <v>-1296</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -5344,22 +5344,22 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-46281</v>
+        <v>-48312</v>
       </c>
       <c r="D98" t="n">
-        <v>-54978</v>
+        <v>-59921</v>
       </c>
       <c r="E98" t="n">
-        <v>-116120</v>
+        <v>-131627</v>
       </c>
       <c r="F98" t="n">
-        <v>17617</v>
+        <v>18181</v>
       </c>
       <c r="G98" t="n">
-        <v>20761</v>
+        <v>24311</v>
       </c>
       <c r="H98" t="n">
-        <v>4554</v>
+        <v>3588</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="M98" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="99">
@@ -5395,22 +5395,22 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>-1319</v>
+        <v>1127</v>
       </c>
       <c r="D99" t="n">
-        <v>-89742</v>
+        <v>-67101</v>
       </c>
       <c r="E99" t="n">
-        <v>-259716</v>
+        <v>-271877</v>
       </c>
       <c r="F99" t="n">
-        <v>12377</v>
+        <v>11738</v>
       </c>
       <c r="G99" t="n">
-        <v>118771</v>
+        <v>100921</v>
       </c>
       <c r="H99" t="n">
-        <v>1239</v>
+        <v>1551</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -5446,22 +5446,22 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>-22473</v>
+        <v>-20729</v>
       </c>
       <c r="D100" t="n">
-        <v>-120324</v>
+        <v>-115021</v>
       </c>
       <c r="E100" t="n">
-        <v>-267341</v>
+        <v>-279055</v>
       </c>
       <c r="F100" t="n">
-        <v>7332</v>
+        <v>7419</v>
       </c>
       <c r="G100" t="n">
-        <v>10672</v>
+        <v>8592</v>
       </c>
       <c r="H100" t="n">
-        <v>7672</v>
+        <v>7808</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -5497,22 +5497,22 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-38177</v>
+        <v>-39125</v>
       </c>
       <c r="D101" t="n">
-        <v>-129839</v>
+        <v>-133415</v>
       </c>
       <c r="E101" t="n">
-        <v>-163989</v>
+        <v>-164333</v>
       </c>
       <c r="F101" t="n">
-        <v>26213</v>
+        <v>25966</v>
       </c>
       <c r="G101" t="n">
-        <v>123785</v>
+        <v>127127</v>
       </c>
       <c r="H101" t="n">
-        <v>6201</v>
+        <v>5999</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -5548,22 +5548,22 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>-42264</v>
+        <v>-34135</v>
       </c>
       <c r="D102" t="n">
-        <v>-199254</v>
+        <v>-175849</v>
       </c>
       <c r="E102" t="n">
-        <v>107517</v>
+        <v>33355</v>
       </c>
       <c r="F102" t="n">
-        <v>-32107</v>
+        <v>-58236</v>
       </c>
       <c r="G102" t="n">
-        <v>138293</v>
+        <v>129701</v>
       </c>
       <c r="H102" t="n">
-        <v>-3564</v>
+        <v>-177</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -5599,22 +5599,22 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>-51598</v>
+        <v>-35494</v>
       </c>
       <c r="D103" t="n">
-        <v>-202897</v>
+        <v>-213241</v>
       </c>
       <c r="E103" t="n">
-        <v>-5345</v>
+        <v>-70481</v>
       </c>
       <c r="F103" t="n">
-        <v>27258</v>
+        <v>28201</v>
       </c>
       <c r="G103" t="n">
-        <v>51698</v>
+        <v>56098</v>
       </c>
       <c r="H103" t="n">
-        <v>-70</v>
+        <v>605</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -5650,22 +5650,22 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>-99074</v>
+        <v>-68160</v>
       </c>
       <c r="D104" t="n">
-        <v>-218817</v>
+        <v>-214912</v>
       </c>
       <c r="E104" t="n">
-        <v>500479</v>
+        <v>475826</v>
       </c>
       <c r="F104" t="n">
-        <v>2963</v>
+        <v>2397</v>
       </c>
       <c r="G104" t="n">
-        <v>1640</v>
+        <v>2481</v>
       </c>
       <c r="H104" t="n">
-        <v>-7852</v>
+        <v>-4617</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -5700,7 +5700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5743,203 +5743,203 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -3,167 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 601 千股)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-800201</v>
+        <v>83549</v>
       </c>
       <c r="D2" t="n">
-        <v>-928939</v>
+        <v>-2207485</v>
       </c>
       <c r="E2" t="n">
-        <v>2221404</v>
+        <v>-132094</v>
       </c>
       <c r="F2" t="n">
-        <v>2237966</v>
+        <v>-2808924</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>勤誠</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,079 千股)</t>
+          <t>📈 20d 巨變(加碼 7 千股)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>699280</v>
+        <v>484836</v>
       </c>
       <c r="D3" t="n">
-        <v>2747557</v>
+        <v>1543754</v>
       </c>
       <c r="E3" t="n">
-        <v>1015205</v>
+        <v>1297337</v>
       </c>
       <c r="F3" t="n">
-        <v>3826862</v>
+        <v>1536366</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>健策</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -89 千股)</t>
+          <t>📈 20d 巨變(加碼 799 千股)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>83675</v>
+        <v>3287626</v>
       </c>
       <c r="D4" t="n">
-        <v>1774295</v>
+        <v>1787781</v>
       </c>
       <c r="E4" t="n">
-        <v>474598</v>
+        <v>938605</v>
       </c>
       <c r="F4" t="n">
-        <v>1863124</v>
+        <v>988549</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>奇鋐</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 119 千股)</t>
+          <t>📈 20d 巨變(加碼 230 千股)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-132094</v>
+        <v>-3720877</v>
       </c>
       <c r="D5" t="n">
-        <v>-2808924</v>
+        <v>-698890</v>
       </c>
       <c r="E5" t="n">
-        <v>-709616</v>
+        <v>-800201</v>
       </c>
       <c r="F5" t="n">
-        <v>-2928253</v>
+        <v>-928939</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>亞翔</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,280 千股)</t>
+          <t>📈 20d 巨變(加碼 317 千股)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>938605</v>
+        <v>320656</v>
       </c>
       <c r="D6" t="n">
-        <v>988549</v>
+        <v>2090908</v>
       </c>
       <c r="E6" t="n">
-        <v>478408</v>
+        <v>83675</v>
       </c>
       <c r="F6" t="n">
-        <v>-291379</v>
+        <v>1774295</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>台光電</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 385 千股)</t>
+          <t>📈 20d 巨變(加碼 491 千股)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1297337</v>
+        <v>435685</v>
       </c>
       <c r="D7" t="n">
-        <v>1536366</v>
+        <v>3238964</v>
       </c>
       <c r="E7" t="n">
-        <v>1500819</v>
+        <v>699280</v>
       </c>
       <c r="F7" t="n">
-        <v>1151151</v>
+        <v>2747557</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>高力</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -225 千股)</t>
+          <t>📈 20d 巨變(加碼 15 千股)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>106496</v>
+        <v>269778</v>
       </c>
       <c r="D8" t="n">
-        <v>5704945</v>
+        <v>-1032083</v>
       </c>
       <c r="E8" t="n">
-        <v>367992</v>
+        <v>216158</v>
       </c>
       <c r="F8" t="n">
-        <v>5930008</v>
+        <v>-1046867</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>旺矽</t>
         </is>
       </c>
     </row>
@@ -5951,20 +5951,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -584 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -321 千股)</t>
         </is>
       </c>
       <c r="C9" t="n">
+        <v>101559</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-1276814</v>
+      </c>
+      <c r="E9" t="n">
         <v>-91018</v>
       </c>
-      <c r="D9" t="n">
+      <c r="F9" t="n">
         <v>-956229</v>
-      </c>
-      <c r="E9" t="n">
-        <v>-357307</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-371924</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -5975,29 +5975,29 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 192 千股)</t>
+          <t>📈 20d 巨變(加碼 40 千股)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>216158</v>
+        <v>20061</v>
       </c>
       <c r="D10" t="n">
-        <v>-1046867</v>
+        <v>5745220</v>
       </c>
       <c r="E10" t="n">
-        <v>-91346</v>
+        <v>106496</v>
       </c>
       <c r="F10" t="n">
-        <v>-1239231</v>
+        <v>5704945</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>致茂</t>
         </is>
       </c>
     </row>
@@ -6009,20 +6009,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 36 千股)</t>
+          <t>📈 20d 巨變(加碼 41 千股)</t>
         </is>
       </c>
       <c r="C11" t="n">
+        <v>331609</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1306969</v>
+      </c>
+      <c r="E11" t="n">
         <v>1219620</v>
       </c>
-      <c r="D11" t="n">
+      <c r="F11" t="n">
         <v>1265482</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1225843</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1229271</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -6033,203 +6033,203 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -997 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 559 千股)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-22473322</v>
+        <v>221635</v>
       </c>
       <c r="D12" t="n">
-        <v>-120324084</v>
+        <v>-3990364</v>
       </c>
       <c r="E12" t="n">
-        <v>-16323468</v>
+        <v>-339140</v>
       </c>
       <c r="F12" t="n">
-        <v>-119326610</v>
+        <v>-4549268</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>雙鴻</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -2,524 千股)</t>
+          <t>📈 20d 巨變(加碼 5,303 千股)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-339140</v>
+        <v>-20728692</v>
       </c>
       <c r="D13" t="n">
-        <v>-4549268</v>
+        <v>-115021028</v>
       </c>
       <c r="E13" t="n">
-        <v>-1182410</v>
+        <v>-22473322</v>
       </c>
       <c r="F13" t="n">
-        <v>-2025299</v>
+        <v>-120324084</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,337 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 23 千股)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-7783974</v>
+        <v>456057</v>
       </c>
       <c r="D14" t="n">
-        <v>-24004830</v>
+        <v>-249653</v>
       </c>
       <c r="E14" t="n">
-        <v>-6430743</v>
+        <v>-958250</v>
       </c>
       <c r="F14" t="n">
-        <v>-22668318</v>
+        <v>-272605</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>佳必琪</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -350 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,152 千股)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>386508</v>
+        <v>664569</v>
       </c>
       <c r="D15" t="n">
-        <v>-753279</v>
+        <v>1878508</v>
       </c>
       <c r="E15" t="n">
-        <v>677088</v>
+        <v>1774135</v>
       </c>
       <c r="F15" t="n">
-        <v>-402934</v>
+        <v>3030859</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>辛耘</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,850 千股)</t>
+          <t>📈 20d 巨變(加碼 2,798 千股)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5706754</v>
+        <v>-1867636</v>
       </c>
       <c r="D16" t="n">
-        <v>10548997</v>
+        <v>-21206568</v>
       </c>
       <c r="E16" t="n">
-        <v>3268019</v>
+        <v>-7783974</v>
       </c>
       <c r="F16" t="n">
-        <v>8699075</v>
+        <v>-24004830</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>台達電</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -400 千股)</t>
+          <t>📈 20d 巨變(加碼 540 千股)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1774135</v>
+        <v>5709338</v>
       </c>
       <c r="D17" t="n">
-        <v>3030859</v>
+        <v>11088894</v>
       </c>
       <c r="E17" t="n">
-        <v>1619690</v>
+        <v>5706754</v>
       </c>
       <c r="F17" t="n">
-        <v>3431095</v>
+        <v>10548997</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>健鼎</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,831 千股)</t>
+          <t>📉 20d 巨變(減碼 -109 千股)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-958250</v>
+        <v>864669</v>
       </c>
       <c r="D18" t="n">
-        <v>-272605</v>
+        <v>-862007</v>
       </c>
       <c r="E18" t="n">
-        <v>-2118763</v>
+        <v>386508</v>
       </c>
       <c r="F18" t="n">
-        <v>-2103936</v>
+        <v>-753279</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>帆宣</t>
         </is>
       </c>
     </row>
@@ -6241,20 +6241,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -31 千股)</t>
+          <t>📈 20d 巨變(加碼 150 千股)</t>
         </is>
       </c>
       <c r="C19" t="n">
+        <v>-240219</v>
+      </c>
+      <c r="D19" t="n">
+        <v>286741</v>
+      </c>
+      <c r="E19" t="n">
         <v>-176894</v>
       </c>
-      <c r="D19" t="n">
+      <c r="F19" t="n">
         <v>136336</v>
-      </c>
-      <c r="E19" t="n">
-        <v>8324</v>
-      </c>
-      <c r="F19" t="n">
-        <v>167197</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -6270,20 +6270,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -449 千股)</t>
+          <t>📉 20d 巨變(減碼 -667 千股)</t>
         </is>
       </c>
       <c r="C20" t="n">
+        <v>-2406640</v>
+      </c>
+      <c r="D20" t="n">
+        <v>525639</v>
+      </c>
+      <c r="E20" t="n">
         <v>-2200986</v>
       </c>
-      <c r="D20" t="n">
+      <c r="F20" t="n">
         <v>1192438</v>
-      </c>
-      <c r="E20" t="n">
-        <v>-1240239</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1641824</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -6294,58 +6294,58 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 4,442 千股)</t>
+          <t>📈 20d 巨變(加碼 287 千股)</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-5327595</v>
+        <v>-255121</v>
       </c>
       <c r="D21" t="n">
-        <v>-15891394</v>
+        <v>832654</v>
       </c>
       <c r="E21" t="n">
-        <v>-5855026</v>
+        <v>-205986</v>
       </c>
       <c r="F21" t="n">
-        <v>-20333622</v>
+        <v>545695</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>建榮</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -409 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,133 千股)</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-205986</v>
+        <v>-2544773</v>
       </c>
       <c r="D22" t="n">
-        <v>545695</v>
+        <v>-17024626</v>
       </c>
       <c r="E22" t="n">
-        <v>-468546</v>
+        <v>-5327595</v>
       </c>
       <c r="F22" t="n">
-        <v>955091</v>
+        <v>-15891394</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>中興電</t>
         </is>
       </c>
     </row>
@@ -6357,20 +6357,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -585 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -236 千股)</t>
         </is>
       </c>
       <c r="C23" t="n">
+        <v>-46203</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1343026</v>
+      </c>
+      <c r="E23" t="n">
         <v>21670</v>
       </c>
-      <c r="D23" t="n">
+      <c r="F23" t="n">
         <v>1578571</v>
-      </c>
-      <c r="E23" t="n">
-        <v>183148</v>
-      </c>
-      <c r="F23" t="n">
-        <v>2163246</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -6386,20 +6386,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 814 千股)</t>
+          <t>📈 20d 巨變(加碼 424 千股)</t>
         </is>
       </c>
       <c r="C24" t="n">
+        <v>-2057302</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-5759726</v>
+      </c>
+      <c r="E24" t="n">
         <v>-2239320</v>
       </c>
-      <c r="D24" t="n">
+      <c r="F24" t="n">
         <v>-6183357</v>
-      </c>
-      <c r="E24" t="n">
-        <v>-2482395</v>
-      </c>
-      <c r="F24" t="n">
-        <v>-6997483</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -6415,20 +6415,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -288 千股)</t>
+          <t>📉 20d 巨變(減碼 -331 千股)</t>
         </is>
       </c>
       <c r="C25" t="n">
+        <v>-1742870</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-2351989</v>
+      </c>
+      <c r="E25" t="n">
         <v>-1614307</v>
       </c>
-      <c r="D25" t="n">
+      <c r="F25" t="n">
         <v>-2021046</v>
-      </c>
-      <c r="E25" t="n">
-        <v>-2005703</v>
-      </c>
-      <c r="F25" t="n">
-        <v>-1732730</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -6444,20 +6444,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 12 千股)</t>
+          <t>📉 20d 巨變(減碼 -11 千股)</t>
         </is>
       </c>
       <c r="C26" t="n">
+        <v>7326</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-154963</v>
+      </c>
+      <c r="E26" t="n">
         <v>15070</v>
       </c>
-      <c r="D26" t="n">
+      <c r="F26" t="n">
         <v>-144136</v>
-      </c>
-      <c r="E26" t="n">
-        <v>13030</v>
-      </c>
-      <c r="F26" t="n">
-        <v>-156176</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -6468,29 +6468,29 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 598 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -459 千股)</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>682338</v>
+        <v>-457748</v>
       </c>
       <c r="D27" t="n">
-        <v>2923758</v>
+        <v>944413</v>
       </c>
       <c r="E27" t="n">
-        <v>207068</v>
+        <v>153502</v>
       </c>
       <c r="F27" t="n">
-        <v>2325399</v>
+        <v>1403663</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>隆大</t>
         </is>
       </c>
     </row>
@@ -6502,20 +6502,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 34 千股)</t>
+          <t>📈 20d 巨變(加碼 13 千股)</t>
         </is>
       </c>
       <c r="C28" t="n">
+        <v>48693</v>
+      </c>
+      <c r="D28" t="n">
+        <v>369457</v>
+      </c>
+      <c r="E28" t="n">
         <v>49273</v>
       </c>
-      <c r="D28" t="n">
+      <c r="F28" t="n">
         <v>356037</v>
-      </c>
-      <c r="E28" t="n">
-        <v>88630</v>
-      </c>
-      <c r="F28" t="n">
-        <v>321994</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -6526,87 +6526,87 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -75 千股)</t>
+          <t>📈 20d 巨變(加碼 725 千股)</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>153502</v>
+        <v>1395204</v>
       </c>
       <c r="D29" t="n">
-        <v>1403663</v>
+        <v>3648892</v>
       </c>
       <c r="E29" t="n">
-        <v>343424</v>
+        <v>682338</v>
       </c>
       <c r="F29" t="n">
-        <v>1479161</v>
+        <v>2923758</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>零壹</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -500 千股)</t>
+          <t>📈 20d 巨變(加碼 246 千股)</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>76291</v>
+        <v>2217419</v>
       </c>
       <c r="D30" t="n">
-        <v>-6097204</v>
+        <v>-2347434</v>
       </c>
       <c r="E30" t="n">
-        <v>-913675</v>
+        <v>1346049</v>
       </c>
       <c r="F30" t="n">
-        <v>-5596978</v>
+        <v>-2593883</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>湧德</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -872 千股)</t>
+          <t>📈 20d 巨變(加碼 730 千股)</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1346049</v>
+        <v>1694120</v>
       </c>
       <c r="D31" t="n">
-        <v>-2593883</v>
+        <v>-5367585</v>
       </c>
       <c r="E31" t="n">
-        <v>734796</v>
+        <v>76291</v>
       </c>
       <c r="F31" t="n">
-        <v>-1721583</v>
+        <v>-6097204</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>建準</t>
         </is>
       </c>
     </row>
@@ -6618,20 +6618,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 753 千股)</t>
+          <t>📈 20d 巨變(加碼 502 千股)</t>
         </is>
       </c>
       <c r="C32" t="n">
+        <v>690556</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2234780</v>
+      </c>
+      <c r="E32" t="n">
         <v>434825</v>
       </c>
-      <c r="D32" t="n">
+      <c r="F32" t="n">
         <v>1733134</v>
-      </c>
-      <c r="E32" t="n">
-        <v>320599</v>
-      </c>
-      <c r="F32" t="n">
-        <v>979888</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -6642,87 +6642,87 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 10,412 千股)</t>
+          <t>📉 20d 巨變(減碼 -246 千股)</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-40076614</v>
+        <v>-456949</v>
       </c>
       <c r="D33" t="n">
-        <v>190400051</v>
+        <v>1054367</v>
       </c>
       <c r="E33" t="n">
-        <v>-19295293</v>
+        <v>-303075</v>
       </c>
       <c r="F33" t="n">
-        <v>179987736</v>
+        <v>1299977</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>寶雅</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,660 千股)</t>
+          <t>📈 20d 巨變(加碼 7,218 千股)</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-2594232</v>
+        <v>-52104977</v>
       </c>
       <c r="D34" t="n">
-        <v>1933566</v>
+        <v>197618224</v>
       </c>
       <c r="E34" t="n">
-        <v>-1185638</v>
+        <v>-40076614</v>
       </c>
       <c r="F34" t="n">
-        <v>3593460</v>
+        <v>190400051</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -30 千股)</t>
+          <t>📉 20d 巨變(減碼 -874 千股)</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-303075</v>
+        <v>-2232522</v>
       </c>
       <c r="D35" t="n">
-        <v>1299977</v>
+        <v>1059866</v>
       </c>
       <c r="E35" t="n">
-        <v>-177113</v>
+        <v>-2594232</v>
       </c>
       <c r="F35" t="n">
-        <v>1330293</v>
+        <v>1933566</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>寶雅</t>
+          <t>卜蜂</t>
         </is>
       </c>
     </row>
@@ -6734,20 +6734,20 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,091 千股)</t>
+          <t>📉 20d 巨變(減碼 -54 千股)</t>
         </is>
       </c>
       <c r="C36" t="n">
+        <v>1748454</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-894008</v>
+      </c>
+      <c r="E36" t="n">
         <v>2234168</v>
       </c>
-      <c r="D36" t="n">
+      <c r="F36" t="n">
         <v>-839539</v>
-      </c>
-      <c r="E36" t="n">
-        <v>1487478</v>
-      </c>
-      <c r="F36" t="n">
-        <v>-1930060</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -6763,20 +6763,20 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -56 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 342 千股)</t>
         </is>
       </c>
       <c r="C37" t="n">
+        <v>187331</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-475501</v>
+      </c>
+      <c r="E37" t="n">
         <v>-295750</v>
       </c>
-      <c r="D37" t="n">
+      <c r="F37" t="n">
         <v>-817582</v>
-      </c>
-      <c r="E37" t="n">
-        <v>-365030</v>
-      </c>
-      <c r="F37" t="n">
-        <v>-761791</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -6787,58 +6787,58 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -11 千股)</t>
+          <t>📈 20d 巨變(加碼 158 千股)</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>60749</v>
+        <v>-519407</v>
       </c>
       <c r="D38" t="n">
-        <v>588845</v>
+        <v>1121682</v>
       </c>
       <c r="E38" t="n">
-        <v>102372</v>
+        <v>-568650</v>
       </c>
       <c r="F38" t="n">
-        <v>600214</v>
+        <v>963359</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>智冠</t>
+          <t>八方雲集</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 21 千股)</t>
+          <t>📉 20d 巨變(減碼 -35 千股)</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1000</v>
+        <v>72356</v>
       </c>
       <c r="D39" t="n">
-        <v>-16000</v>
+        <v>-350985</v>
       </c>
       <c r="E39" t="n">
-        <v>1000</v>
+        <v>263221</v>
       </c>
       <c r="F39" t="n">
-        <v>-37000</v>
+        <v>-315671</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>方土霖</t>
+          <t>穎崴</t>
         </is>
       </c>
     </row>
@@ -6850,20 +6850,20 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -131 千股)</t>
+          <t>📈 20d 巨變(加碼 237 千股)</t>
         </is>
       </c>
       <c r="C40" t="n">
+        <v>205038</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-857067</v>
+      </c>
+      <c r="E40" t="n">
         <v>18543</v>
       </c>
-      <c r="D40" t="n">
+      <c r="F40" t="n">
         <v>-1093984</v>
-      </c>
-      <c r="E40" t="n">
-        <v>-58354</v>
-      </c>
-      <c r="F40" t="n">
-        <v>-963165</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -6874,58 +6874,58 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -133 千股)</t>
+          <t>📉 20d 巨變(減碼 -11,402 千股)</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-568650</v>
+        <v>-43778879</v>
       </c>
       <c r="D41" t="n">
-        <v>963359</v>
+        <v>-1280701</v>
       </c>
       <c r="E41" t="n">
-        <v>-295900</v>
+        <v>-36628981</v>
       </c>
       <c r="F41" t="n">
-        <v>1096119</v>
+        <v>10120854</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>台灣大</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -13,777 千股)</t>
+          <t>📉 20d 巨變(減碼 -8 千股)</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-36628981</v>
+        <v>-48300</v>
       </c>
       <c r="D42" t="n">
-        <v>10120854</v>
+        <v>-275300</v>
       </c>
       <c r="E42" t="n">
-        <v>-21969977</v>
+        <v>-112000</v>
       </c>
       <c r="F42" t="n">
-        <v>23897674</v>
+        <v>-267000</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>聯合</t>
         </is>
       </c>
     </row>
@@ -6937,20 +6937,20 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 5,202 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 2,693 千股)</t>
         </is>
       </c>
       <c r="C43" t="n">
+        <v>782768</v>
+      </c>
+      <c r="D43" t="n">
+        <v>-13492329</v>
+      </c>
+      <c r="E43" t="n">
         <v>-1607048</v>
       </c>
-      <c r="D43" t="n">
+      <c r="F43" t="n">
         <v>-16184928</v>
-      </c>
-      <c r="E43" t="n">
-        <v>-2198490</v>
-      </c>
-      <c r="F43" t="n">
-        <v>-21387001</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -6961,58 +6961,58 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -19 千股)</t>
+          <t>📈 20d 巨變(加碼 1,531 千股)</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-112000</v>
+        <v>-1078303</v>
       </c>
       <c r="D44" t="n">
-        <v>-267000</v>
+        <v>-5613622</v>
       </c>
       <c r="E44" t="n">
-        <v>-44000</v>
+        <v>-606801</v>
       </c>
       <c r="F44" t="n">
-        <v>-248132</v>
+        <v>-7145116</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>聯合</t>
+          <t>亞力</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,336 千股)</t>
+          <t>📉 20d 巨變(減碼 -60 千股)</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-606801</v>
+        <v>-1264743</v>
       </c>
       <c r="D45" t="n">
-        <v>-7145116</v>
+        <v>535803</v>
       </c>
       <c r="E45" t="n">
-        <v>-1846605</v>
+        <v>-1509877</v>
       </c>
       <c r="F45" t="n">
-        <v>-5809350</v>
+        <v>595769</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>大綜</t>
         </is>
       </c>
     </row>
@@ -7024,20 +7024,20 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 457 千股)</t>
+          <t>📈 20d 巨變(加碼 376 千股)</t>
         </is>
       </c>
       <c r="C46" t="n">
+        <v>1534783</v>
+      </c>
+      <c r="D46" t="n">
+        <v>3408935</v>
+      </c>
+      <c r="E46" t="n">
         <v>994079</v>
       </c>
-      <c r="D46" t="n">
+      <c r="F46" t="n">
         <v>3032890</v>
-      </c>
-      <c r="E46" t="n">
-        <v>1602333</v>
-      </c>
-      <c r="F46" t="n">
-        <v>2575458</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -7048,87 +7048,87 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -214 千股)</t>
+          <t>📈 20d 巨變(加碼 286 千股)</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-1509877</v>
+        <v>254005</v>
       </c>
       <c r="D47" t="n">
-        <v>595769</v>
+        <v>-524714</v>
       </c>
       <c r="E47" t="n">
-        <v>-1343877</v>
+        <v>728627</v>
       </c>
       <c r="F47" t="n">
-        <v>809669</v>
+        <v>-810566</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>台燿</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,396 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,654 千股)</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>728627</v>
+        <v>-7498863</v>
       </c>
       <c r="D48" t="n">
-        <v>-810566</v>
+        <v>-9450397</v>
       </c>
       <c r="E48" t="n">
-        <v>880568</v>
+        <v>-4693114</v>
       </c>
       <c r="F48" t="n">
-        <v>585153</v>
+        <v>-7796106</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>立隆電</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -2,104 千股)</t>
+          <t>📉 20d 巨變(減碼 -2,623 千股)</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-4693114</v>
+        <v>-3091857</v>
       </c>
       <c r="D49" t="n">
-        <v>-7796106</v>
+        <v>-9656179</v>
       </c>
       <c r="E49" t="n">
-        <v>-18426</v>
+        <v>-3416100</v>
       </c>
       <c r="F49" t="n">
-        <v>-5691759</v>
+        <v>-7033507</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
@@ -7140,20 +7140,20 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -913 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 480 千股)</t>
         </is>
       </c>
       <c r="C50" t="n">
+        <v>-17179</v>
+      </c>
+      <c r="D50" t="n">
+        <v>-2902713</v>
+      </c>
+      <c r="E50" t="n">
         <v>51493</v>
       </c>
-      <c r="D50" t="n">
+      <c r="F50" t="n">
         <v>-3383069</v>
-      </c>
-      <c r="E50" t="n">
-        <v>943946</v>
-      </c>
-      <c r="F50" t="n">
-        <v>-2470408</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -7164,116 +7164,116 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 6,122 千股)</t>
+          <t>📉 20d 巨變(減碼 -495 千股)</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-3416100</v>
+        <v>-522402</v>
       </c>
       <c r="D51" t="n">
-        <v>-7033507</v>
+        <v>-2608856</v>
       </c>
       <c r="E51" t="n">
-        <v>-3640214</v>
+        <v>-124305</v>
       </c>
       <c r="F51" t="n">
-        <v>-13155791</v>
+        <v>-2114187</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>世芯-KY</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -328 千股)</t>
+          <t>📈 20d 巨變(加碼 1,636 千股)</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-124305</v>
+        <v>8223413</v>
       </c>
       <c r="D52" t="n">
-        <v>-2114187</v>
+        <v>-50737807</v>
       </c>
       <c r="E52" t="n">
-        <v>-103989</v>
+        <v>1187789</v>
       </c>
       <c r="F52" t="n">
-        <v>-1786193</v>
+        <v>-52374080</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 2,976 千股)</t>
+          <t>📈 20d 巨變(加碼 3,929 千股)</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1187789</v>
+        <v>-24206159</v>
       </c>
       <c r="D53" t="n">
-        <v>-52374080</v>
+        <v>-22579037</v>
       </c>
       <c r="E53" t="n">
-        <v>2060861</v>
+        <v>-17322902</v>
       </c>
       <c r="F53" t="n">
-        <v>-55349731</v>
+        <v>-26507588</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 18,117 千股)</t>
+          <t>📈 20d 巨變(加碼 996 千股)</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-17322902</v>
+        <v>-1233776</v>
       </c>
       <c r="D54" t="n">
-        <v>-26507588</v>
+        <v>-6581855</v>
       </c>
       <c r="E54" t="n">
-        <v>-33777436</v>
+        <v>-1325216</v>
       </c>
       <c r="F54" t="n">
-        <v>-44624115</v>
+        <v>-7578161</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>鈊象</t>
         </is>
       </c>
     </row>
@@ -7285,20 +7285,20 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,250 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -17,487 千股)</t>
         </is>
       </c>
       <c r="C55" t="n">
+        <v>-10587111</v>
+      </c>
+      <c r="D55" t="n">
+        <v>41673068</v>
+      </c>
+      <c r="E55" t="n">
         <v>14233120</v>
       </c>
-      <c r="D55" t="n">
+      <c r="F55" t="n">
         <v>59160199</v>
-      </c>
-      <c r="E55" t="n">
-        <v>14184467</v>
-      </c>
-      <c r="F55" t="n">
-        <v>60409860</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -7309,377 +7309,377 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,818 千股)</t>
+          <t>📉 20d 巨變(減碼 -87 千股)</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-1325216</v>
+        <v>-296423</v>
       </c>
       <c r="D56" t="n">
-        <v>-7578161</v>
+        <v>1753434</v>
       </c>
       <c r="E56" t="n">
-        <v>-1178265</v>
+        <v>-148563</v>
       </c>
       <c r="F56" t="n">
-        <v>-9395891</v>
+        <v>1840221</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>達欣工</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -492 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -1,026 千股)</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>388495</v>
+        <v>-534478</v>
       </c>
       <c r="D57" t="n">
-        <v>-1908898</v>
+        <v>-853873</v>
       </c>
       <c r="E57" t="n">
-        <v>377165</v>
+        <v>384803</v>
       </c>
       <c r="F57" t="n">
-        <v>-1416505</v>
+        <v>171932</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>鉅祥</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 154 千股)</t>
+          <t>📉 20d 巨變(減碼 -635 千股)</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-845</v>
+        <v>18289</v>
       </c>
       <c r="D58" t="n">
-        <v>-1161744</v>
+        <v>-2544067</v>
       </c>
       <c r="E58" t="n">
-        <v>-450488</v>
+        <v>388495</v>
       </c>
       <c r="F58" t="n">
-        <v>-1315786</v>
+        <v>-1908898</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>士電</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -80 千股)</t>
+          <t>📈 20d 巨變(加碼 488 千股)</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>-148563</v>
+        <v>262382</v>
       </c>
       <c r="D59" t="n">
-        <v>1840221</v>
+        <v>-673517</v>
       </c>
       <c r="E59" t="n">
-        <v>-6714</v>
+        <v>-845</v>
       </c>
       <c r="F59" t="n">
-        <v>1919964</v>
+        <v>-1161744</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>普萊德</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 1,052 千股)</t>
+          <t>📈 20d 巨變(加碼 71 千股)</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>384803</v>
+        <v>358170</v>
       </c>
       <c r="D60" t="n">
-        <v>171932</v>
+        <v>847896</v>
       </c>
       <c r="E60" t="n">
-        <v>-815013</v>
+        <v>272953</v>
       </c>
       <c r="F60" t="n">
-        <v>-879830</v>
+        <v>776562</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 71 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 104 千股)</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-124160</v>
+        <v>125609</v>
       </c>
       <c r="D61" t="n">
-        <v>129819</v>
+        <v>470834</v>
       </c>
       <c r="E61" t="n">
-        <v>-195344</v>
+        <v>-39925</v>
       </c>
       <c r="F61" t="n">
-        <v>59117</v>
+        <v>367295</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>勝一</t>
+          <t>祥碩</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 202 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -1,532 千股)</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>272953</v>
+        <v>-214109</v>
       </c>
       <c r="D62" t="n">
-        <v>776562</v>
+        <v>1777038</v>
       </c>
       <c r="E62" t="n">
-        <v>150521</v>
+        <v>1893080</v>
       </c>
       <c r="F62" t="n">
-        <v>574950</v>
+        <v>3309115</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>華星光</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -249 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 513 千股)</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>9050</v>
+        <v>491039</v>
       </c>
       <c r="D63" t="n">
-        <v>555900</v>
+        <v>643200</v>
       </c>
       <c r="E63" t="n">
-        <v>-100660</v>
+        <v>-124160</v>
       </c>
       <c r="F63" t="n">
-        <v>805190</v>
+        <v>129819</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>勝一</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 255 千股)</t>
+          <t>📉 20d 巨變(減碼 -16 千股)</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>-39925</v>
+        <v>225430</v>
       </c>
       <c r="D64" t="n">
-        <v>367295</v>
+        <v>540080</v>
       </c>
       <c r="E64" t="n">
-        <v>-107206</v>
+        <v>9050</v>
       </c>
       <c r="F64" t="n">
-        <v>112116</v>
+        <v>555900</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>信立</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,955 千股)</t>
+          <t>📈 20d 巨變(加碼 1,740 千股)</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1893080</v>
+        <v>-1151046</v>
       </c>
       <c r="D65" t="n">
-        <v>3309115</v>
+        <v>-3201906</v>
       </c>
       <c r="E65" t="n">
-        <v>879602</v>
+        <v>-1237054</v>
       </c>
       <c r="F65" t="n">
-        <v>1353770</v>
+        <v>-4941647</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>聯鈞</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -199 千股)</t>
+          <t>📈 20d 巨變(加碼 1,965 千股)</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-1237054</v>
+        <v>-541455</v>
       </c>
       <c r="D66" t="n">
-        <v>-4941647</v>
+        <v>-2842475</v>
       </c>
       <c r="E66" t="n">
-        <v>-2718403</v>
+        <v>-804332</v>
       </c>
       <c r="F66" t="n">
-        <v>-4742207</v>
+        <v>-4807799</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>宇瞻</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,633 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 22,641 千股)</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-6914795</v>
+        <v>1126790</v>
       </c>
       <c r="D67" t="n">
-        <v>-18948592</v>
+        <v>-67101183</v>
       </c>
       <c r="E67" t="n">
-        <v>-6334213</v>
+        <v>-1319042</v>
       </c>
       <c r="F67" t="n">
-        <v>-20581790</v>
+        <v>-89742469</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 31,353 千股)</t>
+          <t>📈 20d 巨變(加碼 541 千股)</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-1319042</v>
+        <v>-7835515</v>
       </c>
       <c r="D68" t="n">
-        <v>-89742469</v>
+        <v>-18407589</v>
       </c>
       <c r="E68" t="n">
-        <v>-5549289</v>
+        <v>-6914795</v>
       </c>
       <c r="F68" t="n">
-        <v>-121095499</v>
+        <v>-18948592</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>瑞昱</t>
         </is>
       </c>
     </row>
@@ -7691,20 +7691,20 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 34,732 千股)</t>
+          <t>📉 20d 巨變(減碼 -10,344 千股)</t>
         </is>
       </c>
       <c r="C69" t="n">
+        <v>-35494025</v>
+      </c>
+      <c r="D69" t="n">
+        <v>-213240835</v>
+      </c>
+      <c r="E69" t="n">
         <v>-51598125</v>
       </c>
-      <c r="D69" t="n">
+      <c r="F69" t="n">
         <v>-202897294</v>
-      </c>
-      <c r="E69" t="n">
-        <v>-56911898</v>
-      </c>
-      <c r="F69" t="n">
-        <v>-237629422</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -7715,116 +7715,116 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -96 千股)</t>
+          <t>📈 20d 巨變(加碼 557 千股)</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-804332</v>
+        <v>1217149</v>
       </c>
       <c r="D70" t="n">
-        <v>-4807799</v>
+        <v>4002810</v>
       </c>
       <c r="E70" t="n">
-        <v>-1432201</v>
+        <v>1270512</v>
       </c>
       <c r="F70" t="n">
-        <v>-4712074</v>
+        <v>3445681</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>聯亞</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 191 千股)</t>
+          <t>📈 20d 巨變(加碼 1,137 千股)</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1270512</v>
+        <v>17374694</v>
       </c>
       <c r="D71" t="n">
-        <v>3445681</v>
+        <v>11837401</v>
       </c>
       <c r="E71" t="n">
-        <v>1172548</v>
+        <v>6851192</v>
       </c>
       <c r="F71" t="n">
-        <v>3254812</v>
+        <v>10700718</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 2,259 千股)</t>
+          <t>📉 20d 巨變(減碼 -123 千股)</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>6851192</v>
+        <v>17317</v>
       </c>
       <c r="D72" t="n">
-        <v>10700718</v>
+        <v>973464</v>
       </c>
       <c r="E72" t="n">
-        <v>2382918</v>
+        <v>56348</v>
       </c>
       <c r="F72" t="n">
-        <v>8441619</v>
+        <v>1096495</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>德昌</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -3,919 千股)</t>
+          <t>📈 20d 巨變(加碼 444 千股)</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-12828305</v>
+        <v>141612</v>
       </c>
       <c r="D73" t="n">
-        <v>-17393261</v>
+        <v>-266294</v>
       </c>
       <c r="E73" t="n">
-        <v>-16676813</v>
+        <v>66659</v>
       </c>
       <c r="F73" t="n">
-        <v>-13474533</v>
+        <v>-710737</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>億泰</t>
         </is>
       </c>
     </row>
@@ -7836,20 +7836,20 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -197 千股)</t>
+          <t>📈 20d 巨變(加碼 154 千股)</t>
         </is>
       </c>
       <c r="C74" t="n">
+        <v>204195</v>
+      </c>
+      <c r="D74" t="n">
+        <v>-276684</v>
+      </c>
+      <c r="E74" t="n">
         <v>153195</v>
       </c>
-      <c r="D74" t="n">
+      <c r="F74" t="n">
         <v>-430684</v>
-      </c>
-      <c r="E74" t="n">
-        <v>166213</v>
-      </c>
-      <c r="F74" t="n">
-        <v>-233434</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -7865,20 +7865,20 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -300 千股)</t>
+          <t>📉 20d 巨變(減碼 -589 千股)</t>
         </is>
       </c>
       <c r="C75" t="n">
+        <v>-163140</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3275973</v>
+      </c>
+      <c r="E75" t="n">
         <v>-1949477</v>
       </c>
-      <c r="D75" t="n">
+      <c r="F75" t="n">
         <v>3864876</v>
-      </c>
-      <c r="E75" t="n">
-        <v>-924698</v>
-      </c>
-      <c r="F75" t="n">
-        <v>4165298</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -7889,29 +7889,29 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,430 千股)</t>
+          <t>📈 20d 巨變(加碼 1,280 千股)</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>66659</v>
+        <v>-9774310</v>
       </c>
       <c r="D76" t="n">
-        <v>-710737</v>
+        <v>-16113473</v>
       </c>
       <c r="E76" t="n">
-        <v>95769</v>
+        <v>-12828305</v>
       </c>
       <c r="F76" t="n">
-        <v>-2140726</v>
+        <v>-17393261</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>億泰</t>
+          <t>台汽電</t>
         </is>
       </c>
     </row>
@@ -7923,20 +7923,20 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 6 千股)</t>
+          <t>📈 20d 巨變(加碼 155 千股)</t>
         </is>
       </c>
       <c r="C77" t="n">
+        <v>4841723</v>
+      </c>
+      <c r="D77" t="n">
+        <v>6567084</v>
+      </c>
+      <c r="E77" t="n">
         <v>3782190</v>
       </c>
-      <c r="D77" t="n">
+      <c r="F77" t="n">
         <v>6411835</v>
-      </c>
-      <c r="E77" t="n">
-        <v>5412854</v>
-      </c>
-      <c r="F77" t="n">
-        <v>6406220</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -7947,145 +7947,145 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 684 千股)</t>
+          <t>📉 20d 巨變(減碼 -10,709 千股)</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>330900</v>
+        <v>-15093238</v>
       </c>
       <c r="D78" t="n">
-        <v>-7773557</v>
+        <v>-23657473</v>
       </c>
       <c r="E78" t="n">
-        <v>794806</v>
+        <v>-19001106</v>
       </c>
       <c r="F78" t="n">
-        <v>-8457319</v>
+        <v>-12948152</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 33 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -895 千股)</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>239004</v>
+        <v>-886416</v>
       </c>
       <c r="D79" t="n">
-        <v>72756</v>
+        <v>-8668666</v>
       </c>
       <c r="E79" t="n">
-        <v>220533</v>
+        <v>330900</v>
       </c>
       <c r="F79" t="n">
-        <v>40010</v>
+        <v>-7773557</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>啟碁</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,000 千股)</t>
+          <t>📈 20d 巨變(加碼 94 千股)</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>-19001106</v>
+        <v>309714</v>
       </c>
       <c r="D80" t="n">
-        <v>-12948152</v>
+        <v>166535</v>
       </c>
       <c r="E80" t="n">
-        <v>-12799990</v>
+        <v>239004</v>
       </c>
       <c r="F80" t="n">
-        <v>-11948556</v>
+        <v>72756</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>精測</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 2,930 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -567 千股)</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-99074232</v>
+        <v>177128</v>
       </c>
       <c r="D81" t="n">
-        <v>-218817336</v>
+        <v>-4446644</v>
       </c>
       <c r="E81" t="n">
-        <v>-76458409</v>
+        <v>-706287</v>
       </c>
       <c r="F81" t="n">
-        <v>-221747342</v>
+        <v>-3879336</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 2,901 千股)</t>
+          <t>📈 20d 巨變(加碼 3,905 千股)</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-706287</v>
+        <v>-68160196</v>
       </c>
       <c r="D82" t="n">
-        <v>-3879336</v>
+        <v>-214912448</v>
       </c>
       <c r="E82" t="n">
-        <v>-1396099</v>
+        <v>-99074232</v>
       </c>
       <c r="F82" t="n">
-        <v>-6779974</v>
+        <v>-218817336</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
@@ -8097,20 +8097,20 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 496 千股)</t>
+          <t>📈 20d 巨變(加碼 307 千股)</t>
         </is>
       </c>
       <c r="C83" t="n">
+        <v>132023</v>
+      </c>
+      <c r="D83" t="n">
+        <v>309852</v>
+      </c>
+      <c r="E83" t="n">
         <v>10373</v>
       </c>
-      <c r="D83" t="n">
+      <c r="F83" t="n">
         <v>3102</v>
-      </c>
-      <c r="E83" t="n">
-        <v>65123</v>
-      </c>
-      <c r="F83" t="n">
-        <v>-493048</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -8121,116 +8121,116 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,349 千股)</t>
+          <t>📈 20d 巨變(加碼 243 千股)</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>889250</v>
+        <v>204469</v>
       </c>
       <c r="D84" t="n">
-        <v>2991504</v>
+        <v>-1169623</v>
       </c>
       <c r="E84" t="n">
-        <v>681000</v>
+        <v>210469</v>
       </c>
       <c r="F84" t="n">
-        <v>1642214</v>
+        <v>-1412623</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>鑫龍騰</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -6 千股)</t>
+          <t>📉 20d 巨變(減碼 -525 千股)</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>210469</v>
+        <v>452250</v>
       </c>
       <c r="D85" t="n">
-        <v>-1412623</v>
+        <v>2466334</v>
       </c>
       <c r="E85" t="n">
-        <v>248000</v>
+        <v>889250</v>
       </c>
       <c r="F85" t="n">
-        <v>-1406962</v>
+        <v>2991504</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>鑫龍騰</t>
+          <t>全友</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 2,726 千股)</t>
+          <t>📈 20d 巨變(加碼 1,348 千股)</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-3341098</v>
+        <v>3361930</v>
       </c>
       <c r="D86" t="n">
-        <v>-3305190</v>
+        <v>3825864</v>
       </c>
       <c r="E86" t="n">
-        <v>-4420252</v>
+        <v>2361825</v>
       </c>
       <c r="F86" t="n">
-        <v>-6030896</v>
+        <v>2477701</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>研華</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -453 千股)</t>
+          <t>📉 20d 巨變(減碼 -162 千股)</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>2361825</v>
+        <v>-1951513</v>
       </c>
       <c r="D87" t="n">
-        <v>2477701</v>
+        <v>-3466975</v>
       </c>
       <c r="E87" t="n">
-        <v>2119415</v>
+        <v>-3341098</v>
       </c>
       <c r="F87" t="n">
-        <v>2931181</v>
+        <v>-3305190</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>宏捷科</t>
         </is>
       </c>
     </row>
@@ -8242,20 +8242,20 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -9,343 千股)</t>
+          <t>📉 20d 巨變(減碼 -4,943 千股)</t>
         </is>
       </c>
       <c r="C88" t="n">
+        <v>-48312465</v>
+      </c>
+      <c r="D88" t="n">
+        <v>-59920994</v>
+      </c>
+      <c r="E88" t="n">
         <v>-46281468</v>
       </c>
-      <c r="D88" t="n">
+      <c r="F88" t="n">
         <v>-54977869</v>
-      </c>
-      <c r="E88" t="n">
-        <v>-35824111</v>
-      </c>
-      <c r="F88" t="n">
-        <v>-45634511</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -8271,20 +8271,20 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -837 千股)</t>
+          <t>📈 20d 巨變(加碼 463 千股)</t>
         </is>
       </c>
       <c r="C89" t="n">
+        <v>-372271</v>
+      </c>
+      <c r="D89" t="n">
+        <v>-5205700</v>
+      </c>
+      <c r="E89" t="n">
         <v>-1382384</v>
       </c>
-      <c r="D89" t="n">
+      <c r="F89" t="n">
         <v>-5668599</v>
-      </c>
-      <c r="E89" t="n">
-        <v>-1712881</v>
-      </c>
-      <c r="F89" t="n">
-        <v>-4831108</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -8300,20 +8300,20 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 26 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -86 千股)</t>
         </is>
       </c>
       <c r="C90" t="n">
+        <v>-54170</v>
+      </c>
+      <c r="D90" t="n">
+        <v>-56939</v>
+      </c>
+      <c r="E90" t="n">
         <v>63395</v>
       </c>
-      <c r="D90" t="n">
+      <c r="F90" t="n">
         <v>29421</v>
-      </c>
-      <c r="E90" t="n">
-        <v>50779</v>
-      </c>
-      <c r="F90" t="n">
-        <v>3639</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -8329,20 +8329,20 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -56 千股)</t>
+          <t>📉 20d 巨變(減碼 -29 千股)</t>
         </is>
       </c>
       <c r="C91" t="n">
+        <v>-93768</v>
+      </c>
+      <c r="D91" t="n">
+        <v>-419308</v>
+      </c>
+      <c r="E91" t="n">
         <v>-88334</v>
       </c>
-      <c r="D91" t="n">
+      <c r="F91" t="n">
         <v>-390520</v>
-      </c>
-      <c r="E91" t="n">
-        <v>-119920</v>
-      </c>
-      <c r="F91" t="n">
-        <v>-334115</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -8353,317 +8353,288 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 2,182 千股)</t>
+          <t>📈 20d 巨變(加碼 23 千股)</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>4954518</v>
+        <v>29000</v>
       </c>
       <c r="D92" t="n">
-        <v>7974993</v>
+        <v>119655</v>
       </c>
       <c r="E92" t="n">
-        <v>2804322</v>
+        <v>6800</v>
       </c>
       <c r="F92" t="n">
-        <v>5793196</v>
+        <v>96605</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>六方科-KY</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 10 千股)</t>
+          <t>📉 20d 巨變(減碼 -3,575 千股)</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>6800</v>
+        <v>-39125116</v>
       </c>
       <c r="D93" t="n">
-        <v>96605</v>
+        <v>-133414697</v>
       </c>
       <c r="E93" t="n">
-        <v>-35117</v>
+        <v>-38176568</v>
       </c>
       <c r="F93" t="n">
-        <v>86311</v>
+        <v>-129839374</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -6,642 千股)</t>
+          <t>📈 20d 巨變(加碼 23,405 千股)</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-38176568</v>
+        <v>-34134732</v>
       </c>
       <c r="D94" t="n">
-        <v>-129839374</v>
+        <v>-175849216</v>
       </c>
       <c r="E94" t="n">
-        <v>-43643905</v>
+        <v>-42264080</v>
       </c>
       <c r="F94" t="n">
-        <v>-123197445</v>
+        <v>-199253908</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 50,942 千股)</t>
+          <t>📉 20d 巨變(減碼 -3,781 千股)</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>-42264080</v>
+        <v>-2045510</v>
       </c>
       <c r="D95" t="n">
-        <v>-199253908</v>
+        <v>-7791846</v>
       </c>
       <c r="E95" t="n">
-        <v>-100573740</v>
+        <v>-3918232</v>
       </c>
       <c r="F95" t="n">
-        <v>-250196137</v>
+        <v>-4010798</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>聯發科</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,430 千股)</t>
+          <t>📈 20d 巨變(加碼 49 千股)</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>-3918232</v>
+        <v>-1635788</v>
       </c>
       <c r="D96" t="n">
-        <v>-4010798</v>
+        <v>-4588416</v>
       </c>
       <c r="E96" t="n">
-        <v>-1442400</v>
+        <v>-1598545</v>
       </c>
       <c r="F96" t="n">
-        <v>-2580348</v>
+        <v>-4637437</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>緯穎</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 134 千股)</t>
+          <t>📉 20d 巨變(減碼 -33 千股)</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>129100</v>
+        <v>169006</v>
       </c>
       <c r="D97" t="n">
-        <v>-4619395</v>
+        <v>237120</v>
       </c>
       <c r="E97" t="n">
-        <v>-159369</v>
+        <v>85783</v>
       </c>
       <c r="F97" t="n">
-        <v>-4753207</v>
+        <v>270401</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>信驊</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -719 千股)</t>
+          <t>📈 20d 巨變(加碼 74 千股)</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-1598545</v>
+        <v>1050787</v>
       </c>
       <c r="D98" t="n">
-        <v>-4637437</v>
+        <v>1755468</v>
       </c>
       <c r="E98" t="n">
-        <v>-778527</v>
+        <v>3415495</v>
       </c>
       <c r="F98" t="n">
-        <v>-3918276</v>
+        <v>1681307</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>金像電</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 75 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -581 千股)</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>85783</v>
+        <v>-151640</v>
       </c>
       <c r="D99" t="n">
-        <v>270401</v>
+        <v>-5200332</v>
       </c>
       <c r="E99" t="n">
-        <v>36613</v>
+        <v>129100</v>
       </c>
       <c r="F99" t="n">
-        <v>195714</v>
+        <v>-4619395</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>創意</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -2,487 千股)</t>
+          <t>📈 20d 巨變(加碼 603 千股)</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>3415495</v>
+        <v>-19819</v>
       </c>
       <c r="D100" t="n">
-        <v>1681307</v>
+        <v>1877650</v>
       </c>
       <c r="E100" t="n">
-        <v>5079686</v>
+        <v>-360963</v>
       </c>
       <c r="F100" t="n">
-        <v>4168699</v>
+        <v>1274192</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>高技</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 592 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 718 千股)</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-360963</v>
+        <v>202678</v>
       </c>
       <c r="D101" t="n">
-        <v>1274192</v>
+        <v>-1842254</v>
       </c>
       <c r="E101" t="n">
-        <v>-1135965</v>
+        <v>-294585</v>
       </c>
       <c r="F101" t="n">
-        <v>682062</v>
+        <v>-2560418</v>
       </c>
       <c r="G101" t="inlineStr">
-        <is>
-          <t>高技</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>6187</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -512 千股)</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
-        <v>-294585</v>
-      </c>
-      <c r="D102" t="n">
-        <v>-2560418</v>
-      </c>
-      <c r="E102" t="n">
-        <v>54750</v>
-      </c>
-      <c r="F102" t="n">
-        <v>-2048783</v>
-      </c>
-      <c r="G102" t="inlineStr">
         <is>
           <t>萬潤</t>
         </is>

--- a/data/台股_外資雷達.xlsx
+++ b/data/台股_外資雷達.xlsx
@@ -496,22 +496,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-52105</v>
+        <v>-48938</v>
       </c>
       <c r="D2" t="n">
-        <v>197618</v>
+        <v>197174</v>
       </c>
       <c r="E2" t="n">
-        <v>-152783</v>
+        <v>-147405</v>
       </c>
       <c r="F2" t="n">
-        <v>54852</v>
+        <v>56342</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>12667</v>
       </c>
       <c r="H2" t="n">
-        <v>11913</v>
+        <v>13467</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -547,22 +547,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-10587</v>
+        <v>-13474</v>
       </c>
       <c r="D3" t="n">
-        <v>41673</v>
+        <v>42427</v>
       </c>
       <c r="E3" t="n">
-        <v>-111</v>
+        <v>-2311</v>
       </c>
       <c r="F3" t="n">
-        <v>1734</v>
+        <v>3886</v>
       </c>
       <c r="G3" t="n">
-        <v>-52231</v>
+        <v>-51634</v>
       </c>
       <c r="H3" t="n">
-        <v>3657</v>
+        <v>4024</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17375</v>
+        <v>23101</v>
       </c>
       <c r="D4" t="n">
-        <v>11837</v>
+        <v>19707</v>
       </c>
       <c r="E4" t="n">
-        <v>147380</v>
+        <v>140106</v>
       </c>
       <c r="F4" t="n">
-        <v>-5806</v>
+        <v>-5550</v>
       </c>
       <c r="G4" t="n">
-        <v>-31687</v>
+        <v>-32737</v>
       </c>
       <c r="H4" t="n">
-        <v>931</v>
+        <v>1883</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -649,22 +649,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5709</v>
+        <v>4516</v>
       </c>
       <c r="D5" t="n">
-        <v>11089</v>
+        <v>10559</v>
       </c>
       <c r="E5" t="n">
-        <v>16385</v>
+        <v>14675</v>
       </c>
       <c r="F5" t="n">
-        <v>-7461</v>
+        <v>-7826</v>
       </c>
       <c r="G5" t="n">
-        <v>-9169</v>
+        <v>-10099</v>
       </c>
       <c r="H5" t="n">
-        <v>371</v>
+        <v>431</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -700,22 +700,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4711</v>
+        <v>4302</v>
       </c>
       <c r="D6" t="n">
-        <v>7977</v>
+        <v>7283</v>
       </c>
       <c r="E6" t="n">
-        <v>11602</v>
+        <v>10741</v>
       </c>
       <c r="F6" t="n">
-        <v>-53</v>
+        <v>-51</v>
       </c>
       <c r="G6" t="n">
-        <v>-565</v>
+        <v>-567</v>
       </c>
       <c r="H6" t="n">
-        <v>644</v>
+        <v>738</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -751,22 +751,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4842</v>
+        <v>3712</v>
       </c>
       <c r="D7" t="n">
-        <v>6567</v>
+        <v>6606</v>
       </c>
       <c r="E7" t="n">
-        <v>11204</v>
+        <v>10931</v>
       </c>
       <c r="F7" t="n">
-        <v>3394</v>
+        <v>3477</v>
       </c>
       <c r="G7" t="n">
-        <v>3579</v>
+        <v>4184</v>
       </c>
       <c r="H7" t="n">
-        <v>247</v>
+        <v>421</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -802,22 +802,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>20</v>
+        <v>-149</v>
       </c>
       <c r="D8" t="n">
-        <v>5745</v>
+        <v>5689</v>
       </c>
       <c r="E8" t="n">
-        <v>9982</v>
+        <v>9432</v>
       </c>
       <c r="F8" t="n">
-        <v>-46</v>
+        <v>-253</v>
       </c>
       <c r="G8" t="n">
-        <v>-4883</v>
+        <v>-5249</v>
       </c>
       <c r="H8" t="n">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -844,31 +844,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>漢科</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1217</v>
+        <v>1738</v>
       </c>
       <c r="D9" t="n">
-        <v>4003</v>
+        <v>3898</v>
       </c>
       <c r="E9" t="n">
-        <v>2120</v>
+        <v>3276</v>
       </c>
       <c r="F9" t="n">
-        <v>-1306</v>
+        <v>91</v>
       </c>
       <c r="G9" t="n">
-        <v>-3454</v>
+        <v>135</v>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -889,37 +889,37 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3362</v>
+        <v>522</v>
       </c>
       <c r="D10" t="n">
-        <v>3826</v>
+        <v>3828</v>
       </c>
       <c r="E10" t="n">
-        <v>18861</v>
+        <v>1770</v>
       </c>
       <c r="F10" t="n">
-        <v>129</v>
+        <v>-1363</v>
       </c>
       <c r="G10" t="n">
-        <v>225</v>
+        <v>-3647</v>
       </c>
       <c r="H10" t="n">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -928,49 +928,49 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1395</v>
+        <v>2480</v>
       </c>
       <c r="D11" t="n">
-        <v>3649</v>
+        <v>3664</v>
       </c>
       <c r="E11" t="n">
-        <v>1400</v>
+        <v>18001</v>
       </c>
       <c r="F11" t="n">
-        <v>-92</v>
+        <v>81</v>
       </c>
       <c r="G11" t="n">
-        <v>-148</v>
+        <v>244</v>
       </c>
       <c r="H11" t="n">
-        <v>-753</v>
+        <v>35</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -979,49 +979,49 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>97</v>
+        <v>61</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>智易</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1535</v>
+        <v>-244</v>
       </c>
       <c r="D12" t="n">
-        <v>3409</v>
+        <v>3434</v>
       </c>
       <c r="E12" t="n">
-        <v>2399</v>
+        <v>5017</v>
       </c>
       <c r="F12" t="n">
-        <v>135</v>
+        <v>1315</v>
       </c>
       <c r="G12" t="n">
-        <v>135</v>
+        <v>5537</v>
       </c>
       <c r="H12" t="n">
-        <v>-3</v>
+        <v>-41</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1034,45 +1034,45 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>零壹</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-163</v>
+        <v>2059</v>
       </c>
       <c r="D13" t="n">
-        <v>3276</v>
+        <v>2796</v>
       </c>
       <c r="E13" t="n">
-        <v>5595</v>
+        <v>1850</v>
       </c>
       <c r="F13" t="n">
-        <v>1756</v>
+        <v>-152</v>
       </c>
       <c r="G13" t="n">
-        <v>5534</v>
+        <v>-146</v>
       </c>
       <c r="H13" t="n">
-        <v>-55</v>
+        <v>-744</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1081,19 +1081,19 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1108,22 +1108,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>436</v>
+        <v>366</v>
       </c>
       <c r="D14" t="n">
-        <v>3239</v>
+        <v>2135</v>
       </c>
       <c r="E14" t="n">
-        <v>2692</v>
+        <v>2994</v>
       </c>
       <c r="F14" t="n">
-        <v>-824</v>
+        <v>-936</v>
       </c>
       <c r="G14" t="n">
-        <v>1134</v>
+        <v>644</v>
       </c>
       <c r="H14" t="n">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1150,31 +1150,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>合機</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>452</v>
+        <v>830</v>
       </c>
       <c r="D15" t="n">
-        <v>2466</v>
+        <v>2067</v>
       </c>
       <c r="E15" t="n">
-        <v>8011</v>
+        <v>2803</v>
       </c>
       <c r="F15" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>-167</v>
+        <v>186</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1183,49 +1183,49 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>合機</t>
+          <t>全友</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>691</v>
+        <v>332</v>
       </c>
       <c r="D16" t="n">
-        <v>2235</v>
+        <v>2028</v>
       </c>
       <c r="E16" t="n">
-        <v>2100</v>
+        <v>8078</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="H16" t="n">
-        <v>144</v>
+        <v>-14</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1234,71 +1234,59 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>321</v>
+        <v>-0</v>
       </c>
       <c r="D17" t="n">
-        <v>2091</v>
+        <v>1924</v>
       </c>
       <c r="E17" t="n">
-        <v>5309</v>
+        <v>-3554</v>
       </c>
       <c r="F17" t="n">
-        <v>-285</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>-193</v>
+        <v>-5746</v>
       </c>
       <c r="H17" t="n">
-        <v>72</v>
+        <v>-77</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>🟢 加碼</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>90</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>🚀 加速器</t>
-        </is>
-      </c>
-      <c r="M17" t="n">
-        <v>4</v>
-      </c>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1312,22 +1300,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>665</v>
+        <v>381</v>
       </c>
       <c r="D18" t="n">
-        <v>1879</v>
+        <v>1517</v>
       </c>
       <c r="E18" t="n">
-        <v>-2267</v>
+        <v>-2189</v>
       </c>
       <c r="F18" t="n">
-        <v>-145</v>
+        <v>-154</v>
       </c>
       <c r="G18" t="n">
-        <v>-127</v>
+        <v>169</v>
       </c>
       <c r="H18" t="n">
-        <v>-75</v>
+        <v>-43</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1354,70 +1342,82 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>達欣工</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-20</v>
+        <v>-255</v>
       </c>
       <c r="D19" t="n">
-        <v>1878</v>
+        <v>1400</v>
       </c>
       <c r="E19" t="n">
-        <v>-3897</v>
+        <v>123</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G19" t="n">
-        <v>-6246</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>-91</v>
+        <v>-219</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>79</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>🛬 穩定</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3288</v>
+        <v>35</v>
       </c>
       <c r="D20" t="n">
-        <v>1788</v>
+        <v>1385</v>
       </c>
       <c r="E20" t="n">
-        <v>-7558</v>
+        <v>-1455</v>
       </c>
       <c r="F20" t="n">
-        <v>2412</v>
+        <v>-415</v>
       </c>
       <c r="G20" t="n">
-        <v>-238</v>
+        <v>-397</v>
       </c>
       <c r="H20" t="n">
-        <v>141</v>
+        <v>-74</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1430,45 +1430,45 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-214</v>
+        <v>-218</v>
       </c>
       <c r="D21" t="n">
-        <v>1777</v>
+        <v>1304</v>
       </c>
       <c r="E21" t="n">
-        <v>-5421</v>
+        <v>4752</v>
       </c>
       <c r="F21" t="n">
-        <v>-1910</v>
+        <v>294</v>
       </c>
       <c r="G21" t="n">
-        <v>-5612</v>
+        <v>1378</v>
       </c>
       <c r="H21" t="n">
-        <v>11</v>
+        <v>-64</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1477,88 +1477,100 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>勝一</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1051</v>
+        <v>945</v>
       </c>
       <c r="D22" t="n">
-        <v>1755</v>
+        <v>1251</v>
       </c>
       <c r="E22" t="n">
-        <v>6207</v>
+        <v>4957</v>
       </c>
       <c r="F22" t="n">
-        <v>-677</v>
+        <v>4</v>
       </c>
       <c r="G22" t="n">
-        <v>-4159</v>
+        <v>6</v>
       </c>
       <c r="H22" t="n">
-        <v>157</v>
+        <v>-19</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>71</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>📉 減速</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>-3</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-296</v>
+        <v>-1190</v>
       </c>
       <c r="D23" t="n">
-        <v>1753</v>
+        <v>1180</v>
       </c>
       <c r="E23" t="n">
-        <v>82</v>
+        <v>-5724</v>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>-1981</v>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>-5739</v>
       </c>
       <c r="H23" t="n">
-        <v>-343</v>
+        <v>-34</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1571,45 +1583,45 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>485</v>
+        <v>2624</v>
       </c>
       <c r="D24" t="n">
-        <v>1544</v>
+        <v>1076</v>
       </c>
       <c r="E24" t="n">
-        <v>-1318</v>
+        <v>-7616</v>
       </c>
       <c r="F24" t="n">
-        <v>-307</v>
+        <v>2393</v>
       </c>
       <c r="G24" t="n">
-        <v>-138</v>
+        <v>-41</v>
       </c>
       <c r="H24" t="n">
-        <v>-114</v>
+        <v>118</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1622,45 +1634,45 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-46</v>
+        <v>-1479</v>
       </c>
       <c r="D25" t="n">
-        <v>1343</v>
+        <v>1050</v>
       </c>
       <c r="E25" t="n">
-        <v>5240</v>
+        <v>-8055</v>
       </c>
       <c r="F25" t="n">
-        <v>474</v>
+        <v>-177</v>
       </c>
       <c r="G25" t="n">
-        <v>1381</v>
+        <v>-5527</v>
       </c>
       <c r="H25" t="n">
-        <v>-115</v>
+        <v>-16</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1677,41 +1689,41 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>德昌</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>332</v>
+        <v>76</v>
       </c>
       <c r="D26" t="n">
-        <v>1307</v>
+        <v>889</v>
       </c>
       <c r="E26" t="n">
-        <v>5181</v>
+        <v>701</v>
       </c>
       <c r="F26" t="n">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>-658</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>139</v>
+        <v>-19</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1720,49 +1732,49 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-519</v>
+        <v>418</v>
       </c>
       <c r="D27" t="n">
-        <v>1122</v>
+        <v>886</v>
       </c>
       <c r="E27" t="n">
-        <v>-1369</v>
+        <v>1949</v>
       </c>
       <c r="F27" t="n">
-        <v>259</v>
+        <v>-15</v>
       </c>
       <c r="G27" t="n">
-        <v>240</v>
+        <v>339</v>
       </c>
       <c r="H27" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1771,15 +1783,15 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>🐌 龜速*</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M27" t="n">
@@ -1789,31 +1801,31 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-2233</v>
+        <v>-512</v>
       </c>
       <c r="D28" t="n">
-        <v>1060</v>
+        <v>868</v>
       </c>
       <c r="E28" t="n">
-        <v>-9566</v>
+        <v>-1375</v>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>257</v>
       </c>
       <c r="G28" t="n">
-        <v>-7046</v>
+        <v>241</v>
       </c>
       <c r="H28" t="n">
-        <v>-15</v>
+        <v>13</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1830,41 +1842,41 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速*</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>寶雅</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-457</v>
+        <v>-541</v>
       </c>
       <c r="D29" t="n">
-        <v>1054</v>
+        <v>799</v>
       </c>
       <c r="E29" t="n">
-        <v>1904</v>
+        <v>-4839</v>
       </c>
       <c r="F29" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>242</v>
+        <v>-4</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1877,45 +1889,45 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>德昌</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>17</v>
+        <v>220</v>
       </c>
       <c r="D30" t="n">
-        <v>973</v>
+        <v>784</v>
       </c>
       <c r="E30" t="n">
-        <v>712</v>
+        <v>5143</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>367</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>-286</v>
       </c>
       <c r="H30" t="n">
-        <v>-19</v>
+        <v>137</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1924,49 +1936,49 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M30" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>寶雅</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-458</v>
+        <v>-825</v>
       </c>
       <c r="D31" t="n">
-        <v>944</v>
+        <v>660</v>
       </c>
       <c r="E31" t="n">
-        <v>-220</v>
+        <v>1851</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="H31" t="n">
-        <v>316</v>
+        <v>246</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1979,45 +1991,45 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>358</v>
+        <v>-1207</v>
       </c>
       <c r="D32" t="n">
-        <v>848</v>
+        <v>629</v>
       </c>
       <c r="E32" t="n">
-        <v>1752</v>
+        <v>4265</v>
       </c>
       <c r="F32" t="n">
-        <v>20</v>
+        <v>-3</v>
       </c>
       <c r="G32" t="n">
-        <v>342</v>
+        <v>66</v>
       </c>
       <c r="H32" t="n">
-        <v>-11</v>
+        <v>176</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2026,40 +2038,40 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-255</v>
+        <v>-742</v>
       </c>
       <c r="D33" t="n">
-        <v>833</v>
+        <v>616</v>
       </c>
       <c r="E33" t="n">
-        <v>-4999</v>
+        <v>-555</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -2068,7 +2080,7 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-47</v>
+        <v>347</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2081,45 +2093,45 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M33" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>勝一</t>
+          <t>智冠</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>491</v>
+        <v>21</v>
       </c>
       <c r="D34" t="n">
-        <v>643</v>
+        <v>475</v>
       </c>
       <c r="E34" t="n">
-        <v>4276</v>
+        <v>396</v>
       </c>
       <c r="F34" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-61</v>
+        <v>-164</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2128,100 +2140,88 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M34" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>智冠</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>78</v>
+        <v>-1571</v>
       </c>
       <c r="D35" t="n">
-        <v>587</v>
+        <v>422</v>
       </c>
       <c r="E35" t="n">
-        <v>425</v>
+        <v>4977</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>962</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>-3875</v>
       </c>
       <c r="H35" t="n">
-        <v>-156</v>
+        <v>-127</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K35" t="n">
-        <v>80</v>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>🐌 龜速</t>
-        </is>
-      </c>
-      <c r="M35" t="n">
-        <v>-2</v>
-      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>225</v>
+        <v>-5432</v>
       </c>
       <c r="D36" t="n">
-        <v>540</v>
+        <v>386</v>
       </c>
       <c r="E36" t="n">
-        <v>-741</v>
+        <v>-4661</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>2860</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>4504</v>
       </c>
       <c r="H36" t="n">
-        <v>-0</v>
+        <v>-896</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2230,40 +2230,40 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M36" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>信立</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-1265</v>
+        <v>-95</v>
       </c>
       <c r="D37" t="n">
-        <v>536</v>
+        <v>377</v>
       </c>
       <c r="E37" t="n">
-        <v>2111</v>
+        <v>-765</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -2272,7 +2272,7 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2299,31 +2299,31 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-2407</v>
+        <v>143</v>
       </c>
       <c r="D38" t="n">
-        <v>526</v>
+        <v>360</v>
       </c>
       <c r="E38" t="n">
-        <v>254</v>
+        <v>-348</v>
       </c>
       <c r="F38" t="n">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>3165</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-50</v>
+        <v>-0</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2332,11 +2332,11 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2344,37 +2344,37 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>崇友</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>126</v>
+        <v>44</v>
       </c>
       <c r="D39" t="n">
-        <v>471</v>
+        <v>353</v>
       </c>
       <c r="E39" t="n">
-        <v>-1936</v>
+        <v>536</v>
       </c>
       <c r="F39" t="n">
-        <v>1379</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>1577</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2383,15 +2383,15 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M39" t="n">
@@ -2401,82 +2401,70 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>49</v>
+        <v>121</v>
       </c>
       <c r="D40" t="n">
-        <v>369</v>
+        <v>306</v>
       </c>
       <c r="E40" t="n">
-        <v>538</v>
+        <v>753</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>-83</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>-259</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K40" t="n">
-        <v>91</v>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>🐌 龜速</t>
-        </is>
-      </c>
-      <c r="M40" t="n">
-        <v>-1</v>
-      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>132</v>
+        <v>-308</v>
       </c>
       <c r="D41" t="n">
-        <v>310</v>
+        <v>275</v>
       </c>
       <c r="E41" t="n">
-        <v>-317</v>
+        <v>-975</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="H41" t="n">
-        <v>-0</v>
+        <v>-113</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2485,49 +2473,49 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M41" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-240</v>
+        <v>-518</v>
       </c>
       <c r="D42" t="n">
-        <v>287</v>
+        <v>264</v>
       </c>
       <c r="E42" t="n">
-        <v>-791</v>
+        <v>-2219</v>
       </c>
       <c r="F42" t="n">
-        <v>65</v>
+        <v>1388</v>
       </c>
       <c r="G42" t="n">
-        <v>50</v>
+        <v>1856</v>
       </c>
       <c r="H42" t="n">
-        <v>-53</v>
+        <v>28</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2536,59 +2524,71 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M42" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>六方科-KY</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>169</v>
+        <v>43</v>
       </c>
       <c r="D43" t="n">
-        <v>237</v>
+        <v>136</v>
       </c>
       <c r="E43" t="n">
-        <v>757</v>
+        <v>-5</v>
       </c>
       <c r="F43" t="n">
-        <v>-69</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>-186</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>-9</v>
+        <v>5</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>77</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>-3</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2602,22 +2602,22 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>310</v>
+        <v>162</v>
       </c>
       <c r="D44" t="n">
-        <v>167</v>
+        <v>113</v>
       </c>
       <c r="E44" t="n">
-        <v>-373</v>
+        <v>-182</v>
       </c>
       <c r="F44" t="n">
-        <v>-650</v>
+        <v>-545</v>
       </c>
       <c r="G44" t="n">
-        <v>-1283</v>
+        <v>-1122</v>
       </c>
       <c r="H44" t="n">
-        <v>-113</v>
+        <v>-101</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2644,22 +2644,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>方土霖</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="D45" t="n">
-        <v>120</v>
+        <v>-17</v>
       </c>
       <c r="E45" t="n">
-        <v>-11</v>
+        <v>-72</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -2668,7 +2668,7 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2677,49 +2677,49 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M45" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>方土霖</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>-120</v>
       </c>
       <c r="D46" t="n">
-        <v>-19</v>
+        <v>-76</v>
       </c>
       <c r="E46" t="n">
-        <v>-66</v>
+        <v>-290</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="H46" t="n">
-        <v>-2</v>
+        <v>26</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2728,49 +2728,49 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M46" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>大車隊</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-54</v>
+        <v>5</v>
       </c>
       <c r="D47" t="n">
-        <v>-57</v>
+        <v>-161</v>
       </c>
       <c r="E47" t="n">
-        <v>-351</v>
+        <v>-284</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>23</v>
+        <v>-1</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2779,40 +2779,40 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M47" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>大車隊</t>
+          <t>聯合</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>7</v>
+        <v>-92</v>
       </c>
       <c r="D48" t="n">
-        <v>-155</v>
+        <v>-234</v>
       </c>
       <c r="E48" t="n">
-        <v>-306</v>
+        <v>-3578</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -2821,7 +2821,7 @@
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-1</v>
+        <v>91</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2834,45 +2834,45 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M48" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>456</v>
+        <v>-1255</v>
       </c>
       <c r="D49" t="n">
-        <v>-250</v>
+        <v>-290</v>
       </c>
       <c r="E49" t="n">
-        <v>386</v>
+        <v>2140</v>
       </c>
       <c r="F49" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-231</v>
+        <v>53</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2881,11 +2881,11 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -2893,37 +2893,37 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>億泰</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>142</v>
+        <v>-3802</v>
       </c>
       <c r="D50" t="n">
-        <v>-266</v>
+        <v>-356</v>
       </c>
       <c r="E50" t="n">
-        <v>-2348</v>
+        <v>-750</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>3954</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>3940</v>
       </c>
       <c r="H50" t="n">
-        <v>202</v>
+        <v>-48</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2932,40 +2932,40 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M50" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>聯合</t>
+          <t>億泰</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-48</v>
+        <v>-141</v>
       </c>
       <c r="D51" t="n">
-        <v>-275</v>
+        <v>-375</v>
       </c>
       <c r="E51" t="n">
-        <v>-3539</v>
+        <v>-2422</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -2974,7 +2974,7 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>62</v>
+        <v>198</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -2983,19 +2983,19 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="52">
@@ -3010,22 +3010,22 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="D52" t="n">
-        <v>-277</v>
+        <v>-380</v>
       </c>
       <c r="E52" t="n">
-        <v>950</v>
+        <v>897</v>
       </c>
       <c r="F52" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
         <v>16</v>
       </c>
       <c r="H52" t="n">
-        <v>-144</v>
+        <v>-77</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3061,22 +3061,22 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>72</v>
+        <v>-167</v>
       </c>
       <c r="D53" t="n">
-        <v>-351</v>
+        <v>-404</v>
       </c>
       <c r="E53" t="n">
-        <v>207</v>
+        <v>55</v>
       </c>
       <c r="F53" t="n">
-        <v>-107</v>
+        <v>64</v>
       </c>
       <c r="G53" t="n">
-        <v>279</v>
+        <v>257</v>
       </c>
       <c r="H53" t="n">
-        <v>-57</v>
+        <v>-55</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3112,13 +3112,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-94</v>
+        <v>-60</v>
       </c>
       <c r="D54" t="n">
-        <v>-419</v>
+        <v>-427</v>
       </c>
       <c r="E54" t="n">
-        <v>-363</v>
+        <v>-385</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -3127,7 +3127,7 @@
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3163,22 +3163,22 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>187</v>
+        <v>123</v>
       </c>
       <c r="D55" t="n">
-        <v>-476</v>
+        <v>-542</v>
       </c>
       <c r="E55" t="n">
-        <v>-749</v>
+        <v>-857</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G55" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H55" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3205,31 +3205,31 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>254</v>
+        <v>207</v>
       </c>
       <c r="D56" t="n">
-        <v>-525</v>
+        <v>-563</v>
       </c>
       <c r="E56" t="n">
-        <v>-1201</v>
+        <v>-1753</v>
       </c>
       <c r="F56" t="n">
-        <v>883</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>5834</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-1915</v>
+        <v>12</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3242,45 +3242,45 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M56" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>262</v>
+        <v>2049</v>
       </c>
       <c r="D57" t="n">
-        <v>-674</v>
+        <v>-776</v>
       </c>
       <c r="E57" t="n">
-        <v>-1613</v>
+        <v>246</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="H57" t="n">
-        <v>2</v>
+        <v>168</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3289,15 +3289,15 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K57" t="n">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M57" t="n">
@@ -3307,31 +3307,31 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-3721</v>
+        <v>842</v>
       </c>
       <c r="D58" t="n">
-        <v>-699</v>
+        <v>-829</v>
       </c>
       <c r="E58" t="n">
-        <v>-3404</v>
+        <v>-360</v>
       </c>
       <c r="F58" t="n">
-        <v>2966</v>
+        <v>-4</v>
       </c>
       <c r="G58" t="n">
-        <v>3989</v>
+        <v>18</v>
       </c>
       <c r="H58" t="n">
-        <v>-1127</v>
+        <v>-257</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3344,36 +3344,36 @@
         </is>
       </c>
       <c r="K58" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M58" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>鑫龍騰</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>-534</v>
+        <v>45</v>
       </c>
       <c r="D59" t="n">
-        <v>-854</v>
+        <v>-1152</v>
       </c>
       <c r="E59" t="n">
-        <v>-2602</v>
+        <v>-2878</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -3382,7 +3382,7 @@
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>1332</v>
+        <v>-1</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3395,45 +3395,45 @@
         </is>
       </c>
       <c r="K59" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M59" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>205</v>
+        <v>-11</v>
       </c>
       <c r="D60" t="n">
-        <v>-857</v>
+        <v>-1159</v>
       </c>
       <c r="E60" t="n">
-        <v>-3911</v>
+        <v>-293</v>
       </c>
       <c r="F60" t="n">
-        <v>3</v>
+        <v>250</v>
       </c>
       <c r="G60" t="n">
-        <v>-100</v>
+        <v>1425</v>
       </c>
       <c r="H60" t="n">
-        <v>-13</v>
+        <v>-42</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3446,15 +3446,15 @@
         </is>
       </c>
       <c r="K60" t="n">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M60" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61">
@@ -3469,22 +3469,22 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>865</v>
+        <v>566</v>
       </c>
       <c r="D61" t="n">
-        <v>-862</v>
+        <v>-1185</v>
       </c>
       <c r="E61" t="n">
-        <v>1541</v>
+        <v>1336</v>
       </c>
       <c r="F61" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="G61" t="n">
-        <v>886</v>
+        <v>869</v>
       </c>
       <c r="H61" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3511,31 +3511,31 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1748</v>
+        <v>-226</v>
       </c>
       <c r="D62" t="n">
-        <v>-894</v>
+        <v>-1203</v>
       </c>
       <c r="E62" t="n">
-        <v>323</v>
+        <v>-870</v>
       </c>
       <c r="F62" t="n">
-        <v>57</v>
+        <v>-55</v>
       </c>
       <c r="G62" t="n">
-        <v>-18</v>
+        <v>-968</v>
       </c>
       <c r="H62" t="n">
-        <v>185</v>
+        <v>-70</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3544,49 +3544,49 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K62" t="n">
-        <v>32</v>
+        <v>96</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M62" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>270</v>
+        <v>3561</v>
       </c>
       <c r="D63" t="n">
-        <v>-1032</v>
+        <v>-1231</v>
       </c>
       <c r="E63" t="n">
-        <v>-68</v>
+        <v>-5773</v>
       </c>
       <c r="F63" t="n">
-        <v>181</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>1523</v>
+        <v>-9</v>
       </c>
       <c r="H63" t="n">
-        <v>-46</v>
+        <v>-142</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3595,49 +3595,49 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K63" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M63" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>鑫龍騰</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>204</v>
+        <v>14</v>
       </c>
       <c r="D64" t="n">
-        <v>-1170</v>
+        <v>-1231</v>
       </c>
       <c r="E64" t="n">
-        <v>-2712</v>
+        <v>-3678</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>-97</v>
       </c>
       <c r="H64" t="n">
-        <v>-0</v>
+        <v>-45</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3646,49 +3646,49 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K64" t="n">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>102</v>
+        <v>-291</v>
       </c>
       <c r="D65" t="n">
-        <v>-1277</v>
+        <v>-1604</v>
       </c>
       <c r="E65" t="n">
-        <v>-892</v>
+        <v>-3720</v>
       </c>
       <c r="F65" t="n">
-        <v>-233</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>-965</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-69</v>
+        <v>1482</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3697,190 +3697,190 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K65" t="n">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M65" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-43779</v>
+        <v>796</v>
       </c>
       <c r="D66" t="n">
-        <v>-1281</v>
+        <v>-1691</v>
       </c>
       <c r="E66" t="n">
-        <v>-3429</v>
+        <v>-3191</v>
       </c>
       <c r="F66" t="n">
-        <v>23673</v>
+        <v>-1340</v>
       </c>
       <c r="G66" t="n">
-        <v>29975</v>
+        <v>-629</v>
       </c>
       <c r="H66" t="n">
-        <v>775</v>
+        <v>57</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K66" t="n">
-        <v>80</v>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>🐌 龜速</t>
-        </is>
-      </c>
-      <c r="M66" t="n">
-        <v>-1</v>
-      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>203</v>
+        <v>-137</v>
       </c>
       <c r="D67" t="n">
-        <v>-1842</v>
+        <v>-1742</v>
       </c>
       <c r="E67" t="n">
-        <v>-4003</v>
+        <v>-7823</v>
       </c>
       <c r="F67" t="n">
-        <v>-1575</v>
+        <v>-519</v>
       </c>
       <c r="G67" t="n">
-        <v>-170</v>
+        <v>-1475</v>
       </c>
       <c r="H67" t="n">
-        <v>40</v>
+        <v>-32</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>90</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>🚀 加速器</t>
+        </is>
+      </c>
+      <c r="M67" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>84</v>
+        <v>991</v>
       </c>
       <c r="D68" t="n">
-        <v>-2207</v>
+        <v>-1943</v>
       </c>
       <c r="E68" t="n">
-        <v>-7557</v>
+        <v>-6464</v>
       </c>
       <c r="F68" t="n">
-        <v>-756</v>
+        <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>-1448</v>
+        <v>79</v>
       </c>
       <c r="H68" t="n">
-        <v>-17</v>
+        <v>-641</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🟡 中性</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K68" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M68" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2217</v>
+        <v>-3508</v>
       </c>
       <c r="D69" t="n">
-        <v>-2347</v>
+        <v>-2502</v>
       </c>
       <c r="E69" t="n">
-        <v>-3325</v>
+        <v>-3765</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>1102</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>5734</v>
       </c>
       <c r="H69" t="n">
-        <v>-295</v>
+        <v>-1709</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3889,49 +3889,49 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K69" t="n">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M69" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-1743</v>
+        <v>-432</v>
       </c>
       <c r="D70" t="n">
-        <v>-2352</v>
+        <v>-2718</v>
       </c>
       <c r="E70" t="n">
-        <v>-30</v>
+        <v>-1822</v>
       </c>
       <c r="F70" t="n">
-        <v>-726</v>
+        <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>801</v>
+        <v>1361</v>
       </c>
       <c r="H70" t="n">
-        <v>359</v>
+        <v>-622</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         </is>
       </c>
       <c r="K70" t="n">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -3952,37 +3952,37 @@
         </is>
       </c>
       <c r="M70" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>18</v>
+        <v>-1842</v>
       </c>
       <c r="D71" t="n">
-        <v>-2544</v>
+        <v>-2749</v>
       </c>
       <c r="E71" t="n">
-        <v>-7308</v>
+        <v>-97</v>
       </c>
       <c r="F71" t="n">
-        <v>2</v>
+        <v>-605</v>
       </c>
       <c r="G71" t="n">
-        <v>77</v>
+        <v>666</v>
       </c>
       <c r="H71" t="n">
-        <v>-1235</v>
+        <v>492</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -3991,11 +3991,11 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K71" t="n">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -4018,22 +4018,22 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-522</v>
+        <v>-1159</v>
       </c>
       <c r="D72" t="n">
-        <v>-2609</v>
+        <v>-3035</v>
       </c>
       <c r="E72" t="n">
-        <v>917</v>
+        <v>-56</v>
       </c>
       <c r="F72" t="n">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="G72" t="n">
-        <v>-206</v>
+        <v>-216</v>
       </c>
       <c r="H72" t="n">
-        <v>241</v>
+        <v>175</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -4069,22 +4069,22 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-541</v>
+        <v>-462</v>
       </c>
       <c r="D73" t="n">
-        <v>-2842</v>
+        <v>-3277</v>
       </c>
       <c r="E73" t="n">
-        <v>-11554</v>
+        <v>-12646</v>
       </c>
       <c r="F73" t="n">
-        <v>214</v>
+        <v>314</v>
       </c>
       <c r="G73" t="n">
-        <v>202</v>
+        <v>302</v>
       </c>
       <c r="H73" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -4111,31 +4111,31 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>湧德</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>-17</v>
+        <v>2150</v>
       </c>
       <c r="D74" t="n">
-        <v>-2903</v>
+        <v>-3296</v>
       </c>
       <c r="E74" t="n">
-        <v>5132</v>
+        <v>-3231</v>
       </c>
       <c r="F74" t="n">
-        <v>-177</v>
+        <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>-1277</v>
+        <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-93</v>
+        <v>-379</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -4144,11 +4144,11 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K74" t="n">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -4156,37 +4156,37 @@
         </is>
       </c>
       <c r="M74" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>玉晶光</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>-1151</v>
+        <v>-1114</v>
       </c>
       <c r="D75" t="n">
-        <v>-3202</v>
+        <v>-3370</v>
       </c>
       <c r="E75" t="n">
-        <v>-2686</v>
+        <v>2942</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="G75" t="n">
-        <v>1362</v>
+        <v>-1259</v>
       </c>
       <c r="H75" t="n">
-        <v>-678</v>
+        <v>-73</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -4195,19 +4195,19 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K75" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M75" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="76">
@@ -4222,13 +4222,13 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-1952</v>
+        <v>-1923</v>
       </c>
       <c r="D76" t="n">
-        <v>-3467</v>
+        <v>-3639</v>
       </c>
       <c r="E76" t="n">
-        <v>-381</v>
+        <v>-894</v>
       </c>
       <c r="F76" t="n">
         <v>1</v>
@@ -4237,7 +4237,7 @@
         <v>1</v>
       </c>
       <c r="H76" t="n">
-        <v>-998</v>
+        <v>-874</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -4273,22 +4273,22 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>222</v>
+        <v>111</v>
       </c>
       <c r="D77" t="n">
-        <v>-3990</v>
+        <v>-3683</v>
       </c>
       <c r="E77" t="n">
-        <v>-3889</v>
+        <v>-4875</v>
       </c>
       <c r="F77" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G77" t="n">
-        <v>6</v>
+        <v>-2</v>
       </c>
       <c r="H77" t="n">
-        <v>-357</v>
+        <v>-293</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -4315,31 +4315,31 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>177</v>
+        <v>-2162</v>
       </c>
       <c r="D78" t="n">
-        <v>-4447</v>
+        <v>-4284</v>
       </c>
       <c r="E78" t="n">
-        <v>-18947</v>
+        <v>-3788</v>
       </c>
       <c r="F78" t="n">
-        <v>2</v>
+        <v>-1428</v>
       </c>
       <c r="G78" t="n">
-        <v>285</v>
+        <v>-9758</v>
       </c>
       <c r="H78" t="n">
-        <v>17</v>
+        <v>228</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -4348,11 +4348,11 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K78" t="n">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         </is>
       </c>
       <c r="M78" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -4375,22 +4375,22 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-1636</v>
+        <v>-1969</v>
       </c>
       <c r="D79" t="n">
-        <v>-4588</v>
+        <v>-4452</v>
       </c>
       <c r="E79" t="n">
-        <v>-8768</v>
+        <v>-8720</v>
       </c>
       <c r="F79" t="n">
-        <v>1985</v>
+        <v>2146</v>
       </c>
       <c r="G79" t="n">
-        <v>871</v>
+        <v>928</v>
       </c>
       <c r="H79" t="n">
-        <v>-161</v>
+        <v>-132</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -4417,31 +4417,31 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>-152</v>
+        <v>71</v>
       </c>
       <c r="D80" t="n">
-        <v>-5200</v>
+        <v>-4589</v>
       </c>
       <c r="E80" t="n">
-        <v>-4497</v>
+        <v>-18608</v>
       </c>
       <c r="F80" t="n">
-        <v>304</v>
+        <v>1</v>
       </c>
       <c r="G80" t="n">
-        <v>3373</v>
+        <v>285</v>
       </c>
       <c r="H80" t="n">
-        <v>-414</v>
+        <v>135</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -4450,49 +4450,49 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K80" t="n">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M80" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-372</v>
+        <v>-1434</v>
       </c>
       <c r="D81" t="n">
-        <v>-5206</v>
+        <v>-4806</v>
       </c>
       <c r="E81" t="n">
-        <v>-5621</v>
+        <v>-11243</v>
       </c>
       <c r="F81" t="n">
-        <v>51</v>
+        <v>-846</v>
       </c>
       <c r="G81" t="n">
-        <v>1592</v>
+        <v>-667</v>
       </c>
       <c r="H81" t="n">
-        <v>-95</v>
+        <v>-64</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4501,15 +4501,15 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K81" t="n">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M81" t="n">
@@ -4519,31 +4519,31 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1694</v>
+        <v>-67</v>
       </c>
       <c r="D82" t="n">
-        <v>-5368</v>
+        <v>-5123</v>
       </c>
       <c r="E82" t="n">
-        <v>-2302</v>
+        <v>-4017</v>
       </c>
       <c r="F82" t="n">
-        <v>226</v>
+        <v>56</v>
       </c>
       <c r="G82" t="n">
-        <v>-89</v>
+        <v>3105</v>
       </c>
       <c r="H82" t="n">
-        <v>-305</v>
+        <v>-311</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -4552,15 +4552,15 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K82" t="n">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M82" t="n">
@@ -4570,32 +4570,32 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>鈊象</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-1078</v>
+        <v>-1724</v>
       </c>
       <c r="D83" t="n">
-        <v>-5614</v>
+        <v>-5443</v>
       </c>
       <c r="E83" t="n">
-        <v>-9481</v>
+        <v>-13446</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>4855</v>
       </c>
       <c r="G83" t="n">
+        <v>10367</v>
+      </c>
+      <c r="H83" t="n">
         <v>-8</v>
       </c>
-      <c r="H83" t="n">
-        <v>-602</v>
-      </c>
       <c r="I83" t="inlineStr">
         <is>
           <t>🟠 減碼</t>
@@ -4607,45 +4607,45 @@
         </is>
       </c>
       <c r="K83" t="n">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M83" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-2057</v>
+        <v>-302</v>
       </c>
       <c r="D84" t="n">
-        <v>-5760</v>
+        <v>-5471</v>
       </c>
       <c r="E84" t="n">
-        <v>-12511</v>
+        <v>-5649</v>
       </c>
       <c r="F84" t="n">
-        <v>-392</v>
+        <v>96</v>
       </c>
       <c r="G84" t="n">
-        <v>-191</v>
+        <v>1650</v>
       </c>
       <c r="H84" t="n">
-        <v>-197</v>
+        <v>-102</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -4654,15 +4654,15 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K84" t="n">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M84" t="n">
@@ -4672,31 +4672,31 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>-1234</v>
+        <v>1725</v>
       </c>
       <c r="D85" t="n">
-        <v>-6582</v>
+        <v>-5545</v>
       </c>
       <c r="E85" t="n">
-        <v>-12264</v>
+        <v>-199</v>
       </c>
       <c r="F85" t="n">
-        <v>4748</v>
+        <v>225</v>
       </c>
       <c r="G85" t="n">
-        <v>11692</v>
+        <v>-92</v>
       </c>
       <c r="H85" t="n">
-        <v>-145</v>
+        <v>-162</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -4705,15 +4705,15 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K85" t="n">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M85" t="n">
@@ -4723,31 +4723,31 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-2046</v>
+        <v>-41422</v>
       </c>
       <c r="D86" t="n">
-        <v>-7792</v>
+        <v>-6206</v>
       </c>
       <c r="E86" t="n">
-        <v>-5365</v>
+        <v>-7627</v>
       </c>
       <c r="F86" t="n">
-        <v>-1430</v>
+        <v>23078</v>
       </c>
       <c r="G86" t="n">
-        <v>-8609</v>
+        <v>34138</v>
       </c>
       <c r="H86" t="n">
-        <v>16</v>
+        <v>891</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -4756,49 +4756,49 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K86" t="n">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>-886</v>
+        <v>-3279</v>
       </c>
       <c r="D87" t="n">
-        <v>-8669</v>
+        <v>-6245</v>
       </c>
       <c r="E87" t="n">
-        <v>29461</v>
+        <v>-24084</v>
       </c>
       <c r="F87" t="n">
-        <v>-71</v>
+        <v>-268</v>
       </c>
       <c r="G87" t="n">
-        <v>-11067</v>
+        <v>-2596</v>
       </c>
       <c r="H87" t="n">
-        <v>-544</v>
+        <v>-1781</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -4807,49 +4807,49 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K87" t="n">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M87" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>-7499</v>
+        <v>-1389</v>
       </c>
       <c r="D88" t="n">
-        <v>-9450</v>
+        <v>-9703</v>
       </c>
       <c r="E88" t="n">
-        <v>-15102</v>
+        <v>29435</v>
       </c>
       <c r="F88" t="n">
-        <v>3840</v>
+        <v>-66</v>
       </c>
       <c r="G88" t="n">
-        <v>8208</v>
+        <v>-11193</v>
       </c>
       <c r="H88" t="n">
-        <v>107</v>
+        <v>-324</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -4858,53 +4858,53 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K88" t="n">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M88" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>立隆電</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-3092</v>
+        <v>-8432</v>
       </c>
       <c r="D89" t="n">
-        <v>-9656</v>
+        <v>-10249</v>
       </c>
       <c r="E89" t="n">
-        <v>-28342</v>
+        <v>-15885</v>
       </c>
       <c r="F89" t="n">
-        <v>-224</v>
+        <v>2433</v>
       </c>
       <c r="G89" t="n">
-        <v>-2905</v>
+        <v>8209</v>
       </c>
       <c r="H89" t="n">
-        <v>-2248</v>
+        <v>66</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🔴 大賣</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -4913,7 +4913,7 @@
         </is>
       </c>
       <c r="K89" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -4936,22 +4936,22 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>783</v>
+        <v>2784</v>
       </c>
       <c r="D90" t="n">
-        <v>-13492</v>
+        <v>-11111</v>
       </c>
       <c r="E90" t="n">
-        <v>-67538</v>
+        <v>-65963</v>
       </c>
       <c r="F90" t="n">
-        <v>608</v>
+        <v>678</v>
       </c>
       <c r="G90" t="n">
-        <v>8103</v>
+        <v>8154</v>
       </c>
       <c r="H90" t="n">
-        <v>-293</v>
+        <v>-298</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -4987,22 +4987,22 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>-9774</v>
+        <v>-7327</v>
       </c>
       <c r="D91" t="n">
-        <v>-16113</v>
+        <v>-13862</v>
       </c>
       <c r="E91" t="n">
-        <v>3009</v>
+        <v>4115</v>
       </c>
       <c r="F91" t="n">
-        <v>3713</v>
+        <v>2030</v>
       </c>
       <c r="G91" t="n">
-        <v>12988</v>
+        <v>12939</v>
       </c>
       <c r="H91" t="n">
-        <v>-22</v>
+        <v>-27</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -5029,31 +5029,31 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>-2545</v>
+        <v>-8175</v>
       </c>
       <c r="D92" t="n">
-        <v>-17025</v>
+        <v>-16386</v>
       </c>
       <c r="E92" t="n">
-        <v>-45192</v>
+        <v>-21414</v>
       </c>
       <c r="F92" t="n">
-        <v>1767</v>
+        <v>6397</v>
       </c>
       <c r="G92" t="n">
-        <v>22841</v>
+        <v>16481</v>
       </c>
       <c r="H92" t="n">
-        <v>-1129</v>
+        <v>-593</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -5062,49 +5062,49 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K92" t="n">
-        <v>94</v>
+        <v>61</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M92" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>-7836</v>
+        <v>492</v>
       </c>
       <c r="D93" t="n">
-        <v>-18408</v>
+        <v>-16682</v>
       </c>
       <c r="E93" t="n">
-        <v>-18183</v>
+        <v>-42210</v>
       </c>
       <c r="F93" t="n">
-        <v>6388</v>
+        <v>1073</v>
       </c>
       <c r="G93" t="n">
-        <v>18303</v>
+        <v>22891</v>
       </c>
       <c r="H93" t="n">
-        <v>-651</v>
+        <v>-724</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -5113,49 +5113,49 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K93" t="n">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M93" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-1868</v>
+        <v>-16887</v>
       </c>
       <c r="D94" t="n">
-        <v>-21207</v>
+        <v>-19831</v>
       </c>
       <c r="E94" t="n">
-        <v>-29704</v>
+        <v>121708</v>
       </c>
       <c r="F94" t="n">
-        <v>-338</v>
+        <v>-15305</v>
       </c>
       <c r="G94" t="n">
-        <v>-11905</v>
+        <v>66572</v>
       </c>
       <c r="H94" t="n">
-        <v>-2059</v>
+        <v>-5897</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -5164,49 +5164,49 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K94" t="n">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>-24206</v>
+        <v>-4067</v>
       </c>
       <c r="D95" t="n">
-        <v>-22579</v>
+        <v>-22249</v>
       </c>
       <c r="E95" t="n">
-        <v>119088</v>
+        <v>-29276</v>
       </c>
       <c r="F95" t="n">
-        <v>-13136</v>
+        <v>-505</v>
       </c>
       <c r="G95" t="n">
-        <v>65569</v>
+        <v>-12337</v>
       </c>
       <c r="H95" t="n">
-        <v>-6176</v>
+        <v>-1854</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -5215,19 +5215,19 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K95" t="n">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M95" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -5242,22 +5242,22 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>-15093</v>
+        <v>-20165</v>
       </c>
       <c r="D96" t="n">
-        <v>-23657</v>
+        <v>-27141</v>
       </c>
       <c r="E96" t="n">
-        <v>102056</v>
+        <v>82620</v>
       </c>
       <c r="F96" t="n">
-        <v>24363</v>
+        <v>24629</v>
       </c>
       <c r="G96" t="n">
-        <v>23855</v>
+        <v>28584</v>
       </c>
       <c r="H96" t="n">
-        <v>21376</v>
+        <v>22293</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -5293,22 +5293,22 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>8223</v>
+        <v>6331</v>
       </c>
       <c r="D97" t="n">
-        <v>-50738</v>
+        <v>-42874</v>
       </c>
       <c r="E97" t="n">
-        <v>-85025</v>
+        <v>-79809</v>
       </c>
       <c r="F97" t="n">
-        <v>-12923</v>
+        <v>-14268</v>
       </c>
       <c r="G97" t="n">
-        <v>32843</v>
+        <v>32875</v>
       </c>
       <c r="H97" t="n">
-        <v>-1296</v>
+        <v>-1890</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -5335,31 +5335,31 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-48312</v>
+        <v>-3318</v>
       </c>
       <c r="D98" t="n">
-        <v>-59921</v>
+        <v>-55976</v>
       </c>
       <c r="E98" t="n">
-        <v>-131627</v>
+        <v>-275419</v>
       </c>
       <c r="F98" t="n">
-        <v>18181</v>
+        <v>10994</v>
       </c>
       <c r="G98" t="n">
-        <v>24311</v>
+        <v>85347</v>
       </c>
       <c r="H98" t="n">
-        <v>3588</v>
+        <v>1606</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -5368,15 +5368,15 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K98" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M98" t="n">
@@ -5386,31 +5386,31 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1127</v>
+        <v>-44289</v>
       </c>
       <c r="D99" t="n">
-        <v>-67101</v>
+        <v>-58249</v>
       </c>
       <c r="E99" t="n">
-        <v>-271877</v>
+        <v>-135089</v>
       </c>
       <c r="F99" t="n">
-        <v>11738</v>
+        <v>17810</v>
       </c>
       <c r="G99" t="n">
-        <v>100921</v>
+        <v>27701</v>
       </c>
       <c r="H99" t="n">
-        <v>1551</v>
+        <v>3784</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -5419,15 +5419,15 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K99" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M99" t="n">
@@ -5446,22 +5446,22 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>-20729</v>
+        <v>-19057</v>
       </c>
       <c r="D100" t="n">
-        <v>-115021</v>
+        <v>-94797</v>
       </c>
       <c r="E100" t="n">
-        <v>-279055</v>
+        <v>-277163</v>
       </c>
       <c r="F100" t="n">
-        <v>7419</v>
+        <v>6880</v>
       </c>
       <c r="G100" t="n">
-        <v>8592</v>
+        <v>8242</v>
       </c>
       <c r="H100" t="n">
-        <v>7808</v>
+        <v>8142</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -5497,22 +5497,22 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-39125</v>
+        <v>-39330</v>
       </c>
       <c r="D101" t="n">
-        <v>-133415</v>
+        <v>-142963</v>
       </c>
       <c r="E101" t="n">
-        <v>-164333</v>
+        <v>-170213</v>
       </c>
       <c r="F101" t="n">
-        <v>25966</v>
+        <v>25682</v>
       </c>
       <c r="G101" t="n">
-        <v>127127</v>
+        <v>135513</v>
       </c>
       <c r="H101" t="n">
-        <v>5999</v>
+        <v>6012</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -5539,31 +5539,31 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>-34135</v>
+        <v>-56286</v>
       </c>
       <c r="D102" t="n">
-        <v>-175849</v>
+        <v>-218200</v>
       </c>
       <c r="E102" t="n">
-        <v>33355</v>
+        <v>427292</v>
       </c>
       <c r="F102" t="n">
-        <v>-58236</v>
+        <v>2800</v>
       </c>
       <c r="G102" t="n">
-        <v>129701</v>
+        <v>4108</v>
       </c>
       <c r="H102" t="n">
-        <v>-177</v>
+        <v>-3426</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -5572,19 +5572,19 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K102" t="n">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M102" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="103">
@@ -5599,22 +5599,22 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>-35494</v>
+        <v>-42300</v>
       </c>
       <c r="D103" t="n">
-        <v>-213241</v>
+        <v>-225029</v>
       </c>
       <c r="E103" t="n">
-        <v>-70481</v>
+        <v>-87034</v>
       </c>
       <c r="F103" t="n">
-        <v>28201</v>
+        <v>27283</v>
       </c>
       <c r="G103" t="n">
-        <v>56098</v>
+        <v>59308</v>
       </c>
       <c r="H103" t="n">
-        <v>605</v>
+        <v>1817</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -5641,31 +5641,31 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>-68160</v>
+        <v>-39178</v>
       </c>
       <c r="D104" t="n">
-        <v>-214912</v>
+        <v>-231922</v>
       </c>
       <c r="E104" t="n">
-        <v>475826</v>
+        <v>11013</v>
       </c>
       <c r="F104" t="n">
-        <v>2397</v>
+        <v>-71638</v>
       </c>
       <c r="G104" t="n">
-        <v>2481</v>
+        <v>137646</v>
       </c>
       <c r="H104" t="n">
-        <v>-4617</v>
+        <v>2020</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -5674,19 +5674,19 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K104" t="n">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M104" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5700,7 +5700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5743,58 +5743,58 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 601 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -1,462 千股)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>83549</v>
+        <v>-1206948</v>
       </c>
       <c r="D2" t="n">
-        <v>-2207485</v>
+        <v>629154</v>
       </c>
       <c r="E2" t="n">
-        <v>-132094</v>
+        <v>320656</v>
       </c>
       <c r="F2" t="n">
-        <v>-2808924</v>
+        <v>2090908</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>台光電</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 7 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,104 千股)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>484836</v>
+        <v>365537</v>
       </c>
       <c r="D3" t="n">
-        <v>1543754</v>
+        <v>2134968</v>
       </c>
       <c r="E3" t="n">
-        <v>1297337</v>
+        <v>435685</v>
       </c>
       <c r="F3" t="n">
-        <v>1536366</v>
+        <v>3238964</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>高力</t>
         </is>
       </c>
     </row>
@@ -5806,20 +5806,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 799 千股)</t>
+          <t>📉 20d 巨變(減碼 -711 千股)</t>
         </is>
       </c>
       <c r="C4" t="n">
+        <v>2623750</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1076448</v>
+      </c>
+      <c r="E4" t="n">
         <v>3287626</v>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>1787781</v>
-      </c>
-      <c r="E4" t="n">
-        <v>938605</v>
-      </c>
-      <c r="F4" t="n">
-        <v>988549</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -5830,435 +5830,435 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 230 千股)</t>
+          <t>📉 20d 巨變(減碼 -158 千股)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-3720877</v>
+        <v>35324</v>
       </c>
       <c r="D5" t="n">
-        <v>-698890</v>
+        <v>1385490</v>
       </c>
       <c r="E5" t="n">
-        <v>-800201</v>
+        <v>484836</v>
       </c>
       <c r="F5" t="n">
-        <v>-928939</v>
+        <v>1543754</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>健策</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 317 千股)</t>
+          <t>📈 20d 巨變(加碼 1,085 千股)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>320656</v>
+        <v>-5432097</v>
       </c>
       <c r="D6" t="n">
-        <v>2090908</v>
+        <v>385624</v>
       </c>
       <c r="E6" t="n">
-        <v>83675</v>
+        <v>-3720877</v>
       </c>
       <c r="F6" t="n">
-        <v>1774295</v>
+        <v>-698890</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>亞翔</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 491 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 466 千股)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>435685</v>
+        <v>-137202</v>
       </c>
       <c r="D7" t="n">
-        <v>3238964</v>
+        <v>-1741839</v>
       </c>
       <c r="E7" t="n">
-        <v>699280</v>
+        <v>83549</v>
       </c>
       <c r="F7" t="n">
-        <v>2747557</v>
+        <v>-2207485</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>勤誠</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 15 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -56 千股)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>269778</v>
+        <v>-149213</v>
       </c>
       <c r="D8" t="n">
-        <v>-1032083</v>
+        <v>5689071</v>
       </c>
       <c r="E8" t="n">
-        <v>216158</v>
+        <v>20061</v>
       </c>
       <c r="F8" t="n">
-        <v>-1046867</v>
+        <v>5745220</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>致茂</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -321 千股)</t>
+          <t>📉 20d 巨變(減碼 -523 千股)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>101559</v>
+        <v>220229</v>
       </c>
       <c r="D9" t="n">
-        <v>-1276814</v>
+        <v>783557</v>
       </c>
       <c r="E9" t="n">
-        <v>-91018</v>
+        <v>331609</v>
       </c>
       <c r="F9" t="n">
-        <v>-956229</v>
+        <v>1306969</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>智邦</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 40 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 73 千股)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>20061</v>
+        <v>-225557</v>
       </c>
       <c r="D10" t="n">
-        <v>5745220</v>
+        <v>-1203395</v>
       </c>
       <c r="E10" t="n">
-        <v>106496</v>
+        <v>101559</v>
       </c>
       <c r="F10" t="n">
-        <v>5704945</v>
+        <v>-1276814</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>光聖</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 41 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -127 千股)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>331609</v>
+        <v>-11364</v>
       </c>
       <c r="D11" t="n">
-        <v>1306969</v>
+        <v>-1158965</v>
       </c>
       <c r="E11" t="n">
-        <v>1219620</v>
+        <v>269778</v>
       </c>
       <c r="F11" t="n">
-        <v>1265482</v>
+        <v>-1032083</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>旺矽</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 559 千股)</t>
+          <t>📈 20d 巨變(加碼 20,224 千股)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>221635</v>
+        <v>-19057291</v>
       </c>
       <c r="D12" t="n">
-        <v>-3990364</v>
+        <v>-94797468</v>
       </c>
       <c r="E12" t="n">
-        <v>-339140</v>
+        <v>-20728692</v>
       </c>
       <c r="F12" t="n">
-        <v>-4549268</v>
+        <v>-115021028</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 5,303 千股)</t>
+          <t>📈 20d 巨變(加碼 307 千股)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-20728692</v>
+        <v>110793</v>
       </c>
       <c r="D13" t="n">
-        <v>-115021028</v>
+        <v>-3683409</v>
       </c>
       <c r="E13" t="n">
-        <v>-22473322</v>
+        <v>221635</v>
       </c>
       <c r="F13" t="n">
-        <v>-120324084</v>
+        <v>-3990364</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>雙鴻</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 23 千股)</t>
+          <t>📉 20d 巨變(減碼 -323 千股)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>456057</v>
+        <v>565831</v>
       </c>
       <c r="D14" t="n">
-        <v>-249653</v>
+        <v>-1185391</v>
       </c>
       <c r="E14" t="n">
-        <v>-958250</v>
+        <v>864669</v>
       </c>
       <c r="F14" t="n">
-        <v>-272605</v>
+        <v>-862007</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>帆宣</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,152 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,043 千股)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>664569</v>
+        <v>-4067211</v>
       </c>
       <c r="D15" t="n">
-        <v>1878508</v>
+        <v>-22249419</v>
       </c>
       <c r="E15" t="n">
-        <v>1774135</v>
+        <v>-1867636</v>
       </c>
       <c r="F15" t="n">
-        <v>3030859</v>
+        <v>-21206568</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>台達電</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 2,798 千股)</t>
+          <t>📉 20d 巨變(減碼 -579 千股)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-1867636</v>
+        <v>842276</v>
       </c>
       <c r="D16" t="n">
-        <v>-21206568</v>
+        <v>-828616</v>
       </c>
       <c r="E16" t="n">
-        <v>-7783974</v>
+        <v>456057</v>
       </c>
       <c r="F16" t="n">
-        <v>-24004830</v>
+        <v>-249653</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>佳必琪</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 540 千股)</t>
+          <t>📉 20d 巨變(減碼 -12 千股)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5709338</v>
+        <v>-308178</v>
       </c>
       <c r="D17" t="n">
-        <v>11088894</v>
+        <v>275142</v>
       </c>
       <c r="E17" t="n">
-        <v>5706754</v>
+        <v>-240219</v>
       </c>
       <c r="F17" t="n">
-        <v>10548997</v>
+        <v>286741</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>川湖</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -109 千股)</t>
+          <t>📉 20d 巨變(減碼 -529 千股)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>864669</v>
+        <v>4515721</v>
       </c>
       <c r="D18" t="n">
-        <v>-862007</v>
+        <v>10559458</v>
       </c>
       <c r="E18" t="n">
-        <v>386508</v>
+        <v>5709338</v>
       </c>
       <c r="F18" t="n">
-        <v>-753279</v>
+        <v>11088894</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>健鼎</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 150 千股)</t>
+          <t>📉 20d 巨變(減碼 -361 千股)</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-240219</v>
+        <v>381391</v>
       </c>
       <c r="D19" t="n">
-        <v>286741</v>
+        <v>1517230</v>
       </c>
       <c r="E19" t="n">
-        <v>-176894</v>
+        <v>664569</v>
       </c>
       <c r="F19" t="n">
-        <v>136336</v>
+        <v>1878508</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>辛耘</t>
         </is>
       </c>
     </row>
@@ -6270,20 +6270,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -667 千股)</t>
+          <t>📉 20d 巨變(減碼 -882 千股)</t>
         </is>
       </c>
       <c r="C20" t="n">
+        <v>-3802047</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-356298</v>
+      </c>
+      <c r="E20" t="n">
         <v>-2406640</v>
       </c>
-      <c r="D20" t="n">
+      <c r="F20" t="n">
         <v>525639</v>
-      </c>
-      <c r="E20" t="n">
-        <v>-2200986</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1192438</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -6294,203 +6294,203 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 287 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 342 千股)</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-255121</v>
+        <v>492096</v>
       </c>
       <c r="D21" t="n">
-        <v>832654</v>
+        <v>-16682304</v>
       </c>
       <c r="E21" t="n">
-        <v>-205986</v>
+        <v>-2544773</v>
       </c>
       <c r="F21" t="n">
-        <v>545695</v>
+        <v>-17024626</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>中興電</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,133 千股)</t>
+          <t>📉 20d 巨變(減碼 -39 千股)</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-2544773</v>
+        <v>-218020</v>
       </c>
       <c r="D22" t="n">
-        <v>-17024626</v>
+        <v>1303799</v>
       </c>
       <c r="E22" t="n">
-        <v>-5327595</v>
+        <v>-46203</v>
       </c>
       <c r="F22" t="n">
-        <v>-15891394</v>
+        <v>1343026</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>中砂</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -236 千股)</t>
+          <t>📉 20d 巨變(減碼 -33 千股)</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-46203</v>
+        <v>-540862</v>
       </c>
       <c r="D23" t="n">
-        <v>1343026</v>
+        <v>799476</v>
       </c>
       <c r="E23" t="n">
-        <v>21670</v>
+        <v>-255121</v>
       </c>
       <c r="F23" t="n">
-        <v>1578571</v>
+        <v>832654</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>建榮</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 424 千股)</t>
+          <t>📉 20d 巨變(減碼 -397 千股)</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-2057302</v>
+        <v>-1842060</v>
       </c>
       <c r="D24" t="n">
-        <v>-5759726</v>
+        <v>-2748932</v>
       </c>
       <c r="E24" t="n">
-        <v>-2239320</v>
+        <v>-1742870</v>
       </c>
       <c r="F24" t="n">
-        <v>-6183357</v>
+        <v>-2351989</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>大立光</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -331 千股)</t>
+          <t>📈 20d 巨變(加碼 953 千股)</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-1742870</v>
+        <v>-1434083</v>
       </c>
       <c r="D25" t="n">
-        <v>-2351989</v>
+        <v>-4806379</v>
       </c>
       <c r="E25" t="n">
-        <v>-1614307</v>
+        <v>-2057302</v>
       </c>
       <c r="F25" t="n">
-        <v>-2021046</v>
+        <v>-5759726</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>華城</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -11 千股)</t>
+          <t>📉 20d 巨變(減碼 -853 千股)</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>7326</v>
+        <v>2058724</v>
       </c>
       <c r="D26" t="n">
-        <v>-154963</v>
+        <v>2795750</v>
       </c>
       <c r="E26" t="n">
-        <v>15070</v>
+        <v>1395204</v>
       </c>
       <c r="F26" t="n">
-        <v>-144136</v>
+        <v>3648892</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>大車隊</t>
+          <t>零壹</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -459 千股)</t>
+          <t>📉 20d 巨變(減碼 -6 千股)</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-457748</v>
+        <v>5286</v>
       </c>
       <c r="D27" t="n">
-        <v>944413</v>
+        <v>-160980</v>
       </c>
       <c r="E27" t="n">
-        <v>153502</v>
+        <v>7326</v>
       </c>
       <c r="F27" t="n">
-        <v>1403663</v>
+        <v>-154963</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>大車隊</t>
         </is>
       </c>
     </row>
@@ -6502,20 +6502,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 13 千股)</t>
+          <t>📉 20d 巨變(減碼 -17 千股)</t>
         </is>
       </c>
       <c r="C28" t="n">
+        <v>44390</v>
+      </c>
+      <c r="D28" t="n">
+        <v>352853</v>
+      </c>
+      <c r="E28" t="n">
         <v>48693</v>
       </c>
-      <c r="D28" t="n">
+      <c r="F28" t="n">
         <v>369457</v>
-      </c>
-      <c r="E28" t="n">
-        <v>49273</v>
-      </c>
-      <c r="F28" t="n">
-        <v>356037</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -6526,116 +6526,116 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 725 千股)</t>
+          <t>📉 20d 巨變(減碼 -948 千股)</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1395204</v>
+        <v>2150396</v>
       </c>
       <c r="D29" t="n">
-        <v>3648892</v>
+        <v>-3295719</v>
       </c>
       <c r="E29" t="n">
-        <v>682338</v>
+        <v>2217419</v>
       </c>
       <c r="F29" t="n">
-        <v>2923758</v>
+        <v>-2347434</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>湧德</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 246 千股)</t>
+          <t>📉 20d 巨變(減碼 -177 千股)</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2217419</v>
+        <v>1725471</v>
       </c>
       <c r="D30" t="n">
-        <v>-2347434</v>
+        <v>-5544849</v>
       </c>
       <c r="E30" t="n">
-        <v>1346049</v>
+        <v>1694120</v>
       </c>
       <c r="F30" t="n">
-        <v>-2593883</v>
+        <v>-5367585</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>建準</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 730 千股)</t>
+          <t>📉 20d 巨變(減碼 -328 千股)</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1694120</v>
+        <v>-741748</v>
       </c>
       <c r="D31" t="n">
-        <v>-5367585</v>
+        <v>616413</v>
       </c>
       <c r="E31" t="n">
-        <v>76291</v>
+        <v>-457748</v>
       </c>
       <c r="F31" t="n">
-        <v>-6097204</v>
+        <v>944413</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>隆大</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 502 千股)</t>
+          <t>📉 20d 巨變(減碼 -10 千股)</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>690556</v>
+        <v>-1478612</v>
       </c>
       <c r="D32" t="n">
-        <v>2234780</v>
+        <v>1049961</v>
       </c>
       <c r="E32" t="n">
-        <v>434825</v>
+        <v>-2232522</v>
       </c>
       <c r="F32" t="n">
-        <v>1733134</v>
+        <v>1059866</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>合機</t>
+          <t>卜蜂</t>
         </is>
       </c>
     </row>
@@ -6647,20 +6647,20 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -246 千股)</t>
+          <t>📉 20d 巨變(減碼 -395 千股)</t>
         </is>
       </c>
       <c r="C33" t="n">
+        <v>-824583</v>
+      </c>
+      <c r="D33" t="n">
+        <v>659823</v>
+      </c>
+      <c r="E33" t="n">
         <v>-456949</v>
       </c>
-      <c r="D33" t="n">
+      <c r="F33" t="n">
         <v>1054367</v>
-      </c>
-      <c r="E33" t="n">
-        <v>-303075</v>
-      </c>
-      <c r="F33" t="n">
-        <v>1299977</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -6671,58 +6671,58 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 7,218 千股)</t>
+          <t>📉 20d 巨變(減碼 -168 千股)</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-52104977</v>
+        <v>829916</v>
       </c>
       <c r="D34" t="n">
-        <v>197618224</v>
+        <v>2066635</v>
       </c>
       <c r="E34" t="n">
-        <v>-40076614</v>
+        <v>690556</v>
       </c>
       <c r="F34" t="n">
-        <v>190400051</v>
+        <v>2234780</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>合機</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -874 千股)</t>
+          <t>📉 20d 巨變(減碼 -66 千股)</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-2232522</v>
+        <v>123331</v>
       </c>
       <c r="D35" t="n">
-        <v>1059866</v>
+        <v>-541501</v>
       </c>
       <c r="E35" t="n">
-        <v>-2594232</v>
+        <v>187331</v>
       </c>
       <c r="F35" t="n">
-        <v>1933566</v>
+        <v>-475501</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>大統益</t>
         </is>
       </c>
     </row>
@@ -6734,20 +6734,20 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -54 千股)</t>
+          <t>📈 20d 巨變(加碼 118 千股)</t>
         </is>
       </c>
       <c r="C36" t="n">
+        <v>2049456</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-775576</v>
+      </c>
+      <c r="E36" t="n">
         <v>1748454</v>
       </c>
-      <c r="D36" t="n">
+      <c r="F36" t="n">
         <v>-894008</v>
-      </c>
-      <c r="E36" t="n">
-        <v>2234168</v>
-      </c>
-      <c r="F36" t="n">
-        <v>-839539</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -6758,348 +6758,348 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 342 千股)</t>
+          <t>📉 20d 巨變(減碼 -444 千股)</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>187331</v>
+        <v>-48937896</v>
       </c>
       <c r="D37" t="n">
-        <v>-475501</v>
+        <v>197174163</v>
       </c>
       <c r="E37" t="n">
-        <v>-295750</v>
+        <v>-52104977</v>
       </c>
       <c r="F37" t="n">
-        <v>-817582</v>
+        <v>197618224</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 158 千股)</t>
+          <t>📉 20d 巨變(減碼 -112 千股)</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-519407</v>
+        <v>21399</v>
       </c>
       <c r="D38" t="n">
-        <v>1121682</v>
+        <v>474845</v>
       </c>
       <c r="E38" t="n">
-        <v>-568650</v>
+        <v>78325</v>
       </c>
       <c r="F38" t="n">
-        <v>963359</v>
+        <v>586845</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>智冠</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -35 千股)</t>
+          <t>📉 20d 巨變(減碼 -374 千股)</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>72356</v>
+        <v>14159</v>
       </c>
       <c r="D39" t="n">
-        <v>-350985</v>
+        <v>-1231370</v>
       </c>
       <c r="E39" t="n">
-        <v>263221</v>
+        <v>205038</v>
       </c>
       <c r="F39" t="n">
-        <v>-315671</v>
+        <v>-857067</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>華景電</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 237 千股)</t>
+          <t>📉 20d 巨變(減碼 -254 千股)</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>205038</v>
+        <v>-512407</v>
       </c>
       <c r="D40" t="n">
-        <v>-857067</v>
+        <v>867682</v>
       </c>
       <c r="E40" t="n">
-        <v>18543</v>
+        <v>-519407</v>
       </c>
       <c r="F40" t="n">
-        <v>-1093984</v>
+        <v>1121682</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>八方雲集</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -11,402 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -53 千股)</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-43778879</v>
+        <v>-166534</v>
       </c>
       <c r="D41" t="n">
-        <v>-1280701</v>
+        <v>-404044</v>
       </c>
       <c r="E41" t="n">
-        <v>-36628981</v>
+        <v>72356</v>
       </c>
       <c r="F41" t="n">
-        <v>10120854</v>
+        <v>-350985</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>穎崴</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -8 千股)</t>
+          <t>📉 20d 巨變(減碼 -4,925 千股)</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-48300</v>
+        <v>-41421559</v>
       </c>
       <c r="D42" t="n">
-        <v>-275300</v>
+        <v>-6205883</v>
       </c>
       <c r="E42" t="n">
-        <v>-112000</v>
+        <v>-43778879</v>
       </c>
       <c r="F42" t="n">
-        <v>-267000</v>
+        <v>-1280701</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>聯合</t>
+          <t>台灣大</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 2,693 千股)</t>
+          <t>📈 20d 巨變(加碼 41 千股)</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>782768</v>
+        <v>-92300</v>
       </c>
       <c r="D43" t="n">
-        <v>-13492329</v>
+        <v>-234300</v>
       </c>
       <c r="E43" t="n">
-        <v>-1607048</v>
+        <v>-48300</v>
       </c>
       <c r="F43" t="n">
-        <v>-16184928</v>
+        <v>-275300</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>聯合</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,531 千股)</t>
+          <t>📈 20d 巨變(加碼 2,382 千股)</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-1078303</v>
+        <v>2784253</v>
       </c>
       <c r="D44" t="n">
-        <v>-5613622</v>
+        <v>-11110546</v>
       </c>
       <c r="E44" t="n">
-        <v>-606801</v>
+        <v>782768</v>
       </c>
       <c r="F44" t="n">
-        <v>-7145116</v>
+        <v>-13492329</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -60 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 4,383 千股)</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-1264743</v>
+        <v>3560636</v>
       </c>
       <c r="D45" t="n">
-        <v>535803</v>
+        <v>-1231035</v>
       </c>
       <c r="E45" t="n">
-        <v>-1509877</v>
+        <v>-1078303</v>
       </c>
       <c r="F45" t="n">
-        <v>595769</v>
+        <v>-5613622</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>亞力</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 376 千股)</t>
+          <t>📉 20d 巨變(減碼 -826 千股)</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1534783</v>
+        <v>-1254743</v>
       </c>
       <c r="D46" t="n">
-        <v>3408935</v>
+        <v>-290424</v>
       </c>
       <c r="E46" t="n">
-        <v>994079</v>
+        <v>-1264743</v>
       </c>
       <c r="F46" t="n">
-        <v>3032890</v>
+        <v>535803</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>大綜</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 286 千股)</t>
+          <t>📈 20d 巨變(加碼 489 千股)</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>254005</v>
+        <v>1737891</v>
       </c>
       <c r="D47" t="n">
-        <v>-524714</v>
+        <v>3897798</v>
       </c>
       <c r="E47" t="n">
-        <v>728627</v>
+        <v>1534783</v>
       </c>
       <c r="F47" t="n">
-        <v>-810566</v>
+        <v>3408935</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>漢科</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,654 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -1,977 千股)</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-7498863</v>
+        <v>-3507738</v>
       </c>
       <c r="D48" t="n">
-        <v>-9450397</v>
+        <v>-2501552</v>
       </c>
       <c r="E48" t="n">
-        <v>-4693114</v>
+        <v>254005</v>
       </c>
       <c r="F48" t="n">
-        <v>-7796106</v>
+        <v>-524714</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>台燿</t>
         </is>
       </c>
     </row>
@@ -7111,20 +7111,20 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -2,623 千股)</t>
+          <t>📈 20d 巨變(加碼 3,411 千股)</t>
         </is>
       </c>
       <c r="C49" t="n">
+        <v>-3278813</v>
+      </c>
+      <c r="D49" t="n">
+        <v>-6245257</v>
+      </c>
+      <c r="E49" t="n">
         <v>-3091857</v>
       </c>
-      <c r="D49" t="n">
+      <c r="F49" t="n">
         <v>-9656179</v>
-      </c>
-      <c r="E49" t="n">
-        <v>-3416100</v>
-      </c>
-      <c r="F49" t="n">
-        <v>-7033507</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -7135,145 +7135,145 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 480 千股)</t>
+          <t>📉 20d 巨變(減碼 -799 千股)</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-17179</v>
+        <v>-8431966</v>
       </c>
       <c r="D50" t="n">
-        <v>-2902713</v>
+        <v>-10249194</v>
       </c>
       <c r="E50" t="n">
-        <v>51493</v>
+        <v>-7498863</v>
       </c>
       <c r="F50" t="n">
-        <v>-3383069</v>
+        <v>-9450397</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>立隆電</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -495 千股)</t>
+          <t>📉 20d 巨變(減碼 -467 千股)</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-522402</v>
+        <v>-1114078</v>
       </c>
       <c r="D51" t="n">
-        <v>-2608856</v>
+        <v>-3369885</v>
       </c>
       <c r="E51" t="n">
-        <v>-124305</v>
+        <v>-17179</v>
       </c>
       <c r="F51" t="n">
-        <v>-2114187</v>
+        <v>-2902713</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>玉晶光</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,636 千股)</t>
+          <t>📉 20d 巨變(減碼 -427 千股)</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>8223413</v>
+        <v>-1159279</v>
       </c>
       <c r="D52" t="n">
-        <v>-50737807</v>
+        <v>-3035464</v>
       </c>
       <c r="E52" t="n">
-        <v>1187789</v>
+        <v>-522402</v>
       </c>
       <c r="F52" t="n">
-        <v>-52374080</v>
+        <v>-2608856</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>世芯-KY</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 3,929 千股)</t>
+          <t>📈 20d 巨變(加碼 7,864 千股)</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-24206159</v>
+        <v>6331225</v>
       </c>
       <c r="D53" t="n">
-        <v>-22579037</v>
+        <v>-42873722</v>
       </c>
       <c r="E53" t="n">
-        <v>-17322902</v>
+        <v>8223413</v>
       </c>
       <c r="F53" t="n">
-        <v>-26507588</v>
+        <v>-50737807</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 996 千股)</t>
+          <t>📈 20d 巨變(加碼 2,748 千股)</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-1233776</v>
+        <v>-16887087</v>
       </c>
       <c r="D54" t="n">
-        <v>-6581855</v>
+        <v>-19831169</v>
       </c>
       <c r="E54" t="n">
-        <v>-1325216</v>
+        <v>-24206159</v>
       </c>
       <c r="F54" t="n">
-        <v>-7578161</v>
+        <v>-22579037</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
@@ -7285,20 +7285,20 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -17,487 千股)</t>
+          <t>📈 20d 巨變(加碼 754 千股)</t>
         </is>
       </c>
       <c r="C55" t="n">
+        <v>-13473886</v>
+      </c>
+      <c r="D55" t="n">
+        <v>42426973</v>
+      </c>
+      <c r="E55" t="n">
         <v>-10587111</v>
       </c>
-      <c r="D55" t="n">
+      <c r="F55" t="n">
         <v>41673068</v>
-      </c>
-      <c r="E55" t="n">
-        <v>14233120</v>
-      </c>
-      <c r="F55" t="n">
-        <v>59160199</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -7309,87 +7309,87 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -87 千股)</t>
+          <t>📈 20d 巨變(加碼 1,138 千股)</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-296423</v>
+        <v>-1723882</v>
       </c>
       <c r="D56" t="n">
-        <v>1753434</v>
+        <v>-5443410</v>
       </c>
       <c r="E56" t="n">
-        <v>-148563</v>
+        <v>-1233776</v>
       </c>
       <c r="F56" t="n">
-        <v>1840221</v>
+        <v>-6581855</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>鈊象</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -1,026 千股)</t>
+          <t>📈 20d 巨變(加碼 601 千股)</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>-534478</v>
+        <v>991321</v>
       </c>
       <c r="D57" t="n">
-        <v>-853873</v>
+        <v>-1942598</v>
       </c>
       <c r="E57" t="n">
-        <v>384803</v>
+        <v>18289</v>
       </c>
       <c r="F57" t="n">
-        <v>171932</v>
+        <v>-2544067</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>士電</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -635 千股)</t>
+          <t>📉 20d 巨變(減碼 -354 千股)</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>18289</v>
+        <v>-255036</v>
       </c>
       <c r="D58" t="n">
-        <v>-2544067</v>
+        <v>1399524</v>
       </c>
       <c r="E58" t="n">
-        <v>388495</v>
+        <v>-296423</v>
       </c>
       <c r="F58" t="n">
-        <v>-1908898</v>
+        <v>1753434</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>達欣工</t>
         </is>
       </c>
     </row>
@@ -7401,20 +7401,20 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 488 千股)</t>
+          <t>📈 20d 巨變(加碼 110 千股)</t>
         </is>
       </c>
       <c r="C59" t="n">
+        <v>207395</v>
+      </c>
+      <c r="D59" t="n">
+        <v>-563324</v>
+      </c>
+      <c r="E59" t="n">
         <v>262382</v>
       </c>
-      <c r="D59" t="n">
+      <c r="F59" t="n">
         <v>-673517</v>
-      </c>
-      <c r="E59" t="n">
-        <v>-845</v>
-      </c>
-      <c r="F59" t="n">
-        <v>-1161744</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -7425,319 +7425,319 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 71 千股)</t>
+          <t>📉 20d 巨變(減碼 -750 千股)</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>358170</v>
+        <v>-290945</v>
       </c>
       <c r="D60" t="n">
-        <v>847896</v>
+        <v>-1603932</v>
       </c>
       <c r="E60" t="n">
-        <v>272953</v>
+        <v>-534478</v>
       </c>
       <c r="F60" t="n">
-        <v>776562</v>
+        <v>-853873</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>鉅祥</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 104 千股)</t>
+          <t>📈 20d 巨變(加碼 38 千股)</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>125609</v>
+        <v>418153</v>
       </c>
       <c r="D61" t="n">
-        <v>470834</v>
+        <v>886170</v>
       </c>
       <c r="E61" t="n">
-        <v>-39925</v>
+        <v>358170</v>
       </c>
       <c r="F61" t="n">
-        <v>367295</v>
+        <v>847896</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -1,532 千股)</t>
+          <t>📈 20d 巨變(加碼 608 千股)</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-214109</v>
+        <v>944822</v>
       </c>
       <c r="D62" t="n">
-        <v>1777038</v>
+        <v>1250837</v>
       </c>
       <c r="E62" t="n">
-        <v>1893080</v>
+        <v>491039</v>
       </c>
       <c r="F62" t="n">
-        <v>3309115</v>
+        <v>643200</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>勝一</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 513 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -163 千股)</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>491039</v>
+        <v>-94562</v>
       </c>
       <c r="D63" t="n">
-        <v>643200</v>
+        <v>377133</v>
       </c>
       <c r="E63" t="n">
-        <v>-124160</v>
+        <v>225430</v>
       </c>
       <c r="F63" t="n">
-        <v>129819</v>
+        <v>540080</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>勝一</t>
+          <t>信立</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -16 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -207 千股)</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>225430</v>
+        <v>-517856</v>
       </c>
       <c r="D64" t="n">
-        <v>540080</v>
+        <v>264288</v>
       </c>
       <c r="E64" t="n">
-        <v>9050</v>
+        <v>125609</v>
       </c>
       <c r="F64" t="n">
-        <v>555900</v>
+        <v>470834</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>祥碩</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,740 千股)</t>
+          <t>📉 20d 巨變(減碼 -597 千股)</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-1151046</v>
+        <v>-1189932</v>
       </c>
       <c r="D65" t="n">
-        <v>-3201906</v>
+        <v>1179910</v>
       </c>
       <c r="E65" t="n">
-        <v>-1237054</v>
+        <v>-214109</v>
       </c>
       <c r="F65" t="n">
-        <v>-4941647</v>
+        <v>1777038</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>華星光</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,965 千股)</t>
+          <t>📈 20d 巨變(加碼 484 千股)</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-541455</v>
+        <v>-432425</v>
       </c>
       <c r="D66" t="n">
-        <v>-2842475</v>
+        <v>-2717631</v>
       </c>
       <c r="E66" t="n">
-        <v>-804332</v>
+        <v>-1151046</v>
       </c>
       <c r="F66" t="n">
-        <v>-4807799</v>
+        <v>-3201906</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>聯鈞</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 22,641 千股)</t>
+          <t>📉 20d 巨變(減碼 -175 千股)</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1126790</v>
+        <v>522223</v>
       </c>
       <c r="D67" t="n">
-        <v>-67101183</v>
+        <v>3827747</v>
       </c>
       <c r="E67" t="n">
-        <v>-1319042</v>
+        <v>1217149</v>
       </c>
       <c r="F67" t="n">
-        <v>-89742469</v>
+        <v>4002810</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>聯亞</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 541 千股)</t>
+          <t>📉 20d 巨變(減碼 -434 千股)</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-7835515</v>
+        <v>-462082</v>
       </c>
       <c r="D68" t="n">
-        <v>-18407589</v>
+        <v>-3276831</v>
       </c>
       <c r="E68" t="n">
-        <v>-6914795</v>
+        <v>-541455</v>
       </c>
       <c r="F68" t="n">
-        <v>-18948592</v>
+        <v>-2842475</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>宇瞻</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -10,344 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 11,125 千股)</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-35494025</v>
+        <v>-3317835</v>
       </c>
       <c r="D69" t="n">
-        <v>-213240835</v>
+        <v>-55975763</v>
       </c>
       <c r="E69" t="n">
-        <v>-51598125</v>
+        <v>1126790</v>
       </c>
       <c r="F69" t="n">
-        <v>-202897294</v>
+        <v>-67101183</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 557 千股)</t>
+          <t>📉 20d 巨變(減碼 -11,788 千股)</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1217149</v>
+        <v>-42300050</v>
       </c>
       <c r="D70" t="n">
-        <v>4002810</v>
+        <v>-225029096</v>
       </c>
       <c r="E70" t="n">
-        <v>1270512</v>
+        <v>-35494025</v>
       </c>
       <c r="F70" t="n">
-        <v>3445681</v>
+        <v>-213240835</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
@@ -7749,20 +7749,20 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,137 千股)</t>
+          <t>📈 20d 巨變(加碼 7,869 千股)</t>
         </is>
       </c>
       <c r="C71" t="n">
+        <v>23100821</v>
+      </c>
+      <c r="D71" t="n">
+        <v>19706634</v>
+      </c>
+      <c r="E71" t="n">
         <v>17374694</v>
       </c>
-      <c r="D71" t="n">
+      <c r="F71" t="n">
         <v>11837401</v>
-      </c>
-      <c r="E71" t="n">
-        <v>6851192</v>
-      </c>
-      <c r="F71" t="n">
-        <v>10700718</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -7773,232 +7773,232 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -123 千股)</t>
+          <t>📈 20d 巨變(加碼 2,021 千股)</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>17317</v>
+        <v>-8175248</v>
       </c>
       <c r="D72" t="n">
-        <v>973464</v>
+        <v>-16386412</v>
       </c>
       <c r="E72" t="n">
-        <v>56348</v>
+        <v>-7835515</v>
       </c>
       <c r="F72" t="n">
-        <v>1096495</v>
+        <v>-18407589</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>德昌</t>
+          <t>瑞昱</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 444 千股)</t>
+          <t>📉 20d 巨變(減碼 -84 千股)</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>141612</v>
+        <v>76083</v>
       </c>
       <c r="D73" t="n">
-        <v>-266294</v>
+        <v>889464</v>
       </c>
       <c r="E73" t="n">
-        <v>66659</v>
+        <v>17317</v>
       </c>
       <c r="F73" t="n">
-        <v>-710737</v>
+        <v>973464</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>億泰</t>
+          <t>德昌</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 154 千股)</t>
+          <t>📈 20d 巨變(加碼 2,251 千股)</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>204195</v>
+        <v>-7327434</v>
       </c>
       <c r="D74" t="n">
-        <v>-276684</v>
+        <v>-13862410</v>
       </c>
       <c r="E74" t="n">
-        <v>153195</v>
+        <v>-9774310</v>
       </c>
       <c r="F74" t="n">
-        <v>-430684</v>
+        <v>-16113473</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>台汽電</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -589 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -109 千股)</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>-163140</v>
+        <v>-141207</v>
       </c>
       <c r="D75" t="n">
-        <v>3275973</v>
+        <v>-375113</v>
       </c>
       <c r="E75" t="n">
-        <v>-1949477</v>
+        <v>141612</v>
       </c>
       <c r="F75" t="n">
-        <v>3864876</v>
+        <v>-266294</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>億泰</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,280 千股)</t>
+          <t>📉 20d 巨變(減碼 -103 千股)</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-9774310</v>
+        <v>180144</v>
       </c>
       <c r="D76" t="n">
-        <v>-16113473</v>
+        <v>-379674</v>
       </c>
       <c r="E76" t="n">
-        <v>-12828305</v>
+        <v>204195</v>
       </c>
       <c r="F76" t="n">
-        <v>-17393261</v>
+        <v>-276684</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>友輝</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 155 千股)</t>
+          <t>📈 20d 巨變(加碼 158 千股)</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>4841723</v>
+        <v>-244260</v>
       </c>
       <c r="D77" t="n">
-        <v>6567084</v>
+        <v>3434342</v>
       </c>
       <c r="E77" t="n">
-        <v>3782190</v>
+        <v>-163140</v>
       </c>
       <c r="F77" t="n">
-        <v>6411835</v>
+        <v>3275973</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>智易</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -10,709 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,034 千股)</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-15093238</v>
+        <v>-1389207</v>
       </c>
       <c r="D78" t="n">
-        <v>-23657473</v>
+        <v>-9702782</v>
       </c>
       <c r="E78" t="n">
-        <v>-19001106</v>
+        <v>-886416</v>
       </c>
       <c r="F78" t="n">
-        <v>-12948152</v>
+        <v>-8668666</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>啟碁</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -895 千股)</t>
+          <t>📈 20d 巨變(加碼 39 千股)</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-886416</v>
+        <v>3712099</v>
       </c>
       <c r="D79" t="n">
-        <v>-8668666</v>
+        <v>6606140</v>
       </c>
       <c r="E79" t="n">
-        <v>330900</v>
+        <v>4841723</v>
       </c>
       <c r="F79" t="n">
-        <v>-7773557</v>
+        <v>6567084</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>原相</t>
         </is>
       </c>
     </row>
@@ -8010,20 +8010,20 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 94 千股)</t>
+          <t>📉 20d 巨變(減碼 -53 千股)</t>
         </is>
       </c>
       <c r="C80" t="n">
+        <v>162258</v>
+      </c>
+      <c r="D80" t="n">
+        <v>113405</v>
+      </c>
+      <c r="E80" t="n">
         <v>309714</v>
       </c>
-      <c r="D80" t="n">
+      <c r="F80" t="n">
         <v>166535</v>
-      </c>
-      <c r="E80" t="n">
-        <v>239004</v>
-      </c>
-      <c r="F80" t="n">
-        <v>72756</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -8034,174 +8034,174 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -567 千股)</t>
+          <t>📉 20d 巨變(減碼 -3,484 千股)</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>177128</v>
+        <v>-20164935</v>
       </c>
       <c r="D81" t="n">
-        <v>-4446644</v>
+        <v>-27141151</v>
       </c>
       <c r="E81" t="n">
-        <v>-706287</v>
+        <v>-15093238</v>
       </c>
       <c r="F81" t="n">
-        <v>-3879336</v>
+        <v>-23657473</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 3,905 千股)</t>
+          <t>📉 20d 巨變(減碼 -142 千股)</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-68160196</v>
+        <v>70693</v>
       </c>
       <c r="D82" t="n">
-        <v>-214912448</v>
+        <v>-4588539</v>
       </c>
       <c r="E82" t="n">
-        <v>-99074232</v>
+        <v>177128</v>
       </c>
       <c r="F82" t="n">
-        <v>-218817336</v>
+        <v>-4446644</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 307 千股)</t>
+          <t>📉 20d 巨變(減碼 -3,287 千股)</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>132023</v>
+        <v>-56285501</v>
       </c>
       <c r="D83" t="n">
-        <v>309852</v>
+        <v>-218199656</v>
       </c>
       <c r="E83" t="n">
-        <v>10373</v>
+        <v>-68160196</v>
       </c>
       <c r="F83" t="n">
-        <v>3102</v>
+        <v>-214912448</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 243 千股)</t>
+          <t>📈 20d 巨變(加碼 50 千股)</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>204469</v>
+        <v>143023</v>
       </c>
       <c r="D84" t="n">
-        <v>-1169623</v>
+        <v>359552</v>
       </c>
       <c r="E84" t="n">
-        <v>210469</v>
+        <v>132023</v>
       </c>
       <c r="F84" t="n">
-        <v>-1412623</v>
+        <v>309852</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>鑫龍騰</t>
+          <t>東科-KY</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -525 千股)</t>
+          <t>📈 20d 巨變(加碼 18 千股)</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>452250</v>
+        <v>44534</v>
       </c>
       <c r="D85" t="n">
-        <v>2466334</v>
+        <v>-1151558</v>
       </c>
       <c r="E85" t="n">
-        <v>889250</v>
+        <v>204469</v>
       </c>
       <c r="F85" t="n">
-        <v>2991504</v>
+        <v>-1169623</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>鑫龍騰</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,348 千股)</t>
+          <t>📉 20d 巨變(減碼 -438 千股)</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>3361930</v>
+        <v>332250</v>
       </c>
       <c r="D86" t="n">
-        <v>3825864</v>
+        <v>2028334</v>
       </c>
       <c r="E86" t="n">
-        <v>2361825</v>
+        <v>452250</v>
       </c>
       <c r="F86" t="n">
-        <v>2477701</v>
+        <v>2466334</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>全友</t>
         </is>
       </c>
     </row>
@@ -8213,20 +8213,20 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -162 千股)</t>
+          <t>📉 20d 巨變(減碼 -172 千股)</t>
         </is>
       </c>
       <c r="C87" t="n">
+        <v>-1923173</v>
+      </c>
+      <c r="D87" t="n">
+        <v>-3638845</v>
+      </c>
+      <c r="E87" t="n">
         <v>-1951513</v>
       </c>
-      <c r="D87" t="n">
+      <c r="F87" t="n">
         <v>-3466975</v>
-      </c>
-      <c r="E87" t="n">
-        <v>-3341098</v>
-      </c>
-      <c r="F87" t="n">
-        <v>-3305190</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -8237,319 +8237,319 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -4,943 千股)</t>
+          <t>📉 20d 巨變(減碼 -162 千股)</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>-48312465</v>
+        <v>2480460</v>
       </c>
       <c r="D88" t="n">
-        <v>-59920994</v>
+        <v>3664056</v>
       </c>
       <c r="E88" t="n">
-        <v>-46281468</v>
+        <v>3361930</v>
       </c>
       <c r="F88" t="n">
-        <v>-54977869</v>
+        <v>3825864</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>研華</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 463 千股)</t>
+          <t>📈 20d 巨變(加碼 1,672 千股)</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-372271</v>
+        <v>-44288983</v>
       </c>
       <c r="D89" t="n">
-        <v>-5205700</v>
+        <v>-58248860</v>
       </c>
       <c r="E89" t="n">
-        <v>-1382384</v>
+        <v>-48312465</v>
       </c>
       <c r="F89" t="n">
-        <v>-5668599</v>
+        <v>-59920994</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -86 千股)</t>
+          <t>📉 20d 巨變(減碼 -265 千股)</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>-54170</v>
+        <v>-301833</v>
       </c>
       <c r="D90" t="n">
-        <v>-56939</v>
+        <v>-5470960</v>
       </c>
       <c r="E90" t="n">
-        <v>63395</v>
+        <v>-372271</v>
       </c>
       <c r="F90" t="n">
-        <v>29421</v>
+        <v>-5205700</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>中保科</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -29 千股)</t>
+          <t>📉 20d 巨變(減碼 -19 千股)</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>-93768</v>
+        <v>-120426</v>
       </c>
       <c r="D91" t="n">
-        <v>-419308</v>
+        <v>-75943</v>
       </c>
       <c r="E91" t="n">
-        <v>-88334</v>
+        <v>-54170</v>
       </c>
       <c r="F91" t="n">
-        <v>-390520</v>
+        <v>-56939</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>竹陞科技</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 23 千股)</t>
+          <t>📉 20d 巨變(減碼 -694 千股)</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>29000</v>
+        <v>4302017</v>
       </c>
       <c r="D92" t="n">
-        <v>119655</v>
+        <v>7283227</v>
       </c>
       <c r="E92" t="n">
-        <v>6800</v>
+        <v>4711281</v>
       </c>
       <c r="F92" t="n">
-        <v>96605</v>
+        <v>7977016</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>長榮航太</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -3,575 千股)</t>
+          <t>📉 20d 巨變(減碼 -8 千股)</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>-39125116</v>
+        <v>-59848</v>
       </c>
       <c r="D93" t="n">
-        <v>-133414697</v>
+        <v>-427316</v>
       </c>
       <c r="E93" t="n">
-        <v>-38176568</v>
+        <v>-93768</v>
       </c>
       <c r="F93" t="n">
-        <v>-129839374</v>
+        <v>-419308</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>安碁資訊</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 23,405 千股)</t>
+          <t>📈 20d 巨變(加碼 16 千股)</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-34134732</v>
+        <v>43000</v>
       </c>
       <c r="D94" t="n">
-        <v>-175849216</v>
+        <v>135636</v>
       </c>
       <c r="E94" t="n">
-        <v>-42264080</v>
+        <v>29000</v>
       </c>
       <c r="F94" t="n">
-        <v>-199253908</v>
+        <v>119655</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>六方科-KY</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -3,781 千股)</t>
+          <t>📉 20d 巨變(減碼 -9,549 千股)</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>-2045510</v>
+        <v>-39329925</v>
       </c>
       <c r="D95" t="n">
-        <v>-7791846</v>
+        <v>-142963374</v>
       </c>
       <c r="E95" t="n">
-        <v>-3918232</v>
+        <v>-39125116</v>
       </c>
       <c r="F95" t="n">
-        <v>-4010798</v>
+        <v>-133414697</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 49 千股)</t>
+          <t>📉 20d 巨變(減碼 -56,073 千股)</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>-1635788</v>
+        <v>-39178294</v>
       </c>
       <c r="D96" t="n">
-        <v>-4588416</v>
+        <v>-231922106</v>
       </c>
       <c r="E96" t="n">
-        <v>-1598545</v>
+        <v>-34134732</v>
       </c>
       <c r="F96" t="n">
-        <v>-4637437</v>
+        <v>-175849216</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -33 千股)</t>
+          <t>📈 20d 巨變(加碼 3,508 千股)</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>169006</v>
+        <v>-2161646</v>
       </c>
       <c r="D97" t="n">
-        <v>237120</v>
+        <v>-4284304</v>
       </c>
       <c r="E97" t="n">
-        <v>85783</v>
+        <v>-2045510</v>
       </c>
       <c r="F97" t="n">
-        <v>270401</v>
+        <v>-7791846</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>聯發科</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 74 千股)</t>
+          <t>📈 20d 巨變(加碼 136 千股)</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1050787</v>
+        <v>-1969103</v>
       </c>
       <c r="D98" t="n">
-        <v>1755468</v>
+        <v>-4452044</v>
       </c>
       <c r="E98" t="n">
-        <v>3415495</v>
+        <v>-1635788</v>
       </c>
       <c r="F98" t="n">
-        <v>1681307</v>
+        <v>-4588416</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>緯穎</t>
         </is>
       </c>
     </row>
@@ -8561,20 +8561,20 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -581 千股)</t>
+          <t>📈 20d 巨變(加碼 78 千股)</t>
         </is>
       </c>
       <c r="C99" t="n">
+        <v>-66651</v>
+      </c>
+      <c r="D99" t="n">
+        <v>-5122664</v>
+      </c>
+      <c r="E99" t="n">
         <v>-151640</v>
       </c>
-      <c r="D99" t="n">
+      <c r="F99" t="n">
         <v>-5200332</v>
-      </c>
-      <c r="E99" t="n">
-        <v>129100</v>
-      </c>
-      <c r="F99" t="n">
-        <v>-4619395</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -8585,56 +8585,114 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 603 千股)</t>
+          <t>📈 20d 巨變(加碼 69 千股)</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>-19819</v>
+        <v>120833</v>
       </c>
       <c r="D100" t="n">
-        <v>1877650</v>
+        <v>306346</v>
       </c>
       <c r="E100" t="n">
-        <v>-360963</v>
+        <v>169006</v>
       </c>
       <c r="F100" t="n">
-        <v>1274192</v>
+        <v>237120</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>信驊</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -1,334 千股)</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>-1571108</v>
+      </c>
+      <c r="D101" t="n">
+        <v>421817</v>
+      </c>
+      <c r="E101" t="n">
+        <v>1050787</v>
+      </c>
+      <c r="F101" t="n">
+        <v>1755468</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>5439</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 47 千股)</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>-232</v>
+      </c>
+      <c r="D102" t="n">
+        <v>1924496</v>
+      </c>
+      <c r="E102" t="n">
+        <v>-19819</v>
+      </c>
+      <c r="F102" t="n">
+        <v>1877650</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>高技</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
           <t>6187</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 718 千股)</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 151 千股)</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>796165</v>
+      </c>
+      <c r="D103" t="n">
+        <v>-1691030</v>
+      </c>
+      <c r="E103" t="n">
         <v>202678</v>
       </c>
-      <c r="D101" t="n">
+      <c r="F103" t="n">
         <v>-1842254</v>
       </c>
-      <c r="E101" t="n">
-        <v>-294585</v>
-      </c>
-      <c r="F101" t="n">
-        <v>-2560418</v>
-      </c>
-      <c r="G101" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t>萬潤</t>
         </is>

--- a/data/台股_外資雷達.xlsx
+++ b/data/台股_外資雷達.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M104"/>
+  <dimension ref="A1:M105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,22 +496,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-48938</v>
+        <v>-23887</v>
       </c>
       <c r="D2" t="n">
-        <v>197174</v>
+        <v>207001</v>
       </c>
       <c r="E2" t="n">
-        <v>-147405</v>
+        <v>-94930</v>
       </c>
       <c r="F2" t="n">
-        <v>56342</v>
+        <v>35548</v>
       </c>
       <c r="G2" t="n">
-        <v>12667</v>
+        <v>26419</v>
       </c>
       <c r="H2" t="n">
-        <v>13467</v>
+        <v>12142</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -547,22 +547,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-13474</v>
+        <v>-22577</v>
       </c>
       <c r="D3" t="n">
-        <v>42427</v>
+        <v>44852</v>
       </c>
       <c r="E3" t="n">
-        <v>-2311</v>
+        <v>-3505</v>
       </c>
       <c r="F3" t="n">
-        <v>3886</v>
+        <v>5874</v>
       </c>
       <c r="G3" t="n">
-        <v>-51634</v>
+        <v>-50272</v>
       </c>
       <c r="H3" t="n">
-        <v>4024</v>
+        <v>3274</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>23101</v>
+        <v>13987</v>
       </c>
       <c r="D4" t="n">
-        <v>19707</v>
+        <v>19225</v>
       </c>
       <c r="E4" t="n">
-        <v>140106</v>
+        <v>142492</v>
       </c>
       <c r="F4" t="n">
-        <v>-5550</v>
+        <v>-4345</v>
       </c>
       <c r="G4" t="n">
-        <v>-32737</v>
+        <v>-33437</v>
       </c>
       <c r="H4" t="n">
-        <v>1883</v>
+        <v>1615</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -649,26 +649,26 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4516</v>
+        <v>2659</v>
       </c>
       <c r="D5" t="n">
-        <v>10559</v>
+        <v>8409</v>
       </c>
       <c r="E5" t="n">
-        <v>14675</v>
+        <v>12049</v>
       </c>
       <c r="F5" t="n">
-        <v>-7826</v>
+        <v>-7375</v>
       </c>
       <c r="G5" t="n">
-        <v>-10099</v>
+        <v>-9552</v>
       </c>
       <c r="H5" t="n">
-        <v>431</v>
+        <v>470</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>🚀 大買</t>
+          <t>🟢 加碼</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -700,22 +700,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4302</v>
+        <v>3987</v>
       </c>
       <c r="D6" t="n">
-        <v>7283</v>
+        <v>7759</v>
       </c>
       <c r="E6" t="n">
-        <v>10741</v>
+        <v>12063</v>
       </c>
       <c r="F6" t="n">
-        <v>-51</v>
+        <v>-46</v>
       </c>
       <c r="G6" t="n">
-        <v>-567</v>
+        <v>-560</v>
       </c>
       <c r="H6" t="n">
-        <v>738</v>
+        <v>389</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -751,22 +751,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3712</v>
+        <v>1272</v>
       </c>
       <c r="D7" t="n">
-        <v>6606</v>
+        <v>6962</v>
       </c>
       <c r="E7" t="n">
-        <v>10931</v>
+        <v>9456</v>
       </c>
       <c r="F7" t="n">
-        <v>3477</v>
+        <v>3392</v>
       </c>
       <c r="G7" t="n">
-        <v>4184</v>
+        <v>4721</v>
       </c>
       <c r="H7" t="n">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -802,22 +802,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-149</v>
+        <v>-183</v>
       </c>
       <c r="D8" t="n">
-        <v>5689</v>
+        <v>5164</v>
       </c>
       <c r="E8" t="n">
-        <v>9432</v>
+        <v>9218</v>
       </c>
       <c r="F8" t="n">
-        <v>-253</v>
+        <v>-827</v>
       </c>
       <c r="G8" t="n">
-        <v>-5249</v>
+        <v>-5225</v>
       </c>
       <c r="H8" t="n">
-        <v>290</v>
+        <v>254</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -844,31 +844,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1738</v>
+        <v>-434</v>
       </c>
       <c r="D9" t="n">
-        <v>3898</v>
+        <v>4820</v>
       </c>
       <c r="E9" t="n">
-        <v>3276</v>
+        <v>16228</v>
       </c>
       <c r="F9" t="n">
-        <v>91</v>
+        <v>401</v>
       </c>
       <c r="G9" t="n">
-        <v>135</v>
+        <v>1141</v>
       </c>
       <c r="H9" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -881,45 +881,45 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器*</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>漢科</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>522</v>
+        <v>1406</v>
       </c>
       <c r="D10" t="n">
-        <v>3828</v>
+        <v>3763</v>
       </c>
       <c r="E10" t="n">
-        <v>1770</v>
+        <v>2998</v>
       </c>
       <c r="F10" t="n">
-        <v>-1363</v>
+        <v>50</v>
       </c>
       <c r="G10" t="n">
-        <v>-3647</v>
+        <v>135</v>
       </c>
       <c r="H10" t="n">
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -940,37 +940,37 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2480</v>
+        <v>477</v>
       </c>
       <c r="D11" t="n">
-        <v>3664</v>
+        <v>3683</v>
       </c>
       <c r="E11" t="n">
-        <v>18001</v>
+        <v>2103</v>
       </c>
       <c r="F11" t="n">
-        <v>81</v>
+        <v>-1039</v>
       </c>
       <c r="G11" t="n">
-        <v>244</v>
+        <v>-3388</v>
       </c>
       <c r="H11" t="n">
-        <v>35</v>
+        <v>123</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -979,19 +979,19 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1006,22 +1006,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-244</v>
+        <v>-768</v>
       </c>
       <c r="D12" t="n">
-        <v>3434</v>
+        <v>3509</v>
       </c>
       <c r="E12" t="n">
-        <v>5017</v>
+        <v>5594</v>
       </c>
       <c r="F12" t="n">
-        <v>1315</v>
+        <v>887</v>
       </c>
       <c r="G12" t="n">
-        <v>5537</v>
+        <v>5541</v>
       </c>
       <c r="H12" t="n">
-        <v>-41</v>
+        <v>-53</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1048,31 +1048,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2059</v>
+        <v>1665</v>
       </c>
       <c r="D13" t="n">
-        <v>2796</v>
+        <v>3404</v>
       </c>
       <c r="E13" t="n">
-        <v>1850</v>
+        <v>17478</v>
       </c>
       <c r="F13" t="n">
-        <v>-152</v>
+        <v>143</v>
       </c>
       <c r="G13" t="n">
-        <v>-146</v>
+        <v>303</v>
       </c>
       <c r="H13" t="n">
-        <v>-744</v>
+        <v>36</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1081,49 +1081,49 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>97</v>
+        <v>61</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>零壹</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>366</v>
+        <v>2149</v>
       </c>
       <c r="D14" t="n">
-        <v>2135</v>
+        <v>2940</v>
       </c>
       <c r="E14" t="n">
-        <v>2994</v>
+        <v>2032</v>
       </c>
       <c r="F14" t="n">
-        <v>-936</v>
+        <v>-206</v>
       </c>
       <c r="G14" t="n">
-        <v>644</v>
+        <v>-143</v>
       </c>
       <c r="H14" t="n">
-        <v>85</v>
+        <v>-730</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1144,178 +1144,190 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>合機</t>
+          <t>全友</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>830</v>
+        <v>191</v>
       </c>
       <c r="D15" t="n">
-        <v>2067</v>
+        <v>1970</v>
       </c>
       <c r="E15" t="n">
-        <v>2803</v>
+        <v>8003</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="H15" t="n">
-        <v>186</v>
+        <v>-36</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>🟢 加碼</t>
+          <t>🟡 中性</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>332</v>
+        <v>271</v>
       </c>
       <c r="D16" t="n">
-        <v>2028</v>
+        <v>1925</v>
       </c>
       <c r="E16" t="n">
-        <v>8078</v>
+        <v>3072</v>
       </c>
       <c r="F16" t="n">
-        <v>-1</v>
+        <v>-927</v>
       </c>
       <c r="G16" t="n">
-        <v>-6</v>
+        <v>50</v>
       </c>
       <c r="H16" t="n">
-        <v>-14</v>
+        <v>-102</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>🟢 加碼</t>
+          <t>🟡 中性</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0</v>
+        <v>170</v>
       </c>
       <c r="D17" t="n">
-        <v>1924</v>
+        <v>1804</v>
       </c>
       <c r="E17" t="n">
-        <v>-3554</v>
+        <v>-1370</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>-414</v>
       </c>
       <c r="G17" t="n">
-        <v>-5746</v>
+        <v>-855</v>
       </c>
       <c r="H17" t="n">
-        <v>-77</v>
+        <v>-13</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>90</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>✈️ 高飛</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>合機</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>381</v>
+        <v>595</v>
       </c>
       <c r="D18" t="n">
-        <v>1517</v>
+        <v>1663</v>
       </c>
       <c r="E18" t="n">
-        <v>-2189</v>
+        <v>2951</v>
       </c>
       <c r="F18" t="n">
-        <v>-154</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>-43</v>
+        <v>152</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1328,147 +1340,123 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-255</v>
+        <v>-38</v>
       </c>
       <c r="D19" t="n">
-        <v>1400</v>
+        <v>1649</v>
       </c>
       <c r="E19" t="n">
-        <v>123</v>
+        <v>-2352</v>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>-5746</v>
       </c>
       <c r="H19" t="n">
-        <v>-219</v>
+        <v>-87</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>79</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>🛬 穩定</t>
-        </is>
-      </c>
-      <c r="M19" t="n">
-        <v>-1</v>
-      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>35</v>
+        <v>-862</v>
       </c>
       <c r="D20" t="n">
-        <v>1385</v>
+        <v>1305</v>
       </c>
       <c r="E20" t="n">
-        <v>-1455</v>
+        <v>6015</v>
       </c>
       <c r="F20" t="n">
-        <v>-415</v>
+        <v>373</v>
       </c>
       <c r="G20" t="n">
-        <v>-397</v>
+        <v>-4936</v>
       </c>
       <c r="H20" t="n">
-        <v>-74</v>
+        <v>-223</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>90</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>✈️ 高飛</t>
-        </is>
-      </c>
-      <c r="M20" t="n">
-        <v>2</v>
-      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-218</v>
+        <v>440</v>
       </c>
       <c r="D21" t="n">
-        <v>1304</v>
+        <v>1263</v>
       </c>
       <c r="E21" t="n">
-        <v>4752</v>
+        <v>-7180</v>
       </c>
       <c r="F21" t="n">
-        <v>294</v>
+        <v>2215</v>
       </c>
       <c r="G21" t="n">
-        <v>1378</v>
+        <v>8</v>
       </c>
       <c r="H21" t="n">
-        <v>-64</v>
+        <v>41</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1481,45 +1469,45 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>勝一</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>945</v>
+        <v>-444</v>
       </c>
       <c r="D22" t="n">
-        <v>1251</v>
+        <v>1206</v>
       </c>
       <c r="E22" t="n">
-        <v>4957</v>
+        <v>4165</v>
       </c>
       <c r="F22" t="n">
-        <v>4</v>
+        <v>209</v>
       </c>
       <c r="G22" t="n">
-        <v>6</v>
+        <v>1430</v>
       </c>
       <c r="H22" t="n">
-        <v>-19</v>
+        <v>-91</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1528,49 +1516,49 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-1190</v>
+        <v>-420</v>
       </c>
       <c r="D23" t="n">
-        <v>1180</v>
+        <v>1198</v>
       </c>
       <c r="E23" t="n">
-        <v>-5724</v>
+        <v>-2118</v>
       </c>
       <c r="F23" t="n">
-        <v>-1981</v>
+        <v>-168</v>
       </c>
       <c r="G23" t="n">
-        <v>-5739</v>
+        <v>162</v>
       </c>
       <c r="H23" t="n">
-        <v>-34</v>
+        <v>-47</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1579,49 +1567,49 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2624</v>
+        <v>687</v>
       </c>
       <c r="D24" t="n">
-        <v>1076</v>
+        <v>1144</v>
       </c>
       <c r="E24" t="n">
-        <v>-7616</v>
+        <v>1806</v>
       </c>
       <c r="F24" t="n">
-        <v>2393</v>
+        <v>-3</v>
       </c>
       <c r="G24" t="n">
-        <v>-41</v>
+        <v>351</v>
       </c>
       <c r="H24" t="n">
-        <v>118</v>
+        <v>5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1630,49 +1618,49 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>勝一</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-1479</v>
+        <v>730</v>
       </c>
       <c r="D25" t="n">
-        <v>1050</v>
+        <v>1078</v>
       </c>
       <c r="E25" t="n">
-        <v>-8055</v>
+        <v>1723</v>
       </c>
       <c r="F25" t="n">
-        <v>-177</v>
+        <v>4</v>
       </c>
       <c r="G25" t="n">
-        <v>-5527</v>
+        <v>6</v>
       </c>
       <c r="H25" t="n">
-        <v>-16</v>
+        <v>4</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1681,11 +1669,11 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1693,37 +1681,37 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>德昌</t>
+          <t>達欣工</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>76</v>
+        <v>-300</v>
       </c>
       <c r="D26" t="n">
-        <v>889</v>
+        <v>1024</v>
       </c>
       <c r="E26" t="n">
-        <v>701</v>
+        <v>-177</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>-19</v>
+        <v>-112</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1744,37 +1732,37 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>德昌</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>418</v>
+        <v>-69</v>
       </c>
       <c r="D27" t="n">
-        <v>886</v>
+        <v>778</v>
       </c>
       <c r="E27" t="n">
-        <v>1949</v>
+        <v>666</v>
       </c>
       <c r="F27" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>339</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>-19</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1787,7 +1775,7 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1795,37 +1783,37 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-512</v>
+        <v>-765</v>
       </c>
       <c r="D28" t="n">
-        <v>868</v>
+        <v>760</v>
       </c>
       <c r="E28" t="n">
-        <v>-1375</v>
+        <v>-6434</v>
       </c>
       <c r="F28" t="n">
-        <v>257</v>
+        <v>-2095</v>
       </c>
       <c r="G28" t="n">
-        <v>241</v>
+        <v>-5856</v>
       </c>
       <c r="H28" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1834,49 +1822,49 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>🐌 龜速*</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-541</v>
+        <v>-293</v>
       </c>
       <c r="D29" t="n">
-        <v>799</v>
+        <v>612</v>
       </c>
       <c r="E29" t="n">
-        <v>-4839</v>
+        <v>-1232</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>257</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="H29" t="n">
-        <v>-4</v>
+        <v>13</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1889,45 +1877,45 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速*</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>220</v>
+        <v>-1442</v>
       </c>
       <c r="D30" t="n">
-        <v>784</v>
+        <v>564</v>
       </c>
       <c r="E30" t="n">
-        <v>5143</v>
+        <v>4729</v>
       </c>
       <c r="F30" t="n">
-        <v>367</v>
+        <v>299</v>
       </c>
       <c r="G30" t="n">
-        <v>-286</v>
+        <v>-138</v>
       </c>
       <c r="H30" t="n">
-        <v>137</v>
+        <v>110</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1940,7 +1928,7 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -1954,31 +1942,31 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>寶雅</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-825</v>
+        <v>-4191</v>
       </c>
       <c r="D31" t="n">
-        <v>660</v>
+        <v>554</v>
       </c>
       <c r="E31" t="n">
-        <v>1851</v>
+        <v>-7188</v>
       </c>
       <c r="F31" t="n">
-        <v>-2</v>
+        <v>2668</v>
       </c>
       <c r="G31" t="n">
-        <v>136</v>
+        <v>4884</v>
       </c>
       <c r="H31" t="n">
-        <v>246</v>
+        <v>-1153</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1991,96 +1979,96 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-1207</v>
+        <v>2014</v>
       </c>
       <c r="D32" t="n">
-        <v>629</v>
+        <v>533</v>
       </c>
       <c r="E32" t="n">
-        <v>4265</v>
+        <v>761</v>
       </c>
       <c r="F32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H32" t="n">
+        <v>213</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>32</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>📉 減速</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
         <v>-3</v>
-      </c>
-      <c r="G32" t="n">
-        <v>66</v>
-      </c>
-      <c r="H32" t="n">
-        <v>176</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K32" t="n">
-        <v>90</v>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>🚀 加速器</t>
-        </is>
-      </c>
-      <c r="M32" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-742</v>
+        <v>-273</v>
       </c>
       <c r="D33" t="n">
-        <v>616</v>
+        <v>527</v>
       </c>
       <c r="E33" t="n">
-        <v>-555</v>
+        <v>-1595</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1342</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>2123</v>
       </c>
       <c r="H33" t="n">
-        <v>347</v>
+        <v>-5</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2089,49 +2077,49 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M33" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>智冠</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>21</v>
+        <v>-306</v>
       </c>
       <c r="D34" t="n">
-        <v>475</v>
+        <v>419</v>
       </c>
       <c r="E34" t="n">
-        <v>396</v>
+        <v>-7041</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>-177</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-3707</v>
       </c>
       <c r="H34" t="n">
-        <v>-164</v>
+        <v>-1</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2144,84 +2132,96 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M34" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-1571</v>
+        <v>65</v>
       </c>
       <c r="D35" t="n">
-        <v>422</v>
+        <v>380</v>
       </c>
       <c r="E35" t="n">
-        <v>4977</v>
+        <v>-254</v>
       </c>
       <c r="F35" t="n">
-        <v>962</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>-3875</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-127</v>
+        <v>2</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>78</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>📉 減速</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>-3</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>智冠</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>-5432</v>
+        <v>-55</v>
       </c>
       <c r="D36" t="n">
-        <v>386</v>
+        <v>373</v>
       </c>
       <c r="E36" t="n">
-        <v>-4661</v>
+        <v>397</v>
       </c>
       <c r="F36" t="n">
-        <v>2860</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>4504</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-896</v>
+        <v>-159</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2234,36 +2234,36 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M36" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>崇友</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-95</v>
+        <v>47</v>
       </c>
       <c r="D37" t="n">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="E37" t="n">
-        <v>-765</v>
+        <v>554</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -2281,15 +2281,15 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M37" t="n">
@@ -2299,31 +2299,31 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>寶雅</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>143</v>
+        <v>-610</v>
       </c>
       <c r="D38" t="n">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="E38" t="n">
-        <v>-348</v>
+        <v>1821</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>-80</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="H38" t="n">
-        <v>-0</v>
+        <v>211</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2332,49 +2332,49 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M38" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>44</v>
+        <v>-691</v>
       </c>
       <c r="D39" t="n">
-        <v>353</v>
+        <v>282</v>
       </c>
       <c r="E39" t="n">
-        <v>536</v>
+        <v>4864</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>566</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>-57</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2387,15 +2387,15 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M39" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
@@ -2410,22 +2410,22 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>121</v>
+        <v>22</v>
       </c>
       <c r="D40" t="n">
-        <v>306</v>
+        <v>260</v>
       </c>
       <c r="E40" t="n">
-        <v>753</v>
+        <v>734</v>
       </c>
       <c r="F40" t="n">
-        <v>-83</v>
+        <v>-110</v>
       </c>
       <c r="G40" t="n">
-        <v>-259</v>
+        <v>-264</v>
       </c>
       <c r="H40" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2449,22 +2449,22 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-308</v>
+        <v>-235</v>
       </c>
       <c r="D41" t="n">
-        <v>275</v>
+        <v>245</v>
       </c>
       <c r="E41" t="n">
-        <v>-975</v>
+        <v>-884</v>
       </c>
       <c r="F41" t="n">
-        <v>31</v>
+        <v>115</v>
       </c>
       <c r="G41" t="n">
-        <v>-10</v>
+        <v>-81</v>
       </c>
       <c r="H41" t="n">
-        <v>-113</v>
+        <v>-42</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2491,31 +2491,31 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>六方科-KY</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-518</v>
+        <v>62</v>
       </c>
       <c r="D42" t="n">
-        <v>264</v>
+        <v>162</v>
       </c>
       <c r="E42" t="n">
-        <v>-2219</v>
+        <v>6</v>
       </c>
       <c r="F42" t="n">
-        <v>1388</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>1856</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2524,49 +2524,49 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M42" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>43</v>
+        <v>-82</v>
       </c>
       <c r="D43" t="n">
-        <v>136</v>
+        <v>58</v>
       </c>
       <c r="E43" t="n">
-        <v>-5</v>
+        <v>-166</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>-359</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>-1289</v>
       </c>
       <c r="H43" t="n">
-        <v>5</v>
+        <v>-100</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2579,45 +2579,45 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M43" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>信立</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>162</v>
+        <v>-461</v>
       </c>
       <c r="D44" t="n">
-        <v>113</v>
+        <v>30</v>
       </c>
       <c r="E44" t="n">
-        <v>-182</v>
+        <v>-779</v>
       </c>
       <c r="F44" t="n">
-        <v>-545</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>-1122</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>-101</v>
+        <v>1</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2630,15 +2630,15 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M44" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="45">
@@ -2653,13 +2653,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>-6</v>
       </c>
       <c r="D45" t="n">
-        <v>-17</v>
+        <v>-14</v>
       </c>
       <c r="E45" t="n">
-        <v>-72</v>
+        <v>-70</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -2695,31 +2695,31 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-120</v>
+        <v>-380</v>
       </c>
       <c r="D46" t="n">
-        <v>-76</v>
+        <v>-30</v>
       </c>
       <c r="E46" t="n">
-        <v>-290</v>
+        <v>-4958</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>26</v>
+        <v>-19</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2728,40 +2728,40 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>大車隊</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>5</v>
+        <v>-1492</v>
       </c>
       <c r="D47" t="n">
-        <v>-161</v>
+        <v>-75</v>
       </c>
       <c r="E47" t="n">
-        <v>-284</v>
+        <v>-1148</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -2770,7 +2770,7 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-1</v>
+        <v>355</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2783,36 +2783,36 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M47" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>聯合</t>
+          <t>大車隊</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-92</v>
+        <v>-36</v>
       </c>
       <c r="D48" t="n">
-        <v>-234</v>
+        <v>-142</v>
       </c>
       <c r="E48" t="n">
-        <v>-3578</v>
+        <v>-268</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -2821,7 +2821,7 @@
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>91</v>
+        <v>-1</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2834,36 +2834,36 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-1255</v>
+        <v>-89</v>
       </c>
       <c r="D49" t="n">
-        <v>-290</v>
+        <v>-148</v>
       </c>
       <c r="E49" t="n">
-        <v>2140</v>
+        <v>-277</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -2872,7 +2872,7 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2889,41 +2889,41 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M49" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>聯合</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-3802</v>
+        <v>-84</v>
       </c>
       <c r="D50" t="n">
-        <v>-356</v>
+        <v>-183</v>
       </c>
       <c r="E50" t="n">
-        <v>-750</v>
+        <v>-3445</v>
       </c>
       <c r="F50" t="n">
-        <v>3954</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>3940</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-48</v>
+        <v>97</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2936,45 +2936,45 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M50" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>億泰</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-141</v>
+        <v>501</v>
       </c>
       <c r="D51" t="n">
-        <v>-375</v>
+        <v>-185</v>
       </c>
       <c r="E51" t="n">
-        <v>-2422</v>
+        <v>-709</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H51" t="n">
-        <v>198</v>
+        <v>-473</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -2983,49 +2983,49 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M51" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>180</v>
+        <v>1920</v>
       </c>
       <c r="D52" t="n">
-        <v>-380</v>
+        <v>-324</v>
       </c>
       <c r="E52" t="n">
-        <v>897</v>
+        <v>-7250</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G52" t="n">
-        <v>16</v>
+        <v>-10</v>
       </c>
       <c r="H52" t="n">
-        <v>-77</v>
+        <v>-198</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3038,45 +3038,45 @@
         </is>
       </c>
       <c r="K52" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M52" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-167</v>
+        <v>-431</v>
       </c>
       <c r="D53" t="n">
-        <v>-404</v>
+        <v>-363</v>
       </c>
       <c r="E53" t="n">
-        <v>55</v>
+        <v>2020</v>
       </c>
       <c r="F53" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>257</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-55</v>
+        <v>58</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3085,49 +3085,49 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K53" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M53" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-60</v>
+        <v>-317</v>
       </c>
       <c r="D54" t="n">
-        <v>-427</v>
+        <v>-435</v>
       </c>
       <c r="E54" t="n">
-        <v>-385</v>
+        <v>-70</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="H54" t="n">
-        <v>61</v>
+        <v>-45</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3136,11 +3136,11 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K54" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -3148,88 +3148,88 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>123</v>
+        <v>-21</v>
       </c>
       <c r="D55" t="n">
-        <v>-542</v>
+        <v>-438</v>
       </c>
       <c r="E55" t="n">
-        <v>-857</v>
+        <v>-261</v>
       </c>
       <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>34</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>77</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>✈️ 高飛*</t>
+        </is>
+      </c>
+      <c r="M55" t="n">
         <v>-1</v>
-      </c>
-      <c r="G55" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H55" t="n">
-        <v>22</v>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K55" t="n">
-        <v>86</v>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>📉 減速</t>
-        </is>
-      </c>
-      <c r="M55" t="n">
-        <v>-3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>友輝</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>207</v>
+        <v>64</v>
       </c>
       <c r="D56" t="n">
-        <v>-563</v>
+        <v>-446</v>
       </c>
       <c r="E56" t="n">
-        <v>-1753</v>
+        <v>971</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H56" t="n">
-        <v>12</v>
+        <v>-33</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -3250,37 +3250,37 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>億泰</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2049</v>
+        <v>-571</v>
       </c>
       <c r="D57" t="n">
-        <v>-776</v>
+        <v>-568</v>
       </c>
       <c r="E57" t="n">
-        <v>246</v>
+        <v>-2436</v>
       </c>
       <c r="F57" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>168</v>
+        <v>199</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3289,49 +3289,49 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K57" t="n">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M57" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>大統益</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>842</v>
+        <v>125</v>
       </c>
       <c r="D58" t="n">
-        <v>-829</v>
+        <v>-590</v>
       </c>
       <c r="E58" t="n">
-        <v>-360</v>
+        <v>-844</v>
       </c>
       <c r="F58" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="G58" t="n">
-        <v>18</v>
+        <v>-2</v>
       </c>
       <c r="H58" t="n">
-        <v>-257</v>
+        <v>32</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3344,36 +3344,36 @@
         </is>
       </c>
       <c r="K58" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M58" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>鑫龍騰</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>45</v>
+        <v>99</v>
       </c>
       <c r="D59" t="n">
-        <v>-1152</v>
+        <v>-626</v>
       </c>
       <c r="E59" t="n">
-        <v>-2878</v>
+        <v>-1748</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -3382,7 +3382,7 @@
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3395,45 +3395,45 @@
         </is>
       </c>
       <c r="K59" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>-11</v>
+        <v>132</v>
       </c>
       <c r="D60" t="n">
-        <v>-1159</v>
+        <v>-838</v>
       </c>
       <c r="E60" t="n">
-        <v>-293</v>
+        <v>-602</v>
       </c>
       <c r="F60" t="n">
-        <v>250</v>
+        <v>167</v>
       </c>
       <c r="G60" t="n">
-        <v>1425</v>
+        <v>-780</v>
       </c>
       <c r="H60" t="n">
-        <v>-42</v>
+        <v>-114</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         </is>
       </c>
       <c r="K60" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -3454,37 +3454,37 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>566</v>
+        <v>-1609</v>
       </c>
       <c r="D61" t="n">
-        <v>-1185</v>
+        <v>-1068</v>
       </c>
       <c r="E61" t="n">
-        <v>1336</v>
+        <v>-2181</v>
       </c>
       <c r="F61" t="n">
-        <v>24</v>
+        <v>740</v>
       </c>
       <c r="G61" t="n">
-        <v>869</v>
+        <v>5419</v>
       </c>
       <c r="H61" t="n">
-        <v>44</v>
+        <v>-1827</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3493,49 +3493,49 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K61" t="n">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-226</v>
+        <v>451</v>
       </c>
       <c r="D62" t="n">
-        <v>-1203</v>
+        <v>-1104</v>
       </c>
       <c r="E62" t="n">
-        <v>-870</v>
+        <v>800</v>
       </c>
       <c r="F62" t="n">
-        <v>-55</v>
+        <v>13</v>
       </c>
       <c r="G62" t="n">
-        <v>-968</v>
+        <v>837</v>
       </c>
       <c r="H62" t="n">
-        <v>-70</v>
+        <v>38</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3548,45 +3548,45 @@
         </is>
       </c>
       <c r="K62" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>鑫龍騰</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3561</v>
+        <v>-4</v>
       </c>
       <c r="D63" t="n">
-        <v>-1231</v>
+        <v>-1104</v>
       </c>
       <c r="E63" t="n">
-        <v>-5773</v>
+        <v>-2811</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-142</v>
+        <v>-0</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3599,45 +3599,45 @@
         </is>
       </c>
       <c r="K63" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M63" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>14</v>
+        <v>484</v>
       </c>
       <c r="D64" t="n">
-        <v>-1231</v>
+        <v>-1110</v>
       </c>
       <c r="E64" t="n">
-        <v>-3678</v>
+        <v>-6926</v>
       </c>
       <c r="F64" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>-97</v>
+        <v>78</v>
       </c>
       <c r="H64" t="n">
-        <v>-45</v>
+        <v>-595</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3646,49 +3646,49 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K64" t="n">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M64" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-291</v>
+        <v>105</v>
       </c>
       <c r="D65" t="n">
-        <v>-1604</v>
+        <v>-1158</v>
       </c>
       <c r="E65" t="n">
-        <v>-3720</v>
+        <v>-427</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>1425</v>
       </c>
       <c r="H65" t="n">
-        <v>1482</v>
+        <v>-9</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3697,88 +3697,100 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K65" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M65" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>796</v>
+        <v>4</v>
       </c>
       <c r="D66" t="n">
-        <v>-1691</v>
+        <v>-1176</v>
       </c>
       <c r="E66" t="n">
-        <v>-3191</v>
+        <v>-3938</v>
       </c>
       <c r="F66" t="n">
-        <v>-1340</v>
+        <v>5</v>
       </c>
       <c r="G66" t="n">
-        <v>-629</v>
+        <v>-117</v>
       </c>
       <c r="H66" t="n">
-        <v>57</v>
+        <v>-111</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>96</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>✈️ 高飛*</t>
+        </is>
+      </c>
+      <c r="M66" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-137</v>
+        <v>-3889</v>
       </c>
       <c r="D67" t="n">
-        <v>-1742</v>
+        <v>-1308</v>
       </c>
       <c r="E67" t="n">
-        <v>-7823</v>
+        <v>-1749</v>
       </c>
       <c r="F67" t="n">
-        <v>-519</v>
+        <v>3758</v>
       </c>
       <c r="G67" t="n">
-        <v>-1475</v>
+        <v>4693</v>
       </c>
       <c r="H67" t="n">
-        <v>-32</v>
+        <v>-42</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3791,45 +3803,45 @@
         </is>
       </c>
       <c r="K67" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M67" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>玉晶光</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>991</v>
+        <v>-721</v>
       </c>
       <c r="D68" t="n">
-        <v>-1943</v>
+        <v>-1842</v>
       </c>
       <c r="E68" t="n">
-        <v>-6464</v>
+        <v>2468</v>
       </c>
       <c r="F68" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="G68" t="n">
-        <v>79</v>
+        <v>-1363</v>
       </c>
       <c r="H68" t="n">
-        <v>-641</v>
+        <v>-433</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3842,96 +3854,84 @@
         </is>
       </c>
       <c r="K68" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M68" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-3508</v>
+        <v>399</v>
       </c>
       <c r="D69" t="n">
-        <v>-2502</v>
+        <v>-2015</v>
       </c>
       <c r="E69" t="n">
-        <v>-3765</v>
+        <v>-4289</v>
       </c>
       <c r="F69" t="n">
-        <v>1102</v>
+        <v>-941</v>
       </c>
       <c r="G69" t="n">
-        <v>5734</v>
+        <v>-751</v>
       </c>
       <c r="H69" t="n">
-        <v>-1709</v>
+        <v>53</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
           <t>🟠 減碼</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K69" t="n">
-        <v>77</v>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>🚀 加速器</t>
-        </is>
-      </c>
-      <c r="M69" t="n">
-        <v>3</v>
-      </c>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-432</v>
+        <v>-473</v>
       </c>
       <c r="D70" t="n">
-        <v>-2718</v>
+        <v>-2123</v>
       </c>
       <c r="E70" t="n">
-        <v>-1822</v>
+        <v>292</v>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>-777</v>
       </c>
       <c r="G70" t="n">
-        <v>1361</v>
+        <v>386</v>
       </c>
       <c r="H70" t="n">
-        <v>-622</v>
+        <v>277</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         </is>
       </c>
       <c r="K70" t="n">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -3952,37 +3952,37 @@
         </is>
       </c>
       <c r="M70" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-1842</v>
+        <v>-268</v>
       </c>
       <c r="D71" t="n">
-        <v>-2749</v>
+        <v>-2367</v>
       </c>
       <c r="E71" t="n">
-        <v>-97</v>
+        <v>-9052</v>
       </c>
       <c r="F71" t="n">
-        <v>-605</v>
+        <v>-962</v>
       </c>
       <c r="G71" t="n">
-        <v>666</v>
+        <v>-2138</v>
       </c>
       <c r="H71" t="n">
-        <v>492</v>
+        <v>-67</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -3991,49 +3991,49 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K71" t="n">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M71" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-1159</v>
+        <v>-2764</v>
       </c>
       <c r="D72" t="n">
-        <v>-3035</v>
+        <v>-2863</v>
       </c>
       <c r="E72" t="n">
-        <v>-56</v>
+        <v>-4323</v>
       </c>
       <c r="F72" t="n">
-        <v>104</v>
+        <v>-914</v>
       </c>
       <c r="G72" t="n">
-        <v>-216</v>
+        <v>-10749</v>
       </c>
       <c r="H72" t="n">
-        <v>175</v>
+        <v>-149</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -4042,49 +4042,49 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K72" t="n">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-462</v>
+        <v>-1239</v>
       </c>
       <c r="D73" t="n">
-        <v>-3277</v>
+        <v>-2896</v>
       </c>
       <c r="E73" t="n">
-        <v>-12646</v>
+        <v>-1215</v>
       </c>
       <c r="F73" t="n">
-        <v>314</v>
+        <v>102</v>
       </c>
       <c r="G73" t="n">
-        <v>302</v>
+        <v>-223</v>
       </c>
       <c r="H73" t="n">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -4093,49 +4093,49 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K73" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M73" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2150</v>
+        <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>-3296</v>
+        <v>-3112</v>
       </c>
       <c r="E74" t="n">
-        <v>-3231</v>
+        <v>-4336</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>1187</v>
       </c>
       <c r="H74" t="n">
-        <v>-379</v>
+        <v>-797</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -4144,49 +4144,49 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K74" t="n">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M74" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>湧德</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>-1114</v>
+        <v>1603</v>
       </c>
       <c r="D75" t="n">
-        <v>-3370</v>
+        <v>-3355</v>
       </c>
       <c r="E75" t="n">
-        <v>2942</v>
+        <v>-3127</v>
       </c>
       <c r="F75" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>-1259</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-73</v>
+        <v>-260</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -4195,11 +4195,11 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K75" t="n">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -4207,37 +4207,37 @@
         </is>
       </c>
       <c r="M75" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-1923</v>
+        <v>1425</v>
       </c>
       <c r="D76" t="n">
-        <v>-3639</v>
+        <v>-3508</v>
       </c>
       <c r="E76" t="n">
-        <v>-894</v>
+        <v>-500</v>
       </c>
       <c r="F76" t="n">
-        <v>1</v>
+        <v>121</v>
       </c>
       <c r="G76" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="H76" t="n">
-        <v>-874</v>
+        <v>-262</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -4246,49 +4246,49 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K76" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M76" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>111</v>
+        <v>-646</v>
       </c>
       <c r="D77" t="n">
-        <v>-3683</v>
+        <v>-3605</v>
       </c>
       <c r="E77" t="n">
-        <v>-4875</v>
+        <v>-6293</v>
       </c>
       <c r="F77" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-293</v>
+        <v>1182</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -4297,49 +4297,49 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K77" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-2162</v>
+        <v>-1338</v>
       </c>
       <c r="D78" t="n">
-        <v>-4284</v>
+        <v>-3746</v>
       </c>
       <c r="E78" t="n">
-        <v>-3788</v>
+        <v>-13546</v>
       </c>
       <c r="F78" t="n">
-        <v>-1428</v>
+        <v>413</v>
       </c>
       <c r="G78" t="n">
-        <v>-9758</v>
+        <v>403</v>
       </c>
       <c r="H78" t="n">
-        <v>228</v>
+        <v>12</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -4348,19 +4348,19 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K78" t="n">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="79">
@@ -4375,22 +4375,22 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-1969</v>
+        <v>-1212</v>
       </c>
       <c r="D79" t="n">
-        <v>-4452</v>
+        <v>-3998</v>
       </c>
       <c r="E79" t="n">
-        <v>-8720</v>
+        <v>-8885</v>
       </c>
       <c r="F79" t="n">
-        <v>2146</v>
+        <v>2183</v>
       </c>
       <c r="G79" t="n">
-        <v>928</v>
+        <v>1347</v>
       </c>
       <c r="H79" t="n">
-        <v>-132</v>
+        <v>-164</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -4417,31 +4417,31 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>71</v>
+        <v>-3097</v>
       </c>
       <c r="D80" t="n">
-        <v>-4589</v>
+        <v>-4174</v>
       </c>
       <c r="E80" t="n">
-        <v>-18608</v>
+        <v>-1065</v>
       </c>
       <c r="F80" t="n">
         <v>1</v>
       </c>
       <c r="G80" t="n">
-        <v>285</v>
+        <v>1</v>
       </c>
       <c r="H80" t="n">
-        <v>135</v>
+        <v>-750</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -4450,49 +4450,49 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K80" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M80" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>鈊象</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-1434</v>
+        <v>-1645</v>
       </c>
       <c r="D81" t="n">
-        <v>-4806</v>
+        <v>-4651</v>
       </c>
       <c r="E81" t="n">
-        <v>-11243</v>
+        <v>-13331</v>
       </c>
       <c r="F81" t="n">
-        <v>-846</v>
+        <v>3881</v>
       </c>
       <c r="G81" t="n">
-        <v>-667</v>
+        <v>9147</v>
       </c>
       <c r="H81" t="n">
-        <v>-64</v>
+        <v>30</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4501,19 +4501,19 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K81" t="n">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M81" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="82">
@@ -4528,22 +4528,22 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-67</v>
+        <v>27</v>
       </c>
       <c r="D82" t="n">
-        <v>-5123</v>
+        <v>-4657</v>
       </c>
       <c r="E82" t="n">
-        <v>-4017</v>
+        <v>-4041</v>
       </c>
       <c r="F82" t="n">
-        <v>56</v>
+        <v>220</v>
       </c>
       <c r="G82" t="n">
-        <v>3105</v>
+        <v>3228</v>
       </c>
       <c r="H82" t="n">
-        <v>-311</v>
+        <v>-402</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -4570,31 +4570,31 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-1724</v>
+        <v>-450</v>
       </c>
       <c r="D83" t="n">
-        <v>-5443</v>
+        <v>-4787</v>
       </c>
       <c r="E83" t="n">
-        <v>-13446</v>
+        <v>-6327</v>
       </c>
       <c r="F83" t="n">
-        <v>4855</v>
+        <v>5</v>
       </c>
       <c r="G83" t="n">
-        <v>10367</v>
+        <v>-4</v>
       </c>
       <c r="H83" t="n">
-        <v>-8</v>
+        <v>-432</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -4603,11 +4603,11 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K83" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -4615,37 +4615,37 @@
         </is>
       </c>
       <c r="M83" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-302</v>
+        <v>-932</v>
       </c>
       <c r="D84" t="n">
-        <v>-5471</v>
+        <v>-5024</v>
       </c>
       <c r="E84" t="n">
-        <v>-5649</v>
+        <v>-18811</v>
       </c>
       <c r="F84" t="n">
-        <v>96</v>
+        <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>1650</v>
+        <v>285</v>
       </c>
       <c r="H84" t="n">
-        <v>-102</v>
+        <v>-158</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -4658,45 +4658,45 @@
         </is>
       </c>
       <c r="K84" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M84" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1725</v>
+        <v>-1251</v>
       </c>
       <c r="D85" t="n">
-        <v>-5545</v>
+        <v>-5157</v>
       </c>
       <c r="E85" t="n">
-        <v>-199</v>
+        <v>-11750</v>
       </c>
       <c r="F85" t="n">
-        <v>225</v>
+        <v>-846</v>
       </c>
       <c r="G85" t="n">
-        <v>-92</v>
+        <v>-919</v>
       </c>
       <c r="H85" t="n">
-        <v>-162</v>
+        <v>-165</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -4709,45 +4709,45 @@
         </is>
       </c>
       <c r="K85" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M85" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-41422</v>
+        <v>-342</v>
       </c>
       <c r="D86" t="n">
-        <v>-6206</v>
+        <v>-5905</v>
       </c>
       <c r="E86" t="n">
-        <v>-7627</v>
+        <v>-5658</v>
       </c>
       <c r="F86" t="n">
-        <v>23078</v>
+        <v>134</v>
       </c>
       <c r="G86" t="n">
-        <v>34138</v>
+        <v>1688</v>
       </c>
       <c r="H86" t="n">
-        <v>891</v>
+        <v>-78</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -4756,11 +4756,11 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K86" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -4768,37 +4768,37 @@
         </is>
       </c>
       <c r="M86" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>-3279</v>
+        <v>-1847</v>
       </c>
       <c r="D87" t="n">
-        <v>-6245</v>
+        <v>-7494</v>
       </c>
       <c r="E87" t="n">
-        <v>-24084</v>
+        <v>135827</v>
       </c>
       <c r="F87" t="n">
-        <v>-268</v>
+        <v>-16596</v>
       </c>
       <c r="G87" t="n">
-        <v>-2596</v>
+        <v>64205</v>
       </c>
       <c r="H87" t="n">
-        <v>-1781</v>
+        <v>-7460</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -4807,11 +4807,11 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K87" t="n">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -4819,37 +4819,37 @@
         </is>
       </c>
       <c r="M87" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>立隆電</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>-1389</v>
+        <v>-1599</v>
       </c>
       <c r="D88" t="n">
-        <v>-9703</v>
+        <v>-7505</v>
       </c>
       <c r="E88" t="n">
-        <v>29435</v>
+        <v>-14267</v>
       </c>
       <c r="F88" t="n">
-        <v>-66</v>
+        <v>1197</v>
       </c>
       <c r="G88" t="n">
-        <v>-11193</v>
+        <v>8348</v>
       </c>
       <c r="H88" t="n">
-        <v>-324</v>
+        <v>-151</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -4858,113 +4858,113 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K88" t="n">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M88" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-8432</v>
+        <v>-5445</v>
       </c>
       <c r="D89" t="n">
-        <v>-10249</v>
+        <v>-7521</v>
       </c>
       <c r="E89" t="n">
-        <v>-15885</v>
+        <v>25383</v>
       </c>
       <c r="F89" t="n">
-        <v>2433</v>
+        <v>-16</v>
       </c>
       <c r="G89" t="n">
-        <v>8209</v>
+        <v>-11448</v>
       </c>
       <c r="H89" t="n">
-        <v>66</v>
+        <v>-254</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>🔴 大賣</t>
+          <t>🟠 減碼</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K89" t="n">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M89" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>2784</v>
+        <v>-2210</v>
       </c>
       <c r="D90" t="n">
-        <v>-11111</v>
+        <v>-8005</v>
       </c>
       <c r="E90" t="n">
-        <v>-65963</v>
+        <v>-20014</v>
       </c>
       <c r="F90" t="n">
-        <v>678</v>
+        <v>-90</v>
       </c>
       <c r="G90" t="n">
-        <v>8154</v>
+        <v>-2371</v>
       </c>
       <c r="H90" t="n">
-        <v>-298</v>
+        <v>-1588</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>🔴 大賣</t>
+          <t>🟠 減碼</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K90" t="n">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -4972,58 +4972,58 @@
         </is>
       </c>
       <c r="M90" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>-7327</v>
+        <v>3515</v>
       </c>
       <c r="D91" t="n">
-        <v>-13862</v>
+        <v>-8178</v>
       </c>
       <c r="E91" t="n">
-        <v>4115</v>
+        <v>-65454</v>
       </c>
       <c r="F91" t="n">
-        <v>2030</v>
+        <v>560</v>
       </c>
       <c r="G91" t="n">
-        <v>12939</v>
+        <v>8206</v>
       </c>
       <c r="H91" t="n">
-        <v>-27</v>
+        <v>-258</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>🔴 大賣</t>
+          <t>🟠 減碼</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K91" t="n">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M91" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="92">
@@ -5038,22 +5038,22 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>-8175</v>
+        <v>-7472</v>
       </c>
       <c r="D92" t="n">
-        <v>-16386</v>
+        <v>-14706</v>
       </c>
       <c r="E92" t="n">
-        <v>-21414</v>
+        <v>-22639</v>
       </c>
       <c r="F92" t="n">
-        <v>6397</v>
+        <v>6245</v>
       </c>
       <c r="G92" t="n">
-        <v>16481</v>
+        <v>14526</v>
       </c>
       <c r="H92" t="n">
-        <v>-593</v>
+        <v>-300</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -5089,22 +5089,22 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>492</v>
+        <v>-16</v>
       </c>
       <c r="D93" t="n">
-        <v>-16682</v>
+        <v>-16459</v>
       </c>
       <c r="E93" t="n">
-        <v>-42210</v>
+        <v>-41668</v>
       </c>
       <c r="F93" t="n">
-        <v>1073</v>
+        <v>463</v>
       </c>
       <c r="G93" t="n">
-        <v>22891</v>
+        <v>23014</v>
       </c>
       <c r="H93" t="n">
-        <v>-724</v>
+        <v>-320</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -5131,31 +5131,31 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-16887</v>
+        <v>-2746</v>
       </c>
       <c r="D94" t="n">
-        <v>-19831</v>
+        <v>-18663</v>
       </c>
       <c r="E94" t="n">
-        <v>121708</v>
+        <v>4509</v>
       </c>
       <c r="F94" t="n">
-        <v>-15305</v>
+        <v>472</v>
       </c>
       <c r="G94" t="n">
-        <v>66572</v>
+        <v>12925</v>
       </c>
       <c r="H94" t="n">
-        <v>-5897</v>
+        <v>-121</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -5164,49 +5164,49 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K94" t="n">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M94" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>-4067</v>
+        <v>-27475</v>
       </c>
       <c r="D95" t="n">
-        <v>-22249</v>
+        <v>-21037</v>
       </c>
       <c r="E95" t="n">
-        <v>-29276</v>
+        <v>79751</v>
       </c>
       <c r="F95" t="n">
-        <v>-505</v>
+        <v>24774</v>
       </c>
       <c r="G95" t="n">
-        <v>-12337</v>
+        <v>33486</v>
       </c>
       <c r="H95" t="n">
-        <v>-1854</v>
+        <v>22947</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -5215,49 +5215,49 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K95" t="n">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>-20165</v>
+        <v>18089</v>
       </c>
       <c r="D96" t="n">
-        <v>-27141</v>
+        <v>-22992</v>
       </c>
       <c r="E96" t="n">
-        <v>82620</v>
+        <v>-71342</v>
       </c>
       <c r="F96" t="n">
-        <v>24629</v>
+        <v>-10661</v>
       </c>
       <c r="G96" t="n">
-        <v>28584</v>
+        <v>29864</v>
       </c>
       <c r="H96" t="n">
-        <v>22293</v>
+        <v>-4531</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -5266,49 +5266,49 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K96" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M96" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>6331</v>
+        <v>-3888</v>
       </c>
       <c r="D97" t="n">
-        <v>-42874</v>
+        <v>-23953</v>
       </c>
       <c r="E97" t="n">
-        <v>-79809</v>
+        <v>-26019</v>
       </c>
       <c r="F97" t="n">
-        <v>-14268</v>
+        <v>-433</v>
       </c>
       <c r="G97" t="n">
-        <v>32875</v>
+        <v>-13079</v>
       </c>
       <c r="H97" t="n">
-        <v>-1890</v>
+        <v>-2284</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -5317,49 +5317,49 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K97" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-3318</v>
+        <v>-41279</v>
       </c>
       <c r="D98" t="n">
-        <v>-55976</v>
+        <v>-24758</v>
       </c>
       <c r="E98" t="n">
-        <v>-275419</v>
+        <v>-14224</v>
       </c>
       <c r="F98" t="n">
-        <v>10994</v>
+        <v>22388</v>
       </c>
       <c r="G98" t="n">
-        <v>85347</v>
+        <v>38213</v>
       </c>
       <c r="H98" t="n">
-        <v>1606</v>
+        <v>2047</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -5368,49 +5368,49 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K98" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M98" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>-44289</v>
+        <v>-8150</v>
       </c>
       <c r="D99" t="n">
-        <v>-58249</v>
+        <v>-48704</v>
       </c>
       <c r="E99" t="n">
-        <v>-135089</v>
+        <v>-277781</v>
       </c>
       <c r="F99" t="n">
-        <v>17810</v>
+        <v>11558</v>
       </c>
       <c r="G99" t="n">
-        <v>27701</v>
+        <v>78151</v>
       </c>
       <c r="H99" t="n">
-        <v>3784</v>
+        <v>2080</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -5419,15 +5419,15 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K99" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M99" t="n">
@@ -5437,31 +5437,31 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>-19057</v>
+        <v>-44629</v>
       </c>
       <c r="D100" t="n">
-        <v>-94797</v>
+        <v>-71517</v>
       </c>
       <c r="E100" t="n">
-        <v>-277163</v>
+        <v>-145997</v>
       </c>
       <c r="F100" t="n">
-        <v>6880</v>
+        <v>17450</v>
       </c>
       <c r="G100" t="n">
-        <v>8242</v>
+        <v>31005</v>
       </c>
       <c r="H100" t="n">
-        <v>8142</v>
+        <v>3524</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -5470,49 +5470,49 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K100" t="n">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M100" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-39330</v>
+        <v>-17548</v>
       </c>
       <c r="D101" t="n">
-        <v>-142963</v>
+        <v>-79706</v>
       </c>
       <c r="E101" t="n">
-        <v>-170213</v>
+        <v>-284274</v>
       </c>
       <c r="F101" t="n">
-        <v>25682</v>
+        <v>7508</v>
       </c>
       <c r="G101" t="n">
-        <v>135513</v>
+        <v>6121</v>
       </c>
       <c r="H101" t="n">
-        <v>6012</v>
+        <v>9158</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -5521,49 +5521,49 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K101" t="n">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M101" t="n">
-        <v>-5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>-56286</v>
+        <v>-35827</v>
       </c>
       <c r="D102" t="n">
-        <v>-218200</v>
+        <v>-151787</v>
       </c>
       <c r="E102" t="n">
-        <v>427292</v>
+        <v>-176893</v>
       </c>
       <c r="F102" t="n">
-        <v>2800</v>
+        <v>23280</v>
       </c>
       <c r="G102" t="n">
-        <v>4108</v>
+        <v>141731</v>
       </c>
       <c r="H102" t="n">
-        <v>-3426</v>
+        <v>6417</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -5584,37 +5584,37 @@
         </is>
       </c>
       <c r="M102" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>-42300</v>
+        <v>-10607</v>
       </c>
       <c r="D103" t="n">
-        <v>-225029</v>
+        <v>-177176</v>
       </c>
       <c r="E103" t="n">
-        <v>-87034</v>
+        <v>13852</v>
       </c>
       <c r="F103" t="n">
-        <v>27283</v>
+        <v>-66968</v>
       </c>
       <c r="G103" t="n">
-        <v>59308</v>
+        <v>131140</v>
       </c>
       <c r="H103" t="n">
-        <v>1817</v>
+        <v>-1057</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -5627,45 +5627,45 @@
         </is>
       </c>
       <c r="K103" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>-39178</v>
+        <v>-50015</v>
       </c>
       <c r="D104" t="n">
-        <v>-231922</v>
+        <v>-218274</v>
       </c>
       <c r="E104" t="n">
-        <v>11013</v>
+        <v>-94836</v>
       </c>
       <c r="F104" t="n">
-        <v>-71638</v>
+        <v>25134</v>
       </c>
       <c r="G104" t="n">
-        <v>137646</v>
+        <v>62504</v>
       </c>
       <c r="H104" t="n">
-        <v>2020</v>
+        <v>2850</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -5678,15 +5678,66 @@
         </is>
       </c>
       <c r="K104" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M104" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2317</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>鴻海</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>-73455</v>
+      </c>
+      <c r="D105" t="n">
+        <v>-225398</v>
+      </c>
+      <c r="E105" t="n">
+        <v>381562</v>
+      </c>
+      <c r="F105" t="n">
+        <v>5386</v>
+      </c>
+      <c r="G105" t="n">
+        <v>5736</v>
+      </c>
+      <c r="H105" t="n">
+        <v>-4010</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>🔴 大賣</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K105" t="n">
+        <v>77</v>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M105" t="n">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
@@ -5700,7 +5751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5743,406 +5794,406 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -1,462 千股)</t>
+          <t>📈 20d 巨變(加碼 168 千股)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-1206948</v>
+        <v>-4191290</v>
       </c>
       <c r="D2" t="n">
-        <v>629154</v>
+        <v>553646</v>
       </c>
       <c r="E2" t="n">
-        <v>320656</v>
+        <v>-5432097</v>
       </c>
       <c r="F2" t="n">
-        <v>2090908</v>
+        <v>385624</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>亞翔</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,104 千股)</t>
+          <t>📈 20d 巨變(加碼 418 千股)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>365537</v>
+        <v>170466</v>
       </c>
       <c r="D3" t="n">
-        <v>2134968</v>
+        <v>1803745</v>
       </c>
       <c r="E3" t="n">
-        <v>435685</v>
+        <v>35324</v>
       </c>
       <c r="F3" t="n">
-        <v>3238964</v>
+        <v>1385490</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>健策</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -711 千股)</t>
+          <t>📉 20d 巨變(減碼 -65 千股)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2623750</v>
+        <v>-1441823</v>
       </c>
       <c r="D4" t="n">
-        <v>1076448</v>
+        <v>564280</v>
       </c>
       <c r="E4" t="n">
-        <v>3287626</v>
+        <v>-1206948</v>
       </c>
       <c r="F4" t="n">
-        <v>1787781</v>
+        <v>629154</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>台光電</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -158 千股)</t>
+          <t>📉 20d 巨變(減碼 -625 千股)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>35324</v>
+        <v>-268060</v>
       </c>
       <c r="D5" t="n">
-        <v>1385490</v>
+        <v>-2366903</v>
       </c>
       <c r="E5" t="n">
-        <v>484836</v>
+        <v>-137202</v>
       </c>
       <c r="F5" t="n">
-        <v>1543754</v>
+        <v>-1741839</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>勤誠</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,085 千股)</t>
+          <t>📉 20d 巨變(減碼 -210 千股)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-5432097</v>
+        <v>270987</v>
       </c>
       <c r="D6" t="n">
-        <v>385624</v>
+        <v>1925416</v>
       </c>
       <c r="E6" t="n">
-        <v>-3720877</v>
+        <v>365537</v>
       </c>
       <c r="F6" t="n">
-        <v>-698890</v>
+        <v>2134968</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>高力</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 466 千股)</t>
+          <t>📈 20d 巨變(加碼 186 千股)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-137202</v>
+        <v>440332</v>
       </c>
       <c r="D7" t="n">
-        <v>-1741839</v>
+        <v>1262617</v>
       </c>
       <c r="E7" t="n">
-        <v>83549</v>
+        <v>2623750</v>
       </c>
       <c r="F7" t="n">
-        <v>-2207485</v>
+        <v>1076448</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>奇鋐</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -56 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -501 千股)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-149213</v>
+        <v>-690759</v>
       </c>
       <c r="D8" t="n">
-        <v>5689071</v>
+        <v>282202</v>
       </c>
       <c r="E8" t="n">
-        <v>20061</v>
+        <v>220229</v>
       </c>
       <c r="F8" t="n">
-        <v>5745220</v>
+        <v>783557</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>智邦</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -523 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -1,103 千股)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>220229</v>
+        <v>-450266</v>
       </c>
       <c r="D9" t="n">
-        <v>783557</v>
+        <v>-4786613</v>
       </c>
       <c r="E9" t="n">
-        <v>331609</v>
+        <v>110793</v>
       </c>
       <c r="F9" t="n">
-        <v>1306969</v>
+        <v>-3683409</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>雙鴻</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 73 千股)</t>
+          <t>📉 20d 巨變(減碼 -525 千股)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-225557</v>
+        <v>-182549</v>
       </c>
       <c r="D10" t="n">
-        <v>-1203395</v>
+        <v>5164022</v>
       </c>
       <c r="E10" t="n">
-        <v>101559</v>
+        <v>-149213</v>
       </c>
       <c r="F10" t="n">
-        <v>-1276814</v>
+        <v>5689071</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>致茂</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -127 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 366 千股)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-11364</v>
+        <v>132049</v>
       </c>
       <c r="D11" t="n">
-        <v>-1158965</v>
+        <v>-837842</v>
       </c>
       <c r="E11" t="n">
-        <v>269778</v>
+        <v>-225557</v>
       </c>
       <c r="F11" t="n">
-        <v>-1032083</v>
+        <v>-1203395</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>光聖</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 20,224 千股)</t>
+          <t>🟢 外資 5d 翻綠</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-19057291</v>
+        <v>104870</v>
       </c>
       <c r="D12" t="n">
-        <v>-94797468</v>
+        <v>-1157789</v>
       </c>
       <c r="E12" t="n">
-        <v>-20728692</v>
+        <v>-11364</v>
       </c>
       <c r="F12" t="n">
-        <v>-115021028</v>
+        <v>-1158965</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>旺矽</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 307 千股)</t>
+          <t>📈 20d 巨變(加碼 15,092 千股)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>110793</v>
+        <v>-17548375</v>
       </c>
       <c r="D13" t="n">
-        <v>-3683409</v>
+        <v>-79705934</v>
       </c>
       <c r="E13" t="n">
-        <v>221635</v>
+        <v>-19057291</v>
       </c>
       <c r="F13" t="n">
-        <v>-3990364</v>
+        <v>-94797468</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -323 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,704 千股)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>565831</v>
+        <v>-3887721</v>
       </c>
       <c r="D14" t="n">
-        <v>-1185391</v>
+        <v>-23953215</v>
       </c>
       <c r="E14" t="n">
-        <v>864669</v>
+        <v>-4067211</v>
       </c>
       <c r="F14" t="n">
-        <v>-862007</v>
+        <v>-22249419</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>台達電</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,043 千股)</t>
+          <t>📈 20d 巨變(加碼 82 千股)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-4067211</v>
+        <v>450801</v>
       </c>
       <c r="D15" t="n">
-        <v>-22249419</v>
+        <v>-1103769</v>
       </c>
       <c r="E15" t="n">
-        <v>-1867636</v>
+        <v>565831</v>
       </c>
       <c r="F15" t="n">
-        <v>-21206568</v>
+        <v>-1185391</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>帆宣</t>
         </is>
       </c>
     </row>
@@ -6154,20 +6205,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -579 千股)</t>
+          <t>📈 20d 巨變(加碼 644 千股)</t>
         </is>
       </c>
       <c r="C16" t="n">
+        <v>501458</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-184741</v>
+      </c>
+      <c r="E16" t="n">
         <v>842276</v>
       </c>
-      <c r="D16" t="n">
+      <c r="F16" t="n">
         <v>-828616</v>
-      </c>
-      <c r="E16" t="n">
-        <v>456057</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-249653</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -6178,29 +6229,29 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -12 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -319 千股)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-308178</v>
+        <v>-419794</v>
       </c>
       <c r="D17" t="n">
-        <v>275142</v>
+        <v>1198347</v>
       </c>
       <c r="E17" t="n">
-        <v>-240219</v>
+        <v>381391</v>
       </c>
       <c r="F17" t="n">
-        <v>286741</v>
+        <v>1517230</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>辛耘</t>
         </is>
       </c>
     </row>
@@ -6212,20 +6263,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -529 千股)</t>
+          <t>📉 20d 巨變(減碼 -2,150 千股)</t>
         </is>
       </c>
       <c r="C18" t="n">
+        <v>2659207</v>
+      </c>
+      <c r="D18" t="n">
+        <v>8409142</v>
+      </c>
+      <c r="E18" t="n">
         <v>4515721</v>
       </c>
-      <c r="D18" t="n">
+      <c r="F18" t="n">
         <v>10559458</v>
-      </c>
-      <c r="E18" t="n">
-        <v>5709338</v>
-      </c>
-      <c r="F18" t="n">
-        <v>11088894</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -6236,29 +6287,29 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -361 千股)</t>
+          <t>📉 20d 巨變(減碼 -31 千股)</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>381391</v>
+        <v>-234934</v>
       </c>
       <c r="D19" t="n">
-        <v>1517230</v>
+        <v>244537</v>
       </c>
       <c r="E19" t="n">
-        <v>664569</v>
+        <v>-308178</v>
       </c>
       <c r="F19" t="n">
-        <v>1878508</v>
+        <v>275142</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>川湖</t>
         </is>
       </c>
     </row>
@@ -6270,20 +6321,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -882 千股)</t>
+          <t>📉 20d 巨變(減碼 -952 千股)</t>
         </is>
       </c>
       <c r="C20" t="n">
+        <v>-3889304</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-1308156</v>
+      </c>
+      <c r="E20" t="n">
         <v>-3802047</v>
       </c>
-      <c r="D20" t="n">
+      <c r="F20" t="n">
         <v>-356298</v>
-      </c>
-      <c r="E20" t="n">
-        <v>-2406640</v>
-      </c>
-      <c r="F20" t="n">
-        <v>525639</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -6299,20 +6350,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 342 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 223 千股)</t>
         </is>
       </c>
       <c r="C21" t="n">
+        <v>-16219</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-16459089</v>
+      </c>
+      <c r="E21" t="n">
         <v>492096</v>
       </c>
-      <c r="D21" t="n">
+      <c r="F21" t="n">
         <v>-16682304</v>
-      </c>
-      <c r="E21" t="n">
-        <v>-2544773</v>
-      </c>
-      <c r="F21" t="n">
-        <v>-17024626</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -6328,20 +6379,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -39 千股)</t>
+          <t>📉 20d 巨變(減碼 -98 千股)</t>
         </is>
       </c>
       <c r="C22" t="n">
+        <v>-443676</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1205811</v>
+      </c>
+      <c r="E22" t="n">
         <v>-218020</v>
       </c>
-      <c r="D22" t="n">
+      <c r="F22" t="n">
         <v>1303799</v>
-      </c>
-      <c r="E22" t="n">
-        <v>-46203</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1343026</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -6357,20 +6408,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -33 千股)</t>
+          <t>📉 20d 巨變(減碼 -829 千股)</t>
         </is>
       </c>
       <c r="C23" t="n">
+        <v>-380293</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-29807</v>
+      </c>
+      <c r="E23" t="n">
         <v>-540862</v>
       </c>
-      <c r="D23" t="n">
+      <c r="F23" t="n">
         <v>799476</v>
-      </c>
-      <c r="E23" t="n">
-        <v>-255121</v>
-      </c>
-      <c r="F23" t="n">
-        <v>832654</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -6381,116 +6432,116 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -397 千股)</t>
+          <t>📉 20d 巨變(減碼 -351 千股)</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-1842060</v>
+        <v>-1251072</v>
       </c>
       <c r="D24" t="n">
-        <v>-2748932</v>
+        <v>-5157480</v>
       </c>
       <c r="E24" t="n">
-        <v>-1742870</v>
+        <v>-1434083</v>
       </c>
       <c r="F24" t="n">
-        <v>-2351989</v>
+        <v>-4806379</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>華城</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 953 千股)</t>
+          <t>📈 20d 巨變(加碼 626 千股)</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-1434083</v>
+        <v>-472714</v>
       </c>
       <c r="D25" t="n">
-        <v>-4806379</v>
+        <v>-2122620</v>
       </c>
       <c r="E25" t="n">
-        <v>-2057302</v>
+        <v>-1842060</v>
       </c>
       <c r="F25" t="n">
-        <v>-5759726</v>
+        <v>-2748932</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>大立光</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -853 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 19 千股)</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2058724</v>
+        <v>-35711</v>
       </c>
       <c r="D26" t="n">
-        <v>2795750</v>
+        <v>-141807</v>
       </c>
       <c r="E26" t="n">
-        <v>1395204</v>
+        <v>5286</v>
       </c>
       <c r="F26" t="n">
-        <v>3648892</v>
+        <v>-160980</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>大車隊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -6 千股)</t>
+          <t>📈 20d 巨變(加碼 145 千股)</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5286</v>
+        <v>2148962</v>
       </c>
       <c r="D27" t="n">
-        <v>-160980</v>
+        <v>2940341</v>
       </c>
       <c r="E27" t="n">
-        <v>7326</v>
+        <v>2058724</v>
       </c>
       <c r="F27" t="n">
-        <v>-154963</v>
+        <v>2795750</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>大車隊</t>
+          <t>零壹</t>
         </is>
       </c>
     </row>
@@ -6502,20 +6553,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -17 千股)</t>
+          <t>📈 20d 巨變(加碼 17 千股)</t>
         </is>
       </c>
       <c r="C28" t="n">
+        <v>47270</v>
+      </c>
+      <c r="D28" t="n">
+        <v>369363</v>
+      </c>
+      <c r="E28" t="n">
         <v>44390</v>
       </c>
-      <c r="D28" t="n">
+      <c r="F28" t="n">
         <v>352853</v>
-      </c>
-      <c r="E28" t="n">
-        <v>48693</v>
-      </c>
-      <c r="F28" t="n">
-        <v>369457</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -6531,20 +6582,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -948 千股)</t>
+          <t>📉 20d 巨變(減碼 -60 千股)</t>
         </is>
       </c>
       <c r="C29" t="n">
+        <v>1603053</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-3355479</v>
+      </c>
+      <c r="E29" t="n">
         <v>2150396</v>
       </c>
-      <c r="D29" t="n">
+      <c r="F29" t="n">
         <v>-3295719</v>
-      </c>
-      <c r="E29" t="n">
-        <v>2217419</v>
-      </c>
-      <c r="F29" t="n">
-        <v>-2347434</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -6555,232 +6606,232 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -177 千股)</t>
+          <t>📉 20d 巨變(減碼 -691 千股)</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1725471</v>
+        <v>-1491748</v>
       </c>
       <c r="D30" t="n">
-        <v>-5544849</v>
+        <v>-75023</v>
       </c>
       <c r="E30" t="n">
-        <v>1694120</v>
+        <v>-741748</v>
       </c>
       <c r="F30" t="n">
-        <v>-5367585</v>
+        <v>616413</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>隆大</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -328 千股)</t>
+          <t>📈 20d 巨變(加碼 2,037 千股)</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-741748</v>
+        <v>1425471</v>
       </c>
       <c r="D31" t="n">
-        <v>616413</v>
+        <v>-3507847</v>
       </c>
       <c r="E31" t="n">
-        <v>-457748</v>
+        <v>1725471</v>
       </c>
       <c r="F31" t="n">
-        <v>944413</v>
+        <v>-5544849</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>建準</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -10 千股)</t>
+          <t>📉 20d 巨變(減碼 -404 千股)</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-1478612</v>
+        <v>594916</v>
       </c>
       <c r="D32" t="n">
-        <v>1049961</v>
+        <v>1662635</v>
       </c>
       <c r="E32" t="n">
-        <v>-2232522</v>
+        <v>829916</v>
       </c>
       <c r="F32" t="n">
-        <v>1059866</v>
+        <v>2066635</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>合機</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -395 千股)</t>
+          <t>📉 20d 巨變(減碼 -631 千股)</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-824583</v>
+        <v>-306200</v>
       </c>
       <c r="D33" t="n">
-        <v>659823</v>
+        <v>418967</v>
       </c>
       <c r="E33" t="n">
-        <v>-456949</v>
+        <v>-1478612</v>
       </c>
       <c r="F33" t="n">
-        <v>1054367</v>
+        <v>1049961</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>寶雅</t>
+          <t>卜蜂</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -168 千股)</t>
+          <t>📈 20d 巨變(加碼 9,826 千股)</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>829916</v>
+        <v>-23887216</v>
       </c>
       <c r="D34" t="n">
-        <v>2066635</v>
+        <v>207000535</v>
       </c>
       <c r="E34" t="n">
-        <v>690556</v>
+        <v>-48937896</v>
       </c>
       <c r="F34" t="n">
-        <v>2234780</v>
+        <v>197174163</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>合機</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -66 千股)</t>
+          <t>📉 20d 巨變(減碼 -304 千股)</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>123331</v>
+        <v>-609650</v>
       </c>
       <c r="D35" t="n">
-        <v>-541501</v>
+        <v>356006</v>
       </c>
       <c r="E35" t="n">
-        <v>187331</v>
+        <v>-824583</v>
       </c>
       <c r="F35" t="n">
-        <v>-475501</v>
+        <v>659823</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>寶雅</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 118 千股)</t>
+          <t>📉 20d 巨變(減碼 -48 千股)</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2049456</v>
+        <v>125331</v>
       </c>
       <c r="D36" t="n">
-        <v>-775576</v>
+        <v>-589501</v>
       </c>
       <c r="E36" t="n">
-        <v>1748454</v>
+        <v>123331</v>
       </c>
       <c r="F36" t="n">
-        <v>-894008</v>
+        <v>-541501</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>大統益</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -444 千股)</t>
+          <t>📈 20d 巨變(加碼 1,309 千股)</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-48937896</v>
+        <v>2013621</v>
       </c>
       <c r="D37" t="n">
-        <v>197174163</v>
+        <v>533088</v>
       </c>
       <c r="E37" t="n">
-        <v>-52104977</v>
+        <v>2049456</v>
       </c>
       <c r="F37" t="n">
-        <v>197618224</v>
+        <v>-775576</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>豐藝</t>
         </is>
       </c>
     </row>
@@ -6792,20 +6843,20 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -112 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -101 千股)</t>
         </is>
       </c>
       <c r="C38" t="n">
+        <v>-55495</v>
+      </c>
+      <c r="D38" t="n">
+        <v>373491</v>
+      </c>
+      <c r="E38" t="n">
         <v>21399</v>
       </c>
-      <c r="D38" t="n">
+      <c r="F38" t="n">
         <v>474845</v>
-      </c>
-      <c r="E38" t="n">
-        <v>78325</v>
-      </c>
-      <c r="F38" t="n">
-        <v>586845</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -6816,348 +6867,348 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -374 千股)</t>
+          <t>🔴 外資 5d 翻紅</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>14159</v>
+        <v>-6000</v>
       </c>
       <c r="D39" t="n">
-        <v>-1231370</v>
+        <v>-14000</v>
       </c>
       <c r="E39" t="n">
-        <v>205038</v>
+        <v>3000</v>
       </c>
       <c r="F39" t="n">
-        <v>-857067</v>
+        <v>-17000</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>方土霖</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -254 千股)</t>
+          <t>📈 20d 巨變(加碼 55 千股)</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-512407</v>
+        <v>4017</v>
       </c>
       <c r="D40" t="n">
-        <v>867682</v>
+        <v>-1176083</v>
       </c>
       <c r="E40" t="n">
-        <v>-519407</v>
+        <v>14159</v>
       </c>
       <c r="F40" t="n">
-        <v>1121682</v>
+        <v>-1231370</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>華景電</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -53 千股)</t>
+          <t>📉 20d 巨變(減碼 -256 千股)</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-166534</v>
+        <v>-292657</v>
       </c>
       <c r="D41" t="n">
-        <v>-404044</v>
+        <v>611560</v>
       </c>
       <c r="E41" t="n">
-        <v>72356</v>
+        <v>-512407</v>
       </c>
       <c r="F41" t="n">
-        <v>-350985</v>
+        <v>867682</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>八方雲集</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -4,925 千股)</t>
+          <t>📉 20d 巨變(減碼 -31 千股)</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-41421559</v>
+        <v>-316505</v>
       </c>
       <c r="D42" t="n">
-        <v>-6205883</v>
+        <v>-434983</v>
       </c>
       <c r="E42" t="n">
-        <v>-43778879</v>
+        <v>-166534</v>
       </c>
       <c r="F42" t="n">
-        <v>-1280701</v>
+        <v>-404044</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>穎崴</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 41 千股)</t>
+          <t>📉 20d 巨變(減碼 -18,552 千股)</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-92300</v>
+        <v>-41279255</v>
       </c>
       <c r="D43" t="n">
-        <v>-234300</v>
+        <v>-24758000</v>
       </c>
       <c r="E43" t="n">
-        <v>-48300</v>
+        <v>-41421559</v>
       </c>
       <c r="F43" t="n">
-        <v>-275300</v>
+        <v>-6205883</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>聯合</t>
+          <t>台灣大</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 2,382 千股)</t>
+          <t>📈 20d 巨變(加碼 51 千股)</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2784253</v>
+        <v>-84300</v>
       </c>
       <c r="D44" t="n">
-        <v>-11110546</v>
+        <v>-183300</v>
       </c>
       <c r="E44" t="n">
-        <v>782768</v>
+        <v>-92300</v>
       </c>
       <c r="F44" t="n">
-        <v>-13492329</v>
+        <v>-234300</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>聯合</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 4,383 千股)</t>
+          <t>📈 20d 巨變(加碼 2,932 千股)</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3560636</v>
+        <v>3514589</v>
       </c>
       <c r="D45" t="n">
-        <v>-1231035</v>
+        <v>-8178400</v>
       </c>
       <c r="E45" t="n">
-        <v>-1078303</v>
+        <v>2784253</v>
       </c>
       <c r="F45" t="n">
-        <v>-5613622</v>
+        <v>-11110546</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -826 千股)</t>
+          <t>📈 20d 巨變(加碼 907 千股)</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-1254743</v>
+        <v>1919835</v>
       </c>
       <c r="D46" t="n">
-        <v>-290424</v>
+        <v>-323904</v>
       </c>
       <c r="E46" t="n">
-        <v>-1264743</v>
+        <v>3560636</v>
       </c>
       <c r="F46" t="n">
-        <v>535803</v>
+        <v>-1231035</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>亞力</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 489 千股)</t>
+          <t>📉 20d 巨變(減碼 -73 千股)</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1737891</v>
+        <v>-431221</v>
       </c>
       <c r="D47" t="n">
-        <v>3897798</v>
+        <v>-363304</v>
       </c>
       <c r="E47" t="n">
-        <v>1534783</v>
+        <v>-1254743</v>
       </c>
       <c r="F47" t="n">
-        <v>3408935</v>
+        <v>-290424</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>大綜</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -1,977 千股)</t>
+          <t>📉 20d 巨變(減碼 -134 千股)</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-3507738</v>
+        <v>1406179</v>
       </c>
       <c r="D48" t="n">
-        <v>-2501552</v>
+        <v>3763436</v>
       </c>
       <c r="E48" t="n">
-        <v>254005</v>
+        <v>1737891</v>
       </c>
       <c r="F48" t="n">
-        <v>-524714</v>
+        <v>3897798</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>漢科</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 3,411 千股)</t>
+          <t>📈 20d 巨變(加碼 2,745 千股)</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-3278813</v>
+        <v>-1598599</v>
       </c>
       <c r="D49" t="n">
-        <v>-6245257</v>
+        <v>-7504632</v>
       </c>
       <c r="E49" t="n">
-        <v>-3091857</v>
+        <v>-8431966</v>
       </c>
       <c r="F49" t="n">
-        <v>-9656179</v>
+        <v>-10249194</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>立隆電</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -799 千股)</t>
+          <t>📈 20d 巨變(加碼 1,433 千股)</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-8431966</v>
+        <v>-1609312</v>
       </c>
       <c r="D50" t="n">
-        <v>-10249194</v>
+        <v>-1068311</v>
       </c>
       <c r="E50" t="n">
-        <v>-7498863</v>
+        <v>-3507738</v>
       </c>
       <c r="F50" t="n">
-        <v>-9450397</v>
+        <v>-2501552</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>台燿</t>
         </is>
       </c>
     </row>
@@ -7169,20 +7220,20 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -467 千股)</t>
+          <t>📈 20d 巨變(加碼 1,528 千股)</t>
         </is>
       </c>
       <c r="C51" t="n">
+        <v>-720685</v>
+      </c>
+      <c r="D51" t="n">
+        <v>-1842070</v>
+      </c>
+      <c r="E51" t="n">
         <v>-1114078</v>
       </c>
-      <c r="D51" t="n">
+      <c r="F51" t="n">
         <v>-3369885</v>
-      </c>
-      <c r="E51" t="n">
-        <v>-17179</v>
-      </c>
-      <c r="F51" t="n">
-        <v>-2902713</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -7193,232 +7244,232 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -427 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,760 千股)</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-1159279</v>
+        <v>-2210124</v>
       </c>
       <c r="D52" t="n">
-        <v>-3035464</v>
+        <v>-8004998</v>
       </c>
       <c r="E52" t="n">
-        <v>-522402</v>
+        <v>-3278813</v>
       </c>
       <c r="F52" t="n">
-        <v>-2608856</v>
+        <v>-6245257</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 7,864 千股)</t>
+          <t>📈 20d 巨變(加碼 139 千股)</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>6331225</v>
+        <v>-1238606</v>
       </c>
       <c r="D53" t="n">
-        <v>-42873722</v>
+        <v>-2896284</v>
       </c>
       <c r="E53" t="n">
-        <v>8223413</v>
+        <v>-1159279</v>
       </c>
       <c r="F53" t="n">
-        <v>-50737807</v>
+        <v>-3035464</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>世芯-KY</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 2,748 千股)</t>
+          <t>📈 20d 巨變(加碼 19,881 千股)</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-16887087</v>
+        <v>18088967</v>
       </c>
       <c r="D54" t="n">
-        <v>-19831169</v>
+        <v>-22992379</v>
       </c>
       <c r="E54" t="n">
-        <v>-24206159</v>
+        <v>6331225</v>
       </c>
       <c r="F54" t="n">
-        <v>-22579037</v>
+        <v>-42873722</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 754 千股)</t>
+          <t>📈 20d 巨變(加碼 12,337 千股)</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>-13473886</v>
+        <v>-1847173</v>
       </c>
       <c r="D55" t="n">
-        <v>42426973</v>
+        <v>-7493987</v>
       </c>
       <c r="E55" t="n">
-        <v>-10587111</v>
+        <v>-16887087</v>
       </c>
       <c r="F55" t="n">
-        <v>41673068</v>
+        <v>-19831169</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,138 千股)</t>
+          <t>📈 20d 巨變(加碼 2,425 千股)</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-1723882</v>
+        <v>-22577470</v>
       </c>
       <c r="D56" t="n">
-        <v>-5443410</v>
+        <v>44851996</v>
       </c>
       <c r="E56" t="n">
-        <v>-1233776</v>
+        <v>-13473886</v>
       </c>
       <c r="F56" t="n">
-        <v>-6581855</v>
+        <v>42426973</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 601 千股)</t>
+          <t>📈 20d 巨變(加碼 792 千股)</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>991321</v>
+        <v>-1645357</v>
       </c>
       <c r="D57" t="n">
-        <v>-1942598</v>
+        <v>-4651302</v>
       </c>
       <c r="E57" t="n">
-        <v>18289</v>
+        <v>-1723882</v>
       </c>
       <c r="F57" t="n">
-        <v>-2544067</v>
+        <v>-5443410</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>鈊象</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -354 千股)</t>
+          <t>📈 20d 巨變(加碼 833 千股)</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-255036</v>
+        <v>483915</v>
       </c>
       <c r="D58" t="n">
-        <v>1399524</v>
+        <v>-1109768</v>
       </c>
       <c r="E58" t="n">
-        <v>-296423</v>
+        <v>991321</v>
       </c>
       <c r="F58" t="n">
-        <v>1753434</v>
+        <v>-1942598</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>士電</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 110 千股)</t>
+          <t>📉 20d 巨變(減碼 -375 千股)</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>207395</v>
+        <v>-300029</v>
       </c>
       <c r="D59" t="n">
-        <v>-563324</v>
+        <v>1024360</v>
       </c>
       <c r="E59" t="n">
-        <v>262382</v>
+        <v>-255036</v>
       </c>
       <c r="F59" t="n">
-        <v>-673517</v>
+        <v>1399524</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>達欣工</t>
         </is>
       </c>
     </row>
@@ -7430,20 +7481,20 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -750 千股)</t>
+          <t>📉 20d 巨變(減碼 -2,001 千股)</t>
         </is>
       </c>
       <c r="C60" t="n">
+        <v>-645510</v>
+      </c>
+      <c r="D60" t="n">
+        <v>-3604968</v>
+      </c>
+      <c r="E60" t="n">
         <v>-290945</v>
       </c>
-      <c r="D60" t="n">
+      <c r="F60" t="n">
         <v>-1603932</v>
-      </c>
-      <c r="E60" t="n">
-        <v>-534478</v>
-      </c>
-      <c r="F60" t="n">
-        <v>-853873</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -7454,29 +7505,29 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 38 千股)</t>
+          <t>📉 20d 巨變(減碼 -62 千股)</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>418153</v>
+        <v>99395</v>
       </c>
       <c r="D61" t="n">
-        <v>886170</v>
+        <v>-625797</v>
       </c>
       <c r="E61" t="n">
-        <v>358170</v>
+        <v>207395</v>
       </c>
       <c r="F61" t="n">
-        <v>847896</v>
+        <v>-563324</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>普萊德</t>
         </is>
       </c>
     </row>
@@ -7488,20 +7539,20 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 608 千股)</t>
+          <t>📉 20d 巨變(減碼 -173 千股)</t>
         </is>
       </c>
       <c r="C62" t="n">
+        <v>730406</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1078023</v>
+      </c>
+      <c r="E62" t="n">
         <v>944822</v>
       </c>
-      <c r="D62" t="n">
+      <c r="F62" t="n">
         <v>1250837</v>
-      </c>
-      <c r="E62" t="n">
-        <v>491039</v>
-      </c>
-      <c r="F62" t="n">
-        <v>643200</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -7512,145 +7563,145 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -163 千股)</t>
+          <t>📈 20d 巨變(加碼 258 千股)</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-94562</v>
+        <v>687098</v>
       </c>
       <c r="D63" t="n">
-        <v>377133</v>
+        <v>1144412</v>
       </c>
       <c r="E63" t="n">
-        <v>225430</v>
+        <v>418153</v>
       </c>
       <c r="F63" t="n">
-        <v>540080</v>
+        <v>886170</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -207 千股)</t>
+          <t>📉 20d 巨變(減碼 -347 千股)</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>-517856</v>
+        <v>-460602</v>
       </c>
       <c r="D64" t="n">
-        <v>264288</v>
+        <v>30083</v>
       </c>
       <c r="E64" t="n">
-        <v>125609</v>
+        <v>-94562</v>
       </c>
       <c r="F64" t="n">
-        <v>470834</v>
+        <v>377133</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>信立</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -597 千股)</t>
+          <t>📈 20d 巨變(加碼 263 千股)</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-1189932</v>
+        <v>-273448</v>
       </c>
       <c r="D65" t="n">
-        <v>1179910</v>
+        <v>526798</v>
       </c>
       <c r="E65" t="n">
-        <v>-214109</v>
+        <v>-517856</v>
       </c>
       <c r="F65" t="n">
-        <v>1777038</v>
+        <v>264288</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>祥碩</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 484 千股)</t>
+          <t>📉 20d 巨變(減碼 -420 千股)</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-432425</v>
+        <v>-764731</v>
       </c>
       <c r="D66" t="n">
-        <v>-2717631</v>
+        <v>759801</v>
       </c>
       <c r="E66" t="n">
-        <v>-1151046</v>
+        <v>-1189932</v>
       </c>
       <c r="F66" t="n">
-        <v>-3201906</v>
+        <v>1179910</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>華星光</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -175 千股)</t>
+          <t>📉 20d 巨變(減碼 -394 千股)</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>522223</v>
+        <v>115</v>
       </c>
       <c r="D67" t="n">
-        <v>3827747</v>
+        <v>-3111902</v>
       </c>
       <c r="E67" t="n">
-        <v>1217149</v>
+        <v>-432425</v>
       </c>
       <c r="F67" t="n">
-        <v>4002810</v>
+        <v>-2717631</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>聯鈞</t>
         </is>
       </c>
     </row>
@@ -7662,20 +7713,20 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -434 千股)</t>
+          <t>📉 20d 巨變(減碼 -469 千股)</t>
         </is>
       </c>
       <c r="C68" t="n">
+        <v>-1338212</v>
+      </c>
+      <c r="D68" t="n">
+        <v>-3745568</v>
+      </c>
+      <c r="E68" t="n">
         <v>-462082</v>
       </c>
-      <c r="D68" t="n">
+      <c r="F68" t="n">
         <v>-3276831</v>
-      </c>
-      <c r="E68" t="n">
-        <v>-541455</v>
-      </c>
-      <c r="F68" t="n">
-        <v>-2842475</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -7686,87 +7737,87 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 11,125 千股)</t>
+          <t>📉 20d 巨變(減碼 -144 千股)</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-3317835</v>
+        <v>477285</v>
       </c>
       <c r="D69" t="n">
-        <v>-55975763</v>
+        <v>3683344</v>
       </c>
       <c r="E69" t="n">
-        <v>1126790</v>
+        <v>522223</v>
       </c>
       <c r="F69" t="n">
-        <v>-67101183</v>
+        <v>3827747</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>聯亞</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -11,788 千股)</t>
+          <t>📈 20d 巨變(加碼 7,271 千股)</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-42300050</v>
+        <v>-8150064</v>
       </c>
       <c r="D70" t="n">
-        <v>-225029096</v>
+        <v>-48704288</v>
       </c>
       <c r="E70" t="n">
-        <v>-35494025</v>
+        <v>-3317835</v>
       </c>
       <c r="F70" t="n">
-        <v>-213240835</v>
+        <v>-55975763</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 7,869 千股)</t>
+          <t>📈 20d 巨變(加碼 6,755 千股)</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>23100821</v>
+        <v>-50014891</v>
       </c>
       <c r="D71" t="n">
-        <v>19706634</v>
+        <v>-218274214</v>
       </c>
       <c r="E71" t="n">
-        <v>17374694</v>
+        <v>-42300050</v>
       </c>
       <c r="F71" t="n">
-        <v>11837401</v>
+        <v>-225029096</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
@@ -7778,20 +7829,20 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 2,021 千股)</t>
+          <t>📈 20d 巨變(加碼 1,680 千股)</t>
         </is>
       </c>
       <c r="C72" t="n">
+        <v>-7472403</v>
+      </c>
+      <c r="D72" t="n">
+        <v>-14706110</v>
+      </c>
+      <c r="E72" t="n">
         <v>-8175248</v>
       </c>
-      <c r="D72" t="n">
+      <c r="F72" t="n">
         <v>-16386412</v>
-      </c>
-      <c r="E72" t="n">
-        <v>-7835515</v>
-      </c>
-      <c r="F72" t="n">
-        <v>-18407589</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -7802,174 +7853,174 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -84 千股)</t>
+          <t>📉 20d 巨變(減碼 -482 千股)</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>76083</v>
+        <v>13986990</v>
       </c>
       <c r="D73" t="n">
-        <v>889464</v>
+        <v>19225034</v>
       </c>
       <c r="E73" t="n">
-        <v>17317</v>
+        <v>23100821</v>
       </c>
       <c r="F73" t="n">
-        <v>973464</v>
+        <v>19706634</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>德昌</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 2,251 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -111 千股)</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>-7327434</v>
+        <v>-68968</v>
       </c>
       <c r="D74" t="n">
-        <v>-13862410</v>
+        <v>778464</v>
       </c>
       <c r="E74" t="n">
-        <v>-9774310</v>
+        <v>76083</v>
       </c>
       <c r="F74" t="n">
-        <v>-16113473</v>
+        <v>889464</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>德昌</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -109 千股)</t>
+          <t>📉 20d 巨變(減碼 -4,800 千股)</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>-141207</v>
+        <v>-2746133</v>
       </c>
       <c r="D75" t="n">
-        <v>-375113</v>
+        <v>-18662602</v>
       </c>
       <c r="E75" t="n">
-        <v>141612</v>
+        <v>-7327434</v>
       </c>
       <c r="F75" t="n">
-        <v>-266294</v>
+        <v>-13862410</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>億泰</t>
+          <t>台汽電</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -103 千股)</t>
+          <t>📉 20d 巨變(減碼 -193 千股)</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>180144</v>
+        <v>-570959</v>
       </c>
       <c r="D76" t="n">
-        <v>-379674</v>
+        <v>-567865</v>
       </c>
       <c r="E76" t="n">
-        <v>204195</v>
+        <v>-141207</v>
       </c>
       <c r="F76" t="n">
-        <v>-276684</v>
+        <v>-375113</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>億泰</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 158 千股)</t>
+          <t>📉 20d 巨變(減碼 -67 千股)</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-244260</v>
+        <v>64000</v>
       </c>
       <c r="D77" t="n">
-        <v>3434342</v>
+        <v>-446414</v>
       </c>
       <c r="E77" t="n">
-        <v>-163140</v>
+        <v>180144</v>
       </c>
       <c r="F77" t="n">
-        <v>3275973</v>
+        <v>-379674</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>友輝</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,034 千股)</t>
+          <t>📈 20d 巨變(加碼 74 千股)</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-1389207</v>
+        <v>-767580</v>
       </c>
       <c r="D78" t="n">
-        <v>-9702782</v>
+        <v>3508622</v>
       </c>
       <c r="E78" t="n">
-        <v>-886416</v>
+        <v>-244260</v>
       </c>
       <c r="F78" t="n">
-        <v>-8668666</v>
+        <v>3434342</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>智易</t>
         </is>
       </c>
     </row>
@@ -7981,20 +8032,20 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 39 千股)</t>
+          <t>📈 20d 巨變(加碼 356 千股)</t>
         </is>
       </c>
       <c r="C79" t="n">
+        <v>1271979</v>
+      </c>
+      <c r="D79" t="n">
+        <v>6962047</v>
+      </c>
+      <c r="E79" t="n">
         <v>3712099</v>
       </c>
-      <c r="D79" t="n">
+      <c r="F79" t="n">
         <v>6606140</v>
-      </c>
-      <c r="E79" t="n">
-        <v>4841723</v>
-      </c>
-      <c r="F79" t="n">
-        <v>6567084</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -8005,87 +8056,87 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -53 千股)</t>
+          <t>📈 20d 巨變(加碼 2,181 千股)</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>162258</v>
+        <v>-5444650</v>
       </c>
       <c r="D80" t="n">
-        <v>113405</v>
+        <v>-7521457</v>
       </c>
       <c r="E80" t="n">
-        <v>309714</v>
+        <v>-1389207</v>
       </c>
       <c r="F80" t="n">
-        <v>166535</v>
+        <v>-9702782</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>啟碁</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -3,484 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -56 千股)</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-20164935</v>
+        <v>-82231</v>
       </c>
       <c r="D81" t="n">
-        <v>-27141151</v>
+        <v>57541</v>
       </c>
       <c r="E81" t="n">
-        <v>-15093238</v>
+        <v>162258</v>
       </c>
       <c r="F81" t="n">
-        <v>-23657473</v>
+        <v>113405</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>精測</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -142 千股)</t>
+          <t>📈 20d 巨變(加碼 6,104 千股)</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>70693</v>
+        <v>-27474758</v>
       </c>
       <c r="D82" t="n">
-        <v>-4588539</v>
+        <v>-21036834</v>
       </c>
       <c r="E82" t="n">
-        <v>177128</v>
+        <v>-20164935</v>
       </c>
       <c r="F82" t="n">
-        <v>-4446644</v>
+        <v>-27141151</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
@@ -8097,20 +8148,20 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -3,287 千股)</t>
+          <t>📉 20d 巨變(減碼 -7,199 千股)</t>
         </is>
       </c>
       <c r="C83" t="n">
+        <v>-73455454</v>
+      </c>
+      <c r="D83" t="n">
+        <v>-225398231</v>
+      </c>
+      <c r="E83" t="n">
         <v>-56285501</v>
       </c>
-      <c r="D83" t="n">
+      <c r="F83" t="n">
         <v>-218199656</v>
-      </c>
-      <c r="E83" t="n">
-        <v>-68160196</v>
-      </c>
-      <c r="F83" t="n">
-        <v>-214912448</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -8121,29 +8172,29 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 50 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -435 千股)</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>143023</v>
+        <v>-932344</v>
       </c>
       <c r="D84" t="n">
-        <v>359552</v>
+        <v>-5023571</v>
       </c>
       <c r="E84" t="n">
-        <v>132023</v>
+        <v>70693</v>
       </c>
       <c r="F84" t="n">
-        <v>309852</v>
+        <v>-4588539</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
     </row>
@@ -8155,20 +8206,20 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 18 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 48 千股)</t>
         </is>
       </c>
       <c r="C85" t="n">
+        <v>-4466</v>
+      </c>
+      <c r="D85" t="n">
+        <v>-1103558</v>
+      </c>
+      <c r="E85" t="n">
         <v>44534</v>
       </c>
-      <c r="D85" t="n">
+      <c r="F85" t="n">
         <v>-1151558</v>
-      </c>
-      <c r="E85" t="n">
-        <v>204469</v>
-      </c>
-      <c r="F85" t="n">
-        <v>-1169623</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -8179,29 +8230,29 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -438 千股)</t>
+          <t>📈 20d 巨變(加碼 20 千股)</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>332250</v>
+        <v>65443</v>
       </c>
       <c r="D86" t="n">
-        <v>2028334</v>
+        <v>379972</v>
       </c>
       <c r="E86" t="n">
-        <v>452250</v>
+        <v>143023</v>
       </c>
       <c r="F86" t="n">
-        <v>2466334</v>
+        <v>359552</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>東科-KY</t>
         </is>
       </c>
     </row>
@@ -8213,20 +8264,20 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -172 千股)</t>
+          <t>📉 20d 巨變(減碼 -535 千股)</t>
         </is>
       </c>
       <c r="C87" t="n">
+        <v>-3097053</v>
+      </c>
+      <c r="D87" t="n">
+        <v>-4173754</v>
+      </c>
+      <c r="E87" t="n">
         <v>-1923173</v>
       </c>
-      <c r="D87" t="n">
+      <c r="F87" t="n">
         <v>-3638845</v>
-      </c>
-      <c r="E87" t="n">
-        <v>-1951513</v>
-      </c>
-      <c r="F87" t="n">
-        <v>-3466975</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -8242,20 +8293,20 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -162 千股)</t>
+          <t>📉 20d 巨變(減碼 -260 千股)</t>
         </is>
       </c>
       <c r="C88" t="n">
+        <v>1665029</v>
+      </c>
+      <c r="D88" t="n">
+        <v>3404004</v>
+      </c>
+      <c r="E88" t="n">
         <v>2480460</v>
       </c>
-      <c r="D88" t="n">
+      <c r="F88" t="n">
         <v>3664056</v>
-      </c>
-      <c r="E88" t="n">
-        <v>3361930</v>
-      </c>
-      <c r="F88" t="n">
-        <v>3825864</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -8266,58 +8317,58 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,672 千股)</t>
+          <t>📉 20d 巨變(減碼 -58 千股)</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-44288983</v>
+        <v>191000</v>
       </c>
       <c r="D89" t="n">
-        <v>-58248860</v>
+        <v>1970078</v>
       </c>
       <c r="E89" t="n">
-        <v>-48312465</v>
+        <v>332250</v>
       </c>
       <c r="F89" t="n">
-        <v>-59920994</v>
+        <v>2028334</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>全友</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -265 千股)</t>
+          <t>📉 20d 巨變(減碼 -13,268 千股)</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>-301833</v>
+        <v>-44628836</v>
       </c>
       <c r="D90" t="n">
-        <v>-5470960</v>
+        <v>-71516742</v>
       </c>
       <c r="E90" t="n">
-        <v>-372271</v>
+        <v>-44288983</v>
       </c>
       <c r="F90" t="n">
-        <v>-5205700</v>
+        <v>-58248860</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
@@ -8329,20 +8380,20 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -19 千股)</t>
+          <t>📉 20d 巨變(減碼 -72 千股)</t>
         </is>
       </c>
       <c r="C91" t="n">
+        <v>-89217</v>
+      </c>
+      <c r="D91" t="n">
+        <v>-147917</v>
+      </c>
+      <c r="E91" t="n">
         <v>-120426</v>
       </c>
-      <c r="D91" t="n">
+      <c r="F91" t="n">
         <v>-75943</v>
-      </c>
-      <c r="E91" t="n">
-        <v>-54170</v>
-      </c>
-      <c r="F91" t="n">
-        <v>-56939</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -8353,116 +8404,116 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -694 千股)</t>
+          <t>📉 20d 巨變(減碼 -434 千股)</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>4302017</v>
+        <v>-341679</v>
       </c>
       <c r="D92" t="n">
-        <v>7283227</v>
+        <v>-5905203</v>
       </c>
       <c r="E92" t="n">
-        <v>4711281</v>
+        <v>-301833</v>
       </c>
       <c r="F92" t="n">
-        <v>7977016</v>
+        <v>-5470960</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>中保科</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -8 千股)</t>
+          <t>📈 20d 巨變(加碼 476 千股)</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>-59848</v>
+        <v>3986842</v>
       </c>
       <c r="D93" t="n">
-        <v>-427316</v>
+        <v>7759116</v>
       </c>
       <c r="E93" t="n">
-        <v>-93768</v>
+        <v>4302017</v>
       </c>
       <c r="F93" t="n">
-        <v>-419308</v>
+        <v>7283227</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>長榮航太</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 16 千股)</t>
+          <t>📉 20d 巨變(減碼 -11 千股)</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>43000</v>
+        <v>-20838</v>
       </c>
       <c r="D94" t="n">
-        <v>135636</v>
+        <v>-438306</v>
       </c>
       <c r="E94" t="n">
-        <v>29000</v>
+        <v>-59848</v>
       </c>
       <c r="F94" t="n">
-        <v>119655</v>
+        <v>-427316</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>安碁資訊</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -9,549 千股)</t>
+          <t>📈 20d 巨變(加碼 26 千股)</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>-39329925</v>
+        <v>62000</v>
       </c>
       <c r="D95" t="n">
-        <v>-142963374</v>
+        <v>162067</v>
       </c>
       <c r="E95" t="n">
-        <v>-39125116</v>
+        <v>43000</v>
       </c>
       <c r="F95" t="n">
-        <v>-133414697</v>
+        <v>135636</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>六方科-KY</t>
         </is>
       </c>
     </row>
@@ -8474,20 +8525,20 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -56,073 千股)</t>
+          <t>📈 20d 巨變(加碼 54,746 千股)</t>
         </is>
       </c>
       <c r="C96" t="n">
+        <v>-10606966</v>
+      </c>
+      <c r="D96" t="n">
+        <v>-177176220</v>
+      </c>
+      <c r="E96" t="n">
         <v>-39178294</v>
       </c>
-      <c r="D96" t="n">
+      <c r="F96" t="n">
         <v>-231922106</v>
-      </c>
-      <c r="E96" t="n">
-        <v>-34134732</v>
-      </c>
-      <c r="F96" t="n">
-        <v>-175849216</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -8503,20 +8554,20 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 3,508 千股)</t>
+          <t>📈 20d 巨變(加碼 1,421 千股)</t>
         </is>
       </c>
       <c r="C97" t="n">
+        <v>-2763754</v>
+      </c>
+      <c r="D97" t="n">
+        <v>-2863058</v>
+      </c>
+      <c r="E97" t="n">
         <v>-2161646</v>
       </c>
-      <c r="D97" t="n">
+      <c r="F97" t="n">
         <v>-4284304</v>
-      </c>
-      <c r="E97" t="n">
-        <v>-2045510</v>
-      </c>
-      <c r="F97" t="n">
-        <v>-7791846</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -8527,29 +8578,29 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 136 千股)</t>
+          <t>📉 20d 巨變(減碼 -8,824 千股)</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-1969103</v>
+        <v>-35826517</v>
       </c>
       <c r="D98" t="n">
-        <v>-4452044</v>
+        <v>-151787473</v>
       </c>
       <c r="E98" t="n">
-        <v>-1635788</v>
+        <v>-39329925</v>
       </c>
       <c r="F98" t="n">
-        <v>-4588416</v>
+        <v>-142963374</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
@@ -8561,20 +8612,20 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 78 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 466 千股)</t>
         </is>
       </c>
       <c r="C99" t="n">
+        <v>26933</v>
+      </c>
+      <c r="D99" t="n">
+        <v>-4657051</v>
+      </c>
+      <c r="E99" t="n">
         <v>-66651</v>
       </c>
-      <c r="D99" t="n">
+      <c r="F99" t="n">
         <v>-5122664</v>
-      </c>
-      <c r="E99" t="n">
-        <v>-151640</v>
-      </c>
-      <c r="F99" t="n">
-        <v>-5200332</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -8590,20 +8641,20 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 69 千股)</t>
+          <t>📉 20d 巨變(減碼 -47 千股)</t>
         </is>
       </c>
       <c r="C100" t="n">
+        <v>21855</v>
+      </c>
+      <c r="D100" t="n">
+        <v>259786</v>
+      </c>
+      <c r="E100" t="n">
         <v>120833</v>
       </c>
-      <c r="D100" t="n">
+      <c r="F100" t="n">
         <v>306346</v>
-      </c>
-      <c r="E100" t="n">
-        <v>169006</v>
-      </c>
-      <c r="F100" t="n">
-        <v>237120</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -8614,29 +8665,29 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -1,334 千股)</t>
+          <t>📈 20d 巨變(加碼 454 千股)</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-1571108</v>
+        <v>-1212339</v>
       </c>
       <c r="D101" t="n">
-        <v>421817</v>
+        <v>-3998149</v>
       </c>
       <c r="E101" t="n">
-        <v>1050787</v>
+        <v>-1969103</v>
       </c>
       <c r="F101" t="n">
-        <v>1755468</v>
+        <v>-4452044</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>緯穎</t>
         </is>
       </c>
     </row>
@@ -8648,20 +8699,20 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 47 千股)</t>
+          <t>📉 20d 巨變(減碼 -276 千股)</t>
         </is>
       </c>
       <c r="C102" t="n">
+        <v>-38286</v>
+      </c>
+      <c r="D102" t="n">
+        <v>1648677</v>
+      </c>
+      <c r="E102" t="n">
         <v>-232</v>
       </c>
-      <c r="D102" t="n">
+      <c r="F102" t="n">
         <v>1924496</v>
-      </c>
-      <c r="E102" t="n">
-        <v>-19819</v>
-      </c>
-      <c r="F102" t="n">
-        <v>1877650</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -8672,27 +8723,56 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 883 千股)</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>-862126</v>
+      </c>
+      <c r="D103" t="n">
+        <v>1304794</v>
+      </c>
+      <c r="E103" t="n">
+        <v>-1571108</v>
+      </c>
+      <c r="F103" t="n">
+        <v>421817</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
           <t>6187</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 151 千股)</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -324 千股)</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>398811</v>
+      </c>
+      <c r="D104" t="n">
+        <v>-2015499</v>
+      </c>
+      <c r="E104" t="n">
         <v>796165</v>
       </c>
-      <c r="D103" t="n">
+      <c r="F104" t="n">
         <v>-1691030</v>
       </c>
-      <c r="E103" t="n">
-        <v>202678</v>
-      </c>
-      <c r="F103" t="n">
-        <v>-1842254</v>
-      </c>
-      <c r="G103" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t>萬潤</t>
         </is>

--- a/data/台股_外資雷達.xlsx
+++ b/data/台股_外資雷達.xlsx
@@ -496,22 +496,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-23887</v>
+        <v>61628</v>
       </c>
       <c r="D2" t="n">
-        <v>207001</v>
+        <v>265870</v>
       </c>
       <c r="E2" t="n">
-        <v>-94930</v>
+        <v>-26039</v>
       </c>
       <c r="F2" t="n">
-        <v>35548</v>
+        <v>8071</v>
       </c>
       <c r="G2" t="n">
-        <v>26419</v>
+        <v>19699</v>
       </c>
       <c r="H2" t="n">
-        <v>12142</v>
+        <v>4495</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -547,22 +547,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-22577</v>
+        <v>-29116</v>
       </c>
       <c r="D3" t="n">
-        <v>44852</v>
+        <v>45493</v>
       </c>
       <c r="E3" t="n">
-        <v>-3505</v>
+        <v>-8145</v>
       </c>
       <c r="F3" t="n">
-        <v>5874</v>
+        <v>5596</v>
       </c>
       <c r="G3" t="n">
-        <v>-50272</v>
+        <v>-49541</v>
       </c>
       <c r="H3" t="n">
-        <v>3274</v>
+        <v>3266</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>13987</v>
+        <v>10255</v>
       </c>
       <c r="D4" t="n">
-        <v>19225</v>
+        <v>20887</v>
       </c>
       <c r="E4" t="n">
-        <v>142492</v>
+        <v>137281</v>
       </c>
       <c r="F4" t="n">
-        <v>-4345</v>
+        <v>-3256</v>
       </c>
       <c r="G4" t="n">
-        <v>-33437</v>
+        <v>-33297</v>
       </c>
       <c r="H4" t="n">
-        <v>1615</v>
+        <v>2713</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -649,22 +649,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2659</v>
+        <v>-248</v>
       </c>
       <c r="D5" t="n">
-        <v>8409</v>
+        <v>8005</v>
       </c>
       <c r="E5" t="n">
-        <v>12049</v>
+        <v>12015</v>
       </c>
       <c r="F5" t="n">
-        <v>-7375</v>
+        <v>-4366</v>
       </c>
       <c r="G5" t="n">
-        <v>-9552</v>
+        <v>-9691</v>
       </c>
       <c r="H5" t="n">
-        <v>470</v>
+        <v>483</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -700,22 +700,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3987</v>
+        <v>2172</v>
       </c>
       <c r="D6" t="n">
-        <v>7759</v>
+        <v>7175</v>
       </c>
       <c r="E6" t="n">
-        <v>12063</v>
+        <v>10879</v>
       </c>
       <c r="F6" t="n">
-        <v>-46</v>
+        <v>-5</v>
       </c>
       <c r="G6" t="n">
-        <v>-560</v>
+        <v>-559</v>
       </c>
       <c r="H6" t="n">
-        <v>389</v>
+        <v>624</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -742,31 +742,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1272</v>
+        <v>1235</v>
       </c>
       <c r="D7" t="n">
-        <v>6962</v>
+        <v>6020</v>
       </c>
       <c r="E7" t="n">
-        <v>9456</v>
+        <v>10569</v>
       </c>
       <c r="F7" t="n">
-        <v>3392</v>
+        <v>-1233</v>
       </c>
       <c r="G7" t="n">
-        <v>4721</v>
+        <v>-5196</v>
       </c>
       <c r="H7" t="n">
-        <v>426</v>
+        <v>249</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -775,11 +775,11 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -787,37 +787,37 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>原相</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-183</v>
+        <v>-1275</v>
       </c>
       <c r="D8" t="n">
-        <v>5164</v>
+        <v>5790</v>
       </c>
       <c r="E8" t="n">
-        <v>9218</v>
+        <v>8915</v>
       </c>
       <c r="F8" t="n">
-        <v>-827</v>
+        <v>2500</v>
       </c>
       <c r="G8" t="n">
-        <v>-5225</v>
+        <v>4790</v>
       </c>
       <c r="H8" t="n">
-        <v>254</v>
+        <v>314</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -826,11 +826,11 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -838,37 +838,37 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-434</v>
+        <v>392</v>
       </c>
       <c r="D9" t="n">
-        <v>4820</v>
+        <v>4088</v>
       </c>
       <c r="E9" t="n">
-        <v>16228</v>
+        <v>2421</v>
       </c>
       <c r="F9" t="n">
-        <v>401</v>
+        <v>-598</v>
       </c>
       <c r="G9" t="n">
-        <v>1141</v>
+        <v>-3323</v>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>178</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -881,45 +881,45 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>🚀 加速器*</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1406</v>
+        <v>-790</v>
       </c>
       <c r="D10" t="n">
-        <v>3763</v>
+        <v>3594</v>
       </c>
       <c r="E10" t="n">
-        <v>2998</v>
+        <v>16125</v>
       </c>
       <c r="F10" t="n">
-        <v>50</v>
+        <v>357</v>
       </c>
       <c r="G10" t="n">
-        <v>135</v>
+        <v>1189</v>
       </c>
       <c r="H10" t="n">
-        <v>44</v>
+        <v>-3</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -932,45 +932,45 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器*</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>漢科</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>477</v>
+        <v>781</v>
       </c>
       <c r="D11" t="n">
-        <v>3683</v>
+        <v>3443</v>
       </c>
       <c r="E11" t="n">
-        <v>2103</v>
+        <v>2665</v>
       </c>
       <c r="F11" t="n">
-        <v>-1039</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
-        <v>-3388</v>
+        <v>135</v>
       </c>
       <c r="H11" t="n">
-        <v>123</v>
+        <v>28</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-768</v>
+        <v>1092</v>
       </c>
       <c r="D12" t="n">
-        <v>3509</v>
+        <v>3383</v>
       </c>
       <c r="E12" t="n">
-        <v>5594</v>
+        <v>17393</v>
       </c>
       <c r="F12" t="n">
-        <v>887</v>
+        <v>214</v>
       </c>
       <c r="G12" t="n">
-        <v>5541</v>
+        <v>288</v>
       </c>
       <c r="H12" t="n">
-        <v>-53</v>
+        <v>203</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1030,11 +1030,11 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1048,31 +1048,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>智易</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1665</v>
+        <v>-83</v>
       </c>
       <c r="D13" t="n">
-        <v>3404</v>
+        <v>3344</v>
       </c>
       <c r="E13" t="n">
-        <v>17478</v>
+        <v>6054</v>
       </c>
       <c r="F13" t="n">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="G13" t="n">
-        <v>303</v>
+        <v>5549</v>
       </c>
       <c r="H13" t="n">
-        <v>36</v>
+        <v>-49</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1081,11 +1081,11 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1108,22 +1108,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2149</v>
+        <v>1819</v>
       </c>
       <c r="D14" t="n">
-        <v>2940</v>
+        <v>2608</v>
       </c>
       <c r="E14" t="n">
-        <v>2032</v>
+        <v>2365</v>
       </c>
       <c r="F14" t="n">
-        <v>-206</v>
+        <v>-6</v>
       </c>
       <c r="G14" t="n">
-        <v>-143</v>
+        <v>-140</v>
       </c>
       <c r="H14" t="n">
-        <v>-730</v>
+        <v>-752</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1150,86 +1150,86 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>191</v>
+        <v>355</v>
       </c>
       <c r="D15" t="n">
-        <v>1970</v>
+        <v>2308</v>
       </c>
       <c r="E15" t="n">
-        <v>8003</v>
+        <v>3270</v>
       </c>
       <c r="F15" t="n">
-        <v>-1</v>
+        <v>-890</v>
       </c>
       <c r="G15" t="n">
-        <v>-5</v>
+        <v>-399</v>
       </c>
       <c r="H15" t="n">
-        <v>-36</v>
+        <v>14</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>🟡 中性</t>
+          <t>🟢 加碼</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>271</v>
+        <v>-324</v>
       </c>
       <c r="D16" t="n">
-        <v>1925</v>
+        <v>2138</v>
       </c>
       <c r="E16" t="n">
-        <v>3072</v>
+        <v>-7415</v>
       </c>
       <c r="F16" t="n">
-        <v>-927</v>
+        <v>1897</v>
       </c>
       <c r="G16" t="n">
-        <v>50</v>
+        <v>262</v>
       </c>
       <c r="H16" t="n">
-        <v>-102</v>
+        <v>173</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>🟡 中性</t>
+          <t>🟢 加碼</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -1261,26 +1261,26 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>170</v>
+        <v>94</v>
       </c>
       <c r="D17" t="n">
-        <v>1804</v>
+        <v>2121</v>
       </c>
       <c r="E17" t="n">
-        <v>-1370</v>
+        <v>-1460</v>
       </c>
       <c r="F17" t="n">
-        <v>-414</v>
+        <v>-242</v>
       </c>
       <c r="G17" t="n">
-        <v>-855</v>
+        <v>-1143</v>
       </c>
       <c r="H17" t="n">
-        <v>-13</v>
+        <v>47</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>🟡 中性</t>
+          <t>🟢 加碼</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1303,121 +1303,121 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>合機</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>595</v>
+        <v>-810</v>
       </c>
       <c r="D18" t="n">
-        <v>1663</v>
+        <v>1948</v>
       </c>
       <c r="E18" t="n">
-        <v>2951</v>
+        <v>5882</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>348</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-7056</v>
       </c>
       <c r="H18" t="n">
-        <v>152</v>
+        <v>-179</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>84</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>🛬 穩定</t>
-        </is>
-      </c>
-      <c r="M18" t="n">
-        <v>-2</v>
-      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-38</v>
+        <v>-745</v>
       </c>
       <c r="D19" t="n">
-        <v>1649</v>
+        <v>1902</v>
       </c>
       <c r="E19" t="n">
-        <v>-2352</v>
+        <v>-1479</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>-85</v>
       </c>
       <c r="G19" t="n">
-        <v>-5746</v>
+        <v>-155</v>
       </c>
       <c r="H19" t="n">
-        <v>-87</v>
+        <v>-4</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>91</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>✈️ 高飛</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-862</v>
+        <v>239</v>
       </c>
       <c r="D20" t="n">
-        <v>1305</v>
+        <v>1108</v>
       </c>
       <c r="E20" t="n">
-        <v>6015</v>
+        <v>-3926</v>
       </c>
       <c r="F20" t="n">
-        <v>373</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>-4936</v>
+        <v>-5746</v>
       </c>
       <c r="H20" t="n">
-        <v>-223</v>
+        <v>-108</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1432,31 +1432,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>440</v>
+        <v>476</v>
       </c>
       <c r="D21" t="n">
-        <v>1263</v>
+        <v>1079</v>
       </c>
       <c r="E21" t="n">
-        <v>-7180</v>
+        <v>1854</v>
       </c>
       <c r="F21" t="n">
-        <v>2215</v>
+        <v>21</v>
       </c>
       <c r="G21" t="n">
-        <v>8</v>
+        <v>376</v>
       </c>
       <c r="H21" t="n">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1465,49 +1465,49 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>勝一</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-444</v>
+        <v>606</v>
       </c>
       <c r="D22" t="n">
-        <v>1206</v>
+        <v>1055</v>
       </c>
       <c r="E22" t="n">
-        <v>4165</v>
+        <v>1582</v>
       </c>
       <c r="F22" t="n">
-        <v>209</v>
+        <v>4</v>
       </c>
       <c r="G22" t="n">
-        <v>1430</v>
+        <v>6</v>
       </c>
       <c r="H22" t="n">
-        <v>-91</v>
+        <v>36</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1516,49 +1516,49 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>合機</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-420</v>
+        <v>204</v>
       </c>
       <c r="D23" t="n">
-        <v>1198</v>
+        <v>1042</v>
       </c>
       <c r="E23" t="n">
-        <v>-2118</v>
+        <v>2858</v>
       </c>
       <c r="F23" t="n">
-        <v>-168</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-47</v>
+        <v>-35</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1571,45 +1571,45 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>687</v>
+        <v>-571</v>
       </c>
       <c r="D24" t="n">
-        <v>1144</v>
+        <v>1019</v>
       </c>
       <c r="E24" t="n">
-        <v>1806</v>
+        <v>3455</v>
       </c>
       <c r="F24" t="n">
-        <v>-3</v>
+        <v>-50</v>
       </c>
       <c r="G24" t="n">
-        <v>351</v>
+        <v>1445</v>
       </c>
       <c r="H24" t="n">
-        <v>5</v>
+        <v>-69</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1618,49 +1618,49 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>勝一</t>
+          <t>達欣工</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>730</v>
+        <v>-191</v>
       </c>
       <c r="D25" t="n">
-        <v>1078</v>
+        <v>989</v>
       </c>
       <c r="E25" t="n">
-        <v>1723</v>
+        <v>123</v>
       </c>
       <c r="F25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G25" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>4</v>
+        <v>-93</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1673,96 +1673,96 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>全友</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-300</v>
+        <v>-903</v>
       </c>
       <c r="D26" t="n">
-        <v>1024</v>
+        <v>772</v>
       </c>
       <c r="E26" t="n">
-        <v>-177</v>
+        <v>6553</v>
       </c>
       <c r="F26" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="G26" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>75</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
         <v>1</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-112</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K26" t="n">
-        <v>79</v>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>🛬 穩定</t>
-        </is>
-      </c>
-      <c r="M26" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>德昌</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-69</v>
+        <v>-491</v>
       </c>
       <c r="D27" t="n">
-        <v>778</v>
+        <v>724</v>
       </c>
       <c r="E27" t="n">
-        <v>666</v>
+        <v>-7407</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>-1544</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-5920</v>
       </c>
       <c r="H27" t="n">
-        <v>-19</v>
+        <v>-351</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1775,45 +1775,45 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>德昌</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-765</v>
+        <v>-195</v>
       </c>
       <c r="D28" t="n">
-        <v>760</v>
+        <v>697</v>
       </c>
       <c r="E28" t="n">
-        <v>-6434</v>
+        <v>590</v>
       </c>
       <c r="F28" t="n">
-        <v>-2095</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>-5856</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1826,45 +1826,45 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-293</v>
+        <v>-1163</v>
       </c>
       <c r="D29" t="n">
-        <v>612</v>
+        <v>601</v>
       </c>
       <c r="E29" t="n">
-        <v>-1232</v>
+        <v>4806</v>
       </c>
       <c r="F29" t="n">
-        <v>257</v>
+        <v>585</v>
       </c>
       <c r="G29" t="n">
-        <v>242</v>
+        <v>-117</v>
       </c>
       <c r="H29" t="n">
-        <v>13</v>
+        <v>135</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1877,45 +1877,45 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>🐌 龜速*</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-1442</v>
+        <v>-59</v>
       </c>
       <c r="D30" t="n">
-        <v>564</v>
+        <v>526</v>
       </c>
       <c r="E30" t="n">
-        <v>4729</v>
+        <v>-1140</v>
       </c>
       <c r="F30" t="n">
-        <v>299</v>
+        <v>1055</v>
       </c>
       <c r="G30" t="n">
-        <v>-138</v>
+        <v>2137</v>
       </c>
       <c r="H30" t="n">
-        <v>110</v>
+        <v>29</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1924,49 +1924,49 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M30" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-4191</v>
+        <v>658</v>
       </c>
       <c r="D31" t="n">
-        <v>554</v>
+        <v>480</v>
       </c>
       <c r="E31" t="n">
-        <v>-7188</v>
+        <v>727</v>
       </c>
       <c r="F31" t="n">
-        <v>2668</v>
+        <v>-15</v>
       </c>
       <c r="G31" t="n">
-        <v>4884</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-1153</v>
+        <v>209</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1975,100 +1975,100 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>5</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>崇友</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2014</v>
+        <v>47</v>
       </c>
       <c r="D32" t="n">
-        <v>533</v>
+        <v>344</v>
       </c>
       <c r="E32" t="n">
-        <v>761</v>
+        <v>551</v>
       </c>
       <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>91</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
         <v>-1</v>
-      </c>
-      <c r="G32" t="n">
-        <v>-6</v>
-      </c>
-      <c r="H32" t="n">
-        <v>213</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="K32" t="n">
-        <v>32</v>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>📉 減速</t>
-        </is>
-      </c>
-      <c r="M32" t="n">
-        <v>-3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>智冠</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-273</v>
+        <v>-74</v>
       </c>
       <c r="D33" t="n">
-        <v>527</v>
+        <v>341</v>
       </c>
       <c r="E33" t="n">
-        <v>-1595</v>
+        <v>401</v>
       </c>
       <c r="F33" t="n">
-        <v>1342</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>2123</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-5</v>
+        <v>-152</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2077,49 +2077,49 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M33" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-306</v>
+        <v>-39</v>
       </c>
       <c r="D34" t="n">
-        <v>419</v>
+        <v>307</v>
       </c>
       <c r="E34" t="n">
-        <v>-7041</v>
+        <v>-120</v>
       </c>
       <c r="F34" t="n">
-        <v>-177</v>
+        <v>-416</v>
       </c>
       <c r="G34" t="n">
-        <v>-3707</v>
+        <v>-1407</v>
       </c>
       <c r="H34" t="n">
-        <v>-1</v>
+        <v>-92</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2128,49 +2128,49 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M34" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>65</v>
+        <v>-99</v>
       </c>
       <c r="D35" t="n">
-        <v>380</v>
+        <v>300</v>
       </c>
       <c r="E35" t="n">
-        <v>-254</v>
+        <v>-1223</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>244</v>
       </c>
       <c r="H35" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2179,40 +2179,40 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速*</t>
         </is>
       </c>
       <c r="M35" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>智冠</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>-55</v>
+        <v>-9</v>
       </c>
       <c r="D36" t="n">
-        <v>373</v>
+        <v>285</v>
       </c>
       <c r="E36" t="n">
-        <v>397</v>
+        <v>-153</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -2221,7 +2221,7 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-159</v>
+        <v>-9</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2230,100 +2230,88 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M36" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>47</v>
+        <v>-18</v>
       </c>
       <c r="D37" t="n">
-        <v>369</v>
+        <v>269</v>
       </c>
       <c r="E37" t="n">
-        <v>554</v>
+        <v>614</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>-129</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K37" t="n">
-        <v>91</v>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>🐌 龜速</t>
-        </is>
-      </c>
-      <c r="M37" t="n">
-        <v>-1</v>
-      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>寶雅</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-610</v>
+        <v>-145</v>
       </c>
       <c r="D38" t="n">
-        <v>356</v>
+        <v>225</v>
       </c>
       <c r="E38" t="n">
-        <v>1821</v>
+        <v>-694</v>
       </c>
       <c r="F38" t="n">
-        <v>-80</v>
+        <v>160</v>
       </c>
       <c r="G38" t="n">
-        <v>116</v>
+        <v>-47</v>
       </c>
       <c r="H38" t="n">
-        <v>211</v>
+        <v>-17</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2336,45 +2324,45 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M38" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-691</v>
+        <v>1376</v>
       </c>
       <c r="D39" t="n">
-        <v>282</v>
+        <v>213</v>
       </c>
       <c r="E39" t="n">
-        <v>4864</v>
+        <v>-7764</v>
       </c>
       <c r="F39" t="n">
-        <v>566</v>
+        <v>-1</v>
       </c>
       <c r="G39" t="n">
-        <v>-57</v>
+        <v>-10</v>
       </c>
       <c r="H39" t="n">
-        <v>76</v>
+        <v>-133</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2383,88 +2371,100 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M39" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>22</v>
+        <v>-152</v>
       </c>
       <c r="D40" t="n">
-        <v>260</v>
+        <v>167</v>
       </c>
       <c r="E40" t="n">
-        <v>734</v>
+        <v>-5078</v>
       </c>
       <c r="F40" t="n">
-        <v>-110</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>-264</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-6</v>
+        <v>-26</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>93</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>🚀 加速器</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>六方科-KY</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-235</v>
+        <v>39</v>
       </c>
       <c r="D41" t="n">
-        <v>245</v>
+        <v>157</v>
       </c>
       <c r="E41" t="n">
-        <v>-884</v>
+        <v>-11</v>
       </c>
       <c r="F41" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>-81</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-42</v>
+        <v>6</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2473,49 +2473,49 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M41" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>寶雅</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>62</v>
+        <v>-491</v>
       </c>
       <c r="D42" t="n">
-        <v>162</v>
+        <v>22</v>
       </c>
       <c r="E42" t="n">
-        <v>6</v>
+        <v>1703</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>-123</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H42" t="n">
-        <v>5</v>
+        <v>153</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2524,49 +2524,49 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M42" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>方土霖</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-82</v>
+        <v>-6</v>
       </c>
       <c r="D43" t="n">
-        <v>58</v>
+        <v>-14</v>
       </c>
       <c r="E43" t="n">
-        <v>-166</v>
+        <v>-65</v>
       </c>
       <c r="F43" t="n">
-        <v>-359</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>-1289</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>-100</v>
+        <v>-2</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2575,11 +2575,11 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2587,37 +2587,37 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-461</v>
+        <v>-1506</v>
       </c>
       <c r="D44" t="n">
-        <v>30</v>
+        <v>-30</v>
       </c>
       <c r="E44" t="n">
-        <v>-779</v>
+        <v>-3944</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>605</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>4507</v>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>-1640</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2638,28 +2638,28 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>方土霖</t>
+          <t>信立</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-6</v>
+        <v>-461</v>
       </c>
       <c r="D45" t="n">
-        <v>-14</v>
+        <v>-32</v>
       </c>
       <c r="E45" t="n">
-        <v>-70</v>
+        <v>-830</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -2668,7 +2668,7 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2677,40 +2677,40 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M45" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-380</v>
+        <v>-40</v>
       </c>
       <c r="D46" t="n">
-        <v>-30</v>
+        <v>-87</v>
       </c>
       <c r="E46" t="n">
-        <v>-4958</v>
+        <v>-232</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -2719,7 +2719,7 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>-19</v>
+        <v>8</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2728,40 +2728,40 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>大車隊</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-1492</v>
+        <v>-14</v>
       </c>
       <c r="D47" t="n">
-        <v>-75</v>
+        <v>-139</v>
       </c>
       <c r="E47" t="n">
-        <v>-1148</v>
+        <v>-272</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -2770,7 +2770,7 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>355</v>
+        <v>-1</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2783,36 +2783,36 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M47" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>大車隊</t>
+          <t>聯合</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-36</v>
+        <v>-117</v>
       </c>
       <c r="D48" t="n">
-        <v>-142</v>
+        <v>-203</v>
       </c>
       <c r="E48" t="n">
-        <v>-268</v>
+        <v>-3410</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -2821,7 +2821,7 @@
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-1</v>
+        <v>97</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2834,45 +2834,45 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M48" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-89</v>
+        <v>-2046</v>
       </c>
       <c r="D49" t="n">
-        <v>-148</v>
+        <v>-213</v>
       </c>
       <c r="E49" t="n">
-        <v>-277</v>
+        <v>3401</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>598</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H49" t="n">
-        <v>18</v>
+        <v>255</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2881,40 +2881,40 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M49" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>聯合</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-84</v>
+        <v>60</v>
       </c>
       <c r="D50" t="n">
-        <v>-183</v>
+        <v>-287</v>
       </c>
       <c r="E50" t="n">
-        <v>-3445</v>
+        <v>2158</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -2923,7 +2923,7 @@
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>97</v>
+        <v>49</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2932,11 +2932,11 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -2944,37 +2944,37 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>501</v>
+        <v>-287</v>
       </c>
       <c r="D51" t="n">
-        <v>-185</v>
+        <v>-399</v>
       </c>
       <c r="E51" t="n">
-        <v>-709</v>
+        <v>-93</v>
       </c>
       <c r="F51" t="n">
-        <v>-2</v>
+        <v>180</v>
       </c>
       <c r="G51" t="n">
-        <v>20</v>
+        <v>255</v>
       </c>
       <c r="H51" t="n">
-        <v>-473</v>
+        <v>-43</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -2987,45 +2987,45 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M51" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>友輝</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1920</v>
+        <v>15</v>
       </c>
       <c r="D52" t="n">
-        <v>-324</v>
+        <v>-470</v>
       </c>
       <c r="E52" t="n">
-        <v>-7250</v>
+        <v>500</v>
       </c>
       <c r="F52" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>-10</v>
+        <v>6</v>
       </c>
       <c r="H52" t="n">
-        <v>-198</v>
+        <v>-26</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3038,36 +3038,36 @@
         </is>
       </c>
       <c r="K52" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M52" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-431</v>
+        <v>12</v>
       </c>
       <c r="D53" t="n">
-        <v>-363</v>
+        <v>-472</v>
       </c>
       <c r="E53" t="n">
-        <v>2020</v>
+        <v>-254</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -3076,7 +3076,7 @@
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3089,11 +3089,11 @@
         </is>
       </c>
       <c r="K53" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M53" t="n">
@@ -3103,31 +3103,31 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>大統益</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-317</v>
+        <v>137</v>
       </c>
       <c r="D54" t="n">
-        <v>-435</v>
+        <v>-602</v>
       </c>
       <c r="E54" t="n">
-        <v>-70</v>
+        <v>-853</v>
       </c>
       <c r="F54" t="n">
-        <v>200</v>
+        <v>-1</v>
       </c>
       <c r="G54" t="n">
-        <v>285</v>
+        <v>-2</v>
       </c>
       <c r="H54" t="n">
-        <v>-45</v>
+        <v>34</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3140,36 +3140,36 @@
         </is>
       </c>
       <c r="K54" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M54" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>億泰</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>-21</v>
+        <v>-644</v>
       </c>
       <c r="D55" t="n">
-        <v>-438</v>
+        <v>-746</v>
       </c>
       <c r="E55" t="n">
-        <v>-261</v>
+        <v>-2491</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -3178,7 +3178,7 @@
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>34</v>
+        <v>198</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3191,45 +3191,45 @@
         </is>
       </c>
       <c r="K55" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M55" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>64</v>
+        <v>-136</v>
       </c>
       <c r="D56" t="n">
-        <v>-446</v>
+        <v>-753</v>
       </c>
       <c r="E56" t="n">
-        <v>971</v>
+        <v>-1927</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-33</v>
+        <v>12</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -3250,139 +3250,127 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>億泰</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>-571</v>
+        <v>454</v>
       </c>
       <c r="D57" t="n">
-        <v>-568</v>
+        <v>-768</v>
       </c>
       <c r="E57" t="n">
-        <v>-2436</v>
+        <v>-5143</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>-535</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>-1502</v>
       </c>
       <c r="H57" t="n">
-        <v>199</v>
+        <v>34</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K57" t="n">
-        <v>78</v>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>🛬 穩定</t>
-        </is>
-      </c>
-      <c r="M57" t="n">
-        <v>-2</v>
-      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>125</v>
+        <v>-1828</v>
       </c>
       <c r="D58" t="n">
-        <v>-590</v>
+        <v>-838</v>
       </c>
       <c r="E58" t="n">
-        <v>-844</v>
+        <v>-1467</v>
       </c>
       <c r="F58" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>343</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>94</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>📉 減速</t>
+        </is>
+      </c>
+      <c r="M58" t="n">
         <v>-2</v>
-      </c>
-      <c r="H58" t="n">
-        <v>32</v>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K58" t="n">
-        <v>86</v>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>📉 減速</t>
-        </is>
-      </c>
-      <c r="M58" t="n">
-        <v>-3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>99</v>
+        <v>-260</v>
       </c>
       <c r="D59" t="n">
-        <v>-626</v>
+        <v>-846</v>
       </c>
       <c r="E59" t="n">
-        <v>-1748</v>
+        <v>-783</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>412</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>1423</v>
       </c>
       <c r="H59" t="n">
-        <v>12</v>
+        <v>-37</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3391,19 +3379,19 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K59" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M59" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
@@ -3418,22 +3406,22 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>132</v>
+        <v>40</v>
       </c>
       <c r="D60" t="n">
-        <v>-838</v>
+        <v>-939</v>
       </c>
       <c r="E60" t="n">
-        <v>-602</v>
+        <v>-389</v>
       </c>
       <c r="F60" t="n">
-        <v>167</v>
+        <v>266</v>
       </c>
       <c r="G60" t="n">
-        <v>-780</v>
+        <v>-962</v>
       </c>
       <c r="H60" t="n">
-        <v>-114</v>
+        <v>-89</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3460,31 +3448,31 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-1609</v>
+        <v>336</v>
       </c>
       <c r="D61" t="n">
-        <v>-1068</v>
+        <v>-996</v>
       </c>
       <c r="E61" t="n">
-        <v>-2181</v>
+        <v>-2861</v>
       </c>
       <c r="F61" t="n">
-        <v>740</v>
+        <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>5419</v>
+        <v>469</v>
       </c>
       <c r="H61" t="n">
-        <v>-1827</v>
+        <v>-685</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3493,49 +3481,49 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K61" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>鑫龍騰</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>451</v>
+        <v>-59</v>
       </c>
       <c r="D62" t="n">
-        <v>-1104</v>
+        <v>-1109</v>
       </c>
       <c r="E62" t="n">
-        <v>800</v>
+        <v>-2999</v>
       </c>
       <c r="F62" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>837</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>38</v>
+        <v>-0</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3544,49 +3532,49 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K62" t="n">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>鑫龍騰</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>-1104</v>
+        <v>-1149</v>
       </c>
       <c r="E63" t="n">
-        <v>-2811</v>
+        <v>544</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>815</v>
       </c>
       <c r="H63" t="n">
-        <v>-0</v>
+        <v>-54</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3595,49 +3583,49 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K63" t="n">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="D64" t="n">
-        <v>-1110</v>
+        <v>-1160</v>
       </c>
       <c r="E64" t="n">
-        <v>-6926</v>
+        <v>318</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G64" t="n">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="H64" t="n">
-        <v>-595</v>
+        <v>-199</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3646,49 +3634,49 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K64" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M64" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>105</v>
+        <v>-156</v>
       </c>
       <c r="D65" t="n">
-        <v>-1158</v>
+        <v>-1283</v>
       </c>
       <c r="E65" t="n">
-        <v>-427</v>
+        <v>-3877</v>
       </c>
       <c r="F65" t="n">
-        <v>280</v>
+        <v>5</v>
       </c>
       <c r="G65" t="n">
-        <v>1425</v>
+        <v>-116</v>
       </c>
       <c r="H65" t="n">
-        <v>-9</v>
+        <v>-143</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3701,45 +3689,45 @@
         </is>
       </c>
       <c r="K65" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M65" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>湧德</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>4</v>
+        <v>505</v>
       </c>
       <c r="D66" t="n">
-        <v>-1176</v>
+        <v>-1298</v>
       </c>
       <c r="E66" t="n">
-        <v>-3938</v>
+        <v>-3847</v>
       </c>
       <c r="F66" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>-117</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-111</v>
+        <v>-11</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3752,45 +3740,45 @@
         </is>
       </c>
       <c r="K66" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M66" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-3889</v>
+        <v>-3897</v>
       </c>
       <c r="D67" t="n">
-        <v>-1308</v>
+        <v>-1540</v>
       </c>
       <c r="E67" t="n">
-        <v>-1749</v>
+        <v>-8145</v>
       </c>
       <c r="F67" t="n">
-        <v>3758</v>
+        <v>2460</v>
       </c>
       <c r="G67" t="n">
-        <v>4693</v>
+        <v>5005</v>
       </c>
       <c r="H67" t="n">
-        <v>-42</v>
+        <v>-1145</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3803,45 +3791,45 @@
         </is>
       </c>
       <c r="K67" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M67" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-721</v>
+        <v>-284</v>
       </c>
       <c r="D68" t="n">
-        <v>-1842</v>
+        <v>-1663</v>
       </c>
       <c r="E68" t="n">
-        <v>2468</v>
+        <v>-6346</v>
       </c>
       <c r="F68" t="n">
-        <v>19</v>
+        <v>-177</v>
       </c>
       <c r="G68" t="n">
-        <v>-1363</v>
+        <v>-1897</v>
       </c>
       <c r="H68" t="n">
-        <v>-433</v>
+        <v>-7</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3850,11 +3838,11 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K68" t="n">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -3862,89 +3850,101 @@
         </is>
       </c>
       <c r="M68" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>399</v>
+        <v>-4327</v>
       </c>
       <c r="D69" t="n">
-        <v>-2015</v>
+        <v>-1783</v>
       </c>
       <c r="E69" t="n">
-        <v>-4289</v>
+        <v>-6220</v>
       </c>
       <c r="F69" t="n">
-        <v>-941</v>
+        <v>-169</v>
       </c>
       <c r="G69" t="n">
-        <v>-751</v>
+        <v>-10577</v>
       </c>
       <c r="H69" t="n">
-        <v>53</v>
+        <v>-237</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>44</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>📉 減速</t>
+        </is>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-473</v>
+        <v>601</v>
       </c>
       <c r="D70" t="n">
-        <v>-2123</v>
+        <v>-1789</v>
       </c>
       <c r="E70" t="n">
-        <v>292</v>
+        <v>-424</v>
       </c>
       <c r="F70" t="n">
-        <v>-777</v>
+        <v>121</v>
       </c>
       <c r="G70" t="n">
-        <v>386</v>
+        <v>29</v>
       </c>
       <c r="H70" t="n">
-        <v>277</v>
+        <v>-145</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🟡 中性</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K70" t="n">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -3952,41 +3952,41 @@
         </is>
       </c>
       <c r="M70" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-268</v>
+        <v>-3018</v>
       </c>
       <c r="D71" t="n">
-        <v>-2367</v>
+        <v>-1805</v>
       </c>
       <c r="E71" t="n">
-        <v>-9052</v>
+        <v>-1893</v>
       </c>
       <c r="F71" t="n">
-        <v>-962</v>
+        <v>3029</v>
       </c>
       <c r="G71" t="n">
-        <v>-2138</v>
+        <v>4711</v>
       </c>
       <c r="H71" t="n">
-        <v>-67</v>
+        <v>-35</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🟡 中性</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -3995,147 +3995,147 @@
         </is>
       </c>
       <c r="K71" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M71" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-2764</v>
+        <v>-2</v>
       </c>
       <c r="D72" t="n">
-        <v>-2863</v>
+        <v>-1828</v>
       </c>
       <c r="E72" t="n">
-        <v>-4323</v>
+        <v>-7453</v>
       </c>
       <c r="F72" t="n">
-        <v>-914</v>
+        <v>10</v>
       </c>
       <c r="G72" t="n">
-        <v>-10749</v>
+        <v>88</v>
       </c>
       <c r="H72" t="n">
-        <v>-149</v>
+        <v>-298</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🟡 中性</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K72" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-1239</v>
+        <v>-193</v>
       </c>
       <c r="D73" t="n">
-        <v>-2896</v>
+        <v>-2058</v>
       </c>
       <c r="E73" t="n">
-        <v>-1215</v>
+        <v>-9858</v>
       </c>
       <c r="F73" t="n">
-        <v>102</v>
+        <v>-984</v>
       </c>
       <c r="G73" t="n">
-        <v>-223</v>
+        <v>-2546</v>
       </c>
       <c r="H73" t="n">
+        <v>-35</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>🟠 減碼</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
         <v>90</v>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>🟠 減碼</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K73" t="n">
-        <v>64</v>
-      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M73" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>玉晶光</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>0</v>
+        <v>-771</v>
       </c>
       <c r="D74" t="n">
-        <v>-3112</v>
+        <v>-2876</v>
       </c>
       <c r="E74" t="n">
-        <v>-4336</v>
+        <v>1966</v>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="G74" t="n">
-        <v>1187</v>
+        <v>-1257</v>
       </c>
       <c r="H74" t="n">
-        <v>-797</v>
+        <v>-436</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -4144,49 +4144,49 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K74" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M74" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1603</v>
+        <v>-1704</v>
       </c>
       <c r="D75" t="n">
-        <v>-3355</v>
+        <v>-3205</v>
       </c>
       <c r="E75" t="n">
-        <v>-3127</v>
+        <v>-1836</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>-187</v>
       </c>
       <c r="H75" t="n">
-        <v>-260</v>
+        <v>162</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -4195,49 +4195,49 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K75" t="n">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M75" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1425</v>
+        <v>-447</v>
       </c>
       <c r="D76" t="n">
-        <v>-3508</v>
+        <v>-3246</v>
       </c>
       <c r="E76" t="n">
-        <v>-500</v>
+        <v>-69</v>
       </c>
       <c r="F76" t="n">
-        <v>121</v>
+        <v>-592</v>
       </c>
       <c r="G76" t="n">
-        <v>28</v>
+        <v>225</v>
       </c>
       <c r="H76" t="n">
-        <v>-262</v>
+        <v>378</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -4246,11 +4246,11 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K76" t="n">
-        <v>90</v>
+        <v>51</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -4258,28 +4258,28 @@
         </is>
       </c>
       <c r="M76" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-646</v>
+        <v>-1347</v>
       </c>
       <c r="D77" t="n">
-        <v>-3605</v>
+        <v>-3673</v>
       </c>
       <c r="E77" t="n">
-        <v>-6293</v>
+        <v>-2553</v>
       </c>
       <c r="F77" t="n">
         <v>0</v>
@@ -4288,7 +4288,7 @@
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>1182</v>
+        <v>-924</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -4297,49 +4297,49 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K77" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M77" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>鈊象</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-1338</v>
+        <v>-352</v>
       </c>
       <c r="D78" t="n">
-        <v>-3746</v>
+        <v>-3674</v>
       </c>
       <c r="E78" t="n">
-        <v>-13546</v>
+        <v>-12933</v>
       </c>
       <c r="F78" t="n">
-        <v>413</v>
+        <v>817</v>
       </c>
       <c r="G78" t="n">
-        <v>403</v>
+        <v>7784</v>
       </c>
       <c r="H78" t="n">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -4352,15 +4352,15 @@
         </is>
       </c>
       <c r="K78" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M78" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="79">
@@ -4375,22 +4375,22 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-1212</v>
+        <v>-1282</v>
       </c>
       <c r="D79" t="n">
-        <v>-3998</v>
+        <v>-4061</v>
       </c>
       <c r="E79" t="n">
-        <v>-8885</v>
+        <v>-8590</v>
       </c>
       <c r="F79" t="n">
-        <v>2183</v>
+        <v>1969</v>
       </c>
       <c r="G79" t="n">
-        <v>1347</v>
+        <v>1674</v>
       </c>
       <c r="H79" t="n">
-        <v>-164</v>
+        <v>-62</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -4417,31 +4417,31 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>-3097</v>
+        <v>-1240</v>
       </c>
       <c r="D80" t="n">
-        <v>-4174</v>
+        <v>-4196</v>
       </c>
       <c r="E80" t="n">
-        <v>-1065</v>
+        <v>-13796</v>
       </c>
       <c r="F80" t="n">
-        <v>1</v>
+        <v>468</v>
       </c>
       <c r="G80" t="n">
-        <v>1</v>
+        <v>504</v>
       </c>
       <c r="H80" t="n">
-        <v>-750</v>
+        <v>27</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -4450,49 +4450,49 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K80" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M80" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-1645</v>
+        <v>-339</v>
       </c>
       <c r="D81" t="n">
-        <v>-4651</v>
+        <v>-4830</v>
       </c>
       <c r="E81" t="n">
-        <v>-13331</v>
+        <v>-12301</v>
       </c>
       <c r="F81" t="n">
-        <v>3881</v>
+        <v>-562</v>
       </c>
       <c r="G81" t="n">
-        <v>9147</v>
+        <v>-943</v>
       </c>
       <c r="H81" t="n">
-        <v>30</v>
+        <v>-100</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4501,19 +4501,19 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K81" t="n">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M81" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="82">
@@ -4528,22 +4528,22 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>27</v>
+        <v>-191</v>
       </c>
       <c r="D82" t="n">
-        <v>-4657</v>
+        <v>-5045</v>
       </c>
       <c r="E82" t="n">
-        <v>-4041</v>
+        <v>-4350</v>
       </c>
       <c r="F82" t="n">
-        <v>220</v>
+        <v>-43</v>
       </c>
       <c r="G82" t="n">
-        <v>3228</v>
+        <v>3170</v>
       </c>
       <c r="H82" t="n">
-        <v>-402</v>
+        <v>-228</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -4570,31 +4570,31 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-450</v>
+        <v>-644</v>
       </c>
       <c r="D83" t="n">
-        <v>-4787</v>
+        <v>-5112</v>
       </c>
       <c r="E83" t="n">
-        <v>-6327</v>
+        <v>-7666</v>
       </c>
       <c r="F83" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>-432</v>
+        <v>1847</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -4603,49 +4603,49 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K83" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-932</v>
+        <v>-1298</v>
       </c>
       <c r="D84" t="n">
-        <v>-5024</v>
+        <v>-5153</v>
       </c>
       <c r="E84" t="n">
-        <v>-18811</v>
+        <v>-7242</v>
       </c>
       <c r="F84" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G84" t="n">
-        <v>285</v>
+        <v>-4</v>
       </c>
       <c r="H84" t="n">
-        <v>-158</v>
+        <v>-531</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -4654,49 +4654,49 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K84" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M84" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>-1251</v>
+        <v>-717</v>
       </c>
       <c r="D85" t="n">
-        <v>-5157</v>
+        <v>-5683</v>
       </c>
       <c r="E85" t="n">
-        <v>-11750</v>
+        <v>-18273</v>
       </c>
       <c r="F85" t="n">
-        <v>-846</v>
+        <v>1</v>
       </c>
       <c r="G85" t="n">
-        <v>-919</v>
+        <v>285</v>
       </c>
       <c r="H85" t="n">
-        <v>-165</v>
+        <v>-175</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -4705,49 +4705,49 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K85" t="n">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M85" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-342</v>
+        <v>877</v>
       </c>
       <c r="D86" t="n">
-        <v>-5905</v>
+        <v>-5977</v>
       </c>
       <c r="E86" t="n">
-        <v>-5658</v>
+        <v>-15404</v>
       </c>
       <c r="F86" t="n">
-        <v>134</v>
+        <v>1696</v>
       </c>
       <c r="G86" t="n">
-        <v>1688</v>
+        <v>-1789</v>
       </c>
       <c r="H86" t="n">
-        <v>-78</v>
+        <v>-1565</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         </is>
       </c>
       <c r="K86" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -4768,37 +4768,37 @@
         </is>
       </c>
       <c r="M86" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>-1847</v>
+        <v>-33</v>
       </c>
       <c r="D87" t="n">
-        <v>-7494</v>
+        <v>-6122</v>
       </c>
       <c r="E87" t="n">
-        <v>135827</v>
+        <v>-5512</v>
       </c>
       <c r="F87" t="n">
-        <v>-16596</v>
+        <v>206</v>
       </c>
       <c r="G87" t="n">
-        <v>64205</v>
+        <v>1760</v>
       </c>
       <c r="H87" t="n">
-        <v>-7460</v>
+        <v>-82</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -4807,11 +4807,11 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K87" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -4819,37 +4819,37 @@
         </is>
       </c>
       <c r="M87" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>-1599</v>
+        <v>-1013</v>
       </c>
       <c r="D88" t="n">
-        <v>-7505</v>
+        <v>-6474</v>
       </c>
       <c r="E88" t="n">
-        <v>-14267</v>
+        <v>20720</v>
       </c>
       <c r="F88" t="n">
-        <v>1197</v>
+        <v>-96</v>
       </c>
       <c r="G88" t="n">
-        <v>8348</v>
+        <v>-11779</v>
       </c>
       <c r="H88" t="n">
-        <v>-151</v>
+        <v>-53</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -4858,49 +4858,49 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K88" t="n">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M88" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-5445</v>
+        <v>4393</v>
       </c>
       <c r="D89" t="n">
-        <v>-7521</v>
+        <v>-6844</v>
       </c>
       <c r="E89" t="n">
-        <v>25383</v>
+        <v>-63686</v>
       </c>
       <c r="F89" t="n">
-        <v>-16</v>
+        <v>335</v>
       </c>
       <c r="G89" t="n">
-        <v>-11448</v>
+        <v>8233</v>
       </c>
       <c r="H89" t="n">
-        <v>-254</v>
+        <v>-241</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4913,45 +4913,45 @@
         </is>
       </c>
       <c r="K89" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M89" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>立隆電</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>-2210</v>
+        <v>-1346</v>
       </c>
       <c r="D90" t="n">
-        <v>-8005</v>
+        <v>-7398</v>
       </c>
       <c r="E90" t="n">
-        <v>-20014</v>
+        <v>-13992</v>
       </c>
       <c r="F90" t="n">
-        <v>-90</v>
+        <v>1179</v>
       </c>
       <c r="G90" t="n">
-        <v>-2371</v>
+        <v>8348</v>
       </c>
       <c r="H90" t="n">
-        <v>-1588</v>
+        <v>-115</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         </is>
       </c>
       <c r="K90" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -4978,31 +4978,31 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>3515</v>
+        <v>-2624</v>
       </c>
       <c r="D91" t="n">
-        <v>-8178</v>
+        <v>-9082</v>
       </c>
       <c r="E91" t="n">
-        <v>-65454</v>
+        <v>146445</v>
       </c>
       <c r="F91" t="n">
-        <v>560</v>
+        <v>-12606</v>
       </c>
       <c r="G91" t="n">
-        <v>8206</v>
+        <v>63776</v>
       </c>
       <c r="H91" t="n">
-        <v>-258</v>
+        <v>-4907</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="K91" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         </is>
       </c>
       <c r="M91" t="n">
-        <v>-4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92">
@@ -5038,22 +5038,22 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>-7472</v>
+        <v>-4746</v>
       </c>
       <c r="D92" t="n">
-        <v>-14706</v>
+        <v>-13103</v>
       </c>
       <c r="E92" t="n">
-        <v>-22639</v>
+        <v>-22770</v>
       </c>
       <c r="F92" t="n">
-        <v>6245</v>
+        <v>3535</v>
       </c>
       <c r="G92" t="n">
-        <v>14526</v>
+        <v>12164</v>
       </c>
       <c r="H92" t="n">
-        <v>-300</v>
+        <v>109</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -5080,31 +5080,31 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>-16</v>
+        <v>8258</v>
       </c>
       <c r="D93" t="n">
-        <v>-16459</v>
+        <v>-13310</v>
       </c>
       <c r="E93" t="n">
-        <v>-41668</v>
+        <v>-69115</v>
       </c>
       <c r="F93" t="n">
-        <v>463</v>
+        <v>-2387</v>
       </c>
       <c r="G93" t="n">
-        <v>23014</v>
+        <v>19964</v>
       </c>
       <c r="H93" t="n">
-        <v>-320</v>
+        <v>-3508</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -5113,49 +5113,49 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K93" t="n">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M93" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-2746</v>
+        <v>-237</v>
       </c>
       <c r="D94" t="n">
-        <v>-18663</v>
+        <v>-17116</v>
       </c>
       <c r="E94" t="n">
-        <v>4509</v>
+        <v>-39665</v>
       </c>
       <c r="F94" t="n">
-        <v>472</v>
+        <v>380</v>
       </c>
       <c r="G94" t="n">
-        <v>12925</v>
+        <v>23020</v>
       </c>
       <c r="H94" t="n">
-        <v>-121</v>
+        <v>128</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -5164,49 +5164,49 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K94" t="n">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M94" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>-27475</v>
+        <v>-5335</v>
       </c>
       <c r="D95" t="n">
-        <v>-21037</v>
+        <v>-18094</v>
       </c>
       <c r="E95" t="n">
-        <v>79751</v>
+        <v>-27604</v>
       </c>
       <c r="F95" t="n">
-        <v>24774</v>
+        <v>-464</v>
       </c>
       <c r="G95" t="n">
-        <v>33486</v>
+        <v>-12790</v>
       </c>
       <c r="H95" t="n">
-        <v>22947</v>
+        <v>-2112</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -5215,49 +5215,49 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K95" t="n">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M95" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>18089</v>
+        <v>-314</v>
       </c>
       <c r="D96" t="n">
-        <v>-22992</v>
+        <v>-19126</v>
       </c>
       <c r="E96" t="n">
-        <v>-71342</v>
+        <v>4491</v>
       </c>
       <c r="F96" t="n">
-        <v>-10661</v>
+        <v>-22</v>
       </c>
       <c r="G96" t="n">
-        <v>29864</v>
+        <v>12867</v>
       </c>
       <c r="H96" t="n">
-        <v>-4531</v>
+        <v>-3</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -5266,11 +5266,11 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K96" t="n">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -5278,37 +5278,37 @@
         </is>
       </c>
       <c r="M96" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>-3888</v>
+        <v>-24401</v>
       </c>
       <c r="D97" t="n">
-        <v>-23953</v>
+        <v>-37359</v>
       </c>
       <c r="E97" t="n">
-        <v>-26019</v>
+        <v>56261</v>
       </c>
       <c r="F97" t="n">
-        <v>-433</v>
+        <v>24040</v>
       </c>
       <c r="G97" t="n">
-        <v>-13079</v>
+        <v>39195</v>
       </c>
       <c r="H97" t="n">
-        <v>-2284</v>
+        <v>24207</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -5317,19 +5317,19 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K97" t="n">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="98">
@@ -5344,22 +5344,22 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-41279</v>
+        <v>-40877</v>
       </c>
       <c r="D98" t="n">
-        <v>-24758</v>
+        <v>-39439</v>
       </c>
       <c r="E98" t="n">
-        <v>-14224</v>
+        <v>-16586</v>
       </c>
       <c r="F98" t="n">
-        <v>22388</v>
+        <v>19605</v>
       </c>
       <c r="G98" t="n">
-        <v>38213</v>
+        <v>39237</v>
       </c>
       <c r="H98" t="n">
-        <v>2047</v>
+        <v>595</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -5395,22 +5395,22 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>-8150</v>
+        <v>-13631</v>
       </c>
       <c r="D99" t="n">
-        <v>-48704</v>
+        <v>-42873</v>
       </c>
       <c r="E99" t="n">
-        <v>-277781</v>
+        <v>-287058</v>
       </c>
       <c r="F99" t="n">
-        <v>11558</v>
+        <v>10154</v>
       </c>
       <c r="G99" t="n">
-        <v>78151</v>
+        <v>58627</v>
       </c>
       <c r="H99" t="n">
-        <v>2080</v>
+        <v>2499</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -5437,31 +5437,31 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>-44629</v>
+        <v>-29103</v>
       </c>
       <c r="D100" t="n">
-        <v>-71517</v>
+        <v>-68318</v>
       </c>
       <c r="E100" t="n">
-        <v>-145997</v>
+        <v>-296734</v>
       </c>
       <c r="F100" t="n">
-        <v>17450</v>
+        <v>3495</v>
       </c>
       <c r="G100" t="n">
-        <v>31005</v>
+        <v>6855</v>
       </c>
       <c r="H100" t="n">
-        <v>3524</v>
+        <v>10357</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -5470,49 +5470,49 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K100" t="n">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M100" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-17548</v>
+        <v>-50794</v>
       </c>
       <c r="D101" t="n">
-        <v>-79706</v>
+        <v>-90106</v>
       </c>
       <c r="E101" t="n">
-        <v>-284274</v>
+        <v>-158342</v>
       </c>
       <c r="F101" t="n">
-        <v>7508</v>
+        <v>15510</v>
       </c>
       <c r="G101" t="n">
-        <v>6121</v>
+        <v>31847</v>
       </c>
       <c r="H101" t="n">
-        <v>9158</v>
+        <v>2815</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -5521,19 +5521,19 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K101" t="n">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M101" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="102">
@@ -5548,22 +5548,22 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>-35827</v>
+        <v>-30456</v>
       </c>
       <c r="D102" t="n">
-        <v>-151787</v>
+        <v>-154694</v>
       </c>
       <c r="E102" t="n">
-        <v>-176893</v>
+        <v>-177137</v>
       </c>
       <c r="F102" t="n">
-        <v>23280</v>
+        <v>19254</v>
       </c>
       <c r="G102" t="n">
-        <v>141731</v>
+        <v>141587</v>
       </c>
       <c r="H102" t="n">
-        <v>6417</v>
+        <v>3585</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -5599,22 +5599,22 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>-10607</v>
+        <v>20455</v>
       </c>
       <c r="D103" t="n">
-        <v>-177176</v>
+        <v>-196537</v>
       </c>
       <c r="E103" t="n">
-        <v>13852</v>
+        <v>22940</v>
       </c>
       <c r="F103" t="n">
-        <v>-66968</v>
+        <v>-76103</v>
       </c>
       <c r="G103" t="n">
-        <v>131140</v>
+        <v>114578</v>
       </c>
       <c r="H103" t="n">
-        <v>-1057</v>
+        <v>2440</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -5650,22 +5650,22 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>-50015</v>
+        <v>-36613</v>
       </c>
       <c r="D104" t="n">
-        <v>-218274</v>
+        <v>-208605</v>
       </c>
       <c r="E104" t="n">
-        <v>-94836</v>
+        <v>-102730</v>
       </c>
       <c r="F104" t="n">
-        <v>25134</v>
+        <v>14767</v>
       </c>
       <c r="G104" t="n">
-        <v>62504</v>
+        <v>62508</v>
       </c>
       <c r="H104" t="n">
-        <v>2850</v>
+        <v>-4377</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -5701,22 +5701,22 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>-73455</v>
+        <v>-51757</v>
       </c>
       <c r="D105" t="n">
-        <v>-225398</v>
+        <v>-210438</v>
       </c>
       <c r="E105" t="n">
-        <v>381562</v>
+        <v>385147</v>
       </c>
       <c r="F105" t="n">
-        <v>5386</v>
+        <v>7835</v>
       </c>
       <c r="G105" t="n">
-        <v>5736</v>
+        <v>7053</v>
       </c>
       <c r="H105" t="n">
-        <v>-4010</v>
+        <v>-1365</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -5751,7 +5751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5799,20 +5799,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 168 千股)</t>
+          <t>📉 20d 巨變(減碼 -2,093 千股)</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>-3897027</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-1539816</v>
+      </c>
+      <c r="E2" t="n">
         <v>-4191290</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
         <v>553646</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-5432097</v>
-      </c>
-      <c r="F2" t="n">
-        <v>385624</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -5828,20 +5828,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 418 千股)</t>
+          <t>📈 20d 巨變(加碼 317 千股)</t>
         </is>
       </c>
       <c r="C3" t="n">
+        <v>94295</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2121244</v>
+      </c>
+      <c r="E3" t="n">
         <v>170466</v>
       </c>
-      <c r="D3" t="n">
+      <c r="F3" t="n">
         <v>1803745</v>
-      </c>
-      <c r="E3" t="n">
-        <v>35324</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1385490</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -5852,261 +5852,261 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -65 千股)</t>
+          <t>📈 20d 巨變(加碼 382 千股)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-1441823</v>
+        <v>355100</v>
       </c>
       <c r="D4" t="n">
-        <v>564280</v>
+        <v>2307636</v>
       </c>
       <c r="E4" t="n">
-        <v>-1206948</v>
+        <v>270987</v>
       </c>
       <c r="F4" t="n">
-        <v>629154</v>
+        <v>1925416</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>高力</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -625 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 876 千股)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-268060</v>
+        <v>-323609</v>
       </c>
       <c r="D5" t="n">
-        <v>-2366903</v>
+        <v>2138123</v>
       </c>
       <c r="E5" t="n">
-        <v>-137202</v>
+        <v>440332</v>
       </c>
       <c r="F5" t="n">
-        <v>-1741839</v>
+        <v>1262617</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>奇鋐</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -210 千股)</t>
+          <t>📈 20d 巨變(加碼 37 千股)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>270987</v>
+        <v>-1162691</v>
       </c>
       <c r="D6" t="n">
-        <v>1925416</v>
+        <v>601448</v>
       </c>
       <c r="E6" t="n">
-        <v>365537</v>
+        <v>-1441823</v>
       </c>
       <c r="F6" t="n">
-        <v>2134968</v>
+        <v>564280</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>台光電</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 186 千股)</t>
+          <t>📈 20d 巨變(加碼 309 千股)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>440332</v>
+        <v>-192820</v>
       </c>
       <c r="D7" t="n">
-        <v>1262617</v>
+        <v>-2057993</v>
       </c>
       <c r="E7" t="n">
-        <v>2623750</v>
+        <v>-268060</v>
       </c>
       <c r="F7" t="n">
-        <v>1076448</v>
+        <v>-2366903</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>勤誠</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -501 千股)</t>
+          <t>📉 20d 巨變(減碼 -101 千股)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-690759</v>
+        <v>39903</v>
       </c>
       <c r="D8" t="n">
-        <v>282202</v>
+        <v>-938739</v>
       </c>
       <c r="E8" t="n">
-        <v>220229</v>
+        <v>132049</v>
       </c>
       <c r="F8" t="n">
-        <v>783557</v>
+        <v>-837842</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>光聖</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -1,103 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 856 千股)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-450266</v>
+        <v>1234767</v>
       </c>
       <c r="D9" t="n">
-        <v>-4786613</v>
+        <v>6020386</v>
       </c>
       <c r="E9" t="n">
-        <v>110793</v>
+        <v>-182549</v>
       </c>
       <c r="F9" t="n">
-        <v>-3683409</v>
+        <v>5164022</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>致茂</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -525 千股)</t>
+          <t>📉 20d 巨變(減碼 -366 千股)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-182549</v>
+        <v>-1297951</v>
       </c>
       <c r="D10" t="n">
-        <v>5164022</v>
+        <v>-5152813</v>
       </c>
       <c r="E10" t="n">
-        <v>-149213</v>
+        <v>-450266</v>
       </c>
       <c r="F10" t="n">
-        <v>5689071</v>
+        <v>-4786613</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>雙鴻</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 366 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 311 千股)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>132049</v>
+        <v>-260392</v>
       </c>
       <c r="D11" t="n">
-        <v>-837842</v>
+        <v>-846371</v>
       </c>
       <c r="E11" t="n">
-        <v>-225557</v>
+        <v>104870</v>
       </c>
       <c r="F11" t="n">
-        <v>-1203395</v>
+        <v>-1157789</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>旺矽</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠</t>
+          <t>📉 20d 巨變(減碼 -495 千股)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>104870</v>
+        <v>-2046039</v>
       </c>
       <c r="D12" t="n">
-        <v>-1157789</v>
+        <v>-213285</v>
       </c>
       <c r="E12" t="n">
-        <v>-11364</v>
+        <v>-690759</v>
       </c>
       <c r="F12" t="n">
-        <v>-1158965</v>
+        <v>282202</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>智邦</t>
         </is>
       </c>
     </row>
@@ -6118,20 +6118,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 15,092 千股)</t>
+          <t>📈 20d 巨變(加碼 11,388 千股)</t>
         </is>
       </c>
       <c r="C13" t="n">
+        <v>-29103170</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-68318244</v>
+      </c>
+      <c r="E13" t="n">
         <v>-17548375</v>
       </c>
-      <c r="D13" t="n">
+      <c r="F13" t="n">
         <v>-79705934</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-19057291</v>
-      </c>
-      <c r="F13" t="n">
-        <v>-94797468</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -6147,20 +6147,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,704 千股)</t>
+          <t>📈 20d 巨變(加碼 5,859 千股)</t>
         </is>
       </c>
       <c r="C14" t="n">
+        <v>-5334800</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-18094076</v>
+      </c>
+      <c r="E14" t="n">
         <v>-3887721</v>
       </c>
-      <c r="D14" t="n">
+      <c r="F14" t="n">
         <v>-23953215</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-4067211</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-22249419</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -6171,116 +6171,116 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 82 千股)</t>
+          <t>📉 20d 巨變(減碼 -976 千股)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>450801</v>
+        <v>472689</v>
       </c>
       <c r="D15" t="n">
-        <v>-1103769</v>
+        <v>-1160383</v>
       </c>
       <c r="E15" t="n">
-        <v>565831</v>
+        <v>501458</v>
       </c>
       <c r="F15" t="n">
-        <v>-1185391</v>
+        <v>-184741</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>佳必琪</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 644 千股)</t>
+          <t>📉 20d 巨變(減碼 -45 千股)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>501458</v>
+        <v>402</v>
       </c>
       <c r="D16" t="n">
-        <v>-184741</v>
+        <v>-1149239</v>
       </c>
       <c r="E16" t="n">
-        <v>842276</v>
+        <v>450801</v>
       </c>
       <c r="F16" t="n">
-        <v>-828616</v>
+        <v>-1103769</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>帆宣</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -319 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -404 千股)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-419794</v>
+        <v>-247558</v>
       </c>
       <c r="D17" t="n">
-        <v>1198347</v>
+        <v>8005023</v>
       </c>
       <c r="E17" t="n">
-        <v>381391</v>
+        <v>2659207</v>
       </c>
       <c r="F17" t="n">
-        <v>1517230</v>
+        <v>8409142</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>健鼎</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -2,150 千股)</t>
+          <t>📈 20d 巨變(加碼 704 千股)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2659207</v>
+        <v>-744946</v>
       </c>
       <c r="D18" t="n">
-        <v>8409142</v>
+        <v>1901973</v>
       </c>
       <c r="E18" t="n">
-        <v>4515721</v>
+        <v>-419794</v>
       </c>
       <c r="F18" t="n">
-        <v>10559458</v>
+        <v>1198347</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>辛耘</t>
         </is>
       </c>
     </row>
@@ -6292,20 +6292,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -31 千股)</t>
+          <t>📉 20d 巨變(減碼 -19 千股)</t>
         </is>
       </c>
       <c r="C19" t="n">
+        <v>-144648</v>
+      </c>
+      <c r="D19" t="n">
+        <v>225441</v>
+      </c>
+      <c r="E19" t="n">
         <v>-234934</v>
       </c>
-      <c r="D19" t="n">
+      <c r="F19" t="n">
         <v>244537</v>
-      </c>
-      <c r="E19" t="n">
-        <v>-308178</v>
-      </c>
-      <c r="F19" t="n">
-        <v>275142</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -6316,29 +6316,29 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -952 千股)</t>
+          <t>📉 20d 巨變(減碼 -187 千股)</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-3889304</v>
+        <v>-571228</v>
       </c>
       <c r="D20" t="n">
-        <v>-1308156</v>
+        <v>1018784</v>
       </c>
       <c r="E20" t="n">
-        <v>-3802047</v>
+        <v>-443676</v>
       </c>
       <c r="F20" t="n">
-        <v>-356298</v>
+        <v>1205811</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>中砂</t>
         </is>
       </c>
     </row>
@@ -6350,20 +6350,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 223 千股)</t>
+          <t>📉 20d 巨變(減碼 -657 千股)</t>
         </is>
       </c>
       <c r="C21" t="n">
+        <v>-237050</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-17115987</v>
+      </c>
+      <c r="E21" t="n">
         <v>-16219</v>
       </c>
-      <c r="D21" t="n">
+      <c r="F21" t="n">
         <v>-16459089</v>
-      </c>
-      <c r="E21" t="n">
-        <v>492096</v>
-      </c>
-      <c r="F21" t="n">
-        <v>-16682304</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -6374,29 +6374,29 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -98 千股)</t>
+          <t>📉 20d 巨變(減碼 -497 千股)</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-443676</v>
+        <v>-3018139</v>
       </c>
       <c r="D22" t="n">
-        <v>1205811</v>
+        <v>-1804776</v>
       </c>
       <c r="E22" t="n">
-        <v>-218020</v>
+        <v>-3889304</v>
       </c>
       <c r="F22" t="n">
-        <v>1303799</v>
+        <v>-1308156</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>崇越</t>
         </is>
       </c>
     </row>
@@ -6408,20 +6408,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -829 千股)</t>
+          <t>📈 20d 巨變(加碼 196 千股)</t>
         </is>
       </c>
       <c r="C23" t="n">
+        <v>-152052</v>
+      </c>
+      <c r="D23" t="n">
+        <v>166575</v>
+      </c>
+      <c r="E23" t="n">
         <v>-380293</v>
       </c>
-      <c r="D23" t="n">
+      <c r="F23" t="n">
         <v>-29807</v>
-      </c>
-      <c r="E23" t="n">
-        <v>-540862</v>
-      </c>
-      <c r="F23" t="n">
-        <v>799476</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -6437,20 +6437,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -351 千股)</t>
+          <t>📈 20d 巨變(加碼 328 千股)</t>
         </is>
       </c>
       <c r="C24" t="n">
+        <v>-339100</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-4829922</v>
+      </c>
+      <c r="E24" t="n">
         <v>-1251072</v>
       </c>
-      <c r="D24" t="n">
+      <c r="F24" t="n">
         <v>-5157480</v>
-      </c>
-      <c r="E24" t="n">
-        <v>-1434083</v>
-      </c>
-      <c r="F24" t="n">
-        <v>-4806379</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -6466,20 +6466,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 626 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,123 千股)</t>
         </is>
       </c>
       <c r="C25" t="n">
+        <v>-447169</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-3245519</v>
+      </c>
+      <c r="E25" t="n">
         <v>-472714</v>
       </c>
-      <c r="D25" t="n">
+      <c r="F25" t="n">
         <v>-2122620</v>
-      </c>
-      <c r="E25" t="n">
-        <v>-1842060</v>
-      </c>
-      <c r="F25" t="n">
-        <v>-2748932</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -6490,348 +6490,348 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 19 千股)</t>
+          <t>📉 20d 巨變(減碼 -332 千股)</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-35711</v>
+        <v>1818959</v>
       </c>
       <c r="D26" t="n">
-        <v>-141807</v>
+        <v>2607894</v>
       </c>
       <c r="E26" t="n">
-        <v>5286</v>
+        <v>2148962</v>
       </c>
       <c r="F26" t="n">
-        <v>-160980</v>
+        <v>2940341</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>大車隊</t>
+          <t>零壹</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 145 千股)</t>
+          <t>📉 20d 巨變(減碼 -763 千股)</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2148962</v>
+        <v>-1827747</v>
       </c>
       <c r="D27" t="n">
-        <v>2940341</v>
+        <v>-838394</v>
       </c>
       <c r="E27" t="n">
-        <v>2058724</v>
+        <v>-1491748</v>
       </c>
       <c r="F27" t="n">
-        <v>2795750</v>
+        <v>-75023</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>隆大</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 17 千股)</t>
+          <t>📈 20d 巨變(加碼 2,057 千股)</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>47270</v>
+        <v>504912</v>
       </c>
       <c r="D28" t="n">
-        <v>369363</v>
+        <v>-1298369</v>
       </c>
       <c r="E28" t="n">
-        <v>44390</v>
+        <v>1603053</v>
       </c>
       <c r="F28" t="n">
-        <v>352853</v>
+        <v>-3355479</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>湧德</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -60 千股)</t>
+          <t>📉 20d 巨變(減碼 -25 千股)</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1603053</v>
+        <v>46920</v>
       </c>
       <c r="D29" t="n">
-        <v>-3355479</v>
+        <v>344005</v>
       </c>
       <c r="E29" t="n">
-        <v>2150396</v>
+        <v>47270</v>
       </c>
       <c r="F29" t="n">
-        <v>-3295719</v>
+        <v>369363</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>崇友</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -691 千股)</t>
+          <t>📈 20d 巨變(加碼 1,719 千股)</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-1491748</v>
+        <v>600952</v>
       </c>
       <c r="D30" t="n">
-        <v>-75023</v>
+        <v>-1788595</v>
       </c>
       <c r="E30" t="n">
-        <v>-741748</v>
+        <v>1425471</v>
       </c>
       <c r="F30" t="n">
-        <v>616413</v>
+        <v>-3507847</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>建準</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 2,037 千股)</t>
+          <t>📉 20d 巨變(減碼 -621 千股)</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1425471</v>
+        <v>203917</v>
       </c>
       <c r="D31" t="n">
-        <v>-3507847</v>
+        <v>1041611</v>
       </c>
       <c r="E31" t="n">
-        <v>1725471</v>
+        <v>594916</v>
       </c>
       <c r="F31" t="n">
-        <v>-5544849</v>
+        <v>1662635</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>合機</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -404 千股)</t>
+          <t>📉 20d 巨變(減碼 -2,082 千股)</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>594916</v>
+        <v>-283718</v>
       </c>
       <c r="D32" t="n">
-        <v>1662635</v>
+        <v>-1663100</v>
       </c>
       <c r="E32" t="n">
-        <v>829916</v>
+        <v>-306200</v>
       </c>
       <c r="F32" t="n">
-        <v>2066635</v>
+        <v>418967</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>合機</t>
+          <t>卜蜂</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -631 千股)</t>
+          <t>📉 20d 巨變(減碼 -12 千股)</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-306200</v>
+        <v>137356</v>
       </c>
       <c r="D33" t="n">
-        <v>418967</v>
+        <v>-601723</v>
       </c>
       <c r="E33" t="n">
-        <v>-1478612</v>
+        <v>125331</v>
       </c>
       <c r="F33" t="n">
-        <v>1049961</v>
+        <v>-589501</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>大統益</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 9,826 千股)</t>
+          <t>📉 20d 巨變(減碼 -334 千股)</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-23887216</v>
+        <v>-490651</v>
       </c>
       <c r="D34" t="n">
-        <v>207000535</v>
+        <v>22010</v>
       </c>
       <c r="E34" t="n">
-        <v>-48937896</v>
+        <v>-609650</v>
       </c>
       <c r="F34" t="n">
-        <v>197174163</v>
+        <v>356006</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>寶雅</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -304 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 58,869 千股)</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-609650</v>
+        <v>61628361</v>
       </c>
       <c r="D35" t="n">
-        <v>356006</v>
+        <v>265869773</v>
       </c>
       <c r="E35" t="n">
-        <v>-824583</v>
+        <v>-23887216</v>
       </c>
       <c r="F35" t="n">
-        <v>659823</v>
+        <v>207000535</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>寶雅</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -48 千股)</t>
+          <t>📉 20d 巨變(減碼 -54 千股)</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>125331</v>
+        <v>657624</v>
       </c>
       <c r="D36" t="n">
-        <v>-589501</v>
+        <v>479507</v>
       </c>
       <c r="E36" t="n">
-        <v>123331</v>
+        <v>2013621</v>
       </c>
       <c r="F36" t="n">
-        <v>-541501</v>
+        <v>533088</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>豐藝</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,309 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -107 千股)</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2013621</v>
+        <v>-156274</v>
       </c>
       <c r="D37" t="n">
-        <v>533088</v>
+        <v>-1282686</v>
       </c>
       <c r="E37" t="n">
-        <v>2049456</v>
+        <v>4017</v>
       </c>
       <c r="F37" t="n">
-        <v>-775576</v>
+        <v>-1176083</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>華景電</t>
         </is>
       </c>
     </row>
@@ -6843,20 +6843,20 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -101 千股)</t>
+          <t>📉 20d 巨變(減碼 -32 千股)</t>
         </is>
       </c>
       <c r="C38" t="n">
+        <v>-73851</v>
+      </c>
+      <c r="D38" t="n">
+        <v>341135</v>
+      </c>
+      <c r="E38" t="n">
         <v>-55495</v>
       </c>
-      <c r="D38" t="n">
+      <c r="F38" t="n">
         <v>373491</v>
-      </c>
-      <c r="E38" t="n">
-        <v>21399</v>
-      </c>
-      <c r="F38" t="n">
-        <v>474845</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -6867,1740 +6867,1740 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅</t>
+          <t>📉 20d 巨變(減碼 -311 千股)</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-6000</v>
+        <v>-98657</v>
       </c>
       <c r="D39" t="n">
-        <v>-14000</v>
+        <v>300380</v>
       </c>
       <c r="E39" t="n">
-        <v>3000</v>
+        <v>-292657</v>
       </c>
       <c r="F39" t="n">
-        <v>-17000</v>
+        <v>611560</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>方土霖</t>
+          <t>八方雲集</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 55 千股)</t>
+          <t>📈 20d 巨變(加碼 36 千股)</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>4017</v>
+        <v>-287345</v>
       </c>
       <c r="D40" t="n">
-        <v>-1176083</v>
+        <v>-399012</v>
       </c>
       <c r="E40" t="n">
-        <v>14159</v>
+        <v>-316505</v>
       </c>
       <c r="F40" t="n">
-        <v>-1231370</v>
+        <v>-434983</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>穎崴</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -256 千股)</t>
+          <t>📉 20d 巨變(減碼 -14,681 千股)</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-292657</v>
+        <v>-40876850</v>
       </c>
       <c r="D41" t="n">
-        <v>611560</v>
+        <v>-39439324</v>
       </c>
       <c r="E41" t="n">
-        <v>-512407</v>
+        <v>-41279255</v>
       </c>
       <c r="F41" t="n">
-        <v>867682</v>
+        <v>-24758000</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>台灣大</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -31 千股)</t>
+          <t>📈 20d 巨變(加碼 1,334 千股)</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-316505</v>
+        <v>4393326</v>
       </c>
       <c r="D42" t="n">
-        <v>-434983</v>
+        <v>-6844060</v>
       </c>
       <c r="E42" t="n">
-        <v>-166534</v>
+        <v>3514589</v>
       </c>
       <c r="F42" t="n">
-        <v>-404044</v>
+        <v>-8178400</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -18,552 千股)</t>
+          <t>📈 20d 巨變(加碼 537 千股)</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-41279255</v>
+        <v>1375736</v>
       </c>
       <c r="D43" t="n">
-        <v>-24758000</v>
+        <v>213106</v>
       </c>
       <c r="E43" t="n">
-        <v>-41421559</v>
+        <v>1919835</v>
       </c>
       <c r="F43" t="n">
-        <v>-6205883</v>
+        <v>-323904</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>亞力</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 51 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 77 千股)</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-84300</v>
+        <v>59866</v>
       </c>
       <c r="D44" t="n">
-        <v>-183300</v>
+        <v>-286692</v>
       </c>
       <c r="E44" t="n">
-        <v>-92300</v>
+        <v>-431221</v>
       </c>
       <c r="F44" t="n">
-        <v>-234300</v>
+        <v>-363304</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>聯合</t>
+          <t>大綜</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 2,932 千股)</t>
+          <t>📉 20d 巨變(減碼 -20 千股)</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3514589</v>
+        <v>-117300</v>
       </c>
       <c r="D45" t="n">
-        <v>-8178400</v>
+        <v>-203300</v>
       </c>
       <c r="E45" t="n">
-        <v>2784253</v>
+        <v>-84300</v>
       </c>
       <c r="F45" t="n">
-        <v>-11110546</v>
+        <v>-183300</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>聯合</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 907 千股)</t>
+          <t>📉 20d 巨變(減碼 -320 千股)</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1919835</v>
+        <v>780969</v>
       </c>
       <c r="D46" t="n">
-        <v>-323904</v>
+        <v>3443089</v>
       </c>
       <c r="E46" t="n">
-        <v>3560636</v>
+        <v>1406179</v>
       </c>
       <c r="F46" t="n">
-        <v>-1231035</v>
+        <v>3763436</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>漢科</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -73 千股)</t>
+          <t>📈 20d 巨變(加碼 1,038 千股)</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-431221</v>
+        <v>-1505654</v>
       </c>
       <c r="D47" t="n">
-        <v>-363304</v>
+        <v>-30463</v>
       </c>
       <c r="E47" t="n">
-        <v>-1254743</v>
+        <v>-1609312</v>
       </c>
       <c r="F47" t="n">
-        <v>-290424</v>
+        <v>-1068311</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>台燿</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -134 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 2,028 千股)</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1406179</v>
+        <v>877367</v>
       </c>
       <c r="D48" t="n">
-        <v>3763436</v>
+        <v>-5977137</v>
       </c>
       <c r="E48" t="n">
-        <v>1737891</v>
+        <v>-2210124</v>
       </c>
       <c r="F48" t="n">
-        <v>3897798</v>
+        <v>-8004998</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 2,745 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,034 千股)</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-1598599</v>
+        <v>-771278</v>
       </c>
       <c r="D49" t="n">
-        <v>-7504632</v>
+        <v>-2876182</v>
       </c>
       <c r="E49" t="n">
-        <v>-8431966</v>
+        <v>-720685</v>
       </c>
       <c r="F49" t="n">
-        <v>-10249194</v>
+        <v>-1842070</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>玉晶光</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,433 千股)</t>
+          <t>📈 20d 巨變(加碼 9,683 千股)</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-1609312</v>
+        <v>8258290</v>
       </c>
       <c r="D50" t="n">
-        <v>-1068311</v>
+        <v>-13309850</v>
       </c>
       <c r="E50" t="n">
-        <v>-3507738</v>
+        <v>18088967</v>
       </c>
       <c r="F50" t="n">
-        <v>-2501552</v>
+        <v>-22992379</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,528 千股)</t>
+          <t>📈 20d 巨變(加碼 107 千股)</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-720685</v>
+        <v>-1346016</v>
       </c>
       <c r="D51" t="n">
-        <v>-1842070</v>
+        <v>-7397642</v>
       </c>
       <c r="E51" t="n">
-        <v>-1114078</v>
+        <v>-1598599</v>
       </c>
       <c r="F51" t="n">
-        <v>-3369885</v>
+        <v>-7504632</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>立隆電</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,760 千股)</t>
+          <t>📉 20d 巨變(減碼 -308 千股)</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-2210124</v>
+        <v>-1704445</v>
       </c>
       <c r="D52" t="n">
-        <v>-8004998</v>
+        <v>-3204783</v>
       </c>
       <c r="E52" t="n">
-        <v>-3278813</v>
+        <v>-1238606</v>
       </c>
       <c r="F52" t="n">
-        <v>-6245257</v>
+        <v>-2896284</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>世芯-KY</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 139 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,588 千股)</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-1238606</v>
+        <v>-2623666</v>
       </c>
       <c r="D53" t="n">
-        <v>-2896284</v>
+        <v>-9081513</v>
       </c>
       <c r="E53" t="n">
-        <v>-1159279</v>
+        <v>-1847173</v>
       </c>
       <c r="F53" t="n">
-        <v>-3035464</v>
+        <v>-7493987</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 19,881 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -718 千股)</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>18088967</v>
+        <v>-1701</v>
       </c>
       <c r="D54" t="n">
-        <v>-22992379</v>
+        <v>-1828177</v>
       </c>
       <c r="E54" t="n">
-        <v>6331225</v>
+        <v>483915</v>
       </c>
       <c r="F54" t="n">
-        <v>-42873722</v>
+        <v>-1109768</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>士電</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 12,337 千股)</t>
+          <t>📈 20d 巨變(加碼 641 千股)</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>-1847173</v>
+        <v>-29116185</v>
       </c>
       <c r="D55" t="n">
-        <v>-7493987</v>
+        <v>45493085</v>
       </c>
       <c r="E55" t="n">
-        <v>-16887087</v>
+        <v>-22577470</v>
       </c>
       <c r="F55" t="n">
-        <v>-19831169</v>
+        <v>44851996</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 2,425 千股)</t>
+          <t>📈 20d 巨變(加碼 978 千股)</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-22577470</v>
+        <v>-351514</v>
       </c>
       <c r="D56" t="n">
-        <v>44851996</v>
+        <v>-3673611</v>
       </c>
       <c r="E56" t="n">
-        <v>-13473886</v>
+        <v>-1645357</v>
       </c>
       <c r="F56" t="n">
-        <v>42426973</v>
+        <v>-4651302</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>鈊象</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 792 千股)</t>
+          <t>📉 20d 巨變(減碼 -36 千股)</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>-1645357</v>
+        <v>-190761</v>
       </c>
       <c r="D57" t="n">
-        <v>-4651302</v>
+        <v>988559</v>
       </c>
       <c r="E57" t="n">
-        <v>-1723882</v>
+        <v>-300029</v>
       </c>
       <c r="F57" t="n">
-        <v>-5443410</v>
+        <v>1024360</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>達欣工</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 833 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,507 千股)</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>483915</v>
+        <v>-644357</v>
       </c>
       <c r="D58" t="n">
-        <v>-1109768</v>
+        <v>-5111833</v>
       </c>
       <c r="E58" t="n">
-        <v>991321</v>
+        <v>-645510</v>
       </c>
       <c r="F58" t="n">
-        <v>-1942598</v>
+        <v>-3604968</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>鉅祥</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -375 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -127 千股)</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>-300029</v>
+        <v>-135730</v>
       </c>
       <c r="D59" t="n">
-        <v>1024360</v>
+        <v>-753135</v>
       </c>
       <c r="E59" t="n">
-        <v>-255036</v>
+        <v>99395</v>
       </c>
       <c r="F59" t="n">
-        <v>1399524</v>
+        <v>-625797</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>普萊德</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -2,001 千股)</t>
+          <t>📉 20d 巨變(減碼 -62 千股)</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>-645510</v>
+        <v>-460802</v>
       </c>
       <c r="D60" t="n">
-        <v>-3604968</v>
+        <v>-31917</v>
       </c>
       <c r="E60" t="n">
-        <v>-290945</v>
+        <v>-460602</v>
       </c>
       <c r="F60" t="n">
-        <v>-1603932</v>
+        <v>30083</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>信立</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -62 千股)</t>
+          <t>📉 20d 巨變(減碼 -23 千股)</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>99395</v>
+        <v>606468</v>
       </c>
       <c r="D61" t="n">
-        <v>-625797</v>
+        <v>1054563</v>
       </c>
       <c r="E61" t="n">
-        <v>207395</v>
+        <v>730406</v>
       </c>
       <c r="F61" t="n">
-        <v>-563324</v>
+        <v>1078023</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>勝一</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -173 千股)</t>
+          <t>📉 20d 巨變(減碼 -65 千股)</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>730406</v>
+        <v>476000</v>
       </c>
       <c r="D62" t="n">
-        <v>1078023</v>
+        <v>1079295</v>
       </c>
       <c r="E62" t="n">
-        <v>944822</v>
+        <v>687098</v>
       </c>
       <c r="F62" t="n">
-        <v>1250837</v>
+        <v>1144412</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>勝一</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 258 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,226 千股)</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>687098</v>
+        <v>-790450</v>
       </c>
       <c r="D63" t="n">
-        <v>1144412</v>
+        <v>3593644</v>
       </c>
       <c r="E63" t="n">
-        <v>418153</v>
+        <v>-434306</v>
       </c>
       <c r="F63" t="n">
-        <v>886170</v>
+        <v>4819709</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>藥華藥</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -347 千股)</t>
+          <t>📉 20d 巨變(減碼 -35 千股)</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>-460602</v>
+        <v>-490858</v>
       </c>
       <c r="D64" t="n">
-        <v>30083</v>
+        <v>724306</v>
       </c>
       <c r="E64" t="n">
-        <v>-94562</v>
+        <v>-764731</v>
       </c>
       <c r="F64" t="n">
-        <v>377133</v>
+        <v>759801</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>華星光</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 263 千股)</t>
+          <t>📈 20d 巨變(加碼 2,116 千股)</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-273448</v>
+        <v>335625</v>
       </c>
       <c r="D65" t="n">
-        <v>526798</v>
+        <v>-995687</v>
       </c>
       <c r="E65" t="n">
-        <v>-517856</v>
+        <v>115</v>
       </c>
       <c r="F65" t="n">
-        <v>264288</v>
+        <v>-3111902</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>聯鈞</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -420 千股)</t>
+          <t>📉 20d 巨變(減碼 -451 千股)</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-764731</v>
+        <v>-1240264</v>
       </c>
       <c r="D66" t="n">
-        <v>759801</v>
+        <v>-4196241</v>
       </c>
       <c r="E66" t="n">
-        <v>-1189932</v>
+        <v>-1338212</v>
       </c>
       <c r="F66" t="n">
-        <v>1179910</v>
+        <v>-3745568</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>宇瞻</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -394 千股)</t>
+          <t>📈 20d 巨變(加碼 5,832 千股)</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>115</v>
+        <v>-13631280</v>
       </c>
       <c r="D67" t="n">
-        <v>-3111902</v>
+        <v>-42872546</v>
       </c>
       <c r="E67" t="n">
-        <v>-432425</v>
+        <v>-8150064</v>
       </c>
       <c r="F67" t="n">
-        <v>-2717631</v>
+        <v>-48704288</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -469 千股)</t>
+          <t>📈 20d 巨變(加碼 404 千股)</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-1338212</v>
+        <v>392015</v>
       </c>
       <c r="D68" t="n">
-        <v>-3745568</v>
+        <v>4087628</v>
       </c>
       <c r="E68" t="n">
-        <v>-462082</v>
+        <v>477285</v>
       </c>
       <c r="F68" t="n">
-        <v>-3276831</v>
+        <v>3683344</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>聯亞</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -144 千股)</t>
+          <t>📈 20d 巨變(加碼 1,604 千股)</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>477285</v>
+        <v>-4746435</v>
       </c>
       <c r="D69" t="n">
-        <v>3683344</v>
+        <v>-13102584</v>
       </c>
       <c r="E69" t="n">
-        <v>522223</v>
+        <v>-7472403</v>
       </c>
       <c r="F69" t="n">
-        <v>3827747</v>
+        <v>-14706110</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>瑞昱</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 7,271 千股)</t>
+          <t>📈 20d 巨變(加碼 9,669 千股)</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-8150064</v>
+        <v>-36612809</v>
       </c>
       <c r="D70" t="n">
-        <v>-48704288</v>
+        <v>-208604968</v>
       </c>
       <c r="E70" t="n">
-        <v>-3317835</v>
+        <v>-50014891</v>
       </c>
       <c r="F70" t="n">
-        <v>-55975763</v>
+        <v>-218274214</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 6,755 千股)</t>
+          <t>📈 20d 巨變(加碼 1,662 千股)</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-50014891</v>
+        <v>10254634</v>
       </c>
       <c r="D71" t="n">
-        <v>-218274214</v>
+        <v>20887461</v>
       </c>
       <c r="E71" t="n">
-        <v>-42300050</v>
+        <v>13986990</v>
       </c>
       <c r="F71" t="n">
-        <v>-225029096</v>
+        <v>19225034</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,680 千股)</t>
+          <t>📉 20d 巨變(減碼 -464 千股)</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-7472403</v>
+        <v>-313847</v>
       </c>
       <c r="D72" t="n">
-        <v>-14706110</v>
+        <v>-19126353</v>
       </c>
       <c r="E72" t="n">
-        <v>-8175248</v>
+        <v>-2746133</v>
       </c>
       <c r="F72" t="n">
-        <v>-16386412</v>
+        <v>-18662602</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>台汽電</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -482 千股)</t>
+          <t>📉 20d 巨變(減碼 -23 千股)</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>13986990</v>
+        <v>15000</v>
       </c>
       <c r="D73" t="n">
-        <v>19225034</v>
+        <v>-469564</v>
       </c>
       <c r="E73" t="n">
-        <v>23100821</v>
+        <v>64000</v>
       </c>
       <c r="F73" t="n">
-        <v>19706634</v>
+        <v>-446414</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>友輝</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -111 千股)</t>
+          <t>📉 20d 巨變(減碼 -178 千股)</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>-68968</v>
+        <v>-643959</v>
       </c>
       <c r="D74" t="n">
-        <v>778464</v>
+        <v>-745865</v>
       </c>
       <c r="E74" t="n">
-        <v>76083</v>
+        <v>-570959</v>
       </c>
       <c r="F74" t="n">
-        <v>889464</v>
+        <v>-567865</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>德昌</t>
+          <t>億泰</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -4,800 千股)</t>
+          <t>📉 20d 巨變(減碼 -81 千股)</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>-2746133</v>
+        <v>-195478</v>
       </c>
       <c r="D75" t="n">
-        <v>-18662602</v>
+        <v>697007</v>
       </c>
       <c r="E75" t="n">
-        <v>-7327434</v>
+        <v>-68968</v>
       </c>
       <c r="F75" t="n">
-        <v>-13862410</v>
+        <v>778464</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>德昌</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -193 千股)</t>
+          <t>📉 20d 巨變(減碼 -165 千股)</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-570959</v>
+        <v>-83216</v>
       </c>
       <c r="D76" t="n">
-        <v>-567865</v>
+        <v>3343533</v>
       </c>
       <c r="E76" t="n">
-        <v>-141207</v>
+        <v>-767580</v>
       </c>
       <c r="F76" t="n">
-        <v>-375113</v>
+        <v>3508622</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>億泰</t>
+          <t>智易</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -67 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -1,172 千股)</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>64000</v>
+        <v>-1274972</v>
       </c>
       <c r="D77" t="n">
-        <v>-446414</v>
+        <v>5790425</v>
       </c>
       <c r="E77" t="n">
-        <v>180144</v>
+        <v>1271979</v>
       </c>
       <c r="F77" t="n">
-        <v>-379674</v>
+        <v>6962047</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>原相</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 74 千股)</t>
+          <t>📈 20d 巨變(加碼 1,048 千股)</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-767580</v>
+        <v>-1012931</v>
       </c>
       <c r="D78" t="n">
-        <v>3508622</v>
+        <v>-6473840</v>
       </c>
       <c r="E78" t="n">
-        <v>-244260</v>
+        <v>-5444650</v>
       </c>
       <c r="F78" t="n">
-        <v>3434342</v>
+        <v>-7521457</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>啟碁</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 356 千股)</t>
+          <t>📉 20d 巨變(減碼 -16,322 千股)</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1271979</v>
+        <v>-24400677</v>
       </c>
       <c r="D79" t="n">
-        <v>6962047</v>
+        <v>-37358945</v>
       </c>
       <c r="E79" t="n">
-        <v>3712099</v>
+        <v>-27474758</v>
       </c>
       <c r="F79" t="n">
-        <v>6606140</v>
+        <v>-21036834</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 2,181 千股)</t>
+          <t>📈 20d 巨變(加碼 250 千股)</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>-5444650</v>
+        <v>-38993</v>
       </c>
       <c r="D80" t="n">
-        <v>-7521457</v>
+        <v>307109</v>
       </c>
       <c r="E80" t="n">
-        <v>-1389207</v>
+        <v>-82231</v>
       </c>
       <c r="F80" t="n">
-        <v>-9702782</v>
+        <v>57541</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>精測</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -56 千股)</t>
+          <t>📉 20d 巨變(減碼 -659 千股)</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-82231</v>
+        <v>-717342</v>
       </c>
       <c r="D81" t="n">
-        <v>57541</v>
+        <v>-5682910</v>
       </c>
       <c r="E81" t="n">
-        <v>162258</v>
+        <v>-932344</v>
       </c>
       <c r="F81" t="n">
-        <v>113405</v>
+        <v>-5023571</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 6,104 千股)</t>
+          <t>📈 20d 巨變(加碼 14,960 千股)</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-27474758</v>
+        <v>-51756901</v>
       </c>
       <c r="D82" t="n">
-        <v>-21036834</v>
+        <v>-210437915</v>
       </c>
       <c r="E82" t="n">
-        <v>-20164935</v>
+        <v>-73455454</v>
       </c>
       <c r="F82" t="n">
-        <v>-27141151</v>
+        <v>-225398231</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -7,199 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -95 千股)</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-73455454</v>
+        <v>-8580</v>
       </c>
       <c r="D83" t="n">
-        <v>-225398231</v>
+        <v>284972</v>
       </c>
       <c r="E83" t="n">
-        <v>-56285501</v>
+        <v>65443</v>
       </c>
       <c r="F83" t="n">
-        <v>-218199656</v>
+        <v>379972</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>東科-KY</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -435 千股)</t>
+          <t>📉 20d 巨變(減碼 -5 千股)</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-932344</v>
+        <v>-59466</v>
       </c>
       <c r="D84" t="n">
-        <v>-5023571</v>
+        <v>-1108558</v>
       </c>
       <c r="E84" t="n">
-        <v>70693</v>
+        <v>-4466</v>
       </c>
       <c r="F84" t="n">
-        <v>-4588539</v>
+        <v>-1103558</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>鑫龍騰</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 48 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -1,198 千股)</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>-4466</v>
+        <v>-903490</v>
       </c>
       <c r="D85" t="n">
-        <v>-1103558</v>
+        <v>771638</v>
       </c>
       <c r="E85" t="n">
-        <v>44534</v>
+        <v>191000</v>
       </c>
       <c r="F85" t="n">
-        <v>-1151558</v>
+        <v>1970078</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>鑫龍騰</t>
+          <t>全友</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 20 千股)</t>
+          <t>📈 20d 巨變(加碼 501 千股)</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>65443</v>
+        <v>-1347436</v>
       </c>
       <c r="D86" t="n">
-        <v>379972</v>
+        <v>-3672853</v>
       </c>
       <c r="E86" t="n">
-        <v>143023</v>
+        <v>-3097053</v>
       </c>
       <c r="F86" t="n">
-        <v>359552</v>
+        <v>-4173754</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>宏捷科</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -535 千股)</t>
+          <t>📉 20d 巨變(減碼 -21 千股)</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>-3097053</v>
+        <v>1092103</v>
       </c>
       <c r="D87" t="n">
-        <v>-4173754</v>
+        <v>3383255</v>
       </c>
       <c r="E87" t="n">
-        <v>-1923173</v>
+        <v>1665029</v>
       </c>
       <c r="F87" t="n">
-        <v>-3638845</v>
+        <v>3404004</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>研華</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -260 千股)</t>
+          <t>📉 20d 巨變(減碼 -217 千股)</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1665029</v>
+        <v>-33420</v>
       </c>
       <c r="D88" t="n">
-        <v>3404004</v>
+        <v>-6121929</v>
       </c>
       <c r="E88" t="n">
-        <v>2480460</v>
+        <v>-341679</v>
       </c>
       <c r="F88" t="n">
-        <v>3664056</v>
+        <v>-5905203</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>中保科</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -58 千股)</t>
+          <t>📉 20d 巨變(減碼 -18,589 千股)</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>191000</v>
+        <v>-50794188</v>
       </c>
       <c r="D89" t="n">
-        <v>1970078</v>
+        <v>-90105685</v>
       </c>
       <c r="E89" t="n">
-        <v>332250</v>
+        <v>-44628836</v>
       </c>
       <c r="F89" t="n">
-        <v>2028334</v>
+        <v>-71516742</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -13,268 千股)</t>
+          <t>📈 20d 巨變(加碼 61 千股)</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>-44628836</v>
+        <v>-39563</v>
       </c>
       <c r="D90" t="n">
-        <v>-71516742</v>
+        <v>-87088</v>
       </c>
       <c r="E90" t="n">
-        <v>-44288983</v>
+        <v>-89217</v>
       </c>
       <c r="F90" t="n">
-        <v>-58248860</v>
+        <v>-147917</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>竹陞科技</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -72 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -34 千股)</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>-89217</v>
+        <v>12202</v>
       </c>
       <c r="D91" t="n">
-        <v>-147917</v>
+        <v>-472192</v>
       </c>
       <c r="E91" t="n">
-        <v>-120426</v>
+        <v>-20838</v>
       </c>
       <c r="F91" t="n">
-        <v>-75943</v>
+        <v>-438306</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>安碁資訊</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -434 千股)</t>
+          <t>📉 20d 巨變(減碼 -585 千股)</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>-341679</v>
+        <v>2171650</v>
       </c>
       <c r="D92" t="n">
-        <v>-5905203</v>
+        <v>7174540</v>
       </c>
       <c r="E92" t="n">
-        <v>-301833</v>
+        <v>3986842</v>
       </c>
       <c r="F92" t="n">
-        <v>-5470960</v>
+        <v>7759116</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>長榮航太</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 476 千股)</t>
+          <t>📉 20d 巨變(減碼 -5 千股)</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>3986842</v>
+        <v>39000</v>
       </c>
       <c r="D93" t="n">
-        <v>7759116</v>
+        <v>157067</v>
       </c>
       <c r="E93" t="n">
-        <v>4302017</v>
+        <v>62000</v>
       </c>
       <c r="F93" t="n">
-        <v>7283227</v>
+        <v>162067</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>六方科-KY</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -11 千股)</t>
+          <t>📈 20d 巨變(加碼 1,080 千股)</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-20838</v>
+        <v>-4326686</v>
       </c>
       <c r="D94" t="n">
-        <v>-438306</v>
+        <v>-1782828</v>
       </c>
       <c r="E94" t="n">
-        <v>-59848</v>
+        <v>-2763754</v>
       </c>
       <c r="F94" t="n">
-        <v>-427316</v>
+        <v>-2863058</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>聯發科</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 26 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -19,361 千股)</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>62000</v>
+        <v>20454693</v>
       </c>
       <c r="D95" t="n">
-        <v>162067</v>
+        <v>-196537443</v>
       </c>
       <c r="E95" t="n">
-        <v>43000</v>
+        <v>-10606966</v>
       </c>
       <c r="F95" t="n">
-        <v>135636</v>
+        <v>-177176220</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 54,746 千股)</t>
+          <t>📉 20d 巨變(減碼 -2,907 千股)</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>-10606966</v>
+        <v>-30456091</v>
       </c>
       <c r="D96" t="n">
-        <v>-177176220</v>
+        <v>-154694218</v>
       </c>
       <c r="E96" t="n">
-        <v>-39178294</v>
+        <v>-35826517</v>
       </c>
       <c r="F96" t="n">
-        <v>-231922106</v>
+        <v>-151787473</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,421 千股)</t>
+          <t>📉 20d 巨變(減碼 -62 千股)</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>-2763754</v>
+        <v>-1281761</v>
       </c>
       <c r="D97" t="n">
-        <v>-2863058</v>
+        <v>-4060574</v>
       </c>
       <c r="E97" t="n">
-        <v>-2161646</v>
+        <v>-1212339</v>
       </c>
       <c r="F97" t="n">
-        <v>-4284304</v>
+        <v>-3998149</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>緯穎</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -8,824 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 10 千股)</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-35826517</v>
+        <v>-18216</v>
       </c>
       <c r="D98" t="n">
-        <v>-151787473</v>
+        <v>269456</v>
       </c>
       <c r="E98" t="n">
-        <v>-39329925</v>
+        <v>21855</v>
       </c>
       <c r="F98" t="n">
-        <v>-142963374</v>
+        <v>259786</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>信驊</t>
         </is>
       </c>
     </row>
@@ -8612,20 +8612,20 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 466 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -388 千股)</t>
         </is>
       </c>
       <c r="C99" t="n">
+        <v>-190875</v>
+      </c>
+      <c r="D99" t="n">
+        <v>-5045426</v>
+      </c>
+      <c r="E99" t="n">
         <v>26933</v>
       </c>
-      <c r="D99" t="n">
+      <c r="F99" t="n">
         <v>-4657051</v>
-      </c>
-      <c r="E99" t="n">
-        <v>-66651</v>
-      </c>
-      <c r="F99" t="n">
-        <v>-5122664</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -8636,143 +8636,85 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -47 千股)</t>
+          <t>📈 20d 巨變(加碼 643 千股)</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>21855</v>
+        <v>-810252</v>
       </c>
       <c r="D100" t="n">
-        <v>259786</v>
+        <v>1947807</v>
       </c>
       <c r="E100" t="n">
-        <v>120833</v>
+        <v>-862126</v>
       </c>
       <c r="F100" t="n">
-        <v>306346</v>
+        <v>1304794</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>金像電</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 454 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -541 千股)</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-1212339</v>
+        <v>239213</v>
       </c>
       <c r="D101" t="n">
-        <v>-3998149</v>
+        <v>1107633</v>
       </c>
       <c r="E101" t="n">
-        <v>-1969103</v>
+        <v>-38286</v>
       </c>
       <c r="F101" t="n">
-        <v>-4452044</v>
+        <v>1648677</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>高技</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -276 千股)</t>
+          <t>📈 20d 巨變(加碼 1,247 千股)</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>-38286</v>
+        <v>454283</v>
       </c>
       <c r="D102" t="n">
-        <v>1648677</v>
+        <v>-768180</v>
       </c>
       <c r="E102" t="n">
-        <v>-232</v>
+        <v>398811</v>
       </c>
       <c r="F102" t="n">
-        <v>1924496</v>
+        <v>-2015499</v>
       </c>
       <c r="G102" t="inlineStr">
-        <is>
-          <t>高技</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>2368</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 883 千股)</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
-        <v>-862126</v>
-      </c>
-      <c r="D103" t="n">
-        <v>1304794</v>
-      </c>
-      <c r="E103" t="n">
-        <v>-1571108</v>
-      </c>
-      <c r="F103" t="n">
-        <v>421817</v>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>金像電</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>6187</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -324 千股)</t>
-        </is>
-      </c>
-      <c r="C104" t="n">
-        <v>398811</v>
-      </c>
-      <c r="D104" t="n">
-        <v>-2015499</v>
-      </c>
-      <c r="E104" t="n">
-        <v>796165</v>
-      </c>
-      <c r="F104" t="n">
-        <v>-1691030</v>
-      </c>
-      <c r="G104" t="inlineStr">
         <is>
           <t>萬潤</t>
         </is>

--- a/data/台股_外資雷達.xlsx
+++ b/data/台股_外資雷達.xlsx
@@ -496,22 +496,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>61628</v>
+        <v>102977</v>
       </c>
       <c r="D2" t="n">
-        <v>265870</v>
+        <v>294172</v>
       </c>
       <c r="E2" t="n">
-        <v>-26039</v>
+        <v>7951</v>
       </c>
       <c r="F2" t="n">
-        <v>8071</v>
+        <v>2021</v>
       </c>
       <c r="G2" t="n">
-        <v>19699</v>
+        <v>22007</v>
       </c>
       <c r="H2" t="n">
-        <v>4495</v>
+        <v>2983</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -547,22 +547,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-29116</v>
+        <v>-30100</v>
       </c>
       <c r="D3" t="n">
-        <v>45493</v>
+        <v>46804</v>
       </c>
       <c r="E3" t="n">
-        <v>-8145</v>
+        <v>-8845</v>
       </c>
       <c r="F3" t="n">
-        <v>5596</v>
+        <v>7760</v>
       </c>
       <c r="G3" t="n">
-        <v>-49541</v>
+        <v>-45500</v>
       </c>
       <c r="H3" t="n">
-        <v>3266</v>
+        <v>3082</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10255</v>
+        <v>6277</v>
       </c>
       <c r="D4" t="n">
-        <v>20887</v>
+        <v>19985</v>
       </c>
       <c r="E4" t="n">
-        <v>137281</v>
+        <v>136480</v>
       </c>
       <c r="F4" t="n">
-        <v>-3256</v>
+        <v>-2524</v>
       </c>
       <c r="G4" t="n">
-        <v>-33297</v>
+        <v>-33353</v>
       </c>
       <c r="H4" t="n">
-        <v>2713</v>
+        <v>2358</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -640,31 +640,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-248</v>
+        <v>6597</v>
       </c>
       <c r="D5" t="n">
-        <v>8005</v>
+        <v>8850</v>
       </c>
       <c r="E5" t="n">
-        <v>12015</v>
+        <v>161875</v>
       </c>
       <c r="F5" t="n">
-        <v>-4366</v>
+        <v>-2388</v>
       </c>
       <c r="G5" t="n">
-        <v>-9691</v>
+        <v>66783</v>
       </c>
       <c r="H5" t="n">
-        <v>483</v>
+        <v>-2019</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -673,11 +673,11 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -700,22 +700,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2172</v>
+        <v>1347</v>
       </c>
       <c r="D6" t="n">
-        <v>7175</v>
+        <v>8656</v>
       </c>
       <c r="E6" t="n">
-        <v>10879</v>
+        <v>12174</v>
       </c>
       <c r="F6" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>-559</v>
+        <v>-565</v>
       </c>
       <c r="H6" t="n">
-        <v>624</v>
+        <v>658</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -742,31 +742,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1235</v>
+        <v>-3062</v>
       </c>
       <c r="D7" t="n">
-        <v>6020</v>
+        <v>7938</v>
       </c>
       <c r="E7" t="n">
-        <v>10569</v>
+        <v>11739</v>
       </c>
       <c r="F7" t="n">
-        <v>-1233</v>
+        <v>-1065</v>
       </c>
       <c r="G7" t="n">
-        <v>-5196</v>
+        <v>-9763</v>
       </c>
       <c r="H7" t="n">
-        <v>249</v>
+        <v>-228</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -787,37 +787,37 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-1275</v>
+        <v>2018</v>
       </c>
       <c r="D8" t="n">
-        <v>5790</v>
+        <v>6149</v>
       </c>
       <c r="E8" t="n">
-        <v>8915</v>
+        <v>11351</v>
       </c>
       <c r="F8" t="n">
-        <v>2500</v>
+        <v>-1688</v>
       </c>
       <c r="G8" t="n">
-        <v>4790</v>
+        <v>-5717</v>
       </c>
       <c r="H8" t="n">
-        <v>314</v>
+        <v>212</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -826,11 +826,11 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -838,37 +838,37 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>原相</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>392</v>
+        <v>-1955</v>
       </c>
       <c r="D9" t="n">
-        <v>4088</v>
+        <v>5078</v>
       </c>
       <c r="E9" t="n">
-        <v>2421</v>
+        <v>8095</v>
       </c>
       <c r="F9" t="n">
-        <v>-598</v>
+        <v>1843</v>
       </c>
       <c r="G9" t="n">
-        <v>-3323</v>
+        <v>4822</v>
       </c>
       <c r="H9" t="n">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -889,37 +889,37 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-790</v>
+        <v>1505</v>
       </c>
       <c r="D10" t="n">
-        <v>3594</v>
+        <v>4238</v>
       </c>
       <c r="E10" t="n">
-        <v>16125</v>
+        <v>18403</v>
       </c>
       <c r="F10" t="n">
-        <v>357</v>
+        <v>121</v>
       </c>
       <c r="G10" t="n">
-        <v>1189</v>
+        <v>536</v>
       </c>
       <c r="H10" t="n">
-        <v>-3</v>
+        <v>178</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -928,49 +928,49 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>🚀 加速器*</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>781</v>
+        <v>-634</v>
       </c>
       <c r="D11" t="n">
-        <v>3443</v>
+        <v>4039</v>
       </c>
       <c r="E11" t="n">
-        <v>2665</v>
+        <v>1968</v>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>-86</v>
       </c>
       <c r="G11" t="n">
-        <v>135</v>
+        <v>-3154</v>
       </c>
       <c r="H11" t="n">
-        <v>28</v>
+        <v>340</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -991,88 +991,76 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1092</v>
+        <v>1183</v>
       </c>
       <c r="D12" t="n">
-        <v>3383</v>
+        <v>3813</v>
       </c>
       <c r="E12" t="n">
-        <v>17393</v>
+        <v>7808</v>
       </c>
       <c r="F12" t="n">
-        <v>214</v>
+        <v>-1792</v>
       </c>
       <c r="G12" t="n">
-        <v>288</v>
+        <v>-9822</v>
       </c>
       <c r="H12" t="n">
-        <v>203</v>
+        <v>58</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>🟢 加碼</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>61</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>📉 減速</t>
-        </is>
-      </c>
-      <c r="M12" t="n">
-        <v>-2</v>
-      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-83</v>
+        <v>-2014</v>
       </c>
       <c r="D13" t="n">
-        <v>3344</v>
+        <v>3469</v>
       </c>
       <c r="E13" t="n">
-        <v>6054</v>
+        <v>14828</v>
       </c>
       <c r="F13" t="n">
-        <v>71</v>
+        <v>209</v>
       </c>
       <c r="G13" t="n">
-        <v>5549</v>
+        <v>1083</v>
       </c>
       <c r="H13" t="n">
-        <v>-49</v>
+        <v>-12</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1085,45 +1073,45 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器*</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>漢科</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1819</v>
+        <v>155</v>
       </c>
       <c r="D14" t="n">
-        <v>2608</v>
+        <v>3319</v>
       </c>
       <c r="E14" t="n">
-        <v>2365</v>
+        <v>2541</v>
       </c>
       <c r="F14" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>-140</v>
+        <v>135</v>
       </c>
       <c r="H14" t="n">
-        <v>-752</v>
+        <v>32</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1132,49 +1120,49 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>智易</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>355</v>
+        <v>300</v>
       </c>
       <c r="D15" t="n">
-        <v>2308</v>
+        <v>2924</v>
       </c>
       <c r="E15" t="n">
-        <v>3270</v>
+        <v>6116</v>
       </c>
       <c r="F15" t="n">
-        <v>-890</v>
+        <v>35</v>
       </c>
       <c r="G15" t="n">
-        <v>-399</v>
+        <v>5554</v>
       </c>
       <c r="H15" t="n">
-        <v>14</v>
+        <v>-70</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1183,49 +1171,49 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-324</v>
+        <v>157</v>
       </c>
       <c r="D16" t="n">
-        <v>2138</v>
+        <v>2742</v>
       </c>
       <c r="E16" t="n">
-        <v>-7415</v>
+        <v>-1347</v>
       </c>
       <c r="F16" t="n">
-        <v>1897</v>
+        <v>-294</v>
       </c>
       <c r="G16" t="n">
-        <v>262</v>
+        <v>-1264</v>
       </c>
       <c r="H16" t="n">
-        <v>173</v>
+        <v>24</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1238,45 +1226,45 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>零壹</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>94</v>
+        <v>1632</v>
       </c>
       <c r="D17" t="n">
-        <v>2121</v>
+        <v>2626</v>
       </c>
       <c r="E17" t="n">
-        <v>-1460</v>
+        <v>2673</v>
       </c>
       <c r="F17" t="n">
-        <v>-242</v>
+        <v>-10</v>
       </c>
       <c r="G17" t="n">
-        <v>-1143</v>
+        <v>-142</v>
       </c>
       <c r="H17" t="n">
-        <v>47</v>
+        <v>-750</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1289,84 +1277,96 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-810</v>
+        <v>-418</v>
       </c>
       <c r="D18" t="n">
-        <v>1948</v>
+        <v>2048</v>
       </c>
       <c r="E18" t="n">
-        <v>5882</v>
+        <v>-7393</v>
       </c>
       <c r="F18" t="n">
-        <v>348</v>
+        <v>637</v>
       </c>
       <c r="G18" t="n">
-        <v>-7056</v>
+        <v>-84</v>
       </c>
       <c r="H18" t="n">
-        <v>-179</v>
+        <v>32</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+          <t>🟢 加碼</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>100</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>🚀 加速器</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-745</v>
+        <v>486</v>
       </c>
       <c r="D19" t="n">
-        <v>1902</v>
+        <v>1879</v>
       </c>
       <c r="E19" t="n">
-        <v>-1479</v>
+        <v>3101</v>
       </c>
       <c r="F19" t="n">
-        <v>-85</v>
+        <v>-767</v>
       </c>
       <c r="G19" t="n">
-        <v>-155</v>
+        <v>-695</v>
       </c>
       <c r="H19" t="n">
-        <v>-4</v>
+        <v>-116</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1379,55 +1379,67 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>239</v>
+        <v>-643</v>
       </c>
       <c r="D20" t="n">
-        <v>1108</v>
+        <v>1707</v>
       </c>
       <c r="E20" t="n">
-        <v>-3926</v>
+        <v>-1240</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>-42</v>
       </c>
       <c r="G20" t="n">
-        <v>-5746</v>
+        <v>-181</v>
       </c>
       <c r="H20" t="n">
-        <v>-108</v>
+        <v>-21</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>91</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>✈️ 高飛</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1441,22 +1453,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>476</v>
+        <v>340</v>
       </c>
       <c r="D21" t="n">
-        <v>1079</v>
+        <v>1110</v>
       </c>
       <c r="E21" t="n">
-        <v>1854</v>
+        <v>1861</v>
       </c>
       <c r="F21" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G21" t="n">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H21" t="n">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1492,22 +1504,22 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>606</v>
+        <v>453</v>
       </c>
       <c r="D22" t="n">
-        <v>1055</v>
+        <v>1101</v>
       </c>
       <c r="E22" t="n">
-        <v>1582</v>
+        <v>1505</v>
       </c>
       <c r="F22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H22" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1534,31 +1546,31 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>合機</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>204</v>
+        <v>-625</v>
       </c>
       <c r="D23" t="n">
-        <v>1042</v>
+        <v>877</v>
       </c>
       <c r="E23" t="n">
-        <v>2858</v>
+        <v>3404</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>-61</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1103</v>
       </c>
       <c r="H23" t="n">
-        <v>-35</v>
+        <v>-70</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1571,45 +1583,45 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>達欣工</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-571</v>
+        <v>-169</v>
       </c>
       <c r="D24" t="n">
-        <v>1019</v>
+        <v>783</v>
       </c>
       <c r="E24" t="n">
-        <v>3455</v>
+        <v>144</v>
       </c>
       <c r="F24" t="n">
-        <v>-50</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>1445</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>-69</v>
+        <v>-95</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1618,151 +1630,139 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>全友</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-191</v>
+        <v>-1472</v>
       </c>
       <c r="D25" t="n">
-        <v>989</v>
+        <v>583</v>
       </c>
       <c r="E25" t="n">
-        <v>123</v>
+        <v>6093</v>
       </c>
       <c r="F25" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="G25" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-26</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>75</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
         <v>1</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-93</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
-        <v>79</v>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>🛬 穩定</t>
-        </is>
-      </c>
-      <c r="M25" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-903</v>
+        <v>-569</v>
       </c>
       <c r="D26" t="n">
-        <v>772</v>
+        <v>487</v>
       </c>
       <c r="E26" t="n">
-        <v>6553</v>
+        <v>-4226</v>
       </c>
       <c r="F26" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>-5</v>
+        <v>-5806</v>
       </c>
       <c r="H26" t="n">
-        <v>-156</v>
+        <v>-121</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K26" t="n">
-        <v>75</v>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>🐌 龜速</t>
-        </is>
-      </c>
-      <c r="M26" t="n">
-        <v>1</v>
-      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-491</v>
+        <v>604</v>
       </c>
       <c r="D27" t="n">
-        <v>724</v>
+        <v>393</v>
       </c>
       <c r="E27" t="n">
-        <v>-7407</v>
+        <v>787</v>
       </c>
       <c r="F27" t="n">
-        <v>-1544</v>
+        <v>-22</v>
       </c>
       <c r="G27" t="n">
-        <v>-5920</v>
+        <v>-3</v>
       </c>
       <c r="H27" t="n">
-        <v>-351</v>
+        <v>52</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1771,40 +1771,40 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>德昌</t>
+          <t>合機</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-195</v>
+        <v>-382</v>
       </c>
       <c r="D28" t="n">
-        <v>697</v>
+        <v>375</v>
       </c>
       <c r="E28" t="n">
-        <v>590</v>
+        <v>2273</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>45</v>
+        <v>-56</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1822,11 +1822,11 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1840,82 +1840,70 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-1163</v>
+        <v>-12</v>
       </c>
       <c r="D29" t="n">
-        <v>601</v>
+        <v>348</v>
       </c>
       <c r="E29" t="n">
-        <v>4806</v>
+        <v>668</v>
       </c>
       <c r="F29" t="n">
-        <v>585</v>
+        <v>-230</v>
       </c>
       <c r="G29" t="n">
-        <v>-117</v>
+        <v>-408</v>
       </c>
       <c r="H29" t="n">
-        <v>135</v>
+        <v>-1</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K29" t="n">
-        <v>90</v>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>🚀 加速器</t>
-        </is>
-      </c>
-      <c r="M29" t="n">
-        <v>4</v>
-      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-59</v>
+        <v>-15</v>
       </c>
       <c r="D30" t="n">
-        <v>526</v>
+        <v>329</v>
       </c>
       <c r="E30" t="n">
-        <v>-1140</v>
+        <v>-162</v>
       </c>
       <c r="F30" t="n">
-        <v>1055</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>2137</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>29</v>
+        <v>-13</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1924,49 +1912,49 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M30" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>崇友</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>658</v>
+        <v>26</v>
       </c>
       <c r="D31" t="n">
-        <v>480</v>
+        <v>328</v>
       </c>
       <c r="E31" t="n">
-        <v>727</v>
+        <v>551</v>
       </c>
       <c r="F31" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>209</v>
+        <v>0</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1975,49 +1963,49 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>32</v>
+        <v>91</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>47</v>
+        <v>1552</v>
       </c>
       <c r="D32" t="n">
-        <v>344</v>
+        <v>323</v>
       </c>
       <c r="E32" t="n">
-        <v>551</v>
+        <v>-8283</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>-66</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2026,49 +2014,49 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>智冠</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-74</v>
+        <v>-313</v>
       </c>
       <c r="D33" t="n">
-        <v>341</v>
+        <v>287</v>
       </c>
       <c r="E33" t="n">
-        <v>401</v>
+        <v>-1314</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>803</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>2138</v>
       </c>
       <c r="H33" t="n">
-        <v>-152</v>
+        <v>20</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2077,49 +2065,49 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M33" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>智冠</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-39</v>
+        <v>-65</v>
       </c>
       <c r="D34" t="n">
-        <v>307</v>
+        <v>286</v>
       </c>
       <c r="E34" t="n">
-        <v>-120</v>
+        <v>410</v>
       </c>
       <c r="F34" t="n">
-        <v>-416</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>-1407</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-92</v>
+        <v>-153</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2128,11 +2116,11 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2140,37 +2128,37 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-99</v>
+        <v>-91</v>
       </c>
       <c r="D35" t="n">
-        <v>300</v>
+        <v>241</v>
       </c>
       <c r="E35" t="n">
-        <v>-1223</v>
+        <v>-158</v>
       </c>
       <c r="F35" t="n">
-        <v>-6</v>
+        <v>-240</v>
       </c>
       <c r="G35" t="n">
-        <v>244</v>
+        <v>-1132</v>
       </c>
       <c r="H35" t="n">
-        <v>9</v>
+        <v>-113</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2179,40 +2167,40 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>🐌 龜速*</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M35" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>六方科-KY</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>-9</v>
+        <v>9</v>
       </c>
       <c r="D36" t="n">
-        <v>285</v>
+        <v>136</v>
       </c>
       <c r="E36" t="n">
-        <v>-153</v>
+        <v>-24</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -2221,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-9</v>
+        <v>6</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2234,11 +2222,11 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M36" t="n">
@@ -2248,70 +2236,82 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-18</v>
+        <v>-2813</v>
       </c>
       <c r="D37" t="n">
-        <v>269</v>
+        <v>119</v>
       </c>
       <c r="E37" t="n">
-        <v>614</v>
+        <v>-7878</v>
       </c>
       <c r="F37" t="n">
-        <v>-129</v>
+        <v>-106</v>
       </c>
       <c r="G37" t="n">
-        <v>-300</v>
+        <v>-5882</v>
       </c>
       <c r="H37" t="n">
-        <v>-6</v>
+        <v>-241</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>66</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>🚀 加速器</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-145</v>
+        <v>-1547</v>
       </c>
       <c r="D38" t="n">
-        <v>225</v>
+        <v>79</v>
       </c>
       <c r="E38" t="n">
-        <v>-694</v>
+        <v>4386</v>
       </c>
       <c r="F38" t="n">
-        <v>160</v>
+        <v>695</v>
       </c>
       <c r="G38" t="n">
-        <v>-47</v>
+        <v>11</v>
       </c>
       <c r="H38" t="n">
-        <v>-17</v>
+        <v>117</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2338,31 +2338,31 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>德昌</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1376</v>
+        <v>-798</v>
       </c>
       <c r="D39" t="n">
-        <v>213</v>
+        <v>78</v>
       </c>
       <c r="E39" t="n">
-        <v>-7764</v>
+        <v>20</v>
       </c>
       <c r="F39" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-133</v>
+        <v>-24</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2383,37 +2383,37 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-152</v>
+        <v>-174</v>
       </c>
       <c r="D40" t="n">
-        <v>167</v>
+        <v>76</v>
       </c>
       <c r="E40" t="n">
-        <v>-5078</v>
+        <v>-1348</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>241</v>
       </c>
       <c r="H40" t="n">
-        <v>-26</v>
+        <v>-10</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2426,46 +2426,46 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速*</t>
         </is>
       </c>
       <c r="M40" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>39</v>
+        <v>-295</v>
       </c>
       <c r="D41" t="n">
-        <v>157</v>
+        <v>16</v>
       </c>
       <c r="E41" t="n">
+        <v>-902</v>
+      </c>
+      <c r="F41" t="n">
+        <v>279</v>
+      </c>
+      <c r="G41" t="n">
+        <v>46</v>
+      </c>
+      <c r="H41" t="n">
         <v>-11</v>
       </c>
-      <c r="F41" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" t="n">
-        <v>6</v>
-      </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>🟡 中性</t>
@@ -2473,49 +2473,49 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M41" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>寶雅</t>
+          <t>方土霖</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-491</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>22</v>
+        <v>-10</v>
       </c>
       <c r="E42" t="n">
-        <v>1703</v>
+        <v>-63</v>
       </c>
       <c r="F42" t="n">
-        <v>-123</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>153</v>
+        <v>-2</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2528,36 +2528,36 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M42" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>方土霖</t>
+          <t>湧德</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-6</v>
+        <v>-77</v>
       </c>
       <c r="D43" t="n">
-        <v>-14</v>
+        <v>-29</v>
       </c>
       <c r="E43" t="n">
-        <v>-65</v>
+        <v>-3678</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -2566,7 +2566,7 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>-2</v>
+        <v>-19</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2579,11 +2579,11 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M43" t="n">
@@ -2593,31 +2593,31 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>寶雅</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-1506</v>
+        <v>-401</v>
       </c>
       <c r="D44" t="n">
-        <v>-30</v>
+        <v>-68</v>
       </c>
       <c r="E44" t="n">
-        <v>-3944</v>
+        <v>1724</v>
       </c>
       <c r="F44" t="n">
-        <v>605</v>
+        <v>-77</v>
       </c>
       <c r="G44" t="n">
-        <v>4507</v>
+        <v>83</v>
       </c>
       <c r="H44" t="n">
-        <v>-1640</v>
+        <v>162</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2626,100 +2626,88 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M44" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-461</v>
+        <v>1472</v>
       </c>
       <c r="D45" t="n">
-        <v>-32</v>
+        <v>-74</v>
       </c>
       <c r="E45" t="n">
-        <v>-830</v>
+        <v>-4551</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>248</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>-1118</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K45" t="n">
-        <v>75</v>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>🚀 加速器</t>
-        </is>
-      </c>
-      <c r="M45" t="n">
-        <v>-1</v>
-      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-40</v>
+        <v>-1936</v>
       </c>
       <c r="D46" t="n">
         <v>-87</v>
       </c>
       <c r="E46" t="n">
-        <v>-232</v>
+        <v>3196</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>506</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H46" t="n">
-        <v>8</v>
+        <v>226</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2728,40 +2716,40 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>大車隊</t>
+          <t>信立</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-14</v>
+        <v>-458</v>
       </c>
       <c r="D47" t="n">
-        <v>-139</v>
+        <v>-90</v>
       </c>
       <c r="E47" t="n">
-        <v>-272</v>
+        <v>-802</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -2770,7 +2758,7 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2779,15 +2767,15 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M47" t="n">
@@ -2797,22 +2785,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>聯合</t>
+          <t>大車隊</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-117</v>
+        <v>-17</v>
       </c>
       <c r="D48" t="n">
-        <v>-203</v>
+        <v>-125</v>
       </c>
       <c r="E48" t="n">
-        <v>-3410</v>
+        <v>-273</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -2821,58 +2809,58 @@
         <v>0</v>
       </c>
       <c r="H48" t="n">
+        <v>52</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
         <v>97</v>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K48" t="n">
-        <v>87</v>
-      </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-2046</v>
+        <v>-89</v>
       </c>
       <c r="D49" t="n">
-        <v>-213</v>
+        <v>-149</v>
       </c>
       <c r="E49" t="n">
-        <v>3401</v>
+        <v>-284</v>
       </c>
       <c r="F49" t="n">
-        <v>598</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>255</v>
+        <v>3</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2881,40 +2869,40 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M49" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>60</v>
+        <v>-114</v>
       </c>
       <c r="D50" t="n">
-        <v>-287</v>
+        <v>-172</v>
       </c>
       <c r="E50" t="n">
-        <v>2158</v>
+        <v>-5059</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -2923,7 +2911,7 @@
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2932,11 +2920,11 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -2944,37 +2932,37 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-287</v>
+        <v>537</v>
       </c>
       <c r="D51" t="n">
-        <v>-399</v>
+        <v>-234</v>
       </c>
       <c r="E51" t="n">
-        <v>-93</v>
+        <v>1084</v>
       </c>
       <c r="F51" t="n">
-        <v>180</v>
+        <v>-512</v>
       </c>
       <c r="G51" t="n">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="H51" t="n">
-        <v>-43</v>
+        <v>-70</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -2987,11 +2975,11 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M51" t="n">
@@ -3001,31 +2989,31 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>聯合</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>15</v>
+        <v>-59</v>
       </c>
       <c r="D52" t="n">
-        <v>-470</v>
+        <v>-276</v>
       </c>
       <c r="E52" t="n">
-        <v>500</v>
+        <v>-3411</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-26</v>
+        <v>98</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3034,49 +3022,49 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M52" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>友輝</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>12</v>
+        <v>-35</v>
       </c>
       <c r="D53" t="n">
-        <v>-472</v>
+        <v>-412</v>
       </c>
       <c r="E53" t="n">
-        <v>-254</v>
+        <v>467</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H53" t="n">
-        <v>34</v>
+        <v>-24</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3093,92 +3081,92 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M53" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>137</v>
+        <v>34</v>
       </c>
       <c r="D54" t="n">
-        <v>-602</v>
+        <v>-430</v>
       </c>
       <c r="E54" t="n">
-        <v>-853</v>
+        <v>-236</v>
       </c>
       <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>16</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>77</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>✈️ 高飛*</t>
+        </is>
+      </c>
+      <c r="M54" t="n">
         <v>-1</v>
-      </c>
-      <c r="G54" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H54" t="n">
-        <v>34</v>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K54" t="n">
-        <v>86</v>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>📉 減速</t>
-        </is>
-      </c>
-      <c r="M54" t="n">
-        <v>-3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>億泰</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>-644</v>
+        <v>-352</v>
       </c>
       <c r="D55" t="n">
-        <v>-746</v>
+        <v>-437</v>
       </c>
       <c r="E55" t="n">
-        <v>-2491</v>
+        <v>-138</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="H55" t="n">
-        <v>198</v>
+        <v>-41</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3187,40 +3175,40 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K55" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M55" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-136</v>
+        <v>283</v>
       </c>
       <c r="D56" t="n">
-        <v>-753</v>
+        <v>-519</v>
       </c>
       <c r="E56" t="n">
-        <v>-1927</v>
+        <v>2188</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -3229,7 +3217,7 @@
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3242,84 +3230,96 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M56" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>大統益</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>454</v>
+        <v>188</v>
       </c>
       <c r="D57" t="n">
-        <v>-768</v>
+        <v>-633</v>
       </c>
       <c r="E57" t="n">
-        <v>-5143</v>
+        <v>-838</v>
       </c>
       <c r="F57" t="n">
-        <v>-535</v>
+        <v>-1</v>
       </c>
       <c r="G57" t="n">
-        <v>-1502</v>
+        <v>-2</v>
       </c>
       <c r="H57" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>86</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>📉 減速</t>
+        </is>
+      </c>
+      <c r="M57" t="n">
+        <v>-3</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-1828</v>
+        <v>81</v>
       </c>
       <c r="D58" t="n">
-        <v>-838</v>
+        <v>-707</v>
       </c>
       <c r="E58" t="n">
-        <v>-1467</v>
+        <v>-392</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>-952</v>
       </c>
       <c r="H58" t="n">
-        <v>343</v>
+        <v>-103</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3332,15 +3332,15 @@
         </is>
       </c>
       <c r="K58" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M58" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -3355,22 +3355,22 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>-260</v>
+        <v>-237</v>
       </c>
       <c r="D59" t="n">
-        <v>-846</v>
+        <v>-712</v>
       </c>
       <c r="E59" t="n">
-        <v>-783</v>
+        <v>-669</v>
       </c>
       <c r="F59" t="n">
-        <v>412</v>
+        <v>303</v>
       </c>
       <c r="G59" t="n">
-        <v>1423</v>
+        <v>1400</v>
       </c>
       <c r="H59" t="n">
-        <v>-37</v>
+        <v>-30</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3397,31 +3397,31 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>億泰</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>40</v>
+        <v>-580</v>
       </c>
       <c r="D60" t="n">
-        <v>-939</v>
+        <v>-717</v>
       </c>
       <c r="E60" t="n">
-        <v>-389</v>
+        <v>-2483</v>
       </c>
       <c r="F60" t="n">
-        <v>266</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>-962</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-89</v>
+        <v>193</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3430,49 +3430,49 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K60" t="n">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M60" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>336</v>
+        <v>-213</v>
       </c>
       <c r="D61" t="n">
-        <v>-996</v>
+        <v>-723</v>
       </c>
       <c r="E61" t="n">
-        <v>-2861</v>
+        <v>-1985</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>469</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-685</v>
+        <v>12</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3481,11 +3481,11 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K61" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="62">
@@ -3508,13 +3508,13 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-59</v>
+        <v>55</v>
       </c>
       <c r="D62" t="n">
-        <v>-1109</v>
+        <v>-740</v>
       </c>
       <c r="E62" t="n">
-        <v>-2999</v>
+        <v>-2892</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -3523,7 +3523,7 @@
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3550,31 +3550,31 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>-1602</v>
       </c>
       <c r="D63" t="n">
-        <v>-1149</v>
+        <v>-776</v>
       </c>
       <c r="E63" t="n">
-        <v>544</v>
+        <v>-4728</v>
       </c>
       <c r="F63" t="n">
-        <v>68</v>
+        <v>523</v>
       </c>
       <c r="G63" t="n">
-        <v>815</v>
+        <v>4027</v>
       </c>
       <c r="H63" t="n">
-        <v>-54</v>
+        <v>-1319</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3583,49 +3583,49 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K63" t="n">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>473</v>
+        <v>-155</v>
       </c>
       <c r="D64" t="n">
-        <v>-1160</v>
+        <v>-915</v>
       </c>
       <c r="E64" t="n">
-        <v>318</v>
+        <v>-3936</v>
       </c>
       <c r="F64" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G64" t="n">
-        <v>23</v>
+        <v>-113</v>
       </c>
       <c r="H64" t="n">
-        <v>-199</v>
+        <v>-66</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3638,45 +3638,45 @@
         </is>
       </c>
       <c r="K64" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M64" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-156</v>
+        <v>375</v>
       </c>
       <c r="D65" t="n">
-        <v>-1283</v>
+        <v>-1000</v>
       </c>
       <c r="E65" t="n">
-        <v>-3877</v>
+        <v>-2859</v>
       </c>
       <c r="F65" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="G65" t="n">
-        <v>-116</v>
+        <v>444</v>
       </c>
       <c r="H65" t="n">
-        <v>-143</v>
+        <v>-590</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3685,15 +3685,15 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K65" t="n">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M65" t="n">
@@ -3703,82 +3703,82 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>505</v>
+        <v>-3903</v>
       </c>
       <c r="D66" t="n">
-        <v>-1298</v>
+        <v>-1034</v>
       </c>
       <c r="E66" t="n">
-        <v>-3847</v>
+        <v>-6909</v>
       </c>
       <c r="F66" t="n">
+        <v>-471</v>
+      </c>
+      <c r="G66" t="n">
+        <v>-11007</v>
+      </c>
+      <c r="H66" t="n">
+        <v>-256</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>44</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>📉 減速</t>
+        </is>
+      </c>
+      <c r="M66" t="n">
         <v>0</v>
-      </c>
-      <c r="G66" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" t="n">
-        <v>-11</v>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K66" t="n">
-        <v>94</v>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>📉 減速</t>
-        </is>
-      </c>
-      <c r="M66" t="n">
-        <v>-2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-3897</v>
+        <v>1006</v>
       </c>
       <c r="D67" t="n">
-        <v>-1540</v>
+        <v>-1350</v>
       </c>
       <c r="E67" t="n">
-        <v>-8145</v>
+        <v>-6995</v>
       </c>
       <c r="F67" t="n">
-        <v>2460</v>
+        <v>5</v>
       </c>
       <c r="G67" t="n">
-        <v>5005</v>
+        <v>85</v>
       </c>
       <c r="H67" t="n">
-        <v>-1145</v>
+        <v>-287</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3787,49 +3787,49 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K67" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M67" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-284</v>
+        <v>-71</v>
       </c>
       <c r="D68" t="n">
-        <v>-1663</v>
+        <v>-1404</v>
       </c>
       <c r="E68" t="n">
-        <v>-6346</v>
+        <v>-738</v>
       </c>
       <c r="F68" t="n">
-        <v>-177</v>
+        <v>355</v>
       </c>
       <c r="G68" t="n">
-        <v>-1897</v>
+        <v>378</v>
       </c>
       <c r="H68" t="n">
-        <v>-7</v>
+        <v>-126</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3842,45 +3842,45 @@
         </is>
       </c>
       <c r="K68" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M68" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-4327</v>
+        <v>-1079</v>
       </c>
       <c r="D69" t="n">
-        <v>-1783</v>
+        <v>-1406</v>
       </c>
       <c r="E69" t="n">
-        <v>-6220</v>
+        <v>-328</v>
       </c>
       <c r="F69" t="n">
-        <v>-169</v>
+        <v>8</v>
       </c>
       <c r="G69" t="n">
-        <v>-10577</v>
+        <v>24</v>
       </c>
       <c r="H69" t="n">
-        <v>-237</v>
+        <v>-105</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3889,49 +3889,49 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K69" t="n">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>601</v>
+        <v>-2242</v>
       </c>
       <c r="D70" t="n">
-        <v>-1789</v>
+        <v>-1429</v>
       </c>
       <c r="E70" t="n">
-        <v>-424</v>
+        <v>-1921</v>
       </c>
       <c r="F70" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-145</v>
+        <v>337</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3944,45 +3944,45 @@
         </is>
       </c>
       <c r="K70" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M70" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-3018</v>
+        <v>-4587</v>
       </c>
       <c r="D71" t="n">
-        <v>-1805</v>
+        <v>-1514</v>
       </c>
       <c r="E71" t="n">
-        <v>-1893</v>
+        <v>-9068</v>
       </c>
       <c r="F71" t="n">
-        <v>3029</v>
+        <v>2033</v>
       </c>
       <c r="G71" t="n">
-        <v>4711</v>
+        <v>5161</v>
       </c>
       <c r="H71" t="n">
-        <v>-35</v>
+        <v>-1169</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -3995,45 +3995,45 @@
         </is>
       </c>
       <c r="K71" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M71" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-2</v>
+        <v>-339</v>
       </c>
       <c r="D72" t="n">
-        <v>-1828</v>
+        <v>-1639</v>
       </c>
       <c r="E72" t="n">
-        <v>-7453</v>
+        <v>-9825</v>
       </c>
       <c r="F72" t="n">
-        <v>10</v>
+        <v>-616</v>
       </c>
       <c r="G72" t="n">
-        <v>88</v>
+        <v>-2820</v>
       </c>
       <c r="H72" t="n">
-        <v>-298</v>
+        <v>-32</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -4042,49 +4042,49 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K72" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M72" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-193</v>
+        <v>-2678</v>
       </c>
       <c r="D73" t="n">
-        <v>-2058</v>
+        <v>-2145</v>
       </c>
       <c r="E73" t="n">
-        <v>-9858</v>
+        <v>-2040</v>
       </c>
       <c r="F73" t="n">
-        <v>-984</v>
+        <v>2282</v>
       </c>
       <c r="G73" t="n">
-        <v>-2546</v>
+        <v>4732</v>
       </c>
       <c r="H73" t="n">
-        <v>-35</v>
+        <v>-40</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -4097,45 +4097,45 @@
         </is>
       </c>
       <c r="K73" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M73" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>-771</v>
+        <v>1265</v>
       </c>
       <c r="D74" t="n">
-        <v>-2876</v>
+        <v>-2289</v>
       </c>
       <c r="E74" t="n">
-        <v>1966</v>
+        <v>23414</v>
       </c>
       <c r="F74" t="n">
-        <v>205</v>
+        <v>-115</v>
       </c>
       <c r="G74" t="n">
-        <v>-1257</v>
+        <v>-12292</v>
       </c>
       <c r="H74" t="n">
-        <v>-436</v>
+        <v>-283</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -4144,49 +4144,49 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K74" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M74" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>-1704</v>
+        <v>1748</v>
       </c>
       <c r="D75" t="n">
-        <v>-3205</v>
+        <v>-2564</v>
       </c>
       <c r="E75" t="n">
-        <v>-1836</v>
+        <v>-5899</v>
       </c>
       <c r="F75" t="n">
-        <v>104</v>
+        <v>-179</v>
       </c>
       <c r="G75" t="n">
-        <v>-187</v>
+        <v>-195</v>
       </c>
       <c r="H75" t="n">
-        <v>162</v>
+        <v>-17</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -4195,49 +4195,49 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K75" t="n">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M75" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>玉晶光</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-447</v>
+        <v>-694</v>
       </c>
       <c r="D76" t="n">
-        <v>-3246</v>
+        <v>-2679</v>
       </c>
       <c r="E76" t="n">
-        <v>-69</v>
+        <v>1805</v>
       </c>
       <c r="F76" t="n">
-        <v>-592</v>
+        <v>282</v>
       </c>
       <c r="G76" t="n">
-        <v>225</v>
+        <v>-1672</v>
       </c>
       <c r="H76" t="n">
-        <v>378</v>
+        <v>-442</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -4246,49 +4246,49 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K76" t="n">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M76" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-1347</v>
+        <v>-1233</v>
       </c>
       <c r="D77" t="n">
-        <v>-3673</v>
+        <v>-2979</v>
       </c>
       <c r="E77" t="n">
-        <v>-2553</v>
+        <v>-1695</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>-75</v>
       </c>
       <c r="H77" t="n">
-        <v>-924</v>
+        <v>213</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -4301,45 +4301,45 @@
         </is>
       </c>
       <c r="K77" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M77" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-352</v>
+        <v>-631</v>
       </c>
       <c r="D78" t="n">
-        <v>-3674</v>
+        <v>-3047</v>
       </c>
       <c r="E78" t="n">
-        <v>-12933</v>
+        <v>-554</v>
       </c>
       <c r="F78" t="n">
-        <v>817</v>
+        <v>-447</v>
       </c>
       <c r="G78" t="n">
-        <v>7784</v>
+        <v>152</v>
       </c>
       <c r="H78" t="n">
-        <v>46</v>
+        <v>386</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -4348,49 +4348,49 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K78" t="n">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M78" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-1282</v>
+        <v>7350</v>
       </c>
       <c r="D79" t="n">
-        <v>-4061</v>
+        <v>-3134</v>
       </c>
       <c r="E79" t="n">
-        <v>-8590</v>
+        <v>-73605</v>
       </c>
       <c r="F79" t="n">
-        <v>1969</v>
+        <v>-11</v>
       </c>
       <c r="G79" t="n">
-        <v>1674</v>
+        <v>15380</v>
       </c>
       <c r="H79" t="n">
-        <v>-62</v>
+        <v>-4170</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -4399,49 +4399,49 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K79" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M79" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>-1240</v>
+        <v>-1727</v>
       </c>
       <c r="D80" t="n">
-        <v>-4196</v>
+        <v>-3213</v>
       </c>
       <c r="E80" t="n">
-        <v>-13796</v>
+        <v>-2994</v>
       </c>
       <c r="F80" t="n">
-        <v>468</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>27</v>
+        <v>-828</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -4450,49 +4450,49 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K80" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M80" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>鈊象</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-339</v>
+        <v>-9</v>
       </c>
       <c r="D81" t="n">
-        <v>-4830</v>
+        <v>-3492</v>
       </c>
       <c r="E81" t="n">
-        <v>-12301</v>
+        <v>-12924</v>
       </c>
       <c r="F81" t="n">
-        <v>-562</v>
+        <v>582</v>
       </c>
       <c r="G81" t="n">
-        <v>-943</v>
+        <v>6485</v>
       </c>
       <c r="H81" t="n">
-        <v>-100</v>
+        <v>-102</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4501,49 +4501,49 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K81" t="n">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M81" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-191</v>
+        <v>802</v>
       </c>
       <c r="D82" t="n">
-        <v>-5045</v>
+        <v>-3975</v>
       </c>
       <c r="E82" t="n">
-        <v>-4350</v>
+        <v>-14796</v>
       </c>
       <c r="F82" t="n">
-        <v>-43</v>
+        <v>1420</v>
       </c>
       <c r="G82" t="n">
-        <v>3170</v>
+        <v>-1805</v>
       </c>
       <c r="H82" t="n">
-        <v>-228</v>
+        <v>-1116</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -4552,15 +4552,15 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K82" t="n">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M82" t="n">
@@ -4570,82 +4570,82 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-644</v>
+        <v>-1580</v>
       </c>
       <c r="D83" t="n">
-        <v>-5112</v>
+        <v>-4332</v>
       </c>
       <c r="E83" t="n">
-        <v>-7666</v>
+        <v>-7436</v>
       </c>
       <c r="F83" t="n">
+        <v>5</v>
+      </c>
+      <c r="G83" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H83" t="n">
+        <v>-323</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>🟠 減碼</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>80</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>✈️ 高飛</t>
+        </is>
+      </c>
+      <c r="M83" t="n">
         <v>0</v>
-      </c>
-      <c r="G83" t="n">
-        <v>0</v>
-      </c>
-      <c r="H83" t="n">
-        <v>1847</v>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>🟠 減碼</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K83" t="n">
-        <v>78</v>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>🐌 龜速</t>
-        </is>
-      </c>
-      <c r="M83" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-1298</v>
+        <v>-797</v>
       </c>
       <c r="D84" t="n">
-        <v>-5153</v>
+        <v>-4856</v>
       </c>
       <c r="E84" t="n">
-        <v>-7242</v>
+        <v>-9016</v>
       </c>
       <c r="F84" t="n">
-        <v>6</v>
+        <v>1583</v>
       </c>
       <c r="G84" t="n">
-        <v>-4</v>
+        <v>2288</v>
       </c>
       <c r="H84" t="n">
-        <v>-531</v>
+        <v>-97</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -4654,49 +4654,49 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K84" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>-717</v>
+        <v>-1896</v>
       </c>
       <c r="D85" t="n">
-        <v>-5683</v>
+        <v>-5062</v>
       </c>
       <c r="E85" t="n">
-        <v>-18273</v>
+        <v>-14191</v>
       </c>
       <c r="F85" t="n">
-        <v>1</v>
+        <v>538</v>
       </c>
       <c r="G85" t="n">
-        <v>285</v>
+        <v>593</v>
       </c>
       <c r="H85" t="n">
-        <v>-175</v>
+        <v>68</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -4709,45 +4709,45 @@
         </is>
       </c>
       <c r="K85" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M85" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>877</v>
+        <v>-874</v>
       </c>
       <c r="D86" t="n">
-        <v>-5977</v>
+        <v>-5351</v>
       </c>
       <c r="E86" t="n">
-        <v>-15404</v>
+        <v>-4789</v>
       </c>
       <c r="F86" t="n">
-        <v>1696</v>
+        <v>145</v>
       </c>
       <c r="G86" t="n">
-        <v>-1789</v>
+        <v>3292</v>
       </c>
       <c r="H86" t="n">
-        <v>-1565</v>
+        <v>-252</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -4756,15 +4756,15 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K86" t="n">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M86" t="n">
@@ -4774,31 +4774,31 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>-33</v>
+        <v>-652</v>
       </c>
       <c r="D87" t="n">
-        <v>-6122</v>
+        <v>-5467</v>
       </c>
       <c r="E87" t="n">
-        <v>-5512</v>
+        <v>-12736</v>
       </c>
       <c r="F87" t="n">
-        <v>206</v>
+        <v>-542</v>
       </c>
       <c r="G87" t="n">
-        <v>1760</v>
+        <v>-938</v>
       </c>
       <c r="H87" t="n">
-        <v>-82</v>
+        <v>-71</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -4807,15 +4807,15 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K87" t="n">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M87" t="n">
@@ -4825,31 +4825,31 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>-1013</v>
+        <v>3633</v>
       </c>
       <c r="D88" t="n">
-        <v>-6474</v>
+        <v>-5523</v>
       </c>
       <c r="E88" t="n">
-        <v>20720</v>
+        <v>-62600</v>
       </c>
       <c r="F88" t="n">
-        <v>-96</v>
+        <v>216</v>
       </c>
       <c r="G88" t="n">
-        <v>-11779</v>
+        <v>7758</v>
       </c>
       <c r="H88" t="n">
-        <v>-53</v>
+        <v>-266</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -4862,45 +4862,45 @@
         </is>
       </c>
       <c r="K88" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M88" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>4393</v>
+        <v>-2290</v>
       </c>
       <c r="D89" t="n">
-        <v>-6844</v>
+        <v>-5973</v>
       </c>
       <c r="E89" t="n">
-        <v>-63686</v>
+        <v>-8384</v>
       </c>
       <c r="F89" t="n">
-        <v>335</v>
+        <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>8233</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>-241</v>
+        <v>2145</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4909,11 +4909,11 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K89" t="n">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -4921,37 +4921,37 @@
         </is>
       </c>
       <c r="M89" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>-1346</v>
+        <v>316</v>
       </c>
       <c r="D90" t="n">
-        <v>-7398</v>
+        <v>-6117</v>
       </c>
       <c r="E90" t="n">
-        <v>-13992</v>
+        <v>-5319</v>
       </c>
       <c r="F90" t="n">
-        <v>1179</v>
+        <v>361</v>
       </c>
       <c r="G90" t="n">
-        <v>8348</v>
+        <v>1917</v>
       </c>
       <c r="H90" t="n">
-        <v>-115</v>
+        <v>-93</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         </is>
       </c>
       <c r="K90" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -4972,37 +4972,37 @@
         </is>
       </c>
       <c r="M90" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>-2624</v>
+        <v>-1194</v>
       </c>
       <c r="D91" t="n">
-        <v>-9082</v>
+        <v>-6255</v>
       </c>
       <c r="E91" t="n">
-        <v>146445</v>
+        <v>-18493</v>
       </c>
       <c r="F91" t="n">
-        <v>-12606</v>
+        <v>1</v>
       </c>
       <c r="G91" t="n">
-        <v>63776</v>
+        <v>285</v>
       </c>
       <c r="H91" t="n">
-        <v>-4907</v>
+        <v>-149</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -5011,100 +5011,100 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K91" t="n">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M91" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>立隆電</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>-4746</v>
+        <v>-365</v>
       </c>
       <c r="D92" t="n">
-        <v>-13103</v>
+        <v>-8714</v>
       </c>
       <c r="E92" t="n">
-        <v>-22770</v>
+        <v>-14749</v>
       </c>
       <c r="F92" t="n">
-        <v>3535</v>
+        <v>1497</v>
       </c>
       <c r="G92" t="n">
-        <v>12164</v>
+        <v>9851</v>
       </c>
       <c r="H92" t="n">
-        <v>109</v>
+        <v>-81</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>🔴 大賣</t>
+          <t>🟠 減碼</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K92" t="n">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M92" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>8258</v>
+        <v>-2706</v>
       </c>
       <c r="D93" t="n">
-        <v>-13310</v>
+        <v>-10154</v>
       </c>
       <c r="E93" t="n">
-        <v>-69115</v>
+        <v>-22140</v>
       </c>
       <c r="F93" t="n">
-        <v>-2387</v>
+        <v>2673</v>
       </c>
       <c r="G93" t="n">
-        <v>19964</v>
+        <v>9734</v>
       </c>
       <c r="H93" t="n">
-        <v>-3508</v>
+        <v>377</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
         </is>
       </c>
       <c r="K93" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         </is>
       </c>
       <c r="M93" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="94">
@@ -5140,22 +5140,22 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-237</v>
+        <v>806</v>
       </c>
       <c r="D94" t="n">
-        <v>-17116</v>
+        <v>-16007</v>
       </c>
       <c r="E94" t="n">
-        <v>-39665</v>
+        <v>-39186</v>
       </c>
       <c r="F94" t="n">
-        <v>380</v>
+        <v>231</v>
       </c>
       <c r="G94" t="n">
-        <v>23020</v>
+        <v>23003</v>
       </c>
       <c r="H94" t="n">
-        <v>128</v>
+        <v>176</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -5191,22 +5191,22 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>-5335</v>
+        <v>-4659</v>
       </c>
       <c r="D95" t="n">
-        <v>-18094</v>
+        <v>-18463</v>
       </c>
       <c r="E95" t="n">
-        <v>-27604</v>
+        <v>-28419</v>
       </c>
       <c r="F95" t="n">
-        <v>-464</v>
+        <v>-521</v>
       </c>
       <c r="G95" t="n">
-        <v>-12790</v>
+        <v>-12838</v>
       </c>
       <c r="H95" t="n">
-        <v>-2112</v>
+        <v>-2290</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -5242,22 +5242,22 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>-314</v>
+        <v>-1936</v>
       </c>
       <c r="D96" t="n">
-        <v>-19126</v>
+        <v>-22033</v>
       </c>
       <c r="E96" t="n">
-        <v>4491</v>
+        <v>977</v>
       </c>
       <c r="F96" t="n">
-        <v>-22</v>
+        <v>-15</v>
       </c>
       <c r="G96" t="n">
-        <v>12867</v>
+        <v>12811</v>
       </c>
       <c r="H96" t="n">
-        <v>-3</v>
+        <v>31</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -5284,31 +5284,31 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>-24401</v>
+        <v>-5075</v>
       </c>
       <c r="D97" t="n">
-        <v>-37359</v>
+        <v>-26073</v>
       </c>
       <c r="E97" t="n">
-        <v>56261</v>
+        <v>8331</v>
       </c>
       <c r="F97" t="n">
-        <v>24040</v>
+        <v>14553</v>
       </c>
       <c r="G97" t="n">
-        <v>39195</v>
+        <v>38989</v>
       </c>
       <c r="H97" t="n">
-        <v>24207</v>
+        <v>-812</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -5317,11 +5317,11 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K97" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
@@ -5335,31 +5335,31 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-40877</v>
+        <v>-16777</v>
       </c>
       <c r="D98" t="n">
-        <v>-39439</v>
+        <v>-34505</v>
       </c>
       <c r="E98" t="n">
-        <v>-16586</v>
+        <v>-291564</v>
       </c>
       <c r="F98" t="n">
-        <v>19605</v>
+        <v>8880</v>
       </c>
       <c r="G98" t="n">
-        <v>39237</v>
+        <v>41851</v>
       </c>
       <c r="H98" t="n">
-        <v>595</v>
+        <v>2510</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -5368,49 +5368,49 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K98" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M98" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>-13631</v>
+        <v>-17188</v>
       </c>
       <c r="D99" t="n">
-        <v>-42873</v>
+        <v>-40811</v>
       </c>
       <c r="E99" t="n">
-        <v>-287058</v>
+        <v>60008</v>
       </c>
       <c r="F99" t="n">
-        <v>10154</v>
+        <v>21313</v>
       </c>
       <c r="G99" t="n">
-        <v>58627</v>
+        <v>41248</v>
       </c>
       <c r="H99" t="n">
-        <v>2499</v>
+        <v>16775</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -5423,15 +5423,15 @@
         </is>
       </c>
       <c r="K99" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M99" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="100">
@@ -5446,22 +5446,22 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>-29103</v>
+        <v>-29598</v>
       </c>
       <c r="D100" t="n">
-        <v>-68318</v>
+        <v>-76163</v>
       </c>
       <c r="E100" t="n">
-        <v>-296734</v>
+        <v>-309483</v>
       </c>
       <c r="F100" t="n">
-        <v>3495</v>
+        <v>2513</v>
       </c>
       <c r="G100" t="n">
-        <v>6855</v>
+        <v>6285</v>
       </c>
       <c r="H100" t="n">
-        <v>10357</v>
+        <v>7538</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -5497,22 +5497,22 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-50794</v>
+        <v>-33457</v>
       </c>
       <c r="D101" t="n">
-        <v>-90106</v>
+        <v>-88983</v>
       </c>
       <c r="E101" t="n">
-        <v>-158342</v>
+        <v>-151366</v>
       </c>
       <c r="F101" t="n">
-        <v>15510</v>
+        <v>11766</v>
       </c>
       <c r="G101" t="n">
-        <v>31847</v>
+        <v>31542</v>
       </c>
       <c r="H101" t="n">
-        <v>2815</v>
+        <v>-8637</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -5548,22 +5548,22 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>-30456</v>
+        <v>-17284</v>
       </c>
       <c r="D102" t="n">
-        <v>-154694</v>
+        <v>-150663</v>
       </c>
       <c r="E102" t="n">
-        <v>-177137</v>
+        <v>-171557</v>
       </c>
       <c r="F102" t="n">
-        <v>19254</v>
+        <v>15436</v>
       </c>
       <c r="G102" t="n">
-        <v>141587</v>
+        <v>141120</v>
       </c>
       <c r="H102" t="n">
-        <v>3585</v>
+        <v>2367</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -5590,31 +5590,31 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>20455</v>
+        <v>-20766</v>
       </c>
       <c r="D103" t="n">
-        <v>-196537</v>
+        <v>-196111</v>
       </c>
       <c r="E103" t="n">
-        <v>22940</v>
+        <v>390890</v>
       </c>
       <c r="F103" t="n">
-        <v>-76103</v>
+        <v>6242</v>
       </c>
       <c r="G103" t="n">
-        <v>114578</v>
+        <v>6266</v>
       </c>
       <c r="H103" t="n">
-        <v>2440</v>
+        <v>-2406</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -5623,49 +5623,49 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K103" t="n">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M103" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>-36613</v>
+        <v>-27735</v>
       </c>
       <c r="D104" t="n">
-        <v>-208605</v>
+        <v>-209936</v>
       </c>
       <c r="E104" t="n">
-        <v>-102730</v>
+        <v>16140</v>
       </c>
       <c r="F104" t="n">
-        <v>14767</v>
+        <v>-40652</v>
       </c>
       <c r="G104" t="n">
-        <v>62508</v>
+        <v>110822</v>
       </c>
       <c r="H104" t="n">
-        <v>-4377</v>
+        <v>2132</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -5678,45 +5678,45 @@
         </is>
       </c>
       <c r="K104" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>-51757</v>
+        <v>-33660</v>
       </c>
       <c r="D105" t="n">
-        <v>-210438</v>
+        <v>-210392</v>
       </c>
       <c r="E105" t="n">
-        <v>385147</v>
+        <v>-108144</v>
       </c>
       <c r="F105" t="n">
-        <v>7835</v>
+        <v>10690</v>
       </c>
       <c r="G105" t="n">
-        <v>7053</v>
+        <v>73649</v>
       </c>
       <c r="H105" t="n">
-        <v>-1365</v>
+        <v>-5030</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -5725,19 +5725,19 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K105" t="n">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M105" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5751,7 +5751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5794,232 +5794,232 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -2,093 千股)</t>
+          <t>📈 20d 巨變(加碼 419 千股)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-3897027</v>
+        <v>-338736</v>
       </c>
       <c r="D2" t="n">
-        <v>-1539816</v>
+        <v>-1638900</v>
       </c>
       <c r="E2" t="n">
-        <v>-4191290</v>
+        <v>-192820</v>
       </c>
       <c r="F2" t="n">
-        <v>553646</v>
+        <v>-2057993</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>勤誠</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 317 千股)</t>
+          <t>📉 20d 巨變(減碼 -90 千股)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>94295</v>
+        <v>-417700</v>
       </c>
       <c r="D3" t="n">
-        <v>2121244</v>
+        <v>2047743</v>
       </c>
       <c r="E3" t="n">
-        <v>170466</v>
+        <v>-323609</v>
       </c>
       <c r="F3" t="n">
-        <v>1803745</v>
+        <v>2138123</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>奇鋐</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 382 千股)</t>
+          <t>📉 20d 巨變(減碼 -523 千股)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>355100</v>
+        <v>-1546922</v>
       </c>
       <c r="D4" t="n">
-        <v>2307636</v>
+        <v>78601</v>
       </c>
       <c r="E4" t="n">
-        <v>270987</v>
+        <v>-1162691</v>
       </c>
       <c r="F4" t="n">
-        <v>1925416</v>
+        <v>601448</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>台光電</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 876 千股)</t>
+          <t>📈 20d 巨變(加碼 621 千股)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-323609</v>
+        <v>157487</v>
       </c>
       <c r="D5" t="n">
-        <v>2138123</v>
+        <v>2742229</v>
       </c>
       <c r="E5" t="n">
-        <v>440332</v>
+        <v>94295</v>
       </c>
       <c r="F5" t="n">
-        <v>1262617</v>
+        <v>2121244</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>健策</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 37 千股)</t>
+          <t>📉 20d 巨變(減碼 -429 千股)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-1162691</v>
+        <v>485589</v>
       </c>
       <c r="D6" t="n">
-        <v>601448</v>
+        <v>1879108</v>
       </c>
       <c r="E6" t="n">
-        <v>-1441823</v>
+        <v>355100</v>
       </c>
       <c r="F6" t="n">
-        <v>564280</v>
+        <v>2307636</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>高力</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 309 千股)</t>
+          <t>📈 20d 巨變(加碼 25 千股)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-192820</v>
+        <v>-4587432</v>
       </c>
       <c r="D7" t="n">
-        <v>-2057993</v>
+        <v>-1514395</v>
       </c>
       <c r="E7" t="n">
-        <v>-268060</v>
+        <v>-3897027</v>
       </c>
       <c r="F7" t="n">
-        <v>-2366903</v>
+        <v>-1539816</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>亞翔</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -101 千股)</t>
+          <t>📈 20d 巨變(加碼 129 千股)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>39903</v>
+        <v>2018468</v>
       </c>
       <c r="D8" t="n">
-        <v>-938739</v>
+        <v>6149043</v>
       </c>
       <c r="E8" t="n">
-        <v>132049</v>
+        <v>1234767</v>
       </c>
       <c r="F8" t="n">
-        <v>-837842</v>
+        <v>6020386</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>致茂</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 856 千股)</t>
+          <t>📈 20d 巨變(加碼 126 千股)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1234767</v>
+        <v>-1935914</v>
       </c>
       <c r="D9" t="n">
-        <v>6020386</v>
+        <v>-87220</v>
       </c>
       <c r="E9" t="n">
-        <v>-182549</v>
+        <v>-2046039</v>
       </c>
       <c r="F9" t="n">
-        <v>5164022</v>
+        <v>-213285</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>智邦</t>
         </is>
       </c>
     </row>
@@ -6031,20 +6031,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -366 千股)</t>
+          <t>📈 20d 巨變(加碼 821 千股)</t>
         </is>
       </c>
       <c r="C10" t="n">
+        <v>-1580184</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-4332184</v>
+      </c>
+      <c r="E10" t="n">
         <v>-1297951</v>
       </c>
-      <c r="D10" t="n">
+      <c r="F10" t="n">
         <v>-5152813</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-450266</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-4786613</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -6055,290 +6055,290 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 311 千股)</t>
+          <t>📈 20d 巨變(加碼 231 千股)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-260392</v>
+        <v>81333</v>
       </c>
       <c r="D11" t="n">
-        <v>-846371</v>
+        <v>-707351</v>
       </c>
       <c r="E11" t="n">
-        <v>104870</v>
+        <v>39903</v>
       </c>
       <c r="F11" t="n">
-        <v>-1157789</v>
+        <v>-938739</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>光聖</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -495 千股)</t>
+          <t>📉 20d 巨變(減碼 -7,844 千股)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-2046039</v>
+        <v>-29598185</v>
       </c>
       <c r="D12" t="n">
-        <v>-213285</v>
+        <v>-76162501</v>
       </c>
       <c r="E12" t="n">
-        <v>-690759</v>
+        <v>-29103170</v>
       </c>
       <c r="F12" t="n">
-        <v>282202</v>
+        <v>-68318244</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 11,388 千股)</t>
+          <t>📈 20d 巨變(加碼 135 千股)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-29103170</v>
+        <v>-237369</v>
       </c>
       <c r="D13" t="n">
-        <v>-68318244</v>
+        <v>-711587</v>
       </c>
       <c r="E13" t="n">
-        <v>-17548375</v>
+        <v>-260392</v>
       </c>
       <c r="F13" t="n">
-        <v>-79705934</v>
+        <v>-846371</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>旺矽</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 5,859 千股)</t>
+          <t>📈 20d 巨變(加碼 916 千股)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-5334800</v>
+        <v>536850</v>
       </c>
       <c r="D14" t="n">
-        <v>-18094076</v>
+        <v>-233731</v>
       </c>
       <c r="E14" t="n">
-        <v>-3887721</v>
+        <v>402</v>
       </c>
       <c r="F14" t="n">
-        <v>-23953215</v>
+        <v>-1149239</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>帆宣</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -976 千股)</t>
+          <t>📉 20d 巨變(減碼 -369 千股)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>472689</v>
+        <v>-4659101</v>
       </c>
       <c r="D15" t="n">
-        <v>-1160383</v>
+        <v>-18463334</v>
       </c>
       <c r="E15" t="n">
-        <v>501458</v>
+        <v>-5334800</v>
       </c>
       <c r="F15" t="n">
-        <v>-184741</v>
+        <v>-18094076</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>台達電</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -45 千股)</t>
+          <t>📉 20d 巨變(減碼 -195 千股)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>402</v>
+        <v>-642866</v>
       </c>
       <c r="D16" t="n">
-        <v>-1149239</v>
+        <v>1706839</v>
       </c>
       <c r="E16" t="n">
-        <v>450801</v>
+        <v>-744946</v>
       </c>
       <c r="F16" t="n">
-        <v>-1103769</v>
+        <v>1901973</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>辛耘</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -404 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -246 千股)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-247558</v>
+        <v>-1078637</v>
       </c>
       <c r="D17" t="n">
-        <v>8005023</v>
+        <v>-1406115</v>
       </c>
       <c r="E17" t="n">
-        <v>2659207</v>
+        <v>472689</v>
       </c>
       <c r="F17" t="n">
-        <v>8409142</v>
+        <v>-1160383</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>佳必琪</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 704 千股)</t>
+          <t>📉 20d 巨變(減碼 -209 千股)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-744946</v>
+        <v>-294861</v>
       </c>
       <c r="D18" t="n">
-        <v>1901973</v>
+        <v>16387</v>
       </c>
       <c r="E18" t="n">
-        <v>-419794</v>
+        <v>-144648</v>
       </c>
       <c r="F18" t="n">
-        <v>1198347</v>
+        <v>225441</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>川湖</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -19 千股)</t>
+          <t>📉 20d 巨變(減碼 -67 千股)</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-144648</v>
+        <v>-3061802</v>
       </c>
       <c r="D19" t="n">
-        <v>225441</v>
+        <v>7937798</v>
       </c>
       <c r="E19" t="n">
-        <v>-234934</v>
+        <v>-247558</v>
       </c>
       <c r="F19" t="n">
-        <v>244537</v>
+        <v>8005023</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>健鼎</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -187 千股)</t>
+          <t>📉 20d 巨變(減碼 -340 千股)</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-571228</v>
+        <v>-2677517</v>
       </c>
       <c r="D20" t="n">
-        <v>1018784</v>
+        <v>-2145024</v>
       </c>
       <c r="E20" t="n">
-        <v>-443676</v>
+        <v>-3018139</v>
       </c>
       <c r="F20" t="n">
-        <v>1205811</v>
+        <v>-1804776</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>崇越</t>
         </is>
       </c>
     </row>
@@ -6350,20 +6350,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -657 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 1,109 千股)</t>
         </is>
       </c>
       <c r="C21" t="n">
+        <v>805811</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-16007257</v>
+      </c>
+      <c r="E21" t="n">
         <v>-237050</v>
       </c>
-      <c r="D21" t="n">
+      <c r="F21" t="n">
         <v>-17115987</v>
-      </c>
-      <c r="E21" t="n">
-        <v>-16219</v>
-      </c>
-      <c r="F21" t="n">
-        <v>-16459089</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -6374,116 +6374,116 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -497 千股)</t>
+          <t>📉 20d 巨變(減碼 -142 千股)</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-3018139</v>
+        <v>-624857</v>
       </c>
       <c r="D22" t="n">
-        <v>-1804776</v>
+        <v>877035</v>
       </c>
       <c r="E22" t="n">
-        <v>-3889304</v>
+        <v>-571228</v>
       </c>
       <c r="F22" t="n">
-        <v>-1308156</v>
+        <v>1018784</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>中砂</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 196 千股)</t>
+          <t>📉 20d 巨變(減碼 -637 千股)</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-152052</v>
+        <v>-651890</v>
       </c>
       <c r="D23" t="n">
-        <v>166575</v>
+        <v>-5466930</v>
       </c>
       <c r="E23" t="n">
-        <v>-380293</v>
+        <v>-339100</v>
       </c>
       <c r="F23" t="n">
-        <v>-29807</v>
+        <v>-4829922</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>華城</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 328 千股)</t>
+          <t>📈 20d 巨變(加碼 198 千股)</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-339100</v>
+        <v>-631103</v>
       </c>
       <c r="D24" t="n">
-        <v>-4829922</v>
+        <v>-3047283</v>
       </c>
       <c r="E24" t="n">
-        <v>-1251072</v>
+        <v>-447169</v>
       </c>
       <c r="F24" t="n">
-        <v>-5157480</v>
+        <v>-3245519</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>大立光</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,123 千股)</t>
+          <t>📉 20d 巨變(減碼 -339 千股)</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-447169</v>
+        <v>-113922</v>
       </c>
       <c r="D25" t="n">
-        <v>-3245519</v>
+        <v>-172466</v>
       </c>
       <c r="E25" t="n">
-        <v>-472714</v>
+        <v>-152052</v>
       </c>
       <c r="F25" t="n">
-        <v>-2122620</v>
+        <v>166575</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>建榮</t>
         </is>
       </c>
     </row>
@@ -6495,20 +6495,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -332 千股)</t>
+          <t>📈 20d 巨變(加碼 18 千股)</t>
         </is>
       </c>
       <c r="C26" t="n">
+        <v>1631793</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2625658</v>
+      </c>
+      <c r="E26" t="n">
         <v>1818959</v>
       </c>
-      <c r="D26" t="n">
+      <c r="F26" t="n">
         <v>2607894</v>
-      </c>
-      <c r="E26" t="n">
-        <v>2148962</v>
-      </c>
-      <c r="F26" t="n">
-        <v>2940341</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -6519,319 +6519,319 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -763 千股)</t>
+          <t>📉 20d 巨變(減碼 -16 千股)</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-1827747</v>
+        <v>26277</v>
       </c>
       <c r="D27" t="n">
-        <v>-838394</v>
+        <v>328405</v>
       </c>
       <c r="E27" t="n">
-        <v>-1491748</v>
+        <v>46920</v>
       </c>
       <c r="F27" t="n">
-        <v>-75023</v>
+        <v>344005</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>崇友</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 2,057 千股)</t>
+          <t>📈 20d 巨變(加碼 14 千股)</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>504912</v>
+        <v>-16751</v>
       </c>
       <c r="D28" t="n">
-        <v>-1298369</v>
+        <v>-124886</v>
       </c>
       <c r="E28" t="n">
-        <v>1603053</v>
+        <v>-13711</v>
       </c>
       <c r="F28" t="n">
-        <v>-3355479</v>
+        <v>-138807</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>大車隊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -25 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 1,270 千股)</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>46920</v>
+        <v>-77256</v>
       </c>
       <c r="D29" t="n">
-        <v>344005</v>
+        <v>-28638</v>
       </c>
       <c r="E29" t="n">
-        <v>47270</v>
+        <v>504912</v>
       </c>
       <c r="F29" t="n">
-        <v>369363</v>
+        <v>-1298369</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>湧德</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,719 千股)</t>
+          <t>📉 20d 巨變(減碼 -591 千股)</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>600952</v>
+        <v>-2242249</v>
       </c>
       <c r="D30" t="n">
-        <v>-1788595</v>
+        <v>-1429063</v>
       </c>
       <c r="E30" t="n">
-        <v>1425471</v>
+        <v>-1827747</v>
       </c>
       <c r="F30" t="n">
-        <v>-3507847</v>
+        <v>-838394</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>隆大</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -621 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 384 千股)</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>203917</v>
+        <v>-70617</v>
       </c>
       <c r="D31" t="n">
-        <v>1041611</v>
+        <v>-1404111</v>
       </c>
       <c r="E31" t="n">
-        <v>594916</v>
+        <v>600952</v>
       </c>
       <c r="F31" t="n">
-        <v>1662635</v>
+        <v>-1788595</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>合機</t>
+          <t>建準</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -2,082 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -667 千股)</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-283718</v>
+        <v>-381908</v>
       </c>
       <c r="D32" t="n">
-        <v>-1663100</v>
+        <v>374792</v>
       </c>
       <c r="E32" t="n">
-        <v>-306200</v>
+        <v>203917</v>
       </c>
       <c r="F32" t="n">
-        <v>418967</v>
+        <v>1041611</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>合機</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -12 千股)</t>
+          <t>📉 20d 巨變(減碼 -90 千股)</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>137356</v>
+        <v>-401425</v>
       </c>
       <c r="D33" t="n">
-        <v>-601723</v>
+        <v>-67839</v>
       </c>
       <c r="E33" t="n">
-        <v>125331</v>
+        <v>-490651</v>
       </c>
       <c r="F33" t="n">
-        <v>-589501</v>
+        <v>22010</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>寶雅</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -334 千股)</t>
+          <t>📈 20d 巨變(加碼 28,303 千股)</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-490651</v>
+        <v>102976642</v>
       </c>
       <c r="D34" t="n">
-        <v>22010</v>
+        <v>294172415</v>
       </c>
       <c r="E34" t="n">
-        <v>-609650</v>
+        <v>61628361</v>
       </c>
       <c r="F34" t="n">
-        <v>356006</v>
+        <v>265869773</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>寶雅</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 58,869 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -901 千股)</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>61628361</v>
+        <v>1747876</v>
       </c>
       <c r="D35" t="n">
-        <v>265869773</v>
+        <v>-2564024</v>
       </c>
       <c r="E35" t="n">
-        <v>-23887216</v>
+        <v>-283718</v>
       </c>
       <c r="F35" t="n">
-        <v>207000535</v>
+        <v>-1663100</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>卜蜂</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -54 千股)</t>
+          <t>📉 20d 巨變(減碼 -32 千股)</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>657624</v>
+        <v>188106</v>
       </c>
       <c r="D36" t="n">
-        <v>479507</v>
+        <v>-633348</v>
       </c>
       <c r="E36" t="n">
-        <v>2013621</v>
+        <v>137356</v>
       </c>
       <c r="F36" t="n">
-        <v>533088</v>
+        <v>-601723</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>大統益</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -107 千股)</t>
+          <t>📉 20d 巨變(減碼 -87 千股)</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-156274</v>
+        <v>603874</v>
       </c>
       <c r="D37" t="n">
-        <v>-1282686</v>
+        <v>392531</v>
       </c>
       <c r="E37" t="n">
-        <v>4017</v>
+        <v>657624</v>
       </c>
       <c r="F37" t="n">
-        <v>-1176083</v>
+        <v>479507</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>豐藝</t>
         </is>
       </c>
     </row>
@@ -6843,20 +6843,20 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -32 千股)</t>
+          <t>📉 20d 巨變(減碼 -55 千股)</t>
         </is>
       </c>
       <c r="C38" t="n">
+        <v>-65050</v>
+      </c>
+      <c r="D38" t="n">
+        <v>285739</v>
+      </c>
+      <c r="E38" t="n">
         <v>-73851</v>
       </c>
-      <c r="D38" t="n">
+      <c r="F38" t="n">
         <v>341135</v>
-      </c>
-      <c r="E38" t="n">
-        <v>-55495</v>
-      </c>
-      <c r="F38" t="n">
-        <v>373491</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -6867,377 +6867,377 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -311 千股)</t>
+          <t>📈 20d 巨變(加碼 367 千股)</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-98657</v>
+        <v>-155463</v>
       </c>
       <c r="D39" t="n">
-        <v>300380</v>
+        <v>-915226</v>
       </c>
       <c r="E39" t="n">
-        <v>-292657</v>
+        <v>-156274</v>
       </c>
       <c r="F39" t="n">
-        <v>611560</v>
+        <v>-1282686</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>華景電</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 36 千股)</t>
+          <t>📉 20d 巨變(減碼 -224 千股)</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-287345</v>
+        <v>-173892</v>
       </c>
       <c r="D40" t="n">
-        <v>-399012</v>
+        <v>76456</v>
       </c>
       <c r="E40" t="n">
-        <v>-316505</v>
+        <v>-98657</v>
       </c>
       <c r="F40" t="n">
-        <v>-434983</v>
+        <v>300380</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>八方雲集</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -14,681 千股)</t>
+          <t>📉 20d 巨變(減碼 -38 千股)</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-40876850</v>
+        <v>-352439</v>
       </c>
       <c r="D41" t="n">
-        <v>-39439324</v>
+        <v>-437104</v>
       </c>
       <c r="E41" t="n">
-        <v>-41279255</v>
+        <v>-287345</v>
       </c>
       <c r="F41" t="n">
-        <v>-24758000</v>
+        <v>-399012</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>穎崴</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,334 千股)</t>
+          <t>📈 20d 巨變(加碼 13,367 千股)</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4393326</v>
+        <v>-5075202</v>
       </c>
       <c r="D42" t="n">
-        <v>-6844060</v>
+        <v>-26072637</v>
       </c>
       <c r="E42" t="n">
-        <v>3514589</v>
+        <v>-40876850</v>
       </c>
       <c r="F42" t="n">
-        <v>-8178400</v>
+        <v>-39439324</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>台灣大</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 537 千股)</t>
+          <t>📉 20d 巨變(減碼 -73 千股)</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1375736</v>
+        <v>-59300</v>
       </c>
       <c r="D43" t="n">
-        <v>213106</v>
+        <v>-276300</v>
       </c>
       <c r="E43" t="n">
-        <v>1919835</v>
+        <v>-117300</v>
       </c>
       <c r="F43" t="n">
-        <v>-323904</v>
+        <v>-203300</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>聯合</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 77 千股)</t>
+          <t>📈 20d 巨變(加碼 1,321 千股)</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>59866</v>
+        <v>3632738</v>
       </c>
       <c r="D44" t="n">
-        <v>-286692</v>
+        <v>-5523286</v>
       </c>
       <c r="E44" t="n">
-        <v>-431221</v>
+        <v>4393326</v>
       </c>
       <c r="F44" t="n">
-        <v>-363304</v>
+        <v>-6844060</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -20 千股)</t>
+          <t>📉 20d 巨變(減碼 -232 千股)</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-117300</v>
+        <v>282866</v>
       </c>
       <c r="D45" t="n">
-        <v>-203300</v>
+        <v>-518692</v>
       </c>
       <c r="E45" t="n">
-        <v>-84300</v>
+        <v>59866</v>
       </c>
       <c r="F45" t="n">
-        <v>-183300</v>
+        <v>-286692</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>聯合</t>
+          <t>大綜</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -320 千股)</t>
+          <t>📈 20d 巨變(加碼 110 千股)</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>780969</v>
+        <v>1551741</v>
       </c>
       <c r="D46" t="n">
-        <v>3443089</v>
+        <v>322959</v>
       </c>
       <c r="E46" t="n">
-        <v>1406179</v>
+        <v>1375736</v>
       </c>
       <c r="F46" t="n">
-        <v>3763436</v>
+        <v>213106</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>亞力</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,038 千股)</t>
+          <t>📉 20d 巨變(減碼 -124 千股)</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-1505654</v>
+        <v>154723</v>
       </c>
       <c r="D47" t="n">
-        <v>-30463</v>
+        <v>3319191</v>
       </c>
       <c r="E47" t="n">
-        <v>-1609312</v>
+        <v>780969</v>
       </c>
       <c r="F47" t="n">
-        <v>-1068311</v>
+        <v>3443089</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>漢科</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 2,028 千股)</t>
+          <t>📉 20d 巨變(減碼 -746 千股)</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>877367</v>
+        <v>-1602097</v>
       </c>
       <c r="D48" t="n">
-        <v>-5977137</v>
+        <v>-776430</v>
       </c>
       <c r="E48" t="n">
-        <v>-2210124</v>
+        <v>-1505654</v>
       </c>
       <c r="F48" t="n">
-        <v>-8004998</v>
+        <v>-30463</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>台燿</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,034 千股)</t>
+          <t>📈 20d 巨變(加碼 2,002 千股)</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-771278</v>
+        <v>801858</v>
       </c>
       <c r="D49" t="n">
-        <v>-2876182</v>
+        <v>-3975426</v>
       </c>
       <c r="E49" t="n">
-        <v>-720685</v>
+        <v>877367</v>
       </c>
       <c r="F49" t="n">
-        <v>-1842070</v>
+        <v>-5977137</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 9,683 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,316 千股)</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>8258290</v>
+        <v>-364777</v>
       </c>
       <c r="D50" t="n">
-        <v>-13309850</v>
+        <v>-8713956</v>
       </c>
       <c r="E50" t="n">
-        <v>18088967</v>
+        <v>-1346016</v>
       </c>
       <c r="F50" t="n">
-        <v>-22992379</v>
+        <v>-7397642</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>立隆電</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 107 千股)</t>
+          <t>📈 20d 巨變(加碼 197 千股)</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-1346016</v>
+        <v>-694425</v>
       </c>
       <c r="D51" t="n">
-        <v>-7397642</v>
+        <v>-2678969</v>
       </c>
       <c r="E51" t="n">
-        <v>-1598599</v>
+        <v>-771278</v>
       </c>
       <c r="F51" t="n">
-        <v>-7504632</v>
+        <v>-2876182</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>玉晶光</t>
         </is>
       </c>
     </row>
@@ -7249,20 +7249,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -308 千股)</t>
+          <t>📈 20d 巨變(加碼 226 千股)</t>
         </is>
       </c>
       <c r="C52" t="n">
+        <v>-1232514</v>
+      </c>
+      <c r="D52" t="n">
+        <v>-2978661</v>
+      </c>
+      <c r="E52" t="n">
         <v>-1704445</v>
       </c>
-      <c r="D52" t="n">
+      <c r="F52" t="n">
         <v>-3204783</v>
-      </c>
-      <c r="E52" t="n">
-        <v>-1238606</v>
-      </c>
-      <c r="F52" t="n">
-        <v>-2896284</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -7278,20 +7278,20 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,588 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 17,931 千股)</t>
         </is>
       </c>
       <c r="C53" t="n">
+        <v>6597485</v>
+      </c>
+      <c r="D53" t="n">
+        <v>8849613</v>
+      </c>
+      <c r="E53" t="n">
         <v>-2623666</v>
       </c>
-      <c r="D53" t="n">
+      <c r="F53" t="n">
         <v>-9081513</v>
-      </c>
-      <c r="E53" t="n">
-        <v>-1847173</v>
-      </c>
-      <c r="F53" t="n">
-        <v>-7493987</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -7302,29 +7302,29 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -718 千股)</t>
+          <t>📈 20d 巨變(加碼 10,176 千股)</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-1701</v>
+        <v>7350345</v>
       </c>
       <c r="D54" t="n">
-        <v>-1828177</v>
+        <v>-3133976</v>
       </c>
       <c r="E54" t="n">
-        <v>483915</v>
+        <v>8258290</v>
       </c>
       <c r="F54" t="n">
-        <v>-1109768</v>
+        <v>-13309850</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
@@ -7336,20 +7336,20 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 641 千股)</t>
+          <t>📈 20d 巨變(加碼 1,311 千股)</t>
         </is>
       </c>
       <c r="C55" t="n">
+        <v>-30100117</v>
+      </c>
+      <c r="D55" t="n">
+        <v>46804087</v>
+      </c>
+      <c r="E55" t="n">
         <v>-29116185</v>
       </c>
-      <c r="D55" t="n">
+      <c r="F55" t="n">
         <v>45493085</v>
-      </c>
-      <c r="E55" t="n">
-        <v>-22577470</v>
-      </c>
-      <c r="F55" t="n">
-        <v>44851996</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -7360,58 +7360,58 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 978 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 478 千股)</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-351514</v>
+        <v>1006160</v>
       </c>
       <c r="D56" t="n">
-        <v>-3673611</v>
+        <v>-1350330</v>
       </c>
       <c r="E56" t="n">
-        <v>-1645357</v>
+        <v>-1701</v>
       </c>
       <c r="F56" t="n">
-        <v>-4651302</v>
+        <v>-1828177</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>士電</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -36 千股)</t>
+          <t>📈 20d 巨變(加碼 181 千股)</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>-190761</v>
+        <v>-8923</v>
       </c>
       <c r="D57" t="n">
-        <v>988559</v>
+        <v>-3492289</v>
       </c>
       <c r="E57" t="n">
-        <v>-300029</v>
+        <v>-351514</v>
       </c>
       <c r="F57" t="n">
-        <v>1024360</v>
+        <v>-3673611</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>鈊象</t>
         </is>
       </c>
     </row>
@@ -7423,20 +7423,20 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,507 千股)</t>
+          <t>📉 20d 巨變(減碼 -862 千股)</t>
         </is>
       </c>
       <c r="C58" t="n">
+        <v>-2289673</v>
+      </c>
+      <c r="D58" t="n">
+        <v>-5973401</v>
+      </c>
+      <c r="E58" t="n">
         <v>-644357</v>
       </c>
-      <c r="D58" t="n">
+      <c r="F58" t="n">
         <v>-5111833</v>
-      </c>
-      <c r="E58" t="n">
-        <v>-645510</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-3604968</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -7447,58 +7447,58 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -127 千股)</t>
+          <t>📉 20d 巨變(減碼 -206 千股)</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>-135730</v>
+        <v>-169018</v>
       </c>
       <c r="D59" t="n">
-        <v>-753135</v>
+        <v>782519</v>
       </c>
       <c r="E59" t="n">
-        <v>99395</v>
+        <v>-190761</v>
       </c>
       <c r="F59" t="n">
-        <v>-625797</v>
+        <v>988559</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>達欣工</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -62 千股)</t>
+          <t>📈 20d 巨變(加碼 31 千股)</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>-460802</v>
+        <v>-212730</v>
       </c>
       <c r="D60" t="n">
-        <v>-31917</v>
+        <v>-722511</v>
       </c>
       <c r="E60" t="n">
-        <v>-460602</v>
+        <v>-135730</v>
       </c>
       <c r="F60" t="n">
-        <v>30083</v>
+        <v>-753135</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>普萊德</t>
         </is>
       </c>
     </row>
@@ -7510,20 +7510,20 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -23 千股)</t>
+          <t>📈 20d 巨變(加碼 47 千股)</t>
         </is>
       </c>
       <c r="C61" t="n">
+        <v>452685</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1101286</v>
+      </c>
+      <c r="E61" t="n">
         <v>606468</v>
       </c>
-      <c r="D61" t="n">
+      <c r="F61" t="n">
         <v>1054563</v>
-      </c>
-      <c r="E61" t="n">
-        <v>730406</v>
-      </c>
-      <c r="F61" t="n">
-        <v>1078023</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -7539,20 +7539,20 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -65 千股)</t>
+          <t>📈 20d 巨變(加碼 30 千股)</t>
         </is>
       </c>
       <c r="C62" t="n">
+        <v>339584</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1109545</v>
+      </c>
+      <c r="E62" t="n">
         <v>476000</v>
       </c>
-      <c r="D62" t="n">
+      <c r="F62" t="n">
         <v>1079295</v>
-      </c>
-      <c r="E62" t="n">
-        <v>687098</v>
-      </c>
-      <c r="F62" t="n">
-        <v>1144412</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -7563,203 +7563,203 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,226 千股)</t>
+          <t>📉 20d 巨變(減碼 -58 千股)</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-790450</v>
+        <v>-458462</v>
       </c>
       <c r="D63" t="n">
-        <v>3593644</v>
+        <v>-89666</v>
       </c>
       <c r="E63" t="n">
-        <v>-434306</v>
+        <v>-460802</v>
       </c>
       <c r="F63" t="n">
-        <v>4819709</v>
+        <v>-31917</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>信立</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -35 千股)</t>
+          <t>📉 20d 巨變(減碼 -239 千股)</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>-490858</v>
+        <v>-313334</v>
       </c>
       <c r="D64" t="n">
-        <v>724306</v>
+        <v>286589</v>
       </c>
       <c r="E64" t="n">
-        <v>-764731</v>
+        <v>-58567</v>
       </c>
       <c r="F64" t="n">
-        <v>759801</v>
+        <v>525660</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>祥碩</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 2,116 千股)</t>
+          <t>📉 20d 巨變(減碼 -605 千股)</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>335625</v>
+        <v>-2813216</v>
       </c>
       <c r="D65" t="n">
-        <v>-995687</v>
+        <v>119299</v>
       </c>
       <c r="E65" t="n">
-        <v>115</v>
+        <v>-490858</v>
       </c>
       <c r="F65" t="n">
-        <v>-3111902</v>
+        <v>724306</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>華星光</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -451 千股)</t>
+          <t>📉 20d 巨變(減碼 -125 千股)</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-1240264</v>
+        <v>-2013643</v>
       </c>
       <c r="D66" t="n">
-        <v>-4196241</v>
+        <v>3469071</v>
       </c>
       <c r="E66" t="n">
-        <v>-1338212</v>
+        <v>-790450</v>
       </c>
       <c r="F66" t="n">
-        <v>-3745568</v>
+        <v>3593644</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>藥華藥</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 5,832 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -48 千股)</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-13631280</v>
+        <v>-633698</v>
       </c>
       <c r="D67" t="n">
-        <v>-42872546</v>
+        <v>4039494</v>
       </c>
       <c r="E67" t="n">
-        <v>-8150064</v>
+        <v>392015</v>
       </c>
       <c r="F67" t="n">
-        <v>-48704288</v>
+        <v>4087628</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>聯亞</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 404 千股)</t>
+          <t>📈 20d 巨變(加碼 8,368 千股)</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>392015</v>
+        <v>-16776571</v>
       </c>
       <c r="D68" t="n">
-        <v>4087628</v>
+        <v>-34504936</v>
       </c>
       <c r="E68" t="n">
-        <v>477285</v>
+        <v>-13631280</v>
       </c>
       <c r="F68" t="n">
-        <v>3683344</v>
+        <v>-42872546</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,604 千股)</t>
+          <t>📉 20d 巨變(減碼 -865 千股)</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-4746435</v>
+        <v>-1896495</v>
       </c>
       <c r="D69" t="n">
-        <v>-13102584</v>
+        <v>-5061734</v>
       </c>
       <c r="E69" t="n">
-        <v>-7472403</v>
+        <v>-1240264</v>
       </c>
       <c r="F69" t="n">
-        <v>-14706110</v>
+        <v>-4196241</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>宇瞻</t>
         </is>
       </c>
     </row>
@@ -7771,20 +7771,20 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 9,669 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,787 千股)</t>
         </is>
       </c>
       <c r="C70" t="n">
+        <v>-33660192</v>
+      </c>
+      <c r="D70" t="n">
+        <v>-210391670</v>
+      </c>
+      <c r="E70" t="n">
         <v>-36612809</v>
       </c>
-      <c r="D70" t="n">
+      <c r="F70" t="n">
         <v>-208604968</v>
-      </c>
-      <c r="E70" t="n">
-        <v>-50014891</v>
-      </c>
-      <c r="F70" t="n">
-        <v>-218274214</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -7795,87 +7795,87 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,662 千股)</t>
+          <t>📈 20d 巨變(加碼 2,948 千股)</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>10254634</v>
+        <v>-2706331</v>
       </c>
       <c r="D71" t="n">
-        <v>20887461</v>
+        <v>-10154168</v>
       </c>
       <c r="E71" t="n">
-        <v>13986990</v>
+        <v>-4746435</v>
       </c>
       <c r="F71" t="n">
-        <v>19225034</v>
+        <v>-13102584</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>瑞昱</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -464 千股)</t>
+          <t>📉 20d 巨變(減碼 -903 千股)</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-313847</v>
+        <v>6277490</v>
       </c>
       <c r="D72" t="n">
-        <v>-19126353</v>
+        <v>19984601</v>
       </c>
       <c r="E72" t="n">
-        <v>-2746133</v>
+        <v>10254634</v>
       </c>
       <c r="F72" t="n">
-        <v>-18662602</v>
+        <v>20887461</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -23 千股)</t>
+          <t>📉 20d 巨變(減碼 -2,907 千股)</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>15000</v>
+        <v>-1936244</v>
       </c>
       <c r="D73" t="n">
-        <v>-469564</v>
+        <v>-22033033</v>
       </c>
       <c r="E73" t="n">
-        <v>64000</v>
+        <v>-313847</v>
       </c>
       <c r="F73" t="n">
-        <v>-446414</v>
+        <v>-19126353</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>台汽電</t>
         </is>
       </c>
     </row>
@@ -7887,20 +7887,20 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -178 千股)</t>
+          <t>📈 20d 巨變(加碼 29 千股)</t>
         </is>
       </c>
       <c r="C74" t="n">
+        <v>-579959</v>
+      </c>
+      <c r="D74" t="n">
+        <v>-717235</v>
+      </c>
+      <c r="E74" t="n">
         <v>-643959</v>
       </c>
-      <c r="D74" t="n">
+      <c r="F74" t="n">
         <v>-745865</v>
-      </c>
-      <c r="E74" t="n">
-        <v>-570959</v>
-      </c>
-      <c r="F74" t="n">
-        <v>-567865</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -7916,20 +7916,20 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -81 千股)</t>
+          <t>📉 20d 巨變(減碼 -619 千股)</t>
         </is>
       </c>
       <c r="C75" t="n">
+        <v>-797741</v>
+      </c>
+      <c r="D75" t="n">
+        <v>78314</v>
+      </c>
+      <c r="E75" t="n">
         <v>-195478</v>
       </c>
-      <c r="D75" t="n">
+      <c r="F75" t="n">
         <v>697007</v>
-      </c>
-      <c r="E75" t="n">
-        <v>-68968</v>
-      </c>
-      <c r="F75" t="n">
-        <v>778464</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -7940,29 +7940,29 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -165 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 58 千股)</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-83216</v>
+        <v>-35000</v>
       </c>
       <c r="D76" t="n">
-        <v>3343533</v>
+        <v>-411564</v>
       </c>
       <c r="E76" t="n">
-        <v>-767580</v>
+        <v>15000</v>
       </c>
       <c r="F76" t="n">
-        <v>3508622</v>
+        <v>-469564</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>友輝</t>
         </is>
       </c>
     </row>
@@ -7974,20 +7974,20 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -1,172 千股)</t>
+          <t>📉 20d 巨變(減碼 -713 千股)</t>
         </is>
       </c>
       <c r="C77" t="n">
+        <v>-1954648</v>
+      </c>
+      <c r="D77" t="n">
+        <v>5077736</v>
+      </c>
+      <c r="E77" t="n">
         <v>-1274972</v>
       </c>
-      <c r="D77" t="n">
+      <c r="F77" t="n">
         <v>5790425</v>
-      </c>
-      <c r="E77" t="n">
-        <v>1271979</v>
-      </c>
-      <c r="F77" t="n">
-        <v>6962047</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -7998,116 +7998,116 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,048 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -420 千股)</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-1012931</v>
+        <v>299534</v>
       </c>
       <c r="D78" t="n">
-        <v>-6473840</v>
+        <v>2923903</v>
       </c>
       <c r="E78" t="n">
-        <v>-5444650</v>
+        <v>-83216</v>
       </c>
       <c r="F78" t="n">
-        <v>-7521457</v>
+        <v>3343533</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>智易</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -16,322 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 4,185 千股)</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-24400677</v>
+        <v>1264568</v>
       </c>
       <c r="D79" t="n">
-        <v>-37358945</v>
+        <v>-2288735</v>
       </c>
       <c r="E79" t="n">
-        <v>-27474758</v>
+        <v>-1012931</v>
       </c>
       <c r="F79" t="n">
-        <v>-21036834</v>
+        <v>-6473840</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>啟碁</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 250 千股)</t>
+          <t>📉 20d 巨變(減碼 -3,452 千股)</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>-38993</v>
+        <v>-17187609</v>
       </c>
       <c r="D80" t="n">
-        <v>307109</v>
+        <v>-40811097</v>
       </c>
       <c r="E80" t="n">
-        <v>-82231</v>
+        <v>-24400677</v>
       </c>
       <c r="F80" t="n">
-        <v>57541</v>
+        <v>-37358945</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -659 千股)</t>
+          <t>📉 20d 巨變(減碼 -66 千股)</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-717342</v>
+        <v>-90882</v>
       </c>
       <c r="D81" t="n">
-        <v>-5682910</v>
+        <v>240815</v>
       </c>
       <c r="E81" t="n">
-        <v>-932344</v>
+        <v>-38993</v>
       </c>
       <c r="F81" t="n">
-        <v>-5023571</v>
+        <v>307109</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>精測</t>
         </is>
       </c>
     </row>
@@ -8119,20 +8119,20 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 14,960 千股)</t>
+          <t>📈 20d 巨變(加碼 14,327 千股)</t>
         </is>
       </c>
       <c r="C82" t="n">
+        <v>-20766181</v>
+      </c>
+      <c r="D82" t="n">
+        <v>-196111151</v>
+      </c>
+      <c r="E82" t="n">
         <v>-51756901</v>
       </c>
-      <c r="D82" t="n">
+      <c r="F82" t="n">
         <v>-210437915</v>
-      </c>
-      <c r="E82" t="n">
-        <v>-73455454</v>
-      </c>
-      <c r="F82" t="n">
-        <v>-225398231</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -8148,20 +8148,20 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -95 千股)</t>
+          <t>📈 20d 巨變(加碼 44 千股)</t>
         </is>
       </c>
       <c r="C83" t="n">
+        <v>-14830</v>
+      </c>
+      <c r="D83" t="n">
+        <v>329194</v>
+      </c>
+      <c r="E83" t="n">
         <v>-8580</v>
       </c>
-      <c r="D83" t="n">
+      <c r="F83" t="n">
         <v>284972</v>
-      </c>
-      <c r="E83" t="n">
-        <v>65443</v>
-      </c>
-      <c r="F83" t="n">
-        <v>379972</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -8172,87 +8172,87 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -5 千股)</t>
+          <t>📉 20d 巨變(減碼 -572 千股)</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-59466</v>
+        <v>-1193641</v>
       </c>
       <c r="D84" t="n">
-        <v>-1108558</v>
+        <v>-6254690</v>
       </c>
       <c r="E84" t="n">
-        <v>-4466</v>
+        <v>-717342</v>
       </c>
       <c r="F84" t="n">
-        <v>-1103558</v>
+        <v>-5682910</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>鑫龍騰</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -1,198 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 369 千股)</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>-903490</v>
+        <v>55065</v>
       </c>
       <c r="D85" t="n">
-        <v>771638</v>
+        <v>-739558</v>
       </c>
       <c r="E85" t="n">
-        <v>191000</v>
+        <v>-59466</v>
       </c>
       <c r="F85" t="n">
-        <v>1970078</v>
+        <v>-1108558</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>鑫龍騰</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 501 千股)</t>
+          <t>📉 20d 巨變(減碼 -189 千股)</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-1347436</v>
+        <v>-1471571</v>
       </c>
       <c r="D86" t="n">
-        <v>-3672853</v>
+        <v>582620</v>
       </c>
       <c r="E86" t="n">
-        <v>-3097053</v>
+        <v>-903490</v>
       </c>
       <c r="F86" t="n">
-        <v>-4173754</v>
+        <v>771638</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>全友</t>
         </is>
       </c>
     </row>
@@ -8264,20 +8264,20 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -21 千股)</t>
+          <t>📈 20d 巨變(加碼 855 千股)</t>
         </is>
       </c>
       <c r="C87" t="n">
+        <v>1504570</v>
+      </c>
+      <c r="D87" t="n">
+        <v>4238328</v>
+      </c>
+      <c r="E87" t="n">
         <v>1092103</v>
       </c>
-      <c r="D87" t="n">
+      <c r="F87" t="n">
         <v>3383255</v>
-      </c>
-      <c r="E87" t="n">
-        <v>1665029</v>
-      </c>
-      <c r="F87" t="n">
-        <v>3404004</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -8288,29 +8288,29 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -217 千股)</t>
+          <t>📈 20d 巨變(加碼 460 千股)</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>-33420</v>
+        <v>-1726873</v>
       </c>
       <c r="D88" t="n">
-        <v>-6121929</v>
+        <v>-3212630</v>
       </c>
       <c r="E88" t="n">
-        <v>-341679</v>
+        <v>-1347436</v>
       </c>
       <c r="F88" t="n">
-        <v>-5905203</v>
+        <v>-3672853</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>宏捷科</t>
         </is>
       </c>
     </row>
@@ -8322,20 +8322,20 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -18,589 千股)</t>
+          <t>📈 20d 巨變(加碼 1,123 千股)</t>
         </is>
       </c>
       <c r="C89" t="n">
+        <v>-33457248</v>
+      </c>
+      <c r="D89" t="n">
+        <v>-88982939</v>
+      </c>
+      <c r="E89" t="n">
         <v>-50794188</v>
       </c>
-      <c r="D89" t="n">
+      <c r="F89" t="n">
         <v>-90105685</v>
-      </c>
-      <c r="E89" t="n">
-        <v>-44628836</v>
-      </c>
-      <c r="F89" t="n">
-        <v>-71516742</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -8346,58 +8346,58 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 61 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 5 千股)</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>-39563</v>
+        <v>316313</v>
       </c>
       <c r="D90" t="n">
-        <v>-87088</v>
+        <v>-6116747</v>
       </c>
       <c r="E90" t="n">
-        <v>-89217</v>
+        <v>-33420</v>
       </c>
       <c r="F90" t="n">
-        <v>-147917</v>
+        <v>-6121929</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>中保科</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -34 千股)</t>
+          <t>📉 20d 巨變(減碼 -61 千股)</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>12202</v>
+        <v>-89468</v>
       </c>
       <c r="D91" t="n">
-        <v>-472192</v>
+        <v>-148545</v>
       </c>
       <c r="E91" t="n">
-        <v>-20838</v>
+        <v>-39563</v>
       </c>
       <c r="F91" t="n">
-        <v>-438306</v>
+        <v>-87088</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>竹陞科技</t>
         </is>
       </c>
     </row>
@@ -8409,20 +8409,20 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -585 千股)</t>
+          <t>📈 20d 巨變(加碼 1,481 千股)</t>
         </is>
       </c>
       <c r="C92" t="n">
+        <v>1346923</v>
+      </c>
+      <c r="D92" t="n">
+        <v>8655988</v>
+      </c>
+      <c r="E92" t="n">
         <v>2171650</v>
       </c>
-      <c r="D92" t="n">
+      <c r="F92" t="n">
         <v>7174540</v>
-      </c>
-      <c r="E92" t="n">
-        <v>3986842</v>
-      </c>
-      <c r="F92" t="n">
-        <v>7759116</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -8433,58 +8433,58 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -5 千股)</t>
+          <t>📈 20d 巨變(加碼 42 千股)</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>39000</v>
+        <v>33616</v>
       </c>
       <c r="D93" t="n">
-        <v>157067</v>
+        <v>-430382</v>
       </c>
       <c r="E93" t="n">
-        <v>62000</v>
+        <v>12202</v>
       </c>
       <c r="F93" t="n">
-        <v>162067</v>
+        <v>-472192</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>安碁資訊</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,080 千股)</t>
+          <t>📉 20d 巨變(減碼 -21 千股)</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-4326686</v>
+        <v>9000</v>
       </c>
       <c r="D94" t="n">
-        <v>-1782828</v>
+        <v>135847</v>
       </c>
       <c r="E94" t="n">
-        <v>-2763754</v>
+        <v>39000</v>
       </c>
       <c r="F94" t="n">
-        <v>-2863058</v>
+        <v>157067</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>六方科-KY</t>
         </is>
       </c>
     </row>
@@ -8496,20 +8496,20 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -19,361 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -13,399 千股)</t>
         </is>
       </c>
       <c r="C95" t="n">
+        <v>-27735143</v>
+      </c>
+      <c r="D95" t="n">
+        <v>-209936265</v>
+      </c>
+      <c r="E95" t="n">
         <v>20454693</v>
       </c>
-      <c r="D95" t="n">
+      <c r="F95" t="n">
         <v>-196537443</v>
-      </c>
-      <c r="E95" t="n">
-        <v>-10606966</v>
-      </c>
-      <c r="F95" t="n">
-        <v>-177176220</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -8520,116 +8520,116 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -2,907 千股)</t>
+          <t>📈 20d 巨變(加碼 749 千股)</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>-30456091</v>
+        <v>-3902539</v>
       </c>
       <c r="D96" t="n">
-        <v>-154694218</v>
+        <v>-1033870</v>
       </c>
       <c r="E96" t="n">
-        <v>-35826517</v>
+        <v>-4326686</v>
       </c>
       <c r="F96" t="n">
-        <v>-151787473</v>
+        <v>-1782828</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>聯發科</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -62 千股)</t>
+          <t>📉 20d 巨變(減碼 -306 千股)</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>-1281761</v>
+        <v>-874364</v>
       </c>
       <c r="D97" t="n">
-        <v>-4060574</v>
+        <v>-5350977</v>
       </c>
       <c r="E97" t="n">
-        <v>-1212339</v>
+        <v>-190875</v>
       </c>
       <c r="F97" t="n">
-        <v>-3998149</v>
+        <v>-5045426</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>創意</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 10 千股)</t>
+          <t>📉 20d 巨變(減碼 -795 千股)</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-18216</v>
+        <v>-796614</v>
       </c>
       <c r="D98" t="n">
-        <v>269456</v>
+        <v>-4855800</v>
       </c>
       <c r="E98" t="n">
-        <v>21855</v>
+        <v>-1281761</v>
       </c>
       <c r="F98" t="n">
-        <v>259786</v>
+        <v>-4060574</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>緯穎</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -388 千股)</t>
+          <t>📈 20d 巨變(加碼 78 千股)</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>-190875</v>
+        <v>-12462</v>
       </c>
       <c r="D99" t="n">
-        <v>-5045426</v>
+        <v>347553</v>
       </c>
       <c r="E99" t="n">
-        <v>26933</v>
+        <v>-18216</v>
       </c>
       <c r="F99" t="n">
-        <v>-4657051</v>
+        <v>269456</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>信驊</t>
         </is>
       </c>
     </row>
@@ -8641,20 +8641,20 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 643 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 1,866 千股)</t>
         </is>
       </c>
       <c r="C100" t="n">
+        <v>1182641</v>
+      </c>
+      <c r="D100" t="n">
+        <v>3813387</v>
+      </c>
+      <c r="E100" t="n">
         <v>-810252</v>
       </c>
-      <c r="D100" t="n">
+      <c r="F100" t="n">
         <v>1947807</v>
-      </c>
-      <c r="E100" t="n">
-        <v>-862126</v>
-      </c>
-      <c r="F100" t="n">
-        <v>1304794</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -8665,56 +8665,85 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -541 千股)</t>
+          <t>📈 20d 巨變(加碼 4,031 千股)</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>239213</v>
+        <v>-17284376</v>
       </c>
       <c r="D101" t="n">
-        <v>1107633</v>
+        <v>-150663423</v>
       </c>
       <c r="E101" t="n">
-        <v>-38286</v>
+        <v>-30456091</v>
       </c>
       <c r="F101" t="n">
-        <v>1648677</v>
+        <v>-154694218</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
+          <t>5439</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -620 千股)</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>-568581</v>
+      </c>
+      <c r="D102" t="n">
+        <v>487443</v>
+      </c>
+      <c r="E102" t="n">
+        <v>239213</v>
+      </c>
+      <c r="F102" t="n">
+        <v>1107633</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>高技</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
           <t>6187</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 1,247 千股)</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 694 千股)</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>1471521</v>
+      </c>
+      <c r="D103" t="n">
+        <v>-73831</v>
+      </c>
+      <c r="E103" t="n">
         <v>454283</v>
       </c>
-      <c r="D102" t="n">
+      <c r="F103" t="n">
         <v>-768180</v>
       </c>
-      <c r="E102" t="n">
-        <v>398811</v>
-      </c>
-      <c r="F102" t="n">
-        <v>-2015499</v>
-      </c>
-      <c r="G102" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t>萬潤</t>
         </is>

--- a/data/台股_外資雷達.xlsx
+++ b/data/台股_外資雷達.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="總覽" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="翻轉警報" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -502,7 +501,7 @@
         <v>294172</v>
       </c>
       <c r="E2" t="n">
-        <v>7951</v>
+        <v>23008</v>
       </c>
       <c r="F2" t="n">
         <v>2021</v>
@@ -532,7 +531,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="3">
@@ -553,7 +552,7 @@
         <v>46804</v>
       </c>
       <c r="E3" t="n">
-        <v>-8845</v>
+        <v>-5248</v>
       </c>
       <c r="F3" t="n">
         <v>7760</v>
@@ -604,7 +603,7 @@
         <v>19985</v>
       </c>
       <c r="E4" t="n">
-        <v>136480</v>
+        <v>123616</v>
       </c>
       <c r="F4" t="n">
         <v>-2524</v>
@@ -634,7 +633,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -655,7 +654,7 @@
         <v>8850</v>
       </c>
       <c r="E5" t="n">
-        <v>161875</v>
+        <v>115843</v>
       </c>
       <c r="F5" t="n">
         <v>-2388</v>
@@ -706,7 +705,7 @@
         <v>8656</v>
       </c>
       <c r="E6" t="n">
-        <v>12174</v>
+        <v>12546</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -757,7 +756,7 @@
         <v>7938</v>
       </c>
       <c r="E7" t="n">
-        <v>11739</v>
+        <v>12603</v>
       </c>
       <c r="F7" t="n">
         <v>-1065</v>
@@ -787,7 +786,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -808,7 +807,7 @@
         <v>6149</v>
       </c>
       <c r="E8" t="n">
-        <v>11351</v>
+        <v>9747</v>
       </c>
       <c r="F8" t="n">
         <v>-1688</v>
@@ -859,7 +858,7 @@
         <v>5078</v>
       </c>
       <c r="E9" t="n">
-        <v>8095</v>
+        <v>8177</v>
       </c>
       <c r="F9" t="n">
         <v>1843</v>
@@ -910,7 +909,7 @@
         <v>4238</v>
       </c>
       <c r="E10" t="n">
-        <v>18403</v>
+        <v>16126</v>
       </c>
       <c r="F10" t="n">
         <v>121</v>
@@ -940,7 +939,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11">
@@ -961,7 +960,7 @@
         <v>4039</v>
       </c>
       <c r="E11" t="n">
-        <v>1968</v>
+        <v>1135</v>
       </c>
       <c r="F11" t="n">
         <v>-86</v>
@@ -1012,7 +1011,7 @@
         <v>3813</v>
       </c>
       <c r="E12" t="n">
-        <v>7808</v>
+        <v>9225</v>
       </c>
       <c r="F12" t="n">
         <v>-1792</v>
@@ -1051,7 +1050,7 @@
         <v>3469</v>
       </c>
       <c r="E13" t="n">
-        <v>14828</v>
+        <v>14836</v>
       </c>
       <c r="F13" t="n">
         <v>209</v>
@@ -1102,7 +1101,7 @@
         <v>3319</v>
       </c>
       <c r="E14" t="n">
-        <v>2541</v>
+        <v>2743</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1132,7 +1131,7 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15">
@@ -1153,7 +1152,7 @@
         <v>2924</v>
       </c>
       <c r="E15" t="n">
-        <v>6116</v>
+        <v>6374</v>
       </c>
       <c r="F15" t="n">
         <v>35</v>
@@ -1183,7 +1182,7 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="16">
@@ -1204,7 +1203,7 @@
         <v>2742</v>
       </c>
       <c r="E16" t="n">
-        <v>-1347</v>
+        <v>-1501</v>
       </c>
       <c r="F16" t="n">
         <v>-294</v>
@@ -1255,7 +1254,7 @@
         <v>2626</v>
       </c>
       <c r="E17" t="n">
-        <v>2673</v>
+        <v>2300</v>
       </c>
       <c r="F17" t="n">
         <v>-10</v>
@@ -1306,7 +1305,7 @@
         <v>2048</v>
       </c>
       <c r="E18" t="n">
-        <v>-7393</v>
+        <v>-6041</v>
       </c>
       <c r="F18" t="n">
         <v>637</v>
@@ -1336,7 +1335,7 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1357,7 +1356,7 @@
         <v>1879</v>
       </c>
       <c r="E19" t="n">
-        <v>3101</v>
+        <v>2826</v>
       </c>
       <c r="F19" t="n">
         <v>-767</v>
@@ -1387,7 +1386,7 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1408,7 +1407,7 @@
         <v>1707</v>
       </c>
       <c r="E20" t="n">
-        <v>-1240</v>
+        <v>-1366</v>
       </c>
       <c r="F20" t="n">
         <v>-42</v>
@@ -1459,7 +1458,7 @@
         <v>1110</v>
       </c>
       <c r="E21" t="n">
-        <v>1861</v>
+        <v>2469</v>
       </c>
       <c r="F21" t="n">
         <v>34</v>
@@ -1489,7 +1488,7 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="22">
@@ -1510,7 +1509,7 @@
         <v>1101</v>
       </c>
       <c r="E22" t="n">
-        <v>1505</v>
+        <v>1252</v>
       </c>
       <c r="F22" t="n">
         <v>1</v>
@@ -1561,7 +1560,7 @@
         <v>877</v>
       </c>
       <c r="E23" t="n">
-        <v>3404</v>
+        <v>3093</v>
       </c>
       <c r="F23" t="n">
         <v>-61</v>
@@ -1591,7 +1590,7 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1612,7 +1611,7 @@
         <v>783</v>
       </c>
       <c r="E24" t="n">
-        <v>144</v>
+        <v>667</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
@@ -1663,7 +1662,7 @@
         <v>583</v>
       </c>
       <c r="E25" t="n">
-        <v>6093</v>
+        <v>5627</v>
       </c>
       <c r="F25" t="n">
         <v>-1</v>
@@ -1714,7 +1713,7 @@
         <v>487</v>
       </c>
       <c r="E26" t="n">
-        <v>-4226</v>
+        <v>-2376</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -1753,7 +1752,7 @@
         <v>393</v>
       </c>
       <c r="E27" t="n">
-        <v>787</v>
+        <v>623</v>
       </c>
       <c r="F27" t="n">
         <v>-22</v>
@@ -1804,7 +1803,7 @@
         <v>375</v>
       </c>
       <c r="E28" t="n">
-        <v>2273</v>
+        <v>2289</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -1855,7 +1854,7 @@
         <v>348</v>
       </c>
       <c r="E29" t="n">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="F29" t="n">
         <v>-230</v>
@@ -1894,7 +1893,7 @@
         <v>329</v>
       </c>
       <c r="E30" t="n">
-        <v>-162</v>
+        <v>-203</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -1945,7 +1944,7 @@
         <v>328</v>
       </c>
       <c r="E31" t="n">
-        <v>551</v>
+        <v>520</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1996,7 +1995,7 @@
         <v>323</v>
       </c>
       <c r="E32" t="n">
-        <v>-8283</v>
+        <v>-8626</v>
       </c>
       <c r="F32" t="n">
         <v>-2</v>
@@ -2026,7 +2025,7 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="33">
@@ -2047,7 +2046,7 @@
         <v>287</v>
       </c>
       <c r="E33" t="n">
-        <v>-1314</v>
+        <v>-1093</v>
       </c>
       <c r="F33" t="n">
         <v>803</v>
@@ -2098,7 +2097,7 @@
         <v>286</v>
       </c>
       <c r="E34" t="n">
-        <v>410</v>
+        <v>464</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -2149,7 +2148,7 @@
         <v>241</v>
       </c>
       <c r="E35" t="n">
-        <v>-158</v>
+        <v>-135</v>
       </c>
       <c r="F35" t="n">
         <v>-240</v>
@@ -2200,7 +2199,7 @@
         <v>136</v>
       </c>
       <c r="E36" t="n">
-        <v>-24</v>
+        <v>-22</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -2251,7 +2250,7 @@
         <v>119</v>
       </c>
       <c r="E37" t="n">
-        <v>-7878</v>
+        <v>-8194</v>
       </c>
       <c r="F37" t="n">
         <v>-106</v>
@@ -2281,7 +2280,7 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="38">
@@ -2302,7 +2301,7 @@
         <v>79</v>
       </c>
       <c r="E38" t="n">
-        <v>4386</v>
+        <v>5096</v>
       </c>
       <c r="F38" t="n">
         <v>695</v>
@@ -2353,7 +2352,7 @@
         <v>78</v>
       </c>
       <c r="E39" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -2404,7 +2403,7 @@
         <v>76</v>
       </c>
       <c r="E40" t="n">
-        <v>-1348</v>
+        <v>-1356</v>
       </c>
       <c r="F40" t="n">
         <v>-7</v>
@@ -2455,7 +2454,7 @@
         <v>16</v>
       </c>
       <c r="E41" t="n">
-        <v>-902</v>
+        <v>-471</v>
       </c>
       <c r="F41" t="n">
         <v>279</v>
@@ -2506,7 +2505,7 @@
         <v>-10</v>
       </c>
       <c r="E42" t="n">
-        <v>-63</v>
+        <v>-77</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -2557,7 +2556,7 @@
         <v>-29</v>
       </c>
       <c r="E43" t="n">
-        <v>-3678</v>
+        <v>-3122</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -2608,7 +2607,7 @@
         <v>-68</v>
       </c>
       <c r="E44" t="n">
-        <v>1724</v>
+        <v>1438</v>
       </c>
       <c r="F44" t="n">
         <v>-77</v>
@@ -2659,7 +2658,7 @@
         <v>-74</v>
       </c>
       <c r="E45" t="n">
-        <v>-4551</v>
+        <v>-5933</v>
       </c>
       <c r="F45" t="n">
         <v>248</v>
@@ -2698,7 +2697,7 @@
         <v>-87</v>
       </c>
       <c r="E46" t="n">
-        <v>3196</v>
+        <v>2573</v>
       </c>
       <c r="F46" t="n">
         <v>506</v>
@@ -2749,7 +2748,7 @@
         <v>-90</v>
       </c>
       <c r="E47" t="n">
-        <v>-802</v>
+        <v>-650</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -2779,7 +2778,7 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -2851,7 +2850,7 @@
         <v>-149</v>
       </c>
       <c r="E49" t="n">
-        <v>-284</v>
+        <v>-227</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -2881,7 +2880,7 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -2902,7 +2901,7 @@
         <v>-172</v>
       </c>
       <c r="E50" t="n">
-        <v>-5059</v>
+        <v>-5088</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -2932,7 +2931,7 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -2953,7 +2952,7 @@
         <v>-234</v>
       </c>
       <c r="E51" t="n">
-        <v>1084</v>
+        <v>1077</v>
       </c>
       <c r="F51" t="n">
         <v>-512</v>
@@ -2983,7 +2982,7 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3004,7 +3003,7 @@
         <v>-276</v>
       </c>
       <c r="E52" t="n">
-        <v>-3411</v>
+        <v>-3195</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -3055,7 +3054,7 @@
         <v>-412</v>
       </c>
       <c r="E53" t="n">
-        <v>467</v>
+        <v>822</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -3106,7 +3105,7 @@
         <v>-430</v>
       </c>
       <c r="E54" t="n">
-        <v>-236</v>
+        <v>-239</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -3157,7 +3156,7 @@
         <v>-437</v>
       </c>
       <c r="E55" t="n">
-        <v>-138</v>
+        <v>-404</v>
       </c>
       <c r="F55" t="n">
         <v>201</v>
@@ -3208,7 +3207,7 @@
         <v>-519</v>
       </c>
       <c r="E56" t="n">
-        <v>2188</v>
+        <v>2106</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -3259,7 +3258,7 @@
         <v>-633</v>
       </c>
       <c r="E57" t="n">
-        <v>-838</v>
+        <v>-828</v>
       </c>
       <c r="F57" t="n">
         <v>-1</v>
@@ -3310,7 +3309,7 @@
         <v>-707</v>
       </c>
       <c r="E58" t="n">
-        <v>-392</v>
+        <v>-1274</v>
       </c>
       <c r="F58" t="n">
         <v>35</v>
@@ -3361,7 +3360,7 @@
         <v>-712</v>
       </c>
       <c r="E59" t="n">
-        <v>-669</v>
+        <v>-783</v>
       </c>
       <c r="F59" t="n">
         <v>303</v>
@@ -3412,7 +3411,7 @@
         <v>-717</v>
       </c>
       <c r="E60" t="n">
-        <v>-2483</v>
+        <v>-2766</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -3463,7 +3462,7 @@
         <v>-723</v>
       </c>
       <c r="E61" t="n">
-        <v>-1985</v>
+        <v>-1927</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -3514,7 +3513,7 @@
         <v>-740</v>
       </c>
       <c r="E62" t="n">
-        <v>-2892</v>
+        <v>-2983</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -3565,7 +3564,7 @@
         <v>-776</v>
       </c>
       <c r="E63" t="n">
-        <v>-4728</v>
+        <v>-4865</v>
       </c>
       <c r="F63" t="n">
         <v>523</v>
@@ -3616,7 +3615,7 @@
         <v>-915</v>
       </c>
       <c r="E64" t="n">
-        <v>-3936</v>
+        <v>-3282</v>
       </c>
       <c r="F64" t="n">
         <v>8</v>
@@ -3646,7 +3645,7 @@
         </is>
       </c>
       <c r="M64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -3667,7 +3666,7 @@
         <v>-1000</v>
       </c>
       <c r="E65" t="n">
-        <v>-2859</v>
+        <v>-490</v>
       </c>
       <c r="F65" t="n">
         <v>-1</v>
@@ -3697,7 +3696,7 @@
         </is>
       </c>
       <c r="M65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -3718,7 +3717,7 @@
         <v>-1034</v>
       </c>
       <c r="E66" t="n">
-        <v>-6909</v>
+        <v>-8244</v>
       </c>
       <c r="F66" t="n">
         <v>-471</v>
@@ -3748,7 +3747,7 @@
         </is>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="67">
@@ -3769,7 +3768,7 @@
         <v>-1350</v>
       </c>
       <c r="E67" t="n">
-        <v>-6995</v>
+        <v>-7226</v>
       </c>
       <c r="F67" t="n">
         <v>5</v>
@@ -3820,7 +3819,7 @@
         <v>-1404</v>
       </c>
       <c r="E68" t="n">
-        <v>-738</v>
+        <v>-719</v>
       </c>
       <c r="F68" t="n">
         <v>355</v>
@@ -3871,7 +3870,7 @@
         <v>-1406</v>
       </c>
       <c r="E69" t="n">
-        <v>-328</v>
+        <v>-1046</v>
       </c>
       <c r="F69" t="n">
         <v>8</v>
@@ -3922,7 +3921,7 @@
         <v>-1429</v>
       </c>
       <c r="E70" t="n">
-        <v>-1921</v>
+        <v>-1577</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -3973,7 +3972,7 @@
         <v>-1514</v>
       </c>
       <c r="E71" t="n">
-        <v>-9068</v>
+        <v>-7965</v>
       </c>
       <c r="F71" t="n">
         <v>2033</v>
@@ -4003,7 +4002,7 @@
         </is>
       </c>
       <c r="M71" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -4024,7 +4023,7 @@
         <v>-1639</v>
       </c>
       <c r="E72" t="n">
-        <v>-9825</v>
+        <v>-8724</v>
       </c>
       <c r="F72" t="n">
         <v>-616</v>
@@ -4075,7 +4074,7 @@
         <v>-2145</v>
       </c>
       <c r="E73" t="n">
-        <v>-2040</v>
+        <v>-2270</v>
       </c>
       <c r="F73" t="n">
         <v>2282</v>
@@ -4126,7 +4125,7 @@
         <v>-2289</v>
       </c>
       <c r="E74" t="n">
-        <v>23414</v>
+        <v>27571</v>
       </c>
       <c r="F74" t="n">
         <v>-115</v>
@@ -4177,7 +4176,7 @@
         <v>-2564</v>
       </c>
       <c r="E75" t="n">
-        <v>-5899</v>
+        <v>-4513</v>
       </c>
       <c r="F75" t="n">
         <v>-179</v>
@@ -4228,7 +4227,7 @@
         <v>-2679</v>
       </c>
       <c r="E76" t="n">
-        <v>1805</v>
+        <v>181</v>
       </c>
       <c r="F76" t="n">
         <v>282</v>
@@ -4279,7 +4278,7 @@
         <v>-2979</v>
       </c>
       <c r="E77" t="n">
-        <v>-1695</v>
+        <v>-2170</v>
       </c>
       <c r="F77" t="n">
         <v>103</v>
@@ -4330,7 +4329,7 @@
         <v>-3047</v>
       </c>
       <c r="E78" t="n">
-        <v>-554</v>
+        <v>-536</v>
       </c>
       <c r="F78" t="n">
         <v>-447</v>
@@ -4381,7 +4380,7 @@
         <v>-3134</v>
       </c>
       <c r="E79" t="n">
-        <v>-73605</v>
+        <v>-80385</v>
       </c>
       <c r="F79" t="n">
         <v>-11</v>
@@ -4411,7 +4410,7 @@
         </is>
       </c>
       <c r="M79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -4432,7 +4431,7 @@
         <v>-3213</v>
       </c>
       <c r="E80" t="n">
-        <v>-2994</v>
+        <v>-4356</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
@@ -4462,7 +4461,7 @@
         </is>
       </c>
       <c r="M80" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="81">
@@ -4483,7 +4482,7 @@
         <v>-3492</v>
       </c>
       <c r="E81" t="n">
-        <v>-12924</v>
+        <v>-13319</v>
       </c>
       <c r="F81" t="n">
         <v>582</v>
@@ -4534,7 +4533,7 @@
         <v>-3975</v>
       </c>
       <c r="E82" t="n">
-        <v>-14796</v>
+        <v>-15278</v>
       </c>
       <c r="F82" t="n">
         <v>1420</v>
@@ -4585,7 +4584,7 @@
         <v>-4332</v>
       </c>
       <c r="E83" t="n">
-        <v>-7436</v>
+        <v>-7022</v>
       </c>
       <c r="F83" t="n">
         <v>5</v>
@@ -4636,7 +4635,7 @@
         <v>-4856</v>
       </c>
       <c r="E84" t="n">
-        <v>-9016</v>
+        <v>-7261</v>
       </c>
       <c r="F84" t="n">
         <v>1583</v>
@@ -4666,7 +4665,7 @@
         </is>
       </c>
       <c r="M84" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -4687,7 +4686,7 @@
         <v>-5062</v>
       </c>
       <c r="E85" t="n">
-        <v>-14191</v>
+        <v>-14340</v>
       </c>
       <c r="F85" t="n">
         <v>538</v>
@@ -4738,7 +4737,7 @@
         <v>-5351</v>
       </c>
       <c r="E86" t="n">
-        <v>-4789</v>
+        <v>-4944</v>
       </c>
       <c r="F86" t="n">
         <v>145</v>
@@ -4789,7 +4788,7 @@
         <v>-5467</v>
       </c>
       <c r="E87" t="n">
-        <v>-12736</v>
+        <v>-12729</v>
       </c>
       <c r="F87" t="n">
         <v>-542</v>
@@ -4840,7 +4839,7 @@
         <v>-5523</v>
       </c>
       <c r="E88" t="n">
-        <v>-62600</v>
+        <v>-61516</v>
       </c>
       <c r="F88" t="n">
         <v>216</v>
@@ -4891,7 +4890,7 @@
         <v>-5973</v>
       </c>
       <c r="E89" t="n">
-        <v>-8384</v>
+        <v>-7023</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -4942,7 +4941,7 @@
         <v>-6117</v>
       </c>
       <c r="E90" t="n">
-        <v>-5319</v>
+        <v>-5230</v>
       </c>
       <c r="F90" t="n">
         <v>361</v>
@@ -4993,7 +4992,7 @@
         <v>-6255</v>
       </c>
       <c r="E91" t="n">
-        <v>-18493</v>
+        <v>-13880</v>
       </c>
       <c r="F91" t="n">
         <v>1</v>
@@ -5044,7 +5043,7 @@
         <v>-8714</v>
       </c>
       <c r="E92" t="n">
-        <v>-14749</v>
+        <v>-13871</v>
       </c>
       <c r="F92" t="n">
         <v>1497</v>
@@ -5074,7 +5073,7 @@
         </is>
       </c>
       <c r="M92" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -5095,7 +5094,7 @@
         <v>-10154</v>
       </c>
       <c r="E93" t="n">
-        <v>-22140</v>
+        <v>-23643</v>
       </c>
       <c r="F93" t="n">
         <v>2673</v>
@@ -5146,7 +5145,7 @@
         <v>-16007</v>
       </c>
       <c r="E94" t="n">
-        <v>-39186</v>
+        <v>-35880</v>
       </c>
       <c r="F94" t="n">
         <v>231</v>
@@ -5197,7 +5196,7 @@
         <v>-18463</v>
       </c>
       <c r="E95" t="n">
-        <v>-28419</v>
+        <v>-28577</v>
       </c>
       <c r="F95" t="n">
         <v>-521</v>
@@ -5227,7 +5226,7 @@
         </is>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -5248,7 +5247,7 @@
         <v>-22033</v>
       </c>
       <c r="E96" t="n">
-        <v>977</v>
+        <v>528</v>
       </c>
       <c r="F96" t="n">
         <v>-15</v>
@@ -5299,7 +5298,7 @@
         <v>-26073</v>
       </c>
       <c r="E97" t="n">
-        <v>8331</v>
+        <v>12148</v>
       </c>
       <c r="F97" t="n">
         <v>14553</v>
@@ -5350,7 +5349,7 @@
         <v>-34505</v>
       </c>
       <c r="E98" t="n">
-        <v>-291564</v>
+        <v>-286027</v>
       </c>
       <c r="F98" t="n">
         <v>8880</v>
@@ -5380,7 +5379,7 @@
         </is>
       </c>
       <c r="M98" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="99">
@@ -5401,7 +5400,7 @@
         <v>-40811</v>
       </c>
       <c r="E99" t="n">
-        <v>60008</v>
+        <v>72145</v>
       </c>
       <c r="F99" t="n">
         <v>21313</v>
@@ -5431,7 +5430,7 @@
         </is>
       </c>
       <c r="M99" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -5452,7 +5451,7 @@
         <v>-76163</v>
       </c>
       <c r="E100" t="n">
-        <v>-309483</v>
+        <v>-268429</v>
       </c>
       <c r="F100" t="n">
         <v>2513</v>
@@ -5503,7 +5502,7 @@
         <v>-88983</v>
       </c>
       <c r="E101" t="n">
-        <v>-151366</v>
+        <v>-137702</v>
       </c>
       <c r="F101" t="n">
         <v>11766</v>
@@ -5554,7 +5553,7 @@
         <v>-150663</v>
       </c>
       <c r="E102" t="n">
-        <v>-171557</v>
+        <v>-169115</v>
       </c>
       <c r="F102" t="n">
         <v>15436</v>
@@ -5605,7 +5604,7 @@
         <v>-196111</v>
       </c>
       <c r="E103" t="n">
-        <v>390890</v>
+        <v>360681</v>
       </c>
       <c r="F103" t="n">
         <v>6242</v>
@@ -5656,7 +5655,7 @@
         <v>-209936</v>
       </c>
       <c r="E104" t="n">
-        <v>16140</v>
+        <v>-11438</v>
       </c>
       <c r="F104" t="n">
         <v>-40652</v>
@@ -5707,7 +5706,7 @@
         <v>-210392</v>
       </c>
       <c r="E105" t="n">
-        <v>-108144</v>
+        <v>-113002</v>
       </c>
       <c r="F105" t="n">
         <v>10690</v>
@@ -5737,3016 +5736,7 @@
         </is>
       </c>
       <c r="M105" t="n">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G103"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>訊號</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>外資5d</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>外資20d</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>外資5d(昨)</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>外資20d(昨)</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>8210</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 419 千股)</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>-338736</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-1638900</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-192820</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-2057993</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>勤誠</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>3017</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -90 千股)</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>-417700</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2047743</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-323609</v>
-      </c>
-      <c r="F3" t="n">
-        <v>2138123</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -523 千股)</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>-1546922</v>
-      </c>
-      <c r="D4" t="n">
-        <v>78601</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-1162691</v>
-      </c>
-      <c r="F4" t="n">
-        <v>601448</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>台光電</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>3653</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 621 千股)</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>157487</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2742229</v>
-      </c>
-      <c r="E5" t="n">
-        <v>94295</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2121244</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>8996</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -429 千股)</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>485589</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1879108</v>
-      </c>
-      <c r="E6" t="n">
-        <v>355100</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2307636</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>高力</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>6139</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 25 千股)</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>-4587432</v>
-      </c>
-      <c r="D7" t="n">
-        <v>-1514395</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-3897027</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-1539816</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>亞翔</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 129 千股)</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>2018468</v>
-      </c>
-      <c r="D8" t="n">
-        <v>6149043</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1234767</v>
-      </c>
-      <c r="F8" t="n">
-        <v>6020386</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>致茂</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 126 千股)</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>-1935914</v>
-      </c>
-      <c r="D9" t="n">
-        <v>-87220</v>
-      </c>
-      <c r="E9" t="n">
-        <v>-2046039</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-213285</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>智邦</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>3324</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 821 千股)</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>-1580184</v>
-      </c>
-      <c r="D10" t="n">
-        <v>-4332184</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-1297951</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-5152813</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>雙鴻</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>6442</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 231 千股)</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>81333</v>
-      </c>
-      <c r="D11" t="n">
-        <v>-707351</v>
-      </c>
-      <c r="E11" t="n">
-        <v>39903</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-938739</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>光聖</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -7,844 千股)</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>-29598185</v>
-      </c>
-      <c r="D12" t="n">
-        <v>-76162501</v>
-      </c>
-      <c r="E12" t="n">
-        <v>-29103170</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-68318244</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>台積電</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>6223</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 135 千股)</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>-237369</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-711587</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-260392</v>
-      </c>
-      <c r="F13" t="n">
-        <v>-846371</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>旺矽</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>6196</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 916 千股)</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>536850</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-233731</v>
-      </c>
-      <c r="E14" t="n">
-        <v>402</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-1149239</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>帆宣</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2308</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -369 千股)</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>-4659101</v>
-      </c>
-      <c r="D15" t="n">
-        <v>-18463334</v>
-      </c>
-      <c r="E15" t="n">
-        <v>-5334800</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-18094076</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>台達電</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>3583</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -195 千股)</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>-642866</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1706839</v>
-      </c>
-      <c r="E16" t="n">
-        <v>-744946</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1901973</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>辛耘</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>6197</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -246 千股)</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>-1078637</v>
-      </c>
-      <c r="D17" t="n">
-        <v>-1406115</v>
-      </c>
-      <c r="E17" t="n">
-        <v>472689</v>
-      </c>
-      <c r="F17" t="n">
-        <v>-1160383</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>佳必琪</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2059</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -209 千股)</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>-294861</v>
-      </c>
-      <c r="D18" t="n">
-        <v>16387</v>
-      </c>
-      <c r="E18" t="n">
-        <v>-144648</v>
-      </c>
-      <c r="F18" t="n">
-        <v>225441</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>川湖</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>3044</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -67 千股)</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>-3061802</v>
-      </c>
-      <c r="D19" t="n">
-        <v>7937798</v>
-      </c>
-      <c r="E19" t="n">
-        <v>-247558</v>
-      </c>
-      <c r="F19" t="n">
-        <v>8005023</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>健鼎</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>5434</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -340 千股)</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>-2677517</v>
-      </c>
-      <c r="D20" t="n">
-        <v>-2145024</v>
-      </c>
-      <c r="E20" t="n">
-        <v>-3018139</v>
-      </c>
-      <c r="F20" t="n">
-        <v>-1804776</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>崇越</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>1513</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 1,109 千股)</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>805811</v>
-      </c>
-      <c r="D21" t="n">
-        <v>-16007257</v>
-      </c>
-      <c r="E21" t="n">
-        <v>-237050</v>
-      </c>
-      <c r="F21" t="n">
-        <v>-17115987</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>中興電</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>1560</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -142 千股)</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>-624857</v>
-      </c>
-      <c r="D22" t="n">
-        <v>877035</v>
-      </c>
-      <c r="E22" t="n">
-        <v>-571228</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1018784</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>中砂</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>1519</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -637 千股)</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>-651890</v>
-      </c>
-      <c r="D23" t="n">
-        <v>-5466930</v>
-      </c>
-      <c r="E23" t="n">
-        <v>-339100</v>
-      </c>
-      <c r="F23" t="n">
-        <v>-4829922</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>華城</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>3008</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 198 千股)</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>-631103</v>
-      </c>
-      <c r="D24" t="n">
-        <v>-3047283</v>
-      </c>
-      <c r="E24" t="n">
-        <v>-447169</v>
-      </c>
-      <c r="F24" t="n">
-        <v>-3245519</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>大立光</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>5340</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -339 千股)</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>-113922</v>
-      </c>
-      <c r="D25" t="n">
-        <v>-172466</v>
-      </c>
-      <c r="E25" t="n">
-        <v>-152052</v>
-      </c>
-      <c r="F25" t="n">
-        <v>166575</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>建榮</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>3029</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 18 千股)</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>1631793</v>
-      </c>
-      <c r="D26" t="n">
-        <v>2625658</v>
-      </c>
-      <c r="E26" t="n">
-        <v>1818959</v>
-      </c>
-      <c r="F26" t="n">
-        <v>2607894</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>零壹</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>4506</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -16 千股)</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>26277</v>
-      </c>
-      <c r="D27" t="n">
-        <v>328405</v>
-      </c>
-      <c r="E27" t="n">
-        <v>46920</v>
-      </c>
-      <c r="F27" t="n">
-        <v>344005</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>崇友</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2640</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 14 千股)</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>-16751</v>
-      </c>
-      <c r="D28" t="n">
-        <v>-124886</v>
-      </c>
-      <c r="E28" t="n">
-        <v>-13711</v>
-      </c>
-      <c r="F28" t="n">
-        <v>-138807</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>大車隊</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>3689</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 1,270 千股)</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>-77256</v>
-      </c>
-      <c r="D29" t="n">
-        <v>-28638</v>
-      </c>
-      <c r="E29" t="n">
-        <v>504912</v>
-      </c>
-      <c r="F29" t="n">
-        <v>-1298369</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>湧德</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>5519</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -591 千股)</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>-2242249</v>
-      </c>
-      <c r="D30" t="n">
-        <v>-1429063</v>
-      </c>
-      <c r="E30" t="n">
-        <v>-1827747</v>
-      </c>
-      <c r="F30" t="n">
-        <v>-838394</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>隆大</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2421</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 384 千股)</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>-70617</v>
-      </c>
-      <c r="D31" t="n">
-        <v>-1404111</v>
-      </c>
-      <c r="E31" t="n">
-        <v>600952</v>
-      </c>
-      <c r="F31" t="n">
-        <v>-1788595</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>建準</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>1618</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -667 千股)</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>-381908</v>
-      </c>
-      <c r="D32" t="n">
-        <v>374792</v>
-      </c>
-      <c r="E32" t="n">
-        <v>203917</v>
-      </c>
-      <c r="F32" t="n">
-        <v>1041611</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>合機</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>5904</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -90 千股)</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>-401425</v>
-      </c>
-      <c r="D33" t="n">
-        <v>-67839</v>
-      </c>
-      <c r="E33" t="n">
-        <v>-490651</v>
-      </c>
-      <c r="F33" t="n">
-        <v>22010</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>寶雅</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2618</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 28,303 千股)</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>102976642</v>
-      </c>
-      <c r="D34" t="n">
-        <v>294172415</v>
-      </c>
-      <c r="E34" t="n">
-        <v>61628361</v>
-      </c>
-      <c r="F34" t="n">
-        <v>265869773</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>長榮航</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>1215</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -901 千股)</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>1747876</v>
-      </c>
-      <c r="D35" t="n">
-        <v>-2564024</v>
-      </c>
-      <c r="E35" t="n">
-        <v>-283718</v>
-      </c>
-      <c r="F35" t="n">
-        <v>-1663100</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>卜蜂</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>1232</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -32 千股)</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>188106</v>
-      </c>
-      <c r="D36" t="n">
-        <v>-633348</v>
-      </c>
-      <c r="E36" t="n">
-        <v>137356</v>
-      </c>
-      <c r="F36" t="n">
-        <v>-601723</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>大統益</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>6189</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -87 千股)</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>603874</v>
-      </c>
-      <c r="D37" t="n">
-        <v>392531</v>
-      </c>
-      <c r="E37" t="n">
-        <v>657624</v>
-      </c>
-      <c r="F37" t="n">
-        <v>479507</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>豐藝</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>5478</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -55 千股)</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>-65050</v>
-      </c>
-      <c r="D38" t="n">
-        <v>285739</v>
-      </c>
-      <c r="E38" t="n">
-        <v>-73851</v>
-      </c>
-      <c r="F38" t="n">
-        <v>341135</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>智冠</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>6788</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 367 千股)</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>-155463</v>
-      </c>
-      <c r="D39" t="n">
-        <v>-915226</v>
-      </c>
-      <c r="E39" t="n">
-        <v>-156274</v>
-      </c>
-      <c r="F39" t="n">
-        <v>-1282686</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>華景電</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2753</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -224 千股)</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>-173892</v>
-      </c>
-      <c r="D40" t="n">
-        <v>76456</v>
-      </c>
-      <c r="E40" t="n">
-        <v>-98657</v>
-      </c>
-      <c r="F40" t="n">
-        <v>300380</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>八方雲集</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -38 千股)</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>-352439</v>
-      </c>
-      <c r="D41" t="n">
-        <v>-437104</v>
-      </c>
-      <c r="E41" t="n">
-        <v>-287345</v>
-      </c>
-      <c r="F41" t="n">
-        <v>-399012</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>3045</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 13,367 千股)</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>-5075202</v>
-      </c>
-      <c r="D42" t="n">
-        <v>-26072637</v>
-      </c>
-      <c r="E42" t="n">
-        <v>-40876850</v>
-      </c>
-      <c r="F42" t="n">
-        <v>-39439324</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>台灣大</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>4129</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -73 千股)</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>-59300</v>
-      </c>
-      <c r="D43" t="n">
-        <v>-276300</v>
-      </c>
-      <c r="E43" t="n">
-        <v>-117300</v>
-      </c>
-      <c r="F43" t="n">
-        <v>-203300</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>聯合</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>2912</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 1,321 千股)</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>3632738</v>
-      </c>
-      <c r="D44" t="n">
-        <v>-5523286</v>
-      </c>
-      <c r="E44" t="n">
-        <v>4393326</v>
-      </c>
-      <c r="F44" t="n">
-        <v>-6844060</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>統一超</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>3147</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -232 千股)</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>282866</v>
-      </c>
-      <c r="D45" t="n">
-        <v>-518692</v>
-      </c>
-      <c r="E45" t="n">
-        <v>59866</v>
-      </c>
-      <c r="F45" t="n">
-        <v>-286692</v>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>大綜</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>1514</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 110 千股)</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>1551741</v>
-      </c>
-      <c r="D46" t="n">
-        <v>322959</v>
-      </c>
-      <c r="E46" t="n">
-        <v>1375736</v>
-      </c>
-      <c r="F46" t="n">
-        <v>213106</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>亞力</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>3402</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -124 千股)</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>154723</v>
-      </c>
-      <c r="D47" t="n">
-        <v>3319191</v>
-      </c>
-      <c r="E47" t="n">
-        <v>780969</v>
-      </c>
-      <c r="F47" t="n">
-        <v>3443089</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>漢科</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -746 千股)</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>-1602097</v>
-      </c>
-      <c r="D48" t="n">
-        <v>-776430</v>
-      </c>
-      <c r="E48" t="n">
-        <v>-1505654</v>
-      </c>
-      <c r="F48" t="n">
-        <v>-30463</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>台燿</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>3260</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 2,002 千股)</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>801858</v>
-      </c>
-      <c r="D49" t="n">
-        <v>-3975426</v>
-      </c>
-      <c r="E49" t="n">
-        <v>877367</v>
-      </c>
-      <c r="F49" t="n">
-        <v>-5977137</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>威剛</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2472</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -1,316 千股)</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>-364777</v>
-      </c>
-      <c r="D50" t="n">
-        <v>-8713956</v>
-      </c>
-      <c r="E50" t="n">
-        <v>-1346016</v>
-      </c>
-      <c r="F50" t="n">
-        <v>-7397642</v>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>立隆電</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>3406</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 197 千股)</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>-694425</v>
-      </c>
-      <c r="D51" t="n">
-        <v>-2678969</v>
-      </c>
-      <c r="E51" t="n">
-        <v>-771278</v>
-      </c>
-      <c r="F51" t="n">
-        <v>-2876182</v>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>玉晶光</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>3661</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 226 千股)</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>-1232514</v>
-      </c>
-      <c r="D52" t="n">
-        <v>-2978661</v>
-      </c>
-      <c r="E52" t="n">
-        <v>-1704445</v>
-      </c>
-      <c r="F52" t="n">
-        <v>-3204783</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>世芯-KY</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 17,931 千股)</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>6597485</v>
-      </c>
-      <c r="D53" t="n">
-        <v>8849613</v>
-      </c>
-      <c r="E53" t="n">
-        <v>-2623666</v>
-      </c>
-      <c r="F53" t="n">
-        <v>-9081513</v>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>南亞科</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>2327</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 10,176 千股)</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>7350345</v>
-      </c>
-      <c r="D54" t="n">
-        <v>-3133976</v>
-      </c>
-      <c r="E54" t="n">
-        <v>8258290</v>
-      </c>
-      <c r="F54" t="n">
-        <v>-13309850</v>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>國巨*</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>3711</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 1,311 千股)</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>-30100117</v>
-      </c>
-      <c r="D55" t="n">
-        <v>46804087</v>
-      </c>
-      <c r="E55" t="n">
-        <v>-29116185</v>
-      </c>
-      <c r="F55" t="n">
-        <v>45493085</v>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>1503</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 478 千股)</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>1006160</v>
-      </c>
-      <c r="D56" t="n">
-        <v>-1350330</v>
-      </c>
-      <c r="E56" t="n">
-        <v>-1701</v>
-      </c>
-      <c r="F56" t="n">
-        <v>-1828177</v>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>士電</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>3293</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 181 千股)</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>-8923</v>
-      </c>
-      <c r="D57" t="n">
-        <v>-3492289</v>
-      </c>
-      <c r="E57" t="n">
-        <v>-351514</v>
-      </c>
-      <c r="F57" t="n">
-        <v>-3673611</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>鈊象</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2476</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -862 千股)</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>-2289673</v>
-      </c>
-      <c r="D58" t="n">
-        <v>-5973401</v>
-      </c>
-      <c r="E58" t="n">
-        <v>-644357</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-5111833</v>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>鉅祥</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2535</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -206 千股)</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>-169018</v>
-      </c>
-      <c r="D59" t="n">
-        <v>782519</v>
-      </c>
-      <c r="E59" t="n">
-        <v>-190761</v>
-      </c>
-      <c r="F59" t="n">
-        <v>988559</v>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>達欣工</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>6263</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 31 千股)</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>-212730</v>
-      </c>
-      <c r="D60" t="n">
-        <v>-722511</v>
-      </c>
-      <c r="E60" t="n">
-        <v>-135730</v>
-      </c>
-      <c r="F60" t="n">
-        <v>-753135</v>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>普萊德</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>1773</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 47 千股)</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>452685</v>
-      </c>
-      <c r="D61" t="n">
-        <v>1101286</v>
-      </c>
-      <c r="E61" t="n">
-        <v>606468</v>
-      </c>
-      <c r="F61" t="n">
-        <v>1054563</v>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>勝一</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>1590</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 30 千股)</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>339584</v>
-      </c>
-      <c r="D62" t="n">
-        <v>1109545</v>
-      </c>
-      <c r="E62" t="n">
-        <v>476000</v>
-      </c>
-      <c r="F62" t="n">
-        <v>1079295</v>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>亞德客-KY</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>4303</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -58 千股)</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>-458462</v>
-      </c>
-      <c r="D63" t="n">
-        <v>-89666</v>
-      </c>
-      <c r="E63" t="n">
-        <v>-460802</v>
-      </c>
-      <c r="F63" t="n">
-        <v>-31917</v>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>信立</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>5269</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -239 千股)</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>-313334</v>
-      </c>
-      <c r="D64" t="n">
-        <v>286589</v>
-      </c>
-      <c r="E64" t="n">
-        <v>-58567</v>
-      </c>
-      <c r="F64" t="n">
-        <v>525660</v>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>祥碩</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>4979</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -605 千股)</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>-2813216</v>
-      </c>
-      <c r="D65" t="n">
-        <v>119299</v>
-      </c>
-      <c r="E65" t="n">
-        <v>-490858</v>
-      </c>
-      <c r="F65" t="n">
-        <v>724306</v>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>華星光</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>6446</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -125 千股)</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>-2013643</v>
-      </c>
-      <c r="D66" t="n">
-        <v>3469071</v>
-      </c>
-      <c r="E66" t="n">
-        <v>-790450</v>
-      </c>
-      <c r="F66" t="n">
-        <v>3593644</v>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>藥華藥</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>3081</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -48 千股)</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>-633698</v>
-      </c>
-      <c r="D67" t="n">
-        <v>4039494</v>
-      </c>
-      <c r="E67" t="n">
-        <v>392015</v>
-      </c>
-      <c r="F67" t="n">
-        <v>4087628</v>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>聯亞</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>2382</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 8,368 千股)</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>-16776571</v>
-      </c>
-      <c r="D68" t="n">
-        <v>-34504936</v>
-      </c>
-      <c r="E68" t="n">
-        <v>-13631280</v>
-      </c>
-      <c r="F68" t="n">
-        <v>-42872546</v>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>廣達</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>8271</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -865 千股)</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>-1896495</v>
-      </c>
-      <c r="D69" t="n">
-        <v>-5061734</v>
-      </c>
-      <c r="E69" t="n">
-        <v>-1240264</v>
-      </c>
-      <c r="F69" t="n">
-        <v>-4196241</v>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>宇瞻</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>3231</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -1,787 千股)</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>-33660192</v>
-      </c>
-      <c r="D70" t="n">
-        <v>-210391670</v>
-      </c>
-      <c r="E70" t="n">
-        <v>-36612809</v>
-      </c>
-      <c r="F70" t="n">
-        <v>-208604968</v>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>緯創</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>2379</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 2,948 千股)</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>-2706331</v>
-      </c>
-      <c r="D71" t="n">
-        <v>-10154168</v>
-      </c>
-      <c r="E71" t="n">
-        <v>-4746435</v>
-      </c>
-      <c r="F71" t="n">
-        <v>-13102584</v>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>瑞昱</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>2301</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -903 千股)</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>6277490</v>
-      </c>
-      <c r="D72" t="n">
-        <v>19984601</v>
-      </c>
-      <c r="E72" t="n">
-        <v>10254634</v>
-      </c>
-      <c r="F72" t="n">
-        <v>20887461</v>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>光寶科</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>8926</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -2,907 千股)</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>-1936244</v>
-      </c>
-      <c r="D73" t="n">
-        <v>-22033033</v>
-      </c>
-      <c r="E73" t="n">
-        <v>-313847</v>
-      </c>
-      <c r="F73" t="n">
-        <v>-19126353</v>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>台汽電</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>1616</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 29 千股)</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>-579959</v>
-      </c>
-      <c r="D74" t="n">
-        <v>-717235</v>
-      </c>
-      <c r="E74" t="n">
-        <v>-643959</v>
-      </c>
-      <c r="F74" t="n">
-        <v>-745865</v>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>億泰</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>5511</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -619 千股)</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>-797741</v>
-      </c>
-      <c r="D75" t="n">
-        <v>78314</v>
-      </c>
-      <c r="E75" t="n">
-        <v>-195478</v>
-      </c>
-      <c r="F75" t="n">
-        <v>697007</v>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>德昌</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>4933</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 58 千股)</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>-35000</v>
-      </c>
-      <c r="D76" t="n">
-        <v>-411564</v>
-      </c>
-      <c r="E76" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F76" t="n">
-        <v>-469564</v>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>友輝</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>3227</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -713 千股)</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>-1954648</v>
-      </c>
-      <c r="D77" t="n">
-        <v>5077736</v>
-      </c>
-      <c r="E77" t="n">
-        <v>-1274972</v>
-      </c>
-      <c r="F77" t="n">
-        <v>5790425</v>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>原相</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>3596</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -420 千股)</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>299534</v>
-      </c>
-      <c r="D78" t="n">
-        <v>2923903</v>
-      </c>
-      <c r="E78" t="n">
-        <v>-83216</v>
-      </c>
-      <c r="F78" t="n">
-        <v>3343533</v>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>智易</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>6285</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 4,185 千股)</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>1264568</v>
-      </c>
-      <c r="D79" t="n">
-        <v>-2288735</v>
-      </c>
-      <c r="E79" t="n">
-        <v>-1012931</v>
-      </c>
-      <c r="F79" t="n">
-        <v>-6473840</v>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>啟碁</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>2356</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -3,452 千股)</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>-17187609</v>
-      </c>
-      <c r="D80" t="n">
-        <v>-40811097</v>
-      </c>
-      <c r="E80" t="n">
-        <v>-24400677</v>
-      </c>
-      <c r="F80" t="n">
-        <v>-37358945</v>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>英業達</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>6510</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -66 千股)</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>-90882</v>
-      </c>
-      <c r="D81" t="n">
-        <v>240815</v>
-      </c>
-      <c r="E81" t="n">
-        <v>-38993</v>
-      </c>
-      <c r="F81" t="n">
-        <v>307109</v>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>精測</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>2317</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 14,327 千股)</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>-20766181</v>
-      </c>
-      <c r="D82" t="n">
-        <v>-196111151</v>
-      </c>
-      <c r="E82" t="n">
-        <v>-51756901</v>
-      </c>
-      <c r="F82" t="n">
-        <v>-210437915</v>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>鴻海</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>5225</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 44 千股)</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>-14830</v>
-      </c>
-      <c r="D83" t="n">
-        <v>329194</v>
-      </c>
-      <c r="E83" t="n">
-        <v>-8580</v>
-      </c>
-      <c r="F83" t="n">
-        <v>284972</v>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>東科-KY</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>5243</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -572 千股)</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>-1193641</v>
-      </c>
-      <c r="D84" t="n">
-        <v>-6254690</v>
-      </c>
-      <c r="E84" t="n">
-        <v>-717342</v>
-      </c>
-      <c r="F84" t="n">
-        <v>-5682910</v>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>乙盛-KY</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>3188</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 369 千股)</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>55065</v>
-      </c>
-      <c r="D85" t="n">
-        <v>-739558</v>
-      </c>
-      <c r="E85" t="n">
-        <v>-59466</v>
-      </c>
-      <c r="F85" t="n">
-        <v>-1108558</v>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>鑫龍騰</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>2305</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -189 千股)</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>-1471571</v>
-      </c>
-      <c r="D86" t="n">
-        <v>582620</v>
-      </c>
-      <c r="E86" t="n">
-        <v>-903490</v>
-      </c>
-      <c r="F86" t="n">
-        <v>771638</v>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>全友</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>2395</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 855 千股)</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>1504570</v>
-      </c>
-      <c r="D87" t="n">
-        <v>4238328</v>
-      </c>
-      <c r="E87" t="n">
-        <v>1092103</v>
-      </c>
-      <c r="F87" t="n">
-        <v>3383255</v>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>研華</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>8086</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 460 千股)</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>-1726873</v>
-      </c>
-      <c r="D88" t="n">
-        <v>-3212630</v>
-      </c>
-      <c r="E88" t="n">
-        <v>-1347436</v>
-      </c>
-      <c r="F88" t="n">
-        <v>-3672853</v>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>宏捷科</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>2412</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 1,123 千股)</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>-33457248</v>
-      </c>
-      <c r="D89" t="n">
-        <v>-88982939</v>
-      </c>
-      <c r="E89" t="n">
-        <v>-50794188</v>
-      </c>
-      <c r="F89" t="n">
-        <v>-90105685</v>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>中華電</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>9917</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 5 千股)</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>316313</v>
-      </c>
-      <c r="D90" t="n">
-        <v>-6116747</v>
-      </c>
-      <c r="E90" t="n">
-        <v>-33420</v>
-      </c>
-      <c r="F90" t="n">
-        <v>-6121929</v>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>中保科</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>6739</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -61 千股)</t>
-        </is>
-      </c>
-      <c r="C91" t="n">
-        <v>-89468</v>
-      </c>
-      <c r="D91" t="n">
-        <v>-148545</v>
-      </c>
-      <c r="E91" t="n">
-        <v>-39563</v>
-      </c>
-      <c r="F91" t="n">
-        <v>-87088</v>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>竹陞科技</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>2645</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 1,481 千股)</t>
-        </is>
-      </c>
-      <c r="C92" t="n">
-        <v>1346923</v>
-      </c>
-      <c r="D92" t="n">
-        <v>8655988</v>
-      </c>
-      <c r="E92" t="n">
-        <v>2171650</v>
-      </c>
-      <c r="F92" t="n">
-        <v>7174540</v>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>長榮航太</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>6690</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 42 千股)</t>
-        </is>
-      </c>
-      <c r="C93" t="n">
-        <v>33616</v>
-      </c>
-      <c r="D93" t="n">
-        <v>-430382</v>
-      </c>
-      <c r="E93" t="n">
-        <v>12202</v>
-      </c>
-      <c r="F93" t="n">
-        <v>-472192</v>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>安碁資訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>4569</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -21 千股)</t>
-        </is>
-      </c>
-      <c r="C94" t="n">
-        <v>9000</v>
-      </c>
-      <c r="D94" t="n">
-        <v>135847</v>
-      </c>
-      <c r="E94" t="n">
-        <v>39000</v>
-      </c>
-      <c r="F94" t="n">
-        <v>157067</v>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>六方科-KY</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -13,399 千股)</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>-27735143</v>
-      </c>
-      <c r="D95" t="n">
-        <v>-209936265</v>
-      </c>
-      <c r="E95" t="n">
-        <v>20454693</v>
-      </c>
-      <c r="F95" t="n">
-        <v>-196537443</v>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>華邦電</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>2454</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 749 千股)</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
-        <v>-3902539</v>
-      </c>
-      <c r="D96" t="n">
-        <v>-1033870</v>
-      </c>
-      <c r="E96" t="n">
-        <v>-4326686</v>
-      </c>
-      <c r="F96" t="n">
-        <v>-1782828</v>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>聯發科</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>3443</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -306 千股)</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
-        <v>-874364</v>
-      </c>
-      <c r="D97" t="n">
-        <v>-5350977</v>
-      </c>
-      <c r="E97" t="n">
-        <v>-190875</v>
-      </c>
-      <c r="F97" t="n">
-        <v>-5045426</v>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>創意</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>6669</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -795 千股)</t>
-        </is>
-      </c>
-      <c r="C98" t="n">
-        <v>-796614</v>
-      </c>
-      <c r="D98" t="n">
-        <v>-4855800</v>
-      </c>
-      <c r="E98" t="n">
-        <v>-1281761</v>
-      </c>
-      <c r="F98" t="n">
-        <v>-4060574</v>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>5274</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 78 千股)</t>
-        </is>
-      </c>
-      <c r="C99" t="n">
-        <v>-12462</v>
-      </c>
-      <c r="D99" t="n">
-        <v>347553</v>
-      </c>
-      <c r="E99" t="n">
-        <v>-18216</v>
-      </c>
-      <c r="F99" t="n">
-        <v>269456</v>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>信驊</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>2368</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 1,866 千股)</t>
-        </is>
-      </c>
-      <c r="C100" t="n">
-        <v>1182641</v>
-      </c>
-      <c r="D100" t="n">
-        <v>3813387</v>
-      </c>
-      <c r="E100" t="n">
-        <v>-810252</v>
-      </c>
-      <c r="F100" t="n">
-        <v>1947807</v>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>金像電</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>4904</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 4,031 千股)</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
-        <v>-17284376</v>
-      </c>
-      <c r="D101" t="n">
-        <v>-150663423</v>
-      </c>
-      <c r="E101" t="n">
-        <v>-30456091</v>
-      </c>
-      <c r="F101" t="n">
-        <v>-154694218</v>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>遠傳</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>5439</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -620 千股)</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
-        <v>-568581</v>
-      </c>
-      <c r="D102" t="n">
-        <v>487443</v>
-      </c>
-      <c r="E102" t="n">
-        <v>239213</v>
-      </c>
-      <c r="F102" t="n">
-        <v>1107633</v>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>高技</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>6187</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 694 千股)</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
-        <v>1471521</v>
-      </c>
-      <c r="D103" t="n">
-        <v>-73831</v>
-      </c>
-      <c r="E103" t="n">
-        <v>454283</v>
-      </c>
-      <c r="F103" t="n">
-        <v>-768180</v>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>萬潤</t>
-        </is>
+        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/data/台股_外資雷達.xlsx
+++ b/data/台股_外資雷達.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="總覽" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="翻轉警報" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,22 +496,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>102977</v>
+        <v>165902</v>
       </c>
       <c r="D2" t="n">
-        <v>294172</v>
+        <v>314443</v>
       </c>
       <c r="E2" t="n">
-        <v>23008</v>
+        <v>79170</v>
       </c>
       <c r="F2" t="n">
-        <v>2021</v>
+        <v>-5607</v>
       </c>
       <c r="G2" t="n">
-        <v>22007</v>
+        <v>24511</v>
       </c>
       <c r="H2" t="n">
-        <v>2983</v>
+        <v>230</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -546,22 +547,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-30100</v>
+        <v>-14884</v>
       </c>
       <c r="D3" t="n">
-        <v>46804</v>
+        <v>42018</v>
       </c>
       <c r="E3" t="n">
-        <v>-5248</v>
+        <v>-3234</v>
       </c>
       <c r="F3" t="n">
-        <v>7760</v>
+        <v>7551</v>
       </c>
       <c r="G3" t="n">
-        <v>-45500</v>
+        <v>-45047</v>
       </c>
       <c r="H3" t="n">
-        <v>3082</v>
+        <v>2844</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -597,22 +598,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6277</v>
+        <v>10098</v>
       </c>
       <c r="D4" t="n">
-        <v>19985</v>
+        <v>21829</v>
       </c>
       <c r="E4" t="n">
-        <v>123616</v>
+        <v>125258</v>
       </c>
       <c r="F4" t="n">
-        <v>-2524</v>
+        <v>-1950</v>
       </c>
       <c r="G4" t="n">
-        <v>-33353</v>
+        <v>-33596</v>
       </c>
       <c r="H4" t="n">
-        <v>2358</v>
+        <v>2072</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -639,31 +640,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6597</v>
+        <v>-3184</v>
       </c>
       <c r="D5" t="n">
-        <v>8850</v>
+        <v>7045</v>
       </c>
       <c r="E5" t="n">
-        <v>115843</v>
+        <v>11714</v>
       </c>
       <c r="F5" t="n">
-        <v>-2388</v>
+        <v>-1016</v>
       </c>
       <c r="G5" t="n">
-        <v>66783</v>
+        <v>-9756</v>
       </c>
       <c r="H5" t="n">
-        <v>-2019</v>
+        <v>-324</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -672,11 +673,11 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -684,88 +685,76 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1347</v>
+        <v>2732</v>
       </c>
       <c r="D6" t="n">
-        <v>8656</v>
+        <v>6545</v>
       </c>
       <c r="E6" t="n">
-        <v>12546</v>
+        <v>10112</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>-3427</v>
       </c>
       <c r="G6" t="n">
-        <v>-565</v>
+        <v>-10288</v>
       </c>
       <c r="H6" t="n">
-        <v>658</v>
+        <v>-1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>🟢 加碼</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>79</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>✈️ 高飛*</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>3</v>
-      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>長榮航太</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-3062</v>
+        <v>-1002</v>
       </c>
       <c r="D7" t="n">
-        <v>7938</v>
+        <v>6408</v>
       </c>
       <c r="E7" t="n">
-        <v>12603</v>
+        <v>10181</v>
       </c>
       <c r="F7" t="n">
-        <v>-1065</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
-        <v>-9763</v>
+        <v>-561</v>
       </c>
       <c r="H7" t="n">
-        <v>-228</v>
+        <v>592</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -774,19 +763,19 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -801,22 +790,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2018</v>
+        <v>2031</v>
       </c>
       <c r="D8" t="n">
-        <v>6149</v>
+        <v>6055</v>
       </c>
       <c r="E8" t="n">
-        <v>9747</v>
+        <v>10006</v>
       </c>
       <c r="F8" t="n">
-        <v>-1688</v>
+        <v>-1675</v>
       </c>
       <c r="G8" t="n">
-        <v>-5717</v>
+        <v>-5645</v>
       </c>
       <c r="H8" t="n">
-        <v>212</v>
+        <v>158</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -852,22 +841,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-1955</v>
+        <v>-2487</v>
       </c>
       <c r="D9" t="n">
-        <v>5078</v>
+        <v>4386</v>
       </c>
       <c r="E9" t="n">
-        <v>8177</v>
+        <v>7716</v>
       </c>
       <c r="F9" t="n">
-        <v>1843</v>
+        <v>778</v>
       </c>
       <c r="G9" t="n">
-        <v>4822</v>
+        <v>4367</v>
       </c>
       <c r="H9" t="n">
-        <v>197</v>
+        <v>125</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -903,22 +892,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1505</v>
+        <v>858</v>
       </c>
       <c r="D10" t="n">
-        <v>4238</v>
+        <v>4019</v>
       </c>
       <c r="E10" t="n">
-        <v>16126</v>
+        <v>15482</v>
       </c>
       <c r="F10" t="n">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="G10" t="n">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="H10" t="n">
-        <v>178</v>
+        <v>214</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -945,31 +934,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>漢科</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-634</v>
+        <v>104</v>
       </c>
       <c r="D11" t="n">
-        <v>4039</v>
+        <v>3652</v>
       </c>
       <c r="E11" t="n">
-        <v>1135</v>
+        <v>3032</v>
       </c>
       <c r="F11" t="n">
-        <v>-86</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>-3154</v>
+        <v>135</v>
       </c>
       <c r="H11" t="n">
-        <v>340</v>
+        <v>38</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -982,7 +971,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -990,76 +979,88 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1183</v>
+        <v>-2413</v>
       </c>
       <c r="D12" t="n">
-        <v>3813</v>
+        <v>2991</v>
       </c>
       <c r="E12" t="n">
-        <v>9225</v>
+        <v>13921</v>
       </c>
       <c r="F12" t="n">
-        <v>-1792</v>
+        <v>229</v>
       </c>
       <c r="G12" t="n">
-        <v>-9822</v>
+        <v>1137</v>
       </c>
       <c r="H12" t="n">
-        <v>58</v>
+        <v>-15</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>🟢 加碼</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>66</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>🚀 加速器*</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>零壹</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-2014</v>
+        <v>1316</v>
       </c>
       <c r="D13" t="n">
-        <v>3469</v>
+        <v>2893</v>
       </c>
       <c r="E13" t="n">
-        <v>14836</v>
+        <v>2710</v>
       </c>
       <c r="F13" t="n">
-        <v>209</v>
+        <v>-7</v>
       </c>
       <c r="G13" t="n">
-        <v>1083</v>
+        <v>-136</v>
       </c>
       <c r="H13" t="n">
-        <v>-12</v>
+        <v>-744</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1068,49 +1069,49 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>66</v>
+        <v>97</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>🚀 加速器*</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>155</v>
+        <v>345</v>
       </c>
       <c r="D14" t="n">
-        <v>3319</v>
+        <v>2841</v>
       </c>
       <c r="E14" t="n">
-        <v>2743</v>
+        <v>-1387</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>-148</v>
       </c>
       <c r="G14" t="n">
-        <v>135</v>
+        <v>-1189</v>
       </c>
       <c r="H14" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1119,19 +1120,19 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1146,22 +1147,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="D15" t="n">
-        <v>2924</v>
+        <v>2452</v>
       </c>
       <c r="E15" t="n">
-        <v>6374</v>
+        <v>7039</v>
       </c>
       <c r="F15" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="G15" t="n">
-        <v>5554</v>
+        <v>5556</v>
       </c>
       <c r="H15" t="n">
-        <v>-70</v>
+        <v>-69</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1188,31 +1189,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>157</v>
+        <v>111</v>
       </c>
       <c r="D16" t="n">
-        <v>2742</v>
+        <v>2326</v>
       </c>
       <c r="E16" t="n">
-        <v>-1501</v>
+        <v>3450</v>
       </c>
       <c r="F16" t="n">
-        <v>-294</v>
+        <v>-252</v>
       </c>
       <c r="G16" t="n">
-        <v>-1264</v>
+        <v>-718</v>
       </c>
       <c r="H16" t="n">
-        <v>24</v>
+        <v>-107</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1225,45 +1226,45 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1632</v>
+        <v>1853</v>
       </c>
       <c r="D17" t="n">
-        <v>2626</v>
+        <v>2138</v>
       </c>
       <c r="E17" t="n">
-        <v>2300</v>
+        <v>27876</v>
       </c>
       <c r="F17" t="n">
-        <v>-10</v>
+        <v>-2519</v>
       </c>
       <c r="G17" t="n">
-        <v>-142</v>
+        <v>-14597</v>
       </c>
       <c r="H17" t="n">
-        <v>-750</v>
+        <v>-118</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1272,19 +1273,19 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1299,26 +1300,26 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-418</v>
+        <v>-1260</v>
       </c>
       <c r="D18" t="n">
-        <v>2048</v>
+        <v>1580</v>
       </c>
       <c r="E18" t="n">
-        <v>-6041</v>
+        <v>-7218</v>
       </c>
       <c r="F18" t="n">
-        <v>637</v>
+        <v>61</v>
       </c>
       <c r="G18" t="n">
-        <v>-84</v>
+        <v>-161</v>
       </c>
       <c r="H18" t="n">
-        <v>32</v>
+        <v>-39</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>🟢 加碼</t>
+          <t>🟡 中性</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1341,31 +1342,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>486</v>
+        <v>169</v>
       </c>
       <c r="D19" t="n">
-        <v>1879</v>
+        <v>1391</v>
       </c>
       <c r="E19" t="n">
-        <v>2826</v>
+        <v>-1546</v>
       </c>
       <c r="F19" t="n">
-        <v>-767</v>
+        <v>-23</v>
       </c>
       <c r="G19" t="n">
-        <v>-695</v>
+        <v>-174</v>
       </c>
       <c r="H19" t="n">
-        <v>-116</v>
+        <v>-27</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1378,45 +1379,45 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-643</v>
+        <v>464</v>
       </c>
       <c r="D20" t="n">
-        <v>1707</v>
+        <v>1267</v>
       </c>
       <c r="E20" t="n">
-        <v>-1366</v>
+        <v>2987</v>
       </c>
       <c r="F20" t="n">
-        <v>-42</v>
+        <v>35</v>
       </c>
       <c r="G20" t="n">
-        <v>-181</v>
+        <v>376</v>
       </c>
       <c r="H20" t="n">
-        <v>-21</v>
+        <v>-8</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1425,49 +1426,49 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>340</v>
+        <v>466</v>
       </c>
       <c r="D21" t="n">
-        <v>1110</v>
+        <v>1164</v>
       </c>
       <c r="E21" t="n">
-        <v>2469</v>
+        <v>869</v>
       </c>
       <c r="F21" t="n">
-        <v>34</v>
+        <v>-16</v>
       </c>
       <c r="G21" t="n">
-        <v>375</v>
+        <v>3</v>
       </c>
       <c r="H21" t="n">
-        <v>-1</v>
+        <v>47</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1476,70 +1477,70 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>勝一</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>453</v>
+        <v>-1024</v>
       </c>
       <c r="D22" t="n">
-        <v>1101</v>
+        <v>1047</v>
       </c>
       <c r="E22" t="n">
-        <v>1252</v>
+        <v>1297</v>
       </c>
       <c r="F22" t="n">
+        <v>96</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-2503</v>
+      </c>
+      <c r="H22" t="n">
+        <v>340</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>70</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
         <v>1</v>
-      </c>
-      <c r="G22" t="n">
-        <v>5</v>
-      </c>
-      <c r="H22" t="n">
-        <v>29</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>71</v>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>📉 減速</t>
-        </is>
-      </c>
-      <c r="M22" t="n">
-        <v>-3</v>
       </c>
     </row>
     <row r="23">
@@ -1554,22 +1555,22 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-625</v>
+        <v>-572</v>
       </c>
       <c r="D23" t="n">
-        <v>877</v>
+        <v>903</v>
       </c>
       <c r="E23" t="n">
-        <v>3093</v>
+        <v>2609</v>
       </c>
       <c r="F23" t="n">
-        <v>-61</v>
+        <v>-16</v>
       </c>
       <c r="G23" t="n">
-        <v>1103</v>
+        <v>887</v>
       </c>
       <c r="H23" t="n">
-        <v>-70</v>
+        <v>-80</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1596,31 +1597,31 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-169</v>
+        <v>-1882</v>
       </c>
       <c r="D24" t="n">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="E24" t="n">
-        <v>667</v>
+        <v>4900</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>596</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>211</v>
       </c>
       <c r="H24" t="n">
-        <v>-95</v>
+        <v>109</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1629,49 +1630,49 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>達欣工</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-1472</v>
+        <v>-138</v>
       </c>
       <c r="D25" t="n">
-        <v>583</v>
+        <v>634</v>
       </c>
       <c r="E25" t="n">
-        <v>5627</v>
+        <v>889</v>
       </c>
       <c r="F25" t="n">
         <v>-1</v>
       </c>
       <c r="G25" t="n">
-        <v>-6</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>-26</v>
+        <v>-120</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1684,84 +1685,96 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>湧德</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-569</v>
+        <v>-178</v>
       </c>
       <c r="D26" t="n">
-        <v>487</v>
+        <v>611</v>
       </c>
       <c r="E26" t="n">
-        <v>-2376</v>
+        <v>-3149</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>-5806</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-121</v>
+        <v>-51</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>94</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>📉 減速</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>604</v>
+        <v>1933</v>
       </c>
       <c r="D27" t="n">
-        <v>393</v>
+        <v>591</v>
       </c>
       <c r="E27" t="n">
-        <v>623</v>
+        <v>-8946</v>
       </c>
       <c r="F27" t="n">
-        <v>-22</v>
+        <v>-2</v>
       </c>
       <c r="G27" t="n">
-        <v>-3</v>
+        <v>-9</v>
       </c>
       <c r="H27" t="n">
-        <v>52</v>
+        <v>-96</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1770,49 +1783,49 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>合機</t>
+          <t>勝一</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-382</v>
+        <v>129</v>
       </c>
       <c r="D28" t="n">
-        <v>375</v>
+        <v>587</v>
       </c>
       <c r="E28" t="n">
-        <v>2289</v>
+        <v>945</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H28" t="n">
-        <v>-56</v>
+        <v>16</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1821,109 +1834,121 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-12</v>
+        <v>86</v>
       </c>
       <c r="D29" t="n">
-        <v>348</v>
+        <v>498</v>
       </c>
       <c r="E29" t="n">
-        <v>664</v>
+        <v>-864</v>
       </c>
       <c r="F29" t="n">
-        <v>-230</v>
+        <v>699</v>
       </c>
       <c r="G29" t="n">
-        <v>-408</v>
+        <v>2328</v>
       </c>
       <c r="H29" t="n">
+        <v>17</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>60</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>✈️ 高飛</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
         <v>-1</v>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-15</v>
+        <v>10347</v>
       </c>
       <c r="D30" t="n">
-        <v>329</v>
+        <v>497</v>
       </c>
       <c r="E30" t="n">
-        <v>-203</v>
+        <v>-80630</v>
       </c>
       <c r="F30" t="n">
+        <v>-4296</v>
+      </c>
+      <c r="G30" t="n">
+        <v>6143</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-5854</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>60</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>📉 減速</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
         <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-13</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K30" t="n">
-        <v>78</v>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>📉 減速</t>
-        </is>
-      </c>
-      <c r="M30" t="n">
-        <v>-3</v>
       </c>
     </row>
     <row r="31">
@@ -1938,13 +1963,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="D31" t="n">
-        <v>328</v>
+        <v>378</v>
       </c>
       <c r="E31" t="n">
-        <v>520</v>
+        <v>593</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1953,7 +1978,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1980,133 +2005,109 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1552</v>
+        <v>-1026</v>
       </c>
       <c r="D32" t="n">
-        <v>323</v>
+        <v>346</v>
       </c>
       <c r="E32" t="n">
-        <v>-8626</v>
+        <v>-1448</v>
       </c>
       <c r="F32" t="n">
-        <v>-2</v>
+        <v>-9</v>
       </c>
       <c r="G32" t="n">
-        <v>-10</v>
+        <v>-5569</v>
       </c>
       <c r="H32" t="n">
-        <v>-66</v>
+        <v>-105</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K32" t="n">
-        <v>79</v>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>🛬 穩定</t>
-        </is>
-      </c>
-      <c r="M32" t="n">
-        <v>-2</v>
-      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-313</v>
+        <v>3</v>
       </c>
       <c r="D33" t="n">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E33" t="n">
-        <v>-1093</v>
+        <v>684</v>
       </c>
       <c r="F33" t="n">
-        <v>803</v>
+        <v>-271</v>
       </c>
       <c r="G33" t="n">
-        <v>2138</v>
+        <v>-418</v>
       </c>
       <c r="H33" t="n">
-        <v>20</v>
+        <v>-7</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K33" t="n">
-        <v>60</v>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>✈️ 高飛</t>
-        </is>
-      </c>
-      <c r="M33" t="n">
-        <v>-1</v>
-      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>智冠</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-65</v>
+        <v>-1017</v>
       </c>
       <c r="D34" t="n">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="E34" t="n">
-        <v>464</v>
+        <v>-8019</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>-626</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-5802</v>
       </c>
       <c r="H34" t="n">
-        <v>-153</v>
+        <v>-236</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2115,49 +2116,49 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M34" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>合機</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-91</v>
+        <v>-983</v>
       </c>
       <c r="D35" t="n">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="E35" t="n">
-        <v>-135</v>
+        <v>2125</v>
       </c>
       <c r="F35" t="n">
-        <v>-240</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>-1132</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-113</v>
+        <v>-78</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2166,40 +2167,40 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M35" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>9</v>
+        <v>-121</v>
       </c>
       <c r="D36" t="n">
-        <v>136</v>
+        <v>203</v>
       </c>
       <c r="E36" t="n">
-        <v>-22</v>
+        <v>-209</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -2208,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>6</v>
+        <v>-9</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2221,11 +2222,11 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M36" t="n">
@@ -2235,31 +2236,31 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>智冠</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-2813</v>
+        <v>-104</v>
       </c>
       <c r="D37" t="n">
-        <v>119</v>
+        <v>196</v>
       </c>
       <c r="E37" t="n">
-        <v>-8194</v>
+        <v>439</v>
       </c>
       <c r="F37" t="n">
-        <v>-106</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>-5882</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-241</v>
+        <v>-147</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2268,49 +2269,49 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M37" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>六方科-KY</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-1547</v>
+        <v>-20</v>
       </c>
       <c r="D38" t="n">
-        <v>79</v>
+        <v>123</v>
       </c>
       <c r="E38" t="n">
-        <v>5096</v>
+        <v>-55</v>
       </c>
       <c r="F38" t="n">
-        <v>695</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>117</v>
+        <v>5</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2319,19 +2320,19 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M38" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="39">
@@ -2346,13 +2347,13 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-798</v>
+        <v>-696</v>
       </c>
       <c r="D39" t="n">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="E39" t="n">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -2361,7 +2362,7 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-24</v>
+        <v>-18</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2388,31 +2389,31 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-174</v>
+        <v>-98</v>
       </c>
       <c r="D40" t="n">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="E40" t="n">
-        <v>-1356</v>
+        <v>-63</v>
       </c>
       <c r="F40" t="n">
-        <v>-7</v>
+        <v>-200</v>
       </c>
       <c r="G40" t="n">
-        <v>241</v>
+        <v>-1088</v>
       </c>
       <c r="H40" t="n">
-        <v>-10</v>
+        <v>-116</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2421,49 +2422,49 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>🐌 龜速*</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M40" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>信立</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-295</v>
+        <v>-297</v>
       </c>
       <c r="D41" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="E41" t="n">
-        <v>-471</v>
+        <v>-417</v>
       </c>
       <c r="F41" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2472,11 +2473,11 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2484,37 +2485,37 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>方土霖</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>-220</v>
       </c>
       <c r="D42" t="n">
-        <v>-10</v>
+        <v>-12</v>
       </c>
       <c r="E42" t="n">
-        <v>-77</v>
+        <v>-377</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>227</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="H42" t="n">
-        <v>-2</v>
+        <v>14</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2527,36 +2528,36 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M42" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>方土霖</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-77</v>
+        <v>-2</v>
       </c>
       <c r="D43" t="n">
-        <v>-29</v>
+        <v>-13</v>
       </c>
       <c r="E43" t="n">
-        <v>-3122</v>
+        <v>-79</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -2565,7 +2566,7 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>-19</v>
+        <v>-2</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2578,11 +2579,11 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M43" t="n">
@@ -2592,31 +2593,31 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>寶雅</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-401</v>
+        <v>989</v>
       </c>
       <c r="D44" t="n">
-        <v>-68</v>
+        <v>-21</v>
       </c>
       <c r="E44" t="n">
-        <v>1438</v>
+        <v>1468</v>
       </c>
       <c r="F44" t="n">
-        <v>-77</v>
+        <v>-962</v>
       </c>
       <c r="G44" t="n">
-        <v>83</v>
+        <v>-811</v>
       </c>
       <c r="H44" t="n">
-        <v>162</v>
+        <v>-114</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2629,84 +2630,96 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M44" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1472</v>
+        <v>-1811</v>
       </c>
       <c r="D45" t="n">
-        <v>-74</v>
+        <v>-87</v>
       </c>
       <c r="E45" t="n">
-        <v>-5933</v>
+        <v>3138</v>
       </c>
       <c r="F45" t="n">
-        <v>248</v>
+        <v>412</v>
       </c>
       <c r="G45" t="n">
-        <v>-1118</v>
+        <v>111</v>
       </c>
       <c r="H45" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>80</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>🚀 加速器</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>大車隊</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-1936</v>
+        <v>-8</v>
       </c>
       <c r="D46" t="n">
-        <v>-87</v>
+        <v>-123</v>
       </c>
       <c r="E46" t="n">
-        <v>2573</v>
+        <v>-278</v>
       </c>
       <c r="F46" t="n">
-        <v>506</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>226</v>
+        <v>53</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2719,45 +2732,45 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M46" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-458</v>
+        <v>-2</v>
       </c>
       <c r="D47" t="n">
-        <v>-90</v>
+        <v>-162</v>
       </c>
       <c r="E47" t="n">
-        <v>-650</v>
+        <v>-154</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H47" t="n">
-        <v>-2</v>
+        <v>9</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2770,11 +2783,11 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M47" t="n">
@@ -2784,31 +2797,31 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>大車隊</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-17</v>
+        <v>817</v>
       </c>
       <c r="D48" t="n">
-        <v>-125</v>
+        <v>-184</v>
       </c>
       <c r="E48" t="n">
-        <v>-273</v>
+        <v>-989</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>-865</v>
       </c>
       <c r="H48" t="n">
-        <v>52</v>
+        <v>-123</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2821,36 +2834,36 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M48" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>聯合</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-89</v>
+        <v>-4</v>
       </c>
       <c r="D49" t="n">
-        <v>-149</v>
+        <v>-251</v>
       </c>
       <c r="E49" t="n">
-        <v>-227</v>
+        <v>-3109</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -2859,7 +2872,7 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>3</v>
+        <v>99</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2868,15 +2881,15 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M49" t="n">
@@ -2886,31 +2899,31 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-114</v>
+        <v>-304</v>
       </c>
       <c r="D50" t="n">
-        <v>-172</v>
+        <v>-304</v>
       </c>
       <c r="E50" t="n">
-        <v>-5088</v>
+        <v>-1325</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="H50" t="n">
-        <v>3</v>
+        <v>-8</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2923,45 +2936,45 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速*</t>
         </is>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>大統益</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>537</v>
+        <v>148</v>
       </c>
       <c r="D51" t="n">
-        <v>-234</v>
+        <v>-309</v>
       </c>
       <c r="E51" t="n">
-        <v>1077</v>
+        <v>-532</v>
       </c>
       <c r="F51" t="n">
-        <v>-512</v>
+        <v>-1</v>
       </c>
       <c r="G51" t="n">
-        <v>250</v>
+        <v>-1</v>
       </c>
       <c r="H51" t="n">
-        <v>-70</v>
+        <v>12</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -2974,7 +2987,7 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -2982,37 +2995,37 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>聯合</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-59</v>
+        <v>341</v>
       </c>
       <c r="D52" t="n">
-        <v>-276</v>
+        <v>-335</v>
       </c>
       <c r="E52" t="n">
-        <v>-3195</v>
+        <v>765</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>445</v>
       </c>
       <c r="H52" t="n">
-        <v>98</v>
+        <v>-570</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3021,15 +3034,15 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M52" t="n">
@@ -3039,31 +3052,31 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>鑫龍騰</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-35</v>
+        <v>83</v>
       </c>
       <c r="D53" t="n">
-        <v>-412</v>
+        <v>-382</v>
       </c>
       <c r="E53" t="n">
-        <v>822</v>
+        <v>-2917</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-24</v>
+        <v>0</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3080,41 +3093,41 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M53" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>友輝</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>34</v>
+        <v>-111</v>
       </c>
       <c r="D54" t="n">
-        <v>-430</v>
+        <v>-428</v>
       </c>
       <c r="E54" t="n">
-        <v>-239</v>
+        <v>534</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H54" t="n">
-        <v>16</v>
+        <v>-23</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3131,41 +3144,41 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M54" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>-352</v>
+        <v>68</v>
       </c>
       <c r="D55" t="n">
-        <v>-437</v>
+        <v>-461</v>
       </c>
       <c r="E55" t="n">
-        <v>-404</v>
+        <v>-245</v>
       </c>
       <c r="F55" t="n">
-        <v>201</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-41</v>
+        <v>-13</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3174,11 +3187,11 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K55" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -3186,139 +3199,127 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>283</v>
+        <v>410</v>
       </c>
       <c r="D56" t="n">
-        <v>-519</v>
+        <v>-462</v>
       </c>
       <c r="E56" t="n">
-        <v>2106</v>
+        <v>-6287</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>294</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>-1195</v>
       </c>
       <c r="H56" t="n">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K56" t="n">
-        <v>76</v>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>🚀 加速器</t>
-        </is>
-      </c>
-      <c r="M56" t="n">
-        <v>-1</v>
-      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>寶雅</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>188</v>
+        <v>-646</v>
       </c>
       <c r="D57" t="n">
-        <v>-633</v>
+        <v>-485</v>
       </c>
       <c r="E57" t="n">
-        <v>-828</v>
+        <v>650</v>
       </c>
       <c r="F57" t="n">
+        <v>-30</v>
+      </c>
+      <c r="G57" t="n">
+        <v>53</v>
+      </c>
+      <c r="H57" t="n">
+        <v>78</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>92</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>🛬 穩定</t>
+        </is>
+      </c>
+      <c r="M57" t="n">
         <v>-1</v>
-      </c>
-      <c r="G57" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H57" t="n">
-        <v>21</v>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K57" t="n">
-        <v>86</v>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>📉 減速</t>
-        </is>
-      </c>
-      <c r="M57" t="n">
-        <v>-3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>81</v>
+        <v>-265</v>
       </c>
       <c r="D58" t="n">
-        <v>-707</v>
+        <v>-490</v>
       </c>
       <c r="E58" t="n">
-        <v>-1274</v>
+        <v>-413</v>
       </c>
       <c r="F58" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="G58" t="n">
-        <v>-952</v>
+        <v>126</v>
       </c>
       <c r="H58" t="n">
-        <v>-103</v>
+        <v>-59</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3331,45 +3332,45 @@
         </is>
       </c>
       <c r="K58" t="n">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>全友</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>-237</v>
+        <v>-1720</v>
       </c>
       <c r="D59" t="n">
-        <v>-712</v>
+        <v>-566</v>
       </c>
       <c r="E59" t="n">
-        <v>-783</v>
+        <v>5608</v>
       </c>
       <c r="F59" t="n">
-        <v>303</v>
+        <v>-1</v>
       </c>
       <c r="G59" t="n">
-        <v>1400</v>
+        <v>-5</v>
       </c>
       <c r="H59" t="n">
-        <v>-30</v>
+        <v>72</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3378,40 +3379,40 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K59" t="n">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M59" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>億泰</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>-580</v>
+        <v>105</v>
       </c>
       <c r="D60" t="n">
-        <v>-717</v>
+        <v>-599</v>
       </c>
       <c r="E60" t="n">
-        <v>-2766</v>
+        <v>2134</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -3420,7 +3421,7 @@
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>193</v>
+        <v>122</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3433,45 +3434,45 @@
         </is>
       </c>
       <c r="K60" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M60" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-213</v>
+        <v>38</v>
       </c>
       <c r="D61" t="n">
-        <v>-723</v>
+        <v>-658</v>
       </c>
       <c r="E61" t="n">
-        <v>-1927</v>
+        <v>-7556</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>-774</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>-3682</v>
       </c>
       <c r="H61" t="n">
-        <v>12</v>
+        <v>-41</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3480,40 +3481,40 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K61" t="n">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M61" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>鑫龍騰</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>55</v>
+        <v>-387</v>
       </c>
       <c r="D62" t="n">
-        <v>-740</v>
+        <v>-696</v>
       </c>
       <c r="E62" t="n">
-        <v>-2983</v>
+        <v>-1921</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -3522,7 +3523,7 @@
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3535,45 +3536,45 @@
         </is>
       </c>
       <c r="K62" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>億泰</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-1602</v>
+        <v>-608</v>
       </c>
       <c r="D63" t="n">
-        <v>-776</v>
+        <v>-854</v>
       </c>
       <c r="E63" t="n">
-        <v>-4865</v>
+        <v>-2756</v>
       </c>
       <c r="F63" t="n">
-        <v>523</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>4027</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-1319</v>
+        <v>196</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3586,45 +3587,45 @@
         </is>
       </c>
       <c r="K63" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M63" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>-155</v>
+        <v>-182</v>
       </c>
       <c r="D64" t="n">
-        <v>-915</v>
+        <v>-872</v>
       </c>
       <c r="E64" t="n">
-        <v>-3282</v>
+        <v>-5110</v>
       </c>
       <c r="F64" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>-113</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-66</v>
+        <v>-22</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3637,11 +3638,11 @@
         </is>
       </c>
       <c r="K64" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M64" t="n">
@@ -3651,31 +3652,31 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>375</v>
+        <v>-752</v>
       </c>
       <c r="D65" t="n">
-        <v>-1000</v>
+        <v>-895</v>
       </c>
       <c r="E65" t="n">
-        <v>-490</v>
+        <v>-4592</v>
       </c>
       <c r="F65" t="n">
-        <v>-1</v>
+        <v>-89</v>
       </c>
       <c r="G65" t="n">
-        <v>444</v>
+        <v>4188</v>
       </c>
       <c r="H65" t="n">
-        <v>-590</v>
+        <v>-1288</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3684,49 +3685,49 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K65" t="n">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-3903</v>
+        <v>-383</v>
       </c>
       <c r="D66" t="n">
-        <v>-1034</v>
+        <v>-1020</v>
       </c>
       <c r="E66" t="n">
-        <v>-8244</v>
+        <v>-3154</v>
       </c>
       <c r="F66" t="n">
-        <v>-471</v>
+        <v>9</v>
       </c>
       <c r="G66" t="n">
-        <v>-11007</v>
+        <v>-110</v>
       </c>
       <c r="H66" t="n">
-        <v>-256</v>
+        <v>-67</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3735,49 +3736,49 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K66" t="n">
-        <v>44</v>
+        <v>96</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M66" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1006</v>
+        <v>-528</v>
       </c>
       <c r="D67" t="n">
-        <v>-1350</v>
+        <v>-1028</v>
       </c>
       <c r="E67" t="n">
-        <v>-7226</v>
+        <v>-1285</v>
       </c>
       <c r="F67" t="n">
-        <v>5</v>
+        <v>315</v>
       </c>
       <c r="G67" t="n">
-        <v>85</v>
+        <v>1353</v>
       </c>
       <c r="H67" t="n">
-        <v>-287</v>
+        <v>-40</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3786,49 +3787,49 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K67" t="n">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M67" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-71</v>
+        <v>702</v>
       </c>
       <c r="D68" t="n">
-        <v>-1404</v>
+        <v>-1223</v>
       </c>
       <c r="E68" t="n">
-        <v>-719</v>
+        <v>-7634</v>
       </c>
       <c r="F68" t="n">
-        <v>355</v>
+        <v>4</v>
       </c>
       <c r="G68" t="n">
-        <v>378</v>
+        <v>88</v>
       </c>
       <c r="H68" t="n">
-        <v>-126</v>
+        <v>-369</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3837,11 +3838,11 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K68" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -3849,37 +3850,37 @@
         </is>
       </c>
       <c r="M68" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-1079</v>
+        <v>-1309</v>
       </c>
       <c r="D69" t="n">
-        <v>-1406</v>
+        <v>-1575</v>
       </c>
       <c r="E69" t="n">
-        <v>-1046</v>
+        <v>-7014</v>
       </c>
       <c r="F69" t="n">
-        <v>8</v>
+        <v>-533</v>
       </c>
       <c r="G69" t="n">
-        <v>24</v>
+        <v>-11388</v>
       </c>
       <c r="H69" t="n">
-        <v>-105</v>
+        <v>-251</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3888,49 +3889,49 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K69" t="n">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M69" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-2242</v>
+        <v>2049</v>
       </c>
       <c r="D70" t="n">
-        <v>-1429</v>
+        <v>-1717</v>
       </c>
       <c r="E70" t="n">
-        <v>-1577</v>
+        <v>-3711</v>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>-181</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>-419</v>
       </c>
       <c r="H70" t="n">
-        <v>337</v>
+        <v>-5</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3951,37 +3952,37 @@
         </is>
       </c>
       <c r="M70" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>玉晶光</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-4587</v>
+        <v>-828</v>
       </c>
       <c r="D71" t="n">
-        <v>-1514</v>
+        <v>-1818</v>
       </c>
       <c r="E71" t="n">
-        <v>-7965</v>
+        <v>-596</v>
       </c>
       <c r="F71" t="n">
-        <v>2033</v>
+        <v>265</v>
       </c>
       <c r="G71" t="n">
-        <v>5161</v>
+        <v>-1670</v>
       </c>
       <c r="H71" t="n">
-        <v>-1169</v>
+        <v>-249</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -3990,53 +3991,53 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K71" t="n">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M71" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-339</v>
+        <v>-1923</v>
       </c>
       <c r="D72" t="n">
-        <v>-1639</v>
+        <v>-2054</v>
       </c>
       <c r="E72" t="n">
-        <v>-8724</v>
+        <v>-2055</v>
       </c>
       <c r="F72" t="n">
-        <v>-616</v>
+        <v>8</v>
       </c>
       <c r="G72" t="n">
-        <v>-2820</v>
+        <v>5</v>
       </c>
       <c r="H72" t="n">
-        <v>-32</v>
+        <v>-226</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>🟡 中性</t>
+          <t>🟠 減碼</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4059,31 +4060,31 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-2678</v>
+        <v>-909</v>
       </c>
       <c r="D73" t="n">
-        <v>-2145</v>
+        <v>-2218</v>
       </c>
       <c r="E73" t="n">
-        <v>-2270</v>
+        <v>-2434</v>
       </c>
       <c r="F73" t="n">
-        <v>2282</v>
+        <v>353</v>
       </c>
       <c r="G73" t="n">
-        <v>4732</v>
+        <v>380</v>
       </c>
       <c r="H73" t="n">
-        <v>-40</v>
+        <v>-253</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -4096,11 +4097,11 @@
         </is>
       </c>
       <c r="K73" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M73" t="n">
@@ -4110,31 +4111,31 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1265</v>
+        <v>-316</v>
       </c>
       <c r="D74" t="n">
-        <v>-2289</v>
+        <v>-2355</v>
       </c>
       <c r="E74" t="n">
-        <v>27571</v>
+        <v>-748</v>
       </c>
       <c r="F74" t="n">
-        <v>-115</v>
+        <v>-311</v>
       </c>
       <c r="G74" t="n">
-        <v>-12292</v>
+        <v>-61</v>
       </c>
       <c r="H74" t="n">
-        <v>-283</v>
+        <v>394</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -4147,45 +4148,45 @@
         </is>
       </c>
       <c r="K74" t="n">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M74" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1748</v>
+        <v>-2480</v>
       </c>
       <c r="D75" t="n">
-        <v>-2564</v>
+        <v>-2499</v>
       </c>
       <c r="E75" t="n">
-        <v>-4513</v>
+        <v>-2301</v>
       </c>
       <c r="F75" t="n">
-        <v>-179</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>-195</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-17</v>
+        <v>344</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -4206,37 +4207,37 @@
         </is>
       </c>
       <c r="M75" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>鈊象</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-694</v>
+        <v>-160</v>
       </c>
       <c r="D76" t="n">
-        <v>-2679</v>
+        <v>-2509</v>
       </c>
       <c r="E76" t="n">
-        <v>181</v>
+        <v>-13587</v>
       </c>
       <c r="F76" t="n">
-        <v>282</v>
+        <v>339</v>
       </c>
       <c r="G76" t="n">
-        <v>-1672</v>
+        <v>5162</v>
       </c>
       <c r="H76" t="n">
-        <v>-442</v>
+        <v>61</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -4249,11 +4250,11 @@
         </is>
       </c>
       <c r="K76" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M76" t="n">
@@ -4272,22 +4273,22 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-1233</v>
+        <v>-805</v>
       </c>
       <c r="D77" t="n">
-        <v>-2979</v>
+        <v>-3050</v>
       </c>
       <c r="E77" t="n">
-        <v>-2170</v>
+        <v>-2575</v>
       </c>
       <c r="F77" t="n">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="G77" t="n">
-        <v>-75</v>
+        <v>-60</v>
       </c>
       <c r="H77" t="n">
-        <v>213</v>
+        <v>167</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -4314,31 +4315,31 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-631</v>
+        <v>1261</v>
       </c>
       <c r="D78" t="n">
-        <v>-3047</v>
+        <v>-3096</v>
       </c>
       <c r="E78" t="n">
-        <v>-536</v>
+        <v>-9987</v>
       </c>
       <c r="F78" t="n">
-        <v>-447</v>
+        <v>1320</v>
       </c>
       <c r="G78" t="n">
-        <v>152</v>
+        <v>-993</v>
       </c>
       <c r="H78" t="n">
-        <v>386</v>
+        <v>-1184</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -4347,11 +4348,11 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K78" t="n">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -4359,37 +4360,37 @@
         </is>
       </c>
       <c r="M78" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>7350</v>
+        <v>-1263</v>
       </c>
       <c r="D79" t="n">
-        <v>-3134</v>
+        <v>-3111</v>
       </c>
       <c r="E79" t="n">
-        <v>-80385</v>
+        <v>-3631</v>
       </c>
       <c r="F79" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>15380</v>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-4170</v>
+        <v>-706</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -4406,41 +4407,41 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>-1727</v>
+        <v>-2727</v>
       </c>
       <c r="D80" t="n">
-        <v>-3213</v>
+        <v>-3480</v>
       </c>
       <c r="E80" t="n">
-        <v>-4356</v>
+        <v>-2979</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>2368</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>5684</v>
       </c>
       <c r="H80" t="n">
-        <v>-828</v>
+        <v>40</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -4449,15 +4450,15 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K80" t="n">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M80" t="n">
@@ -4467,31 +4468,31 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-9</v>
+        <v>-1779</v>
       </c>
       <c r="D81" t="n">
-        <v>-3492</v>
+        <v>-3627</v>
       </c>
       <c r="E81" t="n">
-        <v>-13319</v>
+        <v>-7016</v>
       </c>
       <c r="F81" t="n">
-        <v>582</v>
+        <v>5</v>
       </c>
       <c r="G81" t="n">
-        <v>6485</v>
+        <v>-4</v>
       </c>
       <c r="H81" t="n">
-        <v>-102</v>
+        <v>-150</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4500,11 +4501,11 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K81" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -4512,37 +4513,37 @@
         </is>
       </c>
       <c r="M81" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>802</v>
+        <v>-127</v>
       </c>
       <c r="D82" t="n">
-        <v>-3975</v>
+        <v>-4329</v>
       </c>
       <c r="E82" t="n">
-        <v>-15278</v>
+        <v>-4527</v>
       </c>
       <c r="F82" t="n">
-        <v>1420</v>
+        <v>41</v>
       </c>
       <c r="G82" t="n">
-        <v>-1805</v>
+        <v>2820</v>
       </c>
       <c r="H82" t="n">
-        <v>-1116</v>
+        <v>-206</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -4551,15 +4552,15 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K82" t="n">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M82" t="n">
@@ -4569,31 +4570,31 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-1580</v>
+        <v>-1801</v>
       </c>
       <c r="D83" t="n">
-        <v>-4332</v>
+        <v>-4486</v>
       </c>
       <c r="E83" t="n">
-        <v>-7022</v>
+        <v>-14565</v>
       </c>
       <c r="F83" t="n">
-        <v>5</v>
+        <v>468</v>
       </c>
       <c r="G83" t="n">
-        <v>-5</v>
+        <v>674</v>
       </c>
       <c r="H83" t="n">
-        <v>-323</v>
+        <v>60</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -4602,19 +4603,19 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K83" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="84">
@@ -4629,22 +4630,22 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-797</v>
+        <v>-698</v>
       </c>
       <c r="D84" t="n">
-        <v>-4856</v>
+        <v>-4532</v>
       </c>
       <c r="E84" t="n">
-        <v>-7261</v>
+        <v>-7107</v>
       </c>
       <c r="F84" t="n">
-        <v>1583</v>
+        <v>1321</v>
       </c>
       <c r="G84" t="n">
-        <v>2288</v>
+        <v>2511</v>
       </c>
       <c r="H84" t="n">
-        <v>-97</v>
+        <v>-177</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -4671,31 +4672,31 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>-1896</v>
+        <v>3698</v>
       </c>
       <c r="D85" t="n">
-        <v>-5062</v>
+        <v>-4533</v>
       </c>
       <c r="E85" t="n">
-        <v>-14340</v>
+        <v>-60113</v>
       </c>
       <c r="F85" t="n">
-        <v>538</v>
+        <v>139</v>
       </c>
       <c r="G85" t="n">
-        <v>593</v>
+        <v>7384</v>
       </c>
       <c r="H85" t="n">
-        <v>68</v>
+        <v>-259</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -4704,11 +4705,11 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K85" t="n">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -4716,37 +4717,37 @@
         </is>
       </c>
       <c r="M85" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-874</v>
+        <v>-4835</v>
       </c>
       <c r="D86" t="n">
-        <v>-5351</v>
+        <v>-4709</v>
       </c>
       <c r="E86" t="n">
-        <v>-4944</v>
+        <v>-7905</v>
       </c>
       <c r="F86" t="n">
-        <v>145</v>
+        <v>1486</v>
       </c>
       <c r="G86" t="n">
-        <v>3292</v>
+        <v>5109</v>
       </c>
       <c r="H86" t="n">
-        <v>-252</v>
+        <v>-1322</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -4755,19 +4756,19 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K86" t="n">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M86" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
@@ -4782,22 +4783,22 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>-652</v>
+        <v>-760</v>
       </c>
       <c r="D87" t="n">
-        <v>-5467</v>
+        <v>-5219</v>
       </c>
       <c r="E87" t="n">
-        <v>-12729</v>
+        <v>-12756</v>
       </c>
       <c r="F87" t="n">
-        <v>-542</v>
+        <v>-455</v>
       </c>
       <c r="G87" t="n">
-        <v>-938</v>
+        <v>-936</v>
       </c>
       <c r="H87" t="n">
-        <v>-71</v>
+        <v>-132</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -4824,31 +4825,31 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>3633</v>
+        <v>-837</v>
       </c>
       <c r="D88" t="n">
-        <v>-5523</v>
+        <v>-5385</v>
       </c>
       <c r="E88" t="n">
-        <v>-61516</v>
+        <v>-12266</v>
       </c>
       <c r="F88" t="n">
-        <v>216</v>
+        <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>7758</v>
+        <v>-215</v>
       </c>
       <c r="H88" t="n">
-        <v>-266</v>
+        <v>-140</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -4857,49 +4858,49 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K88" t="n">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M88" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-2290</v>
+        <v>-123</v>
       </c>
       <c r="D89" t="n">
-        <v>-5973</v>
+        <v>-5927</v>
       </c>
       <c r="E89" t="n">
-        <v>-7023</v>
+        <v>-5299</v>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>311</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H89" t="n">
-        <v>2145</v>
+        <v>-93</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4912,7 +4913,7 @@
         </is>
       </c>
       <c r="K89" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -4920,37 +4921,37 @@
         </is>
       </c>
       <c r="M89" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>316</v>
+        <v>-1431</v>
       </c>
       <c r="D90" t="n">
-        <v>-6117</v>
+        <v>-6181</v>
       </c>
       <c r="E90" t="n">
-        <v>-5230</v>
+        <v>-7200</v>
       </c>
       <c r="F90" t="n">
-        <v>361</v>
+        <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>1917</v>
+        <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>-93</v>
+        <v>2039</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -4963,7 +4964,7 @@
         </is>
       </c>
       <c r="K90" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -4971,139 +4972,139 @@
         </is>
       </c>
       <c r="M90" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>立隆電</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>-1194</v>
+        <v>1158</v>
       </c>
       <c r="D91" t="n">
-        <v>-6255</v>
+        <v>-8869</v>
       </c>
       <c r="E91" t="n">
-        <v>-13880</v>
+        <v>-13660</v>
       </c>
       <c r="F91" t="n">
+        <v>1385</v>
+      </c>
+      <c r="G91" t="n">
+        <v>9671</v>
+      </c>
+      <c r="H91" t="n">
+        <v>-133</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>🟠 減碼</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>79</v>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M91" t="n">
         <v>1</v>
-      </c>
-      <c r="G91" t="n">
-        <v>285</v>
-      </c>
-      <c r="H91" t="n">
-        <v>-149</v>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>🟠 減碼</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K91" t="n">
-        <v>78</v>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>📉 減速</t>
-        </is>
-      </c>
-      <c r="M91" t="n">
-        <v>-5</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>-365</v>
+        <v>-3515</v>
       </c>
       <c r="D92" t="n">
-        <v>-8714</v>
+        <v>-12013</v>
       </c>
       <c r="E92" t="n">
-        <v>-13871</v>
+        <v>-26685</v>
       </c>
       <c r="F92" t="n">
-        <v>1497</v>
+        <v>2361</v>
       </c>
       <c r="G92" t="n">
-        <v>9851</v>
+        <v>10380</v>
       </c>
       <c r="H92" t="n">
-        <v>-81</v>
+        <v>330</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🔴 大賣</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K92" t="n">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M92" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>-2706</v>
+        <v>1056</v>
       </c>
       <c r="D93" t="n">
-        <v>-10154</v>
+        <v>-17409</v>
       </c>
       <c r="E93" t="n">
-        <v>-23643</v>
+        <v>-34691</v>
       </c>
       <c r="F93" t="n">
-        <v>2673</v>
+        <v>89</v>
       </c>
       <c r="G93" t="n">
-        <v>9734</v>
+        <v>22959</v>
       </c>
       <c r="H93" t="n">
-        <v>377</v>
+        <v>-142</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -5112,49 +5113,49 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K93" t="n">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M93" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>806</v>
+        <v>-4835</v>
       </c>
       <c r="D94" t="n">
-        <v>-16007</v>
+        <v>-18917</v>
       </c>
       <c r="E94" t="n">
-        <v>-35880</v>
+        <v>-27211</v>
       </c>
       <c r="F94" t="n">
-        <v>231</v>
+        <v>-60</v>
       </c>
       <c r="G94" t="n">
-        <v>23003</v>
+        <v>-11991</v>
       </c>
       <c r="H94" t="n">
-        <v>176</v>
+        <v>-2202</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -5167,7 +5168,7 @@
         </is>
       </c>
       <c r="K94" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -5175,37 +5176,37 @@
         </is>
       </c>
       <c r="M94" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>-4659</v>
+        <v>14833</v>
       </c>
       <c r="D95" t="n">
-        <v>-18463</v>
+        <v>-19024</v>
       </c>
       <c r="E95" t="n">
-        <v>-28577</v>
+        <v>18016</v>
       </c>
       <c r="F95" t="n">
-        <v>-521</v>
+        <v>10554</v>
       </c>
       <c r="G95" t="n">
-        <v>-12838</v>
+        <v>39608</v>
       </c>
       <c r="H95" t="n">
-        <v>-2290</v>
+        <v>-377</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -5218,15 +5219,15 @@
         </is>
       </c>
       <c r="K95" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M95" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="96">
@@ -5241,22 +5242,22 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>-1936</v>
+        <v>-6149</v>
       </c>
       <c r="D96" t="n">
-        <v>-22033</v>
+        <v>-25264</v>
       </c>
       <c r="E96" t="n">
-        <v>528</v>
+        <v>-3200</v>
       </c>
       <c r="F96" t="n">
-        <v>-15</v>
+        <v>-29</v>
       </c>
       <c r="G96" t="n">
-        <v>12811</v>
+        <v>12789</v>
       </c>
       <c r="H96" t="n">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -5283,31 +5284,31 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>-5075</v>
+        <v>-17527</v>
       </c>
       <c r="D97" t="n">
-        <v>-26073</v>
+        <v>-30863</v>
       </c>
       <c r="E97" t="n">
-        <v>12148</v>
+        <v>-287381</v>
       </c>
       <c r="F97" t="n">
-        <v>14553</v>
+        <v>8959</v>
       </c>
       <c r="G97" t="n">
-        <v>38989</v>
+        <v>36222</v>
       </c>
       <c r="H97" t="n">
-        <v>-812</v>
+        <v>2653</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -5316,49 +5317,49 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K97" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M97" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-16777</v>
+        <v>-15028</v>
       </c>
       <c r="D98" t="n">
-        <v>-34505</v>
+        <v>-45392</v>
       </c>
       <c r="E98" t="n">
-        <v>-286027</v>
+        <v>84636</v>
       </c>
       <c r="F98" t="n">
-        <v>8880</v>
+        <v>5404</v>
       </c>
       <c r="G98" t="n">
-        <v>41851</v>
+        <v>67240</v>
       </c>
       <c r="H98" t="n">
-        <v>2510</v>
+        <v>-3555</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -5367,19 +5368,19 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K98" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M98" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99">
@@ -5394,22 +5395,22 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>-17188</v>
+        <v>-42758</v>
       </c>
       <c r="D99" t="n">
-        <v>-40811</v>
+        <v>-58374</v>
       </c>
       <c r="E99" t="n">
-        <v>72145</v>
+        <v>44015</v>
       </c>
       <c r="F99" t="n">
-        <v>21313</v>
+        <v>20343</v>
       </c>
       <c r="G99" t="n">
-        <v>41248</v>
+        <v>44243</v>
       </c>
       <c r="H99" t="n">
-        <v>16775</v>
+        <v>15690</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -5445,22 +5446,22 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>-29598</v>
+        <v>-19106</v>
       </c>
       <c r="D100" t="n">
-        <v>-76163</v>
+        <v>-82135</v>
       </c>
       <c r="E100" t="n">
-        <v>-268429</v>
+        <v>-254691</v>
       </c>
       <c r="F100" t="n">
-        <v>2513</v>
+        <v>2222</v>
       </c>
       <c r="G100" t="n">
-        <v>6285</v>
+        <v>6965</v>
       </c>
       <c r="H100" t="n">
-        <v>7538</v>
+        <v>8341</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -5496,22 +5497,22 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-33457</v>
+        <v>-23531</v>
       </c>
       <c r="D101" t="n">
-        <v>-88983</v>
+        <v>-88104</v>
       </c>
       <c r="E101" t="n">
-        <v>-137702</v>
+        <v>-136635</v>
       </c>
       <c r="F101" t="n">
-        <v>11766</v>
+        <v>8679</v>
       </c>
       <c r="G101" t="n">
-        <v>31542</v>
+        <v>32252</v>
       </c>
       <c r="H101" t="n">
-        <v>-8637</v>
+        <v>-9800</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -5547,22 +5548,22 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>-17284</v>
+        <v>-11528</v>
       </c>
       <c r="D102" t="n">
-        <v>-150663</v>
+        <v>-153043</v>
       </c>
       <c r="E102" t="n">
-        <v>-169115</v>
+        <v>-171211</v>
       </c>
       <c r="F102" t="n">
-        <v>15436</v>
+        <v>18426</v>
       </c>
       <c r="G102" t="n">
-        <v>141120</v>
+        <v>147305</v>
       </c>
       <c r="H102" t="n">
-        <v>2367</v>
+        <v>2324</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -5598,22 +5599,22 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>-20766</v>
+        <v>-22532</v>
       </c>
       <c r="D103" t="n">
-        <v>-196111</v>
+        <v>-199243</v>
       </c>
       <c r="E103" t="n">
-        <v>360681</v>
+        <v>356777</v>
       </c>
       <c r="F103" t="n">
-        <v>6242</v>
+        <v>5231</v>
       </c>
       <c r="G103" t="n">
-        <v>6266</v>
+        <v>6244</v>
       </c>
       <c r="H103" t="n">
-        <v>-2406</v>
+        <v>-3220</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -5640,31 +5641,31 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>-27735</v>
+        <v>-30017</v>
       </c>
       <c r="D104" t="n">
-        <v>-209936</v>
+        <v>-207241</v>
       </c>
       <c r="E104" t="n">
-        <v>-11438</v>
+        <v>-118043</v>
       </c>
       <c r="F104" t="n">
-        <v>-40652</v>
+        <v>6471</v>
       </c>
       <c r="G104" t="n">
-        <v>110822</v>
+        <v>73162</v>
       </c>
       <c r="H104" t="n">
-        <v>2132</v>
+        <v>-5485</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -5677,66 +5678,3046 @@
         </is>
       </c>
       <c r="K104" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M104" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>-31079</v>
+      </c>
+      <c r="D105" t="n">
+        <v>-257171</v>
+      </c>
+      <c r="E105" t="n">
+        <v>-18450</v>
+      </c>
+      <c r="F105" t="n">
+        <v>-22536</v>
+      </c>
+      <c r="G105" t="n">
+        <v>107654</v>
+      </c>
+      <c r="H105" t="n">
+        <v>-1004</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>🔴 大賣</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K105" t="n">
+        <v>56</v>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>📉 減速</t>
+        </is>
+      </c>
+      <c r="M105" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G102"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>代號</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>訊號</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>外資5d</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>外資20d</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>外資5d(昨)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>外資20d(昨)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>名稱</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>8996</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 447 千股)</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>111432</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2326367</v>
+      </c>
+      <c r="E2" t="n">
+        <v>485589</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1879108</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -468 千股)</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>-1260480</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1579726</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-417700</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2047743</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3653</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 99 千股)</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>344513</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2841187</v>
+      </c>
+      <c r="E4" t="n">
+        <v>157487</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2742229</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -3,194 千股)</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>-4835084</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-4708503</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-4587432</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-1514395</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>亞翔</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>8210</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 981 千股)</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>38111</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-657575</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-338736</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-1638900</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>勤誠</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 712 千股)</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>-1882397</v>
+      </c>
+      <c r="D7" t="n">
+        <v>790433</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-1546922</v>
+      </c>
+      <c r="F7" t="n">
+        <v>78601</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>6442</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 523 千股)</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>817238</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-184455</v>
+      </c>
+      <c r="E8" t="n">
+        <v>81333</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-707351</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>光聖</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -316 千股)</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>-528262</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-1027968</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-237369</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-711587</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 705 千股)</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>-1779018</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-3627228</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-1580184</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-4332184</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>雙鴻</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -94 千股)</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2030702</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6054926</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2018468</v>
+      </c>
+      <c r="F11" t="n">
+        <v>6149043</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -5,972 千股)</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>-19106462</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-82134727</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-29598185</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-76162501</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -892 千股)</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>-3183994</v>
+      </c>
+      <c r="D13" t="n">
+        <v>7045383</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-3061802</v>
+      </c>
+      <c r="F13" t="n">
+        <v>7937798</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2308</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -454 千股)</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>-4835097</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-18916841</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-4659101</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-18463334</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>台達電</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>6196</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 213 千股)</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>989236</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-21167</v>
+      </c>
+      <c r="E15" t="n">
+        <v>536850</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-233731</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>帆宣</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>6197</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -648 千股)</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>-1923289</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-2053861</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-1078637</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-1406115</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>佳必琪</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -29 千股)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>-220363</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-12424</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-294861</v>
+      </c>
+      <c r="F17" t="n">
+        <v>16387</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>3583</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -316 千股)</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>168739</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1390786</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-642866</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1706839</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>辛耘</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>5434</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -1,335 千股)</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>-2727139</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-3480074</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-2677517</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-2145024</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>崇越</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1513</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -1,401 千股)</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1056115</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-17408642</v>
+      </c>
+      <c r="E20" t="n">
+        <v>805811</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-16007257</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>中興電</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 692 千股)</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>-315914</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-2355471</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-631103</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-3047283</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1560</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 26 千股)</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>-571714</v>
+      </c>
+      <c r="D22" t="n">
+        <v>902687</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-624857</v>
+      </c>
+      <c r="F22" t="n">
+        <v>877035</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>中砂</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>5340</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -700 千股)</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>-182089</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-872369</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-113922</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-172466</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>建榮</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1519</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 248 千股)</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>-760343</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-5219138</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-651890</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-5466930</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>華城</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>3029</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 267 千股)</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1316327</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2892791</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1631793</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2625658</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>零壹</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>5519</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -1,070 千股)</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>-2480199</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-2499344</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-2242249</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-1429063</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>隆大</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>4506</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 50 千股)</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>73877</v>
+      </c>
+      <c r="D27" t="n">
+        <v>378165</v>
+      </c>
+      <c r="E27" t="n">
+        <v>26277</v>
+      </c>
+      <c r="F27" t="n">
+        <v>328405</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>崇友</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>3689</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 640 千股)</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>-178376</v>
+      </c>
+      <c r="D28" t="n">
+        <v>610952</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-77256</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-28638</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>湧德</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2421</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -813 千股)</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>-908589</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-2217608</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-70617</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-1404111</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>建準</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1618</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -170 千股)</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>-982639</v>
+      </c>
+      <c r="D30" t="n">
+        <v>204816</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-381908</v>
+      </c>
+      <c r="F30" t="n">
+        <v>374792</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>合機</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 847 千股)</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>2049176</v>
+      </c>
+      <c r="D31" t="n">
+        <v>-1717014</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1747876</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-2564024</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>卜蜂</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>6189</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 772 千股)</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>465704</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1164486</v>
+      </c>
+      <c r="E32" t="n">
+        <v>603874</v>
+      </c>
+      <c r="F32" t="n">
+        <v>392531</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>豐藝</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>5904</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -417 千股)</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>-645937</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-484560</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-401425</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-67839</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>寶雅</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1232</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 325 千股)</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>148081</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-308542</v>
+      </c>
+      <c r="E34" t="n">
+        <v>188106</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-633348</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>大統益</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2618</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 20,270 千股)</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>165901765</v>
+      </c>
+      <c r="D35" t="n">
+        <v>314442831</v>
+      </c>
+      <c r="E35" t="n">
+        <v>102976642</v>
+      </c>
+      <c r="F35" t="n">
+        <v>294172415</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>長榮航</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>5478</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -90 千股)</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>-104042</v>
+      </c>
+      <c r="D36" t="n">
+        <v>195746</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-65050</v>
+      </c>
+      <c r="F36" t="n">
+        <v>285739</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>智冠</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -53 千股)</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>-265325</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-490472</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-352439</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-437104</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>6788</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -105 千股)</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>-383436</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-1020135</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-155463</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-915226</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>華景電</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2753</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -381 千股)</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>-304235</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-304465</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-173892</v>
+      </c>
+      <c r="F39" t="n">
+        <v>76456</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>八方雲集</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>3045</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 7,048 千股)</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>14833221</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-19024441</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-5075202</v>
+      </c>
+      <c r="F40" t="n">
+        <v>-26072637</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>台灣大</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>4129</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 25 千股)</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>-4000</v>
+      </c>
+      <c r="D41" t="n">
+        <v>-251300</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-59300</v>
+      </c>
+      <c r="F41" t="n">
+        <v>-276300</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>聯合</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2912</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 990 千股)</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>3697648</v>
+      </c>
+      <c r="D42" t="n">
+        <v>-4532913</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3632738</v>
+      </c>
+      <c r="F42" t="n">
+        <v>-5523286</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>統一超</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>3402</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 333 千股)</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>104209</v>
+      </c>
+      <c r="D43" t="n">
+        <v>3652384</v>
+      </c>
+      <c r="E43" t="n">
+        <v>154723</v>
+      </c>
+      <c r="F43" t="n">
+        <v>3319191</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>漢科</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>1514</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 268 千股)</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1932952</v>
+      </c>
+      <c r="D44" t="n">
+        <v>590996</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1551741</v>
+      </c>
+      <c r="F44" t="n">
+        <v>322959</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>亞力</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -119 千股)</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>-752022</v>
+      </c>
+      <c r="D45" t="n">
+        <v>-895485</v>
+      </c>
+      <c r="E45" t="n">
+        <v>-1602097</v>
+      </c>
+      <c r="F45" t="n">
+        <v>-776430</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>3147</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -81 千股)</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>105365</v>
+      </c>
+      <c r="D46" t="n">
+        <v>-599461</v>
+      </c>
+      <c r="E46" t="n">
+        <v>282866</v>
+      </c>
+      <c r="F46" t="n">
+        <v>-518692</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>大綜</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2472</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -155 千股)</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1157738</v>
+      </c>
+      <c r="D47" t="n">
+        <v>-8868544</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-364777</v>
+      </c>
+      <c r="F47" t="n">
+        <v>-8713956</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>立隆電</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>3260</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 879 千股)</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>1261328</v>
+      </c>
+      <c r="D48" t="n">
+        <v>-3096187</v>
+      </c>
+      <c r="E48" t="n">
+        <v>801858</v>
+      </c>
+      <c r="F48" t="n">
+        <v>-3975426</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>威剛</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>3406</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 861 千股)</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>-827679</v>
+      </c>
+      <c r="D49" t="n">
+        <v>-1817899</v>
+      </c>
+      <c r="E49" t="n">
+        <v>-694425</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-2678969</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>玉晶光</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>3661</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -71 千股)</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>-805452</v>
+      </c>
+      <c r="D50" t="n">
+        <v>-3049831</v>
+      </c>
+      <c r="E50" t="n">
+        <v>-1232514</v>
+      </c>
+      <c r="F50" t="n">
+        <v>-2978661</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>世芯-KY</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -54,242 千股)</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>-15028303</v>
+      </c>
+      <c r="D51" t="n">
+        <v>-45392226</v>
+      </c>
+      <c r="E51" t="n">
+        <v>6597485</v>
+      </c>
+      <c r="F51" t="n">
+        <v>8849613</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2327</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 3,631 千股)</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>10346533</v>
+      </c>
+      <c r="D52" t="n">
+        <v>496568</v>
+      </c>
+      <c r="E52" t="n">
+        <v>7350345</v>
+      </c>
+      <c r="F52" t="n">
+        <v>-3133976</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>3293</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 983 千股)</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>-160203</v>
+      </c>
+      <c r="D53" t="n">
+        <v>-2509047</v>
+      </c>
+      <c r="E53" t="n">
+        <v>-8923</v>
+      </c>
+      <c r="F53" t="n">
+        <v>-3492289</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>鈊象</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -4,786 千股)</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>-14884397</v>
+      </c>
+      <c r="D54" t="n">
+        <v>42017787</v>
+      </c>
+      <c r="E54" t="n">
+        <v>-30100117</v>
+      </c>
+      <c r="F54" t="n">
+        <v>46804087</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2476</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -208 千股)</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>-1431349</v>
+      </c>
+      <c r="D55" t="n">
+        <v>-6181312</v>
+      </c>
+      <c r="E55" t="n">
+        <v>-2289673</v>
+      </c>
+      <c r="F55" t="n">
+        <v>-5973401</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>1503</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 127 千股)</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>702120</v>
+      </c>
+      <c r="D56" t="n">
+        <v>-1223205</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1006160</v>
+      </c>
+      <c r="F56" t="n">
+        <v>-1350330</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>士電</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2535</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -149 千股)</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>-137557</v>
+      </c>
+      <c r="D57" t="n">
+        <v>633627</v>
+      </c>
+      <c r="E57" t="n">
+        <v>-169018</v>
+      </c>
+      <c r="F57" t="n">
+        <v>782519</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>達欣工</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>6263</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 27 千股)</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>-386947</v>
+      </c>
+      <c r="D58" t="n">
+        <v>-695983</v>
+      </c>
+      <c r="E58" t="n">
+        <v>-212730</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-722511</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>普萊德</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>1773</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -515 千股)</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>129382</v>
+      </c>
+      <c r="D59" t="n">
+        <v>586719</v>
+      </c>
+      <c r="E59" t="n">
+        <v>452685</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1101286</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>勝一</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>1590</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 157 千股)</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>464022</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1266597</v>
+      </c>
+      <c r="E60" t="n">
+        <v>339584</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1109545</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>亞德客-KY</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 130 千股)</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>-296842</v>
+      </c>
+      <c r="D61" t="n">
+        <v>40334</v>
+      </c>
+      <c r="E61" t="n">
+        <v>-458462</v>
+      </c>
+      <c r="F61" t="n">
+        <v>-89666</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>信立</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>5269</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 211 千股)</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>86309</v>
+      </c>
+      <c r="D62" t="n">
+        <v>497896</v>
+      </c>
+      <c r="E62" t="n">
+        <v>-313334</v>
+      </c>
+      <c r="F62" t="n">
+        <v>286589</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>祥碩</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>4979</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 155 千股)</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>-1016793</v>
+      </c>
+      <c r="D63" t="n">
+        <v>274016</v>
+      </c>
+      <c r="E63" t="n">
+        <v>-2813216</v>
+      </c>
+      <c r="F63" t="n">
+        <v>119299</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>華星光</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>6446</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -478 千股)</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>-2412807</v>
+      </c>
+      <c r="D64" t="n">
+        <v>2991490</v>
+      </c>
+      <c r="E64" t="n">
+        <v>-2013643</v>
+      </c>
+      <c r="F64" t="n">
+        <v>3469071</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>藥華藥</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>3450</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 665 千股)</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>341101</v>
+      </c>
+      <c r="D65" t="n">
+        <v>-334683</v>
+      </c>
+      <c r="E65" t="n">
+        <v>374711</v>
+      </c>
+      <c r="F65" t="n">
+        <v>-999660</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>聯鈞</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2382</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 3,642 千股)</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>-17526992</v>
+      </c>
+      <c r="D66" t="n">
+        <v>-30863255</v>
+      </c>
+      <c r="E66" t="n">
+        <v>-16776571</v>
+      </c>
+      <c r="F66" t="n">
+        <v>-34504936</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>廣達</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>3081</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -2,993 千股)</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>-1024328</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1046760</v>
+      </c>
+      <c r="E67" t="n">
+        <v>-633698</v>
+      </c>
+      <c r="F67" t="n">
+        <v>4039494</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>8271</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 575 千股)</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>-1800561</v>
+      </c>
+      <c r="D68" t="n">
+        <v>-4486320</v>
+      </c>
+      <c r="E68" t="n">
+        <v>-1896495</v>
+      </c>
+      <c r="F68" t="n">
+        <v>-5061734</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>宇瞻</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
           <t>3231</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 3,151 千股)</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>-30017275</v>
+      </c>
+      <c r="D69" t="n">
+        <v>-207240513</v>
+      </c>
+      <c r="E69" t="n">
+        <v>-33660192</v>
+      </c>
+      <c r="F69" t="n">
+        <v>-210391670</v>
+      </c>
+      <c r="G69" t="inlineStr">
         <is>
           <t>緯創</t>
         </is>
       </c>
-      <c r="C105" t="n">
-        <v>-33660</v>
-      </c>
-      <c r="D105" t="n">
-        <v>-210392</v>
-      </c>
-      <c r="E105" t="n">
-        <v>-113002</v>
-      </c>
-      <c r="F105" t="n">
-        <v>10690</v>
-      </c>
-      <c r="G105" t="n">
-        <v>73649</v>
-      </c>
-      <c r="H105" t="n">
-        <v>-5030</v>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>🔴 大賣</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K105" t="n">
-        <v>62</v>
-      </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>🚀 加速器</t>
-        </is>
-      </c>
-      <c r="M105" t="n">
-        <v>-1</v>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2379</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -1,859 千股)</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>-3514951</v>
+      </c>
+      <c r="D70" t="n">
+        <v>-12013199</v>
+      </c>
+      <c r="E70" t="n">
+        <v>-2706331</v>
+      </c>
+      <c r="F70" t="n">
+        <v>-10154168</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>瑞昱</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 1,845 千股)</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>10098371</v>
+      </c>
+      <c r="D71" t="n">
+        <v>21829304</v>
+      </c>
+      <c r="E71" t="n">
+        <v>6277490</v>
+      </c>
+      <c r="F71" t="n">
+        <v>19984601</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>光寶科</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>1616</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -137 千股)</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>-607571</v>
+      </c>
+      <c r="D72" t="n">
+        <v>-854488</v>
+      </c>
+      <c r="E72" t="n">
+        <v>-579959</v>
+      </c>
+      <c r="F72" t="n">
+        <v>-717235</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>億泰</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>5511</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 37 千股)</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>-696227</v>
+      </c>
+      <c r="D73" t="n">
+        <v>115356</v>
+      </c>
+      <c r="E73" t="n">
+        <v>-797741</v>
+      </c>
+      <c r="F73" t="n">
+        <v>78314</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>德昌</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>8926</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -3,231 千股)</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>-6149467</v>
+      </c>
+      <c r="D74" t="n">
+        <v>-25264054</v>
+      </c>
+      <c r="E74" t="n">
+        <v>-1936244</v>
+      </c>
+      <c r="F74" t="n">
+        <v>-22033033</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>台汽電</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3596</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -472 千股)</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>500132</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2451927</v>
+      </c>
+      <c r="E75" t="n">
+        <v>299534</v>
+      </c>
+      <c r="F75" t="n">
+        <v>2923903</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>智易</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>4933</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -16 千股)</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>-111000</v>
+      </c>
+      <c r="D76" t="n">
+        <v>-427564</v>
+      </c>
+      <c r="E76" t="n">
+        <v>-35000</v>
+      </c>
+      <c r="F76" t="n">
+        <v>-411564</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>友輝</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>3227</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -692 千股)</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>-2486742</v>
+      </c>
+      <c r="D77" t="n">
+        <v>4385555</v>
+      </c>
+      <c r="E77" t="n">
+        <v>-1954648</v>
+      </c>
+      <c r="F77" t="n">
+        <v>5077736</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>原相</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>6285</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 4,427 千股)</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>1853210</v>
+      </c>
+      <c r="D78" t="n">
+        <v>2138111</v>
+      </c>
+      <c r="E78" t="n">
+        <v>1264568</v>
+      </c>
+      <c r="F78" t="n">
+        <v>-2288735</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>啟碁</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>6510</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -131 千股)</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>-98396</v>
+      </c>
+      <c r="D79" t="n">
+        <v>109766</v>
+      </c>
+      <c r="E79" t="n">
+        <v>-90882</v>
+      </c>
+      <c r="F79" t="n">
+        <v>240815</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>精測</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2356</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -17,563 千股)</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>-42758358</v>
+      </c>
+      <c r="D80" t="n">
+        <v>-58373805</v>
+      </c>
+      <c r="E80" t="n">
+        <v>-17187609</v>
+      </c>
+      <c r="F80" t="n">
+        <v>-40811097</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>英業達</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2317</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -3,131 千股)</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>-22531859</v>
+      </c>
+      <c r="D81" t="n">
+        <v>-199242648</v>
+      </c>
+      <c r="E81" t="n">
+        <v>-20766181</v>
+      </c>
+      <c r="F81" t="n">
+        <v>-196111151</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>鴻海</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>5243</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 869 千股)</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>-837370</v>
+      </c>
+      <c r="D82" t="n">
+        <v>-5385329</v>
+      </c>
+      <c r="E82" t="n">
+        <v>-1193641</v>
+      </c>
+      <c r="F82" t="n">
+        <v>-6254690</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>乙盛-KY</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>5225</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -126 千股)</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>-120580</v>
+      </c>
+      <c r="D83" t="n">
+        <v>203295</v>
+      </c>
+      <c r="E83" t="n">
+        <v>-14830</v>
+      </c>
+      <c r="F83" t="n">
+        <v>329194</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>東科-KY</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>8086</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 102 千股)</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>-1263264</v>
+      </c>
+      <c r="D84" t="n">
+        <v>-3110667</v>
+      </c>
+      <c r="E84" t="n">
+        <v>-1726873</v>
+      </c>
+      <c r="F84" t="n">
+        <v>-3212630</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>宏捷科</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>3188</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 358 千股)</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>83065</v>
+      </c>
+      <c r="D85" t="n">
+        <v>-381662</v>
+      </c>
+      <c r="E85" t="n">
+        <v>55065</v>
+      </c>
+      <c r="F85" t="n">
+        <v>-739558</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>鑫龍騰</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2305</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -1,149 千股)</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>-1719571</v>
+      </c>
+      <c r="D86" t="n">
+        <v>-566448</v>
+      </c>
+      <c r="E86" t="n">
+        <v>-1471571</v>
+      </c>
+      <c r="F86" t="n">
+        <v>582620</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>全友</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2395</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -219 千股)</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>857867</v>
+      </c>
+      <c r="D87" t="n">
+        <v>4019230</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1504570</v>
+      </c>
+      <c r="F87" t="n">
+        <v>4238328</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2412</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 879 千股)</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>-23531277</v>
+      </c>
+      <c r="D88" t="n">
+        <v>-88104038</v>
+      </c>
+      <c r="E88" t="n">
+        <v>-33457248</v>
+      </c>
+      <c r="F88" t="n">
+        <v>-88982939</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>中華電</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>9917</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 190 千股)</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>-123084</v>
+      </c>
+      <c r="D89" t="n">
+        <v>-5926808</v>
+      </c>
+      <c r="E89" t="n">
+        <v>316313</v>
+      </c>
+      <c r="F89" t="n">
+        <v>-6116747</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>中保科</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2645</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -2,248 千股)</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>-1002456</v>
+      </c>
+      <c r="D90" t="n">
+        <v>6407559</v>
+      </c>
+      <c r="E90" t="n">
+        <v>1346923</v>
+      </c>
+      <c r="F90" t="n">
+        <v>8655988</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>長榮航太</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>6739</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -13 千股)</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>-1922</v>
+      </c>
+      <c r="D91" t="n">
+        <v>-161697</v>
+      </c>
+      <c r="E91" t="n">
+        <v>-89468</v>
+      </c>
+      <c r="F91" t="n">
+        <v>-148545</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>6690</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -30 千股)</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>68050</v>
+      </c>
+      <c r="D92" t="n">
+        <v>-460745</v>
+      </c>
+      <c r="E92" t="n">
+        <v>33616</v>
+      </c>
+      <c r="F92" t="n">
+        <v>-430382</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>安碁資訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>4904</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -2,380 千股)</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>-11528119</v>
+      </c>
+      <c r="D93" t="n">
+        <v>-153043108</v>
+      </c>
+      <c r="E93" t="n">
+        <v>-17284376</v>
+      </c>
+      <c r="F93" t="n">
+        <v>-150663423</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>遠傳</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>4569</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -13 千股)</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>-20000</v>
+      </c>
+      <c r="D94" t="n">
+        <v>122887</v>
+      </c>
+      <c r="E94" t="n">
+        <v>9000</v>
+      </c>
+      <c r="F94" t="n">
+        <v>135847</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>六方科-KY</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -47,235 千股)</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>-31079291</v>
+      </c>
+      <c r="D95" t="n">
+        <v>-257171105</v>
+      </c>
+      <c r="E95" t="n">
+        <v>-27735143</v>
+      </c>
+      <c r="F95" t="n">
+        <v>-209936265</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 1,022 千股)</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>-126812</v>
+      </c>
+      <c r="D96" t="n">
+        <v>-4329127</v>
+      </c>
+      <c r="E96" t="n">
+        <v>-874364</v>
+      </c>
+      <c r="F96" t="n">
+        <v>-5350977</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -541 千股)</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>-1309348</v>
+      </c>
+      <c r="D97" t="n">
+        <v>-1574947</v>
+      </c>
+      <c r="E97" t="n">
+        <v>-3902539</v>
+      </c>
+      <c r="F97" t="n">
+        <v>-1033870</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 324 千股)</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>-697969</v>
+      </c>
+      <c r="D98" t="n">
+        <v>-4531646</v>
+      </c>
+      <c r="E98" t="n">
+        <v>-796614</v>
+      </c>
+      <c r="F98" t="n">
+        <v>-4855800</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 2,731 千股)</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>2732167</v>
+      </c>
+      <c r="D99" t="n">
+        <v>6544667</v>
+      </c>
+      <c r="E99" t="n">
+        <v>1182641</v>
+      </c>
+      <c r="F99" t="n">
+        <v>3813387</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>5274</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -63 千股)</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>3165</v>
+      </c>
+      <c r="D100" t="n">
+        <v>284998</v>
+      </c>
+      <c r="E100" t="n">
+        <v>-12462</v>
+      </c>
+      <c r="F100" t="n">
+        <v>347553</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>5439</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -142 千股)</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>-1026092</v>
+      </c>
+      <c r="D101" t="n">
+        <v>345829</v>
+      </c>
+      <c r="E101" t="n">
+        <v>-568581</v>
+      </c>
+      <c r="F101" t="n">
+        <v>487443</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>高技</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -388 千股)</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>409811</v>
+      </c>
+      <c r="D102" t="n">
+        <v>-462187</v>
+      </c>
+      <c r="E102" t="n">
+        <v>1471521</v>
+      </c>
+      <c r="F102" t="n">
+        <v>-73831</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/台股_外資雷達.xlsx
+++ b/data/台股_外資雷達.xlsx
@@ -496,22 +496,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>165902</v>
+        <v>213985</v>
       </c>
       <c r="D2" t="n">
-        <v>314443</v>
+        <v>329259</v>
       </c>
       <c r="E2" t="n">
-        <v>79170</v>
+        <v>130166</v>
       </c>
       <c r="F2" t="n">
-        <v>-5607</v>
+        <v>-12936</v>
       </c>
       <c r="G2" t="n">
-        <v>24511</v>
+        <v>28143</v>
       </c>
       <c r="H2" t="n">
-        <v>230</v>
+        <v>1619</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -547,22 +547,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-14884</v>
+        <v>-14745</v>
       </c>
       <c r="D3" t="n">
-        <v>42018</v>
+        <v>36753</v>
       </c>
       <c r="E3" t="n">
-        <v>-3234</v>
+        <v>-1029</v>
       </c>
       <c r="F3" t="n">
-        <v>7551</v>
+        <v>7190</v>
       </c>
       <c r="G3" t="n">
-        <v>-45047</v>
+        <v>-40590</v>
       </c>
       <c r="H3" t="n">
-        <v>2844</v>
+        <v>2884</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10098</v>
+        <v>-3967</v>
       </c>
       <c r="D4" t="n">
-        <v>21829</v>
+        <v>34936</v>
       </c>
       <c r="E4" t="n">
-        <v>125258</v>
+        <v>119257</v>
       </c>
       <c r="F4" t="n">
-        <v>-1950</v>
+        <v>-1182</v>
       </c>
       <c r="G4" t="n">
-        <v>-33596</v>
+        <v>-30805</v>
       </c>
       <c r="H4" t="n">
-        <v>2072</v>
+        <v>2427</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -640,92 +640,92 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-3184</v>
+        <v>5320</v>
       </c>
       <c r="D5" t="n">
-        <v>7045</v>
+        <v>8159</v>
       </c>
       <c r="E5" t="n">
-        <v>11714</v>
+        <v>11972</v>
       </c>
       <c r="F5" t="n">
-        <v>-1016</v>
+        <v>-3892</v>
       </c>
       <c r="G5" t="n">
-        <v>-9756</v>
+        <v>-9979</v>
       </c>
       <c r="H5" t="n">
-        <v>-324</v>
+        <v>-244</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>🟢 加碼</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>90</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>🐌 龜速</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2732</v>
+        <v>2595</v>
       </c>
       <c r="D6" t="n">
-        <v>6545</v>
+        <v>6509</v>
       </c>
       <c r="E6" t="n">
-        <v>10112</v>
+        <v>10716</v>
       </c>
       <c r="F6" t="n">
-        <v>-3427</v>
+        <v>-1740</v>
       </c>
       <c r="G6" t="n">
-        <v>-10288</v>
+        <v>-5700</v>
       </c>
       <c r="H6" t="n">
-        <v>-1</v>
+        <v>201</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>🟢 加碼</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>80</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -739,22 +739,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-1002</v>
+        <v>-289</v>
       </c>
       <c r="D7" t="n">
-        <v>6408</v>
+        <v>5935</v>
       </c>
       <c r="E7" t="n">
-        <v>10181</v>
+        <v>10198</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>-107</v>
       </c>
       <c r="G7" t="n">
-        <v>-561</v>
+        <v>-670</v>
       </c>
       <c r="H7" t="n">
-        <v>592</v>
+        <v>523</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -781,31 +781,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2031</v>
+        <v>-2528</v>
       </c>
       <c r="D8" t="n">
-        <v>6055</v>
+        <v>5026</v>
       </c>
       <c r="E8" t="n">
-        <v>10006</v>
+        <v>11631</v>
       </c>
       <c r="F8" t="n">
-        <v>-1675</v>
+        <v>-358</v>
       </c>
       <c r="G8" t="n">
-        <v>-5645</v>
+        <v>-9857</v>
       </c>
       <c r="H8" t="n">
-        <v>158</v>
+        <v>-272</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-2487</v>
+        <v>-2465</v>
       </c>
       <c r="D9" t="n">
-        <v>4386</v>
+        <v>4276</v>
       </c>
       <c r="E9" t="n">
-        <v>7716</v>
+        <v>7938</v>
       </c>
       <c r="F9" t="n">
-        <v>778</v>
+        <v>416</v>
       </c>
       <c r="G9" t="n">
-        <v>4367</v>
+        <v>4609</v>
       </c>
       <c r="H9" t="n">
-        <v>125</v>
+        <v>-37</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -892,22 +892,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>858</v>
+        <v>798</v>
       </c>
       <c r="D10" t="n">
-        <v>4019</v>
+        <v>3872</v>
       </c>
       <c r="E10" t="n">
-        <v>15482</v>
+        <v>15152</v>
       </c>
       <c r="F10" t="n">
-        <v>132</v>
+        <v>218</v>
       </c>
       <c r="G10" t="n">
-        <v>531</v>
+        <v>617</v>
       </c>
       <c r="H10" t="n">
-        <v>214</v>
+        <v>239</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -934,31 +934,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>104</v>
+        <v>-1556</v>
       </c>
       <c r="D11" t="n">
-        <v>3652</v>
+        <v>3191</v>
       </c>
       <c r="E11" t="n">
-        <v>3032</v>
+        <v>14226</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="G11" t="n">
-        <v>135</v>
+        <v>1180</v>
       </c>
       <c r="H11" t="n">
-        <v>38</v>
+        <v>-27</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -971,45 +971,45 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器*</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-2413</v>
+        <v>2565</v>
       </c>
       <c r="D12" t="n">
-        <v>2991</v>
+        <v>3102</v>
       </c>
       <c r="E12" t="n">
-        <v>13921</v>
+        <v>27849</v>
       </c>
       <c r="F12" t="n">
-        <v>229</v>
+        <v>-2478</v>
       </c>
       <c r="G12" t="n">
-        <v>1137</v>
+        <v>-14616</v>
       </c>
       <c r="H12" t="n">
-        <v>-15</v>
+        <v>-101</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1018,19 +1018,19 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>🚀 加速器*</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1045,19 +1045,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1316</v>
+        <v>946</v>
       </c>
       <c r="D13" t="n">
-        <v>2893</v>
+        <v>3034</v>
       </c>
       <c r="E13" t="n">
-        <v>2710</v>
+        <v>1613</v>
       </c>
       <c r="F13" t="n">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="G13" t="n">
-        <v>-136</v>
+        <v>-135</v>
       </c>
       <c r="H13" t="n">
         <v>-744</v>
@@ -1096,22 +1096,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>345</v>
+        <v>707</v>
       </c>
       <c r="D14" t="n">
-        <v>2841</v>
+        <v>2828</v>
       </c>
       <c r="E14" t="n">
-        <v>-1387</v>
+        <v>-1130</v>
       </c>
       <c r="F14" t="n">
-        <v>-148</v>
+        <v>-178</v>
       </c>
       <c r="G14" t="n">
-        <v>-1189</v>
+        <v>-1218</v>
       </c>
       <c r="H14" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1138,31 +1138,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>漢科</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>500</v>
+        <v>-439</v>
       </c>
       <c r="D15" t="n">
-        <v>2452</v>
+        <v>2725</v>
       </c>
       <c r="E15" t="n">
-        <v>7039</v>
+        <v>2852</v>
       </c>
       <c r="F15" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>5556</v>
+        <v>135</v>
       </c>
       <c r="H15" t="n">
-        <v>-69</v>
+        <v>14</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1175,15 +1175,15 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="16">
@@ -1198,22 +1198,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>111</v>
+        <v>265</v>
       </c>
       <c r="D16" t="n">
-        <v>2326</v>
+        <v>2582</v>
       </c>
       <c r="E16" t="n">
-        <v>3450</v>
+        <v>3624</v>
       </c>
       <c r="F16" t="n">
-        <v>-252</v>
+        <v>-204</v>
       </c>
       <c r="G16" t="n">
-        <v>-718</v>
+        <v>-892</v>
       </c>
       <c r="H16" t="n">
-        <v>-107</v>
+        <v>-206</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1240,48 +1240,48 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1853</v>
+        <v>-630</v>
       </c>
       <c r="D17" t="n">
-        <v>2138</v>
+        <v>1861</v>
       </c>
       <c r="E17" t="n">
-        <v>27876</v>
+        <v>-6535</v>
       </c>
       <c r="F17" t="n">
-        <v>-2519</v>
+        <v>-425</v>
       </c>
       <c r="G17" t="n">
-        <v>-14597</v>
+        <v>-304</v>
       </c>
       <c r="H17" t="n">
-        <v>-118</v>
+        <v>-104</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>🟢 加碼</t>
+          <t>🟡 中性</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M17" t="n">
@@ -1291,31 +1291,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-1260</v>
+        <v>805</v>
       </c>
       <c r="D18" t="n">
-        <v>1580</v>
+        <v>1413</v>
       </c>
       <c r="E18" t="n">
-        <v>-7218</v>
+        <v>-6746</v>
       </c>
       <c r="F18" t="n">
-        <v>61</v>
+        <v>-1096</v>
       </c>
       <c r="G18" t="n">
-        <v>-161</v>
+        <v>-6305</v>
       </c>
       <c r="H18" t="n">
-        <v>-39</v>
+        <v>-321</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1324,11 +1324,11 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1336,37 +1336,37 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>智易</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>169</v>
+        <v>211</v>
       </c>
       <c r="D19" t="n">
-        <v>1391</v>
+        <v>1342</v>
       </c>
       <c r="E19" t="n">
-        <v>-1546</v>
+        <v>7196</v>
       </c>
       <c r="F19" t="n">
-        <v>-23</v>
+        <v>29</v>
       </c>
       <c r="G19" t="n">
-        <v>-174</v>
+        <v>5569</v>
       </c>
       <c r="H19" t="n">
-        <v>-27</v>
+        <v>-69</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1375,49 +1375,49 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>464</v>
+        <v>112</v>
       </c>
       <c r="D20" t="n">
-        <v>1267</v>
+        <v>1274</v>
       </c>
       <c r="E20" t="n">
-        <v>2987</v>
+        <v>-252</v>
       </c>
       <c r="F20" t="n">
-        <v>35</v>
+        <v>-8</v>
       </c>
       <c r="G20" t="n">
-        <v>376</v>
+        <v>-168</v>
       </c>
       <c r="H20" t="n">
-        <v>-8</v>
+        <v>-41</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1426,49 +1426,49 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="D21" t="n">
-        <v>1164</v>
+        <v>1271</v>
       </c>
       <c r="E21" t="n">
-        <v>869</v>
+        <v>3063</v>
       </c>
       <c r="F21" t="n">
-        <v>-16</v>
+        <v>65</v>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>403</v>
       </c>
       <c r="H21" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1477,49 +1477,49 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-1024</v>
+        <v>2002</v>
       </c>
       <c r="D22" t="n">
-        <v>1047</v>
+        <v>1224</v>
       </c>
       <c r="E22" t="n">
-        <v>1297</v>
+        <v>-4923</v>
       </c>
       <c r="F22" t="n">
-        <v>96</v>
+        <v>-1196</v>
       </c>
       <c r="G22" t="n">
-        <v>-2503</v>
+        <v>2824</v>
       </c>
       <c r="H22" t="n">
-        <v>340</v>
+        <v>-987</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1532,45 +1532,45 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-572</v>
+        <v>-614</v>
       </c>
       <c r="D23" t="n">
-        <v>903</v>
+        <v>1184</v>
       </c>
       <c r="E23" t="n">
-        <v>2609</v>
+        <v>1363</v>
       </c>
       <c r="F23" t="n">
-        <v>-16</v>
+        <v>250</v>
       </c>
       <c r="G23" t="n">
-        <v>887</v>
+        <v>-2255</v>
       </c>
       <c r="H23" t="n">
-        <v>-80</v>
+        <v>250</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1579,11 +1579,11 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1597,31 +1597,31 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-1882</v>
+        <v>1429</v>
       </c>
       <c r="D24" t="n">
-        <v>790</v>
+        <v>945</v>
       </c>
       <c r="E24" t="n">
-        <v>4900</v>
+        <v>1672</v>
       </c>
       <c r="F24" t="n">
-        <v>596</v>
+        <v>-960</v>
       </c>
       <c r="G24" t="n">
-        <v>211</v>
+        <v>-939</v>
       </c>
       <c r="H24" t="n">
-        <v>109</v>
+        <v>-157</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1634,96 +1634,84 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-138</v>
+        <v>-1301</v>
       </c>
       <c r="D25" t="n">
-        <v>634</v>
+        <v>916</v>
       </c>
       <c r="E25" t="n">
-        <v>889</v>
+        <v>-1797</v>
       </c>
       <c r="F25" t="n">
-        <v>-1</v>
+        <v>-9</v>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>-3700</v>
       </c>
       <c r="H25" t="n">
-        <v>-120</v>
+        <v>-184</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
-        <v>79</v>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>🛬 穩定</t>
-        </is>
-      </c>
-      <c r="M25" t="n">
-        <v>-1</v>
-      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-178</v>
+        <v>586</v>
       </c>
       <c r="D26" t="n">
-        <v>611</v>
+        <v>835</v>
       </c>
       <c r="E26" t="n">
-        <v>-3149</v>
+        <v>-1312</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>463</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>2371</v>
       </c>
       <c r="H26" t="n">
-        <v>-51</v>
+        <v>-13</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1732,49 +1720,49 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1933</v>
+        <v>-689</v>
       </c>
       <c r="D27" t="n">
-        <v>591</v>
+        <v>720</v>
       </c>
       <c r="E27" t="n">
-        <v>-8946</v>
+        <v>1194</v>
       </c>
       <c r="F27" t="n">
-        <v>-2</v>
+        <v>22</v>
       </c>
       <c r="G27" t="n">
-        <v>-9</v>
+        <v>750</v>
       </c>
       <c r="H27" t="n">
-        <v>-96</v>
+        <v>-163</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1783,49 +1771,49 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>勝一</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>129</v>
+        <v>1722</v>
       </c>
       <c r="D28" t="n">
-        <v>587</v>
+        <v>715</v>
       </c>
       <c r="E28" t="n">
-        <v>945</v>
+        <v>-669</v>
       </c>
       <c r="F28" t="n">
-        <v>-2</v>
+        <v>-57</v>
       </c>
       <c r="G28" t="n">
-        <v>7</v>
+        <v>-926</v>
       </c>
       <c r="H28" t="n">
-        <v>16</v>
+        <v>-131</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1834,49 +1822,49 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>勝一</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>86</v>
+        <v>-384</v>
       </c>
       <c r="D29" t="n">
-        <v>498</v>
+        <v>698</v>
       </c>
       <c r="E29" t="n">
-        <v>-864</v>
+        <v>1385</v>
       </c>
       <c r="F29" t="n">
-        <v>699</v>
+        <v>-2</v>
       </c>
       <c r="G29" t="n">
-        <v>2328</v>
+        <v>6</v>
       </c>
       <c r="H29" t="n">
-        <v>17</v>
+        <v>-13</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1885,49 +1873,49 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>10347</v>
+        <v>225</v>
       </c>
       <c r="D30" t="n">
-        <v>497</v>
+        <v>547</v>
       </c>
       <c r="E30" t="n">
-        <v>-80630</v>
+        <v>1070</v>
       </c>
       <c r="F30" t="n">
-        <v>-4296</v>
+        <v>-9</v>
       </c>
       <c r="G30" t="n">
-        <v>6143</v>
+        <v>3</v>
       </c>
       <c r="H30" t="n">
-        <v>-5854</v>
+        <v>76</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1936,11 +1924,11 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -1948,217 +1936,229 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>74</v>
+        <v>344</v>
       </c>
       <c r="D31" t="n">
-        <v>378</v>
+        <v>505</v>
       </c>
       <c r="E31" t="n">
-        <v>593</v>
+        <v>252</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>-272</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>-1356</v>
       </c>
       <c r="H31" t="n">
+        <v>-109</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>66</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
         <v>2</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K31" t="n">
-        <v>91</v>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>🐌 龜速</t>
-        </is>
-      </c>
-      <c r="M31" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>湧德</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-1026</v>
+        <v>-698</v>
       </c>
       <c r="D32" t="n">
-        <v>346</v>
+        <v>432</v>
       </c>
       <c r="E32" t="n">
-        <v>-1448</v>
+        <v>-3451</v>
       </c>
       <c r="F32" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>-5569</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-105</v>
+        <v>-95</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>94</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>📉 減速</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>崇友</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>82</v>
       </c>
       <c r="D33" t="n">
-        <v>285</v>
+        <v>363</v>
       </c>
       <c r="E33" t="n">
-        <v>684</v>
+        <v>583</v>
       </c>
       <c r="F33" t="n">
-        <v>-271</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>-418</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-7</v>
+        <v>2</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>91</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-1017</v>
+        <v>90</v>
       </c>
       <c r="D34" t="n">
-        <v>274</v>
+        <v>320</v>
       </c>
       <c r="E34" t="n">
-        <v>-8019</v>
+        <v>840</v>
       </c>
       <c r="F34" t="n">
-        <v>-626</v>
+        <v>-293</v>
       </c>
       <c r="G34" t="n">
-        <v>-5802</v>
+        <v>-543</v>
       </c>
       <c r="H34" t="n">
-        <v>-236</v>
+        <v>-8</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K34" t="n">
-        <v>66</v>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>🚀 加速器</t>
-        </is>
-      </c>
-      <c r="M34" t="n">
-        <v>-1</v>
-      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>合機</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-983</v>
+        <v>-331</v>
       </c>
       <c r="D35" t="n">
-        <v>205</v>
+        <v>285</v>
       </c>
       <c r="E35" t="n">
-        <v>2125</v>
+        <v>4531</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>258</v>
       </c>
       <c r="H35" t="n">
-        <v>-78</v>
+        <v>155</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2171,45 +2171,45 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M35" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>達欣工</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>-121</v>
+        <v>-232</v>
       </c>
       <c r="D36" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E36" t="n">
-        <v>-209</v>
+        <v>1159</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>-9</v>
+        <v>-96</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2222,45 +2222,45 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M36" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>智冠</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-104</v>
+        <v>1516</v>
       </c>
       <c r="D37" t="n">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="E37" t="n">
-        <v>439</v>
+        <v>-2587</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>-420</v>
       </c>
       <c r="H37" t="n">
-        <v>-147</v>
+        <v>17</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2273,36 +2273,36 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M37" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-20</v>
+        <v>-161</v>
       </c>
       <c r="D38" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E38" t="n">
-        <v>-55</v>
+        <v>-175</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2311,7 +2311,7 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2324,11 +2324,11 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M38" t="n">
@@ -2338,22 +2338,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>德昌</t>
+          <t>六方科-KY</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-696</v>
+        <v>-59</v>
       </c>
       <c r="D39" t="n">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="E39" t="n">
-        <v>49</v>
+        <v>-80</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -2362,7 +2362,7 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-18</v>
+        <v>5</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2375,45 +2375,45 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M39" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>大統益</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-98</v>
+        <v>573</v>
       </c>
       <c r="D40" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="E40" t="n">
-        <v>-63</v>
+        <v>-211</v>
       </c>
       <c r="F40" t="n">
-        <v>-200</v>
+        <v>-1</v>
       </c>
       <c r="G40" t="n">
-        <v>-1088</v>
+        <v>-2</v>
       </c>
       <c r="H40" t="n">
-        <v>-116</v>
+        <v>22</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2422,40 +2422,40 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M40" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>智冠</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-297</v>
+        <v>-173</v>
       </c>
       <c r="D41" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E41" t="n">
-        <v>-417</v>
+        <v>424</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -2464,7 +2464,7 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>-54</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2473,19 +2473,19 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="42">
@@ -2500,22 +2500,22 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-220</v>
+        <v>-176</v>
       </c>
       <c r="D42" t="n">
-        <v>-12</v>
+        <v>28</v>
       </c>
       <c r="E42" t="n">
-        <v>-377</v>
+        <v>174</v>
       </c>
       <c r="F42" t="n">
-        <v>227</v>
+        <v>259</v>
       </c>
       <c r="G42" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="H42" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2551,13 +2551,13 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="D43" t="n">
-        <v>-13</v>
+        <v>-17</v>
       </c>
       <c r="E43" t="n">
-        <v>-79</v>
+        <v>-78</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -2566,7 +2566,7 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2593,82 +2593,70 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>989</v>
+        <v>296</v>
       </c>
       <c r="D44" t="n">
-        <v>-21</v>
+        <v>-31</v>
       </c>
       <c r="E44" t="n">
-        <v>1468</v>
+        <v>-5689</v>
       </c>
       <c r="F44" t="n">
-        <v>-962</v>
+        <v>310</v>
       </c>
       <c r="G44" t="n">
-        <v>-811</v>
+        <v>-1188</v>
       </c>
       <c r="H44" t="n">
-        <v>-114</v>
+        <v>-54</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K44" t="n">
-        <v>97</v>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>📉 減速</t>
-        </is>
-      </c>
-      <c r="M44" t="n">
-        <v>1</v>
-      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-1811</v>
+        <v>374</v>
       </c>
       <c r="D45" t="n">
-        <v>-87</v>
+        <v>-52</v>
       </c>
       <c r="E45" t="n">
-        <v>3138</v>
+        <v>-6830</v>
       </c>
       <c r="F45" t="n">
-        <v>412</v>
+        <v>-769</v>
       </c>
       <c r="G45" t="n">
-        <v>111</v>
+        <v>-3791</v>
       </c>
       <c r="H45" t="n">
-        <v>21</v>
+        <v>-38</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2681,7 +2669,7 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2695,31 +2683,31 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>大車隊</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-8</v>
+        <v>-1426</v>
       </c>
       <c r="D46" t="n">
-        <v>-123</v>
+        <v>-96</v>
       </c>
       <c r="E46" t="n">
-        <v>-278</v>
+        <v>2443</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H46" t="n">
-        <v>53</v>
+        <v>-202</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2732,45 +2720,45 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M46" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>大車隊</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-2</v>
+        <v>-11</v>
       </c>
       <c r="D47" t="n">
-        <v>-162</v>
+        <v>-131</v>
       </c>
       <c r="E47" t="n">
-        <v>-154</v>
+        <v>-296</v>
       </c>
       <c r="F47" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2779,49 +2767,49 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>817</v>
+        <v>-4</v>
       </c>
       <c r="D48" t="n">
-        <v>-184</v>
+        <v>-172</v>
       </c>
       <c r="E48" t="n">
-        <v>-989</v>
+        <v>-137</v>
       </c>
       <c r="F48" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G48" t="n">
-        <v>-865</v>
+        <v>9</v>
       </c>
       <c r="H48" t="n">
-        <v>-123</v>
+        <v>12</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2830,40 +2818,40 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>聯合</t>
+          <t>鑫龍騰</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-4</v>
+        <v>160</v>
       </c>
       <c r="D49" t="n">
-        <v>-251</v>
+        <v>-209</v>
       </c>
       <c r="E49" t="n">
-        <v>-3109</v>
+        <v>-2733</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -2872,7 +2860,7 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2881,11 +2869,11 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -2908,22 +2896,22 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-304</v>
+        <v>-235</v>
       </c>
       <c r="D50" t="n">
-        <v>-304</v>
+        <v>-231</v>
       </c>
       <c r="E50" t="n">
-        <v>-1325</v>
+        <v>-1127</v>
       </c>
       <c r="F50" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="G50" t="n">
         <v>242</v>
       </c>
       <c r="H50" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2950,31 +2938,31 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>信立</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>148</v>
+        <v>-224</v>
       </c>
       <c r="D51" t="n">
-        <v>-309</v>
+        <v>-236</v>
       </c>
       <c r="E51" t="n">
-        <v>-532</v>
+        <v>-252</v>
       </c>
       <c r="F51" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>12</v>
+        <v>-4</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -2983,49 +2971,49 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M51" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>聯合</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>341</v>
+        <v>-19</v>
       </c>
       <c r="D52" t="n">
-        <v>-335</v>
+        <v>-258</v>
       </c>
       <c r="E52" t="n">
-        <v>765</v>
+        <v>-3002</v>
       </c>
       <c r="F52" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>445</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-570</v>
+        <v>97</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3034,15 +3022,15 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M52" t="n">
@@ -3052,31 +3040,31 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>鑫龍騰</t>
+          <t>全友</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>83</v>
+        <v>-1478</v>
       </c>
       <c r="D53" t="n">
-        <v>-382</v>
+        <v>-292</v>
       </c>
       <c r="E53" t="n">
-        <v>-2917</v>
+        <v>5771</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3089,45 +3077,45 @@
         </is>
       </c>
       <c r="K53" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>德昌</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-111</v>
+        <v>-957</v>
       </c>
       <c r="D54" t="n">
-        <v>-428</v>
+        <v>-306</v>
       </c>
       <c r="E54" t="n">
-        <v>534</v>
+        <v>-207</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-23</v>
+        <v>-19</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3140,11 +3128,11 @@
         </is>
       </c>
       <c r="K54" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M54" t="n">
@@ -3154,31 +3142,31 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>68</v>
+        <v>-2</v>
       </c>
       <c r="D55" t="n">
-        <v>-461</v>
+        <v>-327</v>
       </c>
       <c r="E55" t="n">
-        <v>-245</v>
+        <v>-294</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>-59</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>-130</v>
       </c>
       <c r="H55" t="n">
-        <v>-13</v>
+        <v>-24</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3187,11 +3175,11 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K55" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -3199,76 +3187,88 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>友輝</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>410</v>
+        <v>-26</v>
       </c>
       <c r="D56" t="n">
-        <v>-462</v>
+        <v>-355</v>
       </c>
       <c r="E56" t="n">
-        <v>-6287</v>
+        <v>1198</v>
       </c>
       <c r="F56" t="n">
-        <v>294</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>-1195</v>
+        <v>6</v>
       </c>
       <c r="H56" t="n">
-        <v>1</v>
+        <v>-20</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>77</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M56" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>寶雅</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>-646</v>
+        <v>358</v>
       </c>
       <c r="D57" t="n">
-        <v>-485</v>
+        <v>-362</v>
       </c>
       <c r="E57" t="n">
-        <v>650</v>
+        <v>-4664</v>
       </c>
       <c r="F57" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>78</v>
+        <v>-28</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3281,45 +3281,45 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M57" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-265</v>
+        <v>54</v>
       </c>
       <c r="D58" t="n">
-        <v>-490</v>
+        <v>-460</v>
       </c>
       <c r="E58" t="n">
-        <v>-413</v>
+        <v>-250</v>
       </c>
       <c r="F58" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-59</v>
+        <v>-18</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3328,11 +3328,11 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K58" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -3340,37 +3340,37 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>合機</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>-1720</v>
+        <v>-1562</v>
       </c>
       <c r="D59" t="n">
-        <v>-566</v>
+        <v>-499</v>
       </c>
       <c r="E59" t="n">
-        <v>5608</v>
+        <v>1927</v>
       </c>
       <c r="F59" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>72</v>
+        <v>-84</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3379,40 +3379,40 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K59" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M59" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>105</v>
+        <v>-291</v>
       </c>
       <c r="D60" t="n">
-        <v>-599</v>
+        <v>-622</v>
       </c>
       <c r="E60" t="n">
-        <v>2134</v>
+        <v>-1868</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -3421,7 +3421,7 @@
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>122</v>
+        <v>12</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3434,45 +3434,45 @@
         </is>
       </c>
       <c r="K60" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M60" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>寶雅</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>38</v>
+        <v>-488</v>
       </c>
       <c r="D61" t="n">
-        <v>-658</v>
+        <v>-665</v>
       </c>
       <c r="E61" t="n">
-        <v>-7556</v>
+        <v>243</v>
       </c>
       <c r="F61" t="n">
-        <v>-774</v>
+        <v>58</v>
       </c>
       <c r="G61" t="n">
-        <v>-3682</v>
+        <v>102</v>
       </c>
       <c r="H61" t="n">
-        <v>-41</v>
+        <v>12</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3485,36 +3485,36 @@
         </is>
       </c>
       <c r="K61" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M61" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-387</v>
+        <v>87</v>
       </c>
       <c r="D62" t="n">
-        <v>-696</v>
+        <v>-754</v>
       </c>
       <c r="E62" t="n">
-        <v>-1921</v>
+        <v>2176</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -3523,7 +3523,7 @@
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>12</v>
+        <v>151</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3536,87 +3536,87 @@
         </is>
       </c>
       <c r="K62" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M62" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>億泰</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-608</v>
+        <v>-157</v>
       </c>
       <c r="D63" t="n">
-        <v>-854</v>
+        <v>-887</v>
       </c>
       <c r="E63" t="n">
-        <v>-2756</v>
+        <v>-2991</v>
       </c>
       <c r="F63" t="n">
+        <v>9</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-108</v>
+      </c>
+      <c r="H63" t="n">
+        <v>-113</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>96</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>✈️ 高飛*</t>
+        </is>
+      </c>
+      <c r="M63" t="n">
         <v>0</v>
-      </c>
-      <c r="G63" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" t="n">
-        <v>196</v>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K63" t="n">
-        <v>78</v>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>🛬 穩定</t>
-        </is>
-      </c>
-      <c r="M63" t="n">
-        <v>-2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>億泰</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>-182</v>
+        <v>-475</v>
       </c>
       <c r="D64" t="n">
-        <v>-872</v>
+        <v>-888</v>
       </c>
       <c r="E64" t="n">
-        <v>-5110</v>
+        <v>-2712</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -3625,7 +3625,7 @@
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-22</v>
+        <v>225</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3634,49 +3634,49 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K64" t="n">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-752</v>
+        <v>-498</v>
       </c>
       <c r="D65" t="n">
-        <v>-895</v>
+        <v>-891</v>
       </c>
       <c r="E65" t="n">
-        <v>-4592</v>
+        <v>-1443</v>
       </c>
       <c r="F65" t="n">
-        <v>-89</v>
+        <v>332</v>
       </c>
       <c r="G65" t="n">
-        <v>4188</v>
+        <v>943</v>
       </c>
       <c r="H65" t="n">
-        <v>-1288</v>
+        <v>-63</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3685,11 +3685,11 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K65" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -3697,37 +3697,37 @@
         </is>
       </c>
       <c r="M65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>立隆電</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-383</v>
+        <v>6474</v>
       </c>
       <c r="D66" t="n">
-        <v>-1020</v>
+        <v>-1040</v>
       </c>
       <c r="E66" t="n">
-        <v>-3154</v>
+        <v>-9019</v>
       </c>
       <c r="F66" t="n">
-        <v>9</v>
+        <v>806</v>
       </c>
       <c r="G66" t="n">
-        <v>-110</v>
+        <v>8841</v>
       </c>
       <c r="H66" t="n">
-        <v>-67</v>
+        <v>-184</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3736,49 +3736,49 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K66" t="n">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-528</v>
+        <v>-1497</v>
       </c>
       <c r="D67" t="n">
-        <v>-1028</v>
+        <v>-1638</v>
       </c>
       <c r="E67" t="n">
-        <v>-1285</v>
+        <v>-2326</v>
       </c>
       <c r="F67" t="n">
-        <v>315</v>
+        <v>-52</v>
       </c>
       <c r="G67" t="n">
-        <v>1353</v>
+        <v>-55</v>
       </c>
       <c r="H67" t="n">
-        <v>-40</v>
+        <v>-251</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="K67" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -3805,31 +3805,31 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>鈊象</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>702</v>
+        <v>-148</v>
       </c>
       <c r="D68" t="n">
-        <v>-1223</v>
+        <v>-1807</v>
       </c>
       <c r="E68" t="n">
-        <v>-7634</v>
+        <v>-12947</v>
       </c>
       <c r="F68" t="n">
-        <v>4</v>
+        <v>85</v>
       </c>
       <c r="G68" t="n">
-        <v>88</v>
+        <v>5112</v>
       </c>
       <c r="H68" t="n">
-        <v>-369</v>
+        <v>7</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3842,45 +3842,45 @@
         </is>
       </c>
       <c r="K68" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M68" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-1309</v>
+        <v>-244</v>
       </c>
       <c r="D69" t="n">
-        <v>-1575</v>
+        <v>-1861</v>
       </c>
       <c r="E69" t="n">
-        <v>-7014</v>
+        <v>3910</v>
       </c>
       <c r="F69" t="n">
-        <v>-533</v>
+        <v>-1</v>
       </c>
       <c r="G69" t="n">
-        <v>-11388</v>
+        <v>444</v>
       </c>
       <c r="H69" t="n">
-        <v>-251</v>
+        <v>-742</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3889,104 +3889,104 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K69" t="n">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M69" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2049</v>
+        <v>710</v>
       </c>
       <c r="D70" t="n">
-        <v>-1717</v>
+        <v>-2133</v>
       </c>
       <c r="E70" t="n">
-        <v>-3711</v>
+        <v>-6496</v>
       </c>
       <c r="F70" t="n">
-        <v>-181</v>
+        <v>1214</v>
       </c>
       <c r="G70" t="n">
-        <v>-419</v>
+        <v>-822</v>
       </c>
       <c r="H70" t="n">
-        <v>-5</v>
+        <v>-1304</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>🟡 中性</t>
+          <t>🟠 減碼</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K70" t="n">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M70" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-828</v>
+        <v>-5309</v>
       </c>
       <c r="D71" t="n">
-        <v>-1818</v>
+        <v>-2220</v>
       </c>
       <c r="E71" t="n">
-        <v>-596</v>
+        <v>-12274</v>
       </c>
       <c r="F71" t="n">
-        <v>265</v>
+        <v>-2</v>
       </c>
       <c r="G71" t="n">
-        <v>-1670</v>
+        <v>-7</v>
       </c>
       <c r="H71" t="n">
-        <v>-249</v>
+        <v>-170</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>🟡 中性</t>
+          <t>🟠 減碼</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -3995,42 +3995,42 @@
         </is>
       </c>
       <c r="K71" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M71" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-1923</v>
+        <v>2786</v>
       </c>
       <c r="D72" t="n">
-        <v>-2054</v>
+        <v>-2377</v>
       </c>
       <c r="E72" t="n">
-        <v>-2055</v>
+        <v>-58668</v>
       </c>
       <c r="F72" t="n">
-        <v>8</v>
+        <v>279</v>
       </c>
       <c r="G72" t="n">
-        <v>5</v>
+        <v>6801</v>
       </c>
       <c r="H72" t="n">
         <v>-226</v>
@@ -4042,49 +4042,49 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K72" t="n">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M72" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-909</v>
+        <v>-2094</v>
       </c>
       <c r="D73" t="n">
-        <v>-2218</v>
+        <v>-2395</v>
       </c>
       <c r="E73" t="n">
-        <v>-2434</v>
+        <v>-8237</v>
       </c>
       <c r="F73" t="n">
-        <v>353</v>
+        <v>241</v>
       </c>
       <c r="G73" t="n">
-        <v>380</v>
+        <v>-11763</v>
       </c>
       <c r="H73" t="n">
-        <v>-253</v>
+        <v>-1163</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -4093,15 +4093,15 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K73" t="n">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M73" t="n">
@@ -4111,31 +4111,31 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>-316</v>
+        <v>-1786</v>
       </c>
       <c r="D74" t="n">
-        <v>-2355</v>
+        <v>-2413</v>
       </c>
       <c r="E74" t="n">
-        <v>-748</v>
+        <v>-3169</v>
       </c>
       <c r="F74" t="n">
-        <v>-311</v>
+        <v>355</v>
       </c>
       <c r="G74" t="n">
-        <v>-61</v>
+        <v>380</v>
       </c>
       <c r="H74" t="n">
-        <v>394</v>
+        <v>-417</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -4144,11 +4144,11 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K74" t="n">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -4156,37 +4156,37 @@
         </is>
       </c>
       <c r="M74" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>-2480</v>
+        <v>-1095</v>
       </c>
       <c r="D75" t="n">
-        <v>-2499</v>
+        <v>-2479</v>
       </c>
       <c r="E75" t="n">
-        <v>-2301</v>
+        <v>-8412</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="H75" t="n">
-        <v>344</v>
+        <v>-563</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -4195,15 +4195,15 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K75" t="n">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M75" t="n">
@@ -4213,31 +4213,31 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>玉晶光</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-160</v>
+        <v>-172</v>
       </c>
       <c r="D76" t="n">
-        <v>-2509</v>
+        <v>-2559</v>
       </c>
       <c r="E76" t="n">
-        <v>-13587</v>
+        <v>-618</v>
       </c>
       <c r="F76" t="n">
-        <v>339</v>
+        <v>249</v>
       </c>
       <c r="G76" t="n">
-        <v>5162</v>
+        <v>-1464</v>
       </c>
       <c r="H76" t="n">
-        <v>61</v>
+        <v>-251</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -4250,11 +4250,11 @@
         </is>
       </c>
       <c r="K76" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M76" t="n">
@@ -4264,31 +4264,31 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-805</v>
+        <v>-2433</v>
       </c>
       <c r="D77" t="n">
-        <v>-3050</v>
+        <v>-3147</v>
       </c>
       <c r="E77" t="n">
-        <v>-2575</v>
+        <v>-2528</v>
       </c>
       <c r="F77" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>167</v>
+        <v>368</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -4297,49 +4297,49 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K77" t="n">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M77" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1261</v>
+        <v>-933</v>
       </c>
       <c r="D78" t="n">
-        <v>-3096</v>
+        <v>-3292</v>
       </c>
       <c r="E78" t="n">
-        <v>-9987</v>
+        <v>-946</v>
       </c>
       <c r="F78" t="n">
-        <v>1320</v>
+        <v>230</v>
       </c>
       <c r="G78" t="n">
-        <v>-993</v>
+        <v>175</v>
       </c>
       <c r="H78" t="n">
-        <v>-1184</v>
+        <v>247</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -4348,11 +4348,11 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K78" t="n">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -4360,37 +4360,37 @@
         </is>
       </c>
       <c r="M78" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-1263</v>
+        <v>-906</v>
       </c>
       <c r="D79" t="n">
-        <v>-3111</v>
+        <v>-3446</v>
       </c>
       <c r="E79" t="n">
-        <v>-3631</v>
+        <v>-3829</v>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>-140</v>
       </c>
       <c r="H79" t="n">
-        <v>-706</v>
+        <v>51</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -4403,45 +4403,45 @@
         </is>
       </c>
       <c r="K79" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M79" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>-2727</v>
+        <v>-1560</v>
       </c>
       <c r="D80" t="n">
-        <v>-3480</v>
+        <v>-3684</v>
       </c>
       <c r="E80" t="n">
-        <v>-2979</v>
+        <v>-5144</v>
       </c>
       <c r="F80" t="n">
-        <v>2368</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>5684</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>40</v>
+        <v>-568</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -4450,15 +4450,15 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K80" t="n">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M80" t="n">
@@ -4477,22 +4477,22 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-1779</v>
+        <v>-1772</v>
       </c>
       <c r="D81" t="n">
-        <v>-3627</v>
+        <v>-3946</v>
       </c>
       <c r="E81" t="n">
-        <v>-7016</v>
+        <v>-7330</v>
       </c>
       <c r="F81" t="n">
         <v>5</v>
       </c>
       <c r="G81" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="H81" t="n">
-        <v>-150</v>
+        <v>-426</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4528,22 +4528,22 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-127</v>
+        <v>39</v>
       </c>
       <c r="D82" t="n">
-        <v>-4329</v>
+        <v>-3970</v>
       </c>
       <c r="E82" t="n">
-        <v>-4527</v>
+        <v>-4408</v>
       </c>
       <c r="F82" t="n">
-        <v>41</v>
+        <v>-171</v>
       </c>
       <c r="G82" t="n">
-        <v>2820</v>
+        <v>2380</v>
       </c>
       <c r="H82" t="n">
-        <v>-206</v>
+        <v>-343</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -4570,31 +4570,31 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-1801</v>
+        <v>-2296</v>
       </c>
       <c r="D83" t="n">
-        <v>-4486</v>
+        <v>-4295</v>
       </c>
       <c r="E83" t="n">
-        <v>-14565</v>
+        <v>-3575</v>
       </c>
       <c r="F83" t="n">
-        <v>468</v>
+        <v>2443</v>
       </c>
       <c r="G83" t="n">
-        <v>674</v>
+        <v>6647</v>
       </c>
       <c r="H83" t="n">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -4603,19 +4603,19 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K83" t="n">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M83" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="84">
@@ -4630,22 +4630,22 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-698</v>
+        <v>-419</v>
       </c>
       <c r="D84" t="n">
-        <v>-4532</v>
+        <v>-4362</v>
       </c>
       <c r="E84" t="n">
-        <v>-7107</v>
+        <v>-6877</v>
       </c>
       <c r="F84" t="n">
-        <v>1321</v>
+        <v>1264</v>
       </c>
       <c r="G84" t="n">
-        <v>2511</v>
+        <v>2617</v>
       </c>
       <c r="H84" t="n">
-        <v>-177</v>
+        <v>-165</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -4672,31 +4672,31 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3698</v>
+        <v>-1097</v>
       </c>
       <c r="D85" t="n">
-        <v>-4533</v>
+        <v>-4627</v>
       </c>
       <c r="E85" t="n">
-        <v>-60113</v>
+        <v>-13064</v>
       </c>
       <c r="F85" t="n">
-        <v>139</v>
+        <v>-7</v>
       </c>
       <c r="G85" t="n">
-        <v>7384</v>
+        <v>-914</v>
       </c>
       <c r="H85" t="n">
-        <v>-259</v>
+        <v>-179</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -4705,49 +4705,49 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K85" t="n">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M85" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-4835</v>
+        <v>-247</v>
       </c>
       <c r="D86" t="n">
-        <v>-4709</v>
+        <v>-4684</v>
       </c>
       <c r="E86" t="n">
-        <v>-7905</v>
+        <v>-11628</v>
       </c>
       <c r="F86" t="n">
-        <v>1486</v>
+        <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>5109</v>
+        <v>-215</v>
       </c>
       <c r="H86" t="n">
-        <v>-1322</v>
+        <v>-459</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -4756,49 +4756,49 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K86" t="n">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M86" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>-760</v>
+        <v>-1437</v>
       </c>
       <c r="D87" t="n">
-        <v>-5219</v>
+        <v>-5054</v>
       </c>
       <c r="E87" t="n">
-        <v>-12756</v>
+        <v>-6859</v>
       </c>
       <c r="F87" t="n">
-        <v>-455</v>
+        <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>-936</v>
+        <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>-132</v>
+        <v>1620</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -4807,49 +4807,49 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K87" t="n">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M87" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>-837</v>
+        <v>-1966</v>
       </c>
       <c r="D88" t="n">
-        <v>-5385</v>
+        <v>-5118</v>
       </c>
       <c r="E88" t="n">
-        <v>-12266</v>
+        <v>-15240</v>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>368</v>
       </c>
       <c r="G88" t="n">
-        <v>-215</v>
+        <v>674</v>
       </c>
       <c r="H88" t="n">
-        <v>-140</v>
+        <v>-19</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -4862,15 +4862,15 @@
         </is>
       </c>
       <c r="K88" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M88" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="89">
@@ -4885,22 +4885,22 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-123</v>
+        <v>-136</v>
       </c>
       <c r="D89" t="n">
-        <v>-5927</v>
+        <v>-5196</v>
       </c>
       <c r="E89" t="n">
-        <v>-5299</v>
+        <v>-5155</v>
       </c>
       <c r="F89" t="n">
-        <v>311</v>
+        <v>269</v>
       </c>
       <c r="G89" t="n">
-        <v>1000</v>
+        <v>831</v>
       </c>
       <c r="H89" t="n">
-        <v>-93</v>
+        <v>-91</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4927,82 +4927,82 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>-1431</v>
+        <v>13691</v>
       </c>
       <c r="D90" t="n">
-        <v>-6181</v>
+        <v>-7136</v>
       </c>
       <c r="E90" t="n">
-        <v>-7200</v>
+        <v>-76255</v>
       </c>
       <c r="F90" t="n">
+        <v>-10457</v>
+      </c>
+      <c r="G90" t="n">
+        <v>-357</v>
+      </c>
+      <c r="H90" t="n">
+        <v>-6575</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>🟠 減碼</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K90" t="n">
+        <v>60</v>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>📉 減速</t>
+        </is>
+      </c>
+      <c r="M90" t="n">
         <v>0</v>
-      </c>
-      <c r="G90" t="n">
-        <v>0</v>
-      </c>
-      <c r="H90" t="n">
-        <v>2039</v>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>🟠 減碼</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K90" t="n">
-        <v>78</v>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>🐌 龜速</t>
-        </is>
-      </c>
-      <c r="M90" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1158</v>
+        <v>-4456</v>
       </c>
       <c r="D91" t="n">
-        <v>-8869</v>
+        <v>-8241</v>
       </c>
       <c r="E91" t="n">
-        <v>-13660</v>
+        <v>-8361</v>
       </c>
       <c r="F91" t="n">
-        <v>1385</v>
+        <v>880</v>
       </c>
       <c r="G91" t="n">
-        <v>9671</v>
+        <v>5151</v>
       </c>
       <c r="H91" t="n">
-        <v>-133</v>
+        <v>-1333</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -5011,49 +5011,49 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K91" t="n">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M91" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>-3515</v>
+        <v>25203</v>
       </c>
       <c r="D92" t="n">
-        <v>-12013</v>
+        <v>-12221</v>
       </c>
       <c r="E92" t="n">
-        <v>-26685</v>
+        <v>25440</v>
       </c>
       <c r="F92" t="n">
-        <v>2361</v>
+        <v>6609</v>
       </c>
       <c r="G92" t="n">
-        <v>10380</v>
+        <v>40301</v>
       </c>
       <c r="H92" t="n">
-        <v>330</v>
+        <v>1244</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -5062,49 +5062,49 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K92" t="n">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M92" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1056</v>
+        <v>-3032</v>
       </c>
       <c r="D93" t="n">
-        <v>-17409</v>
+        <v>-12274</v>
       </c>
       <c r="E93" t="n">
-        <v>-34691</v>
+        <v>-26990</v>
       </c>
       <c r="F93" t="n">
-        <v>89</v>
+        <v>1804</v>
       </c>
       <c r="G93" t="n">
-        <v>22959</v>
+        <v>10564</v>
       </c>
       <c r="H93" t="n">
-        <v>-142</v>
+        <v>504</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -5113,49 +5113,49 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K93" t="n">
-        <v>94</v>
+        <v>61</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M93" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-4835</v>
+        <v>-1165</v>
       </c>
       <c r="D94" t="n">
-        <v>-18917</v>
+        <v>-19539</v>
       </c>
       <c r="E94" t="n">
-        <v>-27211</v>
+        <v>-34906</v>
       </c>
       <c r="F94" t="n">
-        <v>-60</v>
+        <v>37</v>
       </c>
       <c r="G94" t="n">
-        <v>-11991</v>
+        <v>22959</v>
       </c>
       <c r="H94" t="n">
-        <v>-2202</v>
+        <v>-515</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         </is>
       </c>
       <c r="K94" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -5176,37 +5176,37 @@
         </is>
       </c>
       <c r="M94" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>14833</v>
+        <v>-5272</v>
       </c>
       <c r="D95" t="n">
-        <v>-19024</v>
+        <v>-19716</v>
       </c>
       <c r="E95" t="n">
-        <v>18016</v>
+        <v>-28951</v>
       </c>
       <c r="F95" t="n">
-        <v>10554</v>
+        <v>579</v>
       </c>
       <c r="G95" t="n">
-        <v>39608</v>
+        <v>-11210</v>
       </c>
       <c r="H95" t="n">
-        <v>-377</v>
+        <v>-2145</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -5219,15 +5219,15 @@
         </is>
       </c>
       <c r="K95" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M95" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -5242,22 +5242,22 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>-6149</v>
+        <v>-5763</v>
       </c>
       <c r="D96" t="n">
-        <v>-25264</v>
+        <v>-23090</v>
       </c>
       <c r="E96" t="n">
-        <v>-3200</v>
+        <v>-1108</v>
       </c>
       <c r="F96" t="n">
-        <v>-29</v>
+        <v>-23</v>
       </c>
       <c r="G96" t="n">
-        <v>12789</v>
+        <v>12726</v>
       </c>
       <c r="H96" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -5293,22 +5293,22 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>-17527</v>
+        <v>-18618</v>
       </c>
       <c r="D97" t="n">
-        <v>-30863</v>
+        <v>-33392</v>
       </c>
       <c r="E97" t="n">
-        <v>-287381</v>
+        <v>-285453</v>
       </c>
       <c r="F97" t="n">
-        <v>8959</v>
+        <v>10323</v>
       </c>
       <c r="G97" t="n">
-        <v>36222</v>
+        <v>39367</v>
       </c>
       <c r="H97" t="n">
-        <v>2653</v>
+        <v>2548</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -5344,22 +5344,22 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-15028</v>
+        <v>-19667</v>
       </c>
       <c r="D98" t="n">
-        <v>-45392</v>
+        <v>-38905</v>
       </c>
       <c r="E98" t="n">
-        <v>84636</v>
+        <v>125897</v>
       </c>
       <c r="F98" t="n">
-        <v>5404</v>
+        <v>6314</v>
       </c>
       <c r="G98" t="n">
-        <v>67240</v>
+        <v>68100</v>
       </c>
       <c r="H98" t="n">
-        <v>-3555</v>
+        <v>-2139</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -5395,22 +5395,22 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>-42758</v>
+        <v>-39841</v>
       </c>
       <c r="D99" t="n">
-        <v>-58374</v>
+        <v>-59452</v>
       </c>
       <c r="E99" t="n">
-        <v>44015</v>
+        <v>36228</v>
       </c>
       <c r="F99" t="n">
-        <v>20343</v>
+        <v>19723</v>
       </c>
       <c r="G99" t="n">
-        <v>44243</v>
+        <v>48673</v>
       </c>
       <c r="H99" t="n">
-        <v>15690</v>
+        <v>15483</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -5437,31 +5437,31 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>-19106</v>
+        <v>-20365</v>
       </c>
       <c r="D100" t="n">
-        <v>-82135</v>
+        <v>-89990</v>
       </c>
       <c r="E100" t="n">
-        <v>-254691</v>
+        <v>-138134</v>
       </c>
       <c r="F100" t="n">
-        <v>2222</v>
+        <v>6051</v>
       </c>
       <c r="G100" t="n">
-        <v>6965</v>
+        <v>33285</v>
       </c>
       <c r="H100" t="n">
-        <v>8341</v>
+        <v>-8994</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -5470,49 +5470,49 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K100" t="n">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M100" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-23531</v>
+        <v>-31282</v>
       </c>
       <c r="D101" t="n">
-        <v>-88104</v>
+        <v>-104198</v>
       </c>
       <c r="E101" t="n">
-        <v>-136635</v>
+        <v>-245925</v>
       </c>
       <c r="F101" t="n">
-        <v>8679</v>
+        <v>3683</v>
       </c>
       <c r="G101" t="n">
-        <v>32252</v>
+        <v>8721</v>
       </c>
       <c r="H101" t="n">
-        <v>-9800</v>
+        <v>10804</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -5521,19 +5521,19 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K101" t="n">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M101" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
@@ -5548,22 +5548,22 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>-11528</v>
+        <v>-1831</v>
       </c>
       <c r="D102" t="n">
-        <v>-153043</v>
+        <v>-153464</v>
       </c>
       <c r="E102" t="n">
-        <v>-171211</v>
+        <v>-171829</v>
       </c>
       <c r="F102" t="n">
-        <v>18426</v>
+        <v>12800</v>
       </c>
       <c r="G102" t="n">
-        <v>147305</v>
+        <v>148168</v>
       </c>
       <c r="H102" t="n">
-        <v>2324</v>
+        <v>3713</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -5590,31 +5590,31 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>-22532</v>
+        <v>-13780</v>
       </c>
       <c r="D103" t="n">
-        <v>-199243</v>
+        <v>-196512</v>
       </c>
       <c r="E103" t="n">
-        <v>356777</v>
+        <v>-107885</v>
       </c>
       <c r="F103" t="n">
-        <v>5231</v>
+        <v>3378</v>
       </c>
       <c r="G103" t="n">
-        <v>6244</v>
+        <v>73422</v>
       </c>
       <c r="H103" t="n">
-        <v>-3220</v>
+        <v>-4652</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -5623,15 +5623,15 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K103" t="n">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M103" t="n">
@@ -5641,31 +5641,31 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>-30017</v>
+        <v>-21100</v>
       </c>
       <c r="D104" t="n">
-        <v>-207241</v>
+        <v>-214915</v>
       </c>
       <c r="E104" t="n">
-        <v>-118043</v>
+        <v>346952</v>
       </c>
       <c r="F104" t="n">
-        <v>6471</v>
+        <v>4186</v>
       </c>
       <c r="G104" t="n">
-        <v>73162</v>
+        <v>7457</v>
       </c>
       <c r="H104" t="n">
-        <v>-5485</v>
+        <v>-2314</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -5674,15 +5674,15 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K104" t="n">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M104" t="n">
@@ -5701,22 +5701,22 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>-31079</v>
+        <v>-9394</v>
       </c>
       <c r="D105" t="n">
-        <v>-257171</v>
+        <v>-277368</v>
       </c>
       <c r="E105" t="n">
-        <v>-18450</v>
+        <v>-16677</v>
       </c>
       <c r="F105" t="n">
-        <v>-22536</v>
+        <v>-20122</v>
       </c>
       <c r="G105" t="n">
-        <v>107654</v>
+        <v>104240</v>
       </c>
       <c r="H105" t="n">
-        <v>-1004</v>
+        <v>-892</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -5794,145 +5794,145 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 447 千股)</t>
+          <t>📉 20d 巨變(減碼 -3,533 千股)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>111432</v>
+        <v>-4456287</v>
       </c>
       <c r="D2" t="n">
-        <v>2326367</v>
+        <v>-8241230</v>
       </c>
       <c r="E2" t="n">
-        <v>485589</v>
+        <v>-4835084</v>
       </c>
       <c r="F2" t="n">
-        <v>1879108</v>
+        <v>-4708503</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>亞翔</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -468 千股)</t>
+          <t>📈 20d 巨變(加碼 256 千股)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-1260480</v>
+        <v>265140</v>
       </c>
       <c r="D3" t="n">
-        <v>1579726</v>
+        <v>2582206</v>
       </c>
       <c r="E3" t="n">
-        <v>-417700</v>
+        <v>111432</v>
       </c>
       <c r="F3" t="n">
-        <v>2047743</v>
+        <v>2326367</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>高力</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 99 千股)</t>
+          <t>📈 20d 巨變(加碼 606 千股)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>344513</v>
+        <v>373899</v>
       </c>
       <c r="D4" t="n">
-        <v>2841187</v>
+        <v>-51936</v>
       </c>
       <c r="E4" t="n">
-        <v>157487</v>
+        <v>38111</v>
       </c>
       <c r="F4" t="n">
-        <v>2742229</v>
+        <v>-657575</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>勤誠</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -3,194 千股)</t>
+          <t>📈 20d 巨變(加碼 281 千股)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-4835084</v>
+        <v>-629868</v>
       </c>
       <c r="D5" t="n">
-        <v>-4708503</v>
+        <v>1860939</v>
       </c>
       <c r="E5" t="n">
-        <v>-4587432</v>
+        <v>-1260480</v>
       </c>
       <c r="F5" t="n">
-        <v>-1514395</v>
+        <v>1579726</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>奇鋐</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 981 千股)</t>
+          <t>📉 20d 巨變(減碼 -13 千股)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38111</v>
+        <v>706964</v>
       </c>
       <c r="D6" t="n">
-        <v>-657575</v>
+        <v>2828466</v>
       </c>
       <c r="E6" t="n">
-        <v>-338736</v>
+        <v>344513</v>
       </c>
       <c r="F6" t="n">
-        <v>-1638900</v>
+        <v>2841187</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>健策</t>
         </is>
       </c>
     </row>
@@ -5944,20 +5944,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 712 千股)</t>
+          <t>📉 20d 巨變(減碼 -505 千股)</t>
         </is>
       </c>
       <c r="C7" t="n">
+        <v>-331149</v>
+      </c>
+      <c r="D7" t="n">
+        <v>285198</v>
+      </c>
+      <c r="E7" t="n">
         <v>-1882397</v>
       </c>
-      <c r="D7" t="n">
+      <c r="F7" t="n">
         <v>790433</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-1546922</v>
-      </c>
-      <c r="F7" t="n">
-        <v>78601</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -5973,20 +5973,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 523 千股)</t>
+          <t>📈 20d 巨變(加碼 899 千股)</t>
         </is>
       </c>
       <c r="C8" t="n">
+        <v>1722469</v>
+      </c>
+      <c r="D8" t="n">
+        <v>714824</v>
+      </c>
+      <c r="E8" t="n">
         <v>817238</v>
       </c>
-      <c r="D8" t="n">
+      <c r="F8" t="n">
         <v>-184455</v>
-      </c>
-      <c r="E8" t="n">
-        <v>81333</v>
-      </c>
-      <c r="F8" t="n">
-        <v>-707351</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -5997,29 +5997,29 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -316 千股)</t>
+          <t>📈 20d 巨變(加碼 454 千股)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-528262</v>
+        <v>2595025</v>
       </c>
       <c r="D9" t="n">
-        <v>-1027968</v>
+        <v>6508636</v>
       </c>
       <c r="E9" t="n">
-        <v>-237369</v>
+        <v>2030702</v>
       </c>
       <c r="F9" t="n">
-        <v>-711587</v>
+        <v>6054926</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>致茂</t>
         </is>
       </c>
     </row>
@@ -6031,20 +6031,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 705 千股)</t>
+          <t>📉 20d 巨變(減碼 -318 千股)</t>
         </is>
       </c>
       <c r="C10" t="n">
+        <v>-1771843</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-3945715</v>
+      </c>
+      <c r="E10" t="n">
         <v>-1779018</v>
       </c>
-      <c r="D10" t="n">
+      <c r="F10" t="n">
         <v>-3627228</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-1580184</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-4332184</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -6055,116 +6055,116 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -94 千股)</t>
+          <t>📉 20d 巨變(減碼 -22,063 千股)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2030702</v>
+        <v>-31281582</v>
       </c>
       <c r="D11" t="n">
-        <v>6054926</v>
+        <v>-104197922</v>
       </c>
       <c r="E11" t="n">
-        <v>2018468</v>
+        <v>-19106462</v>
       </c>
       <c r="F11" t="n">
-        <v>6149043</v>
+        <v>-82134727</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -5,972 千股)</t>
+          <t>📉 20d 巨變(減碼 -799 千股)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-19106462</v>
+        <v>-5272406</v>
       </c>
       <c r="D12" t="n">
-        <v>-82134727</v>
+        <v>-19716087</v>
       </c>
       <c r="E12" t="n">
-        <v>-29598185</v>
+        <v>-4835097</v>
       </c>
       <c r="F12" t="n">
-        <v>-76162501</v>
+        <v>-18916841</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>台達電</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -892 千股)</t>
+          <t>📉 20d 巨變(減碼 -9 千股)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-3183994</v>
+        <v>-1426377</v>
       </c>
       <c r="D13" t="n">
-        <v>7045383</v>
+        <v>-96055</v>
       </c>
       <c r="E13" t="n">
-        <v>-3061802</v>
+        <v>-1811018</v>
       </c>
       <c r="F13" t="n">
-        <v>7937798</v>
+        <v>-86813</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>智邦</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -454 千股)</t>
+          <t>📈 20d 巨變(加碼 137 千股)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-4835097</v>
+        <v>-497991</v>
       </c>
       <c r="D14" t="n">
-        <v>-18916841</v>
+        <v>-890867</v>
       </c>
       <c r="E14" t="n">
-        <v>-4659101</v>
+        <v>-528262</v>
       </c>
       <c r="F14" t="n">
-        <v>-18463334</v>
+        <v>-1027968</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>旺矽</t>
         </is>
       </c>
     </row>
@@ -6176,20 +6176,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 213 千股)</t>
+          <t>📈 20d 巨變(加碼 967 千股)</t>
         </is>
       </c>
       <c r="C15" t="n">
+        <v>1428643</v>
+      </c>
+      <c r="D15" t="n">
+        <v>945337</v>
+      </c>
+      <c r="E15" t="n">
         <v>989236</v>
       </c>
-      <c r="D15" t="n">
+      <c r="F15" t="n">
         <v>-21167</v>
-      </c>
-      <c r="E15" t="n">
-        <v>536850</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-233731</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -6200,29 +6200,29 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -648 千股)</t>
+          <t>📉 20d 巨變(減碼 -117 千股)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-1923289</v>
+        <v>112019</v>
       </c>
       <c r="D16" t="n">
-        <v>-2053861</v>
+        <v>1274055</v>
       </c>
       <c r="E16" t="n">
-        <v>-1078637</v>
+        <v>168739</v>
       </c>
       <c r="F16" t="n">
-        <v>-1406115</v>
+        <v>1390786</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>辛耘</t>
         </is>
       </c>
     </row>
@@ -6234,20 +6234,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -29 千股)</t>
+          <t>📈 20d 巨變(加碼 41 千股)</t>
         </is>
       </c>
       <c r="C17" t="n">
+        <v>-175968</v>
+      </c>
+      <c r="D17" t="n">
+        <v>28296</v>
+      </c>
+      <c r="E17" t="n">
         <v>-220363</v>
       </c>
-      <c r="D17" t="n">
+      <c r="F17" t="n">
         <v>-12424</v>
-      </c>
-      <c r="E17" t="n">
-        <v>-294861</v>
-      </c>
-      <c r="F17" t="n">
-        <v>16387</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -6258,145 +6258,145 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -316 千股)</t>
+          <t>📉 20d 巨變(減碼 -815 千股)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>168739</v>
+        <v>-2295919</v>
       </c>
       <c r="D18" t="n">
-        <v>1390786</v>
+        <v>-4295306</v>
       </c>
       <c r="E18" t="n">
-        <v>-642866</v>
+        <v>-2727139</v>
       </c>
       <c r="F18" t="n">
-        <v>1706839</v>
+        <v>-3480074</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>崇越</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,335 千股)</t>
+          <t>📈 20d 巨變(加碼 416 千股)</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-2727139</v>
+        <v>-1496965</v>
       </c>
       <c r="D19" t="n">
-        <v>-3480074</v>
+        <v>-1638265</v>
       </c>
       <c r="E19" t="n">
-        <v>-2677517</v>
+        <v>-1923289</v>
       </c>
       <c r="F19" t="n">
-        <v>-2145024</v>
+        <v>-2053861</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>佳必琪</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,401 千股)</t>
+          <t>📉 20d 巨變(減碼 -2,019 千股)</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1056115</v>
+        <v>-2528250</v>
       </c>
       <c r="D20" t="n">
-        <v>-17408642</v>
+        <v>5025936</v>
       </c>
       <c r="E20" t="n">
-        <v>805811</v>
+        <v>-3183994</v>
       </c>
       <c r="F20" t="n">
-        <v>-16007257</v>
+        <v>7045383</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>健鼎</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 692 千股)</t>
+          <t>📉 20d 巨變(減碼 -183 千股)</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-315914</v>
+        <v>-689136</v>
       </c>
       <c r="D21" t="n">
-        <v>-2355471</v>
+        <v>720049</v>
       </c>
       <c r="E21" t="n">
-        <v>-631103</v>
+        <v>-571714</v>
       </c>
       <c r="F21" t="n">
-        <v>-3047283</v>
+        <v>902687</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>中砂</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 26 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -2,131 千股)</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-571714</v>
+        <v>-1165454</v>
       </c>
       <c r="D22" t="n">
-        <v>902687</v>
+        <v>-19539272</v>
       </c>
       <c r="E22" t="n">
-        <v>-624857</v>
+        <v>1056115</v>
       </c>
       <c r="F22" t="n">
-        <v>877035</v>
+        <v>-17408642</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>中興電</t>
         </is>
       </c>
     </row>
@@ -6408,20 +6408,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -700 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 510 千股)</t>
         </is>
       </c>
       <c r="C23" t="n">
+        <v>357798</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-362488</v>
+      </c>
+      <c r="E23" t="n">
         <v>-182089</v>
       </c>
-      <c r="D23" t="n">
+      <c r="F23" t="n">
         <v>-872369</v>
-      </c>
-      <c r="E23" t="n">
-        <v>-113922</v>
-      </c>
-      <c r="F23" t="n">
-        <v>-172466</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -6437,20 +6437,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 248 千股)</t>
+          <t>📈 20d 巨變(加碼 592 千股)</t>
         </is>
       </c>
       <c r="C24" t="n">
+        <v>-1096503</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-4626705</v>
+      </c>
+      <c r="E24" t="n">
         <v>-760343</v>
       </c>
-      <c r="D24" t="n">
+      <c r="F24" t="n">
         <v>-5219138</v>
-      </c>
-      <c r="E24" t="n">
-        <v>-651890</v>
-      </c>
-      <c r="F24" t="n">
-        <v>-5466930</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -6461,58 +6461,58 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 267 千股)</t>
+          <t>📉 20d 巨變(減碼 -937 千股)</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1316327</v>
+        <v>-933279</v>
       </c>
       <c r="D25" t="n">
-        <v>2892791</v>
+        <v>-3291981</v>
       </c>
       <c r="E25" t="n">
-        <v>1631793</v>
+        <v>-315914</v>
       </c>
       <c r="F25" t="n">
-        <v>2625658</v>
+        <v>-2355471</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>大立光</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,070 千股)</t>
+          <t>📉 20d 巨變(減碼 -8 千股)</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-2480199</v>
+        <v>-10900</v>
       </c>
       <c r="D26" t="n">
-        <v>-2499344</v>
+        <v>-130786</v>
       </c>
       <c r="E26" t="n">
-        <v>-2242249</v>
+        <v>-8017</v>
       </c>
       <c r="F26" t="n">
-        <v>-1429063</v>
+        <v>-122886</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>大車隊</t>
         </is>
       </c>
     </row>
@@ -6524,20 +6524,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 50 千股)</t>
+          <t>📉 20d 巨變(減碼 -15 千股)</t>
         </is>
       </c>
       <c r="C27" t="n">
+        <v>82421</v>
+      </c>
+      <c r="D27" t="n">
+        <v>362755</v>
+      </c>
+      <c r="E27" t="n">
         <v>73877</v>
       </c>
-      <c r="D27" t="n">
+      <c r="F27" t="n">
         <v>378165</v>
-      </c>
-      <c r="E27" t="n">
-        <v>26277</v>
-      </c>
-      <c r="F27" t="n">
-        <v>328405</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -6548,319 +6548,319 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 640 千股)</t>
+          <t>📉 20d 巨變(減碼 -195 千股)</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-178376</v>
+        <v>-1785884</v>
       </c>
       <c r="D28" t="n">
-        <v>610952</v>
+        <v>-2412895</v>
       </c>
       <c r="E28" t="n">
-        <v>-77256</v>
+        <v>-908589</v>
       </c>
       <c r="F28" t="n">
-        <v>-28638</v>
+        <v>-2217608</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>建準</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -813 千股)</t>
+          <t>📈 20d 巨變(加碼 141 千股)</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-908589</v>
+        <v>945669</v>
       </c>
       <c r="D29" t="n">
-        <v>-2217608</v>
+        <v>3033996</v>
       </c>
       <c r="E29" t="n">
-        <v>-70617</v>
+        <v>1316327</v>
       </c>
       <c r="F29" t="n">
-        <v>-1404111</v>
+        <v>2892791</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>零壹</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -170 千股)</t>
+          <t>📉 20d 巨變(減碼 -648 千股)</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-982639</v>
+        <v>-2433199</v>
       </c>
       <c r="D30" t="n">
-        <v>204816</v>
+        <v>-3147493</v>
       </c>
       <c r="E30" t="n">
-        <v>-381908</v>
+        <v>-2480199</v>
       </c>
       <c r="F30" t="n">
-        <v>374792</v>
+        <v>-2499344</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>合機</t>
+          <t>隆大</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 847 千股)</t>
+          <t>📉 20d 巨變(減碼 -179 千股)</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2049176</v>
+        <v>-697694</v>
       </c>
       <c r="D31" t="n">
-        <v>-1717014</v>
+        <v>431636</v>
       </c>
       <c r="E31" t="n">
-        <v>1747876</v>
+        <v>-178376</v>
       </c>
       <c r="F31" t="n">
-        <v>-2564024</v>
+        <v>610952</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>湧德</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 772 千股)</t>
+          <t>📉 20d 巨變(減碼 -704 千股)</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>465704</v>
+        <v>-1561999</v>
       </c>
       <c r="D32" t="n">
-        <v>1164486</v>
+        <v>-499499</v>
       </c>
       <c r="E32" t="n">
-        <v>603874</v>
+        <v>-982639</v>
       </c>
       <c r="F32" t="n">
-        <v>392531</v>
+        <v>204816</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>合機</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -417 千股)</t>
+          <t>📈 20d 巨變(加碼 1,899 千股)</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-645937</v>
+        <v>1516397</v>
       </c>
       <c r="D33" t="n">
-        <v>-484560</v>
+        <v>182037</v>
       </c>
       <c r="E33" t="n">
-        <v>-401425</v>
+        <v>2049176</v>
       </c>
       <c r="F33" t="n">
-        <v>-67839</v>
+        <v>-1717014</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>寶雅</t>
+          <t>卜蜂</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 325 千股)</t>
+          <t>📈 20d 巨變(加碼 14,816 千股)</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>148081</v>
+        <v>213984721</v>
       </c>
       <c r="D34" t="n">
-        <v>-308542</v>
+        <v>329259102</v>
       </c>
       <c r="E34" t="n">
-        <v>188106</v>
+        <v>165901765</v>
       </c>
       <c r="F34" t="n">
-        <v>-633348</v>
+        <v>314442831</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 20,270 千股)</t>
+          <t>📉 20d 巨變(減碼 -180 千股)</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>165901765</v>
+        <v>-488500</v>
       </c>
       <c r="D35" t="n">
-        <v>314442831</v>
+        <v>-664967</v>
       </c>
       <c r="E35" t="n">
-        <v>102976642</v>
+        <v>-645937</v>
       </c>
       <c r="F35" t="n">
-        <v>294172415</v>
+        <v>-484560</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>寶雅</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -90 千股)</t>
+          <t>📉 20d 巨變(減碼 -618 千股)</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>-104042</v>
+        <v>225150</v>
       </c>
       <c r="D36" t="n">
-        <v>195746</v>
+        <v>546933</v>
       </c>
       <c r="E36" t="n">
-        <v>-65050</v>
+        <v>465704</v>
       </c>
       <c r="F36" t="n">
-        <v>285739</v>
+        <v>1164486</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>智冠</t>
+          <t>豐藝</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -53 千股)</t>
+          <t>📉 20d 巨變(減碼 -166 千股)</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-265325</v>
+        <v>-173368</v>
       </c>
       <c r="D37" t="n">
-        <v>-490472</v>
+        <v>29420</v>
       </c>
       <c r="E37" t="n">
-        <v>-352439</v>
+        <v>-104042</v>
       </c>
       <c r="F37" t="n">
-        <v>-437104</v>
+        <v>195746</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>智冠</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -105 千股)</t>
+          <t>📈 20d 巨變(加碼 379 千股)</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-383436</v>
+        <v>572670</v>
       </c>
       <c r="D38" t="n">
-        <v>-1020135</v>
+        <v>70047</v>
       </c>
       <c r="E38" t="n">
-        <v>-155463</v>
+        <v>148081</v>
       </c>
       <c r="F38" t="n">
-        <v>-915226</v>
+        <v>-308542</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>大統益</t>
         </is>
       </c>
     </row>
@@ -6872,20 +6872,20 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -381 千股)</t>
+          <t>📈 20d 巨變(加碼 73 千股)</t>
         </is>
       </c>
       <c r="C39" t="n">
+        <v>-234890</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-231136</v>
+      </c>
+      <c r="E39" t="n">
         <v>-304235</v>
       </c>
-      <c r="D39" t="n">
+      <c r="F39" t="n">
         <v>-304465</v>
-      </c>
-      <c r="E39" t="n">
-        <v>-173892</v>
-      </c>
-      <c r="F39" t="n">
-        <v>76456</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -6896,174 +6896,174 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 7,048 千股)</t>
+          <t>📈 20d 巨變(加碼 133 千股)</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>14833221</v>
+        <v>-157136</v>
       </c>
       <c r="D40" t="n">
-        <v>-19024441</v>
+        <v>-887055</v>
       </c>
       <c r="E40" t="n">
-        <v>-5075202</v>
+        <v>-383436</v>
       </c>
       <c r="F40" t="n">
-        <v>-26072637</v>
+        <v>-1020135</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>華景電</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 25 千股)</t>
+          <t>📈 20d 巨變(加碼 6,803 千股)</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-4000</v>
+        <v>25203233</v>
       </c>
       <c r="D41" t="n">
-        <v>-251300</v>
+        <v>-12221307</v>
       </c>
       <c r="E41" t="n">
-        <v>-59300</v>
+        <v>14833221</v>
       </c>
       <c r="F41" t="n">
-        <v>-276300</v>
+        <v>-19024441</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>聯合</t>
+          <t>台灣大</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 990 千股)</t>
+          <t>📈 20d 巨變(加碼 163 千股)</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3697648</v>
+        <v>-2400</v>
       </c>
       <c r="D42" t="n">
-        <v>-4532913</v>
+        <v>-327461</v>
       </c>
       <c r="E42" t="n">
-        <v>3632738</v>
+        <v>-265325</v>
       </c>
       <c r="F42" t="n">
-        <v>-5523286</v>
+        <v>-490472</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>穎崴</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 333 千股)</t>
+          <t>📉 20d 巨變(減碼 -7 千股)</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>104209</v>
+        <v>-19000</v>
       </c>
       <c r="D43" t="n">
-        <v>3652384</v>
+        <v>-258300</v>
       </c>
       <c r="E43" t="n">
-        <v>154723</v>
+        <v>-4000</v>
       </c>
       <c r="F43" t="n">
-        <v>3319191</v>
+        <v>-251300</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>聯合</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 268 千股)</t>
+          <t>📈 20d 巨變(加碼 2,156 千股)</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1932952</v>
+        <v>2786256</v>
       </c>
       <c r="D44" t="n">
-        <v>590996</v>
+        <v>-2377147</v>
       </c>
       <c r="E44" t="n">
-        <v>1551741</v>
+        <v>3697648</v>
       </c>
       <c r="F44" t="n">
-        <v>322959</v>
+        <v>-4532913</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -119 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -2,811 千股)</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-752022</v>
+        <v>-5309213</v>
       </c>
       <c r="D45" t="n">
-        <v>-895485</v>
+        <v>-2219578</v>
       </c>
       <c r="E45" t="n">
-        <v>-1602097</v>
+        <v>1932952</v>
       </c>
       <c r="F45" t="n">
-        <v>-776430</v>
+        <v>590996</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>亞力</t>
         </is>
       </c>
     </row>
@@ -7075,20 +7075,20 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -81 千股)</t>
+          <t>📉 20d 巨變(減碼 -154 千股)</t>
         </is>
       </c>
       <c r="C46" t="n">
+        <v>87120</v>
+      </c>
+      <c r="D46" t="n">
+        <v>-753706</v>
+      </c>
+      <c r="E46" t="n">
         <v>105365</v>
       </c>
-      <c r="D46" t="n">
+      <c r="F46" t="n">
         <v>-599461</v>
-      </c>
-      <c r="E46" t="n">
-        <v>282866</v>
-      </c>
-      <c r="F46" t="n">
-        <v>-518692</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -7099,58 +7099,58 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -155 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -927 千股)</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1157738</v>
+        <v>-439468</v>
       </c>
       <c r="D47" t="n">
-        <v>-8868544</v>
+        <v>2725398</v>
       </c>
       <c r="E47" t="n">
-        <v>-364777</v>
+        <v>104209</v>
       </c>
       <c r="F47" t="n">
-        <v>-8713956</v>
+        <v>3652384</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>漢科</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 879 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 2,119 千股)</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1261328</v>
+        <v>2002335</v>
       </c>
       <c r="D48" t="n">
-        <v>-3096187</v>
+        <v>1223778</v>
       </c>
       <c r="E48" t="n">
-        <v>801858</v>
+        <v>-752022</v>
       </c>
       <c r="F48" t="n">
-        <v>-3975426</v>
+        <v>-895485</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>台燿</t>
         </is>
       </c>
     </row>
@@ -7162,20 +7162,20 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 861 千股)</t>
+          <t>📉 20d 巨變(減碼 -741 千股)</t>
         </is>
       </c>
       <c r="C49" t="n">
+        <v>-172267</v>
+      </c>
+      <c r="D49" t="n">
+        <v>-2558809</v>
+      </c>
+      <c r="E49" t="n">
         <v>-827679</v>
       </c>
-      <c r="D49" t="n">
+      <c r="F49" t="n">
         <v>-1817899</v>
-      </c>
-      <c r="E49" t="n">
-        <v>-694425</v>
-      </c>
-      <c r="F49" t="n">
-        <v>-2678969</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -7186,232 +7186,232 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -71 千股)</t>
+          <t>📈 20d 巨變(加碼 7,829 千股)</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-805452</v>
+        <v>6474065</v>
       </c>
       <c r="D50" t="n">
-        <v>-3049831</v>
+        <v>-1039677</v>
       </c>
       <c r="E50" t="n">
-        <v>-1232514</v>
+        <v>1157738</v>
       </c>
       <c r="F50" t="n">
-        <v>-2978661</v>
+        <v>-8868544</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>立隆電</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -54,242 千股)</t>
+          <t>📈 20d 巨變(加碼 963 千股)</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-15028303</v>
+        <v>710474</v>
       </c>
       <c r="D51" t="n">
-        <v>-45392226</v>
+        <v>-2133121</v>
       </c>
       <c r="E51" t="n">
-        <v>6597485</v>
+        <v>1261328</v>
       </c>
       <c r="F51" t="n">
-        <v>8849613</v>
+        <v>-3096187</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 3,631 千股)</t>
+          <t>📉 20d 巨變(減碼 -396 千股)</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>10346533</v>
+        <v>-906305</v>
       </c>
       <c r="D52" t="n">
-        <v>496568</v>
+        <v>-3445921</v>
       </c>
       <c r="E52" t="n">
-        <v>7350345</v>
+        <v>-805452</v>
       </c>
       <c r="F52" t="n">
-        <v>-3133976</v>
+        <v>-3049831</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>世芯-KY</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 983 千股)</t>
+          <t>📉 20d 巨變(減碼 -7,633 千股)</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-160203</v>
+        <v>13691296</v>
       </c>
       <c r="D53" t="n">
-        <v>-2509047</v>
+        <v>-7136115</v>
       </c>
       <c r="E53" t="n">
-        <v>-8923</v>
+        <v>10346533</v>
       </c>
       <c r="F53" t="n">
-        <v>-3492289</v>
+        <v>496568</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -4,786 千股)</t>
+          <t>📈 20d 巨變(加碼 6,487 千股)</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-14884397</v>
+        <v>-19666599</v>
       </c>
       <c r="D54" t="n">
-        <v>42017787</v>
+        <v>-38905078</v>
       </c>
       <c r="E54" t="n">
-        <v>-30100117</v>
+        <v>-15028303</v>
       </c>
       <c r="F54" t="n">
-        <v>46804087</v>
+        <v>-45392226</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -208 千股)</t>
+          <t>📉 20d 巨變(減碼 -5,265 千股)</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>-1431349</v>
+        <v>-14744880</v>
       </c>
       <c r="D55" t="n">
-        <v>-6181312</v>
+        <v>36753211</v>
       </c>
       <c r="E55" t="n">
-        <v>-2289673</v>
+        <v>-14884397</v>
       </c>
       <c r="F55" t="n">
-        <v>-5973401</v>
+        <v>42017787</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 127 千股)</t>
+          <t>📈 20d 巨變(加碼 702 千股)</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>702120</v>
+        <v>-148303</v>
       </c>
       <c r="D56" t="n">
-        <v>-1223205</v>
+        <v>-1806601</v>
       </c>
       <c r="E56" t="n">
-        <v>1006160</v>
+        <v>-160203</v>
       </c>
       <c r="F56" t="n">
-        <v>-1350330</v>
+        <v>-2509047</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>鈊象</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -149 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -1,256 千股)</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>-137557</v>
+        <v>-1094692</v>
       </c>
       <c r="D57" t="n">
-        <v>633627</v>
+        <v>-2478848</v>
       </c>
       <c r="E57" t="n">
-        <v>-169018</v>
+        <v>702120</v>
       </c>
       <c r="F57" t="n">
-        <v>782519</v>
+        <v>-1223205</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>士電</t>
         </is>
       </c>
     </row>
@@ -7423,20 +7423,20 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 27 千股)</t>
+          <t>📈 20d 巨變(加碼 74 千股)</t>
         </is>
       </c>
       <c r="C58" t="n">
+        <v>-290950</v>
+      </c>
+      <c r="D58" t="n">
+        <v>-622221</v>
+      </c>
+      <c r="E58" t="n">
         <v>-386947</v>
       </c>
-      <c r="D58" t="n">
+      <c r="F58" t="n">
         <v>-695983</v>
-      </c>
-      <c r="E58" t="n">
-        <v>-212730</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-722511</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -7447,87 +7447,87 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -515 千股)</t>
+          <t>📈 20d 巨變(加碼 1,127 千股)</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>129382</v>
+        <v>-1437169</v>
       </c>
       <c r="D59" t="n">
-        <v>586719</v>
+        <v>-5054173</v>
       </c>
       <c r="E59" t="n">
-        <v>452685</v>
+        <v>-1431349</v>
       </c>
       <c r="F59" t="n">
-        <v>1101286</v>
+        <v>-6181312</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>勝一</t>
+          <t>鉅祥</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 157 千股)</t>
+          <t>📉 20d 巨變(減碼 -427 千股)</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>464022</v>
+        <v>-231647</v>
       </c>
       <c r="D60" t="n">
-        <v>1266597</v>
+        <v>206433</v>
       </c>
       <c r="E60" t="n">
-        <v>339584</v>
+        <v>-137557</v>
       </c>
       <c r="F60" t="n">
-        <v>1109545</v>
+        <v>633627</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>達欣工</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 130 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 112 千股)</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-296842</v>
+        <v>-384065</v>
       </c>
       <c r="D61" t="n">
-        <v>40334</v>
+        <v>698346</v>
       </c>
       <c r="E61" t="n">
-        <v>-458462</v>
+        <v>129382</v>
       </c>
       <c r="F61" t="n">
-        <v>-89666</v>
+        <v>586719</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>勝一</t>
         </is>
       </c>
     </row>
@@ -7539,20 +7539,20 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 211 千股)</t>
+          <t>📈 20d 巨變(加碼 337 千股)</t>
         </is>
       </c>
       <c r="C62" t="n">
+        <v>586183</v>
+      </c>
+      <c r="D62" t="n">
+        <v>835003</v>
+      </c>
+      <c r="E62" t="n">
         <v>86309</v>
       </c>
-      <c r="D62" t="n">
+      <c r="F62" t="n">
         <v>497896</v>
-      </c>
-      <c r="E62" t="n">
-        <v>-313334</v>
-      </c>
-      <c r="F62" t="n">
-        <v>286589</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -7563,493 +7563,493 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 155 千股)</t>
+          <t>📈 20d 巨變(加碼 199 千股)</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-1016793</v>
+        <v>-1556382</v>
       </c>
       <c r="D63" t="n">
-        <v>274016</v>
+        <v>3190619</v>
       </c>
       <c r="E63" t="n">
-        <v>-2813216</v>
+        <v>-2412807</v>
       </c>
       <c r="F63" t="n">
-        <v>119299</v>
+        <v>2991490</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>藥華藥</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -478 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 1,139 千股)</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>-2412807</v>
+        <v>804593</v>
       </c>
       <c r="D64" t="n">
-        <v>2991490</v>
+        <v>1413209</v>
       </c>
       <c r="E64" t="n">
-        <v>-2013643</v>
+        <v>-1016793</v>
       </c>
       <c r="F64" t="n">
-        <v>3469071</v>
+        <v>274016</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>華星光</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 665 千股)</t>
+          <t>📉 20d 巨變(減碼 -277 千股)</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>341101</v>
+        <v>-223750</v>
       </c>
       <c r="D65" t="n">
-        <v>-334683</v>
+        <v>-236457</v>
       </c>
       <c r="E65" t="n">
-        <v>374711</v>
+        <v>-296842</v>
       </c>
       <c r="F65" t="n">
-        <v>-999660</v>
+        <v>40334</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>信立</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 3,642 千股)</t>
+          <t>📉 20d 巨變(減碼 -631 千股)</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-17526992</v>
+        <v>-1965857</v>
       </c>
       <c r="D66" t="n">
-        <v>-30863255</v>
+        <v>-5117766</v>
       </c>
       <c r="E66" t="n">
-        <v>-16776571</v>
+        <v>-1800561</v>
       </c>
       <c r="F66" t="n">
-        <v>-34504936</v>
+        <v>-4486320</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>宇瞻</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -2,993 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -1,526 千股)</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-1024328</v>
+        <v>-244190</v>
       </c>
       <c r="D67" t="n">
-        <v>1046760</v>
+        <v>-1861101</v>
       </c>
       <c r="E67" t="n">
-        <v>-633698</v>
+        <v>341101</v>
       </c>
       <c r="F67" t="n">
-        <v>4039494</v>
+        <v>-334683</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>聯鈞</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 575 千股)</t>
+          <t>📉 20d 巨變(減碼 -2,529 千股)</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-1800561</v>
+        <v>-18618023</v>
       </c>
       <c r="D68" t="n">
-        <v>-4486320</v>
+        <v>-33391928</v>
       </c>
       <c r="E68" t="n">
-        <v>-1896495</v>
+        <v>-17526992</v>
       </c>
       <c r="F68" t="n">
-        <v>-5061734</v>
+        <v>-30863255</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 3,151 千股)</t>
+          <t>📉 20d 巨變(減碼 -261 千股)</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-30017275</v>
+        <v>-3032354</v>
       </c>
       <c r="D69" t="n">
-        <v>-207240513</v>
+        <v>-12274112</v>
       </c>
       <c r="E69" t="n">
-        <v>-33660192</v>
+        <v>-3514951</v>
       </c>
       <c r="F69" t="n">
-        <v>-210391670</v>
+        <v>-12013199</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>瑞昱</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,859 千股)</t>
+          <t>📈 20d 巨變(加碼 10,728 千股)</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-3514951</v>
+        <v>-13780172</v>
       </c>
       <c r="D70" t="n">
-        <v>-12013199</v>
+        <v>-196512336</v>
       </c>
       <c r="E70" t="n">
-        <v>-2706331</v>
+        <v>-30017275</v>
       </c>
       <c r="F70" t="n">
-        <v>-10154168</v>
+        <v>-207240513</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,845 千股)</t>
+          <t>📈 20d 巨變(加碼 137 千股)</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>10098371</v>
+        <v>-614319</v>
       </c>
       <c r="D71" t="n">
-        <v>21829304</v>
+        <v>1183786</v>
       </c>
       <c r="E71" t="n">
-        <v>6277490</v>
+        <v>-1024328</v>
       </c>
       <c r="F71" t="n">
-        <v>19984601</v>
+        <v>1046760</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>聯亞</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -137 千股)</t>
+          <t>📈 20d 巨變(加碼 2,174 千股)</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-607571</v>
+        <v>-5763419</v>
       </c>
       <c r="D72" t="n">
-        <v>-854488</v>
+        <v>-23090306</v>
       </c>
       <c r="E72" t="n">
-        <v>-579959</v>
+        <v>-6149467</v>
       </c>
       <c r="F72" t="n">
-        <v>-717235</v>
+        <v>-25264054</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>億泰</t>
+          <t>台汽電</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 37 千股)</t>
+          <t>📉 20d 巨變(減碼 -34 千股)</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-696227</v>
+        <v>-474752</v>
       </c>
       <c r="D73" t="n">
-        <v>115356</v>
+        <v>-888229</v>
       </c>
       <c r="E73" t="n">
-        <v>-797741</v>
+        <v>-607571</v>
       </c>
       <c r="F73" t="n">
-        <v>78314</v>
+        <v>-854488</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>德昌</t>
+          <t>億泰</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -3,231 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 13,106 千股)</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>-6149467</v>
+        <v>-3967492</v>
       </c>
       <c r="D74" t="n">
-        <v>-25264054</v>
+        <v>34935536</v>
       </c>
       <c r="E74" t="n">
-        <v>-1936244</v>
+        <v>10098371</v>
       </c>
       <c r="F74" t="n">
-        <v>-22033033</v>
+        <v>21829304</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -472 千股)</t>
+          <t>📈 20d 巨變(加碼 72 千股)</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>500132</v>
+        <v>-25952</v>
       </c>
       <c r="D75" t="n">
-        <v>2451927</v>
+        <v>-355456</v>
       </c>
       <c r="E75" t="n">
-        <v>299534</v>
+        <v>-111000</v>
       </c>
       <c r="F75" t="n">
-        <v>2923903</v>
+        <v>-427564</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>友輝</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -16 千股)</t>
+          <t>📉 20d 巨變(減碼 -421 千股)</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-111000</v>
+        <v>-957327</v>
       </c>
       <c r="D76" t="n">
-        <v>-427564</v>
+        <v>-305744</v>
       </c>
       <c r="E76" t="n">
-        <v>-35000</v>
+        <v>-696227</v>
       </c>
       <c r="F76" t="n">
-        <v>-411564</v>
+        <v>115356</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>德昌</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -692 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,110 千股)</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-2486742</v>
+        <v>211014</v>
       </c>
       <c r="D77" t="n">
-        <v>4385555</v>
+        <v>1342007</v>
       </c>
       <c r="E77" t="n">
-        <v>-1954648</v>
+        <v>500132</v>
       </c>
       <c r="F77" t="n">
-        <v>5077736</v>
+        <v>2451927</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>智易</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 4,427 千股)</t>
+          <t>📉 20d 巨變(減碼 -109 千股)</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1853210</v>
+        <v>-2464797</v>
       </c>
       <c r="D78" t="n">
-        <v>2138111</v>
+        <v>4276282</v>
       </c>
       <c r="E78" t="n">
-        <v>1264568</v>
+        <v>-2486742</v>
       </c>
       <c r="F78" t="n">
-        <v>-2288735</v>
+        <v>4385555</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>原相</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -131 千股)</t>
+          <t>📈 20d 巨變(加碼 964 千股)</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-98396</v>
+        <v>2564589</v>
       </c>
       <c r="D79" t="n">
-        <v>109766</v>
+        <v>3101857</v>
       </c>
       <c r="E79" t="n">
-        <v>-90882</v>
+        <v>1853210</v>
       </c>
       <c r="F79" t="n">
-        <v>240815</v>
+        <v>2138111</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>啟碁</t>
         </is>
       </c>
     </row>
@@ -8061,20 +8061,20 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -17,563 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,079 千股)</t>
         </is>
       </c>
       <c r="C80" t="n">
+        <v>-39841055</v>
+      </c>
+      <c r="D80" t="n">
+        <v>-59452449</v>
+      </c>
+      <c r="E80" t="n">
         <v>-42758358</v>
       </c>
-      <c r="D80" t="n">
+      <c r="F80" t="n">
         <v>-58373805</v>
-      </c>
-      <c r="E80" t="n">
-        <v>-17187609</v>
-      </c>
-      <c r="F80" t="n">
-        <v>-40811097</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -8085,290 +8085,290 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -3,131 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 395 千股)</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-22531859</v>
+        <v>343519</v>
       </c>
       <c r="D81" t="n">
-        <v>-199242648</v>
+        <v>505112</v>
       </c>
       <c r="E81" t="n">
-        <v>-20766181</v>
+        <v>-98396</v>
       </c>
       <c r="F81" t="n">
-        <v>-196111151</v>
+        <v>109766</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>精測</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 869 千股)</t>
+          <t>📉 20d 巨變(減碼 -15,672 千股)</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-837370</v>
+        <v>-21099789</v>
       </c>
       <c r="D82" t="n">
-        <v>-5385329</v>
+        <v>-214914718</v>
       </c>
       <c r="E82" t="n">
-        <v>-1193641</v>
+        <v>-22531859</v>
       </c>
       <c r="F82" t="n">
-        <v>-6254690</v>
+        <v>-199242648</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -126 千股)</t>
+          <t>📈 20d 巨變(加碼 701 千股)</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-120580</v>
+        <v>-246893</v>
       </c>
       <c r="D83" t="n">
-        <v>203295</v>
+        <v>-4684004</v>
       </c>
       <c r="E83" t="n">
-        <v>-14830</v>
+        <v>-837370</v>
       </c>
       <c r="F83" t="n">
-        <v>329194</v>
+        <v>-5385329</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 102 千股)</t>
+          <t>📉 20d 巨變(減碼 -75 千股)</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-1263264</v>
+        <v>-160580</v>
       </c>
       <c r="D84" t="n">
-        <v>-3110667</v>
+        <v>127845</v>
       </c>
       <c r="E84" t="n">
-        <v>-1726873</v>
+        <v>-120580</v>
       </c>
       <c r="F84" t="n">
-        <v>-3212630</v>
+        <v>203295</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>東科-KY</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 358 千股)</t>
+          <t>📈 20d 巨變(加碼 274 千股)</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>83065</v>
+        <v>-1477571</v>
       </c>
       <c r="D85" t="n">
-        <v>-381662</v>
+        <v>-292448</v>
       </c>
       <c r="E85" t="n">
-        <v>55065</v>
+        <v>-1719571</v>
       </c>
       <c r="F85" t="n">
-        <v>-739558</v>
+        <v>-566448</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>鑫龍騰</t>
+          <t>全友</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,149 千股)</t>
+          <t>📈 20d 巨變(加碼 173 千股)</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-1719571</v>
+        <v>160000</v>
       </c>
       <c r="D86" t="n">
-        <v>-566448</v>
+        <v>-208662</v>
       </c>
       <c r="E86" t="n">
-        <v>-1471571</v>
+        <v>83065</v>
       </c>
       <c r="F86" t="n">
-        <v>582620</v>
+        <v>-381662</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>鑫龍騰</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -219 千股)</t>
+          <t>📉 20d 巨變(減碼 -573 千股)</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>857867</v>
+        <v>-1560486</v>
       </c>
       <c r="D87" t="n">
-        <v>4019230</v>
+        <v>-3683884</v>
       </c>
       <c r="E87" t="n">
-        <v>1504570</v>
+        <v>-1263264</v>
       </c>
       <c r="F87" t="n">
-        <v>4238328</v>
+        <v>-3110667</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>宏捷科</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 879 千股)</t>
+          <t>📉 20d 巨變(減碼 -147 千股)</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>-23531277</v>
+        <v>797829</v>
       </c>
       <c r="D88" t="n">
-        <v>-88104038</v>
+        <v>3872431</v>
       </c>
       <c r="E88" t="n">
-        <v>-33457248</v>
+        <v>857867</v>
       </c>
       <c r="F88" t="n">
-        <v>-88982939</v>
+        <v>4019230</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>研華</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 190 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,886 千股)</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-123084</v>
+        <v>-20365313</v>
       </c>
       <c r="D89" t="n">
-        <v>-5926808</v>
+        <v>-89990267</v>
       </c>
       <c r="E89" t="n">
-        <v>316313</v>
+        <v>-23531277</v>
       </c>
       <c r="F89" t="n">
-        <v>-6116747</v>
+        <v>-88104038</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -2,248 千股)</t>
+          <t>📈 20d 巨變(加碼 731 千股)</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>-1002456</v>
+        <v>-136366</v>
       </c>
       <c r="D90" t="n">
-        <v>6407559</v>
+        <v>-5196210</v>
       </c>
       <c r="E90" t="n">
-        <v>1346923</v>
+        <v>-123084</v>
       </c>
       <c r="F90" t="n">
-        <v>8655988</v>
+        <v>-5926808</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>中保科</t>
         </is>
       </c>
     </row>
@@ -8380,20 +8380,20 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -13 千股)</t>
+          <t>📉 20d 巨變(減碼 -10 千股)</t>
         </is>
       </c>
       <c r="C91" t="n">
+        <v>-3529</v>
+      </c>
+      <c r="D91" t="n">
+        <v>-172161</v>
+      </c>
+      <c r="E91" t="n">
         <v>-1922</v>
       </c>
-      <c r="D91" t="n">
+      <c r="F91" t="n">
         <v>-161697</v>
-      </c>
-      <c r="E91" t="n">
-        <v>-89468</v>
-      </c>
-      <c r="F91" t="n">
-        <v>-148545</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -8404,29 +8404,29 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -30 千股)</t>
+          <t>📉 20d 巨變(減碼 -473 千股)</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>68050</v>
+        <v>-288839</v>
       </c>
       <c r="D92" t="n">
-        <v>-460745</v>
+        <v>5934767</v>
       </c>
       <c r="E92" t="n">
-        <v>33616</v>
+        <v>-1002456</v>
       </c>
       <c r="F92" t="n">
-        <v>-430382</v>
+        <v>6407559</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>長榮航太</t>
         </is>
       </c>
     </row>
@@ -8438,20 +8438,20 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -2,380 千股)</t>
+          <t>📉 20d 巨變(減碼 -421 千股)</t>
         </is>
       </c>
       <c r="C93" t="n">
+        <v>-1831280</v>
+      </c>
+      <c r="D93" t="n">
+        <v>-153463886</v>
+      </c>
+      <c r="E93" t="n">
         <v>-11528119</v>
       </c>
-      <c r="D93" t="n">
+      <c r="F93" t="n">
         <v>-153043108</v>
-      </c>
-      <c r="E93" t="n">
-        <v>-17284376</v>
-      </c>
-      <c r="F93" t="n">
-        <v>-150663423</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -8467,20 +8467,20 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -13 千股)</t>
+          <t>📉 20d 巨變(減碼 -30 千股)</t>
         </is>
       </c>
       <c r="C94" t="n">
+        <v>-58923</v>
+      </c>
+      <c r="D94" t="n">
+        <v>92664</v>
+      </c>
+      <c r="E94" t="n">
         <v>-20000</v>
       </c>
-      <c r="D94" t="n">
+      <c r="F94" t="n">
         <v>122887</v>
-      </c>
-      <c r="E94" t="n">
-        <v>9000</v>
-      </c>
-      <c r="F94" t="n">
-        <v>135847</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -8491,87 +8491,87 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -47,235 千股)</t>
+          <t>📉 20d 巨變(減碼 -820 千股)</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>-31079291</v>
+        <v>-2093865</v>
       </c>
       <c r="D95" t="n">
-        <v>-257171105</v>
+        <v>-2394845</v>
       </c>
       <c r="E95" t="n">
-        <v>-27735143</v>
+        <v>-1309348</v>
       </c>
       <c r="F95" t="n">
-        <v>-209936265</v>
+        <v>-1574947</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>聯發科</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,022 千股)</t>
+          <t>📉 20d 巨變(減碼 -20,197 千股)</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>-126812</v>
+        <v>-9393707</v>
       </c>
       <c r="D96" t="n">
-        <v>-4329127</v>
+        <v>-277368453</v>
       </c>
       <c r="E96" t="n">
-        <v>-874364</v>
+        <v>-31079291</v>
       </c>
       <c r="F96" t="n">
-        <v>-5350977</v>
+        <v>-257171105</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -541 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 359 千股)</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>-1309348</v>
+        <v>38681</v>
       </c>
       <c r="D97" t="n">
-        <v>-1574947</v>
+        <v>-3969741</v>
       </c>
       <c r="E97" t="n">
-        <v>-3902539</v>
+        <v>-126812</v>
       </c>
       <c r="F97" t="n">
-        <v>-1033870</v>
+        <v>-4329127</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>創意</t>
         </is>
       </c>
     </row>
@@ -8583,20 +8583,20 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 324 千股)</t>
+          <t>📈 20d 巨變(加碼 169 千股)</t>
         </is>
       </c>
       <c r="C98" t="n">
+        <v>-419324</v>
+      </c>
+      <c r="D98" t="n">
+        <v>-4362453</v>
+      </c>
+      <c r="E98" t="n">
         <v>-697969</v>
       </c>
-      <c r="D98" t="n">
+      <c r="F98" t="n">
         <v>-4531646</v>
-      </c>
-      <c r="E98" t="n">
-        <v>-796614</v>
-      </c>
-      <c r="F98" t="n">
-        <v>-4855800</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -8607,58 +8607,58 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 2,731 千股)</t>
+          <t>📈 20d 巨變(加碼 35 千股)</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>2732167</v>
+        <v>89745</v>
       </c>
       <c r="D99" t="n">
-        <v>6544667</v>
+        <v>319568</v>
       </c>
       <c r="E99" t="n">
-        <v>1182641</v>
+        <v>3165</v>
       </c>
       <c r="F99" t="n">
-        <v>3813387</v>
+        <v>284998</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>信驊</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -63 千股)</t>
+          <t>📈 20d 巨變(加碼 1,614 千股)</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>3165</v>
+        <v>5319599</v>
       </c>
       <c r="D100" t="n">
-        <v>284998</v>
+        <v>8159133</v>
       </c>
       <c r="E100" t="n">
-        <v>-12462</v>
+        <v>2732167</v>
       </c>
       <c r="F100" t="n">
-        <v>347553</v>
+        <v>6544667</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>金像電</t>
         </is>
       </c>
     </row>
@@ -8670,20 +8670,20 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -142 千股)</t>
+          <t>📈 20d 巨變(加碼 570 千股)</t>
         </is>
       </c>
       <c r="C101" t="n">
+        <v>-1300882</v>
+      </c>
+      <c r="D101" t="n">
+        <v>915593</v>
+      </c>
+      <c r="E101" t="n">
         <v>-1026092</v>
       </c>
-      <c r="D101" t="n">
+      <c r="F101" t="n">
         <v>345829</v>
-      </c>
-      <c r="E101" t="n">
-        <v>-568581</v>
-      </c>
-      <c r="F101" t="n">
-        <v>487443</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -8699,20 +8699,20 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -388 千股)</t>
+          <t>📈 20d 巨變(加碼 431 千股)</t>
         </is>
       </c>
       <c r="C102" t="n">
+        <v>296332</v>
+      </c>
+      <c r="D102" t="n">
+        <v>-31353</v>
+      </c>
+      <c r="E102" t="n">
         <v>409811</v>
       </c>
-      <c r="D102" t="n">
+      <c r="F102" t="n">
         <v>-462187</v>
-      </c>
-      <c r="E102" t="n">
-        <v>1471521</v>
-      </c>
-      <c r="F102" t="n">
-        <v>-73831</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>

--- a/data/台股_外資雷達.xlsx
+++ b/data/台股_外資雷達.xlsx
@@ -496,22 +496,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>213985</v>
+        <v>223296</v>
       </c>
       <c r="D2" t="n">
-        <v>329259</v>
+        <v>347498</v>
       </c>
       <c r="E2" t="n">
-        <v>130166</v>
+        <v>154302</v>
       </c>
       <c r="F2" t="n">
-        <v>-12936</v>
+        <v>-22211</v>
       </c>
       <c r="G2" t="n">
-        <v>28143</v>
+        <v>24587</v>
       </c>
       <c r="H2" t="n">
-        <v>1619</v>
+        <v>1145</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -547,22 +547,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-14745</v>
+        <v>-7340</v>
       </c>
       <c r="D3" t="n">
-        <v>36753</v>
+        <v>37007</v>
       </c>
       <c r="E3" t="n">
-        <v>-1029</v>
+        <v>3244</v>
       </c>
       <c r="F3" t="n">
-        <v>7190</v>
+        <v>6923</v>
       </c>
       <c r="G3" t="n">
-        <v>-40590</v>
+        <v>-35932</v>
       </c>
       <c r="H3" t="n">
-        <v>2884</v>
+        <v>3381</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-3967</v>
+        <v>1171</v>
       </c>
       <c r="D4" t="n">
-        <v>34936</v>
+        <v>36294</v>
       </c>
       <c r="E4" t="n">
-        <v>119257</v>
+        <v>121950</v>
       </c>
       <c r="F4" t="n">
-        <v>-1182</v>
+        <v>-585</v>
       </c>
       <c r="G4" t="n">
-        <v>-30805</v>
+        <v>-30768</v>
       </c>
       <c r="H4" t="n">
-        <v>2427</v>
+        <v>2096</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -649,22 +649,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5320</v>
+        <v>5541</v>
       </c>
       <c r="D5" t="n">
-        <v>8159</v>
+        <v>8244</v>
       </c>
       <c r="E5" t="n">
-        <v>11972</v>
+        <v>12682</v>
       </c>
       <c r="F5" t="n">
-        <v>-3892</v>
+        <v>-4438</v>
       </c>
       <c r="G5" t="n">
-        <v>-9979</v>
+        <v>-10894</v>
       </c>
       <c r="H5" t="n">
-        <v>-244</v>
+        <v>-556</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -679,31 +679,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>長榮航太</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2595</v>
+        <v>-1556</v>
       </c>
       <c r="D6" t="n">
-        <v>6509</v>
+        <v>6371</v>
       </c>
       <c r="E6" t="n">
-        <v>10716</v>
+        <v>10528</v>
       </c>
       <c r="F6" t="n">
-        <v>-1740</v>
+        <v>-113</v>
       </c>
       <c r="G6" t="n">
-        <v>-5700</v>
+        <v>-667</v>
       </c>
       <c r="H6" t="n">
-        <v>201</v>
+        <v>505</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -712,49 +712,49 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-289</v>
+        <v>4001</v>
       </c>
       <c r="D7" t="n">
-        <v>5935</v>
+        <v>5928</v>
       </c>
       <c r="E7" t="n">
-        <v>10198</v>
+        <v>28222</v>
       </c>
       <c r="F7" t="n">
-        <v>-107</v>
+        <v>-2290</v>
       </c>
       <c r="G7" t="n">
-        <v>-670</v>
+        <v>-13078</v>
       </c>
       <c r="H7" t="n">
-        <v>523</v>
+        <v>185</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -763,49 +763,49 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-2528</v>
+        <v>2562</v>
       </c>
       <c r="D8" t="n">
-        <v>5026</v>
+        <v>5626</v>
       </c>
       <c r="E8" t="n">
-        <v>11631</v>
+        <v>10669</v>
       </c>
       <c r="F8" t="n">
-        <v>-358</v>
+        <v>-1207</v>
       </c>
       <c r="G8" t="n">
-        <v>-9857</v>
+        <v>-4943</v>
       </c>
       <c r="H8" t="n">
-        <v>-272</v>
+        <v>71</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-2465</v>
+        <v>-2609</v>
       </c>
       <c r="D9" t="n">
-        <v>4276</v>
+        <v>4217</v>
       </c>
       <c r="E9" t="n">
-        <v>7938</v>
+        <v>7645</v>
       </c>
       <c r="F9" t="n">
-        <v>416</v>
+        <v>-290</v>
       </c>
       <c r="G9" t="n">
-        <v>4609</v>
+        <v>4428</v>
       </c>
       <c r="H9" t="n">
-        <v>-37</v>
+        <v>-60</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -892,22 +892,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>798</v>
+        <v>786</v>
       </c>
       <c r="D10" t="n">
-        <v>3872</v>
+        <v>3769</v>
       </c>
       <c r="E10" t="n">
-        <v>15152</v>
+        <v>15198</v>
       </c>
       <c r="F10" t="n">
-        <v>218</v>
+        <v>118</v>
       </c>
       <c r="G10" t="n">
-        <v>617</v>
+        <v>825</v>
       </c>
       <c r="H10" t="n">
-        <v>239</v>
+        <v>294</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -934,31 +934,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>零壹</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-1556</v>
+        <v>1106</v>
       </c>
       <c r="D11" t="n">
-        <v>3191</v>
+        <v>3651</v>
       </c>
       <c r="E11" t="n">
-        <v>14226</v>
+        <v>1945</v>
       </c>
       <c r="F11" t="n">
-        <v>150</v>
+        <v>-1</v>
       </c>
       <c r="G11" t="n">
-        <v>1180</v>
+        <v>-128</v>
       </c>
       <c r="H11" t="n">
-        <v>-27</v>
+        <v>-741</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -967,49 +967,49 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>66</v>
+        <v>97</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>🚀 加速器*</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2565</v>
+        <v>601</v>
       </c>
       <c r="D12" t="n">
-        <v>3102</v>
+        <v>2537</v>
       </c>
       <c r="E12" t="n">
-        <v>27849</v>
+        <v>-1183</v>
       </c>
       <c r="F12" t="n">
-        <v>-2478</v>
+        <v>-182</v>
       </c>
       <c r="G12" t="n">
-        <v>-14616</v>
+        <v>-1154</v>
       </c>
       <c r="H12" t="n">
-        <v>-101</v>
+        <v>2</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1018,15 +1018,15 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M12" t="n">
@@ -1036,31 +1036,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>946</v>
+        <v>-1418</v>
       </c>
       <c r="D13" t="n">
-        <v>3034</v>
+        <v>2461</v>
       </c>
       <c r="E13" t="n">
-        <v>1613</v>
+        <v>11511</v>
       </c>
       <c r="F13" t="n">
-        <v>-3</v>
+        <v>-147</v>
       </c>
       <c r="G13" t="n">
-        <v>-135</v>
+        <v>-9987</v>
       </c>
       <c r="H13" t="n">
-        <v>-744</v>
+        <v>-343</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1073,11 +1073,11 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M13" t="n">
@@ -1087,31 +1087,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>漢科</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>707</v>
+        <v>103</v>
       </c>
       <c r="D14" t="n">
-        <v>2828</v>
+        <v>2394</v>
       </c>
       <c r="E14" t="n">
-        <v>-1130</v>
+        <v>3299</v>
       </c>
       <c r="F14" t="n">
-        <v>-178</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>-1218</v>
+        <v>135</v>
       </c>
       <c r="H14" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1120,49 +1120,49 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-439</v>
+        <v>-1561</v>
       </c>
       <c r="D15" t="n">
-        <v>2725</v>
+        <v>2358</v>
       </c>
       <c r="E15" t="n">
-        <v>2852</v>
+        <v>13842</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G15" t="n">
-        <v>135</v>
+        <v>1186</v>
       </c>
       <c r="H15" t="n">
-        <v>14</v>
+        <v>-10</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1175,15 +1175,15 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器*</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1198,22 +1198,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>265</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
-        <v>2582</v>
+        <v>2113</v>
       </c>
       <c r="E16" t="n">
-        <v>3624</v>
+        <v>3454</v>
       </c>
       <c r="F16" t="n">
-        <v>-204</v>
+        <v>-137</v>
       </c>
       <c r="G16" t="n">
-        <v>-892</v>
+        <v>-998</v>
       </c>
       <c r="H16" t="n">
-        <v>-206</v>
+        <v>-268</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1249,22 +1249,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-630</v>
+        <v>-64</v>
       </c>
       <c r="D17" t="n">
-        <v>1861</v>
+        <v>1896</v>
       </c>
       <c r="E17" t="n">
-        <v>-6535</v>
+        <v>-6459</v>
       </c>
       <c r="F17" t="n">
-        <v>-425</v>
+        <v>-664</v>
       </c>
       <c r="G17" t="n">
-        <v>-304</v>
+        <v>274</v>
       </c>
       <c r="H17" t="n">
-        <v>-104</v>
+        <v>-217</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1291,31 +1291,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>805</v>
+        <v>1437</v>
       </c>
       <c r="D18" t="n">
-        <v>1413</v>
+        <v>1841</v>
       </c>
       <c r="E18" t="n">
-        <v>-6746</v>
+        <v>2020</v>
       </c>
       <c r="F18" t="n">
-        <v>-1096</v>
+        <v>-976</v>
       </c>
       <c r="G18" t="n">
-        <v>-6305</v>
+        <v>-980</v>
       </c>
       <c r="H18" t="n">
-        <v>-321</v>
+        <v>68</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1324,49 +1324,49 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>66</v>
+        <v>97</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>211</v>
+        <v>304</v>
       </c>
       <c r="D19" t="n">
-        <v>1342</v>
+        <v>1749</v>
       </c>
       <c r="E19" t="n">
-        <v>7196</v>
+        <v>2039</v>
       </c>
       <c r="F19" t="n">
-        <v>29</v>
+        <v>-265</v>
       </c>
       <c r="G19" t="n">
-        <v>5569</v>
+        <v>465</v>
       </c>
       <c r="H19" t="n">
-        <v>-69</v>
+        <v>-95</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1375,19 +1375,19 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1402,22 +1402,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>539</v>
       </c>
       <c r="D20" t="n">
-        <v>1274</v>
+        <v>1536</v>
       </c>
       <c r="E20" t="n">
-        <v>-252</v>
+        <v>135</v>
       </c>
       <c r="F20" t="n">
-        <v>-8</v>
+        <v>6</v>
       </c>
       <c r="G20" t="n">
         <v>-168</v>
       </c>
       <c r="H20" t="n">
-        <v>-41</v>
+        <v>11</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1453,22 +1453,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>459</v>
+        <v>356</v>
       </c>
       <c r="D21" t="n">
-        <v>1271</v>
+        <v>1428</v>
       </c>
       <c r="E21" t="n">
-        <v>3063</v>
+        <v>3196</v>
       </c>
       <c r="F21" t="n">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="G21" t="n">
-        <v>403</v>
+        <v>469</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1495,31 +1495,31 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2002</v>
+        <v>1318</v>
       </c>
       <c r="D22" t="n">
-        <v>1224</v>
+        <v>1424</v>
       </c>
       <c r="E22" t="n">
-        <v>-4923</v>
+        <v>-6645</v>
       </c>
       <c r="F22" t="n">
-        <v>-1196</v>
+        <v>-1299</v>
       </c>
       <c r="G22" t="n">
-        <v>2824</v>
+        <v>-6457</v>
       </c>
       <c r="H22" t="n">
-        <v>-987</v>
+        <v>-278</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1540,37 +1540,37 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>智易</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-614</v>
+        <v>240</v>
       </c>
       <c r="D23" t="n">
-        <v>1184</v>
+        <v>1322</v>
       </c>
       <c r="E23" t="n">
-        <v>1363</v>
+        <v>7286</v>
       </c>
       <c r="F23" t="n">
-        <v>250</v>
+        <v>25</v>
       </c>
       <c r="G23" t="n">
-        <v>-2255</v>
+        <v>5238</v>
       </c>
       <c r="H23" t="n">
-        <v>250</v>
+        <v>-54</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1583,45 +1583,45 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>立隆電</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1429</v>
+        <v>2795</v>
       </c>
       <c r="D24" t="n">
-        <v>945</v>
+        <v>1152</v>
       </c>
       <c r="E24" t="n">
-        <v>1672</v>
+        <v>-9948</v>
       </c>
       <c r="F24" t="n">
-        <v>-960</v>
+        <v>864</v>
       </c>
       <c r="G24" t="n">
-        <v>-939</v>
+        <v>8854</v>
       </c>
       <c r="H24" t="n">
-        <v>-157</v>
+        <v>-118</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1630,15 +1630,15 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M24" t="n">
@@ -1648,70 +1648,82 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-1301</v>
+        <v>489</v>
       </c>
       <c r="D25" t="n">
-        <v>916</v>
+        <v>792</v>
       </c>
       <c r="E25" t="n">
-        <v>-1797</v>
+        <v>355</v>
       </c>
       <c r="F25" t="n">
-        <v>-9</v>
+        <v>-154</v>
       </c>
       <c r="G25" t="n">
-        <v>-3700</v>
+        <v>-1414</v>
       </c>
       <c r="H25" t="n">
-        <v>-184</v>
+        <v>-147</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>66</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>586</v>
+        <v>-948</v>
       </c>
       <c r="D26" t="n">
-        <v>835</v>
+        <v>767</v>
       </c>
       <c r="E26" t="n">
-        <v>-1312</v>
+        <v>973</v>
       </c>
       <c r="F26" t="n">
-        <v>463</v>
+        <v>244</v>
       </c>
       <c r="G26" t="n">
-        <v>2371</v>
+        <v>-2236</v>
       </c>
       <c r="H26" t="n">
-        <v>-13</v>
+        <v>-30</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1720,49 +1732,49 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>勝一</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-689</v>
+        <v>278</v>
       </c>
       <c r="D27" t="n">
-        <v>720</v>
+        <v>712</v>
       </c>
       <c r="E27" t="n">
-        <v>1194</v>
+        <v>1765</v>
       </c>
       <c r="F27" t="n">
-        <v>22</v>
+        <v>-5</v>
       </c>
       <c r="G27" t="n">
-        <v>750</v>
+        <v>3</v>
       </c>
       <c r="H27" t="n">
-        <v>-163</v>
+        <v>-13</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1771,49 +1783,49 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1722</v>
+        <v>434</v>
       </c>
       <c r="D28" t="n">
-        <v>715</v>
+        <v>615</v>
       </c>
       <c r="E28" t="n">
-        <v>-669</v>
+        <v>-1318</v>
       </c>
       <c r="F28" t="n">
-        <v>-57</v>
+        <v>247</v>
       </c>
       <c r="G28" t="n">
-        <v>-926</v>
+        <v>2429</v>
       </c>
       <c r="H28" t="n">
-        <v>-131</v>
+        <v>-20</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1822,49 +1834,49 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>勝一</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-384</v>
+        <v>1146</v>
       </c>
       <c r="D29" t="n">
-        <v>698</v>
+        <v>527</v>
       </c>
       <c r="E29" t="n">
-        <v>1385</v>
+        <v>-904</v>
       </c>
       <c r="F29" t="n">
-        <v>-2</v>
+        <v>-325</v>
       </c>
       <c r="G29" t="n">
-        <v>6</v>
+        <v>-979</v>
       </c>
       <c r="H29" t="n">
-        <v>-13</v>
+        <v>-147</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1873,49 +1885,49 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>湧德</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>225</v>
+        <v>-662</v>
       </c>
       <c r="D30" t="n">
-        <v>547</v>
+        <v>466</v>
       </c>
       <c r="E30" t="n">
-        <v>1070</v>
+        <v>-3429</v>
       </c>
       <c r="F30" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>76</v>
+        <v>-207</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1924,11 +1936,11 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>32</v>
+        <v>94</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -1936,37 +1948,37 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>344</v>
+        <v>1434</v>
       </c>
       <c r="D31" t="n">
-        <v>505</v>
+        <v>436</v>
       </c>
       <c r="E31" t="n">
-        <v>252</v>
+        <v>-3971</v>
       </c>
       <c r="F31" t="n">
-        <v>-272</v>
+        <v>-1226</v>
       </c>
       <c r="G31" t="n">
-        <v>-1356</v>
+        <v>2390</v>
       </c>
       <c r="H31" t="n">
-        <v>-109</v>
+        <v>-1052</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1979,45 +1991,45 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-698</v>
+        <v>768</v>
       </c>
       <c r="D32" t="n">
-        <v>432</v>
+        <v>368</v>
       </c>
       <c r="E32" t="n">
-        <v>-3451</v>
+        <v>-6698</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>-346</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-3347</v>
       </c>
       <c r="H32" t="n">
-        <v>-95</v>
+        <v>-7</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2030,15 +2042,15 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
@@ -2053,13 +2065,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D33" t="n">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="E33" t="n">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -2095,70 +2107,82 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>90</v>
+        <v>240</v>
       </c>
       <c r="D34" t="n">
-        <v>320</v>
+        <v>349</v>
       </c>
       <c r="E34" t="n">
-        <v>840</v>
+        <v>1266</v>
       </c>
       <c r="F34" t="n">
-        <v>-293</v>
+        <v>-3</v>
       </c>
       <c r="G34" t="n">
-        <v>-543</v>
+        <v>7</v>
       </c>
       <c r="H34" t="n">
-        <v>-8</v>
+        <v>106</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>32</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>📉 減速</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>-3</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-331</v>
+        <v>1240</v>
       </c>
       <c r="D35" t="n">
-        <v>285</v>
+        <v>256</v>
       </c>
       <c r="E35" t="n">
-        <v>4531</v>
+        <v>-2557</v>
       </c>
       <c r="F35" t="n">
-        <v>385</v>
+        <v>-4</v>
       </c>
       <c r="G35" t="n">
-        <v>258</v>
+        <v>-423</v>
       </c>
       <c r="H35" t="n">
-        <v>155</v>
+        <v>12</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2171,96 +2195,84 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M35" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>-232</v>
+        <v>116</v>
       </c>
       <c r="D36" t="n">
-        <v>206</v>
+        <v>248</v>
       </c>
       <c r="E36" t="n">
-        <v>1159</v>
+        <v>789</v>
       </c>
       <c r="F36" t="n">
-        <v>-1</v>
+        <v>-180</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>-456</v>
       </c>
       <c r="H36" t="n">
-        <v>-96</v>
+        <v>-18</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K36" t="n">
-        <v>79</v>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>🛬 穩定</t>
-        </is>
-      </c>
-      <c r="M36" t="n">
-        <v>-1</v>
-      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1516</v>
+        <v>-82</v>
       </c>
       <c r="D37" t="n">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="E37" t="n">
-        <v>-2587</v>
+        <v>-125</v>
       </c>
       <c r="F37" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>-420</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>17</v>
+        <v>-12</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2269,11 +2281,11 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2281,88 +2293,76 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-161</v>
+        <v>893</v>
       </c>
       <c r="D38" t="n">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="E38" t="n">
-        <v>-175</v>
+        <v>-5563</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>392</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>-1175</v>
       </c>
       <c r="H38" t="n">
-        <v>3</v>
+        <v>-27</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K38" t="n">
-        <v>78</v>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>📉 減速</t>
-        </is>
-      </c>
-      <c r="M38" t="n">
-        <v>-3</v>
-      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>大統益</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-59</v>
+        <v>592</v>
       </c>
       <c r="D39" t="n">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="E39" t="n">
-        <v>-80</v>
+        <v>-227</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H39" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2371,15 +2371,15 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M39" t="n">
@@ -2389,31 +2389,31 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>六方科-KY</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>573</v>
+        <v>-66</v>
       </c>
       <c r="D40" t="n">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="E40" t="n">
-        <v>-211</v>
+        <v>-73</v>
       </c>
       <c r="F40" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2422,15 +2422,15 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M40" t="n">
@@ -2449,13 +2449,13 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-173</v>
+        <v>-126</v>
       </c>
       <c r="D41" t="n">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="E41" t="n">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -2464,7 +2464,7 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-54</v>
+        <v>-33</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2491,31 +2491,31 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>達欣工</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-176</v>
+        <v>-101</v>
       </c>
       <c r="D42" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E42" t="n">
-        <v>174</v>
+        <v>1160</v>
       </c>
       <c r="F42" t="n">
-        <v>259</v>
+        <v>-4</v>
       </c>
       <c r="G42" t="n">
-        <v>70</v>
+        <v>-2</v>
       </c>
       <c r="H42" t="n">
-        <v>30</v>
+        <v>-90</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2524,19 +2524,19 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M42" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="43">
@@ -2554,7 +2554,7 @@
         <v>-6</v>
       </c>
       <c r="D43" t="n">
-        <v>-17</v>
+        <v>-11</v>
       </c>
       <c r="E43" t="n">
         <v>-78</v>
@@ -2593,70 +2593,82 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>大車隊</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>296</v>
+        <v>-15</v>
       </c>
       <c r="D44" t="n">
-        <v>-31</v>
+        <v>-94</v>
       </c>
       <c r="E44" t="n">
-        <v>-5689</v>
+        <v>-295</v>
       </c>
       <c r="F44" t="n">
-        <v>310</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>-1188</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>-54</v>
+        <v>52</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>97</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>🛬 穩定</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>鑫龍騰</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>374</v>
+        <v>212</v>
       </c>
       <c r="D45" t="n">
-        <v>-52</v>
+        <v>-103</v>
       </c>
       <c r="E45" t="n">
-        <v>-6830</v>
+        <v>-2710</v>
       </c>
       <c r="F45" t="n">
-        <v>-769</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>-3791</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>-38</v>
+        <v>-0</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2665,11 +2677,11 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2677,37 +2689,37 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>友輝</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-1426</v>
+        <v>24</v>
       </c>
       <c r="D46" t="n">
-        <v>-96</v>
+        <v>-117</v>
       </c>
       <c r="E46" t="n">
-        <v>2443</v>
+        <v>1203</v>
       </c>
       <c r="F46" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>84</v>
+        <v>6</v>
       </c>
       <c r="H46" t="n">
-        <v>-202</v>
+        <v>-19</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2716,40 +2728,40 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M46" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>大車隊</t>
+          <t>信立</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-11</v>
+        <v>167</v>
       </c>
       <c r="D47" t="n">
-        <v>-131</v>
+        <v>-151</v>
       </c>
       <c r="E47" t="n">
-        <v>-296</v>
+        <v>-58</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -2758,7 +2770,7 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>52</v>
+        <v>-70</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2767,19 +2779,19 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M47" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -2794,22 +2806,22 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-4</v>
+        <v>-88</v>
       </c>
       <c r="D48" t="n">
-        <v>-172</v>
+        <v>-162</v>
       </c>
       <c r="E48" t="n">
-        <v>-137</v>
+        <v>-170</v>
       </c>
       <c r="F48" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G48" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H48" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2836,22 +2848,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>鑫龍騰</t>
+          <t>聯合</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>160</v>
+        <v>-28</v>
       </c>
       <c r="D49" t="n">
-        <v>-209</v>
+        <v>-165</v>
       </c>
       <c r="E49" t="n">
-        <v>-2733</v>
+        <v>-2992</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -2860,7 +2872,7 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2869,11 +2881,11 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -2887,31 +2899,31 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-235</v>
+        <v>-290</v>
       </c>
       <c r="D50" t="n">
-        <v>-231</v>
+        <v>-191</v>
       </c>
       <c r="E50" t="n">
-        <v>-1127</v>
+        <v>65</v>
       </c>
       <c r="F50" t="n">
-        <v>-4</v>
+        <v>235</v>
       </c>
       <c r="G50" t="n">
-        <v>242</v>
+        <v>340</v>
       </c>
       <c r="H50" t="n">
-        <v>-7</v>
+        <v>-0</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2924,45 +2936,45 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>🐌 龜速*</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M50" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-224</v>
+        <v>113</v>
       </c>
       <c r="D51" t="n">
-        <v>-236</v>
+        <v>-235</v>
       </c>
       <c r="E51" t="n">
-        <v>-252</v>
+        <v>-282</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>-108</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>-147</v>
       </c>
       <c r="H51" t="n">
-        <v>-4</v>
+        <v>-26</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -2971,40 +2983,40 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>聯合</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-19</v>
+        <v>45</v>
       </c>
       <c r="D52" t="n">
-        <v>-258</v>
+        <v>-260</v>
       </c>
       <c r="E52" t="n">
-        <v>-3002</v>
+        <v>-227</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -3013,7 +3025,7 @@
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>97</v>
+        <v>-30</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3022,91 +3034,91 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-1478</v>
+        <v>-170</v>
       </c>
       <c r="D53" t="n">
-        <v>-292</v>
+        <v>-328</v>
       </c>
       <c r="E53" t="n">
-        <v>5771</v>
+        <v>-1079</v>
       </c>
       <c r="F53" t="n">
+        <v>-4</v>
+      </c>
+      <c r="G53" t="n">
+        <v>242</v>
+      </c>
+      <c r="H53" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>94</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>🐌 龜速*</t>
+        </is>
+      </c>
+      <c r="M53" t="n">
         <v>-1</v>
-      </c>
-      <c r="G53" t="n">
-        <v>-5</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-2</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K53" t="n">
-        <v>75</v>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>🐌 龜速</t>
-        </is>
-      </c>
-      <c r="M53" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>德昌</t>
+          <t>合機</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-957</v>
+        <v>-1359</v>
       </c>
       <c r="D54" t="n">
-        <v>-306</v>
+        <v>-383</v>
       </c>
       <c r="E54" t="n">
-        <v>-207</v>
+        <v>1975</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -3115,7 +3127,7 @@
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-19</v>
+        <v>-66</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3124,11 +3136,11 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K54" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -3142,31 +3154,31 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>-2</v>
+        <v>-40</v>
       </c>
       <c r="D55" t="n">
-        <v>-327</v>
+        <v>-418</v>
       </c>
       <c r="E55" t="n">
-        <v>-294</v>
+        <v>4476</v>
       </c>
       <c r="F55" t="n">
-        <v>-59</v>
+        <v>392</v>
       </c>
       <c r="G55" t="n">
-        <v>-130</v>
+        <v>396</v>
       </c>
       <c r="H55" t="n">
-        <v>-24</v>
+        <v>131</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3179,45 +3191,45 @@
         </is>
       </c>
       <c r="K55" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-26</v>
+        <v>772</v>
       </c>
       <c r="D56" t="n">
-        <v>-355</v>
+        <v>-465</v>
       </c>
       <c r="E56" t="n">
-        <v>1198</v>
+        <v>-4449</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-20</v>
+        <v>-14</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3226,49 +3238,49 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K56" t="n">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M56" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>358</v>
+        <v>3553</v>
       </c>
       <c r="D57" t="n">
-        <v>-362</v>
+        <v>-591</v>
       </c>
       <c r="E57" t="n">
-        <v>-4664</v>
+        <v>-57843</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>5691</v>
       </c>
       <c r="H57" t="n">
-        <v>-28</v>
+        <v>-117</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3277,40 +3289,40 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K57" t="n">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>54</v>
+        <v>-269</v>
       </c>
       <c r="D58" t="n">
-        <v>-460</v>
+        <v>-597</v>
       </c>
       <c r="E58" t="n">
-        <v>-250</v>
+        <v>-1891</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -3319,7 +3331,7 @@
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-18</v>
+        <v>0</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3332,45 +3344,45 @@
         </is>
       </c>
       <c r="K58" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M58" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>合機</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>-1562</v>
+        <v>-879</v>
       </c>
       <c r="D59" t="n">
-        <v>-499</v>
+        <v>-636</v>
       </c>
       <c r="E59" t="n">
-        <v>1927</v>
+        <v>2392</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="H59" t="n">
-        <v>-84</v>
+        <v>-323</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3383,36 +3395,36 @@
         </is>
       </c>
       <c r="K59" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M59" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>德昌</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>-291</v>
+        <v>-928</v>
       </c>
       <c r="D60" t="n">
-        <v>-622</v>
+        <v>-647</v>
       </c>
       <c r="E60" t="n">
-        <v>-1868</v>
+        <v>-257</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -3421,7 +3433,7 @@
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>12</v>
+        <v>-21</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3434,87 +3446,75 @@
         </is>
       </c>
       <c r="K60" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M60" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>寶雅</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-488</v>
+        <v>-1387</v>
       </c>
       <c r="D61" t="n">
-        <v>-665</v>
+        <v>-710</v>
       </c>
       <c r="E61" t="n">
-        <v>243</v>
+        <v>-2053</v>
       </c>
       <c r="F61" t="n">
-        <v>58</v>
+        <v>-9</v>
       </c>
       <c r="G61" t="n">
-        <v>102</v>
+        <v>-2649</v>
       </c>
       <c r="H61" t="n">
-        <v>12</v>
+        <v>-188</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K61" t="n">
-        <v>92</v>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>🛬 穩定</t>
-        </is>
-      </c>
-      <c r="M61" t="n">
-        <v>-1</v>
-      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>87</v>
+        <v>-987</v>
       </c>
       <c r="D62" t="n">
-        <v>-754</v>
+        <v>-729</v>
       </c>
       <c r="E62" t="n">
-        <v>2176</v>
+        <v>-6261</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -3523,7 +3523,7 @@
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>151</v>
+        <v>1747</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3536,11 +3536,11 @@
         </is>
       </c>
       <c r="K62" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M62" t="n">
@@ -3559,22 +3559,22 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-157</v>
+        <v>-119</v>
       </c>
       <c r="D63" t="n">
-        <v>-887</v>
+        <v>-731</v>
       </c>
       <c r="E63" t="n">
-        <v>-2991</v>
+        <v>-2966</v>
       </c>
       <c r="F63" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G63" t="n">
-        <v>-108</v>
+        <v>-111</v>
       </c>
       <c r="H63" t="n">
-        <v>-113</v>
+        <v>-139</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3601,22 +3601,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>億泰</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>-475</v>
+        <v>152</v>
       </c>
       <c r="D64" t="n">
-        <v>-888</v>
+        <v>-864</v>
       </c>
       <c r="E64" t="n">
-        <v>-2712</v>
+        <v>2222</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -3625,7 +3625,7 @@
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3638,15 +3638,15 @@
         </is>
       </c>
       <c r="K64" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M64" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="65">
@@ -3661,22 +3661,22 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-498</v>
+        <v>-580</v>
       </c>
       <c r="D65" t="n">
-        <v>-891</v>
+        <v>-901</v>
       </c>
       <c r="E65" t="n">
-        <v>-1443</v>
+        <v>-1550</v>
       </c>
       <c r="F65" t="n">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="G65" t="n">
-        <v>943</v>
+        <v>971</v>
       </c>
       <c r="H65" t="n">
-        <v>-63</v>
+        <v>-54</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3703,31 +3703,31 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>億泰</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>6474</v>
+        <v>-169</v>
       </c>
       <c r="D66" t="n">
-        <v>-1040</v>
+        <v>-928</v>
       </c>
       <c r="E66" t="n">
-        <v>-9019</v>
+        <v>-2683</v>
       </c>
       <c r="F66" t="n">
-        <v>806</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>8841</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-184</v>
+        <v>-210</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3740,45 +3740,45 @@
         </is>
       </c>
       <c r="K66" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M66" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>寶雅</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-1497</v>
+        <v>-783</v>
       </c>
       <c r="D67" t="n">
-        <v>-1638</v>
+        <v>-1004</v>
       </c>
       <c r="E67" t="n">
-        <v>-2326</v>
+        <v>-96</v>
       </c>
       <c r="F67" t="n">
-        <v>-52</v>
+        <v>82</v>
       </c>
       <c r="G67" t="n">
-        <v>-55</v>
+        <v>116</v>
       </c>
       <c r="H67" t="n">
-        <v>-251</v>
+        <v>20</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3791,45 +3791,45 @@
         </is>
       </c>
       <c r="K67" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M67" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-148</v>
+        <v>-1471</v>
       </c>
       <c r="D68" t="n">
-        <v>-1807</v>
+        <v>-1523</v>
       </c>
       <c r="E68" t="n">
-        <v>-12947</v>
+        <v>-2784</v>
       </c>
       <c r="F68" t="n">
-        <v>85</v>
+        <v>-54</v>
       </c>
       <c r="G68" t="n">
-        <v>5112</v>
+        <v>-55</v>
       </c>
       <c r="H68" t="n">
-        <v>7</v>
+        <v>-209</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3838,104 +3838,104 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K68" t="n">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M68" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-244</v>
+        <v>-1280</v>
       </c>
       <c r="D69" t="n">
-        <v>-1861</v>
+        <v>-1799</v>
       </c>
       <c r="E69" t="n">
-        <v>3910</v>
+        <v>-2860</v>
       </c>
       <c r="F69" t="n">
+        <v>232</v>
+      </c>
+      <c r="G69" t="n">
+        <v>376</v>
+      </c>
+      <c r="H69" t="n">
+        <v>-420</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>90</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M69" t="n">
         <v>-1</v>
-      </c>
-      <c r="G69" t="n">
-        <v>444</v>
-      </c>
-      <c r="H69" t="n">
-        <v>-742</v>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K69" t="n">
-        <v>64</v>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>🐌 龜速</t>
-        </is>
-      </c>
-      <c r="M69" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>全友</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>710</v>
+        <v>-2975</v>
       </c>
       <c r="D70" t="n">
-        <v>-2133</v>
+        <v>-1819</v>
       </c>
       <c r="E70" t="n">
-        <v>-6496</v>
+        <v>4147</v>
       </c>
       <c r="F70" t="n">
-        <v>1214</v>
+        <v>-1</v>
       </c>
       <c r="G70" t="n">
-        <v>-822</v>
+        <v>-5</v>
       </c>
       <c r="H70" t="n">
-        <v>-1304</v>
+        <v>-14</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🟡 中性</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -3944,7 +3944,7 @@
         </is>
       </c>
       <c r="K70" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -3952,37 +3952,37 @@
         </is>
       </c>
       <c r="M70" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-5309</v>
+        <v>-1828</v>
       </c>
       <c r="D71" t="n">
-        <v>-2220</v>
+        <v>-2083</v>
       </c>
       <c r="E71" t="n">
-        <v>-12274</v>
+        <v>2487</v>
       </c>
       <c r="F71" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="G71" t="n">
-        <v>-7</v>
+        <v>444</v>
       </c>
       <c r="H71" t="n">
-        <v>-170</v>
+        <v>-656</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -3991,49 +3991,49 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K71" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M71" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>鈊象</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2786</v>
+        <v>-643</v>
       </c>
       <c r="D72" t="n">
-        <v>-2377</v>
+        <v>-2161</v>
       </c>
       <c r="E72" t="n">
-        <v>-58668</v>
+        <v>-13606</v>
       </c>
       <c r="F72" t="n">
-        <v>279</v>
+        <v>-214</v>
       </c>
       <c r="G72" t="n">
-        <v>6801</v>
+        <v>5069</v>
       </c>
       <c r="H72" t="n">
-        <v>-226</v>
+        <v>95</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -4042,49 +4042,49 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K72" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M72" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-2094</v>
+        <v>-821</v>
       </c>
       <c r="D73" t="n">
-        <v>-2395</v>
+        <v>-2468</v>
       </c>
       <c r="E73" t="n">
-        <v>-8237</v>
+        <v>-8714</v>
       </c>
       <c r="F73" t="n">
-        <v>241</v>
+        <v>5</v>
       </c>
       <c r="G73" t="n">
-        <v>-11763</v>
+        <v>90</v>
       </c>
       <c r="H73" t="n">
-        <v>-1163</v>
+        <v>-571</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -4093,49 +4093,49 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K73" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M73" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>-1786</v>
+        <v>-5084</v>
       </c>
       <c r="D74" t="n">
-        <v>-2413</v>
+        <v>-2486</v>
       </c>
       <c r="E74" t="n">
-        <v>-3169</v>
+        <v>-13041</v>
       </c>
       <c r="F74" t="n">
-        <v>355</v>
+        <v>-1</v>
       </c>
       <c r="G74" t="n">
-        <v>380</v>
+        <v>-7</v>
       </c>
       <c r="H74" t="n">
-        <v>-417</v>
+        <v>-136</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -4144,49 +4144,49 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K74" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M74" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>玉晶光</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>-1095</v>
+        <v>-698</v>
       </c>
       <c r="D75" t="n">
-        <v>-2479</v>
+        <v>-2698</v>
       </c>
       <c r="E75" t="n">
-        <v>-8412</v>
+        <v>-939</v>
       </c>
       <c r="F75" t="n">
-        <v>4</v>
+        <v>101</v>
       </c>
       <c r="G75" t="n">
-        <v>89</v>
+        <v>-1499</v>
       </c>
       <c r="H75" t="n">
-        <v>-563</v>
+        <v>-498</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -4199,45 +4199,45 @@
         </is>
       </c>
       <c r="K75" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M75" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-172</v>
+        <v>-1982</v>
       </c>
       <c r="D76" t="n">
-        <v>-2559</v>
+        <v>-3399</v>
       </c>
       <c r="E76" t="n">
-        <v>-618</v>
+        <v>-2846</v>
       </c>
       <c r="F76" t="n">
-        <v>249</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>-1464</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-251</v>
+        <v>338</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -4246,11 +4246,11 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K76" t="n">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -4258,37 +4258,37 @@
         </is>
       </c>
       <c r="M76" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-2433</v>
+        <v>-885</v>
       </c>
       <c r="D77" t="n">
-        <v>-3147</v>
+        <v>-3485</v>
       </c>
       <c r="E77" t="n">
-        <v>-2528</v>
+        <v>-3844</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>-203</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>-307</v>
       </c>
       <c r="H77" t="n">
-        <v>368</v>
+        <v>52</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -4297,49 +4297,49 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K77" t="n">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M77" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-933</v>
+        <v>-53</v>
       </c>
       <c r="D78" t="n">
-        <v>-3292</v>
+        <v>-3610</v>
       </c>
       <c r="E78" t="n">
-        <v>-946</v>
+        <v>-4469</v>
       </c>
       <c r="F78" t="n">
-        <v>230</v>
+        <v>-436</v>
       </c>
       <c r="G78" t="n">
-        <v>175</v>
+        <v>2182</v>
       </c>
       <c r="H78" t="n">
-        <v>247</v>
+        <v>-441</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -4352,96 +4352,96 @@
         </is>
       </c>
       <c r="K78" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M78" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-906</v>
+        <v>-182</v>
       </c>
       <c r="D79" t="n">
-        <v>-3446</v>
+        <v>-3842</v>
       </c>
       <c r="E79" t="n">
-        <v>-3829</v>
+        <v>-12792</v>
       </c>
       <c r="F79" t="n">
+        <v>-16</v>
+      </c>
+      <c r="G79" t="n">
+        <v>-929</v>
+      </c>
+      <c r="H79" t="n">
+        <v>-165</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>🟠 減碼</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>89</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>🚀 加速器</t>
+        </is>
+      </c>
+      <c r="M79" t="n">
         <v>-2</v>
-      </c>
-      <c r="G79" t="n">
-        <v>-140</v>
-      </c>
-      <c r="H79" t="n">
-        <v>51</v>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>🟠 減碼</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K79" t="n">
-        <v>64</v>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>🚀 加速器</t>
-        </is>
-      </c>
-      <c r="M79" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>-1560</v>
+        <v>-846</v>
       </c>
       <c r="D80" t="n">
-        <v>-3684</v>
+        <v>-4078</v>
       </c>
       <c r="E80" t="n">
-        <v>-5144</v>
+        <v>-14854</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>269</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>674</v>
       </c>
       <c r="H80" t="n">
-        <v>-568</v>
+        <v>1</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -4450,19 +4450,19 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K80" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M80" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="81">
@@ -4477,22 +4477,22 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-1772</v>
+        <v>-1230</v>
       </c>
       <c r="D81" t="n">
-        <v>-3946</v>
+        <v>-4153</v>
       </c>
       <c r="E81" t="n">
-        <v>-7330</v>
+        <v>-7617</v>
       </c>
       <c r="F81" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G81" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="H81" t="n">
-        <v>-426</v>
+        <v>-263</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4519,31 +4519,31 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>39</v>
+        <v>-2315</v>
       </c>
       <c r="D82" t="n">
-        <v>-3970</v>
+        <v>-4191</v>
       </c>
       <c r="E82" t="n">
-        <v>-4408</v>
+        <v>-2060</v>
       </c>
       <c r="F82" t="n">
-        <v>-171</v>
+        <v>398</v>
       </c>
       <c r="G82" t="n">
-        <v>2380</v>
+        <v>34</v>
       </c>
       <c r="H82" t="n">
-        <v>-343</v>
+        <v>222</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -4556,45 +4556,45 @@
         </is>
       </c>
       <c r="K82" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M82" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-2296</v>
+        <v>-590</v>
       </c>
       <c r="D83" t="n">
-        <v>-4295</v>
+        <v>-4238</v>
       </c>
       <c r="E83" t="n">
-        <v>-3575</v>
+        <v>-6831</v>
       </c>
       <c r="F83" t="n">
-        <v>2443</v>
+        <v>911</v>
       </c>
       <c r="G83" t="n">
-        <v>6647</v>
+        <v>3010</v>
       </c>
       <c r="H83" t="n">
-        <v>7</v>
+        <v>-92</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -4603,49 +4603,49 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K83" t="n">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M83" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-419</v>
+        <v>624</v>
       </c>
       <c r="D84" t="n">
-        <v>-4362</v>
+        <v>-4465</v>
       </c>
       <c r="E84" t="n">
-        <v>-6877</v>
+        <v>-11639</v>
       </c>
       <c r="F84" t="n">
-        <v>1264</v>
+        <v>-2</v>
       </c>
       <c r="G84" t="n">
-        <v>2617</v>
+        <v>-217</v>
       </c>
       <c r="H84" t="n">
-        <v>-165</v>
+        <v>-452</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -4658,45 +4658,45 @@
         </is>
       </c>
       <c r="K84" t="n">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M84" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>-1097</v>
+        <v>254</v>
       </c>
       <c r="D85" t="n">
-        <v>-4627</v>
+        <v>-4522</v>
       </c>
       <c r="E85" t="n">
-        <v>-13064</v>
+        <v>-5032</v>
       </c>
       <c r="F85" t="n">
-        <v>-7</v>
+        <v>353</v>
       </c>
       <c r="G85" t="n">
-        <v>-914</v>
+        <v>895</v>
       </c>
       <c r="H85" t="n">
-        <v>-179</v>
+        <v>-102</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -4705,15 +4705,15 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K85" t="n">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M85" t="n">
@@ -4723,31 +4723,31 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-247</v>
+        <v>-583</v>
       </c>
       <c r="D86" t="n">
-        <v>-4684</v>
+        <v>-4564</v>
       </c>
       <c r="E86" t="n">
-        <v>-11628</v>
+        <v>-5407</v>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G86" t="n">
-        <v>-215</v>
+        <v>-0</v>
       </c>
       <c r="H86" t="n">
-        <v>-459</v>
+        <v>-593</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -4756,49 +4756,49 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K86" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M86" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>-1437</v>
+        <v>-1641</v>
       </c>
       <c r="D87" t="n">
-        <v>-5054</v>
+        <v>-4695</v>
       </c>
       <c r="E87" t="n">
-        <v>-6859</v>
+        <v>-3681</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>1820</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>6887</v>
       </c>
       <c r="H87" t="n">
-        <v>1620</v>
+        <v>35</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -4807,15 +4807,15 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K87" t="n">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M87" t="n">
@@ -4825,31 +4825,31 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>-1966</v>
+        <v>-3617</v>
       </c>
       <c r="D88" t="n">
-        <v>-5118</v>
+        <v>-5166</v>
       </c>
       <c r="E88" t="n">
-        <v>-15240</v>
+        <v>-9548</v>
       </c>
       <c r="F88" t="n">
-        <v>368</v>
+        <v>166</v>
       </c>
       <c r="G88" t="n">
-        <v>674</v>
+        <v>-12068</v>
       </c>
       <c r="H88" t="n">
-        <v>-19</v>
+        <v>-53</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -4858,49 +4858,49 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K88" t="n">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M88" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-136</v>
+        <v>-3145</v>
       </c>
       <c r="D89" t="n">
-        <v>-5196</v>
+        <v>-5385</v>
       </c>
       <c r="E89" t="n">
-        <v>-5155</v>
+        <v>-8404</v>
       </c>
       <c r="F89" t="n">
-        <v>269</v>
+        <v>456</v>
       </c>
       <c r="G89" t="n">
-        <v>831</v>
+        <v>5124</v>
       </c>
       <c r="H89" t="n">
-        <v>-91</v>
+        <v>-1003</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4909,49 +4909,49 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K89" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M89" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>13691</v>
+        <v>1175</v>
       </c>
       <c r="D90" t="n">
-        <v>-7136</v>
+        <v>-6012</v>
       </c>
       <c r="E90" t="n">
-        <v>-76255</v>
+        <v>-6482</v>
       </c>
       <c r="F90" t="n">
-        <v>-10457</v>
+        <v>919</v>
       </c>
       <c r="G90" t="n">
-        <v>-357</v>
+        <v>-887</v>
       </c>
       <c r="H90" t="n">
-        <v>-6575</v>
+        <v>-1218</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -4960,70 +4960,70 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K90" t="n">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>-4456</v>
+        <v>-1581</v>
       </c>
       <c r="D91" t="n">
-        <v>-8241</v>
+        <v>-11734</v>
       </c>
       <c r="E91" t="n">
-        <v>-8361</v>
+        <v>-84242</v>
       </c>
       <c r="F91" t="n">
-        <v>880</v>
+        <v>-9607</v>
       </c>
       <c r="G91" t="n">
-        <v>5151</v>
+        <v>-3432</v>
       </c>
       <c r="H91" t="n">
-        <v>-1333</v>
+        <v>-6551</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🔴 大賣</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K91" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M91" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -5038,22 +5038,22 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>25203</v>
+        <v>36046</v>
       </c>
       <c r="D92" t="n">
-        <v>-12221</v>
+        <v>-13876</v>
       </c>
       <c r="E92" t="n">
-        <v>25440</v>
+        <v>28025</v>
       </c>
       <c r="F92" t="n">
-        <v>6609</v>
+        <v>1489</v>
       </c>
       <c r="G92" t="n">
-        <v>40301</v>
+        <v>39198</v>
       </c>
       <c r="H92" t="n">
-        <v>1244</v>
+        <v>1024</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -5089,22 +5089,22 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>-3032</v>
+        <v>-2778</v>
       </c>
       <c r="D93" t="n">
-        <v>-12274</v>
+        <v>-14069</v>
       </c>
       <c r="E93" t="n">
-        <v>-26990</v>
+        <v>-27278</v>
       </c>
       <c r="F93" t="n">
-        <v>1804</v>
+        <v>1006</v>
       </c>
       <c r="G93" t="n">
-        <v>10564</v>
+        <v>9963</v>
       </c>
       <c r="H93" t="n">
-        <v>504</v>
+        <v>672</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -5140,22 +5140,22 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-1165</v>
+        <v>1037</v>
       </c>
       <c r="D94" t="n">
-        <v>-19539</v>
+        <v>-18808</v>
       </c>
       <c r="E94" t="n">
-        <v>-34906</v>
+        <v>-34163</v>
       </c>
       <c r="F94" t="n">
-        <v>37</v>
+        <v>-116</v>
       </c>
       <c r="G94" t="n">
-        <v>22959</v>
+        <v>22837</v>
       </c>
       <c r="H94" t="n">
-        <v>-515</v>
+        <v>535</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -5191,22 +5191,22 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>-5272</v>
+        <v>-3479</v>
       </c>
       <c r="D95" t="n">
-        <v>-19716</v>
+        <v>-20982</v>
       </c>
       <c r="E95" t="n">
-        <v>-28951</v>
+        <v>-28423</v>
       </c>
       <c r="F95" t="n">
-        <v>579</v>
+        <v>569</v>
       </c>
       <c r="G95" t="n">
-        <v>-11210</v>
+        <v>-10299</v>
       </c>
       <c r="H95" t="n">
-        <v>-2145</v>
+        <v>-2078</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -5242,22 +5242,22 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>-5763</v>
+        <v>-8743</v>
       </c>
       <c r="D96" t="n">
-        <v>-23090</v>
+        <v>-28557</v>
       </c>
       <c r="E96" t="n">
-        <v>-1108</v>
+        <v>-3433</v>
       </c>
       <c r="F96" t="n">
-        <v>-23</v>
+        <v>192</v>
       </c>
       <c r="G96" t="n">
-        <v>12726</v>
+        <v>12074</v>
       </c>
       <c r="H96" t="n">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -5293,22 +5293,22 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>-18618</v>
+        <v>-18245</v>
       </c>
       <c r="D97" t="n">
-        <v>-33392</v>
+        <v>-36449</v>
       </c>
       <c r="E97" t="n">
-        <v>-285453</v>
+        <v>-290072</v>
       </c>
       <c r="F97" t="n">
-        <v>10323</v>
+        <v>10513</v>
       </c>
       <c r="G97" t="n">
-        <v>39367</v>
+        <v>40043</v>
       </c>
       <c r="H97" t="n">
-        <v>2548</v>
+        <v>1477</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -5335,31 +5335,31 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-19667</v>
+        <v>-34707</v>
       </c>
       <c r="D98" t="n">
-        <v>-38905</v>
+        <v>-58910</v>
       </c>
       <c r="E98" t="n">
-        <v>125897</v>
+        <v>36348</v>
       </c>
       <c r="F98" t="n">
-        <v>6314</v>
+        <v>14577</v>
       </c>
       <c r="G98" t="n">
-        <v>68100</v>
+        <v>48384</v>
       </c>
       <c r="H98" t="n">
-        <v>-2139</v>
+        <v>13275</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -5368,11 +5368,11 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K98" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -5380,37 +5380,37 @@
         </is>
       </c>
       <c r="M98" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>-39841</v>
+        <v>-11511</v>
       </c>
       <c r="D99" t="n">
-        <v>-59452</v>
+        <v>-80992</v>
       </c>
       <c r="E99" t="n">
-        <v>36228</v>
+        <v>130747</v>
       </c>
       <c r="F99" t="n">
-        <v>19723</v>
+        <v>12279</v>
       </c>
       <c r="G99" t="n">
-        <v>48673</v>
+        <v>67715</v>
       </c>
       <c r="H99" t="n">
-        <v>15483</v>
+        <v>258</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -5419,11 +5419,11 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K99" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100">
@@ -5446,22 +5446,22 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>-20365</v>
+        <v>-9387</v>
       </c>
       <c r="D100" t="n">
-        <v>-89990</v>
+        <v>-93191</v>
       </c>
       <c r="E100" t="n">
-        <v>-138134</v>
+        <v>-138516</v>
       </c>
       <c r="F100" t="n">
-        <v>6051</v>
+        <v>1870</v>
       </c>
       <c r="G100" t="n">
-        <v>33285</v>
+        <v>32517</v>
       </c>
       <c r="H100" t="n">
-        <v>-8994</v>
+        <v>-9120</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -5497,22 +5497,22 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-31282</v>
+        <v>-34792</v>
       </c>
       <c r="D101" t="n">
-        <v>-104198</v>
+        <v>-107243</v>
       </c>
       <c r="E101" t="n">
-        <v>-245925</v>
+        <v>-249352</v>
       </c>
       <c r="F101" t="n">
-        <v>3683</v>
+        <v>2548</v>
       </c>
       <c r="G101" t="n">
-        <v>8721</v>
+        <v>4275</v>
       </c>
       <c r="H101" t="n">
-        <v>10804</v>
+        <v>11417</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -5548,22 +5548,22 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>-1831</v>
+        <v>6681</v>
       </c>
       <c r="D102" t="n">
-        <v>-153464</v>
+        <v>-157924</v>
       </c>
       <c r="E102" t="n">
-        <v>-171829</v>
+        <v>-170816</v>
       </c>
       <c r="F102" t="n">
-        <v>12800</v>
+        <v>5154</v>
       </c>
       <c r="G102" t="n">
-        <v>148168</v>
+        <v>149886</v>
       </c>
       <c r="H102" t="n">
-        <v>3713</v>
+        <v>3812</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -5599,22 +5599,22 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>-13780</v>
+        <v>-3140</v>
       </c>
       <c r="D103" t="n">
-        <v>-196512</v>
+        <v>-185608</v>
       </c>
       <c r="E103" t="n">
-        <v>-107885</v>
+        <v>-105995</v>
       </c>
       <c r="F103" t="n">
-        <v>3378</v>
+        <v>-952</v>
       </c>
       <c r="G103" t="n">
-        <v>73422</v>
+        <v>72862</v>
       </c>
       <c r="H103" t="n">
-        <v>-4652</v>
+        <v>-4138</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -5650,22 +5650,22 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>-21100</v>
+        <v>3714</v>
       </c>
       <c r="D104" t="n">
-        <v>-214915</v>
+        <v>-217678</v>
       </c>
       <c r="E104" t="n">
-        <v>346952</v>
+        <v>353832</v>
       </c>
       <c r="F104" t="n">
-        <v>4186</v>
+        <v>1542</v>
       </c>
       <c r="G104" t="n">
-        <v>7457</v>
+        <v>7096</v>
       </c>
       <c r="H104" t="n">
-        <v>-2314</v>
+        <v>-1945</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -5701,22 +5701,22 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>-9394</v>
+        <v>-1099</v>
       </c>
       <c r="D105" t="n">
-        <v>-277368</v>
+        <v>-297527</v>
       </c>
       <c r="E105" t="n">
-        <v>-16677</v>
+        <v>-1731</v>
       </c>
       <c r="F105" t="n">
-        <v>-20122</v>
+        <v>-13189</v>
       </c>
       <c r="G105" t="n">
-        <v>104240</v>
+        <v>96253</v>
       </c>
       <c r="H105" t="n">
-        <v>-892</v>
+        <v>-382</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -5751,7 +5751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5794,87 +5794,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -3,533 千股)</t>
+          <t>📉 20d 巨變(減碼 -291 千股)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-4456287</v>
+        <v>600660</v>
       </c>
       <c r="D2" t="n">
-        <v>-8241230</v>
+        <v>2537419</v>
       </c>
       <c r="E2" t="n">
-        <v>-4835084</v>
+        <v>706964</v>
       </c>
       <c r="F2" t="n">
-        <v>-4708503</v>
+        <v>2828466</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>健策</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 256 千股)</t>
+          <t>📈 20d 巨變(加碼 2,856 千股)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>265140</v>
+        <v>-3144712</v>
       </c>
       <c r="D3" t="n">
-        <v>2582206</v>
+        <v>-5385312</v>
       </c>
       <c r="E3" t="n">
-        <v>111432</v>
+        <v>-4456287</v>
       </c>
       <c r="F3" t="n">
-        <v>2326367</v>
+        <v>-8241230</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>亞翔</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 606 千股)</t>
+          <t>📉 20d 巨變(減碼 -703 千股)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>373899</v>
+        <v>-40062</v>
       </c>
       <c r="D4" t="n">
-        <v>-51936</v>
+        <v>-418276</v>
       </c>
       <c r="E4" t="n">
-        <v>38111</v>
+        <v>-331149</v>
       </c>
       <c r="F4" t="n">
-        <v>-657575</v>
+        <v>285198</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>台光電</t>
         </is>
       </c>
     </row>
@@ -5886,20 +5886,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 281 千股)</t>
+          <t>📈 20d 巨變(加碼 35 千股)</t>
         </is>
       </c>
       <c r="C5" t="n">
+        <v>-63563</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1896320</v>
+      </c>
+      <c r="E5" t="n">
         <v>-629868</v>
       </c>
-      <c r="D5" t="n">
+      <c r="F5" t="n">
         <v>1860939</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-1260480</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1579726</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -5910,58 +5910,58 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -13 千股)</t>
+          <t>📈 20d 巨變(加碼 420 千股)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>706964</v>
+        <v>768195</v>
       </c>
       <c r="D6" t="n">
-        <v>2828466</v>
+        <v>368366</v>
       </c>
       <c r="E6" t="n">
-        <v>344513</v>
+        <v>373899</v>
       </c>
       <c r="F6" t="n">
-        <v>2841187</v>
+        <v>-51936</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>勤誠</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -505 千股)</t>
+          <t>📉 20d 巨變(減碼 -469 千股)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-331149</v>
+        <v>41794</v>
       </c>
       <c r="D7" t="n">
-        <v>285198</v>
+        <v>2113080</v>
       </c>
       <c r="E7" t="n">
-        <v>-1882397</v>
+        <v>265140</v>
       </c>
       <c r="F7" t="n">
-        <v>790433</v>
+        <v>2582206</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>高力</t>
         </is>
       </c>
     </row>
@@ -5973,20 +5973,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 899 千股)</t>
+          <t>📉 20d 巨變(減碼 -188 千股)</t>
         </is>
       </c>
       <c r="C8" t="n">
+        <v>1145813</v>
+      </c>
+      <c r="D8" t="n">
+        <v>526605</v>
+      </c>
+      <c r="E8" t="n">
         <v>1722469</v>
       </c>
-      <c r="D8" t="n">
+      <c r="F8" t="n">
         <v>714824</v>
-      </c>
-      <c r="E8" t="n">
-        <v>817238</v>
-      </c>
-      <c r="F8" t="n">
-        <v>-184455</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -6002,20 +6002,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 454 千股)</t>
+          <t>📉 20d 巨變(減碼 -883 千股)</t>
         </is>
       </c>
       <c r="C9" t="n">
+        <v>2562370</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5626073</v>
+      </c>
+      <c r="E9" t="n">
         <v>2595025</v>
       </c>
-      <c r="D9" t="n">
+      <c r="F9" t="n">
         <v>6508636</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2030702</v>
-      </c>
-      <c r="F9" t="n">
-        <v>6054926</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -6026,145 +6026,145 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -318 千股)</t>
+          <t>📉 20d 巨變(減碼 -540 千股)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-1771843</v>
+        <v>-879318</v>
       </c>
       <c r="D10" t="n">
-        <v>-3945715</v>
+        <v>-636134</v>
       </c>
       <c r="E10" t="n">
-        <v>-1779018</v>
+        <v>-1426377</v>
       </c>
       <c r="F10" t="n">
-        <v>-3627228</v>
+        <v>-96055</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>智邦</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -22,063 千股)</t>
+          <t>📉 20d 巨變(減碼 -11 千股)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-31281582</v>
+        <v>-579591</v>
       </c>
       <c r="D11" t="n">
-        <v>-104197922</v>
+        <v>-901483</v>
       </c>
       <c r="E11" t="n">
-        <v>-19106462</v>
+        <v>-497991</v>
       </c>
       <c r="F11" t="n">
-        <v>-82134727</v>
+        <v>-890867</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>旺矽</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -799 千股)</t>
+          <t>📉 20d 巨變(減碼 -207 千股)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-5272406</v>
+        <v>-1229695</v>
       </c>
       <c r="D12" t="n">
-        <v>-19716087</v>
+        <v>-4152705</v>
       </c>
       <c r="E12" t="n">
-        <v>-4835097</v>
+        <v>-1771843</v>
       </c>
       <c r="F12" t="n">
-        <v>-18916841</v>
+        <v>-3945715</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>雙鴻</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -9 千股)</t>
+          <t>📉 20d 巨變(減碼 -3,045 千股)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-1426377</v>
+        <v>-34792005</v>
       </c>
       <c r="D13" t="n">
-        <v>-96055</v>
+        <v>-107243112</v>
       </c>
       <c r="E13" t="n">
-        <v>-1811018</v>
+        <v>-31281582</v>
       </c>
       <c r="F13" t="n">
-        <v>-86813</v>
+        <v>-104197922</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 137 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,265 千股)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-497991</v>
+        <v>-3479292</v>
       </c>
       <c r="D14" t="n">
-        <v>-890867</v>
+        <v>-20981578</v>
       </c>
       <c r="E14" t="n">
-        <v>-528262</v>
+        <v>-5272406</v>
       </c>
       <c r="F14" t="n">
-        <v>-1027968</v>
+        <v>-19716087</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>台達電</t>
         </is>
       </c>
     </row>
@@ -6176,20 +6176,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 967 千股)</t>
+          <t>📈 20d 巨變(加碼 896 千股)</t>
         </is>
       </c>
       <c r="C15" t="n">
+        <v>1436508</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1841138</v>
+      </c>
+      <c r="E15" t="n">
         <v>1428643</v>
       </c>
-      <c r="D15" t="n">
+      <c r="F15" t="n">
         <v>945337</v>
-      </c>
-      <c r="E15" t="n">
-        <v>989236</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-21167</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -6205,20 +6205,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -117 千股)</t>
+          <t>📈 20d 巨變(加碼 262 千股)</t>
         </is>
       </c>
       <c r="C16" t="n">
+        <v>538888</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1536416</v>
+      </c>
+      <c r="E16" t="n">
         <v>112019</v>
       </c>
-      <c r="D16" t="n">
+      <c r="F16" t="n">
         <v>1274055</v>
-      </c>
-      <c r="E16" t="n">
-        <v>168739</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1390786</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -6229,232 +6229,232 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 41 千股)</t>
+          <t>📈 20d 巨變(加碼 115 千股)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-175968</v>
+        <v>-1470748</v>
       </c>
       <c r="D17" t="n">
-        <v>28296</v>
+        <v>-1523077</v>
       </c>
       <c r="E17" t="n">
-        <v>-220363</v>
+        <v>-1496965</v>
       </c>
       <c r="F17" t="n">
-        <v>-12424</v>
+        <v>-1638265</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>佳必琪</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -815 千股)</t>
+          <t>📉 20d 巨變(減碼 -219 千股)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-2295919</v>
+        <v>-289767</v>
       </c>
       <c r="D18" t="n">
-        <v>-4295306</v>
+        <v>-191029</v>
       </c>
       <c r="E18" t="n">
-        <v>-2727139</v>
+        <v>-175968</v>
       </c>
       <c r="F18" t="n">
-        <v>-3480074</v>
+        <v>28296</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>川湖</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 416 千股)</t>
+          <t>📉 20d 巨變(減碼 -2,565 千股)</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-1496965</v>
+        <v>-1417578</v>
       </c>
       <c r="D19" t="n">
-        <v>-1638265</v>
+        <v>2460649</v>
       </c>
       <c r="E19" t="n">
-        <v>-1923289</v>
+        <v>-2528250</v>
       </c>
       <c r="F19" t="n">
-        <v>-2053861</v>
+        <v>5025936</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>健鼎</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -2,019 千股)</t>
+          <t>📉 20d 巨變(減碼 -400 千股)</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-2528250</v>
+        <v>-1640785</v>
       </c>
       <c r="D20" t="n">
-        <v>5025936</v>
+        <v>-4695178</v>
       </c>
       <c r="E20" t="n">
-        <v>-3183994</v>
+        <v>-2295919</v>
       </c>
       <c r="F20" t="n">
-        <v>7045383</v>
+        <v>-4295306</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>崇越</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -183 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 731 千股)</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-689136</v>
+        <v>1036680</v>
       </c>
       <c r="D21" t="n">
-        <v>720049</v>
+        <v>-18807809</v>
       </c>
       <c r="E21" t="n">
-        <v>-571714</v>
+        <v>-1165454</v>
       </c>
       <c r="F21" t="n">
-        <v>902687</v>
+        <v>-19539272</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>中興電</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -2,131 千股)</t>
+          <t>📉 20d 巨變(減碼 -103 千股)</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-1165454</v>
+        <v>771717</v>
       </c>
       <c r="D22" t="n">
-        <v>-19539272</v>
+        <v>-465035</v>
       </c>
       <c r="E22" t="n">
-        <v>1056115</v>
+        <v>357798</v>
       </c>
       <c r="F22" t="n">
-        <v>-17408642</v>
+        <v>-362488</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>建榮</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 510 千股)</t>
+          <t>📈 20d 巨變(加碼 785 千股)</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>357798</v>
+        <v>-181768</v>
       </c>
       <c r="D23" t="n">
-        <v>-362488</v>
+        <v>-3841879</v>
       </c>
       <c r="E23" t="n">
-        <v>-182089</v>
+        <v>-1096503</v>
       </c>
       <c r="F23" t="n">
-        <v>-872369</v>
+        <v>-4626705</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>華城</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 592 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 1,029 千股)</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-1096503</v>
+        <v>304375</v>
       </c>
       <c r="D24" t="n">
-        <v>-4626705</v>
+        <v>1749164</v>
       </c>
       <c r="E24" t="n">
-        <v>-760343</v>
+        <v>-689136</v>
       </c>
       <c r="F24" t="n">
-        <v>-5219138</v>
+        <v>720049</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>中砂</t>
         </is>
       </c>
     </row>
@@ -6466,20 +6466,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -937 千股)</t>
+          <t>📉 20d 巨變(減碼 -899 千股)</t>
         </is>
       </c>
       <c r="C25" t="n">
+        <v>-2314701</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-4191243</v>
+      </c>
+      <c r="E25" t="n">
         <v>-933279</v>
       </c>
-      <c r="D25" t="n">
+      <c r="F25" t="n">
         <v>-3291981</v>
-      </c>
-      <c r="E25" t="n">
-        <v>-315914</v>
-      </c>
-      <c r="F25" t="n">
-        <v>-2355471</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -6495,20 +6495,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -8 千股)</t>
+          <t>📈 20d 巨變(加碼 37 千股)</t>
         </is>
       </c>
       <c r="C26" t="n">
+        <v>-14900</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-93786</v>
+      </c>
+      <c r="E26" t="n">
         <v>-10900</v>
       </c>
-      <c r="D26" t="n">
+      <c r="F26" t="n">
         <v>-130786</v>
-      </c>
-      <c r="E26" t="n">
-        <v>-8017</v>
-      </c>
-      <c r="F26" t="n">
-        <v>-122886</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -6519,116 +6519,116 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -15 千股)</t>
+          <t>📈 20d 巨變(加碼 617 千股)</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>82421</v>
+        <v>1106483</v>
       </c>
       <c r="D27" t="n">
-        <v>362755</v>
+        <v>3651318</v>
       </c>
       <c r="E27" t="n">
-        <v>73877</v>
+        <v>945669</v>
       </c>
       <c r="F27" t="n">
-        <v>378165</v>
+        <v>3033996</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>零壹</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -195 千股)</t>
+          <t>📉 20d 巨變(減碼 -251 千股)</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-1785884</v>
+        <v>-1982199</v>
       </c>
       <c r="D28" t="n">
-        <v>-2412895</v>
+        <v>-3398643</v>
       </c>
       <c r="E28" t="n">
-        <v>-908589</v>
+        <v>-2433199</v>
       </c>
       <c r="F28" t="n">
-        <v>-2217608</v>
+        <v>-3147493</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>隆大</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 141 千股)</t>
+          <t>📉 20d 巨變(減碼 -6 千股)</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>945669</v>
+        <v>77419</v>
       </c>
       <c r="D29" t="n">
-        <v>3033996</v>
+        <v>357073</v>
       </c>
       <c r="E29" t="n">
-        <v>1316327</v>
+        <v>82421</v>
       </c>
       <c r="F29" t="n">
-        <v>2892791</v>
+        <v>362755</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>崇友</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -648 千股)</t>
+          <t>📈 20d 巨變(加碼 614 千股)</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-2433199</v>
+        <v>-1279934</v>
       </c>
       <c r="D30" t="n">
-        <v>-3147493</v>
+        <v>-1798995</v>
       </c>
       <c r="E30" t="n">
-        <v>-2480199</v>
+        <v>-1785884</v>
       </c>
       <c r="F30" t="n">
-        <v>-2499344</v>
+        <v>-2412895</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>建準</t>
         </is>
       </c>
     </row>
@@ -6640,20 +6640,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -179 千股)</t>
+          <t>📈 20d 巨變(加碼 34 千股)</t>
         </is>
       </c>
       <c r="C31" t="n">
+        <v>-662155</v>
+      </c>
+      <c r="D31" t="n">
+        <v>465878</v>
+      </c>
+      <c r="E31" t="n">
         <v>-697694</v>
       </c>
-      <c r="D31" t="n">
+      <c r="F31" t="n">
         <v>431636</v>
-      </c>
-      <c r="E31" t="n">
-        <v>-178376</v>
-      </c>
-      <c r="F31" t="n">
-        <v>610952</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -6669,20 +6669,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -704 千股)</t>
+          <t>📈 20d 巨變(加碼 117 千股)</t>
         </is>
       </c>
       <c r="C32" t="n">
+        <v>-1358999</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-382854</v>
+      </c>
+      <c r="E32" t="n">
         <v>-1561999</v>
       </c>
-      <c r="D32" t="n">
+      <c r="F32" t="n">
         <v>-499499</v>
-      </c>
-      <c r="E32" t="n">
-        <v>-982639</v>
-      </c>
-      <c r="F32" t="n">
-        <v>204816</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -6698,20 +6698,20 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,899 千股)</t>
+          <t>📈 20d 巨變(加碼 74 千股)</t>
         </is>
       </c>
       <c r="C33" t="n">
+        <v>1240471</v>
+      </c>
+      <c r="D33" t="n">
+        <v>256137</v>
+      </c>
+      <c r="E33" t="n">
         <v>1516397</v>
       </c>
-      <c r="D33" t="n">
+      <c r="F33" t="n">
         <v>182037</v>
-      </c>
-      <c r="E33" t="n">
-        <v>2049176</v>
-      </c>
-      <c r="F33" t="n">
-        <v>-1717014</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -6727,20 +6727,20 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 14,816 千股)</t>
+          <t>📈 20d 巨變(加碼 18,239 千股)</t>
         </is>
       </c>
       <c r="C34" t="n">
+        <v>223295717</v>
+      </c>
+      <c r="D34" t="n">
+        <v>347497749</v>
+      </c>
+      <c r="E34" t="n">
         <v>213984721</v>
       </c>
-      <c r="D34" t="n">
+      <c r="F34" t="n">
         <v>329259102</v>
-      </c>
-      <c r="E34" t="n">
-        <v>165901765</v>
-      </c>
-      <c r="F34" t="n">
-        <v>314442831</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -6756,20 +6756,20 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -180 千股)</t>
+          <t>📉 20d 巨變(減碼 -339 千股)</t>
         </is>
       </c>
       <c r="C35" t="n">
+        <v>-783396</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-1004313</v>
+      </c>
+      <c r="E35" t="n">
         <v>-488500</v>
       </c>
-      <c r="D35" t="n">
+      <c r="F35" t="n">
         <v>-664967</v>
-      </c>
-      <c r="E35" t="n">
-        <v>-645937</v>
-      </c>
-      <c r="F35" t="n">
-        <v>-484560</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -6780,174 +6780,174 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -618 千股)</t>
+          <t>📈 20d 巨變(加碼 56 千股)</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>225150</v>
+        <v>591511</v>
       </c>
       <c r="D36" t="n">
-        <v>546933</v>
+        <v>125888</v>
       </c>
       <c r="E36" t="n">
-        <v>465704</v>
+        <v>572670</v>
       </c>
       <c r="F36" t="n">
-        <v>1164486</v>
+        <v>70047</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>大統益</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -166 千股)</t>
+          <t>📉 20d 巨變(減碼 -198 千股)</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-173368</v>
+        <v>239812</v>
       </c>
       <c r="D37" t="n">
-        <v>29420</v>
+        <v>348862</v>
       </c>
       <c r="E37" t="n">
-        <v>-104042</v>
+        <v>225150</v>
       </c>
       <c r="F37" t="n">
-        <v>195746</v>
+        <v>546933</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>智冠</t>
+          <t>豐藝</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 379 千股)</t>
+          <t>📈 20d 巨變(加碼 47 千股)</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>572670</v>
+        <v>-126066</v>
       </c>
       <c r="D38" t="n">
-        <v>70047</v>
+        <v>76874</v>
       </c>
       <c r="E38" t="n">
-        <v>148081</v>
+        <v>-173368</v>
       </c>
       <c r="F38" t="n">
-        <v>-308542</v>
+        <v>29420</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>智冠</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 73 千股)</t>
+          <t>📈 20d 巨變(加碼 6 千股)</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-234890</v>
+        <v>-6000</v>
       </c>
       <c r="D39" t="n">
-        <v>-231136</v>
+        <v>-11000</v>
       </c>
       <c r="E39" t="n">
-        <v>-304235</v>
+        <v>-6000</v>
       </c>
       <c r="F39" t="n">
-        <v>-304465</v>
+        <v>-17000</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>方土霖</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 133 千股)</t>
+          <t>📉 20d 巨變(減碼 -97 千股)</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-157136</v>
+        <v>-169640</v>
       </c>
       <c r="D40" t="n">
-        <v>-887055</v>
+        <v>-328136</v>
       </c>
       <c r="E40" t="n">
-        <v>-383436</v>
+        <v>-234890</v>
       </c>
       <c r="F40" t="n">
-        <v>-1020135</v>
+        <v>-231136</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>八方雲集</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 6,803 千股)</t>
+          <t>📈 20d 巨變(加碼 156 千股)</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>25203233</v>
+        <v>-119221</v>
       </c>
       <c r="D41" t="n">
-        <v>-12221307</v>
+        <v>-731372</v>
       </c>
       <c r="E41" t="n">
-        <v>14833221</v>
+        <v>-157136</v>
       </c>
       <c r="F41" t="n">
-        <v>-19024441</v>
+        <v>-887055</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>華景電</t>
         </is>
       </c>
     </row>
@@ -6959,20 +6959,20 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 163 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 92 千股)</t>
         </is>
       </c>
       <c r="C42" t="n">
+        <v>113341</v>
+      </c>
+      <c r="D42" t="n">
+        <v>-235479</v>
+      </c>
+      <c r="E42" t="n">
         <v>-2400</v>
       </c>
-      <c r="D42" t="n">
+      <c r="F42" t="n">
         <v>-327461</v>
-      </c>
-      <c r="E42" t="n">
-        <v>-265325</v>
-      </c>
-      <c r="F42" t="n">
-        <v>-490472</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -6983,145 +6983,145 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -7 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,654 千股)</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-19000</v>
+        <v>36045928</v>
       </c>
       <c r="D43" t="n">
-        <v>-258300</v>
+        <v>-13875769</v>
       </c>
       <c r="E43" t="n">
-        <v>-4000</v>
+        <v>25203233</v>
       </c>
       <c r="F43" t="n">
-        <v>-251300</v>
+        <v>-12221307</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>聯合</t>
+          <t>台灣大</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 2,156 千股)</t>
+          <t>📈 20d 巨變(加碼 93 千股)</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2786256</v>
+        <v>-28000</v>
       </c>
       <c r="D44" t="n">
-        <v>-2377147</v>
+        <v>-165300</v>
       </c>
       <c r="E44" t="n">
-        <v>3697648</v>
+        <v>-19000</v>
       </c>
       <c r="F44" t="n">
-        <v>-4532913</v>
+        <v>-258300</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>聯合</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -2,811 千股)</t>
+          <t>📈 20d 巨變(加碼 1,786 千股)</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-5309213</v>
+        <v>3552749</v>
       </c>
       <c r="D45" t="n">
-        <v>-2219578</v>
+        <v>-591043</v>
       </c>
       <c r="E45" t="n">
-        <v>1932952</v>
+        <v>2786256</v>
       </c>
       <c r="F45" t="n">
-        <v>590996</v>
+        <v>-2377147</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -154 千股)</t>
+          <t>📉 20d 巨變(減碼 -267 千股)</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>87120</v>
+        <v>-5083904</v>
       </c>
       <c r="D46" t="n">
-        <v>-753706</v>
+        <v>-2486333</v>
       </c>
       <c r="E46" t="n">
-        <v>105365</v>
+        <v>-5309213</v>
       </c>
       <c r="F46" t="n">
-        <v>-599461</v>
+        <v>-2219578</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>亞力</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -927 千股)</t>
+          <t>📉 20d 巨變(減碼 -110 千股)</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-439468</v>
+        <v>151560</v>
       </c>
       <c r="D47" t="n">
-        <v>2725398</v>
+        <v>-864146</v>
       </c>
       <c r="E47" t="n">
-        <v>104209</v>
+        <v>87120</v>
       </c>
       <c r="F47" t="n">
-        <v>3652384</v>
+        <v>-753706</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>大綜</t>
         </is>
       </c>
     </row>
@@ -7133,20 +7133,20 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 2,119 千股)</t>
+          <t>📉 20d 巨變(減碼 -788 千股)</t>
         </is>
       </c>
       <c r="C48" t="n">
+        <v>1433661</v>
+      </c>
+      <c r="D48" t="n">
+        <v>436193</v>
+      </c>
+      <c r="E48" t="n">
         <v>2002335</v>
       </c>
-      <c r="D48" t="n">
+      <c r="F48" t="n">
         <v>1223778</v>
-      </c>
-      <c r="E48" t="n">
-        <v>-752022</v>
-      </c>
-      <c r="F48" t="n">
-        <v>-895485</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -7157,29 +7157,29 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -741 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -331 千股)</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-172267</v>
+        <v>102524</v>
       </c>
       <c r="D49" t="n">
-        <v>-2558809</v>
+        <v>2394154</v>
       </c>
       <c r="E49" t="n">
-        <v>-827679</v>
+        <v>-439468</v>
       </c>
       <c r="F49" t="n">
-        <v>-1817899</v>
+        <v>2725398</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>漢科</t>
         </is>
       </c>
     </row>
@@ -7191,20 +7191,20 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 7,829 千股)</t>
+          <t>📈 20d 巨變(加碼 2,192 千股)</t>
         </is>
       </c>
       <c r="C50" t="n">
+        <v>2794927</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1151928</v>
+      </c>
+      <c r="E50" t="n">
         <v>6474065</v>
       </c>
-      <c r="D50" t="n">
+      <c r="F50" t="n">
         <v>-1039677</v>
-      </c>
-      <c r="E50" t="n">
-        <v>1157738</v>
-      </c>
-      <c r="F50" t="n">
-        <v>-8868544</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -7220,20 +7220,20 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 963 千股)</t>
+          <t>📉 20d 巨變(減碼 -3,879 千股)</t>
         </is>
       </c>
       <c r="C51" t="n">
+        <v>1175412</v>
+      </c>
+      <c r="D51" t="n">
+        <v>-6012208</v>
+      </c>
+      <c r="E51" t="n">
         <v>710474</v>
       </c>
-      <c r="D51" t="n">
+      <c r="F51" t="n">
         <v>-2133121</v>
-      </c>
-      <c r="E51" t="n">
-        <v>1261328</v>
-      </c>
-      <c r="F51" t="n">
-        <v>-3096187</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -7244,174 +7244,174 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -396 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -4,598 千股)</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-906305</v>
+        <v>-1581333</v>
       </c>
       <c r="D52" t="n">
-        <v>-3445921</v>
+        <v>-11734354</v>
       </c>
       <c r="E52" t="n">
-        <v>-805452</v>
+        <v>13691296</v>
       </c>
       <c r="F52" t="n">
-        <v>-3049831</v>
+        <v>-7136115</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -7,633 千股)</t>
+          <t>📉 20d 巨變(減碼 -140 千股)</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>13691296</v>
+        <v>-698120</v>
       </c>
       <c r="D53" t="n">
-        <v>-7136115</v>
+        <v>-2698394</v>
       </c>
       <c r="E53" t="n">
-        <v>10346533</v>
+        <v>-172267</v>
       </c>
       <c r="F53" t="n">
-        <v>496568</v>
+        <v>-2558809</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>玉晶光</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 6,487 千股)</t>
+          <t>📉 20d 巨變(減碼 -39 千股)</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-19666599</v>
+        <v>-885429</v>
       </c>
       <c r="D54" t="n">
-        <v>-38905078</v>
+        <v>-3484933</v>
       </c>
       <c r="E54" t="n">
-        <v>-15028303</v>
+        <v>-906305</v>
       </c>
       <c r="F54" t="n">
-        <v>-45392226</v>
+        <v>-3445921</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>世芯-KY</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -5,265 千股)</t>
+          <t>📉 20d 巨變(減碼 -42,086 千股)</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>-14744880</v>
+        <v>-11511118</v>
       </c>
       <c r="D55" t="n">
-        <v>36753211</v>
+        <v>-80991566</v>
       </c>
       <c r="E55" t="n">
-        <v>-14884397</v>
+        <v>-19666599</v>
       </c>
       <c r="F55" t="n">
-        <v>42017787</v>
+        <v>-38905078</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 702 千股)</t>
+          <t>📈 20d 巨變(加碼 254 千股)</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-148303</v>
+        <v>-7339887</v>
       </c>
       <c r="D56" t="n">
-        <v>-1806601</v>
+        <v>37007447</v>
       </c>
       <c r="E56" t="n">
-        <v>-160203</v>
+        <v>-14744880</v>
       </c>
       <c r="F56" t="n">
-        <v>-2509047</v>
+        <v>36753211</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -1,256 千股)</t>
+          <t>📉 20d 巨變(減碼 -354 千股)</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>-1094692</v>
+        <v>-642704</v>
       </c>
       <c r="D57" t="n">
-        <v>-2478848</v>
+        <v>-2161050</v>
       </c>
       <c r="E57" t="n">
-        <v>702120</v>
+        <v>-148303</v>
       </c>
       <c r="F57" t="n">
-        <v>-1223205</v>
+        <v>-1806601</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>鈊象</t>
         </is>
       </c>
     </row>
@@ -7423,20 +7423,20 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 74 千股)</t>
+          <t>📈 20d 巨變(加碼 25 千股)</t>
         </is>
       </c>
       <c r="C58" t="n">
+        <v>-268910</v>
+      </c>
+      <c r="D58" t="n">
+        <v>-597040</v>
+      </c>
+      <c r="E58" t="n">
         <v>-290950</v>
       </c>
-      <c r="D58" t="n">
+      <c r="F58" t="n">
         <v>-622221</v>
-      </c>
-      <c r="E58" t="n">
-        <v>-386947</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-695983</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -7452,20 +7452,20 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,127 千股)</t>
+          <t>📈 20d 巨變(加碼 4,325 千股)</t>
         </is>
       </c>
       <c r="C59" t="n">
+        <v>-986881</v>
+      </c>
+      <c r="D59" t="n">
+        <v>-728960</v>
+      </c>
+      <c r="E59" t="n">
         <v>-1437169</v>
       </c>
-      <c r="D59" t="n">
+      <c r="F59" t="n">
         <v>-5054173</v>
-      </c>
-      <c r="E59" t="n">
-        <v>-1431349</v>
-      </c>
-      <c r="F59" t="n">
-        <v>-6181312</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -7481,20 +7481,20 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -427 千股)</t>
+          <t>📉 20d 巨變(減碼 -180 千股)</t>
         </is>
       </c>
       <c r="C60" t="n">
+        <v>-100509</v>
+      </c>
+      <c r="D60" t="n">
+        <v>26902</v>
+      </c>
+      <c r="E60" t="n">
         <v>-231647</v>
       </c>
-      <c r="D60" t="n">
+      <c r="F60" t="n">
         <v>206433</v>
-      </c>
-      <c r="E60" t="n">
-        <v>-137557</v>
-      </c>
-      <c r="F60" t="n">
-        <v>633627</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -7505,377 +7505,377 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 112 千股)</t>
+          <t>📈 20d 巨變(加碼 10 千股)</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-384065</v>
+        <v>-821364</v>
       </c>
       <c r="D61" t="n">
-        <v>698346</v>
+        <v>-2468366</v>
       </c>
       <c r="E61" t="n">
-        <v>129382</v>
+        <v>-1094692</v>
       </c>
       <c r="F61" t="n">
-        <v>586719</v>
+        <v>-2478848</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>勝一</t>
+          <t>士電</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 337 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 14 千股)</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>586183</v>
+        <v>277543</v>
       </c>
       <c r="D62" t="n">
-        <v>835003</v>
+        <v>711962</v>
       </c>
       <c r="E62" t="n">
-        <v>86309</v>
+        <v>-384065</v>
       </c>
       <c r="F62" t="n">
-        <v>497896</v>
+        <v>698346</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>勝一</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 199 千股)</t>
+          <t>📈 20d 巨變(加碼 157 千股)</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-1556382</v>
+        <v>356135</v>
       </c>
       <c r="D63" t="n">
-        <v>3190619</v>
+        <v>1428014</v>
       </c>
       <c r="E63" t="n">
-        <v>-2412807</v>
+        <v>459167</v>
       </c>
       <c r="F63" t="n">
-        <v>2991490</v>
+        <v>1271079</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 1,139 千股)</t>
+          <t>📉 20d 巨變(減碼 -220 千股)</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>804593</v>
+        <v>434323</v>
       </c>
       <c r="D64" t="n">
-        <v>1413209</v>
+        <v>615070</v>
       </c>
       <c r="E64" t="n">
-        <v>-1016793</v>
+        <v>586183</v>
       </c>
       <c r="F64" t="n">
-        <v>274016</v>
+        <v>835003</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>祥碩</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -277 千股)</t>
+          <t>📈 20d 巨變(加碼 11 千股)</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-223750</v>
+        <v>1318451</v>
       </c>
       <c r="D65" t="n">
-        <v>-236457</v>
+        <v>1423955</v>
       </c>
       <c r="E65" t="n">
-        <v>-296842</v>
+        <v>804593</v>
       </c>
       <c r="F65" t="n">
-        <v>40334</v>
+        <v>1413209</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>華星光</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -631 千股)</t>
+          <t>📉 20d 巨變(減碼 -833 千股)</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-1965857</v>
+        <v>-1560612</v>
       </c>
       <c r="D66" t="n">
-        <v>-5117766</v>
+        <v>2358053</v>
       </c>
       <c r="E66" t="n">
-        <v>-1800561</v>
+        <v>-1556382</v>
       </c>
       <c r="F66" t="n">
-        <v>-4486320</v>
+        <v>3190619</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>藥華藥</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -1,526 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 86 千股)</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-244190</v>
+        <v>167091</v>
       </c>
       <c r="D67" t="n">
-        <v>-1861101</v>
+        <v>-150616</v>
       </c>
       <c r="E67" t="n">
-        <v>341101</v>
+        <v>-223750</v>
       </c>
       <c r="F67" t="n">
-        <v>-334683</v>
+        <v>-236457</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>信立</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -2,529 千股)</t>
+          <t>📉 20d 巨變(減碼 -221 千股)</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-18618023</v>
+        <v>-1827913</v>
       </c>
       <c r="D68" t="n">
-        <v>-33391928</v>
+        <v>-2082595</v>
       </c>
       <c r="E68" t="n">
-        <v>-17526992</v>
+        <v>-244190</v>
       </c>
       <c r="F68" t="n">
-        <v>-30863255</v>
+        <v>-1861101</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>聯鈞</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -261 千股)</t>
+          <t>📉 20d 巨變(減碼 -417 千股)</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-3032354</v>
+        <v>-948375</v>
       </c>
       <c r="D69" t="n">
-        <v>-12274112</v>
+        <v>766608</v>
       </c>
       <c r="E69" t="n">
-        <v>-3514951</v>
+        <v>-614319</v>
       </c>
       <c r="F69" t="n">
-        <v>-12013199</v>
+        <v>1183786</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>聯亞</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 10,728 千股)</t>
+          <t>📈 20d 巨變(加碼 1,040 千股)</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-13780172</v>
+        <v>-845634</v>
       </c>
       <c r="D70" t="n">
-        <v>-196512336</v>
+        <v>-4077792</v>
       </c>
       <c r="E70" t="n">
-        <v>-30017275</v>
+        <v>-1965857</v>
       </c>
       <c r="F70" t="n">
-        <v>-207240513</v>
+        <v>-5117766</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>宇瞻</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 137 千股)</t>
+          <t>📈 20d 巨變(加碼 10,904 千股)</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-614319</v>
+        <v>-3140336</v>
       </c>
       <c r="D71" t="n">
-        <v>1183786</v>
+        <v>-185608049</v>
       </c>
       <c r="E71" t="n">
-        <v>-1024328</v>
+        <v>-13780172</v>
       </c>
       <c r="F71" t="n">
-        <v>1046760</v>
+        <v>-196512336</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 2,174 千股)</t>
+          <t>📉 20d 巨變(減碼 -3,057 千股)</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-5763419</v>
+        <v>-18245071</v>
       </c>
       <c r="D72" t="n">
-        <v>-23090306</v>
+        <v>-36448543</v>
       </c>
       <c r="E72" t="n">
-        <v>-6149467</v>
+        <v>-18618023</v>
       </c>
       <c r="F72" t="n">
-        <v>-25264054</v>
+        <v>-33391928</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -34 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,795 千股)</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-474752</v>
+        <v>-2778419</v>
       </c>
       <c r="D73" t="n">
-        <v>-888229</v>
+        <v>-14069374</v>
       </c>
       <c r="E73" t="n">
-        <v>-607571</v>
+        <v>-3032354</v>
       </c>
       <c r="F73" t="n">
-        <v>-854488</v>
+        <v>-12274112</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>億泰</t>
+          <t>瑞昱</t>
         </is>
       </c>
     </row>
@@ -7887,20 +7887,20 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 13,106 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 1,359 千股)</t>
         </is>
       </c>
       <c r="C74" t="n">
+        <v>1170830</v>
+      </c>
+      <c r="D74" t="n">
+        <v>36294471</v>
+      </c>
+      <c r="E74" t="n">
         <v>-3967492</v>
       </c>
-      <c r="D74" t="n">
+      <c r="F74" t="n">
         <v>34935536</v>
-      </c>
-      <c r="E74" t="n">
-        <v>10098371</v>
-      </c>
-      <c r="F74" t="n">
-        <v>21829304</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -7911,58 +7911,58 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 72 千股)</t>
+          <t>📉 20d 巨變(減碼 -341 千股)</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>-25952</v>
+        <v>-927748</v>
       </c>
       <c r="D75" t="n">
-        <v>-355456</v>
+        <v>-647165</v>
       </c>
       <c r="E75" t="n">
-        <v>-111000</v>
+        <v>-957327</v>
       </c>
       <c r="F75" t="n">
-        <v>-427564</v>
+        <v>-305744</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>德昌</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -421 千股)</t>
+          <t>📉 20d 巨變(減碼 -5,466 千股)</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-957327</v>
+        <v>-8742903</v>
       </c>
       <c r="D76" t="n">
-        <v>-305744</v>
+        <v>-28556740</v>
       </c>
       <c r="E76" t="n">
-        <v>-696227</v>
+        <v>-5763419</v>
       </c>
       <c r="F76" t="n">
-        <v>115356</v>
+        <v>-23090306</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>德昌</t>
+          <t>台汽電</t>
         </is>
       </c>
     </row>
@@ -7974,20 +7974,20 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,110 千股)</t>
+          <t>📉 20d 巨變(減碼 -20 千股)</t>
         </is>
       </c>
       <c r="C77" t="n">
+        <v>239553</v>
+      </c>
+      <c r="D77" t="n">
+        <v>1322188</v>
+      </c>
+      <c r="E77" t="n">
         <v>211014</v>
       </c>
-      <c r="D77" t="n">
+      <c r="F77" t="n">
         <v>1342007</v>
-      </c>
-      <c r="E77" t="n">
-        <v>500132</v>
-      </c>
-      <c r="F77" t="n">
-        <v>2451927</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -7998,145 +7998,145 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -109 千股)</t>
+          <t>📉 20d 巨變(減碼 -40 千股)</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-2464797</v>
+        <v>-169000</v>
       </c>
       <c r="D78" t="n">
-        <v>4276282</v>
+        <v>-928229</v>
       </c>
       <c r="E78" t="n">
-        <v>-2486742</v>
+        <v>-474752</v>
       </c>
       <c r="F78" t="n">
-        <v>4385555</v>
+        <v>-888229</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>億泰</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 964 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 238 千股)</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2564589</v>
+        <v>24048</v>
       </c>
       <c r="D79" t="n">
-        <v>3101857</v>
+        <v>-117476</v>
       </c>
       <c r="E79" t="n">
-        <v>1853210</v>
+        <v>-25952</v>
       </c>
       <c r="F79" t="n">
-        <v>2138111</v>
+        <v>-355456</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>友輝</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,079 千股)</t>
+          <t>📉 20d 巨變(減碼 -59 千股)</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>-39841055</v>
+        <v>-2609088</v>
       </c>
       <c r="D80" t="n">
-        <v>-59452449</v>
+        <v>4217340</v>
       </c>
       <c r="E80" t="n">
-        <v>-42758358</v>
+        <v>-2464797</v>
       </c>
       <c r="F80" t="n">
-        <v>-58373805</v>
+        <v>4276282</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>原相</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 395 千股)</t>
+          <t>📈 20d 巨變(加碼 2,826 千股)</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>343519</v>
+        <v>4001237</v>
       </c>
       <c r="D81" t="n">
-        <v>505112</v>
+        <v>5928015</v>
       </c>
       <c r="E81" t="n">
-        <v>-98396</v>
+        <v>2564589</v>
       </c>
       <c r="F81" t="n">
-        <v>109766</v>
+        <v>3101857</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>啟碁</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -15,672 千股)</t>
+          <t>📈 20d 巨變(加碼 287 千股)</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-21099789</v>
+        <v>488536</v>
       </c>
       <c r="D82" t="n">
-        <v>-214914718</v>
+        <v>791755</v>
       </c>
       <c r="E82" t="n">
-        <v>-22531859</v>
+        <v>343519</v>
       </c>
       <c r="F82" t="n">
-        <v>-199242648</v>
+        <v>505112</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>精測</t>
         </is>
       </c>
     </row>
@@ -8148,20 +8148,20 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 701 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 219 千股)</t>
         </is>
       </c>
       <c r="C83" t="n">
+        <v>623883</v>
+      </c>
+      <c r="D83" t="n">
+        <v>-4464883</v>
+      </c>
+      <c r="E83" t="n">
         <v>-246893</v>
       </c>
-      <c r="D83" t="n">
+      <c r="F83" t="n">
         <v>-4684004</v>
-      </c>
-      <c r="E83" t="n">
-        <v>-837370</v>
-      </c>
-      <c r="F83" t="n">
-        <v>-5385329</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -8172,549 +8172,636 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -75 千股)</t>
+          <t>📈 20d 巨變(加碼 542 千股)</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-160580</v>
+        <v>-34707479</v>
       </c>
       <c r="D84" t="n">
-        <v>127845</v>
+        <v>-58910368</v>
       </c>
       <c r="E84" t="n">
-        <v>-120580</v>
+        <v>-39841055</v>
       </c>
       <c r="F84" t="n">
-        <v>203295</v>
+        <v>-59452449</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 274 千股)</t>
+          <t>📈 20d 巨變(加碼 64 千股)</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>-1477571</v>
+        <v>-82000</v>
       </c>
       <c r="D85" t="n">
-        <v>-292448</v>
+        <v>191669</v>
       </c>
       <c r="E85" t="n">
-        <v>-1719571</v>
+        <v>-160580</v>
       </c>
       <c r="F85" t="n">
-        <v>-566448</v>
+        <v>127845</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>東科-KY</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 173 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -2,763 千股)</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>160000</v>
+        <v>3714243</v>
       </c>
       <c r="D86" t="n">
-        <v>-208662</v>
+        <v>-217677992</v>
       </c>
       <c r="E86" t="n">
-        <v>83065</v>
+        <v>-21099789</v>
       </c>
       <c r="F86" t="n">
-        <v>-381662</v>
+        <v>-214914718</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>鑫龍騰</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -573 千股)</t>
+          <t>📈 20d 巨變(加碼 106 千股)</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>-1560486</v>
+        <v>212000</v>
       </c>
       <c r="D87" t="n">
-        <v>-3683884</v>
+        <v>-102662</v>
       </c>
       <c r="E87" t="n">
-        <v>-1263264</v>
+        <v>160000</v>
       </c>
       <c r="F87" t="n">
-        <v>-3110667</v>
+        <v>-208662</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>鑫龍騰</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -147 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,527 千股)</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>797829</v>
+        <v>-2975316</v>
       </c>
       <c r="D88" t="n">
-        <v>3872431</v>
+        <v>-1819443</v>
       </c>
       <c r="E88" t="n">
-        <v>857867</v>
+        <v>-1477571</v>
       </c>
       <c r="F88" t="n">
-        <v>4019230</v>
+        <v>-292448</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>全友</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,886 千股)</t>
+          <t>📉 20d 巨變(減碼 -880 千股)</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-20365313</v>
+        <v>-582642</v>
       </c>
       <c r="D89" t="n">
-        <v>-89990267</v>
+        <v>-4564072</v>
       </c>
       <c r="E89" t="n">
-        <v>-23531277</v>
+        <v>-1560486</v>
       </c>
       <c r="F89" t="n">
-        <v>-88104038</v>
+        <v>-3683884</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>宏捷科</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 731 千股)</t>
+          <t>📉 20d 巨變(減碼 -103 千股)</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>-136366</v>
+        <v>785717</v>
       </c>
       <c r="D90" t="n">
-        <v>-5196210</v>
+        <v>3769290</v>
       </c>
       <c r="E90" t="n">
-        <v>-123084</v>
+        <v>797829</v>
       </c>
       <c r="F90" t="n">
-        <v>-5926808</v>
+        <v>3872431</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>研華</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -10 千股)</t>
+          <t>📉 20d 巨變(減碼 -3,200 千股)</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>-3529</v>
+        <v>-9386617</v>
       </c>
       <c r="D91" t="n">
-        <v>-172161</v>
+        <v>-93190530</v>
       </c>
       <c r="E91" t="n">
-        <v>-1922</v>
+        <v>-20365313</v>
       </c>
       <c r="F91" t="n">
-        <v>-161697</v>
+        <v>-89990267</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -473 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 675 千股)</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>-288839</v>
+        <v>253995</v>
       </c>
       <c r="D92" t="n">
-        <v>5934767</v>
+        <v>-4521607</v>
       </c>
       <c r="E92" t="n">
-        <v>-1002456</v>
+        <v>-136366</v>
       </c>
       <c r="F92" t="n">
-        <v>6407559</v>
+        <v>-5196210</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>中保科</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -421 千股)</t>
+          <t>📈 20d 巨變(加碼 10 千股)</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>-1831280</v>
+        <v>-87788</v>
       </c>
       <c r="D93" t="n">
-        <v>-153463886</v>
+        <v>-162486</v>
       </c>
       <c r="E93" t="n">
-        <v>-11528119</v>
+        <v>-3529</v>
       </c>
       <c r="F93" t="n">
-        <v>-153043108</v>
+        <v>-172161</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>竹陞科技</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -30 千股)</t>
+          <t>📈 20d 巨變(加碼 436 千股)</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-58923</v>
+        <v>-1555687</v>
       </c>
       <c r="D94" t="n">
-        <v>92664</v>
+        <v>6371162</v>
       </c>
       <c r="E94" t="n">
-        <v>-20000</v>
+        <v>-288839</v>
       </c>
       <c r="F94" t="n">
-        <v>122887</v>
+        <v>5934767</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>長榮航太</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -820 千股)</t>
+          <t>📈 20d 巨變(加碼 200 千股)</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>-2093865</v>
+        <v>45040</v>
       </c>
       <c r="D95" t="n">
-        <v>-2394845</v>
+        <v>-259735</v>
       </c>
       <c r="E95" t="n">
-        <v>-1309348</v>
+        <v>54050</v>
       </c>
       <c r="F95" t="n">
-        <v>-1574947</v>
+        <v>-460065</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>安碁資訊</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -20,197 千股)</t>
+          <t>📈 20d 巨變(加碼 19 千股)</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>-9393707</v>
+        <v>-65923</v>
       </c>
       <c r="D96" t="n">
-        <v>-277368453</v>
+        <v>111664</v>
       </c>
       <c r="E96" t="n">
-        <v>-31079291</v>
+        <v>-58923</v>
       </c>
       <c r="F96" t="n">
-        <v>-257171105</v>
+        <v>92664</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>六方科-KY</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 359 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -4,460 千股)</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>38681</v>
+        <v>6681300</v>
       </c>
       <c r="D97" t="n">
-        <v>-3969741</v>
+        <v>-157923879</v>
       </c>
       <c r="E97" t="n">
-        <v>-126812</v>
+        <v>-1831280</v>
       </c>
       <c r="F97" t="n">
-        <v>-4329127</v>
+        <v>-153463886</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 169 千股)</t>
+          <t>📉 20d 巨變(減碼 -20,159 千股)</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-419324</v>
+        <v>-1099054</v>
       </c>
       <c r="D98" t="n">
-        <v>-4362453</v>
+        <v>-297527376</v>
       </c>
       <c r="E98" t="n">
-        <v>-697969</v>
+        <v>-9393707</v>
       </c>
       <c r="F98" t="n">
-        <v>-4531646</v>
+        <v>-277368453</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 35 千股)</t>
+          <t>📉 20d 巨變(減碼 -2,772 千股)</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>89745</v>
+        <v>-3616956</v>
       </c>
       <c r="D99" t="n">
-        <v>319568</v>
+        <v>-5166403</v>
       </c>
       <c r="E99" t="n">
-        <v>3165</v>
+        <v>-2093865</v>
       </c>
       <c r="F99" t="n">
-        <v>284998</v>
+        <v>-2394845</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>聯發科</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,614 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 360 千股)</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>5319599</v>
+        <v>-53338</v>
       </c>
       <c r="D100" t="n">
-        <v>8159133</v>
+        <v>-3609777</v>
       </c>
       <c r="E100" t="n">
-        <v>2732167</v>
+        <v>38681</v>
       </c>
       <c r="F100" t="n">
-        <v>6544667</v>
+        <v>-3969741</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>創意</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 570 千股)</t>
+          <t>📈 20d 巨變(加碼 124 千股)</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-1300882</v>
+        <v>-589851</v>
       </c>
       <c r="D101" t="n">
-        <v>915593</v>
+        <v>-4238184</v>
       </c>
       <c r="E101" t="n">
-        <v>-1026092</v>
+        <v>-419324</v>
       </c>
       <c r="F101" t="n">
-        <v>345829</v>
+        <v>-4362453</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>緯穎</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
+          <t>5274</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -71 千股)</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>116286</v>
+      </c>
+      <c r="D102" t="n">
+        <v>248361</v>
+      </c>
+      <c r="E102" t="n">
+        <v>89745</v>
+      </c>
+      <c r="F102" t="n">
+        <v>319568</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 85 千股)</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>5540643</v>
+      </c>
+      <c r="D103" t="n">
+        <v>8243644</v>
+      </c>
+      <c r="E103" t="n">
+        <v>5319599</v>
+      </c>
+      <c r="F103" t="n">
+        <v>8159133</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>5439</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -1,625 千股)</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>-1386511</v>
+      </c>
+      <c r="D104" t="n">
+        <v>-709790</v>
+      </c>
+      <c r="E104" t="n">
+        <v>-1300882</v>
+      </c>
+      <c r="F104" t="n">
+        <v>915593</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>高技</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
           <t>6187</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 431 千股)</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 185 千股)</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>892877</v>
+      </c>
+      <c r="D105" t="n">
+        <v>153911</v>
+      </c>
+      <c r="E105" t="n">
         <v>296332</v>
       </c>
-      <c r="D102" t="n">
+      <c r="F105" t="n">
         <v>-31353</v>
       </c>
-      <c r="E102" t="n">
-        <v>409811</v>
-      </c>
-      <c r="F102" t="n">
-        <v>-462187</v>
-      </c>
-      <c r="G102" t="inlineStr">
+      <c r="G105" t="inlineStr">
         <is>
           <t>萬潤</t>
         </is>

--- a/data/台股_外資雷達.xlsx
+++ b/data/台股_外資雷達.xlsx
@@ -496,22 +496,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>223296</v>
+        <v>169391</v>
       </c>
       <c r="D2" t="n">
-        <v>347498</v>
+        <v>253317</v>
       </c>
       <c r="E2" t="n">
-        <v>154302</v>
+        <v>162256</v>
       </c>
       <c r="F2" t="n">
-        <v>-22211</v>
+        <v>-15395</v>
       </c>
       <c r="G2" t="n">
-        <v>24587</v>
+        <v>30900</v>
       </c>
       <c r="H2" t="n">
-        <v>1145</v>
+        <v>844</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -538,31 +538,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-7340</v>
+        <v>2422</v>
       </c>
       <c r="D3" t="n">
-        <v>37007</v>
+        <v>37228</v>
       </c>
       <c r="E3" t="n">
-        <v>3244</v>
+        <v>123142</v>
       </c>
       <c r="F3" t="n">
-        <v>6923</v>
+        <v>-3099</v>
       </c>
       <c r="G3" t="n">
-        <v>-35932</v>
+        <v>-32994</v>
       </c>
       <c r="H3" t="n">
-        <v>3381</v>
+        <v>2927</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -571,49 +571,49 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>🐌 龜速*</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1171</v>
+        <v>-3755</v>
       </c>
       <c r="D4" t="n">
-        <v>36294</v>
+        <v>36837</v>
       </c>
       <c r="E4" t="n">
-        <v>121950</v>
+        <v>2227</v>
       </c>
       <c r="F4" t="n">
-        <v>-585</v>
+        <v>7466</v>
       </c>
       <c r="G4" t="n">
-        <v>-30768</v>
+        <v>-32407</v>
       </c>
       <c r="H4" t="n">
-        <v>2096</v>
+        <v>3940</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -622,19 +622,19 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🐌 龜速*</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5">
@@ -649,22 +649,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5541</v>
+        <v>5738</v>
       </c>
       <c r="D5" t="n">
-        <v>8244</v>
+        <v>8531</v>
       </c>
       <c r="E5" t="n">
-        <v>12682</v>
+        <v>13046</v>
       </c>
       <c r="F5" t="n">
-        <v>-4438</v>
+        <v>-4698</v>
       </c>
       <c r="G5" t="n">
-        <v>-10894</v>
+        <v>-11108</v>
       </c>
       <c r="H5" t="n">
-        <v>-556</v>
+        <v>-562</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -688,22 +688,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-1556</v>
+        <v>-358</v>
       </c>
       <c r="D6" t="n">
-        <v>6371</v>
+        <v>6420</v>
       </c>
       <c r="E6" t="n">
-        <v>10528</v>
+        <v>10788</v>
       </c>
       <c r="F6" t="n">
-        <v>-113</v>
+        <v>-498</v>
       </c>
       <c r="G6" t="n">
-        <v>-667</v>
+        <v>-1047</v>
       </c>
       <c r="H6" t="n">
-        <v>505</v>
+        <v>558</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -730,31 +730,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>零壹</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4001</v>
+        <v>1581</v>
       </c>
       <c r="D7" t="n">
-        <v>5928</v>
+        <v>3994</v>
       </c>
       <c r="E7" t="n">
-        <v>28222</v>
+        <v>2268</v>
       </c>
       <c r="F7" t="n">
-        <v>-2290</v>
+        <v>-1</v>
       </c>
       <c r="G7" t="n">
-        <v>-13078</v>
+        <v>-124</v>
       </c>
       <c r="H7" t="n">
-        <v>185</v>
+        <v>-737</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -763,49 +763,49 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>原相</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2562</v>
+        <v>-2144</v>
       </c>
       <c r="D8" t="n">
-        <v>5626</v>
+        <v>3887</v>
       </c>
       <c r="E8" t="n">
-        <v>10669</v>
+        <v>7289</v>
       </c>
       <c r="F8" t="n">
-        <v>-1207</v>
+        <v>-890</v>
       </c>
       <c r="G8" t="n">
-        <v>-4943</v>
+        <v>3896</v>
       </c>
       <c r="H8" t="n">
-        <v>71</v>
+        <v>-145</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -814,11 +814,11 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -826,37 +826,37 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-2609</v>
+        <v>187</v>
       </c>
       <c r="D9" t="n">
-        <v>4217</v>
+        <v>3613</v>
       </c>
       <c r="E9" t="n">
-        <v>7645</v>
+        <v>9547</v>
       </c>
       <c r="F9" t="n">
-        <v>-290</v>
+        <v>-93</v>
       </c>
       <c r="G9" t="n">
-        <v>4428</v>
+        <v>-3271</v>
       </c>
       <c r="H9" t="n">
-        <v>-60</v>
+        <v>70</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -865,11 +865,11 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -892,22 +892,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>786</v>
+        <v>521</v>
       </c>
       <c r="D10" t="n">
-        <v>3769</v>
+        <v>3581</v>
       </c>
       <c r="E10" t="n">
-        <v>15198</v>
+        <v>14987</v>
       </c>
       <c r="F10" t="n">
-        <v>118</v>
+        <v>372</v>
       </c>
       <c r="G10" t="n">
-        <v>825</v>
+        <v>1069</v>
       </c>
       <c r="H10" t="n">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -934,82 +934,82 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>漢科</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1106</v>
+        <v>691</v>
       </c>
       <c r="D11" t="n">
-        <v>3651</v>
+        <v>3104</v>
       </c>
       <c r="E11" t="n">
-        <v>1945</v>
+        <v>3589</v>
       </c>
       <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>135</v>
+      </c>
+      <c r="H11" t="n">
+        <v>25</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>🟢 加碼</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>77</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
         <v>-1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-128</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-741</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>🟢 加碼</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>97</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>🚀 加速器</t>
-        </is>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>601</v>
+        <v>3984</v>
       </c>
       <c r="D12" t="n">
-        <v>2537</v>
+        <v>2947</v>
       </c>
       <c r="E12" t="n">
-        <v>-1183</v>
+        <v>-1464</v>
       </c>
       <c r="F12" t="n">
-        <v>-182</v>
+        <v>-3325</v>
       </c>
       <c r="G12" t="n">
-        <v>-1154</v>
+        <v>133</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>-786</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1018,49 +1018,49 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-1418</v>
+        <v>2790</v>
       </c>
       <c r="D13" t="n">
-        <v>2461</v>
+        <v>2700</v>
       </c>
       <c r="E13" t="n">
-        <v>11511</v>
+        <v>-5219</v>
       </c>
       <c r="F13" t="n">
-        <v>-147</v>
+        <v>-1540</v>
       </c>
       <c r="G13" t="n">
-        <v>-9987</v>
+        <v>-6662</v>
       </c>
       <c r="H13" t="n">
-        <v>-343</v>
+        <v>-262</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1069,49 +1069,49 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>103</v>
+        <v>215</v>
       </c>
       <c r="D14" t="n">
-        <v>2394</v>
+        <v>2461</v>
       </c>
       <c r="E14" t="n">
-        <v>3299</v>
+        <v>12486</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>-729</v>
       </c>
       <c r="G14" t="n">
-        <v>135</v>
+        <v>-10507</v>
       </c>
       <c r="H14" t="n">
-        <v>36</v>
+        <v>-304</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1120,11 +1120,11 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1132,37 +1132,37 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-1561</v>
+        <v>-36</v>
       </c>
       <c r="D15" t="n">
-        <v>2358</v>
+        <v>2273</v>
       </c>
       <c r="E15" t="n">
-        <v>13842</v>
+        <v>3638</v>
       </c>
       <c r="F15" t="n">
-        <v>10</v>
+        <v>-248</v>
       </c>
       <c r="G15" t="n">
-        <v>1186</v>
+        <v>-1704</v>
       </c>
       <c r="H15" t="n">
-        <v>-10</v>
+        <v>-123</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1171,15 +1171,15 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>🚀 加速器*</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M15" t="n">
@@ -1189,31 +1189,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>1809</v>
       </c>
       <c r="D16" t="n">
-        <v>2113</v>
+        <v>2197</v>
       </c>
       <c r="E16" t="n">
-        <v>3454</v>
+        <v>2225</v>
       </c>
       <c r="F16" t="n">
-        <v>-137</v>
+        <v>-933</v>
       </c>
       <c r="G16" t="n">
-        <v>-998</v>
+        <v>-898</v>
       </c>
       <c r="H16" t="n">
-        <v>-268</v>
+        <v>60</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1226,96 +1226,96 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-64</v>
+        <v>173</v>
       </c>
       <c r="D17" t="n">
-        <v>1896</v>
+        <v>2163</v>
       </c>
       <c r="E17" t="n">
-        <v>-6459</v>
+        <v>1240</v>
       </c>
       <c r="F17" t="n">
-        <v>-664</v>
+        <v>-3</v>
       </c>
       <c r="G17" t="n">
-        <v>274</v>
+        <v>11</v>
       </c>
       <c r="H17" t="n">
-        <v>-217</v>
+        <v>87</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>🟡 中性</t>
+          <t>🟢 加碼</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1437</v>
+        <v>448</v>
       </c>
       <c r="D18" t="n">
-        <v>1841</v>
+        <v>1991</v>
       </c>
       <c r="E18" t="n">
-        <v>2020</v>
+        <v>-1224</v>
       </c>
       <c r="F18" t="n">
-        <v>-976</v>
+        <v>59</v>
       </c>
       <c r="G18" t="n">
-        <v>-980</v>
+        <v>-1080</v>
       </c>
       <c r="H18" t="n">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1328,45 +1328,45 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>304</v>
+        <v>1051</v>
       </c>
       <c r="D19" t="n">
-        <v>1749</v>
+        <v>1925</v>
       </c>
       <c r="E19" t="n">
-        <v>2039</v>
+        <v>658</v>
       </c>
       <c r="F19" t="n">
-        <v>-265</v>
+        <v>-533</v>
       </c>
       <c r="G19" t="n">
-        <v>465</v>
+        <v>-706</v>
       </c>
       <c r="H19" t="n">
-        <v>-95</v>
+        <v>15</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1379,45 +1379,45 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>539</v>
+        <v>806</v>
       </c>
       <c r="D20" t="n">
-        <v>1536</v>
+        <v>1735</v>
       </c>
       <c r="E20" t="n">
-        <v>135</v>
+        <v>2409</v>
       </c>
       <c r="F20" t="n">
-        <v>6</v>
+        <v>-485</v>
       </c>
       <c r="G20" t="n">
-        <v>-168</v>
+        <v>171</v>
       </c>
       <c r="H20" t="n">
-        <v>11</v>
+        <v>-118</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1430,15 +1430,15 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1453,22 +1453,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>356</v>
+        <v>438</v>
       </c>
       <c r="D21" t="n">
-        <v>1428</v>
+        <v>1442</v>
       </c>
       <c r="E21" t="n">
-        <v>3196</v>
+        <v>3226</v>
       </c>
       <c r="F21" t="n">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="G21" t="n">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H21" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1495,31 +1495,31 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1318</v>
+        <v>-889</v>
       </c>
       <c r="D22" t="n">
-        <v>1424</v>
+        <v>1196</v>
       </c>
       <c r="E22" t="n">
-        <v>-6645</v>
+        <v>1114</v>
       </c>
       <c r="F22" t="n">
-        <v>-1299</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>-6457</v>
+        <v>-2414</v>
       </c>
       <c r="H22" t="n">
-        <v>-278</v>
+        <v>-98</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1532,45 +1532,45 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>勝一</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>240</v>
+        <v>512</v>
       </c>
       <c r="D23" t="n">
-        <v>1322</v>
+        <v>1019</v>
       </c>
       <c r="E23" t="n">
-        <v>7286</v>
+        <v>1948</v>
       </c>
       <c r="F23" t="n">
-        <v>25</v>
+        <v>-6</v>
       </c>
       <c r="G23" t="n">
-        <v>5238</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>-54</v>
+        <v>-0</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1597,31 +1597,31 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>湧德</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2795</v>
+        <v>65</v>
       </c>
       <c r="D24" t="n">
-        <v>1152</v>
+        <v>920</v>
       </c>
       <c r="E24" t="n">
-        <v>-9948</v>
+        <v>-3236</v>
       </c>
       <c r="F24" t="n">
-        <v>864</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>8854</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-118</v>
+        <v>-203</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1630,19 +1630,19 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="25">
@@ -1657,22 +1657,22 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>489</v>
+        <v>421</v>
       </c>
       <c r="D25" t="n">
-        <v>792</v>
+        <v>801</v>
       </c>
       <c r="E25" t="n">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="F25" t="n">
-        <v>-154</v>
+        <v>-103</v>
       </c>
       <c r="G25" t="n">
-        <v>-1414</v>
+        <v>-1408</v>
       </c>
       <c r="H25" t="n">
-        <v>-147</v>
+        <v>-125</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1699,31 +1699,31 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-948</v>
+        <v>510</v>
       </c>
       <c r="D26" t="n">
-        <v>767</v>
+        <v>629</v>
       </c>
       <c r="E26" t="n">
-        <v>973</v>
+        <v>-1258</v>
       </c>
       <c r="F26" t="n">
-        <v>244</v>
+        <v>283</v>
       </c>
       <c r="G26" t="n">
-        <v>-2236</v>
+        <v>2463</v>
       </c>
       <c r="H26" t="n">
-        <v>-30</v>
+        <v>-79</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1732,100 +1732,100 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>勝一</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>278</v>
+        <v>-2266</v>
       </c>
       <c r="D27" t="n">
-        <v>712</v>
+        <v>593</v>
       </c>
       <c r="E27" t="n">
-        <v>1765</v>
+        <v>12884</v>
       </c>
       <c r="F27" t="n">
-        <v>-5</v>
+        <v>9</v>
       </c>
       <c r="G27" t="n">
+        <v>1216</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-41</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>66</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>🚀 加速器*</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
         <v>3</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-13</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K27" t="n">
-        <v>71</v>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>📉 減速</t>
-        </is>
-      </c>
-      <c r="M27" t="n">
-        <v>-3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>大統益</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>434</v>
+        <v>1037</v>
       </c>
       <c r="D28" t="n">
-        <v>615</v>
+        <v>570</v>
       </c>
       <c r="E28" t="n">
-        <v>-1318</v>
+        <v>193</v>
       </c>
       <c r="F28" t="n">
-        <v>247</v>
+        <v>-1</v>
       </c>
       <c r="G28" t="n">
-        <v>2429</v>
+        <v>-2</v>
       </c>
       <c r="H28" t="n">
-        <v>-20</v>
+        <v>20</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1834,49 +1834,49 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>智易</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1146</v>
+        <v>45</v>
       </c>
       <c r="D29" t="n">
-        <v>527</v>
+        <v>440</v>
       </c>
       <c r="E29" t="n">
-        <v>-904</v>
+        <v>7187</v>
       </c>
       <c r="F29" t="n">
-        <v>-325</v>
+        <v>17</v>
       </c>
       <c r="G29" t="n">
-        <v>-979</v>
+        <v>4837</v>
       </c>
       <c r="H29" t="n">
-        <v>-147</v>
+        <v>-89</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1885,49 +1885,49 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-662</v>
+        <v>1031</v>
       </c>
       <c r="D30" t="n">
-        <v>466</v>
+        <v>429</v>
       </c>
       <c r="E30" t="n">
-        <v>-3429</v>
+        <v>-1084</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>-139</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>-910</v>
       </c>
       <c r="H30" t="n">
-        <v>-207</v>
+        <v>-166</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1940,45 +1940,45 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M30" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>崇友</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1434</v>
+        <v>98</v>
       </c>
       <c r="D31" t="n">
-        <v>436</v>
+        <v>372</v>
       </c>
       <c r="E31" t="n">
-        <v>-3971</v>
+        <v>602</v>
       </c>
       <c r="F31" t="n">
-        <v>-1226</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>2390</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-1052</v>
+        <v>2</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1987,49 +1987,49 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>立隆電</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>768</v>
+        <v>2733</v>
       </c>
       <c r="D32" t="n">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E32" t="n">
-        <v>-6698</v>
+        <v>-9853</v>
       </c>
       <c r="F32" t="n">
-        <v>-346</v>
+        <v>702</v>
       </c>
       <c r="G32" t="n">
-        <v>-3347</v>
+        <v>9264</v>
       </c>
       <c r="H32" t="n">
-        <v>-7</v>
+        <v>-249</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2038,100 +2038,100 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>77</v>
+        <v>-1179</v>
       </c>
       <c r="D33" t="n">
         <v>357</v>
       </c>
       <c r="E33" t="n">
-        <v>588</v>
+        <v>-7467</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>-470</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1750</v>
       </c>
       <c r="H33" t="n">
+        <v>-128</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>100</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>🚀 加速器</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
         <v>2</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K33" t="n">
-        <v>91</v>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>🐌 龜速</t>
-        </is>
-      </c>
-      <c r="M33" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>240</v>
+        <v>868</v>
       </c>
       <c r="D34" t="n">
-        <v>349</v>
+        <v>311</v>
       </c>
       <c r="E34" t="n">
-        <v>1266</v>
+        <v>-6715</v>
       </c>
       <c r="F34" t="n">
-        <v>-3</v>
+        <v>-334</v>
       </c>
       <c r="G34" t="n">
-        <v>7</v>
+        <v>-3158</v>
       </c>
       <c r="H34" t="n">
-        <v>106</v>
+        <v>2</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2140,230 +2140,230 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M34" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1240</v>
+        <v>296</v>
       </c>
       <c r="D35" t="n">
-        <v>256</v>
+        <v>284</v>
       </c>
       <c r="E35" t="n">
-        <v>-2557</v>
+        <v>-5705</v>
       </c>
       <c r="F35" t="n">
-        <v>-4</v>
+        <v>586</v>
       </c>
       <c r="G35" t="n">
-        <v>-423</v>
+        <v>-1289</v>
       </c>
       <c r="H35" t="n">
-        <v>12</v>
+        <v>-156</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K35" t="n">
-        <v>94</v>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>📉 減速</t>
-        </is>
-      </c>
-      <c r="M35" t="n">
-        <v>-4</v>
-      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>友輝</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>116</v>
+        <v>54</v>
       </c>
       <c r="D36" t="n">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="E36" t="n">
-        <v>789</v>
+        <v>1191</v>
       </c>
       <c r="F36" t="n">
-        <v>-180</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>-456</v>
+        <v>6</v>
       </c>
       <c r="H36" t="n">
-        <v>-18</v>
+        <v>-23</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>77</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-82</v>
+        <v>145</v>
       </c>
       <c r="D37" t="n">
-        <v>192</v>
+        <v>226</v>
       </c>
       <c r="E37" t="n">
-        <v>-125</v>
+        <v>804</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>-115</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>-404</v>
       </c>
       <c r="H37" t="n">
-        <v>-12</v>
+        <v>-20</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K37" t="n">
-        <v>78</v>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>📉 減速</t>
-        </is>
-      </c>
-      <c r="M37" t="n">
-        <v>-3</v>
-      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>893</v>
+        <v>3420</v>
       </c>
       <c r="D38" t="n">
-        <v>154</v>
+        <v>189</v>
       </c>
       <c r="E38" t="n">
-        <v>-5563</v>
+        <v>-57935</v>
       </c>
       <c r="F38" t="n">
-        <v>392</v>
+        <v>796</v>
       </c>
       <c r="G38" t="n">
-        <v>-1175</v>
+        <v>5461</v>
       </c>
       <c r="H38" t="n">
-        <v>-27</v>
+        <v>-91</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>57</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>-4</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>592</v>
+        <v>-30</v>
       </c>
       <c r="D39" t="n">
-        <v>126</v>
+        <v>176</v>
       </c>
       <c r="E39" t="n">
-        <v>-227</v>
+        <v>-111</v>
       </c>
       <c r="F39" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
         <v>-2</v>
       </c>
-      <c r="H39" t="n">
-        <v>21</v>
-      </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>🟡 中性</t>
@@ -2371,11 +2371,11 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2389,31 +2389,31 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-66</v>
+        <v>2043</v>
       </c>
       <c r="D40" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E40" t="n">
-        <v>-73</v>
+        <v>-1754</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>-423</v>
       </c>
       <c r="H40" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2422,49 +2422,49 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M40" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>智冠</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-126</v>
+        <v>312</v>
       </c>
       <c r="D41" t="n">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="E41" t="n">
-        <v>422</v>
+        <v>-62</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>-399</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>-466</v>
       </c>
       <c r="H41" t="n">
-        <v>-33</v>
+        <v>-27</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2477,45 +2477,45 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M41" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>六方科-KY</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-101</v>
+        <v>-45</v>
       </c>
       <c r="D42" t="n">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="E42" t="n">
-        <v>1160</v>
+        <v>-65</v>
       </c>
       <c r="F42" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>-90</v>
+        <v>1</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2528,36 +2528,36 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M42" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>方土霖</t>
+          <t>智冠</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-6</v>
+        <v>-84</v>
       </c>
       <c r="D43" t="n">
-        <v>-11</v>
+        <v>56</v>
       </c>
       <c r="E43" t="n">
-        <v>-78</v>
+        <v>442</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -2566,7 +2566,7 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>-5</v>
+        <v>-32</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2593,31 +2593,31 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>大車隊</t>
+          <t>達欣工</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-15</v>
+        <v>-21</v>
       </c>
       <c r="D44" t="n">
-        <v>-94</v>
+        <v>-4</v>
       </c>
       <c r="E44" t="n">
-        <v>-295</v>
+        <v>1186</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H44" t="n">
-        <v>52</v>
+        <v>-93</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2626,11 +2626,11 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2644,22 +2644,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>鑫龍騰</t>
+          <t>方土霖</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>212</v>
+        <v>-6</v>
       </c>
       <c r="D45" t="n">
-        <v>-103</v>
+        <v>-11</v>
       </c>
       <c r="E45" t="n">
-        <v>-2710</v>
+        <v>-80</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -2668,7 +2668,7 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>-0</v>
+        <v>-5</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2677,49 +2677,49 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>鑫龍騰</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>24</v>
+        <v>210</v>
       </c>
       <c r="D46" t="n">
-        <v>-117</v>
+        <v>-64</v>
       </c>
       <c r="E46" t="n">
-        <v>1203</v>
+        <v>-2702</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>-19</v>
+        <v>-0</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2736,32 +2736,32 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M46" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>大車隊</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>167</v>
+        <v>-15</v>
       </c>
       <c r="D47" t="n">
-        <v>-151</v>
+        <v>-71</v>
       </c>
       <c r="E47" t="n">
-        <v>-58</v>
+        <v>-299</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -2770,7 +2770,7 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-70</v>
+        <v>52</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2779,19 +2779,19 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="48">
@@ -2806,13 +2806,13 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-88</v>
+        <v>-15</v>
       </c>
       <c r="D48" t="n">
-        <v>-162</v>
+        <v>-91</v>
       </c>
       <c r="E48" t="n">
-        <v>-170</v>
+        <v>-83</v>
       </c>
       <c r="F48" t="n">
         <v>11</v>
@@ -2821,7 +2821,7 @@
         <v>11</v>
       </c>
       <c r="H48" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2848,22 +2848,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>聯合</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-28</v>
+        <v>694</v>
       </c>
       <c r="D49" t="n">
-        <v>-165</v>
+        <v>-149</v>
       </c>
       <c r="E49" t="n">
-        <v>-2992</v>
+        <v>-4469</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -2872,7 +2872,7 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>90</v>
+        <v>-33</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -2899,31 +2899,31 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>聯合</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-290</v>
+        <v>-16</v>
       </c>
       <c r="D50" t="n">
-        <v>-191</v>
+        <v>-159</v>
       </c>
       <c r="E50" t="n">
-        <v>65</v>
+        <v>-2986</v>
       </c>
       <c r="F50" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>340</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-0</v>
+        <v>86</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -2944,37 +2944,37 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>113</v>
+        <v>35</v>
       </c>
       <c r="D51" t="n">
-        <v>-235</v>
+        <v>-181</v>
       </c>
       <c r="E51" t="n">
-        <v>-282</v>
+        <v>-956</v>
       </c>
       <c r="F51" t="n">
-        <v>-108</v>
+        <v>-3</v>
       </c>
       <c r="G51" t="n">
-        <v>-147</v>
+        <v>244</v>
       </c>
       <c r="H51" t="n">
-        <v>-26</v>
+        <v>-8</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -2987,15 +2987,15 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>🐌 龜速*</t>
         </is>
       </c>
       <c r="M51" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="52">
@@ -3010,13 +3010,13 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D52" t="n">
-        <v>-260</v>
+        <v>-191</v>
       </c>
       <c r="E52" t="n">
-        <v>-227</v>
+        <v>-223</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -3025,7 +3025,7 @@
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-30</v>
+        <v>-32</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3052,31 +3052,31 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>信立</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-170</v>
+        <v>126</v>
       </c>
       <c r="D53" t="n">
-        <v>-328</v>
+        <v>-291</v>
       </c>
       <c r="E53" t="n">
-        <v>-1079</v>
+        <v>-153</v>
       </c>
       <c r="F53" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>242</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-8</v>
+        <v>-71</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3085,19 +3085,19 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K53" t="n">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>🐌 龜速*</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M53" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3112,13 +3112,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-1359</v>
+        <v>-1184</v>
       </c>
       <c r="D54" t="n">
-        <v>-383</v>
+        <v>-473</v>
       </c>
       <c r="E54" t="n">
-        <v>1975</v>
+        <v>1909</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -3127,7 +3127,7 @@
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-66</v>
+        <v>-52</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3154,31 +3154,31 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>-40</v>
+        <v>-118</v>
       </c>
       <c r="D55" t="n">
-        <v>-418</v>
+        <v>-481</v>
       </c>
       <c r="E55" t="n">
-        <v>4476</v>
+        <v>-3004</v>
       </c>
       <c r="F55" t="n">
-        <v>392</v>
+        <v>5</v>
       </c>
       <c r="G55" t="n">
-        <v>396</v>
+        <v>-110</v>
       </c>
       <c r="H55" t="n">
-        <v>131</v>
+        <v>-127</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3191,45 +3191,45 @@
         </is>
       </c>
       <c r="K55" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M55" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>772</v>
+        <v>-493</v>
       </c>
       <c r="D56" t="n">
-        <v>-465</v>
+        <v>-481</v>
       </c>
       <c r="E56" t="n">
-        <v>-4449</v>
+        <v>-126</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>387</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>606</v>
       </c>
       <c r="H56" t="n">
-        <v>-14</v>
+        <v>-6</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -3250,37 +3250,37 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>3553</v>
+        <v>-110</v>
       </c>
       <c r="D57" t="n">
-        <v>-591</v>
+        <v>-636</v>
       </c>
       <c r="E57" t="n">
-        <v>-57843</v>
+        <v>-1930</v>
       </c>
       <c r="F57" t="n">
-        <v>216</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>5691</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-117</v>
+        <v>0</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3289,11 +3289,11 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K57" t="n">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -3301,37 +3301,37 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-269</v>
+        <v>-464</v>
       </c>
       <c r="D58" t="n">
-        <v>-597</v>
+        <v>-740</v>
       </c>
       <c r="E58" t="n">
-        <v>-1891</v>
+        <v>4393</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>282</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>461</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>259</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3340,49 +3340,49 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K58" t="n">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M58" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>-879</v>
+        <v>1867</v>
       </c>
       <c r="D59" t="n">
-        <v>-636</v>
+        <v>-818</v>
       </c>
       <c r="E59" t="n">
-        <v>2392</v>
+        <v>26523</v>
       </c>
       <c r="F59" t="n">
-        <v>218</v>
+        <v>-2154</v>
       </c>
       <c r="G59" t="n">
-        <v>165</v>
+        <v>-6539</v>
       </c>
       <c r="H59" t="n">
-        <v>-323</v>
+        <v>-225</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3391,49 +3391,49 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K59" t="n">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M59" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>德昌</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>-928</v>
+        <v>-374</v>
       </c>
       <c r="D60" t="n">
-        <v>-647</v>
+        <v>-873</v>
       </c>
       <c r="E60" t="n">
-        <v>-257</v>
+        <v>2261</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="H60" t="n">
-        <v>-21</v>
+        <v>-132</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3442,79 +3442,91 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K60" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M60" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-1387</v>
+        <v>56952</v>
       </c>
       <c r="D61" t="n">
-        <v>-710</v>
+        <v>-878</v>
       </c>
       <c r="E61" t="n">
-        <v>-2053</v>
+        <v>40388</v>
       </c>
       <c r="F61" t="n">
-        <v>-9</v>
+        <v>-2813</v>
       </c>
       <c r="G61" t="n">
-        <v>-2649</v>
+        <v>35567</v>
       </c>
       <c r="H61" t="n">
-        <v>-188</v>
+        <v>1039</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>80</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M61" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>德昌</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-987</v>
+        <v>-1101</v>
       </c>
       <c r="D62" t="n">
-        <v>-729</v>
+        <v>-883</v>
       </c>
       <c r="E62" t="n">
-        <v>-6261</v>
+        <v>-501</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -3523,7 +3535,7 @@
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>1747</v>
+        <v>-19</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3536,45 +3548,45 @@
         </is>
       </c>
       <c r="K62" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M62" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-119</v>
+        <v>-386</v>
       </c>
       <c r="D63" t="n">
-        <v>-731</v>
+        <v>-900</v>
       </c>
       <c r="E63" t="n">
-        <v>-2966</v>
+        <v>-1515</v>
       </c>
       <c r="F63" t="n">
-        <v>5</v>
+        <v>180</v>
       </c>
       <c r="G63" t="n">
-        <v>-111</v>
+        <v>940</v>
       </c>
       <c r="H63" t="n">
-        <v>-139</v>
+        <v>-51</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3587,45 +3599,45 @@
         </is>
       </c>
       <c r="K63" t="n">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>152</v>
+        <v>-5166</v>
       </c>
       <c r="D64" t="n">
-        <v>-864</v>
+        <v>-961</v>
       </c>
       <c r="E64" t="n">
-        <v>2222</v>
+        <v>-13349</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="H64" t="n">
-        <v>185</v>
+        <v>-119</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3638,45 +3650,45 @@
         </is>
       </c>
       <c r="K64" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M64" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-580</v>
+        <v>124</v>
       </c>
       <c r="D65" t="n">
-        <v>-901</v>
+        <v>-978</v>
       </c>
       <c r="E65" t="n">
-        <v>-1550</v>
+        <v>2237</v>
       </c>
       <c r="F65" t="n">
-        <v>323</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>971</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-54</v>
+        <v>150</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3685,11 +3697,11 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K65" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -3697,7 +3709,7 @@
         </is>
       </c>
       <c r="M65" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="66">
@@ -3712,13 +3724,13 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-169</v>
+        <v>-55</v>
       </c>
       <c r="D66" t="n">
-        <v>-928</v>
+        <v>-980</v>
       </c>
       <c r="E66" t="n">
-        <v>-2683</v>
+        <v>-2721</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
@@ -3727,7 +3739,7 @@
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-210</v>
+        <v>-249</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3763,22 +3775,22 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-783</v>
+        <v>-735</v>
       </c>
       <c r="D67" t="n">
-        <v>-1004</v>
+        <v>-1040</v>
       </c>
       <c r="E67" t="n">
-        <v>-96</v>
+        <v>-108</v>
       </c>
       <c r="F67" t="n">
-        <v>82</v>
+        <v>35</v>
       </c>
       <c r="G67" t="n">
-        <v>116</v>
+        <v>87</v>
       </c>
       <c r="H67" t="n">
-        <v>20</v>
+        <v>-313</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3805,31 +3817,31 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-1471</v>
+        <v>553</v>
       </c>
       <c r="D68" t="n">
-        <v>-1523</v>
+        <v>-1090</v>
       </c>
       <c r="E68" t="n">
-        <v>-2784</v>
+        <v>-5934</v>
       </c>
       <c r="F68" t="n">
-        <v>-54</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-209</v>
+        <v>1915</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3838,49 +3850,49 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K68" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M68" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-1280</v>
+        <v>-1804</v>
       </c>
       <c r="D69" t="n">
-        <v>-1799</v>
+        <v>-1227</v>
       </c>
       <c r="E69" t="n">
-        <v>-2860</v>
+        <v>2758</v>
       </c>
       <c r="F69" t="n">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>376</v>
+        <v>445</v>
       </c>
       <c r="H69" t="n">
-        <v>-420</v>
+        <v>-677</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3889,11 +3901,11 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K69" t="n">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -3901,37 +3913,37 @@
         </is>
       </c>
       <c r="M69" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-2975</v>
+        <v>-1086</v>
       </c>
       <c r="D70" t="n">
-        <v>-1819</v>
+        <v>-1348</v>
       </c>
       <c r="E70" t="n">
-        <v>4147</v>
+        <v>-9165</v>
       </c>
       <c r="F70" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
       <c r="G70" t="n">
-        <v>-5</v>
+        <v>91</v>
       </c>
       <c r="H70" t="n">
-        <v>-14</v>
+        <v>-723</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3944,7 +3956,7 @@
         </is>
       </c>
       <c r="K70" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -3952,92 +3964,80 @@
         </is>
       </c>
       <c r="M70" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-1828</v>
+        <v>-1165</v>
       </c>
       <c r="D71" t="n">
-        <v>-2083</v>
+        <v>-1533</v>
       </c>
       <c r="E71" t="n">
-        <v>2487</v>
+        <v>-2239</v>
       </c>
       <c r="F71" t="n">
-        <v>-1</v>
+        <v>52</v>
       </c>
       <c r="G71" t="n">
-        <v>444</v>
+        <v>-1588</v>
       </c>
       <c r="H71" t="n">
-        <v>-656</v>
+        <v>-182</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K71" t="n">
-        <v>64</v>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>🐌 龜速</t>
-        </is>
-      </c>
-      <c r="M71" t="n">
-        <v>0</v>
-      </c>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>玉晶光</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-643</v>
+        <v>-316</v>
       </c>
       <c r="D72" t="n">
-        <v>-2161</v>
+        <v>-1689</v>
       </c>
       <c r="E72" t="n">
-        <v>-13606</v>
+        <v>-753</v>
       </c>
       <c r="F72" t="n">
-        <v>-214</v>
+        <v>-143</v>
       </c>
       <c r="G72" t="n">
-        <v>5069</v>
+        <v>-1395</v>
       </c>
       <c r="H72" t="n">
-        <v>95</v>
+        <v>-393</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🟡 中性</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4046,11 +4046,11 @@
         </is>
       </c>
       <c r="K72" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M72" t="n">
@@ -4060,35 +4060,35 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>全友</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-821</v>
+        <v>-1837</v>
       </c>
       <c r="D73" t="n">
-        <v>-2468</v>
+        <v>-1883</v>
       </c>
       <c r="E73" t="n">
-        <v>-8714</v>
+        <v>4272</v>
       </c>
       <c r="F73" t="n">
-        <v>5</v>
+        <v>-3</v>
       </c>
       <c r="G73" t="n">
-        <v>90</v>
+        <v>-7</v>
       </c>
       <c r="H73" t="n">
-        <v>-571</v>
+        <v>11</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🟡 中性</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="K73" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -4105,88 +4105,88 @@
         </is>
       </c>
       <c r="M73" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>-5084</v>
+        <v>-1811</v>
       </c>
       <c r="D74" t="n">
-        <v>-2486</v>
+        <v>-1950</v>
       </c>
       <c r="E74" t="n">
-        <v>-13041</v>
+        <v>-3414</v>
       </c>
       <c r="F74" t="n">
+        <v>232</v>
+      </c>
+      <c r="G74" t="n">
+        <v>369</v>
+      </c>
+      <c r="H74" t="n">
+        <v>-455</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>90</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M74" t="n">
         <v>-1</v>
-      </c>
-      <c r="G74" t="n">
-        <v>-7</v>
-      </c>
-      <c r="H74" t="n">
-        <v>-136</v>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>🟠 減碼</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K74" t="n">
-        <v>79</v>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>🛬 穩定</t>
-        </is>
-      </c>
-      <c r="M74" t="n">
-        <v>-2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>-698</v>
+        <v>-1379</v>
       </c>
       <c r="D75" t="n">
-        <v>-2698</v>
+        <v>-2483</v>
       </c>
       <c r="E75" t="n">
-        <v>-939</v>
+        <v>-2987</v>
       </c>
       <c r="F75" t="n">
-        <v>101</v>
+        <v>-57</v>
       </c>
       <c r="G75" t="n">
-        <v>-1499</v>
+        <v>-55</v>
       </c>
       <c r="H75" t="n">
-        <v>-498</v>
+        <v>-254</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -4195,49 +4195,49 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K75" t="n">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M75" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>鈊象</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-1982</v>
+        <v>-1366</v>
       </c>
       <c r="D76" t="n">
-        <v>-3399</v>
+        <v>-3063</v>
       </c>
       <c r="E76" t="n">
-        <v>-2846</v>
+        <v>-13844</v>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>-247</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>5228</v>
       </c>
       <c r="H76" t="n">
-        <v>338</v>
+        <v>41</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -4246,100 +4246,100 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K76" t="n">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M76" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-885</v>
+        <v>54</v>
       </c>
       <c r="D77" t="n">
-        <v>-3485</v>
+        <v>-3194</v>
       </c>
       <c r="E77" t="n">
-        <v>-3844</v>
+        <v>-4512</v>
       </c>
       <c r="F77" t="n">
-        <v>-203</v>
+        <v>-382</v>
       </c>
       <c r="G77" t="n">
-        <v>-307</v>
+        <v>2045</v>
       </c>
       <c r="H77" t="n">
+        <v>-466</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>🟠 減碼</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
         <v>52</v>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>🟠 減碼</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K77" t="n">
-        <v>64</v>
-      </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M77" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-53</v>
+        <v>-495</v>
       </c>
       <c r="D78" t="n">
-        <v>-3610</v>
+        <v>-3251</v>
       </c>
       <c r="E78" t="n">
-        <v>-4469</v>
+        <v>-3823</v>
       </c>
       <c r="F78" t="n">
-        <v>-436</v>
+        <v>-222</v>
       </c>
       <c r="G78" t="n">
-        <v>2182</v>
+        <v>-298</v>
       </c>
       <c r="H78" t="n">
-        <v>-441</v>
+        <v>50</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -4352,15 +4352,15 @@
         </is>
       </c>
       <c r="K78" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M78" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4375,22 +4375,22 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-182</v>
+        <v>-144</v>
       </c>
       <c r="D79" t="n">
-        <v>-3842</v>
+        <v>-3659</v>
       </c>
       <c r="E79" t="n">
-        <v>-12792</v>
+        <v>-12992</v>
       </c>
       <c r="F79" t="n">
-        <v>-16</v>
+        <v>-21</v>
       </c>
       <c r="G79" t="n">
-        <v>-929</v>
+        <v>-932</v>
       </c>
       <c r="H79" t="n">
-        <v>-165</v>
+        <v>-234</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -4417,31 +4417,31 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>-846</v>
+        <v>-1690</v>
       </c>
       <c r="D80" t="n">
-        <v>-4078</v>
+        <v>-3778</v>
       </c>
       <c r="E80" t="n">
-        <v>-14854</v>
+        <v>-2962</v>
       </c>
       <c r="F80" t="n">
-        <v>269</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>674</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>1</v>
+        <v>351</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -4450,15 +4450,15 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K80" t="n">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M80" t="n">
@@ -4468,31 +4468,31 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-1230</v>
+        <v>313</v>
       </c>
       <c r="D81" t="n">
-        <v>-4153</v>
+        <v>-3937</v>
       </c>
       <c r="E81" t="n">
-        <v>-7617</v>
+        <v>-4956</v>
       </c>
       <c r="F81" t="n">
-        <v>8</v>
+        <v>379</v>
       </c>
       <c r="G81" t="n">
-        <v>2</v>
+        <v>942</v>
       </c>
       <c r="H81" t="n">
-        <v>-263</v>
+        <v>-96</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4501,49 +4501,49 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K81" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-2315</v>
+        <v>659</v>
       </c>
       <c r="D82" t="n">
-        <v>-4191</v>
+        <v>-3962</v>
       </c>
       <c r="E82" t="n">
-        <v>-2060</v>
+        <v>-11613</v>
       </c>
       <c r="F82" t="n">
-        <v>398</v>
+        <v>-1</v>
       </c>
       <c r="G82" t="n">
-        <v>34</v>
+        <v>-216</v>
       </c>
       <c r="H82" t="n">
-        <v>222</v>
+        <v>-428</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -4552,49 +4552,49 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K82" t="n">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M82" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-590</v>
+        <v>-287</v>
       </c>
       <c r="D83" t="n">
-        <v>-4238</v>
+        <v>-4024</v>
       </c>
       <c r="E83" t="n">
-        <v>-6831</v>
+        <v>-14726</v>
       </c>
       <c r="F83" t="n">
-        <v>911</v>
+        <v>164</v>
       </c>
       <c r="G83" t="n">
-        <v>3010</v>
+        <v>669</v>
       </c>
       <c r="H83" t="n">
-        <v>-92</v>
+        <v>66</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -4607,45 +4607,45 @@
         </is>
       </c>
       <c r="K83" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M83" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>624</v>
+        <v>-524</v>
       </c>
       <c r="D84" t="n">
-        <v>-4465</v>
+        <v>-4098</v>
       </c>
       <c r="E84" t="n">
-        <v>-11639</v>
+        <v>-7543</v>
       </c>
       <c r="F84" t="n">
-        <v>-2</v>
+        <v>6</v>
       </c>
       <c r="G84" t="n">
-        <v>-217</v>
+        <v>2</v>
       </c>
       <c r="H84" t="n">
-        <v>-452</v>
+        <v>-366</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -4654,49 +4654,49 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K84" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M84" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>254</v>
+        <v>-325</v>
       </c>
       <c r="D85" t="n">
-        <v>-4522</v>
+        <v>-4165</v>
       </c>
       <c r="E85" t="n">
-        <v>-5032</v>
+        <v>-6809</v>
       </c>
       <c r="F85" t="n">
-        <v>353</v>
+        <v>710</v>
       </c>
       <c r="G85" t="n">
-        <v>895</v>
+        <v>3031</v>
       </c>
       <c r="H85" t="n">
-        <v>-102</v>
+        <v>-152</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -4709,45 +4709,45 @@
         </is>
       </c>
       <c r="K85" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M85" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-583</v>
+        <v>-647</v>
       </c>
       <c r="D86" t="n">
-        <v>-4564</v>
+        <v>-4185</v>
       </c>
       <c r="E86" t="n">
-        <v>-5407</v>
+        <v>-2849</v>
       </c>
       <c r="F86" t="n">
-        <v>-0</v>
+        <v>2007</v>
       </c>
       <c r="G86" t="n">
-        <v>-0</v>
+        <v>7197</v>
       </c>
       <c r="H86" t="n">
-        <v>-593</v>
+        <v>54</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -4756,15 +4756,15 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K86" t="n">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M86" t="n">
@@ -4774,31 +4774,31 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>-1641</v>
+        <v>-2114</v>
       </c>
       <c r="D87" t="n">
-        <v>-4695</v>
+        <v>-4502</v>
       </c>
       <c r="E87" t="n">
-        <v>-3681</v>
+        <v>-2059</v>
       </c>
       <c r="F87" t="n">
-        <v>1820</v>
+        <v>627</v>
       </c>
       <c r="G87" t="n">
-        <v>6887</v>
+        <v>-216</v>
       </c>
       <c r="H87" t="n">
-        <v>35</v>
+        <v>284</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -4807,49 +4807,49 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K87" t="n">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M87" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>-3617</v>
+        <v>-2549</v>
       </c>
       <c r="D88" t="n">
-        <v>-5166</v>
+        <v>-4579</v>
       </c>
       <c r="E88" t="n">
-        <v>-9548</v>
+        <v>-9009</v>
       </c>
       <c r="F88" t="n">
-        <v>166</v>
+        <v>-32</v>
       </c>
       <c r="G88" t="n">
-        <v>-12068</v>
+        <v>4809</v>
       </c>
       <c r="H88" t="n">
-        <v>-53</v>
+        <v>-869</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -4858,49 +4858,49 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K88" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M88" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-3145</v>
+        <v>-3174</v>
       </c>
       <c r="D89" t="n">
-        <v>-5385</v>
+        <v>-4741</v>
       </c>
       <c r="E89" t="n">
-        <v>-8404</v>
+        <v>-10174</v>
       </c>
       <c r="F89" t="n">
-        <v>456</v>
+        <v>-495</v>
       </c>
       <c r="G89" t="n">
-        <v>5124</v>
+        <v>-11773</v>
       </c>
       <c r="H89" t="n">
-        <v>-1003</v>
+        <v>41</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4909,49 +4909,49 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K89" t="n">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M89" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1175</v>
+        <v>-987</v>
       </c>
       <c r="D90" t="n">
-        <v>-6012</v>
+        <v>-4891</v>
       </c>
       <c r="E90" t="n">
-        <v>-6482</v>
+        <v>-5540</v>
       </c>
       <c r="F90" t="n">
-        <v>919</v>
+        <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>-887</v>
+        <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>-1218</v>
+        <v>-742</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -4960,15 +4960,15 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K90" t="n">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M90" t="n">
@@ -4978,103 +4978,103 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>-1581</v>
+        <v>703</v>
       </c>
       <c r="D91" t="n">
-        <v>-11734</v>
+        <v>-5013</v>
       </c>
       <c r="E91" t="n">
-        <v>-84242</v>
+        <v>-6957</v>
       </c>
       <c r="F91" t="n">
-        <v>-9607</v>
+        <v>347</v>
       </c>
       <c r="G91" t="n">
-        <v>-3432</v>
+        <v>-863</v>
       </c>
       <c r="H91" t="n">
-        <v>-6551</v>
+        <v>-1293</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>🔴 大賣</t>
+          <t>🟠 減碼</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K91" t="n">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>36046</v>
+        <v>-7529</v>
       </c>
       <c r="D92" t="n">
-        <v>-13876</v>
+        <v>-7899</v>
       </c>
       <c r="E92" t="n">
-        <v>28025</v>
+        <v>-86713</v>
       </c>
       <c r="F92" t="n">
-        <v>1489</v>
+        <v>-8022</v>
       </c>
       <c r="G92" t="n">
-        <v>39198</v>
+        <v>-6323</v>
       </c>
       <c r="H92" t="n">
-        <v>1024</v>
+        <v>-5190</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>🔴 大賣</t>
+          <t>🟠 減碼</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K92" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M92" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -5089,22 +5089,22 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>-2778</v>
+        <v>-1886</v>
       </c>
       <c r="D93" t="n">
-        <v>-14069</v>
+        <v>-13564</v>
       </c>
       <c r="E93" t="n">
-        <v>-27278</v>
+        <v>-26201</v>
       </c>
       <c r="F93" t="n">
-        <v>1006</v>
+        <v>-354</v>
       </c>
       <c r="G93" t="n">
-        <v>9963</v>
+        <v>8666</v>
       </c>
       <c r="H93" t="n">
-        <v>672</v>
+        <v>463</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -5140,22 +5140,22 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1037</v>
+        <v>1189</v>
       </c>
       <c r="D94" t="n">
-        <v>-18808</v>
+        <v>-17119</v>
       </c>
       <c r="E94" t="n">
-        <v>-34163</v>
+        <v>-34235</v>
       </c>
       <c r="F94" t="n">
-        <v>-116</v>
+        <v>-710</v>
       </c>
       <c r="G94" t="n">
-        <v>22837</v>
+        <v>22235</v>
       </c>
       <c r="H94" t="n">
-        <v>535</v>
+        <v>200</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -5191,22 +5191,22 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>-3479</v>
+        <v>-2982</v>
       </c>
       <c r="D95" t="n">
-        <v>-20982</v>
+        <v>-19622</v>
       </c>
       <c r="E95" t="n">
-        <v>-28423</v>
+        <v>-28976</v>
       </c>
       <c r="F95" t="n">
-        <v>569</v>
+        <v>1047</v>
       </c>
       <c r="G95" t="n">
-        <v>-10299</v>
+        <v>-8448</v>
       </c>
       <c r="H95" t="n">
-        <v>-2078</v>
+        <v>-1931</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -5242,22 +5242,22 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>-8743</v>
+        <v>-8811</v>
       </c>
       <c r="D96" t="n">
-        <v>-28557</v>
+        <v>-28949</v>
       </c>
       <c r="E96" t="n">
-        <v>-3433</v>
+        <v>-3669</v>
       </c>
       <c r="F96" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G96" t="n">
-        <v>12074</v>
+        <v>11293</v>
       </c>
       <c r="H96" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -5293,22 +5293,22 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>-18245</v>
+        <v>-12638</v>
       </c>
       <c r="D97" t="n">
-        <v>-36449</v>
+        <v>-35916</v>
       </c>
       <c r="E97" t="n">
-        <v>-290072</v>
+        <v>-287835</v>
       </c>
       <c r="F97" t="n">
-        <v>10513</v>
+        <v>7741</v>
       </c>
       <c r="G97" t="n">
-        <v>40043</v>
+        <v>37431</v>
       </c>
       <c r="H97" t="n">
-        <v>1477</v>
+        <v>-4742</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -5344,22 +5344,22 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-34707</v>
+        <v>-17333</v>
       </c>
       <c r="D98" t="n">
-        <v>-58910</v>
+        <v>-51843</v>
       </c>
       <c r="E98" t="n">
-        <v>36348</v>
+        <v>46169</v>
       </c>
       <c r="F98" t="n">
-        <v>14577</v>
+        <v>4990</v>
       </c>
       <c r="G98" t="n">
-        <v>48384</v>
+        <v>44556</v>
       </c>
       <c r="H98" t="n">
-        <v>13275</v>
+        <v>10924</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -5386,31 +5386,31 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>-11511</v>
+        <v>17715</v>
       </c>
       <c r="D99" t="n">
-        <v>-80992</v>
+        <v>-76879</v>
       </c>
       <c r="E99" t="n">
-        <v>130747</v>
+        <v>-124907</v>
       </c>
       <c r="F99" t="n">
-        <v>12279</v>
+        <v>591</v>
       </c>
       <c r="G99" t="n">
-        <v>67715</v>
+        <v>31913</v>
       </c>
       <c r="H99" t="n">
-        <v>258</v>
+        <v>-8949</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="K99" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -5431,37 +5431,37 @@
         </is>
       </c>
       <c r="M99" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>-9387</v>
+        <v>-34852</v>
       </c>
       <c r="D100" t="n">
-        <v>-93191</v>
+        <v>-104581</v>
       </c>
       <c r="E100" t="n">
-        <v>-138516</v>
+        <v>-253567</v>
       </c>
       <c r="F100" t="n">
-        <v>1870</v>
+        <v>2346</v>
       </c>
       <c r="G100" t="n">
-        <v>32517</v>
+        <v>5121</v>
       </c>
       <c r="H100" t="n">
-        <v>-9120</v>
+        <v>11583</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -5470,49 +5470,49 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K100" t="n">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M100" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-34792</v>
+        <v>-30700</v>
       </c>
       <c r="D101" t="n">
-        <v>-107243</v>
+        <v>-107070</v>
       </c>
       <c r="E101" t="n">
-        <v>-249352</v>
+        <v>108816</v>
       </c>
       <c r="F101" t="n">
-        <v>2548</v>
+        <v>10815</v>
       </c>
       <c r="G101" t="n">
-        <v>4275</v>
+        <v>64104</v>
       </c>
       <c r="H101" t="n">
-        <v>11417</v>
+        <v>-402</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -5521,19 +5521,19 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K101" t="n">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M101" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102">
@@ -5548,22 +5548,22 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>6681</v>
+        <v>17328</v>
       </c>
       <c r="D102" t="n">
-        <v>-157924</v>
+        <v>-153926</v>
       </c>
       <c r="E102" t="n">
-        <v>-170816</v>
+        <v>-162330</v>
       </c>
       <c r="F102" t="n">
-        <v>5154</v>
+        <v>3248</v>
       </c>
       <c r="G102" t="n">
-        <v>149886</v>
+        <v>152844</v>
       </c>
       <c r="H102" t="n">
-        <v>3812</v>
+        <v>3817</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -5599,22 +5599,22 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>-3140</v>
+        <v>6972</v>
       </c>
       <c r="D103" t="n">
-        <v>-185608</v>
+        <v>-165187</v>
       </c>
       <c r="E103" t="n">
-        <v>-105995</v>
+        <v>-95342</v>
       </c>
       <c r="F103" t="n">
-        <v>-952</v>
+        <v>-7567</v>
       </c>
       <c r="G103" t="n">
-        <v>72862</v>
+        <v>64985</v>
       </c>
       <c r="H103" t="n">
-        <v>-4138</v>
+        <v>-4677</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -5650,22 +5650,22 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>3714</v>
+        <v>11105</v>
       </c>
       <c r="D104" t="n">
-        <v>-217678</v>
+        <v>-203750</v>
       </c>
       <c r="E104" t="n">
-        <v>353832</v>
+        <v>360531</v>
       </c>
       <c r="F104" t="n">
-        <v>1542</v>
+        <v>-666</v>
       </c>
       <c r="G104" t="n">
-        <v>7096</v>
+        <v>6636</v>
       </c>
       <c r="H104" t="n">
-        <v>-1945</v>
+        <v>-15</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -5701,22 +5701,22 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>-1099</v>
+        <v>-16969</v>
       </c>
       <c r="D105" t="n">
-        <v>-297527</v>
+        <v>-296018</v>
       </c>
       <c r="E105" t="n">
-        <v>-1731</v>
+        <v>-9218</v>
       </c>
       <c r="F105" t="n">
-        <v>-13189</v>
+        <v>-4328</v>
       </c>
       <c r="G105" t="n">
-        <v>96253</v>
+        <v>87932</v>
       </c>
       <c r="H105" t="n">
-        <v>-382</v>
+        <v>-705</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -5751,7 +5751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5794,145 +5794,145 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -291 千股)</t>
+          <t>📉 20d 巨變(減碼 -57 千股)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>600660</v>
+        <v>867932</v>
       </c>
       <c r="D2" t="n">
-        <v>2537419</v>
+        <v>311094</v>
       </c>
       <c r="E2" t="n">
-        <v>706964</v>
+        <v>768195</v>
       </c>
       <c r="F2" t="n">
-        <v>2828466</v>
+        <v>368366</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>勤誠</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 2,856 千股)</t>
+          <t>📉 20d 巨變(減碼 -547 千股)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-3144712</v>
+        <v>448183</v>
       </c>
       <c r="D3" t="n">
-        <v>-5385312</v>
+        <v>1990651</v>
       </c>
       <c r="E3" t="n">
-        <v>-4456287</v>
+        <v>600660</v>
       </c>
       <c r="F3" t="n">
-        <v>-8241230</v>
+        <v>2537419</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>健策</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -703 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,540 千股)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-40062</v>
+        <v>-1178698</v>
       </c>
       <c r="D4" t="n">
-        <v>-418276</v>
+        <v>356519</v>
       </c>
       <c r="E4" t="n">
-        <v>-331149</v>
+        <v>-63563</v>
       </c>
       <c r="F4" t="n">
-        <v>285198</v>
+        <v>1896320</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>奇鋐</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 35 千股)</t>
+          <t>📈 20d 巨變(加碼 806 千股)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-63563</v>
+        <v>-2549347</v>
       </c>
       <c r="D5" t="n">
-        <v>1896320</v>
+        <v>-4579196</v>
       </c>
       <c r="E5" t="n">
-        <v>-629868</v>
+        <v>-3144712</v>
       </c>
       <c r="F5" t="n">
-        <v>1860939</v>
+        <v>-5385312</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>亞翔</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 420 千股)</t>
+          <t>📉 20d 巨變(減碼 -321 千股)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>768195</v>
+        <v>-463613</v>
       </c>
       <c r="D6" t="n">
-        <v>368366</v>
+        <v>-739593</v>
       </c>
       <c r="E6" t="n">
-        <v>373899</v>
+        <v>-40062</v>
       </c>
       <c r="F6" t="n">
-        <v>-51936</v>
+        <v>-418276</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>台光電</t>
         </is>
       </c>
     </row>
@@ -5944,20 +5944,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -469 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 160 千股)</t>
         </is>
       </c>
       <c r="C7" t="n">
+        <v>-35985</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2273023</v>
+      </c>
+      <c r="E7" t="n">
         <v>41794</v>
       </c>
-      <c r="D7" t="n">
+      <c r="F7" t="n">
         <v>2113080</v>
-      </c>
-      <c r="E7" t="n">
-        <v>265140</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2582206</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -5973,20 +5973,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -188 千股)</t>
+          <t>📉 20d 巨變(減碼 -98 千股)</t>
         </is>
       </c>
       <c r="C8" t="n">
+        <v>1031422</v>
+      </c>
+      <c r="D8" t="n">
+        <v>428998</v>
+      </c>
+      <c r="E8" t="n">
         <v>1145813</v>
       </c>
-      <c r="D8" t="n">
+      <c r="F8" t="n">
         <v>526605</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1722469</v>
-      </c>
-      <c r="F8" t="n">
-        <v>714824</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -5997,87 +5997,87 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -883 千股)</t>
+          <t>📈 20d 巨變(加碼 2,662 千股)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2562370</v>
+        <v>-34851569</v>
       </c>
       <c r="D9" t="n">
-        <v>5626073</v>
+        <v>-104580988</v>
       </c>
       <c r="E9" t="n">
-        <v>2595025</v>
+        <v>-34792005</v>
       </c>
       <c r="F9" t="n">
-        <v>6508636</v>
+        <v>-107243112</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -540 千股)</t>
+          <t>📉 20d 巨變(減碼 -2,013 千股)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-879318</v>
+        <v>187015</v>
       </c>
       <c r="D10" t="n">
-        <v>-636134</v>
+        <v>3612787</v>
       </c>
       <c r="E10" t="n">
-        <v>-1426377</v>
+        <v>2562370</v>
       </c>
       <c r="F10" t="n">
-        <v>-96055</v>
+        <v>5626073</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>致茂</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -11 千股)</t>
+          <t>📉 20d 巨變(減碼 -236 千股)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-579591</v>
+        <v>-373590</v>
       </c>
       <c r="D11" t="n">
-        <v>-901483</v>
+        <v>-872623</v>
       </c>
       <c r="E11" t="n">
-        <v>-497991</v>
+        <v>-879318</v>
       </c>
       <c r="F11" t="n">
-        <v>-890867</v>
+        <v>-636134</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>智邦</t>
         </is>
       </c>
     </row>
@@ -6089,20 +6089,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -207 千股)</t>
+          <t>📈 20d 巨變(加碼 55 千股)</t>
         </is>
       </c>
       <c r="C12" t="n">
+        <v>-524471</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-4097912</v>
+      </c>
+      <c r="E12" t="n">
         <v>-1229695</v>
       </c>
-      <c r="D12" t="n">
+      <c r="F12" t="n">
         <v>-4152705</v>
-      </c>
-      <c r="E12" t="n">
-        <v>-1771843</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-3945715</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -6113,87 +6113,87 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -3,045 千股)</t>
+          <t>📈 20d 巨變(加碼 1,360 千股)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-34792005</v>
+        <v>-2982018</v>
       </c>
       <c r="D13" t="n">
-        <v>-107243112</v>
+        <v>-19621911</v>
       </c>
       <c r="E13" t="n">
-        <v>-31281582</v>
+        <v>-3479292</v>
       </c>
       <c r="F13" t="n">
-        <v>-104197922</v>
+        <v>-20981578</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>台達電</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,265 千股)</t>
+          <t>📈 20d 巨變(加碼 356 千股)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-3479292</v>
+        <v>1809475</v>
       </c>
       <c r="D14" t="n">
-        <v>-20981578</v>
+        <v>2197283</v>
       </c>
       <c r="E14" t="n">
-        <v>-5272406</v>
+        <v>1436508</v>
       </c>
       <c r="F14" t="n">
-        <v>-19716087</v>
+        <v>1841138</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>帆宣</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 896 千股)</t>
+          <t>🟢 外資 5d 翻綠</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1436508</v>
+        <v>215439</v>
       </c>
       <c r="D15" t="n">
-        <v>1841138</v>
+        <v>2461006</v>
       </c>
       <c r="E15" t="n">
-        <v>1428643</v>
+        <v>-1417578</v>
       </c>
       <c r="F15" t="n">
-        <v>945337</v>
+        <v>2460649</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>健鼎</t>
         </is>
       </c>
     </row>
@@ -6205,20 +6205,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 262 千股)</t>
+          <t>📈 20d 巨變(加碼 388 千股)</t>
         </is>
       </c>
       <c r="C16" t="n">
+        <v>1051329</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1924701</v>
+      </c>
+      <c r="E16" t="n">
         <v>538888</v>
       </c>
-      <c r="D16" t="n">
+      <c r="F16" t="n">
         <v>1536416</v>
-      </c>
-      <c r="E16" t="n">
-        <v>112019</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1274055</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -6234,20 +6234,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 115 千股)</t>
+          <t>📉 20d 巨變(減碼 -960 千股)</t>
         </is>
       </c>
       <c r="C17" t="n">
+        <v>-1378822</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-2482843</v>
+      </c>
+      <c r="E17" t="n">
         <v>-1470748</v>
       </c>
-      <c r="D17" t="n">
+      <c r="F17" t="n">
         <v>-1523077</v>
-      </c>
-      <c r="E17" t="n">
-        <v>-1496965</v>
-      </c>
-      <c r="F17" t="n">
-        <v>-1638265</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -6263,20 +6263,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -219 千股)</t>
+          <t>📉 20d 巨變(減碼 -290 千股)</t>
         </is>
       </c>
       <c r="C18" t="n">
+        <v>-492705</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-480659</v>
+      </c>
+      <c r="E18" t="n">
         <v>-289767</v>
       </c>
-      <c r="D18" t="n">
+      <c r="F18" t="n">
         <v>-191029</v>
-      </c>
-      <c r="E18" t="n">
-        <v>-175968</v>
-      </c>
-      <c r="F18" t="n">
-        <v>28296</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -6287,87 +6287,87 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -2,565 千股)</t>
+          <t>📈 20d 巨變(加碼 510 千股)</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-1417578</v>
+        <v>-647109</v>
       </c>
       <c r="D19" t="n">
-        <v>2460649</v>
+        <v>-4185217</v>
       </c>
       <c r="E19" t="n">
-        <v>-2528250</v>
+        <v>-1640785</v>
       </c>
       <c r="F19" t="n">
-        <v>5025936</v>
+        <v>-4695178</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>崇越</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -400 千股)</t>
+          <t>📈 20d 巨變(加碼 1,689 千股)</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-1640785</v>
+        <v>1189163</v>
       </c>
       <c r="D20" t="n">
-        <v>-4695178</v>
+        <v>-17119142</v>
       </c>
       <c r="E20" t="n">
-        <v>-2295919</v>
+        <v>1036680</v>
       </c>
       <c r="F20" t="n">
-        <v>-4295306</v>
+        <v>-18807809</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>中興電</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 731 千股)</t>
+          <t>📈 20d 巨變(加碼 183 千股)</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1036680</v>
+        <v>-143519</v>
       </c>
       <c r="D21" t="n">
-        <v>-18807809</v>
+        <v>-3658741</v>
       </c>
       <c r="E21" t="n">
-        <v>-1165454</v>
+        <v>-181768</v>
       </c>
       <c r="F21" t="n">
-        <v>-19539272</v>
+        <v>-3841879</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>華城</t>
         </is>
       </c>
     </row>
@@ -6379,20 +6379,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -103 千股)</t>
+          <t>📈 20d 巨變(加碼 316 千股)</t>
         </is>
       </c>
       <c r="C22" t="n">
+        <v>693902</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-148978</v>
+      </c>
+      <c r="E22" t="n">
         <v>771717</v>
       </c>
-      <c r="D22" t="n">
+      <c r="F22" t="n">
         <v>-465035</v>
-      </c>
-      <c r="E22" t="n">
-        <v>357798</v>
-      </c>
-      <c r="F22" t="n">
-        <v>-362488</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -6403,203 +6403,203 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 785 千股)</t>
+          <t>📉 20d 巨變(減碼 -15 千股)</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-181768</v>
+        <v>805704</v>
       </c>
       <c r="D23" t="n">
-        <v>-3841879</v>
+        <v>1734575</v>
       </c>
       <c r="E23" t="n">
-        <v>-1096503</v>
+        <v>304375</v>
       </c>
       <c r="F23" t="n">
-        <v>-4626705</v>
+        <v>1749164</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>中砂</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 1,029 千股)</t>
+          <t>📉 20d 巨變(減碼 -311 千股)</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>304375</v>
+        <v>-2113585</v>
       </c>
       <c r="D24" t="n">
-        <v>1749164</v>
+        <v>-4501958</v>
       </c>
       <c r="E24" t="n">
-        <v>-689136</v>
+        <v>-2314701</v>
       </c>
       <c r="F24" t="n">
-        <v>720049</v>
+        <v>-4191243</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>大立光</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -899 千股)</t>
+          <t>📈 20d 巨變(加碼 23 千股)</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-2314701</v>
+        <v>-14900</v>
       </c>
       <c r="D25" t="n">
-        <v>-4191243</v>
+        <v>-70786</v>
       </c>
       <c r="E25" t="n">
-        <v>-933279</v>
+        <v>-14900</v>
       </c>
       <c r="F25" t="n">
-        <v>-3291981</v>
+        <v>-93786</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>大車隊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 37 千股)</t>
+          <t>📈 20d 巨變(加碼 343 千股)</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-14900</v>
+        <v>1580903</v>
       </c>
       <c r="D26" t="n">
-        <v>-93786</v>
+        <v>3994486</v>
       </c>
       <c r="E26" t="n">
-        <v>-10900</v>
+        <v>1106483</v>
       </c>
       <c r="F26" t="n">
-        <v>-130786</v>
+        <v>3651318</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>大車隊</t>
+          <t>零壹</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 617 千股)</t>
+          <t>📉 20d 巨變(減碼 -379 千股)</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1106483</v>
+        <v>-1690200</v>
       </c>
       <c r="D27" t="n">
-        <v>3651318</v>
+        <v>-3777823</v>
       </c>
       <c r="E27" t="n">
-        <v>945669</v>
+        <v>-1982199</v>
       </c>
       <c r="F27" t="n">
-        <v>3033996</v>
+        <v>-3398643</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>隆大</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -251 千股)</t>
+          <t>📈 20d 巨變(加碼 15 千股)</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-1982199</v>
+        <v>97579</v>
       </c>
       <c r="D28" t="n">
-        <v>-3398643</v>
+        <v>371883</v>
       </c>
       <c r="E28" t="n">
-        <v>-2433199</v>
+        <v>77419</v>
       </c>
       <c r="F28" t="n">
-        <v>-3147493</v>
+        <v>357073</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>崇友</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -6 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 454 千股)</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>77419</v>
+        <v>64670</v>
       </c>
       <c r="D29" t="n">
-        <v>357073</v>
+        <v>919628</v>
       </c>
       <c r="E29" t="n">
-        <v>82421</v>
+        <v>-662155</v>
       </c>
       <c r="F29" t="n">
-        <v>362755</v>
+        <v>465878</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>湧德</t>
         </is>
       </c>
     </row>
@@ -6611,20 +6611,20 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 614 千股)</t>
+          <t>📉 20d 巨變(減碼 -151 千股)</t>
         </is>
       </c>
       <c r="C30" t="n">
+        <v>-1811354</v>
+      </c>
+      <c r="D30" t="n">
+        <v>-1950045</v>
+      </c>
+      <c r="E30" t="n">
         <v>-1279934</v>
       </c>
-      <c r="D30" t="n">
+      <c r="F30" t="n">
         <v>-1798995</v>
-      </c>
-      <c r="E30" t="n">
-        <v>-1785884</v>
-      </c>
-      <c r="F30" t="n">
-        <v>-2412895</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -6635,145 +6635,145 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 34 千股)</t>
+          <t>📉 20d 巨變(減碼 -90 千股)</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-662155</v>
+        <v>-1184000</v>
       </c>
       <c r="D31" t="n">
-        <v>465878</v>
+        <v>-472754</v>
       </c>
       <c r="E31" t="n">
-        <v>-697694</v>
+        <v>-1358999</v>
       </c>
       <c r="F31" t="n">
-        <v>431636</v>
+        <v>-382854</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>合機</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 117 千股)</t>
+          <t>📉 20d 巨變(減碼 -148 千股)</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-1358999</v>
+        <v>2043151</v>
       </c>
       <c r="D32" t="n">
-        <v>-382854</v>
+        <v>107794</v>
       </c>
       <c r="E32" t="n">
-        <v>-1561999</v>
+        <v>1240471</v>
       </c>
       <c r="F32" t="n">
-        <v>-499499</v>
+        <v>256137</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>合機</t>
+          <t>卜蜂</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 74 千股)</t>
+          <t>📉 20d 巨變(減碼 -94,180 千股)</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1240471</v>
+        <v>169390686</v>
       </c>
       <c r="D33" t="n">
-        <v>256137</v>
+        <v>253317450</v>
       </c>
       <c r="E33" t="n">
-        <v>1516397</v>
+        <v>223295717</v>
       </c>
       <c r="F33" t="n">
-        <v>182037</v>
+        <v>347497749</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 18,239 千股)</t>
+          <t>📉 20d 巨變(減碼 -36 千股)</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>223295717</v>
+        <v>-734530</v>
       </c>
       <c r="D34" t="n">
-        <v>347497749</v>
+        <v>-1040316</v>
       </c>
       <c r="E34" t="n">
-        <v>213984721</v>
+        <v>-783396</v>
       </c>
       <c r="F34" t="n">
-        <v>329259102</v>
+        <v>-1004313</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>寶雅</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -339 千股)</t>
+          <t>📈 20d 巨變(加碼 1,814 千股)</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-783396</v>
+        <v>173371</v>
       </c>
       <c r="D35" t="n">
-        <v>-1004313</v>
+        <v>2162782</v>
       </c>
       <c r="E35" t="n">
-        <v>-488500</v>
+        <v>239812</v>
       </c>
       <c r="F35" t="n">
-        <v>-664967</v>
+        <v>348862</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>寶雅</t>
+          <t>豐藝</t>
         </is>
       </c>
     </row>
@@ -6785,20 +6785,20 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 56 千股)</t>
+          <t>📈 20d 巨變(加碼 444 千股)</t>
         </is>
       </c>
       <c r="C36" t="n">
+        <v>1037277</v>
+      </c>
+      <c r="D36" t="n">
+        <v>569645</v>
+      </c>
+      <c r="E36" t="n">
         <v>591511</v>
       </c>
-      <c r="D36" t="n">
+      <c r="F36" t="n">
         <v>125888</v>
-      </c>
-      <c r="E36" t="n">
-        <v>572670</v>
-      </c>
-      <c r="F36" t="n">
-        <v>70047</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -6809,435 +6809,435 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -198 千股)</t>
+          <t>📉 20d 巨變(減碼 -21 千股)</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>239812</v>
+        <v>-83710</v>
       </c>
       <c r="D37" t="n">
-        <v>348862</v>
+        <v>55974</v>
       </c>
       <c r="E37" t="n">
-        <v>225150</v>
+        <v>-126066</v>
       </c>
       <c r="F37" t="n">
-        <v>546933</v>
+        <v>76874</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>智冠</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 47 千股)</t>
+          <t>📈 20d 巨變(加碼 341 千股)</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-126066</v>
+        <v>311985</v>
       </c>
       <c r="D38" t="n">
-        <v>76874</v>
+        <v>105332</v>
       </c>
       <c r="E38" t="n">
-        <v>-173368</v>
+        <v>113341</v>
       </c>
       <c r="F38" t="n">
-        <v>29420</v>
+        <v>-235479</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>智冠</t>
+          <t>穎崴</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 6 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 147 千股)</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-6000</v>
+        <v>35360</v>
       </c>
       <c r="D39" t="n">
-        <v>-11000</v>
+        <v>-181199</v>
       </c>
       <c r="E39" t="n">
-        <v>-6000</v>
+        <v>-169640</v>
       </c>
       <c r="F39" t="n">
-        <v>-17000</v>
+        <v>-328136</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>方土霖</t>
+          <t>八方雲集</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -97 千股)</t>
+          <t>📈 20d 巨變(加碼 251 千股)</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-169640</v>
+        <v>-118316</v>
       </c>
       <c r="D40" t="n">
-        <v>-328136</v>
+        <v>-480501</v>
       </c>
       <c r="E40" t="n">
-        <v>-234890</v>
+        <v>-119221</v>
       </c>
       <c r="F40" t="n">
-        <v>-231136</v>
+        <v>-731372</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>華景電</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 156 千股)</t>
+          <t>📈 20d 巨變(加碼 12,998 千股)</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-119221</v>
+        <v>56952446</v>
       </c>
       <c r="D41" t="n">
-        <v>-731372</v>
+        <v>-877656</v>
       </c>
       <c r="E41" t="n">
-        <v>-157136</v>
+        <v>36045928</v>
       </c>
       <c r="F41" t="n">
-        <v>-887055</v>
+        <v>-13875769</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>台灣大</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 92 千股)</t>
+          <t>📈 20d 巨變(加碼 6 千股)</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>113341</v>
+        <v>-16000</v>
       </c>
       <c r="D42" t="n">
-        <v>-235479</v>
+        <v>-159300</v>
       </c>
       <c r="E42" t="n">
-        <v>-2400</v>
+        <v>-28000</v>
       </c>
       <c r="F42" t="n">
-        <v>-327461</v>
+        <v>-165300</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>聯合</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,654 千股)</t>
+          <t>📈 20d 巨變(加碼 780 千股)</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>36045928</v>
+        <v>3420434</v>
       </c>
       <c r="D43" t="n">
-        <v>-13875769</v>
+        <v>188850</v>
       </c>
       <c r="E43" t="n">
-        <v>25203233</v>
+        <v>3552749</v>
       </c>
       <c r="F43" t="n">
-        <v>-12221307</v>
+        <v>-591043</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 93 千股)</t>
+          <t>📈 20d 巨變(加碼 1,525 千股)</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-28000</v>
+        <v>-5165772</v>
       </c>
       <c r="D44" t="n">
-        <v>-165300</v>
+        <v>-961059</v>
       </c>
       <c r="E44" t="n">
-        <v>-19000</v>
+        <v>-5083904</v>
       </c>
       <c r="F44" t="n">
-        <v>-258300</v>
+        <v>-2486333</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>聯合</t>
+          <t>亞力</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,786 千股)</t>
+          <t>📉 20d 巨變(減碼 -114 千股)</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3552749</v>
+        <v>123948</v>
       </c>
       <c r="D45" t="n">
-        <v>-591043</v>
+        <v>-978146</v>
       </c>
       <c r="E45" t="n">
-        <v>2786256</v>
+        <v>151560</v>
       </c>
       <c r="F45" t="n">
-        <v>-2377147</v>
+        <v>-864146</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>大綜</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -267 千股)</t>
+          <t>📈 20d 巨變(加碼 710 千股)</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-5083904</v>
+        <v>691474</v>
       </c>
       <c r="D46" t="n">
-        <v>-2486333</v>
+        <v>3104147</v>
       </c>
       <c r="E46" t="n">
-        <v>-5309213</v>
+        <v>102524</v>
       </c>
       <c r="F46" t="n">
-        <v>-2219578</v>
+        <v>2394154</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>漢科</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -110 千股)</t>
+          <t>📈 20d 巨變(加碼 2,511 千股)</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>151560</v>
+        <v>3984293</v>
       </c>
       <c r="D47" t="n">
-        <v>-864146</v>
+        <v>2947301</v>
       </c>
       <c r="E47" t="n">
-        <v>87120</v>
+        <v>1433661</v>
       </c>
       <c r="F47" t="n">
-        <v>-753706</v>
+        <v>436193</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>台燿</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -788 千股)</t>
+          <t>📉 20d 巨變(減碼 -785 千股)</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1433661</v>
+        <v>2733181</v>
       </c>
       <c r="D48" t="n">
-        <v>436193</v>
+        <v>367317</v>
       </c>
       <c r="E48" t="n">
-        <v>2002335</v>
+        <v>2794927</v>
       </c>
       <c r="F48" t="n">
-        <v>1223778</v>
+        <v>1151928</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>立隆電</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -331 千股)</t>
+          <t>📈 20d 巨變(加碼 1,009 千股)</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>102524</v>
+        <v>-316357</v>
       </c>
       <c r="D49" t="n">
-        <v>2394154</v>
+        <v>-1689156</v>
       </c>
       <c r="E49" t="n">
-        <v>-439468</v>
+        <v>-698120</v>
       </c>
       <c r="F49" t="n">
-        <v>2725398</v>
+        <v>-2698394</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>玉晶光</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 2,192 千股)</t>
+          <t>📈 20d 巨變(加碼 999 千股)</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2794927</v>
+        <v>703187</v>
       </c>
       <c r="D50" t="n">
-        <v>1151928</v>
+        <v>-5012967</v>
       </c>
       <c r="E50" t="n">
-        <v>6474065</v>
+        <v>1175412</v>
       </c>
       <c r="F50" t="n">
-        <v>-1039677</v>
+        <v>-6012208</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -3,879 千股)</t>
+          <t>📈 20d 巨變(加碼 234 千股)</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1175412</v>
+        <v>-495008</v>
       </c>
       <c r="D51" t="n">
-        <v>-6012208</v>
+        <v>-3250524</v>
       </c>
       <c r="E51" t="n">
-        <v>710474</v>
+        <v>-885429</v>
       </c>
       <c r="F51" t="n">
-        <v>-2133121</v>
+        <v>-3484933</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>世芯-KY</t>
         </is>
       </c>
     </row>
@@ -7249,20 +7249,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -4,598 千股)</t>
+          <t>📈 20d 巨變(加碼 3,835 千股)</t>
         </is>
       </c>
       <c r="C52" t="n">
+        <v>-7528529</v>
+      </c>
+      <c r="D52" t="n">
+        <v>-7899180</v>
+      </c>
+      <c r="E52" t="n">
         <v>-1581333</v>
       </c>
-      <c r="D52" t="n">
+      <c r="F52" t="n">
         <v>-11734354</v>
-      </c>
-      <c r="E52" t="n">
-        <v>13691296</v>
-      </c>
-      <c r="F52" t="n">
-        <v>-7136115</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -7273,290 +7273,290 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -140 千股)</t>
+          <t>📉 20d 巨變(減碼 -26,078 千股)</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-698120</v>
+        <v>-30700231</v>
       </c>
       <c r="D53" t="n">
-        <v>-2698394</v>
+        <v>-107069506</v>
       </c>
       <c r="E53" t="n">
-        <v>-172267</v>
+        <v>-11511118</v>
       </c>
       <c r="F53" t="n">
-        <v>-2558809</v>
+        <v>-80991566</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -39 千股)</t>
+          <t>📉 20d 巨變(減碼 -170 千股)</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-885429</v>
+        <v>-3754653</v>
       </c>
       <c r="D54" t="n">
-        <v>-3484933</v>
+        <v>36837450</v>
       </c>
       <c r="E54" t="n">
-        <v>-906305</v>
+        <v>-7339887</v>
       </c>
       <c r="F54" t="n">
-        <v>-3445921</v>
+        <v>37007447</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -42,086 千股)</t>
+          <t>📉 20d 巨變(減碼 -902 千股)</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>-11511118</v>
+        <v>-1365556</v>
       </c>
       <c r="D55" t="n">
-        <v>-80991566</v>
+        <v>-3063006</v>
       </c>
       <c r="E55" t="n">
-        <v>-19666599</v>
+        <v>-642704</v>
       </c>
       <c r="F55" t="n">
-        <v>-38905078</v>
+        <v>-2161050</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>鈊象</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 254 千股)</t>
+          <t>📈 20d 巨變(加碼 1,120 千股)</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-7339887</v>
+        <v>-1085784</v>
       </c>
       <c r="D56" t="n">
-        <v>37007447</v>
+        <v>-1348417</v>
       </c>
       <c r="E56" t="n">
-        <v>-14744880</v>
+        <v>-821364</v>
       </c>
       <c r="F56" t="n">
-        <v>36753211</v>
+        <v>-2468366</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>士電</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -354 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -361 千股)</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>-642704</v>
+        <v>552943</v>
       </c>
       <c r="D57" t="n">
-        <v>-2161050</v>
+        <v>-1089883</v>
       </c>
       <c r="E57" t="n">
-        <v>-148303</v>
+        <v>-986881</v>
       </c>
       <c r="F57" t="n">
-        <v>-1806601</v>
+        <v>-728960</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>鉅祥</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 25 千股)</t>
+          <t>📉 20d 巨變(減碼 -31 千股)</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-268910</v>
+        <v>-21429</v>
       </c>
       <c r="D58" t="n">
-        <v>-597040</v>
+        <v>-4133</v>
       </c>
       <c r="E58" t="n">
-        <v>-290950</v>
+        <v>-100509</v>
       </c>
       <c r="F58" t="n">
-        <v>-622221</v>
+        <v>26902</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>達欣工</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 4,325 千股)</t>
+          <t>📉 20d 巨變(減碼 -39 千股)</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>-986881</v>
+        <v>-109930</v>
       </c>
       <c r="D59" t="n">
-        <v>-728960</v>
+        <v>-636010</v>
       </c>
       <c r="E59" t="n">
-        <v>-1437169</v>
+        <v>-268910</v>
       </c>
       <c r="F59" t="n">
-        <v>-5054173</v>
+        <v>-597040</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>普萊德</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -180 千股)</t>
+          <t>📈 20d 巨變(加碼 307 千股)</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>-100509</v>
+        <v>512289</v>
       </c>
       <c r="D60" t="n">
-        <v>26902</v>
+        <v>1019064</v>
       </c>
       <c r="E60" t="n">
-        <v>-231647</v>
+        <v>277543</v>
       </c>
       <c r="F60" t="n">
-        <v>206433</v>
+        <v>711962</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>勝一</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 10 千股)</t>
+          <t>📉 20d 巨變(減碼 -140 千股)</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-821364</v>
+        <v>126141</v>
       </c>
       <c r="D61" t="n">
-        <v>-2468366</v>
+        <v>-290671</v>
       </c>
       <c r="E61" t="n">
-        <v>-1094692</v>
+        <v>167091</v>
       </c>
       <c r="F61" t="n">
-        <v>-2478848</v>
+        <v>-150616</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>信立</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 14 千股)</t>
+          <t>📈 20d 巨變(加碼 14 千股)</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>277543</v>
+        <v>510343</v>
       </c>
       <c r="D62" t="n">
-        <v>711962</v>
+        <v>628910</v>
       </c>
       <c r="E62" t="n">
-        <v>-384065</v>
+        <v>434323</v>
       </c>
       <c r="F62" t="n">
-        <v>698346</v>
+        <v>615070</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>勝一</t>
+          <t>祥碩</t>
         </is>
       </c>
     </row>
@@ -7568,20 +7568,20 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 157 千股)</t>
+          <t>📈 20d 巨變(加碼 14 千股)</t>
         </is>
       </c>
       <c r="C63" t="n">
+        <v>437797</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1442046</v>
+      </c>
+      <c r="E63" t="n">
         <v>356135</v>
       </c>
-      <c r="D63" t="n">
+      <c r="F63" t="n">
         <v>1428014</v>
-      </c>
-      <c r="E63" t="n">
-        <v>459167</v>
-      </c>
-      <c r="F63" t="n">
-        <v>1271079</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -7592,29 +7592,29 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -220 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,765 千股)</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>434323</v>
+        <v>-2265526</v>
       </c>
       <c r="D64" t="n">
-        <v>615070</v>
+        <v>592978</v>
       </c>
       <c r="E64" t="n">
-        <v>586183</v>
+        <v>-1560612</v>
       </c>
       <c r="F64" t="n">
-        <v>835003</v>
+        <v>2358053</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>藥華藥</t>
         </is>
       </c>
     </row>
@@ -7626,20 +7626,20 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 11 千股)</t>
+          <t>📈 20d 巨變(加碼 1,276 千股)</t>
         </is>
       </c>
       <c r="C65" t="n">
+        <v>2789825</v>
+      </c>
+      <c r="D65" t="n">
+        <v>2699829</v>
+      </c>
+      <c r="E65" t="n">
         <v>1318451</v>
       </c>
-      <c r="D65" t="n">
+      <c r="F65" t="n">
         <v>1423955</v>
-      </c>
-      <c r="E65" t="n">
-        <v>804593</v>
-      </c>
-      <c r="F65" t="n">
-        <v>1413209</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -7650,203 +7650,203 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -833 千股)</t>
+          <t>📈 20d 巨變(加碼 54 千股)</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-1560612</v>
+        <v>-286937</v>
       </c>
       <c r="D66" t="n">
-        <v>2358053</v>
+        <v>-4024104</v>
       </c>
       <c r="E66" t="n">
-        <v>-1556382</v>
+        <v>-845634</v>
       </c>
       <c r="F66" t="n">
-        <v>3190619</v>
+        <v>-4077792</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>宇瞻</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 86 千股)</t>
+          <t>📈 20d 巨變(加碼 855 千股)</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>167091</v>
+        <v>-1803760</v>
       </c>
       <c r="D67" t="n">
-        <v>-150616</v>
+        <v>-1227153</v>
       </c>
       <c r="E67" t="n">
-        <v>-223750</v>
+        <v>-1827913</v>
       </c>
       <c r="F67" t="n">
-        <v>-236457</v>
+        <v>-2082595</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>聯鈞</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -221 千股)</t>
+          <t>📈 20d 巨變(加碼 533 千股)</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-1827913</v>
+        <v>-12638431</v>
       </c>
       <c r="D68" t="n">
-        <v>-2082595</v>
+        <v>-35915687</v>
       </c>
       <c r="E68" t="n">
-        <v>-244190</v>
+        <v>-18245071</v>
       </c>
       <c r="F68" t="n">
-        <v>-1861101</v>
+        <v>-36448543</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -417 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 20,421 千股)</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-948375</v>
+        <v>6972004</v>
       </c>
       <c r="D69" t="n">
-        <v>766608</v>
+        <v>-165187385</v>
       </c>
       <c r="E69" t="n">
-        <v>-614319</v>
+        <v>-3140336</v>
       </c>
       <c r="F69" t="n">
-        <v>1183786</v>
+        <v>-185608049</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,040 千股)</t>
+          <t>📈 20d 巨變(加碼 430 千股)</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-845634</v>
+        <v>-888600</v>
       </c>
       <c r="D70" t="n">
-        <v>-4077792</v>
+        <v>1196384</v>
       </c>
       <c r="E70" t="n">
-        <v>-1965857</v>
+        <v>-948375</v>
       </c>
       <c r="F70" t="n">
-        <v>-5117766</v>
+        <v>766608</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>聯亞</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 10,904 千股)</t>
+          <t>📈 20d 巨變(加碼 934 千股)</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-3140336</v>
+        <v>2422313</v>
       </c>
       <c r="D71" t="n">
-        <v>-185608049</v>
+        <v>37228026</v>
       </c>
       <c r="E71" t="n">
-        <v>-13780172</v>
+        <v>1170830</v>
       </c>
       <c r="F71" t="n">
-        <v>-196512336</v>
+        <v>36294471</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -3,057 千股)</t>
+          <t>📉 20d 巨變(減碼 -236 千股)</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-18245071</v>
+        <v>-1101301</v>
       </c>
       <c r="D72" t="n">
-        <v>-36448543</v>
+        <v>-883225</v>
       </c>
       <c r="E72" t="n">
-        <v>-18618023</v>
+        <v>-927748</v>
       </c>
       <c r="F72" t="n">
-        <v>-33391928</v>
+        <v>-647165</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>德昌</t>
         </is>
       </c>
     </row>
@@ -7858,20 +7858,20 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,795 千股)</t>
+          <t>📈 20d 巨變(加碼 505 千股)</t>
         </is>
       </c>
       <c r="C73" t="n">
+        <v>-1886345</v>
+      </c>
+      <c r="D73" t="n">
+        <v>-13564402</v>
+      </c>
+      <c r="E73" t="n">
         <v>-2778419</v>
       </c>
-      <c r="D73" t="n">
+      <c r="F73" t="n">
         <v>-14069374</v>
-      </c>
-      <c r="E73" t="n">
-        <v>-3032354</v>
-      </c>
-      <c r="F73" t="n">
-        <v>-12274112</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -7882,667 +7882,667 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 1,359 千股)</t>
+          <t>📉 20d 巨變(減碼 -393 千股)</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1170830</v>
+        <v>-8811198</v>
       </c>
       <c r="D74" t="n">
-        <v>36294471</v>
+        <v>-28949458</v>
       </c>
       <c r="E74" t="n">
-        <v>-3967492</v>
+        <v>-8742903</v>
       </c>
       <c r="F74" t="n">
-        <v>34935536</v>
+        <v>-28556740</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>台汽電</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -341 千股)</t>
+          <t>📉 20d 巨變(減碼 -52 千股)</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>-927748</v>
+        <v>-55000</v>
       </c>
       <c r="D75" t="n">
-        <v>-647165</v>
+        <v>-980229</v>
       </c>
       <c r="E75" t="n">
-        <v>-957327</v>
+        <v>-169000</v>
       </c>
       <c r="F75" t="n">
-        <v>-305744</v>
+        <v>-928229</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>德昌</t>
+          <t>億泰</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -5,466 千股)</t>
+          <t>📈 20d 巨變(加碼 360 千股)</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-8742903</v>
+        <v>54048</v>
       </c>
       <c r="D76" t="n">
-        <v>-28556740</v>
+        <v>242654</v>
       </c>
       <c r="E76" t="n">
-        <v>-5763419</v>
+        <v>24048</v>
       </c>
       <c r="F76" t="n">
-        <v>-23090306</v>
+        <v>-117476</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>友輝</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -20 千股)</t>
+          <t>📉 20d 巨變(減碼 -6,746 千股)</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>239553</v>
+        <v>1867075</v>
       </c>
       <c r="D77" t="n">
-        <v>1322188</v>
+        <v>-818035</v>
       </c>
       <c r="E77" t="n">
-        <v>211014</v>
+        <v>4001237</v>
       </c>
       <c r="F77" t="n">
-        <v>1342007</v>
+        <v>5928015</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>啟碁</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -40 千股)</t>
+          <t>📉 20d 巨變(減碼 -882 千股)</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-169000</v>
+        <v>45226</v>
       </c>
       <c r="D78" t="n">
-        <v>-928229</v>
+        <v>440352</v>
       </c>
       <c r="E78" t="n">
-        <v>-474752</v>
+        <v>239553</v>
       </c>
       <c r="F78" t="n">
-        <v>-888229</v>
+        <v>1322188</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>億泰</t>
+          <t>智易</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 238 千股)</t>
+          <t>📉 20d 巨變(減碼 -330 千股)</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>24048</v>
+        <v>-2143796</v>
       </c>
       <c r="D79" t="n">
-        <v>-117476</v>
+        <v>3887192</v>
       </c>
       <c r="E79" t="n">
-        <v>-25952</v>
+        <v>-2609088</v>
       </c>
       <c r="F79" t="n">
-        <v>-355456</v>
+        <v>4217340</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>原相</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -59 千股)</t>
+          <t>📈 20d 巨變(加碼 7,068 千股)</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>-2609088</v>
+        <v>-17332511</v>
       </c>
       <c r="D80" t="n">
-        <v>4217340</v>
+        <v>-51842609</v>
       </c>
       <c r="E80" t="n">
-        <v>-2464797</v>
+        <v>-34707479</v>
       </c>
       <c r="F80" t="n">
-        <v>4276282</v>
+        <v>-58910368</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 2,826 千股)</t>
+          <t>📈 20d 巨變(加碼 9 千股)</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>4001237</v>
+        <v>420803</v>
       </c>
       <c r="D81" t="n">
-        <v>5928015</v>
+        <v>800901</v>
       </c>
       <c r="E81" t="n">
-        <v>2564589</v>
+        <v>488536</v>
       </c>
       <c r="F81" t="n">
-        <v>3101857</v>
+        <v>791755</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>精測</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 287 千股)</t>
+          <t>📈 20d 巨變(加碼 13,928 千股)</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>488536</v>
+        <v>11104509</v>
       </c>
       <c r="D82" t="n">
-        <v>791755</v>
+        <v>-203749757</v>
       </c>
       <c r="E82" t="n">
-        <v>343519</v>
+        <v>3714243</v>
       </c>
       <c r="F82" t="n">
-        <v>505112</v>
+        <v>-217677992</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 219 千股)</t>
+          <t>📉 20d 巨變(減碼 -16 千股)</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>623883</v>
+        <v>-29914</v>
       </c>
       <c r="D83" t="n">
-        <v>-4464883</v>
+        <v>175834</v>
       </c>
       <c r="E83" t="n">
-        <v>-246893</v>
+        <v>-82000</v>
       </c>
       <c r="F83" t="n">
-        <v>-4684004</v>
+        <v>191669</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>東科-KY</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 542 千股)</t>
+          <t>📈 20d 巨變(加碼 39 千股)</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-34707479</v>
+        <v>210000</v>
       </c>
       <c r="D84" t="n">
-        <v>-58910368</v>
+        <v>-63662</v>
       </c>
       <c r="E84" t="n">
-        <v>-39841055</v>
+        <v>212000</v>
       </c>
       <c r="F84" t="n">
-        <v>-59452449</v>
+        <v>-102662</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>鑫龍騰</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 64 千股)</t>
+          <t>📉 20d 巨變(減碼 -64 千股)</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>-82000</v>
+        <v>-1837359</v>
       </c>
       <c r="D85" t="n">
-        <v>191669</v>
+        <v>-1883400</v>
       </c>
       <c r="E85" t="n">
-        <v>-160580</v>
+        <v>-2975316</v>
       </c>
       <c r="F85" t="n">
-        <v>127845</v>
+        <v>-1819443</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>全友</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -2,763 千股)</t>
+          <t>📈 20d 巨變(加碼 503 千股)</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>3714243</v>
+        <v>658671</v>
       </c>
       <c r="D86" t="n">
-        <v>-217677992</v>
+        <v>-3961623</v>
       </c>
       <c r="E86" t="n">
-        <v>-21099789</v>
+        <v>623883</v>
       </c>
       <c r="F86" t="n">
-        <v>-214914718</v>
+        <v>-4464883</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 106 千股)</t>
+          <t>📉 20d 巨變(減碼 -327 千股)</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>212000</v>
+        <v>-986921</v>
       </c>
       <c r="D87" t="n">
-        <v>-102662</v>
+        <v>-4891102</v>
       </c>
       <c r="E87" t="n">
-        <v>160000</v>
+        <v>-582642</v>
       </c>
       <c r="F87" t="n">
-        <v>-208662</v>
+        <v>-4564072</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>鑫龍騰</t>
+          <t>宏捷科</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,527 千股)</t>
+          <t>📉 20d 巨變(減碼 -188 千股)</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>-2975316</v>
+        <v>520676</v>
       </c>
       <c r="D88" t="n">
-        <v>-1819443</v>
+        <v>3581160</v>
       </c>
       <c r="E88" t="n">
-        <v>-1477571</v>
+        <v>785717</v>
       </c>
       <c r="F88" t="n">
-        <v>-292448</v>
+        <v>3769290</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>研華</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -880 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 16,312 千股)</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-582642</v>
+        <v>17714941</v>
       </c>
       <c r="D89" t="n">
-        <v>-4564072</v>
+        <v>-76878717</v>
       </c>
       <c r="E89" t="n">
-        <v>-1560486</v>
+        <v>-9386617</v>
       </c>
       <c r="F89" t="n">
-        <v>-3683884</v>
+        <v>-93190530</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -103 千股)</t>
+          <t>📈 20d 巨變(加碼 585 千股)</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>785717</v>
+        <v>313416</v>
       </c>
       <c r="D90" t="n">
-        <v>3769290</v>
+        <v>-3936900</v>
       </c>
       <c r="E90" t="n">
-        <v>797829</v>
+        <v>253995</v>
       </c>
       <c r="F90" t="n">
-        <v>3872431</v>
+        <v>-4521607</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>中保科</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -3,200 千股)</t>
+          <t>📈 20d 巨變(加碼 71 千股)</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>-9386617</v>
+        <v>-14746</v>
       </c>
       <c r="D91" t="n">
-        <v>-93190530</v>
+        <v>-91000</v>
       </c>
       <c r="E91" t="n">
-        <v>-20365313</v>
+        <v>-87788</v>
       </c>
       <c r="F91" t="n">
-        <v>-89990267</v>
+        <v>-162486</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>竹陞科技</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 675 千股)</t>
+          <t>📈 20d 巨變(加碼 69 千股)</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>253995</v>
+        <v>48090</v>
       </c>
       <c r="D92" t="n">
-        <v>-4521607</v>
+        <v>-190645</v>
       </c>
       <c r="E92" t="n">
-        <v>-136366</v>
+        <v>45040</v>
       </c>
       <c r="F92" t="n">
-        <v>-5196210</v>
+        <v>-259735</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>安碁資訊</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 10 千股)</t>
+          <t>📈 20d 巨變(加碼 49 千股)</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>-87788</v>
+        <v>-358251</v>
       </c>
       <c r="D93" t="n">
-        <v>-162486</v>
+        <v>6419854</v>
       </c>
       <c r="E93" t="n">
-        <v>-3529</v>
+        <v>-1555687</v>
       </c>
       <c r="F93" t="n">
-        <v>-172161</v>
+        <v>6371162</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>長榮航太</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 436 千股)</t>
+          <t>📉 20d 巨變(減碼 -36 千股)</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-1555687</v>
+        <v>-44764</v>
       </c>
       <c r="D94" t="n">
-        <v>6371162</v>
+        <v>75823</v>
       </c>
       <c r="E94" t="n">
-        <v>-288839</v>
+        <v>-65923</v>
       </c>
       <c r="F94" t="n">
-        <v>5934767</v>
+        <v>111664</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>六方科-KY</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 200 千股)</t>
+          <t>📈 20d 巨變(加碼 1,509 千股)</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>45040</v>
+        <v>-16968839</v>
       </c>
       <c r="D95" t="n">
-        <v>-259735</v>
+        <v>-296018253</v>
       </c>
       <c r="E95" t="n">
-        <v>54050</v>
+        <v>-1099054</v>
       </c>
       <c r="F95" t="n">
-        <v>-460065</v>
+        <v>-297527376</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 19 千股)</t>
+          <t>📈 20d 巨變(加碼 426 千股)</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>-65923</v>
+        <v>-3174311</v>
       </c>
       <c r="D96" t="n">
-        <v>111664</v>
+        <v>-4740613</v>
       </c>
       <c r="E96" t="n">
-        <v>-58923</v>
+        <v>-3616956</v>
       </c>
       <c r="F96" t="n">
-        <v>92664</v>
+        <v>-5166403</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>聯發科</t>
         </is>
       </c>
     </row>
@@ -8554,20 +8554,20 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -4,460 千股)</t>
+          <t>📈 20d 巨變(加碼 3,997 千股)</t>
         </is>
       </c>
       <c r="C97" t="n">
+        <v>17327640</v>
+      </c>
+      <c r="D97" t="n">
+        <v>-153926493</v>
+      </c>
+      <c r="E97" t="n">
         <v>6681300</v>
       </c>
-      <c r="D97" t="n">
+      <c r="F97" t="n">
         <v>-157923879</v>
-      </c>
-      <c r="E97" t="n">
-        <v>-1831280</v>
-      </c>
-      <c r="F97" t="n">
-        <v>-153463886</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -8578,230 +8578,172 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -20,159 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 416 千股)</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-1099054</v>
+        <v>53602</v>
       </c>
       <c r="D98" t="n">
-        <v>-297527376</v>
+        <v>-3193884</v>
       </c>
       <c r="E98" t="n">
-        <v>-9393707</v>
+        <v>-53338</v>
       </c>
       <c r="F98" t="n">
-        <v>-277368453</v>
+        <v>-3609777</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>創意</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -2,772 千股)</t>
+          <t>📈 20d 巨變(加碼 73 千股)</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>-3616956</v>
+        <v>-325101</v>
       </c>
       <c r="D99" t="n">
-        <v>-5166403</v>
+        <v>-4165027</v>
       </c>
       <c r="E99" t="n">
-        <v>-2093865</v>
+        <v>-589851</v>
       </c>
       <c r="F99" t="n">
-        <v>-2394845</v>
+        <v>-4238184</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>緯穎</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 360 千股)</t>
+          <t>📉 20d 巨變(減碼 -22 千股)</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>-53338</v>
+        <v>144843</v>
       </c>
       <c r="D100" t="n">
-        <v>-3609777</v>
+        <v>226387</v>
       </c>
       <c r="E100" t="n">
-        <v>38681</v>
+        <v>116286</v>
       </c>
       <c r="F100" t="n">
-        <v>-3969741</v>
+        <v>248361</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>信驊</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 124 千股)</t>
+          <t>📈 20d 巨變(加碼 288 千股)</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-589851</v>
+        <v>5737633</v>
       </c>
       <c r="D101" t="n">
-        <v>-4238184</v>
+        <v>8531429</v>
       </c>
       <c r="E101" t="n">
-        <v>-419324</v>
+        <v>5540643</v>
       </c>
       <c r="F101" t="n">
-        <v>-4362453</v>
+        <v>8243644</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>金像電</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -71 千股)</t>
+          <t>📉 20d 巨變(減碼 -823 千股)</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>116286</v>
+        <v>-1164682</v>
       </c>
       <c r="D102" t="n">
-        <v>248361</v>
+        <v>-1533001</v>
       </c>
       <c r="E102" t="n">
-        <v>89745</v>
+        <v>-1386511</v>
       </c>
       <c r="F102" t="n">
-        <v>319568</v>
+        <v>-709790</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>高技</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 85 千股)</t>
+          <t>📈 20d 巨變(加碼 130 千股)</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>5540643</v>
+        <v>296376</v>
       </c>
       <c r="D103" t="n">
-        <v>8243644</v>
+        <v>284240</v>
       </c>
       <c r="E103" t="n">
-        <v>5319599</v>
+        <v>892877</v>
       </c>
       <c r="F103" t="n">
-        <v>8159133</v>
+        <v>153911</v>
       </c>
       <c r="G103" t="inlineStr">
-        <is>
-          <t>金像電</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>5439</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -1,625 千股)</t>
-        </is>
-      </c>
-      <c r="C104" t="n">
-        <v>-1386511</v>
-      </c>
-      <c r="D104" t="n">
-        <v>-709790</v>
-      </c>
-      <c r="E104" t="n">
-        <v>-1300882</v>
-      </c>
-      <c r="F104" t="n">
-        <v>915593</v>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>高技</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>6187</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 185 千股)</t>
-        </is>
-      </c>
-      <c r="C105" t="n">
-        <v>892877</v>
-      </c>
-      <c r="D105" t="n">
-        <v>153911</v>
-      </c>
-      <c r="E105" t="n">
-        <v>296332</v>
-      </c>
-      <c r="F105" t="n">
-        <v>-31353</v>
-      </c>
-      <c r="G105" t="inlineStr">
         <is>
           <t>萬潤</t>
         </is>

--- a/data/台股_外資雷達.xlsx
+++ b/data/台股_外資雷達.xlsx
@@ -496,22 +496,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>169391</v>
+        <v>152009</v>
       </c>
       <c r="D2" t="n">
-        <v>253317</v>
+        <v>259419</v>
       </c>
       <c r="E2" t="n">
-        <v>162256</v>
+        <v>176385</v>
       </c>
       <c r="F2" t="n">
-        <v>-15395</v>
+        <v>-23867</v>
       </c>
       <c r="G2" t="n">
-        <v>30900</v>
+        <v>24304</v>
       </c>
       <c r="H2" t="n">
-        <v>844</v>
+        <v>2645</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -547,22 +547,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2422</v>
+        <v>-5173</v>
       </c>
       <c r="D3" t="n">
-        <v>37228</v>
+        <v>23856</v>
       </c>
       <c r="E3" t="n">
-        <v>123142</v>
+        <v>104114</v>
       </c>
       <c r="F3" t="n">
-        <v>-3099</v>
+        <v>-5513</v>
       </c>
       <c r="G3" t="n">
-        <v>-32994</v>
+        <v>-31177</v>
       </c>
       <c r="H3" t="n">
-        <v>2927</v>
+        <v>3249</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -589,31 +589,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-3755</v>
+        <v>46768</v>
       </c>
       <c r="D4" t="n">
-        <v>36837</v>
+        <v>12451</v>
       </c>
       <c r="E4" t="n">
-        <v>2227</v>
+        <v>52791</v>
       </c>
       <c r="F4" t="n">
-        <v>7466</v>
+        <v>-7742</v>
       </c>
       <c r="G4" t="n">
-        <v>-32407</v>
+        <v>31048</v>
       </c>
       <c r="H4" t="n">
-        <v>3940</v>
+        <v>2642</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -622,139 +622,139 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>🐌 龜速*</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5738</v>
+        <v>-14797</v>
       </c>
       <c r="D5" t="n">
-        <v>8531</v>
+        <v>11731</v>
       </c>
       <c r="E5" t="n">
-        <v>13046</v>
+        <v>-9890</v>
       </c>
       <c r="F5" t="n">
-        <v>-4698</v>
+        <v>3081</v>
       </c>
       <c r="G5" t="n">
-        <v>-11108</v>
+        <v>-23942</v>
       </c>
       <c r="H5" t="n">
-        <v>-562</v>
+        <v>2302</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>🟢 加碼</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+          <t>🚀 大買</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>68</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>🐌 龜速*</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-358</v>
+        <v>4873</v>
       </c>
       <c r="D6" t="n">
-        <v>6420</v>
+        <v>10426</v>
       </c>
       <c r="E6" t="n">
-        <v>10788</v>
+        <v>13502</v>
       </c>
       <c r="F6" t="n">
-        <v>-498</v>
+        <v>-2307</v>
       </c>
       <c r="G6" t="n">
-        <v>-1047</v>
+        <v>-11406</v>
       </c>
       <c r="H6" t="n">
-        <v>558</v>
+        <v>-609</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>🟢 加碼</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>79</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>✈️ 高飛*</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>3</v>
-      </c>
+          <t>🚀 大買</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>長榮航太</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1581</v>
+        <v>1255</v>
       </c>
       <c r="D7" t="n">
-        <v>3994</v>
+        <v>8860</v>
       </c>
       <c r="E7" t="n">
-        <v>2268</v>
+        <v>12521</v>
       </c>
       <c r="F7" t="n">
-        <v>-1</v>
+        <v>-853</v>
       </c>
       <c r="G7" t="n">
-        <v>-124</v>
+        <v>-1277</v>
       </c>
       <c r="H7" t="n">
-        <v>-737</v>
+        <v>579</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -763,49 +763,49 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-2144</v>
+        <v>5374</v>
       </c>
       <c r="D8" t="n">
-        <v>3887</v>
+        <v>5720</v>
       </c>
       <c r="E8" t="n">
-        <v>7289</v>
+        <v>-2774</v>
       </c>
       <c r="F8" t="n">
-        <v>-890</v>
+        <v>-1464</v>
       </c>
       <c r="G8" t="n">
-        <v>3896</v>
+        <v>-6257</v>
       </c>
       <c r="H8" t="n">
-        <v>-145</v>
+        <v>-240</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -818,11 +818,11 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M8" t="n">
@@ -832,31 +832,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>零壹</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>1888</v>
       </c>
       <c r="D9" t="n">
-        <v>3613</v>
+        <v>4545</v>
       </c>
       <c r="E9" t="n">
-        <v>9547</v>
+        <v>3709</v>
       </c>
       <c r="F9" t="n">
-        <v>-93</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>-3271</v>
+        <v>-119</v>
       </c>
       <c r="H9" t="n">
-        <v>70</v>
+        <v>-737</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -869,11 +869,11 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M9" t="n">
@@ -883,31 +883,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>521</v>
+        <v>6288</v>
       </c>
       <c r="D10" t="n">
-        <v>3581</v>
+        <v>4011</v>
       </c>
       <c r="E10" t="n">
-        <v>14987</v>
+        <v>965</v>
       </c>
       <c r="F10" t="n">
-        <v>372</v>
+        <v>-3354</v>
       </c>
       <c r="G10" t="n">
-        <v>1069</v>
+        <v>-436</v>
       </c>
       <c r="H10" t="n">
-        <v>301</v>
+        <v>-752</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -916,49 +916,49 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>691</v>
+        <v>2350</v>
       </c>
       <c r="D11" t="n">
-        <v>3104</v>
+        <v>3945</v>
       </c>
       <c r="E11" t="n">
-        <v>3589</v>
+        <v>-57812</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>2176</v>
       </c>
       <c r="G11" t="n">
-        <v>135</v>
+        <v>6146</v>
       </c>
       <c r="H11" t="n">
-        <v>25</v>
+        <v>-143</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -967,11 +967,11 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -979,37 +979,37 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3984</v>
+        <v>-830</v>
       </c>
       <c r="D12" t="n">
-        <v>2947</v>
+        <v>3417</v>
       </c>
       <c r="E12" t="n">
-        <v>-1464</v>
+        <v>10696</v>
       </c>
       <c r="F12" t="n">
-        <v>-3325</v>
+        <v>869</v>
       </c>
       <c r="G12" t="n">
-        <v>133</v>
+        <v>1668</v>
       </c>
       <c r="H12" t="n">
-        <v>-786</v>
+        <v>292</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1018,49 +1018,49 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>漢科</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2790</v>
+        <v>791</v>
       </c>
       <c r="D13" t="n">
-        <v>2700</v>
+        <v>3221</v>
       </c>
       <c r="E13" t="n">
-        <v>-5219</v>
+        <v>3847</v>
       </c>
       <c r="F13" t="n">
-        <v>-1540</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>-6662</v>
+        <v>135</v>
       </c>
       <c r="H13" t="n">
-        <v>-262</v>
+        <v>25</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1073,45 +1073,45 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>原相</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>215</v>
+        <v>-2140</v>
       </c>
       <c r="D14" t="n">
-        <v>2461</v>
+        <v>3076</v>
       </c>
       <c r="E14" t="n">
-        <v>12486</v>
+        <v>5819</v>
       </c>
       <c r="F14" t="n">
-        <v>-729</v>
+        <v>-1358</v>
       </c>
       <c r="G14" t="n">
-        <v>-10507</v>
+        <v>3390</v>
       </c>
       <c r="H14" t="n">
-        <v>-304</v>
+        <v>-261</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1120,11 +1120,11 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1132,37 +1132,37 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-36</v>
+        <v>-1323</v>
       </c>
       <c r="D15" t="n">
-        <v>2273</v>
+        <v>2418</v>
       </c>
       <c r="E15" t="n">
-        <v>3638</v>
+        <v>9819</v>
       </c>
       <c r="F15" t="n">
-        <v>-248</v>
+        <v>750</v>
       </c>
       <c r="G15" t="n">
-        <v>-1704</v>
+        <v>-2578</v>
       </c>
       <c r="H15" t="n">
-        <v>-123</v>
+        <v>173</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1175,45 +1175,45 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>立隆電</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1809</v>
+        <v>5588</v>
       </c>
       <c r="D16" t="n">
-        <v>2197</v>
+        <v>2154</v>
       </c>
       <c r="E16" t="n">
-        <v>2225</v>
+        <v>-7795</v>
       </c>
       <c r="F16" t="n">
-        <v>-933</v>
+        <v>-1114</v>
       </c>
       <c r="G16" t="n">
-        <v>-898</v>
+        <v>7878</v>
       </c>
       <c r="H16" t="n">
-        <v>60</v>
+        <v>-568</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1222,15 +1222,15 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M16" t="n">
@@ -1249,26 +1249,26 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>173</v>
+        <v>-45</v>
       </c>
       <c r="D17" t="n">
-        <v>2163</v>
+        <v>1940</v>
       </c>
       <c r="E17" t="n">
-        <v>1240</v>
+        <v>929</v>
       </c>
       <c r="F17" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H17" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>🟢 加碼</t>
+          <t>🟡 中性</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1291,32 +1291,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>448</v>
+        <v>-243</v>
       </c>
       <c r="D18" t="n">
-        <v>1991</v>
+        <v>1862</v>
       </c>
       <c r="E18" t="n">
-        <v>-1224</v>
+        <v>4359</v>
       </c>
       <c r="F18" t="n">
+        <v>-116</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-2850</v>
+      </c>
+      <c r="H18" t="n">
         <v>59</v>
       </c>
-      <c r="G18" t="n">
-        <v>-1080</v>
-      </c>
-      <c r="H18" t="n">
-        <v>43</v>
-      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>🟡 中性</t>
@@ -1328,45 +1328,45 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1051</v>
+        <v>1090</v>
       </c>
       <c r="D19" t="n">
-        <v>1925</v>
+        <v>1842</v>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>2901</v>
       </c>
       <c r="F19" t="n">
-        <v>-533</v>
+        <v>-372</v>
       </c>
       <c r="G19" t="n">
-        <v>-706</v>
+        <v>-1086</v>
       </c>
       <c r="H19" t="n">
-        <v>15</v>
+        <v>-105</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1379,45 +1379,45 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>806</v>
+        <v>16</v>
       </c>
       <c r="D20" t="n">
-        <v>1735</v>
+        <v>1830</v>
       </c>
       <c r="E20" t="n">
-        <v>2409</v>
+        <v>-1242</v>
       </c>
       <c r="F20" t="n">
-        <v>-485</v>
+        <v>292</v>
       </c>
       <c r="G20" t="n">
-        <v>171</v>
+        <v>-1011</v>
       </c>
       <c r="H20" t="n">
-        <v>-118</v>
+        <v>32</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1430,45 +1430,45 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>438</v>
+        <v>2606</v>
       </c>
       <c r="D21" t="n">
-        <v>1442</v>
+        <v>1578</v>
       </c>
       <c r="E21" t="n">
-        <v>3226</v>
+        <v>-293</v>
       </c>
       <c r="F21" t="n">
-        <v>33</v>
+        <v>-91</v>
       </c>
       <c r="G21" t="n">
-        <v>466</v>
+        <v>-270</v>
       </c>
       <c r="H21" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1477,15 +1477,15 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M21" t="n">
@@ -1504,22 +1504,22 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-889</v>
+        <v>232</v>
       </c>
       <c r="D22" t="n">
-        <v>1196</v>
+        <v>1422</v>
       </c>
       <c r="E22" t="n">
-        <v>1114</v>
+        <v>2665</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>-142</v>
       </c>
       <c r="G22" t="n">
-        <v>-2414</v>
+        <v>-1776</v>
       </c>
       <c r="H22" t="n">
-        <v>-98</v>
+        <v>-236</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1546,82 +1546,82 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>勝一</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>512</v>
+        <v>456</v>
       </c>
       <c r="D23" t="n">
-        <v>1019</v>
+        <v>1337</v>
       </c>
       <c r="E23" t="n">
-        <v>1948</v>
+        <v>1376</v>
       </c>
       <c r="F23" t="n">
-        <v>-6</v>
+        <v>-566</v>
       </c>
       <c r="G23" t="n">
+        <v>-737</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-81</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>91</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>✈️ 高飛</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
         <v>2</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-0</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>71</v>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>📉 減速</t>
-        </is>
-      </c>
-      <c r="M23" t="n">
-        <v>-3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>65</v>
+        <v>449</v>
       </c>
       <c r="D24" t="n">
-        <v>920</v>
+        <v>1324</v>
       </c>
       <c r="E24" t="n">
-        <v>-3236</v>
+        <v>3387</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>544</v>
       </c>
       <c r="H24" t="n">
-        <v>-203</v>
+        <v>-12</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1630,49 +1630,49 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>421</v>
+        <v>367</v>
       </c>
       <c r="D25" t="n">
-        <v>801</v>
+        <v>1242</v>
       </c>
       <c r="E25" t="n">
-        <v>362</v>
+        <v>11250</v>
       </c>
       <c r="F25" t="n">
-        <v>-103</v>
+        <v>-1048</v>
       </c>
       <c r="G25" t="n">
-        <v>-1408</v>
+        <v>-10424</v>
       </c>
       <c r="H25" t="n">
-        <v>-125</v>
+        <v>-100</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1681,11 +1681,11 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1693,37 +1693,37 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>智易</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>510</v>
+        <v>-47</v>
       </c>
       <c r="D26" t="n">
-        <v>629</v>
+        <v>832</v>
       </c>
       <c r="E26" t="n">
-        <v>-1258</v>
+        <v>7280</v>
       </c>
       <c r="F26" t="n">
-        <v>283</v>
+        <v>12</v>
       </c>
       <c r="G26" t="n">
-        <v>2463</v>
+        <v>4507</v>
       </c>
       <c r="H26" t="n">
-        <v>-79</v>
+        <v>-123</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1732,49 +1732,49 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-2266</v>
+        <v>416</v>
       </c>
       <c r="D27" t="n">
-        <v>593</v>
+        <v>707</v>
       </c>
       <c r="E27" t="n">
-        <v>12884</v>
+        <v>450</v>
       </c>
       <c r="F27" t="n">
-        <v>9</v>
+        <v>-42</v>
       </c>
       <c r="G27" t="n">
-        <v>1216</v>
+        <v>-1337</v>
       </c>
       <c r="H27" t="n">
-        <v>-41</v>
+        <v>-62</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1791,41 +1791,41 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>🚀 加速器*</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>勝一</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1037</v>
+        <v>453</v>
       </c>
       <c r="D28" t="n">
-        <v>570</v>
+        <v>630</v>
       </c>
       <c r="E28" t="n">
-        <v>193</v>
+        <v>1354</v>
       </c>
       <c r="F28" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="G28" t="n">
-        <v>-2</v>
+        <v>9</v>
       </c>
       <c r="H28" t="n">
-        <v>20</v>
+        <v>-11</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1834,11 +1834,11 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1852,31 +1852,31 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>45</v>
+        <v>-84</v>
       </c>
       <c r="D29" t="n">
-        <v>440</v>
+        <v>531</v>
       </c>
       <c r="E29" t="n">
-        <v>7187</v>
+        <v>1746</v>
       </c>
       <c r="F29" t="n">
-        <v>17</v>
+        <v>-426</v>
       </c>
       <c r="G29" t="n">
-        <v>4837</v>
+        <v>202</v>
       </c>
       <c r="H29" t="n">
-        <v>-89</v>
+        <v>-196</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1885,49 +1885,49 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1031</v>
+        <v>595</v>
       </c>
       <c r="D30" t="n">
-        <v>429</v>
+        <v>460</v>
       </c>
       <c r="E30" t="n">
-        <v>-1084</v>
+        <v>-1544</v>
       </c>
       <c r="F30" t="n">
-        <v>-139</v>
+        <v>390</v>
       </c>
       <c r="G30" t="n">
-        <v>-910</v>
+        <v>2578</v>
       </c>
       <c r="H30" t="n">
-        <v>-166</v>
+        <v>-134</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1936,100 +1936,100 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M30" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>98</v>
+        <v>709</v>
       </c>
       <c r="D31" t="n">
-        <v>372</v>
+        <v>448</v>
       </c>
       <c r="E31" t="n">
-        <v>602</v>
+        <v>356</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>-755</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>-795</v>
       </c>
       <c r="H31" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>84</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>✈️ 高飛*</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
         <v>2</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K31" t="n">
-        <v>91</v>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>🐌 龜速</t>
-        </is>
-      </c>
-      <c r="M31" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>崇友</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2733</v>
+        <v>137</v>
       </c>
       <c r="D32" t="n">
-        <v>367</v>
+        <v>395</v>
       </c>
       <c r="E32" t="n">
-        <v>-9853</v>
+        <v>588</v>
       </c>
       <c r="F32" t="n">
-        <v>702</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>9264</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-249</v>
+        <v>2</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2038,11 +2038,11 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2050,37 +2050,37 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-1179</v>
+        <v>1184</v>
       </c>
       <c r="D33" t="n">
-        <v>357</v>
+        <v>307</v>
       </c>
       <c r="E33" t="n">
-        <v>-7467</v>
+        <v>-4315</v>
       </c>
       <c r="F33" t="n">
-        <v>-470</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>1750</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-128</v>
+        <v>-57</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2101,37 +2101,37 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>湧德</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>868</v>
+        <v>-1088</v>
       </c>
       <c r="D34" t="n">
-        <v>311</v>
+        <v>275</v>
       </c>
       <c r="E34" t="n">
-        <v>-6715</v>
+        <v>-3759</v>
       </c>
       <c r="F34" t="n">
-        <v>-334</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>-3158</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>2</v>
+        <v>-274</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2144,174 +2144,186 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M34" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>296</v>
+        <v>-462</v>
       </c>
       <c r="D35" t="n">
-        <v>284</v>
+        <v>212</v>
       </c>
       <c r="E35" t="n">
-        <v>-5705</v>
+        <v>13497</v>
       </c>
       <c r="F35" t="n">
-        <v>586</v>
+        <v>32</v>
       </c>
       <c r="G35" t="n">
-        <v>-1289</v>
+        <v>1122</v>
       </c>
       <c r="H35" t="n">
-        <v>-156</v>
+        <v>-61</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>66</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>🚀 加速器*</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>54</v>
+        <v>97</v>
       </c>
       <c r="D36" t="n">
-        <v>243</v>
+        <v>194</v>
       </c>
       <c r="E36" t="n">
-        <v>1191</v>
+        <v>757</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G36" t="n">
-        <v>6</v>
+        <v>-350</v>
       </c>
       <c r="H36" t="n">
-        <v>-23</v>
+        <v>-17</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K36" t="n">
-        <v>77</v>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>🐌 龜速</t>
-        </is>
-      </c>
-      <c r="M36" t="n">
-        <v>-2</v>
-      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>友輝</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>145</v>
+        <v>14</v>
       </c>
       <c r="D37" t="n">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="E37" t="n">
-        <v>804</v>
+        <v>1274</v>
       </c>
       <c r="F37" t="n">
-        <v>-115</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>-404</v>
+        <v>6</v>
       </c>
       <c r="H37" t="n">
-        <v>-20</v>
+        <v>-22</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>77</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3420</v>
+        <v>794</v>
       </c>
       <c r="D38" t="n">
-        <v>189</v>
+        <v>118</v>
       </c>
       <c r="E38" t="n">
-        <v>-57935</v>
+        <v>-1071</v>
       </c>
       <c r="F38" t="n">
-        <v>796</v>
+        <v>-136</v>
       </c>
       <c r="G38" t="n">
-        <v>5461</v>
+        <v>-901</v>
       </c>
       <c r="H38" t="n">
-        <v>-91</v>
+        <v>-179</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2320,40 +2332,40 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M38" t="n">
-        <v>-4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>智冠</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-30</v>
+        <v>-110</v>
       </c>
       <c r="D39" t="n">
-        <v>176</v>
+        <v>114</v>
       </c>
       <c r="E39" t="n">
-        <v>-111</v>
+        <v>418</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -2362,58 +2374,58 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
+        <v>-32</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>80</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
         <v>-2</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K39" t="n">
-        <v>78</v>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>📉 減速</t>
-        </is>
-      </c>
-      <c r="M39" t="n">
-        <v>-3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2043</v>
+        <v>889</v>
       </c>
       <c r="D40" t="n">
-        <v>108</v>
+        <v>66</v>
       </c>
       <c r="E40" t="n">
-        <v>-1754</v>
+        <v>-6943</v>
       </c>
       <c r="F40" t="n">
-        <v>-4</v>
+        <v>-301</v>
       </c>
       <c r="G40" t="n">
-        <v>-423</v>
+        <v>-2737</v>
       </c>
       <c r="H40" t="n">
-        <v>20</v>
+        <v>-19</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2426,45 +2438,45 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M40" t="n">
-        <v>-4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>達欣工</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>312</v>
+        <v>-69</v>
       </c>
       <c r="D41" t="n">
-        <v>105</v>
+        <v>38</v>
       </c>
       <c r="E41" t="n">
-        <v>-62</v>
+        <v>1181</v>
       </c>
       <c r="F41" t="n">
-        <v>-399</v>
+        <v>3</v>
       </c>
       <c r="G41" t="n">
-        <v>-466</v>
+        <v>5</v>
       </c>
       <c r="H41" t="n">
-        <v>-27</v>
+        <v>-78</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2473,19 +2485,19 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M41" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="42">
@@ -2500,13 +2512,13 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-45</v>
+        <v>-26</v>
       </c>
       <c r="D42" t="n">
-        <v>76</v>
+        <v>12</v>
       </c>
       <c r="E42" t="n">
-        <v>-65</v>
+        <v>-48</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -2515,7 +2527,7 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2542,22 +2554,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>智冠</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-84</v>
+        <v>-146</v>
       </c>
       <c r="D43" t="n">
-        <v>56</v>
+        <v>-8</v>
       </c>
       <c r="E43" t="n">
-        <v>442</v>
+        <v>-291</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -2566,7 +2578,7 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>-32</v>
+        <v>-4</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2575,49 +2587,49 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M43" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>方土霖</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-21</v>
+        <v>-7</v>
       </c>
       <c r="D44" t="n">
-        <v>-4</v>
+        <v>-9</v>
       </c>
       <c r="E44" t="n">
-        <v>1186</v>
+        <v>-78</v>
       </c>
       <c r="F44" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>-93</v>
+        <v>-5</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2626,49 +2638,49 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M44" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>方土霖</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-6</v>
+        <v>-1332</v>
       </c>
       <c r="D45" t="n">
-        <v>-11</v>
+        <v>-44</v>
       </c>
       <c r="E45" t="n">
-        <v>-80</v>
+        <v>-6737</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>-189</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>2456</v>
       </c>
       <c r="H45" t="n">
-        <v>-5</v>
+        <v>-174</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2681,36 +2693,36 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M45" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>鑫龍騰</t>
+          <t>大車隊</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>210</v>
+        <v>-9</v>
       </c>
       <c r="D46" t="n">
-        <v>-64</v>
+        <v>-52</v>
       </c>
       <c r="E46" t="n">
-        <v>-2702</v>
+        <v>-278</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -2719,7 +2731,7 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>-0</v>
+        <v>52</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2728,49 +2740,49 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>大車隊</t>
+          <t>大統益</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-15</v>
+        <v>299</v>
       </c>
       <c r="D47" t="n">
-        <v>-71</v>
+        <v>-57</v>
       </c>
       <c r="E47" t="n">
-        <v>-299</v>
+        <v>-506</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H47" t="n">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2783,15 +2795,15 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M47" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="48">
@@ -2806,13 +2818,13 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-15</v>
+        <v>27</v>
       </c>
       <c r="D48" t="n">
-        <v>-91</v>
+        <v>-69</v>
       </c>
       <c r="E48" t="n">
-        <v>-83</v>
+        <v>-191</v>
       </c>
       <c r="F48" t="n">
         <v>11</v>
@@ -2821,7 +2833,7 @@
         <v>11</v>
       </c>
       <c r="H48" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2848,22 +2860,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>聯合</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>694</v>
+        <v>-61</v>
       </c>
       <c r="D49" t="n">
-        <v>-149</v>
+        <v>-167</v>
       </c>
       <c r="E49" t="n">
-        <v>-4469</v>
+        <v>-2991</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -2872,7 +2884,7 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-33</v>
+        <v>86</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2885,7 +2897,7 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -2899,31 +2911,31 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>聯合</t>
+          <t>全友</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-16</v>
+        <v>84</v>
       </c>
       <c r="D50" t="n">
-        <v>-159</v>
+        <v>-173</v>
       </c>
       <c r="E50" t="n">
-        <v>-2986</v>
+        <v>4923</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H50" t="n">
-        <v>86</v>
+        <v>7</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2932,19 +2944,19 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -2959,22 +2971,22 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>35</v>
+        <v>248</v>
       </c>
       <c r="D51" t="n">
-        <v>-181</v>
+        <v>-206</v>
       </c>
       <c r="E51" t="n">
-        <v>-956</v>
+        <v>-744</v>
       </c>
       <c r="F51" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="H51" t="n">
-        <v>-8</v>
+        <v>-11</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3010,13 +3022,13 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>48</v>
+        <v>-33</v>
       </c>
       <c r="D52" t="n">
-        <v>-191</v>
+        <v>-217</v>
       </c>
       <c r="E52" t="n">
-        <v>-223</v>
+        <v>-320</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -3052,22 +3064,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>鑫龍騰</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>126</v>
+        <v>-62</v>
       </c>
       <c r="D53" t="n">
-        <v>-291</v>
+        <v>-403</v>
       </c>
       <c r="E53" t="n">
-        <v>-153</v>
+        <v>-2675</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -3076,7 +3088,7 @@
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-71</v>
+        <v>-0</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3089,7 +3101,7 @@
         </is>
       </c>
       <c r="K53" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3103,82 +3115,70 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>合機</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-1184</v>
+        <v>-870</v>
       </c>
       <c r="D54" t="n">
-        <v>-473</v>
+        <v>-411</v>
       </c>
       <c r="E54" t="n">
-        <v>1909</v>
+        <v>-4121</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>-1272</v>
       </c>
       <c r="H54" t="n">
-        <v>-52</v>
+        <v>-153</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K54" t="n">
-        <v>84</v>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>🛬 穩定</t>
-        </is>
-      </c>
-      <c r="M54" t="n">
-        <v>-2</v>
-      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>信立</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>-118</v>
+        <v>44</v>
       </c>
       <c r="D55" t="n">
-        <v>-481</v>
+        <v>-417</v>
       </c>
       <c r="E55" t="n">
-        <v>-3004</v>
+        <v>-19</v>
       </c>
       <c r="F55" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>-110</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-127</v>
+        <v>-71</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3187,15 +3187,15 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K55" t="n">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M55" t="n">
@@ -3205,31 +3205,31 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-493</v>
+        <v>-13</v>
       </c>
       <c r="D56" t="n">
-        <v>-481</v>
+        <v>-433</v>
       </c>
       <c r="E56" t="n">
-        <v>-126</v>
+        <v>-2410</v>
       </c>
       <c r="F56" t="n">
-        <v>387</v>
+        <v>2</v>
       </c>
       <c r="G56" t="n">
-        <v>606</v>
+        <v>-110</v>
       </c>
       <c r="H56" t="n">
-        <v>-6</v>
+        <v>-175</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3246,41 +3246,41 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M56" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>寶雅</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>-110</v>
+        <v>-140</v>
       </c>
       <c r="D57" t="n">
-        <v>-636</v>
+        <v>-444</v>
       </c>
       <c r="E57" t="n">
-        <v>-1930</v>
+        <v>511</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>-386</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3289,49 +3289,49 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K57" t="n">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M57" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-464</v>
+        <v>629</v>
       </c>
       <c r="D58" t="n">
-        <v>-740</v>
+        <v>-539</v>
       </c>
       <c r="E58" t="n">
-        <v>4393</v>
+        <v>-3107</v>
       </c>
       <c r="F58" t="n">
-        <v>282</v>
+        <v>-640</v>
       </c>
       <c r="G58" t="n">
-        <v>461</v>
+        <v>-15</v>
       </c>
       <c r="H58" t="n">
-        <v>259</v>
+        <v>-547</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3340,49 +3340,49 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K58" t="n">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M58" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1867</v>
+        <v>-330</v>
       </c>
       <c r="D59" t="n">
-        <v>-818</v>
+        <v>-551</v>
       </c>
       <c r="E59" t="n">
-        <v>26523</v>
+        <v>-218</v>
       </c>
       <c r="F59" t="n">
-        <v>-2154</v>
+        <v>273</v>
       </c>
       <c r="G59" t="n">
-        <v>-6539</v>
+        <v>657</v>
       </c>
       <c r="H59" t="n">
-        <v>-225</v>
+        <v>26</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3391,49 +3391,49 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K59" t="n">
-        <v>63</v>
+        <v>96</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M59" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>-374</v>
+        <v>-4147</v>
       </c>
       <c r="D60" t="n">
-        <v>-873</v>
+        <v>-569</v>
       </c>
       <c r="E60" t="n">
-        <v>2261</v>
+        <v>-13189</v>
       </c>
       <c r="F60" t="n">
-        <v>188</v>
+        <v>-1</v>
       </c>
       <c r="G60" t="n">
-        <v>239</v>
+        <v>-4</v>
       </c>
       <c r="H60" t="n">
-        <v>-132</v>
+        <v>-147</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3442,49 +3442,49 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K60" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M60" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>合機</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>56952</v>
+        <v>-770</v>
       </c>
       <c r="D61" t="n">
-        <v>-878</v>
+        <v>-586</v>
       </c>
       <c r="E61" t="n">
-        <v>40388</v>
+        <v>1705</v>
       </c>
       <c r="F61" t="n">
-        <v>-2813</v>
+        <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>35567</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>1039</v>
+        <v>-72</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3497,36 +3497,36 @@
         </is>
       </c>
       <c r="K61" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M61" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>德昌</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-1101</v>
+        <v>-128</v>
       </c>
       <c r="D62" t="n">
-        <v>-883</v>
+        <v>-659</v>
       </c>
       <c r="E62" t="n">
-        <v>-501</v>
+        <v>-2068</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -3535,7 +3535,7 @@
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-19</v>
+        <v>-12</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3548,15 +3548,15 @@
         </is>
       </c>
       <c r="K62" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M62" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="63">
@@ -3571,22 +3571,22 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-386</v>
+        <v>-424</v>
       </c>
       <c r="D63" t="n">
-        <v>-900</v>
+        <v>-795</v>
       </c>
       <c r="E63" t="n">
-        <v>-1515</v>
+        <v>-1190</v>
       </c>
       <c r="F63" t="n">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="G63" t="n">
-        <v>940</v>
+        <v>1009</v>
       </c>
       <c r="H63" t="n">
-        <v>-51</v>
+        <v>-30</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3613,31 +3613,31 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>億泰</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>-5166</v>
+        <v>-144</v>
       </c>
       <c r="D64" t="n">
-        <v>-961</v>
+        <v>-895</v>
       </c>
       <c r="E64" t="n">
-        <v>-13349</v>
+        <v>-2968</v>
       </c>
       <c r="F64" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-119</v>
+        <v>-248</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         </is>
       </c>
       <c r="K64" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -3664,22 +3664,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>德昌</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>124</v>
+        <v>-398</v>
       </c>
       <c r="D65" t="n">
-        <v>-978</v>
+        <v>-910</v>
       </c>
       <c r="E65" t="n">
-        <v>2237</v>
+        <v>-343</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -3688,7 +3688,7 @@
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>150</v>
+        <v>-15</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3701,11 +3701,11 @@
         </is>
       </c>
       <c r="K65" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M65" t="n">
@@ -3715,22 +3715,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>億泰</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-55</v>
+        <v>119</v>
       </c>
       <c r="D66" t="n">
-        <v>-980</v>
+        <v>-1008</v>
       </c>
       <c r="E66" t="n">
-        <v>-2721</v>
+        <v>2259</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
@@ -3739,7 +3739,7 @@
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-249</v>
+        <v>48</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3752,45 +3752,45 @@
         </is>
       </c>
       <c r="K66" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M66" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>寶雅</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-735</v>
+        <v>-592</v>
       </c>
       <c r="D67" t="n">
-        <v>-1040</v>
+        <v>-1058</v>
       </c>
       <c r="E67" t="n">
-        <v>-108</v>
+        <v>566</v>
       </c>
       <c r="F67" t="n">
-        <v>35</v>
+        <v>23